--- a/data/trade_tracker_results.xlsx
+++ b/data/trade_tracker_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,80 +493,78 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11028</v>
+        <v>7258</v>
       </c>
       <c r="C2" t="n">
-        <v>10922</v>
+        <v>7174.5</v>
       </c>
       <c r="D2" t="n">
-        <v>11074</v>
+        <v>7334</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.37% (152.0)</t>
+          <t>2.17% (159.5)</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11226</v>
+        <v>7493.5</v>
       </c>
       <c r="G2" t="n">
-        <v>11378</v>
+        <v>7653</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-11 13:45</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ENTRY EXPIRED (Week End)</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-11 15:00 (Week End)</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>11134</v>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>0.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>235.84</v>
+        <v>11028</v>
       </c>
       <c r="C3" t="n">
-        <v>234.06</v>
+        <v>10922</v>
       </c>
       <c r="D3" t="n">
-        <v>236.11</v>
+        <v>11074</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.87% (2.05)</t>
+          <t>1.37% (152.0)</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>238.16</v>
+        <v>11226</v>
       </c>
       <c r="G3" t="n">
-        <v>240.21</v>
+        <v>11378</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-11 10:15</t>
+          <t>2026-09-11 13:45</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -576,45 +574,45 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-11 15:15 (Week End)</t>
+          <t>2026-09-11 15:00 (Week End)</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>238.13</v>
+        <v>11134</v>
       </c>
       <c r="L3" t="n">
-        <v>0.86</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>402.9</v>
+        <v>235.84</v>
       </c>
       <c r="C4" t="n">
-        <v>399.75</v>
+        <v>234.06</v>
       </c>
       <c r="D4" t="n">
-        <v>405</v>
+        <v>236.11</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.3% (5.25)</t>
+          <t>0.87% (2.05)</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>410.25</v>
+        <v>238.16</v>
       </c>
       <c r="G4" t="n">
-        <v>415.5</v>
+        <v>240.21</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-11 14:15</t>
+          <t>2026-09-11 10:15</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -628,137 +626,137 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>404.35</v>
+        <v>238.13</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.16</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1151</v>
+        <v>402.9</v>
       </c>
       <c r="C5" t="n">
-        <v>1132</v>
+        <v>399.75</v>
       </c>
       <c r="D5" t="n">
-        <v>1152.6</v>
+        <v>405</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.79% (20.6)</t>
+          <t>1.3% (5.25)</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1173.2</v>
+        <v>410.25</v>
       </c>
       <c r="G5" t="n">
-        <v>1193.8</v>
+        <v>415.5</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-11 11:00</t>
+          <t>2026-09-11 14:15</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-11 11:45</t>
+          <t>2026-09-11 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1173.2</v>
+        <v>404.35</v>
       </c>
       <c r="L5" t="n">
-        <v>1.79</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>859.55</v>
+        <v>1151</v>
       </c>
       <c r="C6" t="n">
-        <v>855.45</v>
+        <v>1132</v>
       </c>
       <c r="D6" t="n">
-        <v>864.85</v>
+        <v>1152.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.09% (9.4)</t>
+          <t>1.79% (20.6)</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>874.25</v>
+        <v>1173.2</v>
       </c>
       <c r="G6" t="n">
-        <v>883.65</v>
+        <v>1193.8</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-11 09:45</t>
+          <t>2026-09-11 11:00</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-11 15:15 (Week End)</t>
+          <t>2026-09-11 11:45</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>865</v>
+        <v>1173.2</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>698.5</v>
+        <v>859.55</v>
       </c>
       <c r="C7" t="n">
-        <v>682.1</v>
+        <v>855.45</v>
       </c>
       <c r="D7" t="n">
-        <v>704.55</v>
+        <v>864.85</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3.19% (22.45)</t>
+          <t>1.09% (9.4)</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>727</v>
+        <v>874.25</v>
       </c>
       <c r="G7" t="n">
-        <v>749.45</v>
+        <v>883.65</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-11 14:00</t>
+          <t>2026-09-11 09:45</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -772,41 +770,41 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>708.25</v>
+        <v>865</v>
       </c>
       <c r="L7" t="n">
-        <v>0.53</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4908.5</v>
+        <v>698.5</v>
       </c>
       <c r="C8" t="n">
-        <v>4822</v>
+        <v>682.1</v>
       </c>
       <c r="D8" t="n">
-        <v>4945</v>
+        <v>704.55</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2.49% (123.0)</t>
+          <t>3.19% (22.45)</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5068</v>
+        <v>727</v>
       </c>
       <c r="G8" t="n">
-        <v>5191</v>
+        <v>749.45</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-11 14:45</t>
+          <t>2026-09-11 14:00</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -820,131 +818,133 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>4973</v>
+        <v>708.25</v>
       </c>
       <c r="L8" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>134.32</v>
+        <v>4908.5</v>
       </c>
       <c r="C9" t="n">
-        <v>133.11</v>
+        <v>4822</v>
       </c>
       <c r="D9" t="n">
-        <v>134.45</v>
+        <v>4945</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.0% (1.34)</t>
+          <t>2.49% (123.0)</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>135.79</v>
+        <v>5068</v>
       </c>
       <c r="G9" t="n">
-        <v>137.13</v>
+        <v>5191</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-11 12:30</t>
+          <t>2026-09-11 14:45</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-11 14:30</t>
+          <t>2026-09-11 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>135.79</v>
+        <v>4973</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>418.95</v>
+        <v>134.32</v>
       </c>
       <c r="C10" t="n">
-        <v>409.25</v>
+        <v>133.11</v>
       </c>
       <c r="D10" t="n">
-        <v>420.45</v>
+        <v>134.45</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.66% (11.2)</t>
+          <t>1.0% (1.34)</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>431.65</v>
+        <v>135.79</v>
       </c>
       <c r="G10" t="n">
-        <v>442.85</v>
+        <v>137.13</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-09-11 12:30</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ENTRY EXPIRED (Week End)</t>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>2026-09-11 14:30</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>135.79</v>
+      </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1026.1</v>
+        <v>418.95</v>
       </c>
       <c r="C11" t="n">
-        <v>1013.3</v>
+        <v>409.25</v>
       </c>
       <c r="D11" t="n">
-        <v>1038</v>
+        <v>420.45</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2.38% (24.7)</t>
+          <t>2.66% (11.2)</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1062.7</v>
+        <v>431.65</v>
       </c>
       <c r="G11" t="n">
-        <v>1087.4</v>
+        <v>442.85</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -969,28 +969,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>181.4</v>
+        <v>1026.1</v>
       </c>
       <c r="C12" t="n">
-        <v>180.86</v>
+        <v>1013.3</v>
       </c>
       <c r="D12" t="n">
-        <v>186.78</v>
+        <v>1038</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3.17% (5.92)</t>
+          <t>2.38% (24.7)</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>192.7</v>
+        <v>1062.7</v>
       </c>
       <c r="G12" t="n">
-        <v>198.62</v>
+        <v>1087.4</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1015,28 +1015,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4952</v>
+        <v>181.4</v>
       </c>
       <c r="C13" t="n">
-        <v>4945</v>
+        <v>180.86</v>
       </c>
       <c r="D13" t="n">
-        <v>5021</v>
+        <v>186.78</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.51% (76.0)</t>
+          <t>3.17% (5.92)</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5097</v>
+        <v>192.7</v>
       </c>
       <c r="G13" t="n">
-        <v>5173</v>
+        <v>198.62</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1055,6 +1055,52 @@
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>4952</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4945</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5021</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1.51% (76.0)</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>5097</v>
+      </c>
+      <c r="G14" t="n">
+        <v>5173</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ENTRY EXPIRED (Week End)</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/trade_tracker_results.xlsx
+++ b/data/trade_tracker_results.xlsx
@@ -647,14 +647,14 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 09:15 (Active)</t>
+          <t>2026-09-24 09:45 (Active)</t>
         </is>
       </c>
       <c r="K3" s="2" t="n">
-        <v>1820.6</v>
+        <v>1819.3</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>-0.67</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="4">
@@ -731,22 +731,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-09-24 09:30</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr"/>
+          <t>2026-09-24 09:45 (Active)</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>1342.6</v>
+      </c>
       <c r="L5" s="4" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="6">
@@ -869,24 +871,22 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 11:00</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 09:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>989.8</v>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="4" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -946,7 +946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1028,128 +1028,128 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1832.1</v>
+        <v>986</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1824</v>
+        <v>984.1</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>1835.7</v>
+        <v>991</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>0.64% (11.7)</t>
+          <t>0.7% (6.9)</t>
         </is>
       </c>
       <c r="F2" s="4" t="n">
-        <v>1847.4</v>
+        <v>997.9</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>1859.1</v>
+        <v>1004.8</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 09:15</t>
-        </is>
-      </c>
-      <c r="I2" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>2026-09-23 11:00</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 09:15</t>
+          <t>2026-09-24 09:15 (Active)</t>
         </is>
       </c>
       <c r="K2" s="2" t="n">
-        <v>1859.1</v>
+        <v>989.8</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>1.27</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1818.6</v>
+        <v>1832.1</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1813</v>
+        <v>1824</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>1832.8</v>
+        <v>1835.7</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>1.08% (19.8)</t>
+          <t>0.64% (11.7)</t>
         </is>
       </c>
       <c r="F3" s="4" t="n">
-        <v>1852.6</v>
+        <v>1847.4</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>1872.4</v>
+        <v>1859.1</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 14:15</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>2026-09-23 09:15</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 09:15 (Active)</t>
+          <t>2026-09-23 09:15</t>
         </is>
       </c>
       <c r="K3" s="2" t="n">
-        <v>1820.6</v>
+        <v>1859.1</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>-0.67</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>986</v>
+        <v>1818.6</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>984.1</v>
+        <v>1813</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>991</v>
+        <v>1832.8</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>0.7% (6.9)</t>
+          <t>1.08% (19.8)</t>
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>997.9</v>
+        <v>1852.6</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>1004.8</v>
+        <v>1872.4</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 11:00</t>
+          <t>2026-09-23 14:15</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
@@ -1159,14 +1159,62 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 09:15 (Active)</t>
+          <t>2026-09-24 09:45 (Active)</t>
         </is>
       </c>
       <c r="K4" s="2" t="n">
-        <v>989.8</v>
+        <v>1819.3</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>-0.12</v>
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>1338.9</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1331.3</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>1342.3</v>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>0.82% (11.0)</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>1353.3</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>1364.3</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 09:30</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 09:45 (Active)</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>1342.6</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>

--- a/data/trade_tracker_results.xlsx
+++ b/data/trade_tracker_results.xlsx
@@ -647,14 +647,14 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 09:45 (Active)</t>
+          <t>2026-09-24 10:00 (Active)</t>
         </is>
       </c>
       <c r="K3" s="2" t="n">
-        <v>1819.3</v>
+        <v>1816.2</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>-0.74</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="4">
@@ -731,24 +731,22 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 09:30</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 09:45 (Active)</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>1342.6</v>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="4" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -825,22 +823,24 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-09-24 10:00</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr"/>
+          <t>2026-09-24 10:00 (Active)</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>309.3</v>
+      </c>
       <c r="L7" s="4" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="8">
@@ -946,7 +946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1076,128 +1076,128 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1832.1</v>
+        <v>1338.9</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1824</v>
+        <v>1331.3</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>1835.7</v>
+        <v>1342.3</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>0.64% (11.7)</t>
+          <t>0.82% (11.0)</t>
         </is>
       </c>
       <c r="F3" s="4" t="n">
-        <v>1847.4</v>
+        <v>1353.3</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>1859.1</v>
+        <v>1364.3</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 09:15</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>2026-09-24 09:30</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 09:15</t>
+          <t>2026-09-24 09:45 (Active)</t>
         </is>
       </c>
       <c r="K3" s="2" t="n">
-        <v>1859.1</v>
+        <v>1342.6</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>1.27</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1818.6</v>
+        <v>1832.1</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1813</v>
+        <v>1824</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>1832.8</v>
+        <v>1835.7</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>1.08% (19.8)</t>
+          <t>0.64% (11.7)</t>
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>1852.6</v>
+        <v>1847.4</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>1872.4</v>
+        <v>1859.1</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 14:15</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>2026-09-23 09:15</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 09:45 (Active)</t>
+          <t>2026-09-23 09:15</t>
         </is>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1819.3</v>
+        <v>1859.1</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>-0.74</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1338.9</v>
+        <v>1818.6</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1331.3</v>
+        <v>1813</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1342.3</v>
+        <v>1832.8</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>0.82% (11.0)</t>
+          <t>1.08% (19.8)</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1353.3</v>
+        <v>1852.6</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>1364.3</v>
+        <v>1872.4</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 09:30</t>
+          <t>2026-09-23 14:15</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
@@ -1207,14 +1207,62 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 09:45 (Active)</t>
+          <t>2026-09-24 10:00 (Active)</t>
         </is>
       </c>
       <c r="K5" s="2" t="n">
-        <v>1342.6</v>
+        <v>1816.2</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.02</v>
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>RECLTD</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>308.5</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>307.1</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>308.85</v>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>0.57% (1.75)</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>310.6</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>312.35</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 10:00</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 10:00 (Active)</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>309.3</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>0.15</v>
       </c>
     </row>
   </sheetData>

--- a/data/trade_tracker_results.xlsx
+++ b/data/trade_tracker_results.xlsx
@@ -637,24 +637,22 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 14:15</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 10:00 (Active)</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>1816.2</v>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="4" t="n">
-        <v>-0.91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -685,22 +683,24 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-09-24 10:00</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr"/>
+          <t>2026-09-24 15:00 (Active)</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>3163.1</v>
+      </c>
       <c r="L4" s="4" t="n">
-        <v>0</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="5">
@@ -713,21 +713,21 @@
         <v>1338.9</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1331.3</v>
+        <v>1330.2</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1342.3</v>
+        <v>1347.8</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>0.82% (11.0)</t>
+          <t>1.31% (17.6)</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1353.3</v>
+        <v>1365.4</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>1364.3</v>
+        <v>1383</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -759,21 +759,21 @@
         <v>3029.5</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3022.4</v>
+        <v>3009.4</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>3062.1</v>
+        <v>3041.5</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>1.3% (39.7)</t>
+          <t>1.06% (32.1)</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>3101.8</v>
+        <v>3073.6</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>3141.5</v>
+        <v>3105.7</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 10:00</t>
+          <t>2026-09-24 12:30</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
@@ -833,14 +833,14 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 10:00 (Active)</t>
+          <t>2026-09-24 15:00 (Active)</t>
         </is>
       </c>
       <c r="K7" s="2" t="n">
-        <v>309.3</v>
+        <v>307.7</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.15</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="8">
@@ -853,21 +853,21 @@
         <v>986</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>984.1</v>
+        <v>983</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>0.7% (6.9)</t>
+          <t>0.51% (5.0)</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>997.9</v>
+        <v>993</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1004.8</v>
+        <v>998</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1124,80 +1124,80 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1832.1</v>
+        <v>1818.6</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1824</v>
+        <v>1813</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>1835.7</v>
+        <v>1832.8</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>0.64% (11.7)</t>
+          <t>1.08% (19.8)</t>
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>1847.4</v>
+        <v>1852.6</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>1859.1</v>
+        <v>1872.4</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 09:15</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>2026-09-23 14:15</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 09:15</t>
+          <t>2026-09-24 10:00 (Active)</t>
         </is>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1859.1</v>
+        <v>1816.2</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>1.27</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1818.6</v>
+        <v>308.5</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1813</v>
+        <v>307.1</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1832.8</v>
+        <v>308.85</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>1.08% (19.8)</t>
+          <t>0.57% (1.75)</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1852.6</v>
+        <v>310.6</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>1872.4</v>
+        <v>312.35</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 14:15</t>
+          <t>2026-09-24 10:00</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
@@ -1211,58 +1211,154 @@
         </is>
       </c>
       <c r="K5" s="2" t="n">
-        <v>1816.2</v>
+        <v>309.3</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>-0.91</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>1832.1</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1824</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>1835.7</v>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>0.64% (11.7)</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>1847.4</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>1859.1</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23 09:15</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23 09:15</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>1859.1</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>3159</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>3125</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>3176.9</v>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>1.63% (51.9)</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>3228.8</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>3280.7</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 10:00</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 15:00 (Active)</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>3163.1</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>RECLTD</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B8" s="2" t="n">
         <v>308.5</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C8" s="3" t="n">
         <v>307.1</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D8" s="4" t="n">
         <v>308.85</v>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>0.57% (1.75)</t>
         </is>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F8" s="4" t="n">
         <v>310.6</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>312.35</v>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-24 10:00</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 12:30</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-24 10:00 (Active)</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>309.3</v>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>0.15</v>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 15:00 (Active)</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>307.7</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>-0.37</v>
       </c>
     </row>
   </sheetData>

--- a/data/trade_tracker_results.xlsx
+++ b/data/trade_tracker_results.xlsx
@@ -693,14 +693,14 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 15:00 (Active)</t>
+          <t>2026-09-24 15:15 (Active)</t>
         </is>
       </c>
       <c r="K4" s="2" t="n">
-        <v>3163.1</v>
+        <v>3166.5</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>-0.43</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="5">
@@ -833,14 +833,14 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 15:00 (Active)</t>
+          <t>2026-09-24 15:15 (Active)</t>
         </is>
       </c>
       <c r="K7" s="2" t="n">
-        <v>307.7</v>
+        <v>308.25</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.37</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="8">
@@ -1303,14 +1303,14 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 15:00 (Active)</t>
+          <t>2026-09-24 15:15 (Active)</t>
         </is>
       </c>
       <c r="K7" s="2" t="n">
-        <v>3163.1</v>
+        <v>3166.5</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.43</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="8">
@@ -1351,14 +1351,14 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 15:00 (Active)</t>
+          <t>2026-09-24 15:15 (Active)</t>
         </is>
       </c>
       <c r="K8" s="2" t="n">
-        <v>307.7</v>
+        <v>308.25</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.37</v>
+        <v>-0.19</v>
       </c>
     </row>
   </sheetData>

--- a/data/trade_tracker_results.xlsx
+++ b/data/trade_tracker_results.xlsx
@@ -482,14 +482,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
@@ -932,6 +932,282 @@
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>1336.5</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>1335.9</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>1347.2</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>0.84% (11.3)</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>1358.5</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>1369.8</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>516.1</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>514.25</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>565.4</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>9.05% (51.15)</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>616.55</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>667.7</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>1927</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>1925.5</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>1935.6</v>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>0.52% (10.1)</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>1945.7</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>1955.8</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>ICICIPRULI</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>456.95</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>446.15</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>485</v>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>8.01% (38.85)</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>523.85</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>562.7</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>472</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>463.7</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>481.7</v>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>3.74% (18.0)</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>499.7</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>517.7</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>1521.1</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>1517.5</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>1558.5</v>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>2.63% (41.0)</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>1599.5</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>1640.5</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/trade_tracker_results.xlsx
+++ b/data/trade_tracker_results.xlsx
@@ -482,13 +482,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
@@ -693,14 +693,14 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 15:15 (Active)</t>
+          <t>2026-09-25 15:15 (Active)</t>
         </is>
       </c>
       <c r="K4" s="2" t="n">
-        <v>3166.5</v>
+        <v>3191</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>-0.33</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="5">
@@ -759,40 +759,42 @@
         <v>3029.5</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3009.4</v>
+        <v>2967.1</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>3041.5</v>
+        <v>3039</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>1.06% (32.1)</t>
+          <t>2.37% (71.9)</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>3073.6</v>
+        <v>3110.9</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>3105.7</v>
+        <v>3182.8</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-09-25 14:15</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr"/>
+          <t>2026-09-25 15:00 (Active)</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>3035</v>
+      </c>
       <c r="L6" s="4" t="n">
-        <v>0</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="7">
@@ -823,24 +825,24 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 12:30</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>2026-09-25 10:00</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 15:15 (Active)</t>
+          <t>2026-09-25 15:00</t>
         </is>
       </c>
       <c r="K7" s="2" t="n">
-        <v>308.25</v>
+        <v>312.35</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.19</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="8">
@@ -853,21 +855,21 @@
         <v>986</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>983</v>
+        <v>982.8</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>988</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>0.51% (5.0)</t>
+          <t>0.53% (5.2)</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>993</v>
+        <v>993.2</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>998</v>
+        <v>998.4</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -945,21 +947,21 @@
         <v>1336.5</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1335.9</v>
+        <v>1315</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1347.2</v>
+        <v>1343</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>0.84% (11.3)</t>
+          <t>2.08% (28.0)</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1358.5</v>
+        <v>1371</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1369.8</v>
+        <v>1399</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1037,40 +1039,42 @@
         <v>1927</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1925.5</v>
+        <v>1915.1</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1935.6</v>
+        <v>1935.1</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>0.52% (10.1)</t>
+          <t>1.03% (20.0)</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1945.7</v>
+        <v>1955.1</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1955.8</v>
+        <v>1975.1</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-09-25 14:00</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr"/>
+          <t>2026-09-25 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>1942.9</v>
+      </c>
       <c r="L12" s="4" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="13">
@@ -1208,6 +1212,332 @@
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>2907</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>2898.2</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>2945.7</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>1.61% (47.5)</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>2993.2</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>3040.7</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>200.4</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>196.1</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>203.34</v>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>3.56% (7.24)</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>210.58</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>217.82</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:15</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>202.75</v>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>-0.29</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>AXISBANK</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>1219.9</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>1175.1</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>1247.4</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>5.8% (72.3)</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>1319.7</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>1392</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>10821.29</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>10746</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>11023</v>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>2.51% (277.0)</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>11300</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>11577</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>4933</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>4883.5</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>4936</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>1.06% (52.5)</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>4988.5</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>5041</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>1242.8</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>1202.6</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>1246</v>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>3.48% (43.4)</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>1289.4</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>1332.8</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:00</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>1254.8</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>WIPRO</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>163.3</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>161.67</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>164.85</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>1.93% (3.18)</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>168.03</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>171.21</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1222,7 +1552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1496,145 +1826,385 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1832.1</v>
+        <v>308.5</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1824</v>
+        <v>307.1</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1835.7</v>
+        <v>308.85</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>0.64% (11.7)</t>
+          <t>0.57% (1.75)</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1847.4</v>
+        <v>310.6</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1859.1</v>
+        <v>312.35</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 09:15</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>2026-09-24 12:30</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 09:15</t>
+          <t>2026-09-24 15:15 (Active)</t>
         </is>
       </c>
       <c r="K6" s="2" t="n">
-        <v>1859.1</v>
+        <v>308.25</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>1.27</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>3159</v>
+        <v>1832.1</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>3125</v>
+        <v>1824</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3176.9</v>
+        <v>1835.7</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>1.63% (51.9)</t>
+          <t>0.64% (11.7)</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>3228.8</v>
+        <v>1847.4</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>3280.7</v>
+        <v>1859.1</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 10:00</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>2026-09-23 09:15</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 15:15 (Active)</t>
+          <t>2026-09-23 09:15</t>
         </is>
       </c>
       <c r="K7" s="2" t="n">
-        <v>3166.5</v>
+        <v>1859.1</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.33</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>3159</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>3125</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>3176.9</v>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>1.63% (51.9)</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>3228.8</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>3280.7</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 10:00</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>3191</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>3029.5</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>2967.1</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>3039</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>2.37% (71.9)</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>3110.9</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>3182.8</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:15</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 15:00 (Active)</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>3035</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
           <t>RECLTD</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B10" s="2" t="n">
         <v>308.5</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C10" s="3" t="n">
         <v>307.1</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D10" s="4" t="n">
         <v>308.85</v>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>0.57% (1.75)</t>
         </is>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F10" s="4" t="n">
         <v>310.6</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>312.35</v>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-24 12:30</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:00</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 15:00</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>312.35</v>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>1927</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>1915.1</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>1935.1</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>1.03% (20.0)</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>1955.1</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>1975.1</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:00</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-24 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>308.25</v>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v>-0.19</v>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>1942.9</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>200.4</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>196.1</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>203.34</v>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>3.56% (7.24)</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>210.58</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>217.82</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:15</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>202.75</v>
+      </c>
+      <c r="L12" s="4" t="n">
+        <v>-0.29</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>1242.8</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>1202.6</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>1246</v>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>3.48% (43.4)</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>1289.4</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>1332.8</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:00</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>1254.8</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>0.71</v>
       </c>
     </row>
   </sheetData>

--- a/data/trade_tracker_results.xlsx
+++ b/data/trade_tracker_results.xlsx
@@ -68,14 +68,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -111,10 +111,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -482,18 +482,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="33" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
@@ -564,590 +564,596 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1832.1</v>
+        <v>196.1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1824</v>
+        <v>195.37</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>1835.7</v>
+        <v>197.36</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>0.64% (11.7)</t>
+          <t>1.01% (1.99)</t>
         </is>
       </c>
       <c r="F2" s="4" t="n">
-        <v>1847.4</v>
+        <v>199.35</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>1859.1</v>
+        <v>201.34</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 09:15</t>
-        </is>
-      </c>
-      <c r="I2" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23 09:15</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>1859.1</v>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1818.6</v>
+        <v>8821.5</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1813</v>
+        <v>8804.5</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>1832.8</v>
+        <v>8893</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>1.08% (19.8)</t>
+          <t>1.0% (88.5)</t>
         </is>
       </c>
       <c r="F3" s="4" t="n">
-        <v>1852.6</v>
+        <v>8981.5</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>1872.4</v>
+        <v>9070</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-09-28 10:00</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr"/>
+          <t>2026-09-28 15:00 (Active)</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>8860</v>
+      </c>
       <c r="L3" s="4" t="n">
-        <v>0</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3159</v>
+        <v>411.8</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3125</v>
+        <v>407.35</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>3176.9</v>
+        <v>416.55</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>1.63% (51.9)</t>
+          <t>2.21% (9.2)</t>
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>3228.8</v>
+        <v>425.75</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>3280.7</v>
+        <v>434.95</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 10:00</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>3191</v>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="4" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1338.9</v>
+        <v>4883</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1330.2</v>
+        <v>4869</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1347.8</v>
+        <v>4902.5</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>1.31% (17.6)</t>
+          <t>0.68% (33.5)</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1365.4</v>
+        <v>4936</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>1383</v>
+        <v>4969.5</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-09-28 13:45</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr"/>
+          <t>2026-09-28 15:00 (Active)</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>4915</v>
+      </c>
       <c r="L5" s="4" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>3029.5</v>
+        <v>1629.9</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>2967.1</v>
+        <v>1621</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>3039</v>
+        <v>1660.4</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>2.37% (71.9)</t>
+          <t>2.37% (39.4)</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>3110.9</v>
+        <v>1699.8</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>3182.8</v>
+        <v>1739.2</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 14:15</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:00 (Active)</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>3035</v>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="4" t="n">
-        <v>-0.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>COLPAL</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>308.5</v>
+        <v>1835.4</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>307.1</v>
+        <v>1827</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>308.85</v>
+        <v>1857.9</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>0.57% (1.75)</t>
+          <t>1.66% (30.9)</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>310.6</v>
+        <v>1888.8</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>312.35</v>
+        <v>1919.7</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 10:00</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:00</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>312.35</v>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>986</v>
+        <v>171.35</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>982.8</v>
+        <v>171.05</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>988</v>
+        <v>172.2</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>0.53% (5.2)</t>
+          <t>0.67% (1.15)</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>993.2</v>
+        <v>173.35</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>998.4</v>
+        <v>174.5</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-09-28 15:15</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr"/>
+          <t>2026-09-28 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>172.45</v>
+      </c>
       <c r="L8" s="4" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>TMPV</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>299.3</v>
+        <v>864.2</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>298.65</v>
+        <v>859.7</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>301.4</v>
+        <v>864.8</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>0.91% (2.75)</t>
+          <t>0.59% (5.1)</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>304.15</v>
+        <v>869.9</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>306.9</v>
+        <v>875</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-09-28 12:00</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr"/>
+          <t>2026-09-28 12:30</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>869.9</v>
+      </c>
       <c r="L9" s="4" t="n">
-        <v>0</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1336.5</v>
+        <v>906.9</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1315</v>
+        <v>889.7</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1343</v>
+        <v>907.5</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>2.08% (28.0)</t>
+          <t>1.96% (17.8)</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1371</v>
+        <v>925.3</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1399</v>
+        <v>943.1</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-09-28 15:15</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
+          <t>2026-09-28 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>909.7</v>
+      </c>
       <c r="L10" s="4" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>516.1</v>
+        <v>991.6</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>514.25</v>
+        <v>986.6</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>565.4</v>
+        <v>993.4</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>9.05% (51.15)</t>
+          <t>0.68% (6.8)</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>616.55</v>
+        <v>1000.2</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>667.7</v>
+        <v>1007</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-09-28 11:30</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr"/>
+          <t>2026-09-28 13:30</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>1007</v>
+      </c>
       <c r="L11" s="4" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>1927</v>
+        <v>399.3</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1915.1</v>
+        <v>396</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1935.1</v>
+        <v>402</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>1.03% (20.0)</t>
+          <t>1.49% (6.0)</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1955.1</v>
+        <v>408</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1975.1</v>
+        <v>414</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 14:00</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
+          <t>2026-09-28 14:00</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:15 (Active)</t>
+          <t>2026-09-28 15:15 (Active)</t>
         </is>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1942.9</v>
+        <v>401.55</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.4</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>ICICIPRULI</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>456.95</v>
+        <v>11975</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>446.15</v>
+        <v>11945</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>485</v>
+        <v>12020</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>8.01% (38.85)</t>
+          <t>0.62% (75.0)</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>523.85</v>
+        <v>12095</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>562.7</v>
+        <v>12170</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-09-28 13:15</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr"/>
+          <t>2026-09-28 15:00 (Active)</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>12008</v>
+      </c>
       <c r="L13" s="4" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>472</v>
+        <v>1495.7</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>463.7</v>
+        <v>1487.1</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>481.7</v>
+        <v>1498</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>3.74% (18.0)</t>
+          <t>0.73% (10.9)</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>499.7</v>
+        <v>1508.9</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>517.7</v>
+        <v>1519.8</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1172,28 +1178,28 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>1521.1</v>
+        <v>22165</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1517.5</v>
+        <v>22070</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1558.5</v>
+        <v>22190</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>2.63% (41.0)</t>
+          <t>0.54% (120.0)</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1599.5</v>
+        <v>22310</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1640.5</v>
+        <v>22430</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1218,28 +1224,28 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>TATACOMM</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>2907</v>
+        <v>1650.1</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2898.2</v>
+        <v>1637</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>2945.7</v>
+        <v>1661.2</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>1.61% (47.5)</t>
+          <t>1.46% (24.2)</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2993.2</v>
+        <v>1685.4</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>3040.7</v>
+        <v>1709.6</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1264,280 +1270,46 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>200.4</v>
+        <v>10983</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>196.1</v>
+        <v>10981</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>203.34</v>
+        <v>11042</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>3.56% (7.24)</t>
+          <t>0.55% (61.0)</t>
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>210.58</v>
+        <v>11103</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>217.82</v>
+        <v>11164</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 14:15</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="n">
-        <v>202.75</v>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="4" t="n">
-        <v>-0.29</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>AXISBANK</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>1219.9</v>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>1175.1</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>1247.4</v>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>5.8% (72.3)</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>1319.7</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>1392</v>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>BAJAJHLDNG</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>10821.29</v>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>10746</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>11023</v>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>2.51% (277.0)</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>11300</v>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>11577</v>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>BRITANNIA</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>4933</v>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>4883.5</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>4936</v>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>1.06% (52.5)</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>4988.5</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>5041</v>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>NAUKRI</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>1242.8</v>
-      </c>
-      <c r="C21" s="3" t="n">
-        <v>1202.6</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>1246</v>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>3.48% (43.4)</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>1289.4</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>1332.8</v>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-25 14:00</t>
-        </is>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-25 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="n">
-        <v>1254.8</v>
-      </c>
-      <c r="L21" s="4" t="n">
-        <v>0.71</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>WIPRO</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>163.3</v>
-      </c>
-      <c r="C22" s="3" t="n">
-        <v>161.67</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>164.85</v>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>1.93% (3.18)</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="n">
-        <v>168.03</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>171.21</v>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1552,18 +1324,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="33" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
@@ -1662,7 +1434,7 @@
           <t>2026-09-23 11:00</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -1710,7 +1482,7 @@
           <t>2026-09-24 09:30</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -1758,7 +1530,7 @@
           <t>2026-09-23 14:15</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -1806,7 +1578,7 @@
           <t>2026-09-24 10:00</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -1854,7 +1626,7 @@
           <t>2026-09-24 12:30</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -1902,7 +1674,7 @@
           <t>2026-09-23 09:15</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -1950,7 +1722,7 @@
           <t>2026-09-24 10:00</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -1998,7 +1770,7 @@
           <t>2026-09-25 14:15</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -2046,7 +1818,7 @@
           <t>2026-09-25 10:00</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -2094,7 +1866,7 @@
           <t>2026-09-25 14:00</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -2142,7 +1914,7 @@
           <t>2026-09-25 14:15</t>
         </is>
       </c>
-      <c r="I12" s="6" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -2190,7 +1962,7 @@
           <t>2026-09-25 14:00</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -2205,6 +1977,390 @@
       </c>
       <c r="L13" s="4" t="n">
         <v>0.71</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>8821.5</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>8804.5</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>8893</v>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>1.0% (88.5)</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>8981.5</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>9070</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 10:00</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:00 (Active)</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>8860</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>4883</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>4869</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>4902.5</v>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>0.68% (33.5)</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>4936</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>4969.5</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:45</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:00 (Active)</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>4915</v>
+      </c>
+      <c r="L15" s="4" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>171.35</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>171.05</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>172.2</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>0.67% (1.15)</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>173.35</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>174.5</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:15</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>172.45</v>
+      </c>
+      <c r="L16" s="4" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>GODREJCP</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>864.2</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>859.7</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>864.8</v>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>0.59% (5.1)</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>869.9</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>875</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:00</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:30</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>869.9</v>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>INDUSINDBK</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>906.9</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>889.7</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>907.5</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>1.96% (17.8)</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>925.3</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>943.1</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:15</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>909.7</v>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>991.6</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>986.6</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>993.4</v>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>0.68% (6.8)</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>1000.2</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>1007</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 11:30</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:30</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>1007</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>399.3</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>396</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>402</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>1.49% (6.0)</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>408</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>414</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:00</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>401.55</v>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>11975</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>11945</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>12020</v>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>0.62% (75.0)</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>12095</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>12170</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:15</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:00 (Active)</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>12008</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>-0.1</v>
       </c>
     </row>
   </sheetData>

--- a/data/trade_tracker_results.xlsx
+++ b/data/trade_tracker_results.xlsx
@@ -53,7 +53,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -70,6 +70,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFEB9C"/>
         <bgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -97,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -114,7 +120,10 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -482,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -571,40 +580,42 @@
         <v>196.1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>195.37</v>
+        <v>192.45</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>197.36</v>
+        <v>196.67</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>1.01% (1.99)</t>
+          <t>2.15% (4.22)</t>
         </is>
       </c>
       <c r="F2" s="4" t="n">
-        <v>199.35</v>
+        <v>200.89</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>201.34</v>
+        <v>205.11</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-09-29 13:00</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr"/>
+          <t>2026-09-29 15:00 (Active)</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>196.3</v>
+      </c>
       <c r="L2" s="4" t="n">
-        <v>0</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="3">
@@ -638,21 +649,21 @@
           <t>2026-09-28 10:00</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 15:00 (Active)</t>
+          <t>2026-09-29 10:00</t>
         </is>
       </c>
       <c r="K3" s="2" t="n">
-        <v>8860</v>
+        <v>8804.5</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>-0.37</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4">
@@ -665,40 +676,42 @@
         <v>411.8</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>407.35</v>
+        <v>402.75</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>416.55</v>
+        <v>411.9</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>2.21% (9.2)</t>
+          <t>2.22% (9.15)</t>
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>425.75</v>
+        <v>421.05</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>434.95</v>
+        <v>430.2</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-09-29 14:00</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr"/>
+          <t>2026-09-29 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>413.35</v>
+      </c>
       <c r="L4" s="4" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="5">
@@ -732,21 +745,21 @@
           <t>2026-09-28 13:45</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 15:00 (Active)</t>
+          <t>2026-09-29 09:30</t>
         </is>
       </c>
       <c r="K5" s="2" t="n">
-        <v>4915</v>
+        <v>4869</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.25</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="6">
@@ -759,40 +772,42 @@
         <v>1629.9</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1621</v>
+        <v>1600.2</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1660.4</v>
+        <v>1642.9</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>2.37% (39.4)</t>
+          <t>2.6% (42.7)</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1699.8</v>
+        <v>1685.6</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1739.2</v>
+        <v>1728.3</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-09-29 14:45</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr"/>
+          <t>2026-09-29 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>1627.3</v>
+      </c>
       <c r="L6" s="4" t="n">
-        <v>0</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="7">
@@ -851,42 +866,40 @@
         <v>171.35</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>171.05</v>
+        <v>168.57</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>172.2</v>
+        <v>173.18</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>0.67% (1.15)</t>
+          <t>2.66% (4.61)</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>173.35</v>
+        <v>177.79</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>174.5</v>
+        <v>182.4</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 15:15</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>172.45</v>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="4" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -920,21 +933,21 @@
           <t>2026-09-28 12:00</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 12:30</t>
+          <t>2026-09-29 09:30</t>
         </is>
       </c>
       <c r="K9" s="2" t="n">
-        <v>869.9</v>
+        <v>859.7</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.59</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="10">
@@ -968,21 +981,21 @@
           <t>2026-09-28 15:15</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 15:15 (Active)</t>
+          <t>2026-09-29 10:15</t>
         </is>
       </c>
       <c r="K10" s="2" t="n">
-        <v>909.7</v>
+        <v>889.7</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.24</v>
+        <v>-1.96</v>
       </c>
     </row>
     <row r="11">
@@ -995,42 +1008,40 @@
         <v>991.6</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>986.6</v>
+        <v>980.4</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>993.4</v>
+        <v>992.7</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>0.68% (6.8)</t>
+          <t>1.24% (12.3)</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1000.2</v>
+        <v>1005</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1007</v>
+        <v>1017.3</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 11:30</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 13:30</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="n">
-        <v>1007</v>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="4" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1043,25 +1054,25 @@
         <v>399.3</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>396</v>
+        <v>394.7</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>402</v>
+        <v>403.65</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>1.49% (6.0)</t>
+          <t>2.22% (8.95)</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>408</v>
+        <v>412.6</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>414</v>
+        <v>421.55</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:00</t>
+          <t>2026-09-29 11:30</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -1071,14 +1082,14 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 15:15 (Active)</t>
+          <t>2026-09-29 15:15 (Active)</t>
         </is>
       </c>
       <c r="K12" s="2" t="n">
-        <v>401.55</v>
+        <v>406</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.11</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="13">
@@ -1091,25 +1102,25 @@
         <v>11975</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>11945</v>
+        <v>11832</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>12020</v>
+        <v>12000</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>0.62% (75.0)</t>
+          <t>1.4% (168.0)</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>12095</v>
+        <v>12168</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>12170</v>
+        <v>12336</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 13:15</t>
+          <t>2026-09-29 12:00</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1119,14 +1130,14 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 15:00 (Active)</t>
+          <t>2026-09-29 15:15 (Active)</t>
         </is>
       </c>
       <c r="K13" s="2" t="n">
-        <v>12008</v>
+        <v>11877</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.1</v>
+        <v>-1.03</v>
       </c>
     </row>
     <row r="14">
@@ -1157,22 +1168,24 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-09-29 11:30</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr"/>
+          <t>2026-09-29 12:30</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>1487.1</v>
+      </c>
       <c r="L14" s="4" t="n">
-        <v>0</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="15">
@@ -1185,40 +1198,42 @@
         <v>22165</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>22070</v>
+        <v>22025</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>22190</v>
+        <v>22195</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>0.54% (120.0)</t>
+          <t>0.77% (170.0)</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>22310</v>
+        <v>22365</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>22430</v>
+        <v>22535</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-09-29 14:45</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr"/>
+          <t>2026-09-29 15:00</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>22025</v>
+      </c>
       <c r="L15" s="4" t="n">
-        <v>0</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="16">
@@ -1231,21 +1246,21 @@
         <v>1650.1</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1637</v>
+        <v>1630.8</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1661.2</v>
+        <v>1665.8</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>1.46% (24.2)</t>
+          <t>2.1% (35.0)</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1685.4</v>
+        <v>1700.8</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1709.6</v>
+        <v>1735.8</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1277,21 +1292,21 @@
         <v>10983</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>10981</v>
+        <v>10869</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>11042</v>
+        <v>11030</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>0.55% (61.0)</t>
+          <t>1.46% (161.0)</t>
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>11103</v>
+        <v>11191</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>11164</v>
+        <v>11352</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1310,6 +1325,478 @@
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>2898.2</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>2793.7</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>2920.1</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>4.33% (126.4)</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>3046.5</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>3172.9</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>1766.7</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>1736.8</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>1770.1</v>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>1.88% (33.3)</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>1803.4</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>1836.7</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:00</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:15</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>1803.4</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>2391</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>2381.6</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>2420</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>1.59% (38.4)</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>2458.4</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>2496.8</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:00</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>2415</v>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>IRFC</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>79.95</v>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>3.56% (2.85)</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>85.65000000000001</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>263.55</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>263.3</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>266.2</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>1.09% (2.9)</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>269.1</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>272</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:45</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>265.1</v>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>-0.41</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>1127.1</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>1127</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>1139.6</v>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>1.11% (12.6)</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>1152.2</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>1164.8</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:15</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:00 (Active)</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>1130</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>JSWSTEEL</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>1264.4</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>1247</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>1267.7</v>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>1.63% (20.7)</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>1288.4</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>1309.1</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>4848.5</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>4837</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>4872</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>0.72% (35.0)</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>4907</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>4942</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:00</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:45</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>4942</v>
+      </c>
+      <c r="L25" s="4" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>4057</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>4043.3</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>4095</v>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>1.26% (51.7)</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>4146.7</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>4198.4</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:30</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:30</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>4146.7</v>
+      </c>
+      <c r="L26" s="4" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>VEDL</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>259</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>256.15</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>260.45</v>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>1.65% (4.3)</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>264.75</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>269.05</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1324,14 +1811,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
@@ -1674,7 +2161,7 @@
           <t>2026-09-23 09:15</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -1818,7 +2305,7 @@
           <t>2026-09-25 10:00</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -1982,32 +2469,32 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>8821.5</v>
+        <v>171.35</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>8804.5</v>
+        <v>171.05</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>8893</v>
+        <v>172.2</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>1.0% (88.5)</t>
+          <t>0.67% (1.15)</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>8981.5</v>
+        <v>173.35</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>9070</v>
+        <v>174.5</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 10:00</t>
+          <t>2026-09-28 15:15</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -2017,93 +2504,93 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 15:00 (Active)</t>
+          <t>2026-09-28 15:15 (Active)</t>
         </is>
       </c>
       <c r="K14" s="2" t="n">
-        <v>8860</v>
+        <v>172.45</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.37</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>4883</v>
+        <v>991.6</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>4869</v>
+        <v>986.6</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>4902.5</v>
+        <v>993.4</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>0.68% (33.5)</t>
+          <t>0.68% (6.8)</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>4936</v>
+        <v>1000.2</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>4969.5</v>
+        <v>1007</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 13:45</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>2026-09-28 11:30</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 15:00 (Active)</t>
+          <t>2026-09-28 13:30</t>
         </is>
       </c>
       <c r="K15" s="2" t="n">
-        <v>4915</v>
+        <v>1007</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.25</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>171.35</v>
+        <v>399.3</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>171.05</v>
+        <v>396</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>172.2</v>
+        <v>402</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>0.67% (1.15)</t>
+          <t>1.49% (6.0)</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>173.35</v>
+        <v>408</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>174.5</v>
+        <v>414</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 15:15</t>
+          <t>2026-09-28 14:00</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -2117,89 +2604,89 @@
         </is>
       </c>
       <c r="K16" s="2" t="n">
-        <v>172.45</v>
+        <v>401.55</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.15</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>864.2</v>
+        <v>11975</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>859.7</v>
+        <v>11945</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>864.8</v>
+        <v>12020</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>0.59% (5.1)</t>
+          <t>0.62% (75.0)</t>
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>869.9</v>
+        <v>12095</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>875</v>
+        <v>12170</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 12:00</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+          <t>2026-09-28 13:15</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 12:30</t>
+          <t>2026-09-28 15:00 (Active)</t>
         </is>
       </c>
       <c r="K17" s="2" t="n">
-        <v>869.9</v>
+        <v>12008</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.59</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>906.9</v>
+        <v>196.1</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>889.7</v>
+        <v>192.45</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>907.5</v>
+        <v>196.67</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>1.96% (17.8)</t>
+          <t>2.15% (4.22)</t>
         </is>
       </c>
       <c r="F18" s="4" t="n">
-        <v>925.3</v>
+        <v>200.89</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>943.1</v>
+        <v>205.11</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 15:15</t>
+          <t>2026-09-29 13:00</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -2209,93 +2696,93 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 15:15 (Active)</t>
+          <t>2026-09-29 15:00 (Active)</t>
         </is>
       </c>
       <c r="K18" s="2" t="n">
-        <v>909.7</v>
+        <v>196.3</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.24</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>991.6</v>
+        <v>8821.5</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>986.6</v>
+        <v>8804.5</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>993.4</v>
+        <v>8893</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>0.68% (6.8)</t>
+          <t>1.0% (88.5)</t>
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1000.2</v>
+        <v>8981.5</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1007</v>
+        <v>9070</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 11:30</t>
+          <t>2026-09-28 10:00</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 13:30</t>
+          <t>2026-09-29 10:00</t>
         </is>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1007</v>
+        <v>8804.5</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.37</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>399.3</v>
+        <v>411.8</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>396</v>
+        <v>402.75</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>402</v>
+        <v>411.9</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>1.49% (6.0)</t>
+          <t>2.22% (9.15)</t>
         </is>
       </c>
       <c r="F20" s="4" t="n">
-        <v>408</v>
+        <v>421.05</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>414</v>
+        <v>430.2</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:00</t>
+          <t>2026-09-29 14:00</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -2305,62 +2792,686 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 15:15 (Active)</t>
+          <t>2026-09-29 15:15 (Active)</t>
         </is>
       </c>
       <c r="K20" s="2" t="n">
-        <v>401.55</v>
+        <v>413.35</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.11</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>4883</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>4869</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>4902.5</v>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>0.68% (33.5)</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>4936</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>4969.5</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:45</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:30</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>4869</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>-0.68</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>1629.9</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>1600.2</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>1642.9</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>2.6% (42.7)</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>1685.6</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>1728.3</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:45</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>1627.3</v>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>-0.95</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>GODREJCP</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>864.2</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>859.7</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>864.8</v>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>0.59% (5.1)</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>869.9</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>875</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:00</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Then SL)</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:30</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>859.7</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>INDUSINDBK</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>906.9</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>889.7</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>907.5</v>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>1.96% (17.8)</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>925.3</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>943.1</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:15</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:15</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>889.7</v>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>-1.96</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>399.3</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>394.7</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>403.65</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>2.22% (8.95)</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>412.6</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>421.55</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:30</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>406</v>
+      </c>
+      <c r="L25" s="4" t="n">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>MARUTI</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n">
+      <c r="B26" s="2" t="n">
         <v>11975</v>
       </c>
-      <c r="C21" s="3" t="n">
-        <v>11945</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>12020</v>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>0.62% (75.0)</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>12095</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>12170</v>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 13:15</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="C26" s="3" t="n">
+        <v>11832</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>1.4% (168.0)</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>12168</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>12336</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 12:00</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 15:00 (Active)</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="n">
-        <v>12008</v>
-      </c>
-      <c r="L21" s="4" t="n">
-        <v>-0.1</v>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>11877</v>
+      </c>
+      <c r="L26" s="4" t="n">
+        <v>-1.03</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>1495.7</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>1487.1</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>1498</v>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>0.73% (10.9)</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>1508.9</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>1519.8</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:30</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 12:30</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>1487.1</v>
+      </c>
+      <c r="L27" s="4" t="n">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>SHREECEM</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>22165</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>22025</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>22195</v>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>0.77% (170.0)</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>22365</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>22535</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:45</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:00</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>22025</v>
+      </c>
+      <c r="L28" s="4" t="n">
+        <v>-0.77</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>1766.7</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>1736.8</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>1770.1</v>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>1.88% (33.3)</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>1803.4</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>1836.7</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:00</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:15</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>1803.4</v>
+      </c>
+      <c r="L29" s="4" t="n">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>2391</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>2381.6</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>2420</v>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>1.59% (38.4)</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>2458.4</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>2496.8</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:00</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>2415</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>263.55</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>263.3</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>266.2</v>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>1.09% (2.9)</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>269.1</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>272</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:45</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>265.1</v>
+      </c>
+      <c r="L31" s="4" t="n">
+        <v>-0.41</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>1127.1</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>1127</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>1139.6</v>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>1.11% (12.6)</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>1152.2</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>1164.8</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:15</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:00 (Active)</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>1130</v>
+      </c>
+      <c r="L32" s="4" t="n">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>4848.5</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>4837</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>4872</v>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>0.72% (35.0)</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>4907</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>4942</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:00</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:45</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>4942</v>
+      </c>
+      <c r="L33" s="4" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>4057</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>4043.3</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>4095</v>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>1.26% (51.7)</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>4146.7</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>4198.4</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:30</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:30</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>4146.7</v>
+      </c>
+      <c r="L34" s="4" t="n">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/data/trade_tracker_results.xlsx
+++ b/data/trade_tracker_results.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,8 +52,14 @@
       <color rgb="00008000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -84,6 +90,12 @@
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -103,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -124,6 +136,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -508,7 +523,7 @@
     <col width="8" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Ticker</t>
@@ -570,7 +585,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>ADANIPOWER</t>
@@ -618,7 +633,7 @@
         <v>-0.19</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="18" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>APOLLOHOSP</t>
@@ -666,7 +681,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="18" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>BHEL</t>
@@ -714,7 +729,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="18" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>BRITANNIA</t>
@@ -762,7 +777,7 @@
         <v>-0.68</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="18" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>CHOLAFIN</t>
@@ -810,7 +825,7 @@
         <v>-0.95</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="18" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>COLPAL</t>
@@ -856,7 +871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="18" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>GAIL</t>
@@ -902,7 +917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="18" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>GODREJCP</t>
@@ -950,7 +965,7 @@
         <v>-0.59</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="18" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>INDUSINDBK</t>
@@ -998,7 +1013,7 @@
         <v>-1.96</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="18" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>INFY</t>
@@ -1044,7 +1059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="18" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>KOTAKBANK</t>
@@ -1092,7 +1107,7 @@
         <v>0.58</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="18" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>MARUTI</t>
@@ -1140,7 +1155,7 @@
         <v>-1.03</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="18" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>PIDILITIND</t>
@@ -1188,7 +1203,7 @@
         <v>-0.73</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="18" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>SHREECEM</t>
@@ -1236,7 +1251,7 @@
         <v>-0.77</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="18" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>TATACOMM</t>
@@ -1282,7 +1297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="18" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>ULTRACEMCO</t>
@@ -1328,7 +1343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="18" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>ADANIENT</t>
@@ -1374,7 +1389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="18" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
           <t>ADANIPORTS</t>
@@ -1422,7 +1437,7 @@
         <v>1.88</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="18" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>ASIANPAINT</t>
@@ -1470,7 +1485,7 @@
         <v>-0.21</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="18" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t>IRFC</t>
@@ -1516,7 +1531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="18" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>ITC</t>
@@ -1564,7 +1579,7 @@
         <v>-0.41</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="18" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
           <t>JINDALSTEL</t>
@@ -1612,7 +1627,7 @@
         <v>-0.84</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="18" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>JSWSTEEL</t>
@@ -1658,7 +1673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="18" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
           <t>TORNTPHARM</t>
@@ -1706,7 +1721,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="18" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t>TVSMOTOR</t>
@@ -1754,7 +1769,7 @@
         <v>1.26</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="18" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
           <t>VEDL</t>
@@ -1811,7 +1826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1826,9 +1841,10 @@
     <col width="27" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
+    <col hidden="1" width="28" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Ticker</t>
@@ -1889,296 +1905,297 @@
           <t>PnL_%</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Week_Range</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Week Range: (21-09-2026 to 27-09-2026)</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="n"/>
+      <c r="C2" s="8" t="n"/>
+      <c r="D2" s="8" t="n"/>
+      <c r="E2" s="8" t="n"/>
+      <c r="F2" s="8" t="n"/>
+      <c r="G2" s="8" t="n"/>
+      <c r="H2" s="8" t="n"/>
+      <c r="I2" s="8" t="n"/>
+      <c r="J2" s="8" t="n"/>
+      <c r="K2" s="8" t="n"/>
+      <c r="L2" s="8" t="n"/>
+      <c r="M2" s="8" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>1832.1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1824</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>1835.7</v>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>0.64% (11.7)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>1847.4</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>1859.1</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23 09:15</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23 09:15</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>1859.1</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>(21-09-2026 to 27-09-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>TATACONSUM</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B4" s="2" t="n">
         <v>986</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C4" s="3" t="n">
         <v>984.1</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D4" s="4" t="n">
         <v>991</v>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>0.7% (6.9)</t>
         </is>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="F4" s="4" t="n">
         <v>997.9</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="G4" s="4" t="n">
         <v>1004.8</v>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2026-09-23 11:00</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>2026-09-24 09:15 (Active)</t>
         </is>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K4" s="2" t="n">
         <v>989.8</v>
       </c>
-      <c r="L2" s="4" t="n">
+      <c r="L4" s="4" t="n">
         <v>-0.12</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>(21-09-2026 to 27-09-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>1818.6</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1813</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>1832.8</v>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>1.08% (19.8)</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>1852.6</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>1872.4</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23 14:15</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 10:00 (Active)</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>1816.2</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>(21-09-2026 to 27-09-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>ICICIBANK</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B6" s="2" t="n">
         <v>1338.9</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C6" s="3" t="n">
         <v>1331.3</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D6" s="4" t="n">
         <v>1342.3</v>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>0.82% (11.0)</t>
         </is>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F6" s="4" t="n">
         <v>1353.3</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>1364.3</v>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2026-09-24 09:30</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>2026-09-24 09:45 (Active)</t>
         </is>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="K6" s="2" t="n">
         <v>1342.6</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="L6" s="4" t="n">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>BHARTIARTL</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>1818.6</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>1813</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>1832.8</v>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>1.08% (19.8)</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>1852.6</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>1872.4</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-23 14:15</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>(21-09-2026 to 27-09-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>RECLTD</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>308.5</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>307.1</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>308.85</v>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>0.57% (1.75)</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>310.6</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>312.35</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24 10:00</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>2026-09-24 10:00 (Active)</t>
         </is>
       </c>
-      <c r="K4" s="2" t="n">
-        <v>1816.2</v>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v>-0.91</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>RECLTD</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>308.5</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>307.1</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>308.85</v>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>0.57% (1.75)</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>310.6</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>312.35</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-24 10:00</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-24 10:00 (Active)</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="n">
+      <c r="K7" s="2" t="n">
         <v>309.3</v>
       </c>
-      <c r="L5" s="4" t="n">
+      <c r="L7" s="4" t="n">
         <v>0.15</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>RECLTD</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>308.5</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>307.1</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>308.85</v>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>0.57% (1.75)</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>310.6</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>312.35</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-24 12:30</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-24 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>308.25</v>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>-0.19</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>BAJAJFINSV</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>1832.1</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>1824</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>1835.7</v>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>0.64% (11.7)</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>1847.4</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>1859.1</v>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-23 09:15</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-23 09:15</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>1859.1</v>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v>1.27</v>
-      </c>
-    </row>
-    <row r="8">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>(21-09-2026 to 27-09-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>GRASIM</t>
@@ -2225,36 +2242,41 @@
       <c r="L8" s="4" t="n">
         <v>0.44</v>
       </c>
-    </row>
-    <row r="9">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>(21-09-2026 to 27-09-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>3029.5</v>
+        <v>308.5</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2967.1</v>
+        <v>307.1</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>3039</v>
+        <v>308.85</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>2.37% (71.9)</t>
+          <t>0.57% (1.75)</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>3110.9</v>
+        <v>310.6</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3182.8</v>
+        <v>312.35</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 14:15</t>
+          <t>2026-09-24 12:30</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -2264,17 +2286,22 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:00 (Active)</t>
+          <t>2026-09-24 15:15 (Active)</t>
         </is>
       </c>
       <c r="K9" s="2" t="n">
-        <v>3035</v>
+        <v>308.25</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.13</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>-0.19</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>(21-09-2026 to 27-09-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>RECLTD</t>
@@ -2321,1064 +2348,1145 @@
       <c r="L10" s="4" t="n">
         <v>1.13</v>
       </c>
-    </row>
-    <row r="11">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>(21-09-2026 to 27-09-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>1242.8</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>1202.6</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>1246</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>3.48% (43.4)</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>1289.4</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>1332.8</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:00</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>1254.8</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>(21-09-2026 to 27-09-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>HINDUNILVR</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B12" s="2" t="n">
         <v>1927</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="C12" s="3" t="n">
         <v>1915.1</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D12" s="4" t="n">
         <v>1935.1</v>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>1.03% (20.0)</t>
         </is>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F12" s="4" t="n">
         <v>1955.1</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>1975.1</v>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2026-09-25 14:00</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>2026-09-25 15:15 (Active)</t>
         </is>
       </c>
-      <c r="K11" s="2" t="n">
+      <c r="K12" s="2" t="n">
         <v>1942.9</v>
       </c>
-      <c r="L11" s="4" t="n">
+      <c r="L12" s="4" t="n">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>(21-09-2026 to 27-09-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>ADANIPOWER</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B13" s="2" t="n">
         <v>200.4</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C13" s="3" t="n">
         <v>196.1</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D13" s="4" t="n">
         <v>203.34</v>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>3.56% (7.24)</t>
         </is>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F13" s="4" t="n">
         <v>210.58</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>217.82</v>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>2026-09-25 14:15</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>2026-09-25 15:15 (Active)</t>
         </is>
       </c>
-      <c r="K12" s="2" t="n">
+      <c r="K13" s="2" t="n">
         <v>202.75</v>
       </c>
-      <c r="L12" s="4" t="n">
+      <c r="L13" s="4" t="n">
         <v>-0.29</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>NAUKRI</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>1242.8</v>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>1202.6</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>1246</v>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>3.48% (43.4)</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>1289.4</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>1332.8</v>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-25 14:00</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>(21-09-2026 to 27-09-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>3029.5</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>2967.1</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>3039</v>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>2.37% (71.9)</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>3110.9</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>3182.8</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:15</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-25 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>1254.8</v>
-      </c>
-      <c r="L13" s="4" t="n">
-        <v>0.71</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 15:00 (Active)</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>3035</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>(21-09-2026 to 27-09-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Week Range: (28-09-2026 to 04-10-2026)</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="8" t="n"/>
+      <c r="G15" s="8" t="n"/>
+      <c r="H15" s="8" t="n"/>
+      <c r="I15" s="8" t="n"/>
+      <c r="J15" s="8" t="n"/>
+      <c r="K15" s="8" t="n"/>
+      <c r="L15" s="8" t="n"/>
+      <c r="M15" s="8" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>8821.5</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>8804.5</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>8893</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>1.0% (88.5)</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>8981.5</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>9070</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 10:00</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:00</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>8804.5</v>
+      </c>
+      <c r="L16" s="4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>(28-09-2026 to 04-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>991.6</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>986.6</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>993.4</v>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>0.68% (6.8)</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>1000.2</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>1007</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 11:30</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:30</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>1007</v>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>(28-09-2026 to 04-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>GODREJCP</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>864.2</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>859.7</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>864.8</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>0.59% (5.1)</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>869.9</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>875</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:00</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Then SL)</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:30</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>859.7</v>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>(28-09-2026 to 04-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>11975</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>11945</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>12020</v>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>0.62% (75.0)</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>12095</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>12170</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:15</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:00 (Active)</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>12008</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>(28-09-2026 to 04-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>4883</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>4869</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>4902.5</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>0.68% (33.5)</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>4936</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>4969.5</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:45</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:30</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>4869</v>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>(28-09-2026 to 04-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>399.3</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>396</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>402</v>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>1.49% (6.0)</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>408</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>414</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:00</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>401.55</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>(28-09-2026 to 04-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>GAIL</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B22" s="2" t="n">
         <v>171.35</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C22" s="3" t="n">
         <v>171.05</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D22" s="4" t="n">
         <v>172.2</v>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>0.67% (1.15)</t>
         </is>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="F22" s="4" t="n">
         <v>173.35</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G22" s="4" t="n">
         <v>174.5</v>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>2026-09-28 15:15</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>2026-09-28 15:15 (Active)</t>
         </is>
       </c>
-      <c r="K14" s="2" t="n">
+      <c r="K22" s="2" t="n">
         <v>172.45</v>
       </c>
-      <c r="L14" s="4" t="n">
+      <c r="L22" s="4" t="n">
         <v>0.15</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>INFY</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>991.6</v>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>986.6</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>993.4</v>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>0.68% (6.8)</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>1000.2</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>1007</v>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 11:30</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 13:30</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>1007</v>
-      </c>
-      <c r="L15" s="4" t="n">
-        <v>1.37</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>(28-09-2026 to 04-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>INDUSINDBK</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>906.9</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>889.7</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>907.5</v>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>1.96% (17.8)</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>925.3</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>943.1</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:15</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:15</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>889.7</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>(28-09-2026 to 04-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>4057</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>4043.3</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>4095</v>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>1.26% (51.7)</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>4146.7</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>4198.4</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:30</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:30</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>4146.7</v>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>(28-09-2026 to 04-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>2391</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>2381.6</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>2420</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>1.59% (38.4)</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>2458.4</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>2496.8</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:00</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>2415</v>
+      </c>
+      <c r="L25" s="4" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>(28-09-2026 to 04-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>1127.1</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>1127</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>1139.6</v>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>1.11% (12.6)</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>1152.2</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>1164.8</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:15</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:00 (Active)</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>1130</v>
+      </c>
+      <c r="L26" s="4" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>(28-09-2026 to 04-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>KOTAKBANK</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n">
+      <c r="B27" s="2" t="n">
         <v>399.3</v>
       </c>
-      <c r="C16" s="3" t="n">
-        <v>396</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>402</v>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>1.49% (6.0)</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>408</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>414</v>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 14:00</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="C27" s="3" t="n">
+        <v>394.7</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>403.65</v>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>2.22% (8.95)</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>412.6</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>421.55</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:30</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="n">
-        <v>401.55</v>
-      </c>
-      <c r="L16" s="4" t="n">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>406</v>
+      </c>
+      <c r="L27" s="4" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>(28-09-2026 to 04-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>1495.7</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>1487.1</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>1498</v>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>0.73% (10.9)</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>1508.9</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>1519.8</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:30</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 12:30</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>1487.1</v>
+      </c>
+      <c r="L28" s="4" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>(28-09-2026 to 04-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>263.55</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>263.3</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>266.2</v>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>1.09% (2.9)</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>269.1</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>272</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:45</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>265.1</v>
+      </c>
+      <c r="L29" s="4" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>(28-09-2026 to 04-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>MARUTI</t>
         </is>
       </c>
-      <c r="B17" s="2" t="n">
+      <c r="B30" s="2" t="n">
         <v>11975</v>
       </c>
-      <c r="C17" s="3" t="n">
-        <v>11945</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>12020</v>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>0.62% (75.0)</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>12095</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>12170</v>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 13:15</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="C30" s="3" t="n">
+        <v>11832</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>1.4% (168.0)</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>12168</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>12336</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 12:00</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 15:00 (Active)</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="n">
-        <v>12008</v>
-      </c>
-      <c r="L17" s="4" t="n">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>11877</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>(28-09-2026 to 04-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>ADANIPOWER</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n">
+      <c r="B31" s="2" t="n">
         <v>196.1</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="C31" s="3" t="n">
         <v>192.45</v>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D31" s="4" t="n">
         <v>196.67</v>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>2.15% (4.22)</t>
         </is>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="F31" s="4" t="n">
         <v>200.89</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="G31" s="4" t="n">
         <v>205.11</v>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 13:00</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 15:00 (Active)</t>
         </is>
       </c>
-      <c r="K18" s="2" t="n">
+      <c r="K31" s="2" t="n">
         <v>196.3</v>
       </c>
-      <c r="L18" s="4" t="n">
+      <c r="L31" s="4" t="n">
         <v>-0.19</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>APOLLOHOSP</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>8821.5</v>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>8804.5</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>8893</v>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>1.0% (88.5)</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>8981.5</v>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>9070</v>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 10:00</t>
-        </is>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 10:00</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="n">
-        <v>8804.5</v>
-      </c>
-      <c r="L19" s="4" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>(28-09-2026 to 04-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>BHEL</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n">
+      <c r="B32" s="2" t="n">
         <v>411.8</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="C32" s="3" t="n">
         <v>402.75</v>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D32" s="4" t="n">
         <v>411.9</v>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>2.22% (9.15)</t>
         </is>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="F32" s="4" t="n">
         <v>421.05</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="G32" s="4" t="n">
         <v>430.2</v>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 14:00</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 15:15 (Active)</t>
         </is>
       </c>
-      <c r="K20" s="2" t="n">
+      <c r="K32" s="2" t="n">
         <v>413.35</v>
       </c>
-      <c r="L20" s="4" t="n">
+      <c r="L32" s="4" t="n">
         <v>0.35</v>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>BRITANNIA</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>4883</v>
-      </c>
-      <c r="C21" s="3" t="n">
-        <v>4869</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>4902.5</v>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>0.68% (33.5)</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>4936</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>4969.5</v>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 13:45</t>
-        </is>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 09:30</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="n">
-        <v>4869</v>
-      </c>
-      <c r="L21" s="4" t="n">
-        <v>-0.68</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CHOLAFIN</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>1629.9</v>
-      </c>
-      <c r="C22" s="3" t="n">
-        <v>1600.2</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>1642.9</v>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>2.6% (42.7)</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="n">
-        <v>1685.6</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>1728.3</v>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 14:45</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="n">
-        <v>1627.3</v>
-      </c>
-      <c r="L22" s="4" t="n">
-        <v>-0.95</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>GODREJCP</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>864.2</v>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>859.7</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>864.8</v>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>0.59% (5.1)</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="n">
-        <v>869.9</v>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>875</v>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 12:00</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 09:30</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="n">
-        <v>859.7</v>
-      </c>
-      <c r="L23" s="4" t="n">
-        <v>-0.59</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>INDUSINDBK</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>906.9</v>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>889.7</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>907.5</v>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>1.96% (17.8)</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="n">
-        <v>925.3</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>943.1</v>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28 15:15</t>
-        </is>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 10:15</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="n">
-        <v>889.7</v>
-      </c>
-      <c r="L24" s="4" t="n">
-        <v>-1.96</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>KOTAKBANK</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>399.3</v>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>394.7</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>403.65</v>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>2.22% (8.95)</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="n">
-        <v>412.6</v>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>421.55</v>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 11:30</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="n">
-        <v>406</v>
-      </c>
-      <c r="L25" s="4" t="n">
-        <v>0.58</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>MARUTI</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>11975</v>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>11832</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>12000</v>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>1.4% (168.0)</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="n">
-        <v>12168</v>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>12336</v>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:00</t>
-        </is>
-      </c>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="n">
-        <v>11877</v>
-      </c>
-      <c r="L26" s="4" t="n">
-        <v>-1.03</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>PIDILITIND</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>1495.7</v>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>1487.1</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>1498</v>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>0.73% (10.9)</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="n">
-        <v>1508.9</v>
-      </c>
-      <c r="G27" s="4" t="n">
-        <v>1519.8</v>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 11:30</t>
-        </is>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:30</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="n">
-        <v>1487.1</v>
-      </c>
-      <c r="L27" s="4" t="n">
-        <v>-0.73</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>SHREECEM</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>22165</v>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>22025</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>22195</v>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>0.77% (170.0)</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="n">
-        <v>22365</v>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v>22535</v>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 14:45</t>
-        </is>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 15:00</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="n">
-        <v>22025</v>
-      </c>
-      <c r="L28" s="4" t="n">
-        <v>-0.77</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>ADANIPORTS</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>1766.7</v>
-      </c>
-      <c r="C29" s="3" t="n">
-        <v>1736.8</v>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>1770.1</v>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>1.88% (33.3)</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="n">
-        <v>1803.4</v>
-      </c>
-      <c r="G29" s="4" t="n">
-        <v>1836.7</v>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 15:00</t>
-        </is>
-      </c>
-      <c r="I29" s="7" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 15:15</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="n">
-        <v>1803.4</v>
-      </c>
-      <c r="L29" s="4" t="n">
-        <v>1.88</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>ASIANPAINT</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>2391</v>
-      </c>
-      <c r="C30" s="3" t="n">
-        <v>2381.6</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>2420</v>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>1.59% (38.4)</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="n">
-        <v>2458.4</v>
-      </c>
-      <c r="G30" s="4" t="n">
-        <v>2496.8</v>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 11:00</t>
-        </is>
-      </c>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="n">
-        <v>2415</v>
-      </c>
-      <c r="L30" s="4" t="n">
-        <v>-0.21</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>ITC</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>263.55</v>
-      </c>
-      <c r="C31" s="3" t="n">
-        <v>263.3</v>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>266.2</v>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>1.09% (2.9)</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="n">
-        <v>269.1</v>
-      </c>
-      <c r="G31" s="4" t="n">
-        <v>272</v>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 11:45</t>
-        </is>
-      </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="n">
-        <v>265.1</v>
-      </c>
-      <c r="L31" s="4" t="n">
-        <v>-0.41</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>JINDALSTEL</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>1127.1</v>
-      </c>
-      <c r="C32" s="3" t="n">
-        <v>1127</v>
-      </c>
-      <c r="D32" s="4" t="n">
-        <v>1139.6</v>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>1.11% (12.6)</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="n">
-        <v>1152.2</v>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>1164.8</v>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 11:15</t>
-        </is>
-      </c>
-      <c r="I32" s="5" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 15:00 (Active)</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="n">
-        <v>1130</v>
-      </c>
-      <c r="L32" s="4" t="n">
-        <v>-0.84</v>
-      </c>
-    </row>
-    <row r="33">
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>(28-09-2026 to 04-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
           <t>TORNTPHARM</t>
@@ -3425,56 +3533,176 @@
       <c r="L33" s="4" t="n">
         <v>1.44</v>
       </c>
-    </row>
-    <row r="34">
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>(28-09-2026 to 04-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>4057</v>
+        <v>22165</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>4043.3</v>
+        <v>22025</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>4095</v>
+        <v>22195</v>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>1.26% (51.7)</t>
+          <t>0.77% (170.0)</t>
         </is>
       </c>
       <c r="F34" s="4" t="n">
-        <v>4146.7</v>
+        <v>22365</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>4198.4</v>
+        <v>22535</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 09:30</t>
-        </is>
-      </c>
-      <c r="I34" s="7" t="inlineStr">
+          <t>2026-09-29 14:45</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:00</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>22025</v>
+      </c>
+      <c r="L34" s="4" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>(28-09-2026 to 04-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>1629.9</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>1600.2</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>1642.9</v>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>2.6% (42.7)</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>1685.6</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>1728.3</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:45</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>1627.3</v>
+      </c>
+      <c r="L35" s="4" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>(28-09-2026 to 04-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>1766.7</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>1736.8</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>1770.1</v>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>1.88% (33.3)</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>1803.4</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>1836.7</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:00</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 11:30</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="n">
-        <v>4146.7</v>
-      </c>
-      <c r="L34" s="4" t="n">
-        <v>1.26</v>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:15</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>1803.4</v>
+      </c>
+      <c r="L36" s="4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>(28-09-2026 to 04-10-2026)</t>
+        </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A15:M15"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/trade_tracker_results.xlsx
+++ b/data/trade_tracker_results.xlsx
@@ -629,7 +629,7 @@
       <c r="K2" s="2" t="n">
         <v>196.3</v>
       </c>
-      <c r="L2" s="4" t="n">
+      <c r="L2" s="3" t="n">
         <v>-0.19</v>
       </c>
     </row>
@@ -677,7 +677,7 @@
       <c r="K3" s="2" t="n">
         <v>8804.5</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="L3" s="3" t="n">
         <v>-1</v>
       </c>
     </row>
@@ -773,7 +773,7 @@
       <c r="K5" s="2" t="n">
         <v>4869</v>
       </c>
-      <c r="L5" s="4" t="n">
+      <c r="L5" s="3" t="n">
         <v>-0.68</v>
       </c>
     </row>
@@ -821,7 +821,7 @@
       <c r="K6" s="2" t="n">
         <v>1627.3</v>
       </c>
-      <c r="L6" s="4" t="n">
+      <c r="L6" s="3" t="n">
         <v>-0.95</v>
       </c>
     </row>
@@ -961,7 +961,7 @@
       <c r="K9" s="2" t="n">
         <v>859.7</v>
       </c>
-      <c r="L9" s="4" t="n">
+      <c r="L9" s="3" t="n">
         <v>-0.59</v>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       <c r="K10" s="2" t="n">
         <v>889.7</v>
       </c>
-      <c r="L10" s="4" t="n">
+      <c r="L10" s="3" t="n">
         <v>-1.96</v>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       <c r="K13" s="2" t="n">
         <v>11877</v>
       </c>
-      <c r="L13" s="4" t="n">
+      <c r="L13" s="3" t="n">
         <v>-1.03</v>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       <c r="K14" s="2" t="n">
         <v>1487.1</v>
       </c>
-      <c r="L14" s="4" t="n">
+      <c r="L14" s="3" t="n">
         <v>-0.73</v>
       </c>
     </row>
@@ -1247,7 +1247,7 @@
       <c r="K15" s="2" t="n">
         <v>22025</v>
       </c>
-      <c r="L15" s="4" t="n">
+      <c r="L15" s="3" t="n">
         <v>-0.77</v>
       </c>
     </row>
@@ -1481,7 +1481,7 @@
       <c r="K20" s="2" t="n">
         <v>2415</v>
       </c>
-      <c r="L20" s="4" t="n">
+      <c r="L20" s="3" t="n">
         <v>-0.21</v>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
       <c r="K22" s="2" t="n">
         <v>265.1</v>
       </c>
-      <c r="L22" s="4" t="n">
+      <c r="L22" s="3" t="n">
         <v>-0.41</v>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
       <c r="K23" s="2" t="n">
         <v>1130</v>
       </c>
-      <c r="L23" s="4" t="n">
+      <c r="L23" s="3" t="n">
         <v>-0.84</v>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="33" customWidth="1" min="9" max="9"/>
-    <col width="27" customWidth="1" min="10" max="10"/>
+    <col width="29" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
     <col hidden="1" width="28" customWidth="1" min="13" max="13"/>
@@ -2016,18 +2016,18 @@
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 09:15 (Active)</t>
+          <t>2026-09-24 09:15 (Week End)</t>
         </is>
       </c>
       <c r="K4" s="2" t="n">
         <v>989.8</v>
       </c>
-      <c r="L4" s="4" t="n">
+      <c r="L4" s="3" t="n">
         <v>-0.12</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -2069,18 +2069,18 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 10:00 (Active)</t>
+          <t>2026-09-24 10:00 (Week End)</t>
         </is>
       </c>
       <c r="K5" s="2" t="n">
         <v>1816.2</v>
       </c>
-      <c r="L5" s="4" t="n">
+      <c r="L5" s="3" t="n">
         <v>-0.91</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2122,12 +2122,12 @@
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 09:45 (Active)</t>
+          <t>2026-09-24 09:45 (Week End)</t>
         </is>
       </c>
       <c r="K6" s="2" t="n">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 10:00 (Active)</t>
+          <t>2026-09-24 10:00 (Week End)</t>
         </is>
       </c>
       <c r="K7" s="2" t="n">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:15 (Active)</t>
+          <t>2026-09-25 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K8" s="2" t="n">
@@ -2281,18 +2281,18 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24 15:15 (Active)</t>
+          <t>2026-09-24 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K9" s="2" t="n">
         <v>308.25</v>
       </c>
-      <c r="L9" s="4" t="n">
+      <c r="L9" s="3" t="n">
         <v>-0.19</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -2357,28 +2357,28 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>1242.8</v>
+        <v>1927</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1202.6</v>
+        <v>1915.1</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1246</v>
+        <v>1935.1</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>3.48% (43.4)</t>
+          <t>1.03% (20.0)</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1289.4</v>
+        <v>1955.1</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1332.8</v>
+        <v>1975.1</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -2387,19 +2387,19 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:15 (Active)</t>
+          <t>2026-09-25 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1254.8</v>
+        <v>1942.9</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.71</v>
+        <v>0.4</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
@@ -2410,28 +2410,28 @@
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>1927</v>
+        <v>1242.8</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1915.1</v>
+        <v>1202.6</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1935.1</v>
+        <v>1246</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>1.03% (20.0)</t>
+          <t>3.48% (43.4)</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1955.1</v>
+        <v>1289.4</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1975.1</v>
+        <v>1332.8</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -2440,19 +2440,19 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:15 (Active)</t>
+          <t>2026-09-25 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1942.9</v>
+        <v>1254.8</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.4</v>
+        <v>0.71</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
@@ -2493,18 +2493,18 @@
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:15 (Active)</t>
+          <t>2026-09-25 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K13" s="2" t="n">
         <v>202.75</v>
       </c>
-      <c r="L13" s="4" t="n">
+      <c r="L13" s="3" t="n">
         <v>-0.29</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -2546,18 +2546,18 @@
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:00 (Active)</t>
+          <t>2026-09-25 15:00 (Week End)</t>
         </is>
       </c>
       <c r="K14" s="2" t="n">
         <v>3035</v>
       </c>
-      <c r="L14" s="4" t="n">
+      <c r="L14" s="3" t="n">
         <v>-0.13</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -2629,7 +2629,7 @@
       <c r="K16" s="2" t="n">
         <v>8804.5</v>
       </c>
-      <c r="L16" s="4" t="n">
+      <c r="L16" s="3" t="n">
         <v>-1</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
       <c r="K18" s="2" t="n">
         <v>859.7</v>
       </c>
-      <c r="L18" s="4" t="n">
+      <c r="L18" s="3" t="n">
         <v>-0.59</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -2788,7 +2788,7 @@
       <c r="K19" s="2" t="n">
         <v>12008</v>
       </c>
-      <c r="L19" s="4" t="n">
+      <c r="L19" s="3" t="n">
         <v>-0.1</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       <c r="K20" s="2" t="n">
         <v>4869</v>
       </c>
-      <c r="L20" s="4" t="n">
+      <c r="L20" s="3" t="n">
         <v>-0.68</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2894,7 +2894,7 @@
       <c r="K21" s="2" t="n">
         <v>401.55</v>
       </c>
-      <c r="L21" s="4" t="n">
+      <c r="L21" s="3" t="n">
         <v>-0.11</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -3000,7 +3000,7 @@
       <c r="K23" s="2" t="n">
         <v>889.7</v>
       </c>
-      <c r="L23" s="4" t="n">
+      <c r="L23" s="3" t="n">
         <v>-1.96</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -3106,7 +3106,7 @@
       <c r="K25" s="2" t="n">
         <v>2415</v>
       </c>
-      <c r="L25" s="4" t="n">
+      <c r="L25" s="3" t="n">
         <v>-0.21</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -3159,7 +3159,7 @@
       <c r="K26" s="2" t="n">
         <v>1130</v>
       </c>
-      <c r="L26" s="4" t="n">
+      <c r="L26" s="3" t="n">
         <v>-0.84</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3265,7 +3265,7 @@
       <c r="K28" s="2" t="n">
         <v>1487.1</v>
       </c>
-      <c r="L28" s="4" t="n">
+      <c r="L28" s="3" t="n">
         <v>-0.73</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       <c r="K29" s="2" t="n">
         <v>265.1</v>
       </c>
-      <c r="L29" s="4" t="n">
+      <c r="L29" s="3" t="n">
         <v>-0.41</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -3371,7 +3371,7 @@
       <c r="K30" s="2" t="n">
         <v>11877</v>
       </c>
-      <c r="L30" s="4" t="n">
+      <c r="L30" s="3" t="n">
         <v>-1.03</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       <c r="K31" s="2" t="n">
         <v>196.3</v>
       </c>
-      <c r="L31" s="4" t="n">
+      <c r="L31" s="3" t="n">
         <v>-0.19</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -3583,7 +3583,7 @@
       <c r="K34" s="2" t="n">
         <v>22025</v>
       </c>
-      <c r="L34" s="4" t="n">
+      <c r="L34" s="3" t="n">
         <v>-0.77</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       <c r="K35" s="2" t="n">
         <v>1627.3</v>
       </c>
-      <c r="L35" s="4" t="n">
+      <c r="L35" s="3" t="n">
         <v>-0.95</v>
       </c>
       <c r="M35" s="2" t="inlineStr">

--- a/data/trade_tracker_results.xlsx
+++ b/data/trade_tracker_results.xlsx
@@ -74,12 +74,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
         <bgColor rgb="00FFC7CE"/>
       </patternFill>
@@ -94,6 +88,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
         <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -129,16 +129,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -517,8 +517,8 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="33" customWidth="1" min="9" max="9"/>
-    <col width="27" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
   </cols>
@@ -613,24 +613,22 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:00</t>
-        </is>
-      </c>
-      <c r="I2" s="5" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:00 (Active)</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>196.3</v>
-      </c>
-      <c r="L2" s="3" t="n">
-        <v>-0.19</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
@@ -661,10 +659,10 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 10:00</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
+          <t>2026-09-29 09:15</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -709,24 +707,22 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 14:00</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>413.35</v>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="4" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -757,24 +753,22 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 13:45</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 09:30</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>4869</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>-0.68</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -805,24 +799,22 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 14:45</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>1627.3</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>-0.95</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -945,10 +937,10 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 12:00</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
+          <t>2026-09-29 09:15</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
@@ -993,10 +985,10 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 15:15</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
+          <t>2026-09-29 09:15</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -1087,24 +1079,22 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 11:30</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>406</v>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="4" t="n">
-        <v>0.58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -1135,24 +1125,22 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:00</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>11877</v>
-      </c>
-      <c r="L13" s="3" t="n">
-        <v>-1.03</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -1186,7 +1174,7 @@
           <t>2026-09-29 11:30</t>
         </is>
       </c>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -1231,24 +1219,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 14:45</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:00</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>22025</v>
-      </c>
-      <c r="L15" s="3" t="n">
-        <v>-0.77</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -1417,24 +1403,22 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:00</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:15</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="n">
-        <v>1803.4</v>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="4" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -1465,24 +1449,22 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 11:00</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="n">
-        <v>2415</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>-0.21</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -1559,24 +1541,22 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 11:45</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="n">
-        <v>265.1</v>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v>-0.41</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -1607,24 +1587,22 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 11:15</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:00 (Active)</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="n">
-        <v>1130</v>
-      </c>
-      <c r="L23" s="3" t="n">
-        <v>-0.84</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -1701,24 +1679,22 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 14:00</t>
-        </is>
-      </c>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 14:45</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="n">
-        <v>4942</v>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -1749,24 +1725,22 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 09:30</t>
-        </is>
-      </c>
-      <c r="I26" s="7" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 11:30</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="n">
-        <v>4146.7</v>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="4" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -1826,7 +1800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1912,23 +1886,23 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Week Range: (21-09-2026 to 27-09-2026)</t>
         </is>
       </c>
-      <c r="B2" s="8" t="n"/>
-      <c r="C2" s="8" t="n"/>
-      <c r="D2" s="8" t="n"/>
-      <c r="E2" s="8" t="n"/>
-      <c r="F2" s="8" t="n"/>
-      <c r="G2" s="8" t="n"/>
-      <c r="H2" s="8" t="n"/>
-      <c r="I2" s="8" t="n"/>
-      <c r="J2" s="8" t="n"/>
-      <c r="K2" s="8" t="n"/>
-      <c r="L2" s="8" t="n"/>
-      <c r="M2" s="8" t="n"/>
+      <c r="B2" s="7" t="n"/>
+      <c r="C2" s="7" t="n"/>
+      <c r="D2" s="7" t="n"/>
+      <c r="E2" s="7" t="n"/>
+      <c r="F2" s="7" t="n"/>
+      <c r="G2" s="7" t="n"/>
+      <c r="H2" s="7" t="n"/>
+      <c r="I2" s="7" t="n"/>
+      <c r="J2" s="7" t="n"/>
+      <c r="K2" s="7" t="n"/>
+      <c r="L2" s="7" t="n"/>
+      <c r="M2" s="7" t="n"/>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -1961,7 +1935,7 @@
           <t>2026-09-23 09:15</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -2014,7 +1988,7 @@
           <t>2026-09-23 11:00</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2067,7 +2041,7 @@
           <t>2026-09-23 14:15</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2120,7 +2094,7 @@
           <t>2026-09-24 09:30</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2173,7 +2147,7 @@
           <t>2026-09-24 10:00</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2226,7 +2200,7 @@
           <t>2026-09-24 10:00</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2279,7 +2253,7 @@
           <t>2026-09-24 12:30</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I9" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2332,7 +2306,7 @@
           <t>2026-09-25 10:00</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -2357,35 +2331,35 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>1927</v>
+        <v>1242.8</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1915.1</v>
+        <v>1202.6</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1935.1</v>
+        <v>1246</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>1.03% (20.0)</t>
+          <t>3.48% (43.4)</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1955.1</v>
+        <v>1289.4</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1975.1</v>
+        <v>1332.8</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
           <t>2026-09-25 14:00</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="I11" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2396,10 +2370,10 @@
         </is>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1942.9</v>
+        <v>1254.8</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.4</v>
+        <v>0.71</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
@@ -2410,35 +2384,35 @@
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>1242.8</v>
+        <v>1927</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1202.6</v>
+        <v>1915.1</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1246</v>
+        <v>1935.1</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>3.48% (43.4)</t>
+          <t>1.03% (20.0)</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1289.4</v>
+        <v>1955.1</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1332.8</v>
+        <v>1975.1</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2026-09-25 14:00</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2449,10 +2423,10 @@
         </is>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1254.8</v>
+        <v>1942.9</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.71</v>
+        <v>0.4</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
@@ -2491,7 +2465,7 @@
           <t>2026-09-25 14:15</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="I13" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2544,7 +2518,7 @@
           <t>2026-09-25 14:15</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2567,23 +2541,23 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>Week Range: (28-09-2026 to 04-10-2026)</t>
         </is>
       </c>
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="n"/>
-      <c r="E15" s="8" t="n"/>
-      <c r="F15" s="8" t="n"/>
-      <c r="G15" s="8" t="n"/>
-      <c r="H15" s="8" t="n"/>
-      <c r="I15" s="8" t="n"/>
-      <c r="J15" s="8" t="n"/>
-      <c r="K15" s="8" t="n"/>
-      <c r="L15" s="8" t="n"/>
-      <c r="M15" s="8" t="n"/>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="7" t="n"/>
+      <c r="I15" s="7" t="n"/>
+      <c r="J15" s="7" t="n"/>
+      <c r="K15" s="7" t="n"/>
+      <c r="L15" s="7" t="n"/>
+      <c r="M15" s="7" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -2616,7 +2590,7 @@
           <t>2026-09-28 10:00</t>
         </is>
       </c>
-      <c r="I16" s="6" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -2669,7 +2643,7 @@
           <t>2026-09-28 11:30</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -2722,7 +2696,7 @@
           <t>2026-09-28 12:00</t>
         </is>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
@@ -2775,7 +2749,7 @@
           <t>2026-09-28 13:15</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="I19" s="8" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -2828,7 +2802,7 @@
           <t>2026-09-28 13:45</t>
         </is>
       </c>
-      <c r="I20" s="6" t="inlineStr">
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -2881,7 +2855,7 @@
           <t>2026-09-28 14:00</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I21" s="8" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -2934,7 +2908,7 @@
           <t>2026-09-28 15:15</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="I22" s="8" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -2987,7 +2961,7 @@
           <t>2026-09-28 15:15</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -3012,49 +2986,49 @@
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>4057</v>
+        <v>864.2</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>4043.3</v>
+        <v>859.7</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>4095</v>
+        <v>864.8</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>1.26% (51.7)</t>
+          <t>0.59% (5.1)</t>
         </is>
       </c>
       <c r="F24" s="4" t="n">
-        <v>4146.7</v>
+        <v>869.9</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>4198.4</v>
+        <v>875</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
+          <t>2026-09-29 09:15</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Then SL)</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>2026-09-29 09:30</t>
         </is>
       </c>
-      <c r="I24" s="7" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 11:30</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="n">
-        <v>4146.7</v>
-      </c>
-      <c r="L24" s="4" t="n">
-        <v>1.26</v>
+        <v>859.7</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>-0.59</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
@@ -3065,49 +3039,49 @@
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>2391</v>
+        <v>8821.5</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>2381.6</v>
+        <v>8804.5</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2420</v>
+        <v>8893</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>1.59% (38.4)</t>
+          <t>1.0% (88.5)</t>
         </is>
       </c>
       <c r="F25" s="4" t="n">
-        <v>2458.4</v>
+        <v>8981.5</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2496.8</v>
+        <v>9070</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 11:00</t>
+          <t>2026-09-29 09:15</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:15 (Active)</t>
+          <t>2026-09-29 10:00</t>
         </is>
       </c>
       <c r="K25" s="2" t="n">
-        <v>2415</v>
+        <v>8804.5</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>-0.21</v>
+        <v>-1</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
@@ -3118,49 +3092,49 @@
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>1127.1</v>
+        <v>906.9</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>1127</v>
+        <v>889.7</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1139.6</v>
+        <v>907.5</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>1.11% (12.6)</t>
+          <t>1.96% (17.8)</t>
         </is>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1152.2</v>
+        <v>925.3</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1164.8</v>
+        <v>943.1</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 11:15</t>
+          <t>2026-09-29 09:15</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:00 (Active)</t>
+          <t>2026-09-29 10:15</t>
         </is>
       </c>
       <c r="K26" s="2" t="n">
-        <v>1130</v>
+        <v>889.7</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-0.84</v>
+        <v>-1.96</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
@@ -3171,49 +3145,49 @@
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>399.3</v>
+        <v>4057</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>394.7</v>
+        <v>4043.3</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>403.65</v>
+        <v>4095</v>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>2.22% (8.95)</t>
+          <t>1.26% (51.7)</t>
         </is>
       </c>
       <c r="F27" s="4" t="n">
-        <v>412.6</v>
+        <v>4146.7</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>421.55</v>
+        <v>4198.4</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
+          <t>2026-09-29 09:30</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>2026-09-29 11:30</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 15:15 (Active)</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="n">
-        <v>406</v>
+        <v>4146.7</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.58</v>
+        <v>1.26</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
@@ -3224,49 +3198,49 @@
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>1495.7</v>
+        <v>2391</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1487.1</v>
+        <v>2381.6</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1498</v>
+        <v>2420</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>0.73% (10.9)</t>
+          <t>1.59% (38.4)</t>
         </is>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1508.9</v>
+        <v>2458.4</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>1519.8</v>
+        <v>2496.8</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 11:30</t>
-        </is>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+          <t>2026-09-29 11:00</t>
+        </is>
+      </c>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:30</t>
+          <t>2026-09-29 15:15 (Active)</t>
         </is>
       </c>
       <c r="K28" s="2" t="n">
-        <v>1487.1</v>
+        <v>2415</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>-0.73</v>
+        <v>-0.21</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
@@ -3277,49 +3251,49 @@
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>263.55</v>
+        <v>1127.1</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>263.3</v>
+        <v>1127</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>266.2</v>
+        <v>1139.6</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>1.09% (2.9)</t>
+          <t>1.11% (12.6)</t>
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>269.1</v>
+        <v>1152.2</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>272</v>
+        <v>1164.8</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 11:45</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
+          <t>2026-09-29 11:15</t>
+        </is>
+      </c>
+      <c r="I29" s="8" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:15 (Active)</t>
+          <t>2026-09-29 15:00 (Active)</t>
         </is>
       </c>
       <c r="K29" s="2" t="n">
-        <v>265.1</v>
+        <v>1130</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.84</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
@@ -3330,49 +3304,49 @@
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>11975</v>
+        <v>1495.7</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>11832</v>
+        <v>1487.1</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>12000</v>
+        <v>1498</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>1.4% (168.0)</t>
+          <t>0.73% (10.9)</t>
         </is>
       </c>
       <c r="F30" s="4" t="n">
-        <v>12168</v>
+        <v>1508.9</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>12336</v>
+        <v>1519.8</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:00</t>
+          <t>2026-09-29 11:30</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:15 (Active)</t>
+          <t>2026-09-29 12:30</t>
         </is>
       </c>
       <c r="K30" s="2" t="n">
-        <v>11877</v>
+        <v>1487.1</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-1.03</v>
+        <v>-0.73</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
@@ -3383,49 +3357,49 @@
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>196.1</v>
+        <v>399.3</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>192.45</v>
+        <v>394.7</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>196.67</v>
+        <v>403.65</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>2.15% (4.22)</t>
+          <t>2.22% (8.95)</t>
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>200.89</v>
+        <v>412.6</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>205.11</v>
+        <v>421.55</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 13:00</t>
-        </is>
-      </c>
-      <c r="I31" s="5" t="inlineStr">
+          <t>2026-09-29 11:30</t>
+        </is>
+      </c>
+      <c r="I31" s="8" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:00 (Active)</t>
+          <t>2026-09-29 15:15 (Active)</t>
         </is>
       </c>
       <c r="K31" s="2" t="n">
-        <v>196.3</v>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>-0.19</v>
+        <v>406</v>
+      </c>
+      <c r="L31" s="4" t="n">
+        <v>0.58</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
@@ -3436,35 +3410,35 @@
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>411.8</v>
+        <v>263.55</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>402.75</v>
+        <v>263.3</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>411.9</v>
+        <v>266.2</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>2.22% (9.15)</t>
+          <t>1.09% (2.9)</t>
         </is>
       </c>
       <c r="F32" s="4" t="n">
-        <v>421.05</v>
+        <v>269.1</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>430.2</v>
+        <v>272</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 14:00</t>
-        </is>
-      </c>
-      <c r="I32" s="5" t="inlineStr">
+          <t>2026-09-29 11:45</t>
+        </is>
+      </c>
+      <c r="I32" s="8" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -3475,10 +3449,10 @@
         </is>
       </c>
       <c r="K32" s="2" t="n">
-        <v>413.35</v>
-      </c>
-      <c r="L32" s="4" t="n">
-        <v>0.35</v>
+        <v>265.1</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>-0.41</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
@@ -3489,49 +3463,49 @@
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>4848.5</v>
+        <v>11975</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>4837</v>
+        <v>11832</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>4872</v>
+        <v>12000</v>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>0.72% (35.0)</t>
+          <t>1.4% (168.0)</t>
         </is>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4907</v>
+        <v>12168</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>4942</v>
+        <v>12336</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 14:00</t>
-        </is>
-      </c>
-      <c r="I33" s="7" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>2026-09-29 12:00</t>
+        </is>
+      </c>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 14:45</t>
+          <t>2026-09-29 15:15 (Active)</t>
         </is>
       </c>
       <c r="K33" s="2" t="n">
-        <v>4942</v>
-      </c>
-      <c r="L33" s="4" t="n">
-        <v>1.44</v>
+        <v>11877</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>-1.03</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
@@ -3542,49 +3516,49 @@
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>22165</v>
+        <v>196.1</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>22025</v>
+        <v>192.45</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>22195</v>
+        <v>196.67</v>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>0.77% (170.0)</t>
+          <t>2.15% (4.22)</t>
         </is>
       </c>
       <c r="F34" s="4" t="n">
-        <v>22365</v>
+        <v>200.89</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>22535</v>
+        <v>205.11</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 14:45</t>
-        </is>
-      </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+          <t>2026-09-29 13:00</t>
+        </is>
+      </c>
+      <c r="I34" s="8" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:00</t>
+          <t>2026-09-29 15:00 (Active)</t>
         </is>
       </c>
       <c r="K34" s="2" t="n">
-        <v>22025</v>
+        <v>196.3</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>-0.77</v>
+        <v>-0.19</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
@@ -3595,35 +3569,35 @@
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>1629.9</v>
+        <v>411.8</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>1600.2</v>
+        <v>402.75</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>1642.9</v>
+        <v>411.9</v>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>2.6% (42.7)</t>
+          <t>2.22% (9.15)</t>
         </is>
       </c>
       <c r="F35" s="4" t="n">
-        <v>1685.6</v>
+        <v>421.05</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>1728.3</v>
+        <v>430.2</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 14:45</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="inlineStr">
+          <t>2026-09-29 14:00</t>
+        </is>
+      </c>
+      <c r="I35" s="8" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -3634,10 +3608,10 @@
         </is>
       </c>
       <c r="K35" s="2" t="n">
-        <v>1627.3</v>
-      </c>
-      <c r="L35" s="3" t="n">
-        <v>-0.95</v>
+        <v>413.35</v>
+      </c>
+      <c r="L35" s="4" t="n">
+        <v>0.35</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
@@ -3648,51 +3622,210 @@
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>4848.5</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>4837</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>4872</v>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>0.72% (35.0)</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>4907</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>4942</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:00</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:45</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>4942</v>
+      </c>
+      <c r="L36" s="4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>(28-09-2026 to 04-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>SHREECEM</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>22165</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>22025</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>22195</v>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>0.77% (170.0)</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>22365</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>22535</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:45</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:00</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>22025</v>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>(28-09-2026 to 04-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>1629.9</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>1600.2</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>1642.9</v>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>2.6% (42.7)</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>1685.6</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>1728.3</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:45</t>
+        </is>
+      </c>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>1627.3</v>
+      </c>
+      <c r="L38" s="3" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>(28-09-2026 to 04-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
           <t>ADANIPORTS</t>
         </is>
       </c>
-      <c r="B36" s="2" t="n">
+      <c r="B39" s="2" t="n">
         <v>1766.7</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="C39" s="3" t="n">
         <v>1736.8</v>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="D39" s="4" t="n">
         <v>1770.1</v>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>1.88% (33.3)</t>
         </is>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="F39" s="4" t="n">
         <v>1803.4</v>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="G39" s="4" t="n">
         <v>1836.7</v>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 15:00</t>
         </is>
       </c>
-      <c r="I36" s="7" t="inlineStr">
+      <c r="I39" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="J39" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 15:15</t>
         </is>
       </c>
-      <c r="K36" s="2" t="n">
+      <c r="K39" s="2" t="n">
         <v>1803.4</v>
       </c>
-      <c r="L36" s="4" t="n">
+      <c r="L39" s="4" t="n">
         <v>1.88</v>
       </c>
-      <c r="M36" s="2" t="inlineStr">
+      <c r="M39" s="2" t="inlineStr">
         <is>
           <t>(28-09-2026 to 04-10-2026)</t>
         </is>

--- a/data/trade_tracker_results.xlsx
+++ b/data/trade_tracker_results.xlsx
@@ -74,26 +74,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
         <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
         <bgColor rgb="00D9E1F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -129,16 +129,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -506,19 +506,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="33" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
   </cols>
@@ -613,22 +613,24 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-09-30 09:15</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr"/>
+          <t>2026-09-30 09:15</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>200.89</v>
+      </c>
       <c r="L2" s="4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
@@ -662,7 +664,7 @@
           <t>2026-09-29 09:15</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -940,7 +942,7 @@
           <t>2026-09-29 09:15</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
@@ -988,7 +990,7 @@
           <t>2026-09-29 09:15</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -1033,22 +1035,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-09-30 09:15</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr"/>
+          <t>2026-09-30 09:45</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>1017.3</v>
+      </c>
       <c r="L11" s="4" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -1079,22 +1083,24 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-09-30 09:15</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr"/>
+          <t>2026-09-30 10:00</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>412.6</v>
+      </c>
       <c r="L12" s="4" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -1174,7 +1180,7 @@
           <t>2026-09-29 11:30</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -1201,21 +1207,21 @@
         <v>22165</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>22025</v>
+        <v>21585</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>22195</v>
+        <v>22340</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>0.77% (170.0)</t>
+          <t>3.38% (755.0)</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>22365</v>
+        <v>23095</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>22535</v>
+        <v>23850</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1403,22 +1409,24 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-09-30 09:15</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr"/>
+          <t>2026-09-30 12:30 (Active)</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>1789.3</v>
+      </c>
       <c r="L19" s="4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -1449,22 +1457,24 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-09-30 09:15</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="4" t="n">
-        <v>0</v>
+          <t>2026-09-30 12:30 (Active)</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>2409.1</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>-0.45</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -1541,22 +1551,24 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-09-30 09:15</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="4" t="n">
-        <v>0</v>
+          <t>2026-09-30 12:30 (Active)</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>265.5</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>-0.26</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -1569,21 +1581,21 @@
         <v>1127.1</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1127</v>
+        <v>1125.1</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1139.6</v>
+        <v>1149</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>1.11% (12.6)</t>
+          <t>2.08% (23.9)</t>
         </is>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1152.2</v>
+        <v>1172.9</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1164.8</v>
+        <v>1196.8</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1679,22 +1691,24 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-09-30 09:15</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="4" t="n">
-        <v>0</v>
+          <t>2026-09-30 10:30</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>4837</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>-0.72</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -1725,22 +1739,24 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-09-30 09:15</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr"/>
+          <t>2026-09-30 09:45</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>4146.7</v>
+      </c>
       <c r="L26" s="4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -1786,6 +1802,882 @@
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>1315</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>1275.8</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>1316.9</v>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>3.12% (41.1)</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>1358</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>1399.1</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>1270.2</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>1223.9</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>1277</v>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>4.16% (53.1)</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>1330.1</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>1383.2</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>10738</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>10600</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>10809</v>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>1.93% (209.0)</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>11018</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>11227</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>BANKBARODA</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>232.52</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>223.95</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>234.94</v>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>4.68% (10.99)</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>245.93</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>256.92</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>388.6</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>382.25</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>393.1</v>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>2.76% (10.85)</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>403.95</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>414.8</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>47145</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>45700</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>47165</v>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>3.11% (1465.0)</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>48630</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>50095</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>DABUR</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>381.55</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>378.05</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>386.25</v>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>2.12% (8.2)</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>394.45</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>402.65</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>9312.5</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>9280</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>9400</v>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>1.28% (120.0)</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>9520</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>9640</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>1234.6</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>1222</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>1241.6</v>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>1.58% (19.6)</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>1261.2</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>1280.8</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>514</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>513.5</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>516.1</v>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>0.5% (2.6)</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>518.7</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>521.3</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>1312</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>1291.1</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>1312.6</v>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>1.64% (21.5)</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>1334.1</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>1355.6</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>ICICIPRULI</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>445.35</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>442.8</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>447.8</v>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>1.12% (5.0)</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>452.8</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>457.8</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>721.95</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>704.8</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>726.45</v>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>2.98% (21.65)</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>748.1</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>769.75</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>457.7</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>448.55</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>458.65</v>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>2.2% (10.1)</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>468.75</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>478.85</v>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>LTM</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>3996</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>3936</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>4183.6</v>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>5.92% (247.6)</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>4431.2</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>4678.8</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>160.5</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>159.41</v>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>162.37</v>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>1.82% (2.96)</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>165.33</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>168.29</v>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:30 (Active)</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>163.25</v>
+      </c>
+      <c r="L43" s="4" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>1832.2</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>1814.2</v>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>1841.1</v>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>1.46% (26.9)</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>1868</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>1894.9</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>1525.1</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>1510.5</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>1540.5</v>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>1.95% (30.0)</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>1570.5</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>1600.5</v>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>1152.1</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>1149.5</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>1221.1</v>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>5.86% (71.6)</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>1292.7</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>1364.3</v>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1800,7 +2692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1886,23 +2778,23 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Week Range: (21-09-2026 to 27-09-2026)</t>
         </is>
       </c>
-      <c r="B2" s="7" t="n"/>
-      <c r="C2" s="7" t="n"/>
-      <c r="D2" s="7" t="n"/>
-      <c r="E2" s="7" t="n"/>
-      <c r="F2" s="7" t="n"/>
-      <c r="G2" s="7" t="n"/>
-      <c r="H2" s="7" t="n"/>
-      <c r="I2" s="7" t="n"/>
-      <c r="J2" s="7" t="n"/>
-      <c r="K2" s="7" t="n"/>
-      <c r="L2" s="7" t="n"/>
-      <c r="M2" s="7" t="n"/>
+      <c r="B2" s="8" t="n"/>
+      <c r="C2" s="8" t="n"/>
+      <c r="D2" s="8" t="n"/>
+      <c r="E2" s="8" t="n"/>
+      <c r="F2" s="8" t="n"/>
+      <c r="G2" s="8" t="n"/>
+      <c r="H2" s="8" t="n"/>
+      <c r="I2" s="8" t="n"/>
+      <c r="J2" s="8" t="n"/>
+      <c r="K2" s="8" t="n"/>
+      <c r="L2" s="8" t="n"/>
+      <c r="M2" s="8" t="n"/>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -1935,7 +2827,7 @@
           <t>2026-09-23 09:15</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -1988,7 +2880,7 @@
           <t>2026-09-23 11:00</t>
         </is>
       </c>
-      <c r="I4" s="8" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2041,7 +2933,7 @@
           <t>2026-09-23 14:15</t>
         </is>
       </c>
-      <c r="I5" s="8" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2094,7 +2986,7 @@
           <t>2026-09-24 09:30</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2147,7 +3039,7 @@
           <t>2026-09-24 10:00</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2200,7 +3092,7 @@
           <t>2026-09-24 10:00</t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2253,7 +3145,7 @@
           <t>2026-09-24 12:30</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2306,7 +3198,7 @@
           <t>2026-09-25 10:00</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -2359,7 +3251,7 @@
           <t>2026-09-25 14:00</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2412,7 +3304,7 @@
           <t>2026-09-25 14:00</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2465,7 +3357,7 @@
           <t>2026-09-25 14:15</t>
         </is>
       </c>
-      <c r="I13" s="8" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2518,7 +3410,7 @@
           <t>2026-09-25 14:15</t>
         </is>
       </c>
-      <c r="I14" s="8" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2541,23 +3433,23 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>Week Range: (28-09-2026 to 04-10-2026)</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="n"/>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="7" t="n"/>
-      <c r="I15" s="7" t="n"/>
-      <c r="J15" s="7" t="n"/>
-      <c r="K15" s="7" t="n"/>
-      <c r="L15" s="7" t="n"/>
-      <c r="M15" s="7" t="n"/>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="8" t="n"/>
+      <c r="G15" s="8" t="n"/>
+      <c r="H15" s="8" t="n"/>
+      <c r="I15" s="8" t="n"/>
+      <c r="J15" s="8" t="n"/>
+      <c r="K15" s="8" t="n"/>
+      <c r="L15" s="8" t="n"/>
+      <c r="M15" s="8" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -2590,7 +3482,7 @@
           <t>2026-09-28 10:00</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I16" s="6" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -2643,7 +3535,7 @@
           <t>2026-09-28 11:30</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -2696,7 +3588,7 @@
           <t>2026-09-28 12:00</t>
         </is>
       </c>
-      <c r="I18" s="6" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
@@ -2749,7 +3641,7 @@
           <t>2026-09-28 13:15</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -2802,7 +3694,7 @@
           <t>2026-09-28 13:45</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I20" s="6" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -2855,7 +3747,7 @@
           <t>2026-09-28 14:00</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr">
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -2908,7 +3800,7 @@
           <t>2026-09-28 15:15</t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr">
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -2961,7 +3853,7 @@
           <t>2026-09-28 15:15</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="I23" s="6" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -2986,28 +3878,28 @@
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>864.2</v>
+        <v>906.9</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>859.7</v>
+        <v>889.7</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>864.8</v>
+        <v>907.5</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>0.59% (5.1)</t>
+          <t>1.96% (17.8)</t>
         </is>
       </c>
       <c r="F24" s="4" t="n">
-        <v>869.9</v>
+        <v>925.3</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>875</v>
+        <v>943.1</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -3016,19 +3908,19 @@
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 09:30</t>
+          <t>2026-09-29 10:15</t>
         </is>
       </c>
       <c r="K24" s="2" t="n">
-        <v>859.7</v>
+        <v>889.7</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>-0.59</v>
+        <v>-1.96</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
@@ -3039,28 +3931,28 @@
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>8821.5</v>
+        <v>864.2</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>8804.5</v>
+        <v>859.7</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>8893</v>
+        <v>864.8</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>1.0% (88.5)</t>
+          <t>0.59% (5.1)</t>
         </is>
       </c>
       <c r="F25" s="4" t="n">
-        <v>8981.5</v>
+        <v>869.9</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>9070</v>
+        <v>875</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -3069,19 +3961,19 @@
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>SL HIT</t>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:00</t>
+          <t>2026-09-29 09:30</t>
         </is>
       </c>
       <c r="K25" s="2" t="n">
-        <v>8804.5</v>
+        <v>859.7</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>-1</v>
+        <v>-0.59</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
@@ -3092,49 +3984,49 @@
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>906.9</v>
+        <v>8821.5</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>889.7</v>
+        <v>8804.5</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>907.5</v>
+        <v>8893</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>1.96% (17.8)</t>
+          <t>1.0% (88.5)</t>
         </is>
       </c>
       <c r="F26" s="4" t="n">
-        <v>925.3</v>
+        <v>8981.5</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>943.1</v>
+        <v>9070</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 09:15</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="I26" s="6" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:15</t>
+          <t>2026-09-29 10:00</t>
         </is>
       </c>
       <c r="K26" s="2" t="n">
-        <v>889.7</v>
+        <v>8804.5</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-1.96</v>
+        <v>-1</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
@@ -3173,7 +4065,7 @@
           <t>2026-09-29 09:30</t>
         </is>
       </c>
-      <c r="I27" s="6" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
@@ -3226,7 +4118,7 @@
           <t>2026-09-29 11:00</t>
         </is>
       </c>
-      <c r="I28" s="8" t="inlineStr">
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -3279,7 +4171,7 @@
           <t>2026-09-29 11:15</t>
         </is>
       </c>
-      <c r="I29" s="8" t="inlineStr">
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -3304,49 +4196,49 @@
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>1495.7</v>
+        <v>399.3</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1487.1</v>
+        <v>394.7</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1498</v>
+        <v>403.65</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>0.73% (10.9)</t>
+          <t>2.22% (8.95)</t>
         </is>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1508.9</v>
+        <v>412.6</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1519.8</v>
+        <v>421.55</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 11:30</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:30</t>
+          <t>2026-09-29 15:15 (Active)</t>
         </is>
       </c>
       <c r="K30" s="2" t="n">
-        <v>1487.1</v>
-      </c>
-      <c r="L30" s="3" t="n">
-        <v>-0.73</v>
+        <v>406</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>0.58</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
@@ -3357,49 +4249,49 @@
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>399.3</v>
+        <v>1495.7</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>394.7</v>
+        <v>1487.1</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>403.65</v>
+        <v>1498</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>2.22% (8.95)</t>
+          <t>0.73% (10.9)</t>
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>412.6</v>
+        <v>1508.9</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>421.55</v>
+        <v>1519.8</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 11:30</t>
         </is>
       </c>
-      <c r="I31" s="8" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:15 (Active)</t>
+          <t>2026-09-29 12:30</t>
         </is>
       </c>
       <c r="K31" s="2" t="n">
-        <v>406</v>
-      </c>
-      <c r="L31" s="4" t="n">
-        <v>0.58</v>
+        <v>1487.1</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>-0.73</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
@@ -3438,7 +4330,7 @@
           <t>2026-09-29 11:45</t>
         </is>
       </c>
-      <c r="I32" s="8" t="inlineStr">
+      <c r="I32" s="7" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -3491,7 +4383,7 @@
           <t>2026-09-29 12:00</t>
         </is>
       </c>
-      <c r="I33" s="8" t="inlineStr">
+      <c r="I33" s="7" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -3544,7 +4436,7 @@
           <t>2026-09-29 13:00</t>
         </is>
       </c>
-      <c r="I34" s="8" t="inlineStr">
+      <c r="I34" s="7" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -3597,7 +4489,7 @@
           <t>2026-09-29 14:00</t>
         </is>
       </c>
-      <c r="I35" s="8" t="inlineStr">
+      <c r="I35" s="7" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -3650,7 +4542,7 @@
           <t>2026-09-29 14:00</t>
         </is>
       </c>
-      <c r="I36" s="6" t="inlineStr">
+      <c r="I36" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -3703,7 +4595,7 @@
           <t>2026-09-29 14:45</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="I37" s="6" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -3756,7 +4648,7 @@
           <t>2026-09-29 14:45</t>
         </is>
       </c>
-      <c r="I38" s="8" t="inlineStr">
+      <c r="I38" s="7" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -3809,7 +4701,7 @@
           <t>2026-09-29 15:00</t>
         </is>
       </c>
-      <c r="I39" s="6" t="inlineStr">
+      <c r="I39" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
@@ -3826,6 +4718,483 @@
         <v>1.88</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>(28-09-2026 to 04-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>4848.5</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>4837</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>4872</v>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>0.72% (35.0)</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>4907</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>4942</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Then SL)</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 10:30</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>4837</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>(28-09-2026 to 04-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>263.55</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>263.3</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>266.2</v>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>1.09% (2.9)</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>269.1</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>272</v>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:30 (Active)</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>265.5</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>(28-09-2026 to 04-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>2391</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>2381.6</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>2420</v>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>1.59% (38.4)</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>2458.4</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>2496.8</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15</t>
+        </is>
+      </c>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:30 (Active)</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>2409.1</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>(28-09-2026 to 04-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>4057</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>4043.3</v>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>4095</v>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>1.26% (51.7)</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>4146.7</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>4198.4</v>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:45</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>4146.7</v>
+      </c>
+      <c r="L43" s="4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>(28-09-2026 to 04-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>399.3</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>394.7</v>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>403.65</v>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>2.22% (8.95)</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>412.6</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>421.55</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 10:00</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>412.6</v>
+      </c>
+      <c r="L44" s="4" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>(28-09-2026 to 04-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>991.6</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>980.4</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>992.7</v>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>1.24% (12.3)</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>1005</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>1017.3</v>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:45</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>1017.3</v>
+      </c>
+      <c r="L45" s="4" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>(28-09-2026 to 04-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>196.1</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>192.45</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>196.67</v>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>2.15% (4.22)</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>200.89</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>205.11</v>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>200.89</v>
+      </c>
+      <c r="L46" s="4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>(28-09-2026 to 04-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>1766.7</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>1736.8</v>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>1770.1</v>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>1.88% (33.3)</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>1803.4</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>1836.7</v>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15</t>
+        </is>
+      </c>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:30 (Active)</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>1789.3</v>
+      </c>
+      <c r="L47" s="4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>(28-09-2026 to 04-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>160.5</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>159.41</v>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>162.37</v>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>1.82% (2.96)</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>165.33</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>168.29</v>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15</t>
+        </is>
+      </c>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:30 (Active)</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>163.25</v>
+      </c>
+      <c r="L48" s="4" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
         <is>
           <t>(28-09-2026 to 04-10-2026)</t>
         </is>

--- a/data/trade_tracker_results.xlsx
+++ b/data/trade_tracker_results.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L46"/>
+  <dimension ref="A1:L47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1419,14 +1419,14 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:30 (Active)</t>
+          <t>2026-09-30 15:15 (Active)</t>
         </is>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1789.3</v>
+        <v>1798.3</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.08</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -1457,24 +1457,22 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:15</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:30 (Active)</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="n">
-        <v>2409.1</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>-0.45</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -1554,21 +1552,21 @@
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:30 (Active)</t>
+          <t>2026-09-30 14:15</t>
         </is>
       </c>
       <c r="K22" s="2" t="n">
-        <v>265.5</v>
+        <v>263.3</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>-0.26</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2533,14 +2531,14 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:30 (Active)</t>
+          <t>2026-09-30 15:15 (Active)</t>
         </is>
       </c>
       <c r="K43" s="2" t="n">
-        <v>163.25</v>
+        <v>163.26</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -2678,6 +2676,52 @@
       </c>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>LODHA</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>1127</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>1091.9</v>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>1130.7</v>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>3.43% (38.8)</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>1169.5</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>1208.3</v>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4461,49 +4505,49 @@
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>411.8</v>
+        <v>4848.5</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>402.75</v>
+        <v>4837</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>411.9</v>
+        <v>4872</v>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>2.22% (9.15)</t>
+          <t>0.72% (35.0)</t>
         </is>
       </c>
       <c r="F35" s="4" t="n">
-        <v>421.05</v>
+        <v>4907</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>430.2</v>
+        <v>4942</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 14:00</t>
         </is>
       </c>
-      <c r="I35" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:15 (Active)</t>
+          <t>2026-09-29 14:45</t>
         </is>
       </c>
       <c r="K35" s="2" t="n">
-        <v>413.35</v>
+        <v>4942</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.35</v>
+        <v>1.44</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
@@ -4514,49 +4558,49 @@
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>4848.5</v>
+        <v>411.8</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>4837</v>
+        <v>402.75</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>4872</v>
+        <v>411.9</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>0.72% (35.0)</t>
+          <t>2.22% (9.15)</t>
         </is>
       </c>
       <c r="F36" s="4" t="n">
-        <v>4907</v>
+        <v>421.05</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>4942</v>
+        <v>430.2</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 14:00</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 14:45</t>
+          <t>2026-09-29 15:15 (Active)</t>
         </is>
       </c>
       <c r="K36" s="2" t="n">
-        <v>4942</v>
+        <v>413.35</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>1.44</v>
+        <v>0.35</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
@@ -4726,49 +4770,49 @@
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>4848.5</v>
+        <v>2391</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>4837</v>
+        <v>2381.6</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>4872</v>
+        <v>2420</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>0.72% (35.0)</t>
+          <t>1.59% (38.4)</t>
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>4907</v>
+        <v>2458.4</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>4942</v>
+        <v>2496.8</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I40" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 10:30</t>
+          <t>2026-09-30 12:30 (Active)</t>
         </is>
       </c>
       <c r="K40" s="2" t="n">
-        <v>4837</v>
+        <v>2409.1</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>-0.72</v>
+        <v>-0.45</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
@@ -4779,49 +4823,49 @@
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>263.55</v>
+        <v>196.1</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>263.3</v>
+        <v>192.45</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>266.2</v>
+        <v>196.67</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>1.09% (2.9)</t>
+          <t>2.15% (4.22)</t>
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>269.1</v>
+        <v>200.89</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>272</v>
+        <v>205.11</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I41" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:30 (Active)</t>
+          <t>2026-09-30 09:15</t>
         </is>
       </c>
       <c r="K41" s="2" t="n">
-        <v>265.5</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>-0.26</v>
+        <v>200.89</v>
+      </c>
+      <c r="L41" s="4" t="n">
+        <v>2.15</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
@@ -4832,49 +4876,49 @@
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>2391</v>
+        <v>4057</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>2381.6</v>
+        <v>4043.3</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>2420</v>
+        <v>4095</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>1.59% (38.4)</t>
+          <t>1.26% (51.7)</t>
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>2458.4</v>
+        <v>4146.7</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>2496.8</v>
+        <v>4198.4</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I42" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:30 (Active)</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
       <c r="K42" s="2" t="n">
-        <v>2409.1</v>
-      </c>
-      <c r="L42" s="3" t="n">
-        <v>-0.45</v>
+        <v>4146.7</v>
+      </c>
+      <c r="L42" s="4" t="n">
+        <v>1.26</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
@@ -4885,28 +4929,28 @@
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>4057</v>
+        <v>991.6</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>4043.3</v>
+        <v>980.4</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>4095</v>
+        <v>992.7</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>1.26% (51.7)</t>
+          <t>1.24% (12.3)</t>
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>4146.7</v>
+        <v>1005</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>4198.4</v>
+        <v>1017.3</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -4915,7 +4959,7 @@
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -4924,10 +4968,10 @@
         </is>
       </c>
       <c r="K43" s="2" t="n">
-        <v>4146.7</v>
+        <v>1017.3</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>1.26</v>
+        <v>2.48</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
@@ -4991,49 +5035,49 @@
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>991.6</v>
+        <v>1766.7</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>980.4</v>
+        <v>1736.8</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>992.7</v>
+        <v>1770.1</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>1.24% (12.3)</t>
+          <t>1.88% (33.3)</t>
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>1005</v>
+        <v>1803.4</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>1017.3</v>
+        <v>1836.7</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-30 15:15 (Active)</t>
         </is>
       </c>
       <c r="K45" s="2" t="n">
-        <v>1017.3</v>
+        <v>1798.3</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>2.48</v>
+        <v>1.59</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
@@ -5044,49 +5088,49 @@
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>196.1</v>
+        <v>263.55</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>192.45</v>
+        <v>263.3</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>196.67</v>
+        <v>266.2</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>2.15% (4.22)</t>
+          <t>1.09% (2.9)</t>
         </is>
       </c>
       <c r="F46" s="4" t="n">
-        <v>200.89</v>
+        <v>269.1</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>205.11</v>
+        <v>272</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I46" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:15</t>
+          <t>2026-09-30 14:15</t>
         </is>
       </c>
       <c r="K46" s="2" t="n">
-        <v>200.89</v>
-      </c>
-      <c r="L46" s="4" t="n">
-        <v>2.15</v>
+        <v>263.3</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>-1.09</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
@@ -5097,49 +5141,49 @@
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>1766.7</v>
+        <v>4848.5</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>1736.8</v>
+        <v>4837</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>1770.1</v>
+        <v>4872</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>1.88% (33.3)</t>
+          <t>0.72% (35.0)</t>
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>1803.4</v>
+        <v>4907</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>1836.7</v>
+        <v>4942</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I47" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:30 (Active)</t>
+          <t>2026-09-30 10:30</t>
         </is>
       </c>
       <c r="K47" s="2" t="n">
-        <v>1789.3</v>
-      </c>
-      <c r="L47" s="4" t="n">
-        <v>1.08</v>
+        <v>4837</v>
+      </c>
+      <c r="L47" s="3" t="n">
+        <v>-0.72</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
@@ -5185,14 +5229,14 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:30 (Active)</t>
+          <t>2026-09-30 15:15 (Active)</t>
         </is>
       </c>
       <c r="K48" s="2" t="n">
-        <v>163.25</v>
+        <v>163.26</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>

--- a/data/trade_tracker_results.xlsx
+++ b/data/trade_tracker_results.xlsx
@@ -74,14 +74,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -129,10 +129,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L47"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -517,7 +517,7 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="33" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
@@ -613,24 +613,22 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:15</t>
-        </is>
-      </c>
-      <c r="I2" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:15</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>200.89</v>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
@@ -664,7 +662,7 @@
           <t>2026-09-29 09:15</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -942,7 +940,7 @@
           <t>2026-09-29 09:15</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
@@ -990,7 +988,7 @@
           <t>2026-09-29 09:15</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -1038,7 +1036,7 @@
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -1086,21 +1084,21 @@
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 10:00</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="K12" s="2" t="n">
-        <v>412.6</v>
+        <v>421.55</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>2.22</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -1180,7 +1178,7 @@
           <t>2026-09-29 11:30</t>
         </is>
       </c>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -1253,21 +1251,21 @@
         <v>1650.1</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1630.8</v>
+        <v>1618.1</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1665.8</v>
+        <v>1651.1</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>2.1% (35.0)</t>
+          <t>2.0% (33.0)</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1700.8</v>
+        <v>1684.1</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1735.8</v>
+        <v>1717.1</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1409,24 +1407,22 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:15</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="n">
-        <v>1798.3</v>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="4" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -1439,21 +1435,21 @@
         <v>2391</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2381.6</v>
+        <v>2377</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2420</v>
+        <v>2402.6</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>1.59% (38.4)</t>
+          <t>1.07% (25.6)</t>
         </is>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2458.4</v>
+        <v>2428.2</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2496.8</v>
+        <v>2453.8</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1552,7 +1548,7 @@
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I22" s="6" t="inlineStr">
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -1692,7 +1688,7 @@
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I25" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
@@ -1740,21 +1736,21 @@
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="K26" s="2" t="n">
-        <v>4146.7</v>
-      </c>
-      <c r="L26" s="4" t="n">
-        <v>1.26</v>
+        <v>4043.3</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>-1.26</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2245,22 +2241,24 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-01 09:15</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr"/>
+          <t>2026-10-01 09:15</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>521.3</v>
+      </c>
       <c r="L37" s="4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -2319,21 +2317,21 @@
         <v>445.35</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>442.8</v>
+        <v>441.8</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>447.8</v>
+        <v>448.55</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>1.12% (5.0)</t>
+          <t>1.5% (6.75)</t>
         </is>
       </c>
       <c r="F39" s="4" t="n">
-        <v>452.8</v>
+        <v>455.3</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>457.8</v>
+        <v>462.05</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2383,22 +2381,24 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-01 09:15</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="4" t="n">
-        <v>0</v>
+          <t>2026-10-01 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>718</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>-1.16</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -2411,21 +2411,21 @@
         <v>457.7</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>448.55</v>
+        <v>447.25</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>458.65</v>
+        <v>459.65</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>2.2% (10.1)</t>
+          <t>2.7% (12.4)</t>
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>468.75</v>
+        <v>472.05</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>478.85</v>
+        <v>484.45</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2503,42 +2503,40 @@
         <v>160.5</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>159.41</v>
+        <v>158.51</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>162.37</v>
+        <v>163.52</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>1.82% (2.96)</t>
+          <t>3.06% (5.01)</t>
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>165.33</v>
+        <v>168.53</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>168.29</v>
+        <v>173.54</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:15</t>
-        </is>
-      </c>
-      <c r="I43" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="n">
-        <v>163.26</v>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="4" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -2722,6 +2720,144 @@
       </c>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>877.1</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>854.2</v>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>878.6</v>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>2.78% (24.4)</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>903</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>927.4</v>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>1699.9</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>1677.7</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>1704</v>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>1.54% (26.3)</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>1730.3</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>1756.6</v>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>VBL</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>422</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>415.75</v>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>425.85</v>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>2.37% (10.1)</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>435.95</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>446.05</v>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2736,7 +2872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2871,7 +3007,7 @@
           <t>2026-09-23 09:15</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -3242,7 +3378,7 @@
           <t>2026-09-25 10:00</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -3526,7 +3662,7 @@
           <t>2026-09-28 10:00</t>
         </is>
       </c>
-      <c r="I16" s="6" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -3579,7 +3715,7 @@
           <t>2026-09-28 11:30</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -3632,7 +3768,7 @@
           <t>2026-09-28 12:00</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
@@ -3738,7 +3874,7 @@
           <t>2026-09-28 13:45</t>
         </is>
       </c>
-      <c r="I20" s="6" t="inlineStr">
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -3897,7 +4033,7 @@
           <t>2026-09-28 15:15</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -3950,7 +4086,7 @@
           <t>2026-09-29 09:15</t>
         </is>
       </c>
-      <c r="I24" s="6" t="inlineStr">
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -4003,7 +4139,7 @@
           <t>2026-09-29 09:15</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I25" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
@@ -4056,7 +4192,7 @@
           <t>2026-09-29 09:15</t>
         </is>
       </c>
-      <c r="I26" s="6" t="inlineStr">
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -4109,7 +4245,7 @@
           <t>2026-09-29 09:30</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I27" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
@@ -4240,49 +4376,49 @@
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>399.3</v>
+        <v>1495.7</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>394.7</v>
+        <v>1487.1</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>403.65</v>
+        <v>1498</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>2.22% (8.95)</t>
+          <t>0.73% (10.9)</t>
         </is>
       </c>
       <c r="F30" s="4" t="n">
-        <v>412.6</v>
+        <v>1508.9</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>421.55</v>
+        <v>1519.8</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 11:30</t>
         </is>
       </c>
-      <c r="I30" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:15 (Active)</t>
+          <t>2026-09-29 12:30</t>
         </is>
       </c>
       <c r="K30" s="2" t="n">
-        <v>406</v>
-      </c>
-      <c r="L30" s="4" t="n">
-        <v>0.58</v>
+        <v>1487.1</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>-0.73</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
@@ -4293,49 +4429,49 @@
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>1495.7</v>
+        <v>399.3</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1487.1</v>
+        <v>394.7</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1498</v>
+        <v>403.65</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>0.73% (10.9)</t>
+          <t>2.22% (8.95)</t>
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1508.9</v>
+        <v>412.6</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1519.8</v>
+        <v>421.55</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 11:30</t>
         </is>
       </c>
-      <c r="I31" s="6" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:30</t>
+          <t>2026-09-29 15:15 (Active)</t>
         </is>
       </c>
       <c r="K31" s="2" t="n">
-        <v>1487.1</v>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>-0.73</v>
+        <v>406</v>
+      </c>
+      <c r="L31" s="4" t="n">
+        <v>0.58</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
@@ -4533,7 +4669,7 @@
           <t>2026-09-29 14:00</t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="I35" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -4611,49 +4747,49 @@
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>22165</v>
+        <v>1629.9</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>22025</v>
+        <v>1600.2</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>22195</v>
+        <v>1642.9</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>0.77% (170.0)</t>
+          <t>2.6% (42.7)</t>
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>22365</v>
+        <v>1685.6</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>22535</v>
+        <v>1728.3</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 14:45</t>
         </is>
       </c>
-      <c r="I37" s="6" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:00</t>
+          <t>2026-09-29 15:15 (Active)</t>
         </is>
       </c>
       <c r="K37" s="2" t="n">
-        <v>22025</v>
+        <v>1627.3</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>-0.77</v>
+        <v>-0.95</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
@@ -4664,49 +4800,49 @@
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>1629.9</v>
+        <v>22165</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>1600.2</v>
+        <v>22025</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>1642.9</v>
+        <v>22195</v>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>2.6% (42.7)</t>
+          <t>0.77% (170.0)</t>
         </is>
       </c>
       <c r="F38" s="4" t="n">
-        <v>1685.6</v>
+        <v>22365</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>1728.3</v>
+        <v>22535</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 14:45</t>
         </is>
       </c>
-      <c r="I38" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:15 (Active)</t>
+          <t>2026-09-29 15:00</t>
         </is>
       </c>
       <c r="K38" s="2" t="n">
-        <v>1627.3</v>
+        <v>22025</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>-0.95</v>
+        <v>-0.77</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
@@ -4745,7 +4881,7 @@
           <t>2026-09-29 15:00</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="I39" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
@@ -4770,49 +4906,49 @@
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>2391</v>
+        <v>196.1</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>2381.6</v>
+        <v>192.45</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>2420</v>
+        <v>196.67</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>1.59% (38.4)</t>
+          <t>2.15% (4.22)</t>
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>2458.4</v>
+        <v>200.89</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>2496.8</v>
+        <v>205.11</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I40" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:30 (Active)</t>
+          <t>2026-09-30 09:15</t>
         </is>
       </c>
       <c r="K40" s="2" t="n">
-        <v>2409.1</v>
-      </c>
-      <c r="L40" s="3" t="n">
-        <v>-0.45</v>
+        <v>200.89</v>
+      </c>
+      <c r="L40" s="4" t="n">
+        <v>2.15</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
@@ -4823,49 +4959,49 @@
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>196.1</v>
+        <v>1766.7</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>192.45</v>
+        <v>1736.8</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>196.67</v>
+        <v>1770.1</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>2.15% (4.22)</t>
+          <t>1.88% (33.3)</t>
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>200.89</v>
+        <v>1803.4</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>205.11</v>
+        <v>1836.7</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:15</t>
+          <t>2026-09-30 15:15 (Active)</t>
         </is>
       </c>
       <c r="K41" s="2" t="n">
-        <v>200.89</v>
+        <v>1798.3</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>2.15</v>
+        <v>1.59</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
@@ -4876,49 +5012,49 @@
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>4057</v>
+        <v>160.5</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>4043.3</v>
+        <v>159.41</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>4095</v>
+        <v>162.37</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>1.26% (51.7)</t>
+          <t>1.82% (2.96)</t>
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>4146.7</v>
+        <v>165.33</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>4198.4</v>
+        <v>168.29</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I42" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-30 15:15 (Active)</t>
         </is>
       </c>
       <c r="K42" s="2" t="n">
-        <v>4146.7</v>
+        <v>163.26</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>1.26</v>
+        <v>0.55</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
@@ -4957,7 +5093,7 @@
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="I43" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -5010,21 +5146,21 @@
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I44" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 10:00</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="K44" s="2" t="n">
-        <v>412.6</v>
+        <v>421.55</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>2.22</v>
+        <v>4.43</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
@@ -5035,49 +5171,49 @@
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>1766.7</v>
+        <v>263.55</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1736.8</v>
+        <v>263.3</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>1770.1</v>
+        <v>266.2</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>1.88% (33.3)</t>
+          <t>1.09% (2.9)</t>
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>1803.4</v>
+        <v>269.1</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>1836.7</v>
+        <v>272</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I45" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 15:15 (Active)</t>
+          <t>2026-09-30 14:15</t>
         </is>
       </c>
       <c r="K45" s="2" t="n">
-        <v>1798.3</v>
-      </c>
-      <c r="L45" s="4" t="n">
-        <v>1.59</v>
+        <v>263.3</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>-1.09</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
@@ -5088,28 +5224,28 @@
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>263.55</v>
+        <v>4848.5</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>263.3</v>
+        <v>4837</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>266.2</v>
+        <v>4872</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>1.09% (2.9)</t>
+          <t>0.72% (35.0)</t>
         </is>
       </c>
       <c r="F46" s="4" t="n">
-        <v>269.1</v>
+        <v>4907</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>272</v>
+        <v>4942</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -5118,19 +5254,19 @@
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>SL HIT</t>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:15</t>
+          <t>2026-09-30 10:30</t>
         </is>
       </c>
       <c r="K46" s="2" t="n">
-        <v>263.3</v>
+        <v>4837</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>-1.09</v>
+        <v>-0.72</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
@@ -5141,49 +5277,49 @@
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>4848.5</v>
+        <v>4057</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>4837</v>
+        <v>4043.3</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>4872</v>
+        <v>4095</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>0.72% (35.0)</t>
+          <t>1.26% (51.7)</t>
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>4907</v>
+        <v>4146.7</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>4942</v>
+        <v>4198.4</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I47" s="5" t="inlineStr">
+      <c r="I47" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 10:30</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="K47" s="2" t="n">
-        <v>4837</v>
+        <v>4043.3</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>-0.72</v>
+        <v>-1.26</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
@@ -5194,28 +5330,28 @@
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>160.5</v>
+        <v>2391</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>159.41</v>
+        <v>2381.6</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>162.37</v>
+        <v>2420</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>1.82% (2.96)</t>
+          <t>1.59% (38.4)</t>
         </is>
       </c>
       <c r="F48" s="4" t="n">
-        <v>165.33</v>
+        <v>2458.4</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>168.29</v>
+        <v>2496.8</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -5229,16 +5365,122 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 15:15 (Active)</t>
+          <t>2026-09-30 12:30 (Active)</t>
         </is>
       </c>
       <c r="K48" s="2" t="n">
-        <v>163.26</v>
-      </c>
-      <c r="L48" s="4" t="n">
-        <v>0.55</v>
+        <v>2409.1</v>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>-0.45</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>(28-09-2026 to 04-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>514</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>513.5</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>516.1</v>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>0.5% (2.6)</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>518.7</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>521.3</v>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01 09:15</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01 09:15</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>521.3</v>
+      </c>
+      <c r="L49" s="4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>(28-09-2026 to 04-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>721.95</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>704.8</v>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>726.45</v>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>2.98% (21.65)</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>748.1</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>769.75</v>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01 09:15</t>
+        </is>
+      </c>
+      <c r="I50" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>718</v>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
         <is>
           <t>(28-09-2026 to 04-10-2026)</t>
         </is>

--- a/data/trade_tracker_results.xlsx
+++ b/data/trade_tracker_results.xlsx
@@ -4747,49 +4747,49 @@
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>1629.9</v>
+        <v>22165</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1600.2</v>
+        <v>22025</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>1642.9</v>
+        <v>22195</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>2.6% (42.7)</t>
+          <t>0.77% (170.0)</t>
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>1685.6</v>
+        <v>22365</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>1728.3</v>
+        <v>22535</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 14:45</t>
         </is>
       </c>
-      <c r="I37" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:15 (Active)</t>
+          <t>2026-09-29 15:00</t>
         </is>
       </c>
       <c r="K37" s="2" t="n">
-        <v>1627.3</v>
+        <v>22025</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>-0.95</v>
+        <v>-0.77</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
@@ -4800,49 +4800,49 @@
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>22165</v>
+        <v>1629.9</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>22025</v>
+        <v>1600.2</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>22195</v>
+        <v>1642.9</v>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>0.77% (170.0)</t>
+          <t>2.6% (42.7)</t>
         </is>
       </c>
       <c r="F38" s="4" t="n">
-        <v>22365</v>
+        <v>1685.6</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>22535</v>
+        <v>1728.3</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 14:45</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:00</t>
+          <t>2026-09-29 15:15 (Active)</t>
         </is>
       </c>
       <c r="K38" s="2" t="n">
-        <v>22025</v>
+        <v>1627.3</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>-0.77</v>
+        <v>-0.95</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
@@ -4906,49 +4906,49 @@
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>196.1</v>
+        <v>1766.7</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>192.45</v>
+        <v>1736.8</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>196.67</v>
+        <v>1770.1</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>2.15% (4.22)</t>
+          <t>1.88% (33.3)</t>
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>200.89</v>
+        <v>1803.4</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>205.11</v>
+        <v>1836.7</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I40" s="6" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:15</t>
+          <t>2026-09-30 15:15 (Active)</t>
         </is>
       </c>
       <c r="K40" s="2" t="n">
-        <v>200.89</v>
+        <v>1798.3</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>2.15</v>
+        <v>1.59</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
@@ -4959,28 +4959,28 @@
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>1766.7</v>
+        <v>160.5</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>1736.8</v>
+        <v>159.41</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>1770.1</v>
+        <v>162.37</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>1.88% (33.3)</t>
+          <t>1.82% (2.96)</t>
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>1803.4</v>
+        <v>165.33</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>1836.7</v>
+        <v>168.29</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -4998,10 +4998,10 @@
         </is>
       </c>
       <c r="K41" s="2" t="n">
-        <v>1798.3</v>
+        <v>163.26</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>1.59</v>
+        <v>0.55</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
@@ -5012,28 +5012,28 @@
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>160.5</v>
+        <v>2391</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>159.41</v>
+        <v>2381.6</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>162.37</v>
+        <v>2420</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>1.82% (2.96)</t>
+          <t>1.59% (38.4)</t>
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>165.33</v>
+        <v>2458.4</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>168.29</v>
+        <v>2496.8</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -5047,14 +5047,14 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 15:15 (Active)</t>
+          <t>2026-09-30 12:30 (Active)</t>
         </is>
       </c>
       <c r="K42" s="2" t="n">
-        <v>163.26</v>
-      </c>
-      <c r="L42" s="4" t="n">
-        <v>0.55</v>
+        <v>2409.1</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>-0.45</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
@@ -5330,49 +5330,49 @@
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>2391</v>
+        <v>196.1</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2381.6</v>
+        <v>192.45</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>2420</v>
+        <v>196.67</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>1.59% (38.4)</t>
+          <t>2.15% (4.22)</t>
         </is>
       </c>
       <c r="F48" s="4" t="n">
-        <v>2458.4</v>
+        <v>200.89</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>2496.8</v>
+        <v>205.11</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I48" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:30 (Active)</t>
+          <t>2026-09-30 09:15</t>
         </is>
       </c>
       <c r="K48" s="2" t="n">
-        <v>2409.1</v>
-      </c>
-      <c r="L48" s="3" t="n">
-        <v>-0.45</v>
+        <v>200.89</v>
+      </c>
+      <c r="L48" s="4" t="n">
+        <v>2.15</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>

--- a/data/trade_tracker_results.xlsx
+++ b/data/trade_tracker_results.xlsx
@@ -4747,49 +4747,49 @@
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>22165</v>
+        <v>1629.9</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>22025</v>
+        <v>1600.2</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>22195</v>
+        <v>1642.9</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>0.77% (170.0)</t>
+          <t>2.6% (42.7)</t>
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>22365</v>
+        <v>1685.6</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>22535</v>
+        <v>1728.3</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 14:45</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:00</t>
+          <t>2026-09-29 15:15 (Active)</t>
         </is>
       </c>
       <c r="K37" s="2" t="n">
-        <v>22025</v>
+        <v>1627.3</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>-0.77</v>
+        <v>-0.95</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
@@ -4800,49 +4800,49 @@
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>1629.9</v>
+        <v>22165</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>1600.2</v>
+        <v>22025</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>1642.9</v>
+        <v>22195</v>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>2.6% (42.7)</t>
+          <t>0.77% (170.0)</t>
         </is>
       </c>
       <c r="F38" s="4" t="n">
-        <v>1685.6</v>
+        <v>22365</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>1728.3</v>
+        <v>22535</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 14:45</t>
         </is>
       </c>
-      <c r="I38" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:15 (Active)</t>
+          <t>2026-09-29 15:00</t>
         </is>
       </c>
       <c r="K38" s="2" t="n">
-        <v>1627.3</v>
+        <v>22025</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>-0.95</v>
+        <v>-0.77</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
@@ -4906,28 +4906,28 @@
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>1766.7</v>
+        <v>160.5</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1736.8</v>
+        <v>159.41</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>1770.1</v>
+        <v>162.37</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>1.88% (33.3)</t>
+          <t>1.82% (2.96)</t>
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>1803.4</v>
+        <v>165.33</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>1836.7</v>
+        <v>168.29</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -4945,10 +4945,10 @@
         </is>
       </c>
       <c r="K40" s="2" t="n">
-        <v>1798.3</v>
+        <v>163.26</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>1.59</v>
+        <v>0.55</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
@@ -4959,28 +4959,28 @@
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>160.5</v>
+        <v>2391</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>159.41</v>
+        <v>2381.6</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>162.37</v>
+        <v>2420</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>1.82% (2.96)</t>
+          <t>1.59% (38.4)</t>
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>165.33</v>
+        <v>2458.4</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>168.29</v>
+        <v>2496.8</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -4994,14 +4994,14 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 15:15 (Active)</t>
+          <t>2026-09-30 12:30 (Active)</t>
         </is>
       </c>
       <c r="K41" s="2" t="n">
-        <v>163.26</v>
-      </c>
-      <c r="L41" s="4" t="n">
-        <v>0.55</v>
+        <v>2409.1</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>-0.45</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
@@ -5012,49 +5012,49 @@
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>2391</v>
+        <v>196.1</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>2381.6</v>
+        <v>192.45</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>2420</v>
+        <v>196.67</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>1.59% (38.4)</t>
+          <t>2.15% (4.22)</t>
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>2458.4</v>
+        <v>200.89</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>2496.8</v>
+        <v>205.11</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I42" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:30 (Active)</t>
+          <t>2026-09-30 09:15</t>
         </is>
       </c>
       <c r="K42" s="2" t="n">
-        <v>2409.1</v>
-      </c>
-      <c r="L42" s="3" t="n">
-        <v>-0.45</v>
+        <v>200.89</v>
+      </c>
+      <c r="L42" s="4" t="n">
+        <v>2.15</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
@@ -5330,49 +5330,49 @@
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>196.1</v>
+        <v>1766.7</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>192.45</v>
+        <v>1736.8</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>196.67</v>
+        <v>1770.1</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>2.15% (4.22)</t>
+          <t>1.88% (33.3)</t>
         </is>
       </c>
       <c r="F48" s="4" t="n">
-        <v>200.89</v>
+        <v>1803.4</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>205.11</v>
+        <v>1836.7</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I48" s="6" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:15</t>
+          <t>2026-09-30 15:15 (Active)</t>
         </is>
       </c>
       <c r="K48" s="2" t="n">
-        <v>200.89</v>
+        <v>1798.3</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>2.15</v>
+        <v>1.59</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>

--- a/data/trade_tracker_results.xlsx
+++ b/data/trade_tracker_results.xlsx
@@ -74,8 +74,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -92,8 +92,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-        <bgColor rgb="00D9E1F2"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -129,7 +129,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -138,7 +138,7 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -506,19 +506,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L50"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="27" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
   </cols>
@@ -588,28 +588,28 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>196.1</v>
+        <v>378.65</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>192.45</v>
+        <v>377.05</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>196.67</v>
+        <v>384.35</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2.15% (4.22)</t>
+          <t>1.9% (7.3)</t>
         </is>
       </c>
       <c r="F2" s="4" t="n">
-        <v>200.89</v>
+        <v>391.65</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>205.11</v>
+        <v>398.95</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -634,76 +634,74 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>BPCL</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>8821.5</v>
+        <v>296.5</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>8804.5</v>
+        <v>294.55</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>8893</v>
+        <v>296.8</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>1.0% (88.5)</t>
+          <t>0.76% (2.25)</t>
         </is>
       </c>
       <c r="F3" s="4" t="n">
-        <v>8981.5</v>
+        <v>299.05</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>9070</v>
+        <v>301.3</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 09:15</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:00</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>8804.5</v>
-      </c>
-      <c r="L3" s="3" t="n">
-        <v>-1</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>411.8</v>
+        <v>4737</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>402.75</v>
+        <v>4734.1</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>411.9</v>
+        <v>4770.2</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>2.22% (9.15)</t>
+          <t>0.76% (36.1)</t>
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>421.05</v>
+        <v>4806.3</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>430.2</v>
+        <v>4842.4</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -728,28 +726,28 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4883</v>
+        <v>1333.4</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>4869</v>
+        <v>1321.3</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>4902.5</v>
+        <v>1334</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>0.68% (33.5)</t>
+          <t>0.95% (12.7)</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>4936</v>
+        <v>1346.7</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>4969.5</v>
+        <v>1359.4</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -774,28 +772,28 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1629.9</v>
+        <v>1194.9</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1600.2</v>
+        <v>1189.9</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1642.9</v>
+        <v>1202.9</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>2.6% (42.7)</t>
+          <t>1.08% (13.0)</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1685.6</v>
+        <v>1215.9</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1728.3</v>
+        <v>1228.9</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -820,28 +818,28 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>COLPAL</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1835.4</v>
+        <v>5051</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1827</v>
+        <v>4995.5</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1857.9</v>
+        <v>5200</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>1.66% (30.9)</t>
+          <t>3.93% (204.5)</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1888.8</v>
+        <v>5404.5</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1919.7</v>
+        <v>5609</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -866,28 +864,28 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>171.35</v>
+        <v>1295</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>168.57</v>
+        <v>1293</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>173.18</v>
+        <v>1299.4</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>2.66% (4.61)</t>
+          <t>0.49% (6.4)</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>177.79</v>
+        <v>1305.8</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>182.4</v>
+        <v>1312.2</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -912,1952 +910,92 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>864.2</v>
+        <v>4717.3</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>859.7</v>
+        <v>4710</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>864.8</v>
+        <v>4724.4</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>0.59% (5.1)</t>
+          <t>0.3% (14.4)</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>869.9</v>
+        <v>4738.8</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>875</v>
+        <v>4753.2</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 09:15</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 09:30</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>859.7</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>-0.59</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>906.9</v>
+        <v>3930.1</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>889.7</v>
+        <v>3920</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>907.5</v>
+        <v>4031.6</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>1.96% (17.8)</t>
+          <t>2.77% (111.6)</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>925.3</v>
+        <v>4143.2</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>943.1</v>
+        <v>4254.8</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 09:15</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:15</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>889.7</v>
-      </c>
-      <c r="L10" s="3" t="n">
-        <v>-1.96</v>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>INFY</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>991.6</v>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>980.4</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>992.7</v>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>1.24% (12.3)</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>1005</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>1017.3</v>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30 09:15</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30 09:45</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="n">
-        <v>1017.3</v>
-      </c>
-      <c r="L11" s="4" t="n">
-        <v>2.48</v>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>KOTAKBANK</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>399.3</v>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>394.7</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>403.65</v>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>2.22% (8.95)</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>412.6</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>421.55</v>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30 09:15</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-01 09:15</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>421.55</v>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v>4.43</v>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>MARUTI</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>11975</v>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>11832</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>12000</v>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>1.4% (168.0)</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>12168</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>12336</v>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>PIDILITIND</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>1495.7</v>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>1487.1</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>1498</v>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>0.73% (10.9)</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>1508.9</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>1519.8</v>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 11:30</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:30</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>1487.1</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>-0.73</v>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>SHREECEM</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>22165</v>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>21585</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>22340</v>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>3.38% (755.0)</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>23095</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>23850</v>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TATACOMM</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>1650.1</v>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>1618.1</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>1651.1</v>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>2.0% (33.0)</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>1684.1</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>1717.1</v>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>ULTRACEMCO</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>10983</v>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>10869</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>11030</v>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>1.46% (161.0)</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>11191</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>11352</v>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>ADANIENT</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>2898.2</v>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>2793.7</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>2920.1</v>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>4.33% (126.4)</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>3046.5</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>3172.9</v>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>ADANIPORTS</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>1766.7</v>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>1736.8</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>1770.1</v>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>1.88% (33.3)</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>1803.4</v>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>1836.7</v>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>ASIANPAINT</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>2391</v>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>2377</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>2402.6</v>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>1.07% (25.6)</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>2428.2</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>2453.8</v>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>IRFC</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>79.2</v>
-      </c>
-      <c r="C21" s="3" t="n">
-        <v>77.09999999999999</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>79.95</v>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>3.56% (2.85)</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>82.8</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>85.65000000000001</v>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>ITC</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>263.55</v>
-      </c>
-      <c r="C22" s="3" t="n">
-        <v>263.3</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>266.2</v>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>1.09% (2.9)</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="n">
-        <v>269.1</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>272</v>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30 09:15</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30 14:15</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="n">
-        <v>263.3</v>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v>-1.09</v>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>JINDALSTEL</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>1127.1</v>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>1125.1</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>1149</v>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>2.08% (23.9)</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="n">
-        <v>1172.9</v>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>1196.8</v>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>JSWSTEEL</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>1264.4</v>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>1247</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>1267.7</v>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>1.63% (20.7)</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="n">
-        <v>1288.4</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>1309.1</v>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>TORNTPHARM</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>4848.5</v>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>4837</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>4872</v>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>0.72% (35.0)</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="n">
-        <v>4907</v>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>4942</v>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30 09:15</t>
-        </is>
-      </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30 10:30</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="n">
-        <v>4837</v>
-      </c>
-      <c r="L25" s="3" t="n">
-        <v>-0.72</v>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>TVSMOTOR</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>4057</v>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>4043.3</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>4095</v>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>1.26% (51.7)</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="n">
-        <v>4146.7</v>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>4198.4</v>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30 09:15</t>
-        </is>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-01 09:15</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="n">
-        <v>4043.3</v>
-      </c>
-      <c r="L26" s="3" t="n">
-        <v>-1.26</v>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>VEDL</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>259</v>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>256.15</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>260.45</v>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>1.65% (4.3)</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="n">
-        <v>264.75</v>
-      </c>
-      <c r="G27" s="4" t="n">
-        <v>269.05</v>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>ADANIENSOL</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>1315</v>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>1275.8</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>1316.9</v>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>3.12% (41.1)</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="n">
-        <v>1358</v>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v>1399.1</v>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>ADANIGREEN</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>1270.2</v>
-      </c>
-      <c r="C29" s="3" t="n">
-        <v>1223.9</v>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>1277</v>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>4.16% (53.1)</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="n">
-        <v>1330.1</v>
-      </c>
-      <c r="G29" s="4" t="n">
-        <v>1383.2</v>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>BAJAJHLDNG</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>10738</v>
-      </c>
-      <c r="C30" s="3" t="n">
-        <v>10600</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>10809</v>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>1.93% (209.0)</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="n">
-        <v>11018</v>
-      </c>
-      <c r="G30" s="4" t="n">
-        <v>11227</v>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>BANKBARODA</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>232.52</v>
-      </c>
-      <c r="C31" s="3" t="n">
-        <v>223.95</v>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>234.94</v>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>4.68% (10.99)</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="n">
-        <v>245.93</v>
-      </c>
-      <c r="G31" s="4" t="n">
-        <v>256.92</v>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr"/>
-      <c r="L31" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>BEL</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>388.6</v>
-      </c>
-      <c r="C32" s="3" t="n">
-        <v>382.25</v>
-      </c>
-      <c r="D32" s="4" t="n">
-        <v>393.1</v>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>2.76% (10.85)</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="n">
-        <v>403.95</v>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>414.8</v>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>BOSCHLTD</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>47145</v>
-      </c>
-      <c r="C33" s="3" t="n">
-        <v>45700</v>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>47165</v>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>3.11% (1465.0)</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="n">
-        <v>48630</v>
-      </c>
-      <c r="G33" s="4" t="n">
-        <v>50095</v>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>DABUR</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>381.55</v>
-      </c>
-      <c r="C34" s="3" t="n">
-        <v>378.05</v>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>386.25</v>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>2.12% (8.2)</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="n">
-        <v>394.45</v>
-      </c>
-      <c r="G34" s="4" t="n">
-        <v>402.65</v>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>DIVISLAB</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="n">
-        <v>9312.5</v>
-      </c>
-      <c r="C35" s="3" t="n">
-        <v>9280</v>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>9400</v>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>1.28% (120.0)</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="n">
-        <v>9520</v>
-      </c>
-      <c r="G35" s="4" t="n">
-        <v>9640</v>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr"/>
-      <c r="L35" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>HCLTECH</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>1234.6</v>
-      </c>
-      <c r="C36" s="3" t="n">
-        <v>1222</v>
-      </c>
-      <c r="D36" s="4" t="n">
-        <v>1241.6</v>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>1.58% (19.6)</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="n">
-        <v>1261.2</v>
-      </c>
-      <c r="G36" s="4" t="n">
-        <v>1280.8</v>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>HDFCLIFE</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n">
-        <v>514</v>
-      </c>
-      <c r="C37" s="3" t="n">
-        <v>513.5</v>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>516.1</v>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>0.5% (2.6)</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="n">
-        <v>518.7</v>
-      </c>
-      <c r="G37" s="4" t="n">
-        <v>521.3</v>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-01 09:15</t>
-        </is>
-      </c>
-      <c r="I37" s="6" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-01 09:15</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="n">
-        <v>521.3</v>
-      </c>
-      <c r="L37" s="4" t="n">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>ICICIBANK</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>1312</v>
-      </c>
-      <c r="C38" s="3" t="n">
-        <v>1291.1</v>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>1312.6</v>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>1.64% (21.5)</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="n">
-        <v>1334.1</v>
-      </c>
-      <c r="G38" s="4" t="n">
-        <v>1355.6</v>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>ICICIPRULI</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="n">
-        <v>445.35</v>
-      </c>
-      <c r="C39" s="3" t="n">
-        <v>441.8</v>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>448.55</v>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>1.5% (6.75)</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="n">
-        <v>455.3</v>
-      </c>
-      <c r="G39" s="4" t="n">
-        <v>462.05</v>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>INDHOTEL</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>721.95</v>
-      </c>
-      <c r="C40" s="3" t="n">
-        <v>704.8</v>
-      </c>
-      <c r="D40" s="4" t="n">
-        <v>726.45</v>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>2.98% (21.65)</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="n">
-        <v>748.1</v>
-      </c>
-      <c r="G40" s="4" t="n">
-        <v>769.75</v>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-01 09:15</t>
-        </is>
-      </c>
-      <c r="I40" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-01 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="n">
-        <v>718</v>
-      </c>
-      <c r="L40" s="3" t="n">
-        <v>-1.16</v>
-      </c>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>IRCTC</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="n">
-        <v>457.7</v>
-      </c>
-      <c r="C41" s="3" t="n">
-        <v>447.25</v>
-      </c>
-      <c r="D41" s="4" t="n">
-        <v>459.65</v>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>2.7% (12.4)</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="n">
-        <v>472.05</v>
-      </c>
-      <c r="G41" s="4" t="n">
-        <v>484.45</v>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>LTM</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="n">
-        <v>3996</v>
-      </c>
-      <c r="C42" s="3" t="n">
-        <v>3936</v>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>4183.6</v>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>5.92% (247.6)</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="n">
-        <v>4431.2</v>
-      </c>
-      <c r="G42" s="4" t="n">
-        <v>4678.8</v>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>MOTHERSON</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="n">
-        <v>160.5</v>
-      </c>
-      <c r="C43" s="3" t="n">
-        <v>158.51</v>
-      </c>
-      <c r="D43" s="4" t="n">
-        <v>163.52</v>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>3.06% (5.01)</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="n">
-        <v>168.53</v>
-      </c>
-      <c r="G43" s="4" t="n">
-        <v>173.54</v>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>SUNPHARMA</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="n">
-        <v>1832.2</v>
-      </c>
-      <c r="C44" s="3" t="n">
-        <v>1814.2</v>
-      </c>
-      <c r="D44" s="4" t="n">
-        <v>1841.1</v>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>1.46% (26.9)</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="n">
-        <v>1868</v>
-      </c>
-      <c r="G44" s="4" t="n">
-        <v>1894.9</v>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>TECHM</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="n">
-        <v>1525.1</v>
-      </c>
-      <c r="C45" s="3" t="n">
-        <v>1510.5</v>
-      </c>
-      <c r="D45" s="4" t="n">
-        <v>1540.5</v>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>1.95% (30.0)</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="n">
-        <v>1570.5</v>
-      </c>
-      <c r="G45" s="4" t="n">
-        <v>1600.5</v>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>ZYDUSLIFE</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="n">
-        <v>1152.1</v>
-      </c>
-      <c r="C46" s="3" t="n">
-        <v>1149.5</v>
-      </c>
-      <c r="D46" s="4" t="n">
-        <v>1221.1</v>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>5.86% (71.6)</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="n">
-        <v>1292.7</v>
-      </c>
-      <c r="G46" s="4" t="n">
-        <v>1364.3</v>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>LODHA</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="n">
-        <v>1127</v>
-      </c>
-      <c r="C47" s="3" t="n">
-        <v>1091.9</v>
-      </c>
-      <c r="D47" s="4" t="n">
-        <v>1130.7</v>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>3.43% (38.8)</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="n">
-        <v>1169.5</v>
-      </c>
-      <c r="G47" s="4" t="n">
-        <v>1208.3</v>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr"/>
-      <c r="L47" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>CGPOWER</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="n">
-        <v>877.1</v>
-      </c>
-      <c r="C48" s="3" t="n">
-        <v>854.2</v>
-      </c>
-      <c r="D48" s="4" t="n">
-        <v>878.6</v>
-      </c>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>2.78% (24.4)</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="n">
-        <v>903</v>
-      </c>
-      <c r="G48" s="4" t="n">
-        <v>927.4</v>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>SBILIFE</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="n">
-        <v>1699.9</v>
-      </c>
-      <c r="C49" s="3" t="n">
-        <v>1677.7</v>
-      </c>
-      <c r="D49" s="4" t="n">
-        <v>1704</v>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>1.54% (26.3)</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="n">
-        <v>1730.3</v>
-      </c>
-      <c r="G49" s="4" t="n">
-        <v>1756.6</v>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr"/>
-      <c r="L49" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>VBL</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="n">
-        <v>422</v>
-      </c>
-      <c r="C50" s="3" t="n">
-        <v>415.75</v>
-      </c>
-      <c r="D50" s="4" t="n">
-        <v>425.85</v>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>2.37% (10.1)</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="n">
-        <v>435.95</v>
-      </c>
-      <c r="G50" s="4" t="n">
-        <v>446.05</v>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr"/>
-      <c r="L50" s="4" t="n">
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2883,7 +1021,7 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="33" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
     <col width="29" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
@@ -2958,23 +1096,23 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Week Range: (21-09-2026 to 27-09-2026)</t>
         </is>
       </c>
-      <c r="B2" s="8" t="n"/>
-      <c r="C2" s="8" t="n"/>
-      <c r="D2" s="8" t="n"/>
-      <c r="E2" s="8" t="n"/>
-      <c r="F2" s="8" t="n"/>
-      <c r="G2" s="8" t="n"/>
-      <c r="H2" s="8" t="n"/>
-      <c r="I2" s="8" t="n"/>
-      <c r="J2" s="8" t="n"/>
-      <c r="K2" s="8" t="n"/>
-      <c r="L2" s="8" t="n"/>
-      <c r="M2" s="8" t="n"/>
+      <c r="B2" s="5" t="n"/>
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="5" t="n"/>
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="n"/>
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="5" t="n"/>
+      <c r="L2" s="5" t="n"/>
+      <c r="M2" s="5" t="n"/>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -3509,28 +1647,28 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>200.4</v>
+        <v>3029.5</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>196.1</v>
+        <v>2967.1</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>203.34</v>
+        <v>3039</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>3.56% (7.24)</t>
+          <t>2.37% (71.9)</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>210.58</v>
+        <v>3110.9</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>217.82</v>
+        <v>3182.8</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -3544,14 +1682,14 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:15 (Week End)</t>
+          <t>2026-09-25 15:00 (Week End)</t>
         </is>
       </c>
       <c r="K13" s="2" t="n">
-        <v>202.75</v>
+        <v>3035</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>-0.29</v>
+        <v>-0.13</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
@@ -3562,28 +1700,28 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>3029.5</v>
+        <v>200.4</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>2967.1</v>
+        <v>196.1</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3039</v>
+        <v>203.34</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>2.37% (71.9)</t>
+          <t>3.56% (7.24)</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3110.9</v>
+        <v>210.58</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3182.8</v>
+        <v>217.82</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -3597,14 +1735,14 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:00 (Week End)</t>
+          <t>2026-09-25 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K14" s="2" t="n">
-        <v>3035</v>
+        <v>202.75</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>-0.13</v>
+        <v>-0.29</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
@@ -3613,23 +1751,23 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Week Range: (28-09-2026 to 04-10-2026)</t>
         </is>
       </c>
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="n"/>
-      <c r="E15" s="8" t="n"/>
-      <c r="F15" s="8" t="n"/>
-      <c r="G15" s="8" t="n"/>
-      <c r="H15" s="8" t="n"/>
-      <c r="I15" s="8" t="n"/>
-      <c r="J15" s="8" t="n"/>
-      <c r="K15" s="8" t="n"/>
-      <c r="L15" s="8" t="n"/>
-      <c r="M15" s="8" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -3662,7 +1800,7 @@
           <t>2026-09-28 10:00</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -3823,12 +1961,12 @@
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 15:00 (Active)</t>
+          <t>2026-09-28 15:00 (Week End)</t>
         </is>
       </c>
       <c r="K19" s="2" t="n">
@@ -3874,7 +2012,7 @@
           <t>2026-09-28 13:45</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I20" s="8" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -3929,12 +2067,12 @@
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 15:15 (Active)</t>
+          <t>2026-09-28 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K21" s="2" t="n">
@@ -3982,12 +2120,12 @@
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 15:15 (Active)</t>
+          <t>2026-09-28 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K22" s="2" t="n">
@@ -4033,7 +2171,7 @@
           <t>2026-09-28 15:15</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="I23" s="8" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -4058,49 +2196,49 @@
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>906.9</v>
+        <v>864.2</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>889.7</v>
+        <v>859.7</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>907.5</v>
+        <v>864.8</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>1.96% (17.8)</t>
+          <t>0.59% (5.1)</t>
         </is>
       </c>
       <c r="F24" s="4" t="n">
-        <v>925.3</v>
+        <v>869.9</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>943.1</v>
+        <v>875</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 09:15</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:15</t>
+          <t>2026-09-29 09:30</t>
         </is>
       </c>
       <c r="K24" s="2" t="n">
-        <v>889.7</v>
+        <v>859.7</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>-1.96</v>
+        <v>-0.59</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
@@ -4111,49 +2249,49 @@
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>864.2</v>
+        <v>906.9</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>859.7</v>
+        <v>889.7</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>864.8</v>
+        <v>907.5</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>0.59% (5.1)</t>
+          <t>1.96% (17.8)</t>
         </is>
       </c>
       <c r="F25" s="4" t="n">
-        <v>869.9</v>
+        <v>925.3</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>875</v>
+        <v>943.1</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 09:15</t>
         </is>
       </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 09:30</t>
+          <t>2026-09-29 10:15</t>
         </is>
       </c>
       <c r="K25" s="2" t="n">
-        <v>859.7</v>
+        <v>889.7</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>-0.59</v>
+        <v>-1.96</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
@@ -4192,7 +2330,7 @@
           <t>2026-09-29 09:15</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="I26" s="8" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -4245,9 +2383,9 @@
           <t>2026-09-29 09:30</t>
         </is>
       </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -4300,12 +2438,12 @@
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:15 (Active)</t>
+          <t>2026-09-29 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K28" s="2" t="n">
@@ -4353,12 +2491,12 @@
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:00 (Active)</t>
+          <t>2026-09-29 15:00 (Week End)</t>
         </is>
       </c>
       <c r="K29" s="2" t="n">
@@ -4404,7 +2542,7 @@
           <t>2026-09-29 11:30</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="I30" s="8" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -4459,12 +2597,12 @@
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:15 (Active)</t>
+          <t>2026-09-29 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K31" s="2" t="n">
@@ -4512,12 +2650,12 @@
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:15 (Active)</t>
+          <t>2026-09-29 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K32" s="2" t="n">
@@ -4565,12 +2703,12 @@
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:15 (Active)</t>
+          <t>2026-09-29 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K33" s="2" t="n">
@@ -4618,12 +2756,12 @@
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:00 (Active)</t>
+          <t>2026-09-29 15:00 (Week End)</t>
         </is>
       </c>
       <c r="K34" s="2" t="n">
@@ -4724,12 +2862,12 @@
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:15 (Active)</t>
+          <t>2026-09-29 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K36" s="2" t="n">
@@ -4777,12 +2915,12 @@
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:15 (Active)</t>
+          <t>2026-09-29 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K37" s="2" t="n">
@@ -4828,7 +2966,7 @@
           <t>2026-09-29 14:45</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="I38" s="8" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -4881,9 +3019,9 @@
           <t>2026-09-29 15:00</t>
         </is>
       </c>
-      <c r="I39" s="6" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4936,12 +3074,12 @@
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 15:15 (Active)</t>
+          <t>2026-09-30 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K40" s="2" t="n">
@@ -4989,12 +3127,12 @@
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:30 (Active)</t>
+          <t>2026-09-30 12:30 (Week End)</t>
         </is>
       </c>
       <c r="K41" s="2" t="n">
@@ -5040,9 +3178,9 @@
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I42" s="6" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5199,7 +3337,7 @@
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="I45" s="8" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -5360,12 +3498,12 @@
       </c>
       <c r="I48" s="7" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 15:15 (Active)</t>
+          <t>2026-09-30 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K48" s="2" t="n">
@@ -5466,12 +3604,12 @@
       </c>
       <c r="I50" s="7" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 15:15 (Active)</t>
+          <t>2026-10-01 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K50" s="2" t="n">

--- a/data/trade_tracker_results.xlsx
+++ b/data/trade_tracker_results.xlsx
@@ -74,8 +74,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-        <bgColor rgb="00D9E1F2"/>
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -86,8 +86,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -129,13 +129,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -518,7 +518,7 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
   </cols>
@@ -588,28 +588,28 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>378.65</v>
+        <v>7910</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>377.05</v>
+        <v>7807.5</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>384.35</v>
+        <v>8005</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>1.9% (7.3)</t>
+          <t>2.47% (197.5)</t>
         </is>
       </c>
       <c r="F2" s="4" t="n">
-        <v>391.65</v>
+        <v>8202.5</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>398.95</v>
+        <v>8400</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -634,74 +634,76 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>296.5</v>
+        <v>378.65</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>294.55</v>
+        <v>377.05</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>296.8</v>
+        <v>384.35</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>0.76% (2.25)</t>
+          <t>1.9% (7.3)</t>
         </is>
       </c>
       <c r="F3" s="4" t="n">
-        <v>299.05</v>
+        <v>391.65</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>301.3</v>
+        <v>398.95</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-06 09:15</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr"/>
+          <t>2026-10-06 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>387.4</v>
+      </c>
       <c r="L3" s="4" t="n">
-        <v>0</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>BPCL</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>4737</v>
+        <v>296.5</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>4734.1</v>
+        <v>294.55</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>4770.2</v>
+        <v>296.8</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>0.76% (36.1)</t>
+          <t>0.76% (2.25)</t>
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>4806.3</v>
+        <v>299.05</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>4842.4</v>
+        <v>301.3</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -726,74 +728,76 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1333.4</v>
+        <v>4737</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1321.3</v>
+        <v>4734.1</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1334</v>
+        <v>4770.2</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>0.95% (12.7)</t>
+          <t>0.76% (36.1)</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1346.7</v>
+        <v>4806.3</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>1359.4</v>
+        <v>4842.4</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-06 09:15</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr"/>
+          <t>2026-10-06 11:15</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>4842.4</v>
+      </c>
       <c r="L5" s="4" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1194.9</v>
+        <v>1333.4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1189.9</v>
+        <v>1321.3</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1202.9</v>
+        <v>1334</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>1.08% (13.0)</t>
+          <t>0.95% (12.7)</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1215.9</v>
+        <v>1346.7</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1228.9</v>
+        <v>1359.4</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -818,74 +822,76 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>5051</v>
+        <v>1194.9</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>4995.5</v>
+        <v>1189.9</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>5200</v>
+        <v>1202.9</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>3.93% (204.5)</t>
+          <t>1.08% (13.0)</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>5404.5</v>
+        <v>1215.9</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>5609</v>
+        <v>1228.9</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-06 09:15</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr"/>
+          <t>2026-10-06 15:00 (Active)</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>1208</v>
+      </c>
       <c r="L7" s="4" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1295</v>
+        <v>5051</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1293</v>
+        <v>4995.5</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1299.4</v>
+        <v>5200</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>0.49% (6.4)</t>
+          <t>3.93% (204.5)</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1305.8</v>
+        <v>5404.5</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1312.2</v>
+        <v>5609</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -910,28 +916,28 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>4717.3</v>
+        <v>1295</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>4710</v>
+        <v>1293</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>4724.4</v>
+        <v>1299.4</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>0.3% (14.4)</t>
+          <t>0.49% (6.4)</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>4738.8</v>
+        <v>1305.8</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>4753.2</v>
+        <v>1312.2</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -956,28 +962,28 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>3930.1</v>
+        <v>1510.5</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>3920</v>
+        <v>1505.4</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>4031.6</v>
+        <v>1539.5</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>2.77% (111.6)</t>
+          <t>2.22% (34.1)</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4143.2</v>
+        <v>1573.6</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>4254.8</v>
+        <v>1607.7</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -996,6 +1002,560 @@
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>4717.3</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>4702.5</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>4777.2</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>1.56% (74.7)</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>4851.9</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>4926.6</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>3930.1</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>3920</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>4031.6</v>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>2.77% (111.6)</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>4143.2</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>4254.8</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:15</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>3981</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>-1.26</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>2377</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>2336.9</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>2393.6</v>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>2.37% (56.7)</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>2450.3</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>2507</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>168.43</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>166.48</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>168.99</v>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>1.49% (2.51)</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>171.5</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>174.01</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>2944.4</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>2936.1</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>2955</v>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>0.64% (18.9)</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>2973.9</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>2992.8</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>706.25</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>701</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>706.6</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>0.79% (5.6)</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>712.2</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>717.8</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>131.02</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>129.72</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>131.11</v>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>1.06% (1.39)</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>133.89</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>IRFC</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>76.51000000000001</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>76.06999999999999</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>77.12</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>1.36% (1.05)</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>78.17</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>79.22</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>1079</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>1035.8</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>1097.3</v>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>5.6% (61.5)</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>1158.8</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>1220.3</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>MAXHEALTH</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>902.05</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>892.9</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>918.6</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>2.8% (25.7)</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>944.3</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>970</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>3709.5</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>3695</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>3723.8</v>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>0.77% (28.8)</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>3752.6</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>3781.4</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>1792.6</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>1769.1</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>1797.1</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>1.56% (28.0)</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>1825.1</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>1853.1</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1010,7 +1570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1096,23 +1656,23 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Week Range: (21-09-2026 to 27-09-2026)</t>
         </is>
       </c>
-      <c r="B2" s="5" t="n"/>
-      <c r="C2" s="5" t="n"/>
-      <c r="D2" s="5" t="n"/>
-      <c r="E2" s="5" t="n"/>
-      <c r="F2" s="5" t="n"/>
-      <c r="G2" s="5" t="n"/>
-      <c r="H2" s="5" t="n"/>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="n"/>
-      <c r="L2" s="5" t="n"/>
-      <c r="M2" s="5" t="n"/>
+      <c r="B2" s="7" t="n"/>
+      <c r="C2" s="7" t="n"/>
+      <c r="D2" s="7" t="n"/>
+      <c r="E2" s="7" t="n"/>
+      <c r="F2" s="7" t="n"/>
+      <c r="G2" s="7" t="n"/>
+      <c r="H2" s="7" t="n"/>
+      <c r="I2" s="7" t="n"/>
+      <c r="J2" s="7" t="n"/>
+      <c r="K2" s="7" t="n"/>
+      <c r="L2" s="7" t="n"/>
+      <c r="M2" s="7" t="n"/>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -1198,7 +1758,7 @@
           <t>2026-09-23 11:00</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -1251,7 +1811,7 @@
           <t>2026-09-23 14:15</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -1304,7 +1864,7 @@
           <t>2026-09-24 09:30</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -1357,7 +1917,7 @@
           <t>2026-09-24 10:00</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -1410,7 +1970,7 @@
           <t>2026-09-24 10:00</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -1463,7 +2023,7 @@
           <t>2026-09-24 12:30</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -1569,7 +2129,7 @@
           <t>2026-09-25 14:00</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -1622,7 +2182,7 @@
           <t>2026-09-25 14:00</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -1675,7 +2235,7 @@
           <t>2026-09-25 14:15</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -1728,7 +2288,7 @@
           <t>2026-09-25 14:15</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -1751,23 +2311,23 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>Week Range: (28-09-2026 to 04-10-2026)</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="n"/>
-      <c r="L15" s="5" t="n"/>
-      <c r="M15" s="5" t="n"/>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="7" t="n"/>
+      <c r="I15" s="7" t="n"/>
+      <c r="J15" s="7" t="n"/>
+      <c r="K15" s="7" t="n"/>
+      <c r="L15" s="7" t="n"/>
+      <c r="M15" s="7" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -1959,7 +2519,7 @@
           <t>2026-09-28 13:15</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2065,7 +2625,7 @@
           <t>2026-09-28 14:00</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2118,7 +2678,7 @@
           <t>2026-09-28 15:15</t>
         </is>
       </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2383,7 +2943,7 @@
           <t>2026-09-29 09:30</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2436,7 +2996,7 @@
           <t>2026-09-29 11:00</t>
         </is>
       </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2489,7 +3049,7 @@
           <t>2026-09-29 11:15</t>
         </is>
       </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="I29" s="5" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2595,7 +3155,7 @@
           <t>2026-09-29 11:30</t>
         </is>
       </c>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2648,7 +3208,7 @@
           <t>2026-09-29 11:45</t>
         </is>
       </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2701,7 +3261,7 @@
           <t>2026-09-29 12:00</t>
         </is>
       </c>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2754,7 +3314,7 @@
           <t>2026-09-29 13:00</t>
         </is>
       </c>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="I34" s="5" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2860,7 +3420,7 @@
           <t>2026-09-29 14:00</t>
         </is>
       </c>
-      <c r="I36" s="7" t="inlineStr">
+      <c r="I36" s="5" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2913,7 +3473,7 @@
           <t>2026-09-29 14:45</t>
         </is>
       </c>
-      <c r="I37" s="7" t="inlineStr">
+      <c r="I37" s="5" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3019,7 +3579,7 @@
           <t>2026-09-29 15:00</t>
         </is>
       </c>
-      <c r="I39" s="7" t="inlineStr">
+      <c r="I39" s="5" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3044,35 +3604,35 @@
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>160.5</v>
+        <v>1766.7</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>159.41</v>
+        <v>1736.8</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>162.37</v>
+        <v>1770.1</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>1.82% (2.96)</t>
+          <t>1.88% (33.3)</t>
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>165.33</v>
+        <v>1803.4</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>168.29</v>
+        <v>1836.7</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I40" s="7" t="inlineStr">
+      <c r="I40" s="5" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3083,10 +3643,10 @@
         </is>
       </c>
       <c r="K40" s="2" t="n">
-        <v>163.26</v>
+        <v>1798.3</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>0.55</v>
+        <v>1.59</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
@@ -3097,49 +3657,49 @@
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>2391</v>
+        <v>4057</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>2381.6</v>
+        <v>4043.3</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>2420</v>
+        <v>4095</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>1.59% (38.4)</t>
+          <t>1.26% (51.7)</t>
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>2458.4</v>
+        <v>4146.7</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>2496.8</v>
+        <v>4198.4</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I41" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:30 (Week End)</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="K41" s="2" t="n">
-        <v>2409.1</v>
+        <v>4043.3</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-0.45</v>
+        <v>-1.26</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
@@ -3150,49 +3710,49 @@
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>196.1</v>
+        <v>4848.5</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>192.45</v>
+        <v>4837</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>196.67</v>
+        <v>4872</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>2.15% (4.22)</t>
+          <t>0.72% (35.0)</t>
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>200.89</v>
+        <v>4907</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>205.11</v>
+        <v>4942</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I42" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:15</t>
+          <t>2026-09-30 10:30</t>
         </is>
       </c>
       <c r="K42" s="2" t="n">
-        <v>200.89</v>
-      </c>
-      <c r="L42" s="4" t="n">
-        <v>2.15</v>
+        <v>4837</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>-0.72</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
@@ -3203,49 +3763,49 @@
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>991.6</v>
+        <v>263.55</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>980.4</v>
+        <v>263.3</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>992.7</v>
+        <v>266.2</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>1.24% (12.3)</t>
+          <t>1.09% (2.9)</t>
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>1005</v>
+        <v>269.1</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>1017.3</v>
+        <v>272</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I43" s="6" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I43" s="8" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-30 14:15</t>
         </is>
       </c>
       <c r="K43" s="2" t="n">
-        <v>1017.3</v>
-      </c>
-      <c r="L43" s="4" t="n">
-        <v>2.48</v>
+        <v>263.3</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>-1.09</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
@@ -3256,49 +3816,49 @@
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>399.3</v>
+        <v>196.1</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>394.7</v>
+        <v>192.45</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>403.65</v>
+        <v>196.67</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>2.22% (8.95)</t>
+          <t>2.15% (4.22)</t>
         </is>
       </c>
       <c r="F44" s="4" t="n">
-        <v>412.6</v>
+        <v>200.89</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>421.55</v>
+        <v>205.11</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I44" s="6" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 09:15</t>
+          <t>2026-09-30 09:15</t>
         </is>
       </c>
       <c r="K44" s="2" t="n">
-        <v>421.55</v>
+        <v>200.89</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>4.43</v>
+        <v>2.15</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
@@ -3309,49 +3869,49 @@
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>263.55</v>
+        <v>991.6</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>263.3</v>
+        <v>980.4</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>266.2</v>
+        <v>992.7</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>1.09% (2.9)</t>
+          <t>1.24% (12.3)</t>
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>269.1</v>
+        <v>1005</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>272</v>
+        <v>1017.3</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I45" s="8" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:15</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
       <c r="K45" s="2" t="n">
-        <v>263.3</v>
-      </c>
-      <c r="L45" s="3" t="n">
-        <v>-1.09</v>
+        <v>1017.3</v>
+      </c>
+      <c r="L45" s="4" t="n">
+        <v>2.48</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
@@ -3362,49 +3922,49 @@
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>4848.5</v>
+        <v>2391</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>4837</v>
+        <v>2381.6</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>4872</v>
+        <v>2420</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>0.72% (35.0)</t>
+          <t>1.59% (38.4)</t>
         </is>
       </c>
       <c r="F46" s="4" t="n">
-        <v>4907</v>
+        <v>2458.4</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>4942</v>
+        <v>2496.8</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I46" s="6" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 10:30</t>
+          <t>2026-09-30 12:30 (Week End)</t>
         </is>
       </c>
       <c r="K46" s="2" t="n">
-        <v>4837</v>
+        <v>2409.1</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>-0.72</v>
+        <v>-0.45</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
@@ -3415,49 +3975,49 @@
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>4057</v>
+        <v>160.5</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>4043.3</v>
+        <v>159.41</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>4095</v>
+        <v>162.37</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>1.26% (51.7)</t>
+          <t>1.82% (2.96)</t>
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>4146.7</v>
+        <v>165.33</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>4198.4</v>
+        <v>168.29</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I47" s="6" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 09:15</t>
+          <t>2026-09-30 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K47" s="2" t="n">
-        <v>4043.3</v>
-      </c>
-      <c r="L47" s="3" t="n">
-        <v>-1.26</v>
+        <v>163.26</v>
+      </c>
+      <c r="L47" s="4" t="n">
+        <v>0.55</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
@@ -3468,49 +4028,49 @@
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>1766.7</v>
+        <v>399.3</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1736.8</v>
+        <v>394.7</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>1770.1</v>
+        <v>403.65</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>1.88% (33.3)</t>
+          <t>2.22% (8.95)</t>
         </is>
       </c>
       <c r="F48" s="4" t="n">
-        <v>1803.4</v>
+        <v>412.6</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>1836.7</v>
+        <v>421.55</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I48" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 15:15 (Week End)</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="K48" s="2" t="n">
-        <v>1798.3</v>
+        <v>421.55</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>1.59</v>
+        <v>4.43</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
@@ -3602,7 +4162,7 @@
           <t>2026-10-01 09:15</t>
         </is>
       </c>
-      <c r="I50" s="7" t="inlineStr">
+      <c r="I50" s="5" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3624,9 +4184,241 @@
         </is>
       </c>
     </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>Week Range: (05-10-2026 to 11-10-2026)</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="n"/>
+      <c r="C51" s="7" t="n"/>
+      <c r="D51" s="7" t="n"/>
+      <c r="E51" s="7" t="n"/>
+      <c r="F51" s="7" t="n"/>
+      <c r="G51" s="7" t="n"/>
+      <c r="H51" s="7" t="n"/>
+      <c r="I51" s="7" t="n"/>
+      <c r="J51" s="7" t="n"/>
+      <c r="K51" s="7" t="n"/>
+      <c r="L51" s="7" t="n"/>
+      <c r="M51" s="7" t="n"/>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>1194.9</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>1189.9</v>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>1202.9</v>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>1.08% (13.0)</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>1215.9</v>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>1228.9</v>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:15</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06 15:00 (Active)</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>1208</v>
+      </c>
+      <c r="L52" s="4" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>(05-10-2026 to 11-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>378.65</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>377.05</v>
+      </c>
+      <c r="D53" s="4" t="n">
+        <v>384.35</v>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>1.9% (7.3)</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>391.65</v>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>398.95</v>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:15</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>387.4</v>
+      </c>
+      <c r="L53" s="4" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>(05-10-2026 to 11-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>4737</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>4734.1</v>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>4770.2</v>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>0.76% (36.1)</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>4806.3</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>4842.4</v>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:15</t>
+        </is>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:15</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>4842.4</v>
+      </c>
+      <c r="L54" s="4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>(05-10-2026 to 11-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>3930.1</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>3920</v>
+      </c>
+      <c r="D55" s="4" t="n">
+        <v>4031.6</v>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>2.77% (111.6)</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>4143.2</v>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>4254.8</v>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:15</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>3981</v>
+      </c>
+      <c r="L55" s="3" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>(05-10-2026 to 11-10-2026)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A51:M51"/>
     <mergeCell ref="A15:M15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trade_tracker_results.xlsx
+++ b/data/trade_tracker_results.xlsx
@@ -74,14 +74,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -129,10 +129,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -506,13 +506,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
@@ -659,24 +659,22 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 09:15</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>387.4</v>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="4" t="n">
-        <v>0.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -756,7 +754,7 @@
           <t>2026-10-06 09:15</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -832,39 +830,37 @@
         <v>1189.9</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1202.9</v>
+        <v>1198.7</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>1.08% (13.0)</t>
+          <t>0.73% (8.8)</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1215.9</v>
+        <v>1207.5</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1228.9</v>
+        <v>1216.3</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 09:15</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 15:00 (Active)</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>1208</v>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="4" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -941,22 +937,24 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-07 09:15</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr"/>
+          <t>2026-10-07 09:15</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>1312.2</v>
+      </c>
       <c r="L9" s="4" t="n">
-        <v>0</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -969,21 +967,21 @@
         <v>1510.5</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1505.4</v>
+        <v>1493.6</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>1539.5</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>2.22% (34.1)</t>
+          <t>2.98% (45.9)</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1573.6</v>
+        <v>1585.4</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1607.7</v>
+        <v>1631.3</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1061,42 +1059,40 @@
         <v>3930.1</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>3920</v>
+        <v>3870.8</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>4031.6</v>
+        <v>3977</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>2.77% (111.6)</t>
+          <t>2.67% (106.2)</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>4143.2</v>
+        <v>4083.2</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>4254.8</v>
+        <v>4189.4</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 09:15</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>3981</v>
-      </c>
-      <c r="L12" s="3" t="n">
-        <v>-1.26</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -1173,22 +1169,24 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-07 09:15</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr"/>
+          <t>2026-10-07 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>170.71</v>
+      </c>
       <c r="L14" s="4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -1201,21 +1199,21 @@
         <v>2944.4</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>2936.1</v>
+        <v>2928.9</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>2955</v>
+        <v>2969</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>0.64% (18.9)</t>
+          <t>1.35% (40.1)</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2973.9</v>
+        <v>3009.1</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2992.8</v>
+        <v>3049.2</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1339,21 +1337,21 @@
         <v>76.51000000000001</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>76.06999999999999</v>
+        <v>76.06</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>77.12</v>
+        <v>76.97</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>1.36% (1.05)</t>
+          <t>1.18% (0.91)</t>
         </is>
       </c>
       <c r="F18" s="4" t="n">
-        <v>78.17</v>
+        <v>77.88</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>79.22</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1431,21 +1429,21 @@
         <v>902.05</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>892.9</v>
+        <v>891.8</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>918.6</v>
+        <v>903</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>2.8% (25.7)</t>
+          <t>1.24% (11.2)</t>
         </is>
       </c>
       <c r="F20" s="4" t="n">
-        <v>944.3</v>
+        <v>914.2</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>970</v>
+        <v>925.4</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1495,22 +1493,24 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-07 09:15</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr"/>
+          <t>2026-10-07 09:15</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>3781.4</v>
+      </c>
       <c r="L21" s="4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -1556,6 +1556,190 @@
       </c>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>AMBUJACEM</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>356.3</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>352.8</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>359.1</v>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>1.75% (6.3)</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>365.4</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>371.7</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>945.8</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>945.7</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>949.9</v>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>0.44% (4.2)</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>954.1</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>958.3</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>936</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>930</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>960</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>3.12% (30.0)</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>990</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>1020</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>10612</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>10595</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>10759</v>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>1.52% (164.0)</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>10923</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>11087</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1570,7 +1754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1705,7 +1889,7 @@
           <t>2026-09-23 09:15</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -1758,7 +1942,7 @@
           <t>2026-09-23 11:00</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -1811,7 +1995,7 @@
           <t>2026-09-23 14:15</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -1864,7 +2048,7 @@
           <t>2026-09-24 09:30</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -1917,7 +2101,7 @@
           <t>2026-09-24 10:00</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -1970,7 +2154,7 @@
           <t>2026-09-24 10:00</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2023,7 +2207,7 @@
           <t>2026-09-24 12:30</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2076,7 +2260,7 @@
           <t>2026-09-25 10:00</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -2129,7 +2313,7 @@
           <t>2026-09-25 14:00</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2182,7 +2366,7 @@
           <t>2026-09-25 14:00</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2235,7 +2419,7 @@
           <t>2026-09-25 14:15</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2288,7 +2472,7 @@
           <t>2026-09-25 14:15</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2413,7 +2597,7 @@
           <t>2026-09-28 11:30</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -2466,7 +2650,7 @@
           <t>2026-09-28 12:00</t>
         </is>
       </c>
-      <c r="I18" s="6" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
@@ -2519,7 +2703,7 @@
           <t>2026-09-28 13:15</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="I19" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2625,7 +2809,7 @@
           <t>2026-09-28 14:00</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I21" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2678,7 +2862,7 @@
           <t>2026-09-28 15:15</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="I22" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2784,7 +2968,7 @@
           <t>2026-09-29 09:15</t>
         </is>
       </c>
-      <c r="I24" s="6" t="inlineStr">
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
@@ -2943,7 +3127,7 @@
           <t>2026-09-29 09:30</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I27" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2996,7 +3180,7 @@
           <t>2026-09-29 11:00</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="I28" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3049,7 +3233,7 @@
           <t>2026-09-29 11:15</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="I29" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3074,49 +3258,49 @@
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>1495.7</v>
+        <v>399.3</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1487.1</v>
+        <v>394.7</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1498</v>
+        <v>403.65</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>0.73% (10.9)</t>
+          <t>2.22% (8.95)</t>
         </is>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1508.9</v>
+        <v>412.6</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1519.8</v>
+        <v>421.55</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 11:30</t>
         </is>
       </c>
-      <c r="I30" s="8" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:30</t>
+          <t>2026-09-29 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K30" s="2" t="n">
-        <v>1487.1</v>
-      </c>
-      <c r="L30" s="3" t="n">
-        <v>-0.73</v>
+        <v>406</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>0.58</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
@@ -3127,49 +3311,49 @@
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>399.3</v>
+        <v>1495.7</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>394.7</v>
+        <v>1487.1</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>403.65</v>
+        <v>1498</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>2.22% (8.95)</t>
+          <t>0.73% (10.9)</t>
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>412.6</v>
+        <v>1508.9</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>421.55</v>
+        <v>1519.8</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 11:30</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I31" s="8" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:15 (Week End)</t>
+          <t>2026-09-29 12:30</t>
         </is>
       </c>
       <c r="K31" s="2" t="n">
-        <v>406</v>
-      </c>
-      <c r="L31" s="4" t="n">
-        <v>0.58</v>
+        <v>1487.1</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>-0.73</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
@@ -3208,7 +3392,7 @@
           <t>2026-09-29 11:45</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="I32" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3261,7 +3445,7 @@
           <t>2026-09-29 12:00</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="I33" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3314,7 +3498,7 @@
           <t>2026-09-29 13:00</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="I34" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3367,7 +3551,7 @@
           <t>2026-09-29 14:00</t>
         </is>
       </c>
-      <c r="I35" s="6" t="inlineStr">
+      <c r="I35" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -3420,7 +3604,7 @@
           <t>2026-09-29 14:00</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="I36" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3473,7 +3657,7 @@
           <t>2026-09-29 14:45</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="I37" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3579,7 +3763,7 @@
           <t>2026-09-29 15:00</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="I39" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3604,28 +3788,28 @@
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>1766.7</v>
+        <v>399.3</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1736.8</v>
+        <v>394.7</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>1770.1</v>
+        <v>403.65</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>1.88% (33.3)</t>
+          <t>2.22% (8.95)</t>
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>1803.4</v>
+        <v>412.6</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>1836.7</v>
+        <v>421.55</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -3634,19 +3818,19 @@
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>ACTIVE (Week End)</t>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 15:15 (Week End)</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="K40" s="2" t="n">
-        <v>1798.3</v>
+        <v>421.55</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>1.59</v>
+        <v>4.43</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
@@ -3657,28 +3841,28 @@
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>4057</v>
+        <v>160.5</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>4043.3</v>
+        <v>159.41</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>4095</v>
+        <v>162.37</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>1.26% (51.7)</t>
+          <t>1.82% (2.96)</t>
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>4146.7</v>
+        <v>165.33</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>4198.4</v>
+        <v>168.29</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -3687,19 +3871,19 @@
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 09:15</t>
+          <t>2026-09-30 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K41" s="2" t="n">
-        <v>4043.3</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>-1.26</v>
+        <v>163.26</v>
+      </c>
+      <c r="L41" s="4" t="n">
+        <v>0.55</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
@@ -3710,28 +3894,28 @@
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>4848.5</v>
+        <v>2391</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>4837</v>
+        <v>2381.6</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>4872</v>
+        <v>2420</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>0.72% (35.0)</t>
+          <t>1.59% (38.4)</t>
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>4907</v>
+        <v>2458.4</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>4942</v>
+        <v>2496.8</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -3740,19 +3924,19 @@
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 10:30</t>
+          <t>2026-09-30 12:30 (Week End)</t>
         </is>
       </c>
       <c r="K42" s="2" t="n">
-        <v>4837</v>
+        <v>2409.1</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>-0.72</v>
+        <v>-0.45</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
@@ -3763,49 +3947,49 @@
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>263.55</v>
+        <v>991.6</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>263.3</v>
+        <v>980.4</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>266.2</v>
+        <v>992.7</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>1.09% (2.9)</t>
+          <t>1.24% (12.3)</t>
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>269.1</v>
+        <v>1005</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>272</v>
+        <v>1017.3</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I43" s="8" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:15</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
       <c r="K43" s="2" t="n">
-        <v>263.3</v>
-      </c>
-      <c r="L43" s="3" t="n">
-        <v>-1.09</v>
+        <v>1017.3</v>
+      </c>
+      <c r="L43" s="4" t="n">
+        <v>2.48</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
@@ -3844,7 +4028,7 @@
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I44" s="5" t="inlineStr">
+      <c r="I44" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3869,49 +4053,49 @@
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>991.6</v>
+        <v>263.55</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>980.4</v>
+        <v>263.3</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>992.7</v>
+        <v>266.2</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>1.24% (12.3)</t>
+          <t>1.09% (2.9)</t>
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>1005</v>
+        <v>269.1</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>1017.3</v>
+        <v>272</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I45" s="8" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-30 14:15</t>
         </is>
       </c>
       <c r="K45" s="2" t="n">
-        <v>1017.3</v>
-      </c>
-      <c r="L45" s="4" t="n">
-        <v>2.48</v>
+        <v>263.3</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>-1.09</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
@@ -3922,28 +4106,28 @@
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>2391</v>
+        <v>4848.5</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>2381.6</v>
+        <v>4837</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>2420</v>
+        <v>4872</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>1.59% (38.4)</t>
+          <t>0.72% (35.0)</t>
         </is>
       </c>
       <c r="F46" s="4" t="n">
-        <v>2458.4</v>
+        <v>4907</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>2496.8</v>
+        <v>4942</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -3952,19 +4136,19 @@
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>ACTIVE (Week End)</t>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:30 (Week End)</t>
+          <t>2026-09-30 10:30</t>
         </is>
       </c>
       <c r="K46" s="2" t="n">
-        <v>2409.1</v>
+        <v>4837</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>-0.45</v>
+        <v>-0.72</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
@@ -3975,28 +4159,28 @@
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>160.5</v>
+        <v>4057</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>159.41</v>
+        <v>4043.3</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>162.37</v>
+        <v>4095</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>1.82% (2.96)</t>
+          <t>1.26% (51.7)</t>
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>165.33</v>
+        <v>4146.7</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>168.29</v>
+        <v>4198.4</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -4005,19 +4189,19 @@
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>ACTIVE (Week End)</t>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 15:15 (Week End)</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="K47" s="2" t="n">
-        <v>163.26</v>
-      </c>
-      <c r="L47" s="4" t="n">
-        <v>0.55</v>
+        <v>4043.3</v>
+      </c>
+      <c r="L47" s="3" t="n">
+        <v>-1.26</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
@@ -4028,28 +4212,28 @@
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>399.3</v>
+        <v>1766.7</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>394.7</v>
+        <v>1736.8</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>403.65</v>
+        <v>1770.1</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>2.22% (8.95)</t>
+          <t>1.88% (33.3)</t>
         </is>
       </c>
       <c r="F48" s="4" t="n">
-        <v>412.6</v>
+        <v>1803.4</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>421.55</v>
+        <v>1836.7</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -4058,19 +4242,19 @@
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 09:15</t>
+          <t>2026-09-30 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K48" s="2" t="n">
-        <v>421.55</v>
+        <v>1798.3</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>4.43</v>
+        <v>1.59</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
@@ -4109,7 +4293,7 @@
           <t>2026-10-01 09:15</t>
         </is>
       </c>
-      <c r="I49" s="6" t="inlineStr">
+      <c r="I49" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -4162,7 +4346,7 @@
           <t>2026-10-01 09:15</t>
         </is>
       </c>
-      <c r="I50" s="5" t="inlineStr">
+      <c r="I50" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -4234,7 +4418,7 @@
           <t>2026-10-06 09:15</t>
         </is>
       </c>
-      <c r="I52" s="5" t="inlineStr">
+      <c r="I52" s="6" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -4287,7 +4471,7 @@
           <t>2026-10-06 09:15</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="I53" s="6" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -4312,28 +4496,28 @@
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>4737</v>
+        <v>3930.1</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>4734.1</v>
+        <v>3920</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>4770.2</v>
+        <v>4031.6</v>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>0.76% (36.1)</t>
+          <t>2.77% (111.6)</t>
         </is>
       </c>
       <c r="F54" s="4" t="n">
-        <v>4806.3</v>
+        <v>4143.2</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>4842.4</v>
+        <v>4254.8</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -4342,19 +4526,19 @@
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 11:15</t>
+          <t>2026-10-06 15:15 (Active)</t>
         </is>
       </c>
       <c r="K54" s="2" t="n">
-        <v>4842.4</v>
-      </c>
-      <c r="L54" s="4" t="n">
-        <v>1.51</v>
+        <v>3981</v>
+      </c>
+      <c r="L54" s="3" t="n">
+        <v>-1.26</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
@@ -4365,28 +4549,28 @@
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>3930.1</v>
+        <v>4737</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>3920</v>
+        <v>4734.1</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>4031.6</v>
+        <v>4770.2</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>2.77% (111.6)</t>
+          <t>0.76% (36.1)</t>
         </is>
       </c>
       <c r="F55" s="4" t="n">
-        <v>4143.2</v>
+        <v>4806.3</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>4254.8</v>
+        <v>4842.4</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -4395,21 +4579,180 @@
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:15</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>4842.4</v>
+      </c>
+      <c r="L55" s="4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>(05-10-2026 to 11-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>1295</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>1293</v>
+      </c>
+      <c r="D56" s="4" t="n">
+        <v>1299.4</v>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>0.49% (6.4)</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>1305.8</v>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>1312.2</v>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07 09:15</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07 09:15</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>1312.2</v>
+      </c>
+      <c r="L56" s="4" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>(05-10-2026 to 11-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>168.43</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>166.48</v>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>168.99</v>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>1.49% (2.51)</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>171.5</v>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>174.01</v>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07 09:15</t>
+        </is>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-06 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="n">
-        <v>3981</v>
-      </c>
-      <c r="L55" s="3" t="n">
-        <v>-1.26</v>
-      </c>
-      <c r="M55" s="2" t="inlineStr">
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>170.71</v>
+      </c>
+      <c r="L57" s="4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>(05-10-2026 to 11-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>3709.5</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>3695</v>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>3723.8</v>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>0.77% (28.8)</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>3752.6</v>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>3781.4</v>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07 09:15</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07 09:15</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>3781.4</v>
+      </c>
+      <c r="L58" s="4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
         <is>
           <t>(05-10-2026 to 11-10-2026)</t>
         </is>

--- a/data/trade_tracker_results.xlsx
+++ b/data/trade_tracker_results.xlsx
@@ -80,8 +80,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -92,8 +92,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -132,13 +132,13 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -518,7 +518,7 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="27" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
   </cols>
@@ -827,21 +827,21 @@
         <v>1194.9</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1189.9</v>
+        <v>1189.5</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1198.7</v>
+        <v>1203.8</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>0.73% (8.8)</t>
+          <t>1.19% (14.3)</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1207.5</v>
+        <v>1218.1</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1216.3</v>
+        <v>1232.4</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -967,21 +967,21 @@
         <v>1510.5</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1493.6</v>
+        <v>1487</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1539.5</v>
+        <v>1513</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>2.98% (45.9)</t>
+          <t>1.72% (26.0)</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1585.4</v>
+        <v>1539</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1631.3</v>
+        <v>1565</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1169,24 +1169,22 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 09:15</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>170.71</v>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -1633,22 +1631,24 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-08 09:15</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="4" t="n">
-        <v>0</v>
+          <t>2026-10-08 12:00</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>945.7</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>-0.44</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -1740,6 +1740,236 @@
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>1223.6</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>1209.4</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>1282</v>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>5.66% (72.6)</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>1354.6</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>1427.2</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>1702.1</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>1701</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>1710.1</v>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>0.53% (9.1)</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>1719.2</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>1728.3</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>254.65</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>253.2</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>255.4</v>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>0.86% (2.2)</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>257.6</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>259.8</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>1674.8</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>1658.6</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>1684.2</v>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>1.52% (25.6)</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>1709.8</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>1735.4</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>UNITDSPR</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>1316.5</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>1308.7</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>1323.7</v>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>1.13% (15.0)</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>1338.7</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>1353.7</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1754,7 +1984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1942,7 +2172,7 @@
           <t>2026-09-23 11:00</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -1995,7 +2225,7 @@
           <t>2026-09-23 14:15</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="I5" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2048,7 +2278,7 @@
           <t>2026-09-24 09:30</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2101,7 +2331,7 @@
           <t>2026-09-24 10:00</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2154,7 +2384,7 @@
           <t>2026-09-24 10:00</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2207,7 +2437,7 @@
           <t>2026-09-24 12:30</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="I9" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2313,7 +2543,7 @@
           <t>2026-09-25 14:00</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="I11" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2366,7 +2596,7 @@
           <t>2026-09-25 14:00</t>
         </is>
       </c>
-      <c r="I12" s="6" t="inlineStr">
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2419,7 +2649,7 @@
           <t>2026-09-25 14:15</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="I13" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2472,7 +2702,7 @@
           <t>2026-09-25 14:15</t>
         </is>
       </c>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2544,7 +2774,7 @@
           <t>2026-09-28 10:00</t>
         </is>
       </c>
-      <c r="I16" s="8" t="inlineStr">
+      <c r="I16" s="6" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -2703,7 +2933,7 @@
           <t>2026-09-28 13:15</t>
         </is>
       </c>
-      <c r="I19" s="6" t="inlineStr">
+      <c r="I19" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2756,7 +2986,7 @@
           <t>2026-09-28 13:45</t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="I20" s="6" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -2809,7 +3039,7 @@
           <t>2026-09-28 14:00</t>
         </is>
       </c>
-      <c r="I21" s="6" t="inlineStr">
+      <c r="I21" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2862,7 +3092,7 @@
           <t>2026-09-28 15:15</t>
         </is>
       </c>
-      <c r="I22" s="6" t="inlineStr">
+      <c r="I22" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2915,7 +3145,7 @@
           <t>2026-09-28 15:15</t>
         </is>
       </c>
-      <c r="I23" s="8" t="inlineStr">
+      <c r="I23" s="6" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -3021,7 +3251,7 @@
           <t>2026-09-29 09:15</t>
         </is>
       </c>
-      <c r="I25" s="8" t="inlineStr">
+      <c r="I25" s="6" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -3074,7 +3304,7 @@
           <t>2026-09-29 09:15</t>
         </is>
       </c>
-      <c r="I26" s="8" t="inlineStr">
+      <c r="I26" s="6" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -3127,7 +3357,7 @@
           <t>2026-09-29 09:30</t>
         </is>
       </c>
-      <c r="I27" s="6" t="inlineStr">
+      <c r="I27" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3180,7 +3410,7 @@
           <t>2026-09-29 11:00</t>
         </is>
       </c>
-      <c r="I28" s="6" t="inlineStr">
+      <c r="I28" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3233,7 +3463,7 @@
           <t>2026-09-29 11:15</t>
         </is>
       </c>
-      <c r="I29" s="6" t="inlineStr">
+      <c r="I29" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3258,28 +3488,28 @@
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>399.3</v>
+        <v>1495.7</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>394.7</v>
+        <v>1487.1</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>403.65</v>
+        <v>1498</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>2.22% (8.95)</t>
+          <t>0.73% (10.9)</t>
         </is>
       </c>
       <c r="F30" s="4" t="n">
-        <v>412.6</v>
+        <v>1508.9</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>421.55</v>
+        <v>1519.8</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -3288,19 +3518,19 @@
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>ACTIVE (Week End)</t>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:15 (Week End)</t>
+          <t>2026-09-29 12:30</t>
         </is>
       </c>
       <c r="K30" s="2" t="n">
-        <v>406</v>
-      </c>
-      <c r="L30" s="4" t="n">
-        <v>0.58</v>
+        <v>1487.1</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>-0.73</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
@@ -3311,28 +3541,28 @@
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>1495.7</v>
+        <v>399.3</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1487.1</v>
+        <v>394.7</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1498</v>
+        <v>403.65</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>0.73% (10.9)</t>
+          <t>2.22% (8.95)</t>
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1508.9</v>
+        <v>412.6</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1519.8</v>
+        <v>421.55</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -3341,19 +3571,19 @@
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>SL HIT</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:30</t>
+          <t>2026-09-29 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K31" s="2" t="n">
-        <v>1487.1</v>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>-0.73</v>
+        <v>406</v>
+      </c>
+      <c r="L31" s="4" t="n">
+        <v>0.58</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
@@ -3392,7 +3622,7 @@
           <t>2026-09-29 11:45</t>
         </is>
       </c>
-      <c r="I32" s="6" t="inlineStr">
+      <c r="I32" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3445,7 +3675,7 @@
           <t>2026-09-29 12:00</t>
         </is>
       </c>
-      <c r="I33" s="6" t="inlineStr">
+      <c r="I33" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3498,7 +3728,7 @@
           <t>2026-09-29 13:00</t>
         </is>
       </c>
-      <c r="I34" s="6" t="inlineStr">
+      <c r="I34" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3604,7 +3834,7 @@
           <t>2026-09-29 14:00</t>
         </is>
       </c>
-      <c r="I36" s="6" t="inlineStr">
+      <c r="I36" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3657,7 +3887,7 @@
           <t>2026-09-29 14:45</t>
         </is>
       </c>
-      <c r="I37" s="6" t="inlineStr">
+      <c r="I37" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3710,7 +3940,7 @@
           <t>2026-09-29 14:45</t>
         </is>
       </c>
-      <c r="I38" s="8" t="inlineStr">
+      <c r="I38" s="6" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -3763,7 +3993,7 @@
           <t>2026-09-29 15:00</t>
         </is>
       </c>
-      <c r="I39" s="6" t="inlineStr">
+      <c r="I39" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3788,49 +4018,49 @@
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>399.3</v>
+        <v>196.1</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>394.7</v>
+        <v>192.45</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>403.65</v>
+        <v>196.67</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>2.22% (8.95)</t>
+          <t>2.15% (4.22)</t>
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>412.6</v>
+        <v>200.89</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>421.55</v>
+        <v>205.11</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I40" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 09:15</t>
+          <t>2026-09-30 09:15</t>
         </is>
       </c>
       <c r="K40" s="2" t="n">
-        <v>421.55</v>
+        <v>200.89</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>4.43</v>
+        <v>2.15</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
@@ -3841,35 +4071,35 @@
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>160.5</v>
+        <v>1766.7</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>159.41</v>
+        <v>1736.8</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>162.37</v>
+        <v>1770.1</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>1.82% (2.96)</t>
+          <t>1.88% (33.3)</t>
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>165.33</v>
+        <v>1803.4</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>168.29</v>
+        <v>1836.7</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I41" s="6" t="inlineStr">
+      <c r="I41" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3880,10 +4110,10 @@
         </is>
       </c>
       <c r="K41" s="2" t="n">
-        <v>163.26</v>
+        <v>1798.3</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>0.55</v>
+        <v>1.59</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
@@ -3894,49 +4124,49 @@
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>2391</v>
+        <v>4057</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>2381.6</v>
+        <v>4043.3</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>2420</v>
+        <v>4095</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>1.59% (38.4)</t>
+          <t>1.26% (51.7)</t>
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>2458.4</v>
+        <v>4146.7</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>2496.8</v>
+        <v>4198.4</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I42" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:30 (Week End)</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="K42" s="2" t="n">
-        <v>2409.1</v>
+        <v>4043.3</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>-0.45</v>
+        <v>-1.26</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
@@ -3947,28 +4177,28 @@
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>991.6</v>
+        <v>4848.5</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>980.4</v>
+        <v>4837</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>992.7</v>
+        <v>4872</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>1.24% (12.3)</t>
+          <t>0.72% (35.0)</t>
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>1005</v>
+        <v>4907</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>1017.3</v>
+        <v>4942</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -3977,19 +4207,19 @@
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-30 10:30</t>
         </is>
       </c>
       <c r="K43" s="2" t="n">
-        <v>1017.3</v>
-      </c>
-      <c r="L43" s="4" t="n">
-        <v>2.48</v>
+        <v>4837</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>-0.72</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
@@ -4000,28 +4230,28 @@
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>196.1</v>
+        <v>263.55</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>192.45</v>
+        <v>263.3</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>196.67</v>
+        <v>266.2</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>2.15% (4.22)</t>
+          <t>1.09% (2.9)</t>
         </is>
       </c>
       <c r="F44" s="4" t="n">
-        <v>200.89</v>
+        <v>269.1</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>205.11</v>
+        <v>272</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -4030,19 +4260,19 @@
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>ACTIVE (Week End)</t>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:15</t>
+          <t>2026-09-30 14:15</t>
         </is>
       </c>
       <c r="K44" s="2" t="n">
-        <v>200.89</v>
-      </c>
-      <c r="L44" s="4" t="n">
-        <v>2.15</v>
+        <v>263.3</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>-1.09</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
@@ -4053,49 +4283,49 @@
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>263.55</v>
+        <v>991.6</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>263.3</v>
+        <v>980.4</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>266.2</v>
+        <v>992.7</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>1.09% (2.9)</t>
+          <t>1.24% (12.3)</t>
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>269.1</v>
+        <v>1005</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>272</v>
+        <v>1017.3</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I45" s="8" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:15</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
       <c r="K45" s="2" t="n">
-        <v>263.3</v>
-      </c>
-      <c r="L45" s="3" t="n">
-        <v>-1.09</v>
+        <v>1017.3</v>
+      </c>
+      <c r="L45" s="4" t="n">
+        <v>2.48</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
@@ -4106,49 +4336,49 @@
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>4848.5</v>
+        <v>2391</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>4837</v>
+        <v>2381.6</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>4872</v>
+        <v>2420</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>0.72% (35.0)</t>
+          <t>1.59% (38.4)</t>
         </is>
       </c>
       <c r="F46" s="4" t="n">
-        <v>4907</v>
+        <v>2458.4</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>4942</v>
+        <v>2496.8</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I46" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
+      <c r="I46" s="8" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 10:30</t>
+          <t>2026-09-30 12:30 (Week End)</t>
         </is>
       </c>
       <c r="K46" s="2" t="n">
-        <v>4837</v>
+        <v>2409.1</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>-0.72</v>
+        <v>-0.45</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
@@ -4159,49 +4389,49 @@
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>4057</v>
+        <v>160.5</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>4043.3</v>
+        <v>159.41</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>4095</v>
+        <v>162.37</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>1.26% (51.7)</t>
+          <t>1.82% (2.96)</t>
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>4146.7</v>
+        <v>165.33</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>4198.4</v>
+        <v>168.29</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I47" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
+      <c r="I47" s="8" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 09:15</t>
+          <t>2026-09-30 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K47" s="2" t="n">
-        <v>4043.3</v>
-      </c>
-      <c r="L47" s="3" t="n">
-        <v>-1.26</v>
+        <v>163.26</v>
+      </c>
+      <c r="L47" s="4" t="n">
+        <v>0.55</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
@@ -4212,49 +4442,49 @@
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>1766.7</v>
+        <v>399.3</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1736.8</v>
+        <v>394.7</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>1770.1</v>
+        <v>403.65</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>1.88% (33.3)</t>
+          <t>2.22% (8.95)</t>
         </is>
       </c>
       <c r="F48" s="4" t="n">
-        <v>1803.4</v>
+        <v>412.6</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>1836.7</v>
+        <v>421.55</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I48" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 15:15 (Week End)</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="K48" s="2" t="n">
-        <v>1798.3</v>
+        <v>421.55</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>1.59</v>
+        <v>4.43</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
@@ -4346,7 +4576,7 @@
           <t>2026-10-01 09:15</t>
         </is>
       </c>
-      <c r="I50" s="6" t="inlineStr">
+      <c r="I50" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -4418,7 +4648,7 @@
           <t>2026-10-06 09:15</t>
         </is>
       </c>
-      <c r="I52" s="6" t="inlineStr">
+      <c r="I52" s="8" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -4471,7 +4701,7 @@
           <t>2026-10-06 09:15</t>
         </is>
       </c>
-      <c r="I53" s="6" t="inlineStr">
+      <c r="I53" s="8" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -4524,7 +4754,7 @@
           <t>2026-10-06 09:15</t>
         </is>
       </c>
-      <c r="I54" s="6" t="inlineStr">
+      <c r="I54" s="8" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -4655,49 +4885,49 @@
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>168.43</v>
+        <v>3709.5</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>166.48</v>
+        <v>3695</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>168.99</v>
+        <v>3723.8</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>1.49% (2.51)</t>
+          <t>0.77% (28.8)</t>
         </is>
       </c>
       <c r="F57" s="4" t="n">
-        <v>171.5</v>
+        <v>3752.6</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>174.01</v>
+        <v>3781.4</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
           <t>2026-10-07 09:15</t>
         </is>
       </c>
-      <c r="I57" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 15:15 (Active)</t>
+          <t>2026-10-07 09:15</t>
         </is>
       </c>
       <c r="K57" s="2" t="n">
-        <v>170.71</v>
+        <v>3781.4</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
@@ -4708,51 +4938,104 @@
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>3709.5</v>
+        <v>168.43</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>3695</v>
+        <v>166.48</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>3723.8</v>
+        <v>168.99</v>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>0.77% (28.8)</t>
+          <t>1.49% (2.51)</t>
         </is>
       </c>
       <c r="F58" s="4" t="n">
-        <v>3752.6</v>
+        <v>171.5</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>3781.4</v>
+        <v>174.01</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
           <t>2026-10-07 09:15</t>
         </is>
       </c>
-      <c r="I58" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I58" s="8" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 09:15</t>
+          <t>2026-10-07 15:15 (Active)</t>
         </is>
       </c>
       <c r="K58" s="2" t="n">
-        <v>3781.4</v>
+        <v>170.71</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>1.55</v>
+        <v>1.02</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>(05-10-2026 to 11-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>945.8</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>945.7</v>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>949.9</v>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>0.44% (4.2)</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>954.1</v>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>958.3</v>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08 09:15</t>
+        </is>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:00</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>945.7</v>
+      </c>
+      <c r="L59" s="3" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
         <is>
           <t>(05-10-2026 to 11-10-2026)</t>
         </is>

--- a/data/trade_tracker_results.xlsx
+++ b/data/trade_tracker_results.xlsx
@@ -86,14 +86,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-        <bgColor rgb="00D9E1F2"/>
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -135,10 +135,10 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -518,7 +518,7 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
   </cols>
@@ -595,21 +595,21 @@
         <v>7910</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>7807.5</v>
+        <v>7608</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>8005</v>
+        <v>7917</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2.47% (197.5)</t>
+          <t>3.9% (309.0)</t>
         </is>
       </c>
       <c r="F2" s="4" t="n">
-        <v>8202.5</v>
+        <v>8226</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>8400</v>
+        <v>8535</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -827,21 +827,21 @@
         <v>1194.9</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1189.5</v>
+        <v>1167.4</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1203.8</v>
+        <v>1201</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>1.19% (14.3)</t>
+          <t>2.8% (33.6)</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1218.1</v>
+        <v>1234.6</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1232.4</v>
+        <v>1268.2</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -1243,21 +1243,21 @@
         <v>706.25</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>701</v>
+        <v>690.55</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>706.6</v>
+        <v>706.9</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>0.79% (5.6)</t>
+          <t>2.31% (16.35)</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>712.2</v>
+        <v>723.25</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>717.8</v>
+        <v>739.6</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1445,22 +1445,24 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-09 09:15</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="4" t="n">
-        <v>0</v>
+          <t>2026-10-09 09:15</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>891.8</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>-1.24</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -1613,42 +1615,40 @@
         <v>945.8</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>945.7</v>
+        <v>937.55</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>949.9</v>
+        <v>951.3</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>0.44% (4.2)</t>
+          <t>1.45% (13.75)</t>
         </is>
       </c>
       <c r="F24" s="4" t="n">
-        <v>954.1</v>
+        <v>965.05</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>958.3</v>
+        <v>978.8</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 09:15</t>
-        </is>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 12:00</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="n">
-        <v>945.7</v>
-      </c>
-      <c r="L24" s="3" t="n">
-        <v>-0.44</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -1661,21 +1661,21 @@
         <v>936</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>930</v>
+        <v>917.25</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>960</v>
+        <v>938.7</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>3.12% (30.0)</t>
+          <t>2.29% (21.45)</t>
         </is>
       </c>
       <c r="F25" s="4" t="n">
-        <v>990</v>
+        <v>960.15</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1020</v>
+        <v>981.6</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1707,21 +1707,21 @@
         <v>10612</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>10595</v>
+        <v>10426</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>10759</v>
+        <v>10690</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>1.52% (164.0)</t>
+          <t>2.47% (264.0)</t>
         </is>
       </c>
       <c r="F26" s="4" t="n">
-        <v>10923</v>
+        <v>10954</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>11087</v>
+        <v>11218</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -1817,22 +1817,24 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-09 09:15</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr"/>
+          <t>2026-10-09 09:45</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>1728.3</v>
+      </c>
       <c r="L28" s="4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -1863,22 +1865,24 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-09 09:15</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr"/>
+          <t>2026-10-09 10:00</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>259.8</v>
+      </c>
       <c r="L29" s="4" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -1909,22 +1913,24 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-09 09:15</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="4" t="n">
-        <v>0</v>
+          <t>2026-10-09 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>1682</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -1955,21 +1961,485 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
+          <t>2026-10-09 09:15</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09 10:15</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>1353.7</v>
+      </c>
+      <c r="L31" s="4" t="n">
+        <v>2.27</v>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>6660.5</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>6578</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>6789</v>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>3.11% (211.0)</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>7000</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>7211</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>WAIT (No Entry)</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr"/>
-      <c r="L31" s="4" t="n">
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>1716</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>1675</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>1750.1</v>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>4.29% (75.1)</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>1825.2</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>1900.3</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>854.2</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>840.15</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>864.45</v>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>2.81% (24.3)</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>888.75</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>913.05</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>1563.2</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>1543.1</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>1567.7</v>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>1.57% (24.6)</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>1592.3</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>1616.9</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>CUMMINSIND</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>4741</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>4671.1</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>4792.4</v>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>2.53% (121.3)</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>4913.7</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>5035</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>6840</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>6767.5</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>6872</v>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>1.52% (104.5)</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>6976.5</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>7081</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>3655.9</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>3607.1</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>3673.5</v>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>1.81% (66.4)</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>3739.9</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>3806.3</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>LTM</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>3936</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>3908.4</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>3941.6</v>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>0.84% (33.2)</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>3974.8</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>4008</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:15</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:15</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>4008</v>
+      </c>
+      <c r="L39" s="4" t="n">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>11305</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>11225</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>11342</v>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>1.03% (117.0)</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>11459</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>11576</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>220.6</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>218.75</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>220.85</v>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>0.95% (2.1)</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>222.95</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>225.05</v>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1984,7 +2454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2070,23 +2540,23 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Week Range: (21-09-2026 to 27-09-2026)</t>
         </is>
       </c>
-      <c r="B2" s="7" t="n"/>
-      <c r="C2" s="7" t="n"/>
-      <c r="D2" s="7" t="n"/>
-      <c r="E2" s="7" t="n"/>
-      <c r="F2" s="7" t="n"/>
-      <c r="G2" s="7" t="n"/>
-      <c r="H2" s="7" t="n"/>
-      <c r="I2" s="7" t="n"/>
-      <c r="J2" s="7" t="n"/>
-      <c r="K2" s="7" t="n"/>
-      <c r="L2" s="7" t="n"/>
-      <c r="M2" s="7" t="n"/>
+      <c r="B2" s="8" t="n"/>
+      <c r="C2" s="8" t="n"/>
+      <c r="D2" s="8" t="n"/>
+      <c r="E2" s="8" t="n"/>
+      <c r="F2" s="8" t="n"/>
+      <c r="G2" s="8" t="n"/>
+      <c r="H2" s="8" t="n"/>
+      <c r="I2" s="8" t="n"/>
+      <c r="J2" s="8" t="n"/>
+      <c r="K2" s="8" t="n"/>
+      <c r="L2" s="8" t="n"/>
+      <c r="M2" s="8" t="n"/>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -2172,7 +2642,7 @@
           <t>2026-09-23 11:00</t>
         </is>
       </c>
-      <c r="I4" s="8" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2225,7 +2695,7 @@
           <t>2026-09-23 14:15</t>
         </is>
       </c>
-      <c r="I5" s="8" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2278,7 +2748,7 @@
           <t>2026-09-24 09:30</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2331,7 +2801,7 @@
           <t>2026-09-24 10:00</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2384,7 +2854,7 @@
           <t>2026-09-24 10:00</t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2437,7 +2907,7 @@
           <t>2026-09-24 12:30</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2543,7 +3013,7 @@
           <t>2026-09-25 14:00</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2596,7 +3066,7 @@
           <t>2026-09-25 14:00</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2649,7 +3119,7 @@
           <t>2026-09-25 14:15</t>
         </is>
       </c>
-      <c r="I13" s="8" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2702,7 +3172,7 @@
           <t>2026-09-25 14:15</t>
         </is>
       </c>
-      <c r="I14" s="8" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2725,23 +3195,23 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>Week Range: (28-09-2026 to 04-10-2026)</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="n"/>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="7" t="n"/>
-      <c r="I15" s="7" t="n"/>
-      <c r="J15" s="7" t="n"/>
-      <c r="K15" s="7" t="n"/>
-      <c r="L15" s="7" t="n"/>
-      <c r="M15" s="7" t="n"/>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="8" t="n"/>
+      <c r="G15" s="8" t="n"/>
+      <c r="H15" s="8" t="n"/>
+      <c r="I15" s="8" t="n"/>
+      <c r="J15" s="8" t="n"/>
+      <c r="K15" s="8" t="n"/>
+      <c r="L15" s="8" t="n"/>
+      <c r="M15" s="8" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -2933,7 +3403,7 @@
           <t>2026-09-28 13:15</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3039,7 +3509,7 @@
           <t>2026-09-28 14:00</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr">
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3092,7 +3562,7 @@
           <t>2026-09-28 15:15</t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr">
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3357,7 +3827,7 @@
           <t>2026-09-29 09:30</t>
         </is>
       </c>
-      <c r="I27" s="8" t="inlineStr">
+      <c r="I27" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3410,7 +3880,7 @@
           <t>2026-09-29 11:00</t>
         </is>
       </c>
-      <c r="I28" s="8" t="inlineStr">
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3463,7 +3933,7 @@
           <t>2026-09-29 11:15</t>
         </is>
       </c>
-      <c r="I29" s="8" t="inlineStr">
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3569,7 +4039,7 @@
           <t>2026-09-29 11:30</t>
         </is>
       </c>
-      <c r="I31" s="8" t="inlineStr">
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3622,7 +4092,7 @@
           <t>2026-09-29 11:45</t>
         </is>
       </c>
-      <c r="I32" s="8" t="inlineStr">
+      <c r="I32" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3675,7 +4145,7 @@
           <t>2026-09-29 12:00</t>
         </is>
       </c>
-      <c r="I33" s="8" t="inlineStr">
+      <c r="I33" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3728,7 +4198,7 @@
           <t>2026-09-29 13:00</t>
         </is>
       </c>
-      <c r="I34" s="8" t="inlineStr">
+      <c r="I34" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3834,7 +4304,7 @@
           <t>2026-09-29 14:00</t>
         </is>
       </c>
-      <c r="I36" s="8" t="inlineStr">
+      <c r="I36" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3887,7 +4357,7 @@
           <t>2026-09-29 14:45</t>
         </is>
       </c>
-      <c r="I37" s="8" t="inlineStr">
+      <c r="I37" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3993,7 +4463,7 @@
           <t>2026-09-29 15:00</t>
         </is>
       </c>
-      <c r="I39" s="8" t="inlineStr">
+      <c r="I39" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -4046,7 +4516,7 @@
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I40" s="8" t="inlineStr">
+      <c r="I40" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -4099,7 +4569,7 @@
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I41" s="8" t="inlineStr">
+      <c r="I41" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -4364,7 +4834,7 @@
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I46" s="8" t="inlineStr">
+      <c r="I46" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -4417,7 +4887,7 @@
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I47" s="8" t="inlineStr">
+      <c r="I47" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -4495,49 +4965,49 @@
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>514</v>
+        <v>721.95</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>513.5</v>
+        <v>704.8</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>516.1</v>
+        <v>726.45</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>0.5% (2.6)</t>
+          <t>2.98% (21.65)</t>
         </is>
       </c>
       <c r="F49" s="4" t="n">
-        <v>518.7</v>
+        <v>748.1</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>521.3</v>
+        <v>769.75</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
           <t>2026-10-01 09:15</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 09:15</t>
+          <t>2026-10-01 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K49" s="2" t="n">
-        <v>521.3</v>
-      </c>
-      <c r="L49" s="4" t="n">
-        <v>1.01</v>
+        <v>718</v>
+      </c>
+      <c r="L49" s="3" t="n">
+        <v>-1.16</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
@@ -4548,49 +5018,49 @@
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>721.95</v>
+        <v>514</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>704.8</v>
+        <v>513.5</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>726.45</v>
+        <v>516.1</v>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>2.98% (21.65)</t>
+          <t>0.5% (2.6)</t>
         </is>
       </c>
       <c r="F50" s="4" t="n">
-        <v>748.1</v>
+        <v>518.7</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>769.75</v>
+        <v>521.3</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
           <t>2026-10-01 09:15</t>
         </is>
       </c>
-      <c r="I50" s="8" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 15:15 (Week End)</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="K50" s="2" t="n">
-        <v>718</v>
-      </c>
-      <c r="L50" s="3" t="n">
-        <v>-1.16</v>
+        <v>521.3</v>
+      </c>
+      <c r="L50" s="4" t="n">
+        <v>1.01</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
@@ -4599,23 +5069,23 @@
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="7" t="inlineStr">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>Week Range: (05-10-2026 to 11-10-2026)</t>
         </is>
       </c>
-      <c r="B51" s="7" t="n"/>
-      <c r="C51" s="7" t="n"/>
-      <c r="D51" s="7" t="n"/>
-      <c r="E51" s="7" t="n"/>
-      <c r="F51" s="7" t="n"/>
-      <c r="G51" s="7" t="n"/>
-      <c r="H51" s="7" t="n"/>
-      <c r="I51" s="7" t="n"/>
-      <c r="J51" s="7" t="n"/>
-      <c r="K51" s="7" t="n"/>
-      <c r="L51" s="7" t="n"/>
-      <c r="M51" s="7" t="n"/>
+      <c r="B51" s="8" t="n"/>
+      <c r="C51" s="8" t="n"/>
+      <c r="D51" s="8" t="n"/>
+      <c r="E51" s="8" t="n"/>
+      <c r="F51" s="8" t="n"/>
+      <c r="G51" s="8" t="n"/>
+      <c r="H51" s="8" t="n"/>
+      <c r="I51" s="8" t="n"/>
+      <c r="J51" s="8" t="n"/>
+      <c r="K51" s="8" t="n"/>
+      <c r="L51" s="8" t="n"/>
+      <c r="M51" s="8" t="n"/>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
@@ -4648,7 +5118,7 @@
           <t>2026-10-06 09:15</t>
         </is>
       </c>
-      <c r="I52" s="8" t="inlineStr">
+      <c r="I52" s="7" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -4701,7 +5171,7 @@
           <t>2026-10-06 09:15</t>
         </is>
       </c>
-      <c r="I53" s="8" t="inlineStr">
+      <c r="I53" s="7" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -4754,7 +5224,7 @@
           <t>2026-10-06 09:15</t>
         </is>
       </c>
-      <c r="I54" s="8" t="inlineStr">
+      <c r="I54" s="7" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -4832,49 +5302,49 @@
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>1295</v>
+        <v>168.43</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>1293</v>
+        <v>166.48</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>1299.4</v>
+        <v>168.99</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>0.49% (6.4)</t>
+          <t>1.49% (2.51)</t>
         </is>
       </c>
       <c r="F56" s="4" t="n">
-        <v>1305.8</v>
+        <v>171.5</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>1312.2</v>
+        <v>174.01</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
           <t>2026-10-07 09:15</t>
         </is>
       </c>
-      <c r="I56" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I56" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 09:15</t>
+          <t>2026-10-07 15:15 (Active)</t>
         </is>
       </c>
       <c r="K56" s="2" t="n">
-        <v>1312.2</v>
+        <v>170.71</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>0.99</v>
+        <v>1.02</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
@@ -4885,28 +5355,28 @@
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>3709.5</v>
+        <v>1295</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>3695</v>
+        <v>1293</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>3723.8</v>
+        <v>1299.4</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>0.77% (28.8)</t>
+          <t>0.49% (6.4)</t>
         </is>
       </c>
       <c r="F57" s="4" t="n">
-        <v>3752.6</v>
+        <v>1305.8</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>3781.4</v>
+        <v>1312.2</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -4924,10 +5394,10 @@
         </is>
       </c>
       <c r="K57" s="2" t="n">
-        <v>3781.4</v>
+        <v>1312.2</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>1.55</v>
+        <v>0.99</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
@@ -4938,49 +5408,49 @@
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>168.43</v>
+        <v>3709.5</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>166.48</v>
+        <v>3695</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>168.99</v>
+        <v>3723.8</v>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>1.49% (2.51)</t>
+          <t>0.77% (28.8)</t>
         </is>
       </c>
       <c r="F58" s="4" t="n">
-        <v>171.5</v>
+        <v>3752.6</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>174.01</v>
+        <v>3781.4</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
           <t>2026-10-07 09:15</t>
         </is>
       </c>
-      <c r="I58" s="8" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 15:15 (Active)</t>
+          <t>2026-10-07 09:15</t>
         </is>
       </c>
       <c r="K58" s="2" t="n">
-        <v>170.71</v>
+        <v>3781.4</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
@@ -5036,6 +5506,324 @@
         <v>-0.44</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>(05-10-2026 to 11-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>MAXHEALTH</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>902.05</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>891.8</v>
+      </c>
+      <c r="D60" s="4" t="n">
+        <v>903</v>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>1.24% (11.2)</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>914.2</v>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>925.4</v>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:15</t>
+        </is>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:15</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>891.8</v>
+      </c>
+      <c r="L60" s="3" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>(05-10-2026 to 11-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>1702.1</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>1701</v>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>1710.1</v>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>0.53% (9.1)</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>1719.2</v>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>1728.3</v>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:15</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:45</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>1728.3</v>
+      </c>
+      <c r="L61" s="4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>(05-10-2026 to 11-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>254.65</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>253.2</v>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>255.4</v>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>0.86% (2.2)</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>257.6</v>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>259.8</v>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:15</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09 10:00</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>259.8</v>
+      </c>
+      <c r="L62" s="4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>(05-10-2026 to 11-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>1674.8</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>1658.6</v>
+      </c>
+      <c r="D63" s="4" t="n">
+        <v>1684.2</v>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>1.52% (25.6)</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="n">
+        <v>1709.8</v>
+      </c>
+      <c r="G63" s="4" t="n">
+        <v>1735.4</v>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:15</t>
+        </is>
+      </c>
+      <c r="I63" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="n">
+        <v>1682</v>
+      </c>
+      <c r="L63" s="3" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>(05-10-2026 to 11-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>UNITDSPR</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>1316.5</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>1308.7</v>
+      </c>
+      <c r="D64" s="4" t="n">
+        <v>1323.7</v>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>1.13% (15.0)</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>1338.7</v>
+      </c>
+      <c r="G64" s="4" t="n">
+        <v>1353.7</v>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:15</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09 10:15</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>1353.7</v>
+      </c>
+      <c r="L64" s="4" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>(05-10-2026 to 11-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>LTM</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>3936</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>3908.4</v>
+      </c>
+      <c r="D65" s="4" t="n">
+        <v>3941.6</v>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>0.84% (33.2)</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>3974.8</v>
+      </c>
+      <c r="G65" s="4" t="n">
+        <v>4008</v>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:15</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:15</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="n">
+        <v>4008</v>
+      </c>
+      <c r="L65" s="4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
         <is>
           <t>(05-10-2026 to 11-10-2026)</t>
         </is>

--- a/data/trade_tracker_results.xlsx
+++ b/data/trade_tracker_results.xlsx
@@ -74,14 +74,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -92,8 +92,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-        <bgColor rgb="00D9E1F2"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -129,16 +129,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -506,19 +506,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="27" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
   </cols>
@@ -588,28 +588,28 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>7910</v>
+        <v>1124.6</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>7608</v>
+        <v>1123.1</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>7917</v>
+        <v>1131.1</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>3.9% (309.0)</t>
+          <t>0.71% (8.0)</t>
         </is>
       </c>
       <c r="F2" s="4" t="n">
-        <v>8226</v>
+        <v>1139.1</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>8535</v>
+        <v>1147.1</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -634,28 +634,28 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>378.65</v>
+        <v>403.85</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>377.05</v>
+        <v>402.15</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>384.35</v>
+        <v>410.15</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>1.9% (7.3)</t>
+          <t>1.95% (8.0)</t>
         </is>
       </c>
       <c r="F3" s="4" t="n">
-        <v>391.65</v>
+        <v>418.15</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>398.95</v>
+        <v>426.15</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -680,28 +680,28 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>296.5</v>
+        <v>373.3</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>294.55</v>
+        <v>373</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>296.8</v>
+        <v>375.4</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>0.76% (2.25)</t>
+          <t>0.64% (2.4)</t>
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>299.05</v>
+        <v>377.8</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>301.3</v>
+        <v>380.2</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -726,76 +726,74 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4737</v>
+        <v>709.75</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>4734.1</v>
+        <v>708.8</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>4770.2</v>
+        <v>711.4</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>0.76% (36.1)</t>
+          <t>0.37% (2.6)</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>4806.3</v>
+        <v>714</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>4842.4</v>
+        <v>716.6</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 09:15</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 11:15</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>4842.4</v>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="4" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1333.4</v>
+        <v>308.45</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1321.3</v>
+        <v>305.85</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1334</v>
+        <v>314.3</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>0.95% (12.7)</t>
+          <t>2.69% (8.45)</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1346.7</v>
+        <v>322.75</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1359.4</v>
+        <v>331.2</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -820,28 +818,28 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1194.9</v>
+        <v>441.05</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1167.4</v>
+        <v>441</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1201</v>
+        <v>445.8</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>2.8% (33.6)</t>
+          <t>1.08% (4.8)</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1234.6</v>
+        <v>450.6</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1268.2</v>
+        <v>455.4</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -866,28 +864,28 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>5051</v>
+        <v>1658.1</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>4995.5</v>
+        <v>1658</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>5200</v>
+        <v>1673.9</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>3.93% (204.5)</t>
+          <t>0.95% (15.9)</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>5404.5</v>
+        <v>1689.8</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>5609</v>
+        <v>1705.7</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -906,1540 +904,6 @@
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>NESTLEIND</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>1295</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>1293</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>1299.4</v>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>0.49% (6.4)</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>1305.8</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>1312.2</v>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-07 09:15</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-07 09:15</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>1312.2</v>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TECHM</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>1510.5</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>1487</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>1513</v>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>1.72% (26.0)</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>1539</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>1565</v>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TORNTPHARM</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>4717.3</v>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>4702.5</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>4777.2</v>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>1.56% (74.7)</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>4851.9</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>4926.6</v>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TVSMOTOR</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>3930.1</v>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>3870.8</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>3977</v>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>2.67% (106.2)</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>4083.2</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>4189.4</v>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>ASIANPAINT</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>2377</v>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>2336.9</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>2393.6</v>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>2.37% (56.7)</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>2450.3</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>2507</v>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>GAIL</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>168.43</v>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>166.48</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>168.99</v>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>1.49% (2.51)</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>171.5</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>174.01</v>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>GRASIM</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>2944.4</v>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>2928.9</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>2969</v>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>1.35% (40.1)</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>3009.1</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>3049.2</v>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>HDFCBANK</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>706.25</v>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>690.55</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>706.9</v>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>2.31% (16.35)</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>723.25</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>739.6</v>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>IOC</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>131.02</v>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>129.72</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>131.11</v>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>1.06% (1.39)</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>133.89</v>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>IRFC</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>76.51000000000001</v>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>76.06</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>76.97</v>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>1.18% (0.91)</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>77.88</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>78.79000000000001</v>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>JINDALSTEL</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>1079</v>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>1035.8</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>1097.3</v>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>5.6% (61.5)</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>1158.8</v>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>1220.3</v>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>MAXHEALTH</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>902.05</v>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>891.8</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>903</v>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>1.24% (11.2)</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>914.2</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>925.4</v>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-09 09:15</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-09 09:15</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="n">
-        <v>891.8</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>-1.24</v>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>SIEMENS</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>3709.5</v>
-      </c>
-      <c r="C21" s="3" t="n">
-        <v>3695</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>3723.8</v>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>0.77% (28.8)</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>3752.6</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>3781.4</v>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-07 09:15</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-07 09:15</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="n">
-        <v>3781.4</v>
-      </c>
-      <c r="L21" s="4" t="n">
-        <v>1.55</v>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>SUNPHARMA</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>1792.6</v>
-      </c>
-      <c r="C22" s="3" t="n">
-        <v>1769.1</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>1797.1</v>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>1.56% (28.0)</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="n">
-        <v>1825.1</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>1853.1</v>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>AMBUJACEM</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>356.3</v>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>352.8</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>359.1</v>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>1.75% (6.3)</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="n">
-        <v>365.4</v>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>371.7</v>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>SBIN</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>945.8</v>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>937.55</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>951.3</v>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>1.45% (13.75)</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="n">
-        <v>965.05</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>978.8</v>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>SHRIRAMFIN</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>936</v>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>917.25</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>938.7</v>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>2.29% (21.45)</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="n">
-        <v>960.15</v>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>981.6</v>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>ULTRACEMCO</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>10612</v>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>10426</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>10690</v>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>2.47% (264.0)</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="n">
-        <v>10954</v>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>11218</v>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>ADANIGREEN</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>1223.6</v>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>1209.4</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>1282</v>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>5.66% (72.6)</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="n">
-        <v>1354.6</v>
-      </c>
-      <c r="G27" s="4" t="n">
-        <v>1427.2</v>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>BAJAJFINSV</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>1702.1</v>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>1701</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>1710.1</v>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>0.53% (9.1)</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="n">
-        <v>1719.2</v>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v>1728.3</v>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-09 09:15</t>
-        </is>
-      </c>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-09 09:45</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="n">
-        <v>1728.3</v>
-      </c>
-      <c r="L28" s="4" t="n">
-        <v>1.06</v>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>ITC</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>254.65</v>
-      </c>
-      <c r="C29" s="3" t="n">
-        <v>253.2</v>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>255.4</v>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>0.86% (2.2)</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="n">
-        <v>257.6</v>
-      </c>
-      <c r="G29" s="4" t="n">
-        <v>259.8</v>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-09 09:15</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-09 10:00</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="n">
-        <v>259.8</v>
-      </c>
-      <c r="L29" s="4" t="n">
-        <v>1.72</v>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>SBILIFE</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>1674.8</v>
-      </c>
-      <c r="C30" s="3" t="n">
-        <v>1658.6</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>1684.2</v>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>1.52% (25.6)</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="n">
-        <v>1709.8</v>
-      </c>
-      <c r="G30" s="4" t="n">
-        <v>1735.4</v>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-09 09:15</t>
-        </is>
-      </c>
-      <c r="I30" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-09 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="n">
-        <v>1682</v>
-      </c>
-      <c r="L30" s="3" t="n">
-        <v>-0.13</v>
-      </c>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>UNITDSPR</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>1316.5</v>
-      </c>
-      <c r="C31" s="3" t="n">
-        <v>1308.7</v>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>1323.7</v>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>1.13% (15.0)</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="n">
-        <v>1338.7</v>
-      </c>
-      <c r="G31" s="4" t="n">
-        <v>1353.7</v>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-09 09:15</t>
-        </is>
-      </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-09 10:15</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="n">
-        <v>1353.7</v>
-      </c>
-      <c r="L31" s="4" t="n">
-        <v>2.27</v>
-      </c>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>ABB</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>6660.5</v>
-      </c>
-      <c r="C32" s="3" t="n">
-        <v>6578</v>
-      </c>
-      <c r="D32" s="4" t="n">
-        <v>6789</v>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>3.11% (211.0)</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="n">
-        <v>7000</v>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>7211</v>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>ADANIPORTS</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>1716</v>
-      </c>
-      <c r="C33" s="3" t="n">
-        <v>1675</v>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>1750.1</v>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>4.29% (75.1)</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="n">
-        <v>1825.2</v>
-      </c>
-      <c r="G33" s="4" t="n">
-        <v>1900.3</v>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>CGPOWER</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>854.2</v>
-      </c>
-      <c r="C34" s="3" t="n">
-        <v>840.15</v>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>864.45</v>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>2.81% (24.3)</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="n">
-        <v>888.75</v>
-      </c>
-      <c r="G34" s="4" t="n">
-        <v>913.05</v>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>CHOLAFIN</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="n">
-        <v>1563.2</v>
-      </c>
-      <c r="C35" s="3" t="n">
-        <v>1543.1</v>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>1567.7</v>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>1.57% (24.6)</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="n">
-        <v>1592.3</v>
-      </c>
-      <c r="G35" s="4" t="n">
-        <v>1616.9</v>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr"/>
-      <c r="L35" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>CUMMINSIND</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>4741</v>
-      </c>
-      <c r="C36" s="3" t="n">
-        <v>4671.1</v>
-      </c>
-      <c r="D36" s="4" t="n">
-        <v>4792.4</v>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>2.53% (121.3)</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="n">
-        <v>4913.7</v>
-      </c>
-      <c r="G36" s="4" t="n">
-        <v>5035</v>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>EICHERMOT</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n">
-        <v>6840</v>
-      </c>
-      <c r="C37" s="3" t="n">
-        <v>6767.5</v>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>6872</v>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>1.52% (104.5)</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="n">
-        <v>6976.5</v>
-      </c>
-      <c r="G37" s="4" t="n">
-        <v>7081</v>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>LT</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>3655.9</v>
-      </c>
-      <c r="C38" s="3" t="n">
-        <v>3607.1</v>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>3673.5</v>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>1.81% (66.4)</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="n">
-        <v>3739.9</v>
-      </c>
-      <c r="G38" s="4" t="n">
-        <v>3806.3</v>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>LTM</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="n">
-        <v>3936</v>
-      </c>
-      <c r="C39" s="3" t="n">
-        <v>3908.4</v>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>3941.6</v>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>0.84% (33.2)</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="n">
-        <v>3974.8</v>
-      </c>
-      <c r="G39" s="4" t="n">
-        <v>4008</v>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-09 09:15</t>
-        </is>
-      </c>
-      <c r="I39" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-09 09:15</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="n">
-        <v>4008</v>
-      </c>
-      <c r="L39" s="4" t="n">
-        <v>1.68</v>
-      </c>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>MARUTI</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>11305</v>
-      </c>
-      <c r="C40" s="3" t="n">
-        <v>11225</v>
-      </c>
-      <c r="D40" s="4" t="n">
-        <v>11342</v>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>1.03% (117.0)</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="n">
-        <v>11459</v>
-      </c>
-      <c r="G40" s="4" t="n">
-        <v>11576</v>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>ONGC</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="n">
-        <v>220.6</v>
-      </c>
-      <c r="C41" s="3" t="n">
-        <v>218.75</v>
-      </c>
-      <c r="D41" s="4" t="n">
-        <v>220.85</v>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>0.95% (2.1)</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="n">
-        <v>222.95</v>
-      </c>
-      <c r="G41" s="4" t="n">
-        <v>225.05</v>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2540,23 +1004,23 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Week Range: (21-09-2026 to 27-09-2026)</t>
         </is>
       </c>
-      <c r="B2" s="8" t="n"/>
-      <c r="C2" s="8" t="n"/>
-      <c r="D2" s="8" t="n"/>
-      <c r="E2" s="8" t="n"/>
-      <c r="F2" s="8" t="n"/>
-      <c r="G2" s="8" t="n"/>
-      <c r="H2" s="8" t="n"/>
-      <c r="I2" s="8" t="n"/>
-      <c r="J2" s="8" t="n"/>
-      <c r="K2" s="8" t="n"/>
-      <c r="L2" s="8" t="n"/>
-      <c r="M2" s="8" t="n"/>
+      <c r="B2" s="5" t="n"/>
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="5" t="n"/>
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="n"/>
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="5" t="n"/>
+      <c r="L2" s="5" t="n"/>
+      <c r="M2" s="5" t="n"/>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -2589,7 +1053,7 @@
           <t>2026-09-23 09:15</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -2960,7 +1424,7 @@
           <t>2026-09-25 10:00</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -3195,23 +1659,23 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Week Range: (28-09-2026 to 04-10-2026)</t>
         </is>
       </c>
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="n"/>
-      <c r="E15" s="8" t="n"/>
-      <c r="F15" s="8" t="n"/>
-      <c r="G15" s="8" t="n"/>
-      <c r="H15" s="8" t="n"/>
-      <c r="I15" s="8" t="n"/>
-      <c r="J15" s="8" t="n"/>
-      <c r="K15" s="8" t="n"/>
-      <c r="L15" s="8" t="n"/>
-      <c r="M15" s="8" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -3244,7 +1708,7 @@
           <t>2026-09-28 10:00</t>
         </is>
       </c>
-      <c r="I16" s="6" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -3297,7 +1761,7 @@
           <t>2026-09-28 11:30</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -3350,7 +1814,7 @@
           <t>2026-09-28 12:00</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
@@ -3456,7 +1920,7 @@
           <t>2026-09-28 13:45</t>
         </is>
       </c>
-      <c r="I20" s="6" t="inlineStr">
+      <c r="I20" s="8" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -3615,7 +2079,7 @@
           <t>2026-09-28 15:15</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
+      <c r="I23" s="8" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -3668,7 +2132,7 @@
           <t>2026-09-29 09:15</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="I24" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
@@ -3721,7 +2185,7 @@
           <t>2026-09-29 09:15</t>
         </is>
       </c>
-      <c r="I25" s="6" t="inlineStr">
+      <c r="I25" s="8" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -3774,7 +2238,7 @@
           <t>2026-09-29 09:15</t>
         </is>
       </c>
-      <c r="I26" s="6" t="inlineStr">
+      <c r="I26" s="8" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -3986,7 +2450,7 @@
           <t>2026-09-29 11:30</t>
         </is>
       </c>
-      <c r="I30" s="6" t="inlineStr">
+      <c r="I30" s="8" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -4251,7 +2715,7 @@
           <t>2026-09-29 14:00</t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="I35" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -4410,7 +2874,7 @@
           <t>2026-09-29 14:45</t>
         </is>
       </c>
-      <c r="I38" s="6" t="inlineStr">
+      <c r="I38" s="8" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -4622,7 +3086,7 @@
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I42" s="5" t="inlineStr">
+      <c r="I42" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
@@ -4675,7 +3139,7 @@
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="I43" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
@@ -4728,7 +3192,7 @@
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I44" s="6" t="inlineStr">
+      <c r="I44" s="8" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -4781,7 +3245,7 @@
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="I45" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -4940,7 +3404,7 @@
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I48" s="5" t="inlineStr">
+      <c r="I48" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -4965,49 +3429,49 @@
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>721.95</v>
+        <v>514</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>704.8</v>
+        <v>513.5</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>726.45</v>
+        <v>516.1</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>2.98% (21.65)</t>
+          <t>0.5% (2.6)</t>
         </is>
       </c>
       <c r="F49" s="4" t="n">
-        <v>748.1</v>
+        <v>518.7</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>769.75</v>
+        <v>521.3</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
           <t>2026-10-01 09:15</t>
         </is>
       </c>
-      <c r="I49" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 15:15 (Week End)</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="K49" s="2" t="n">
-        <v>718</v>
-      </c>
-      <c r="L49" s="3" t="n">
-        <v>-1.16</v>
+        <v>521.3</v>
+      </c>
+      <c r="L49" s="4" t="n">
+        <v>1.01</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
@@ -5018,49 +3482,49 @@
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>514</v>
+        <v>721.95</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>513.5</v>
+        <v>704.8</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>516.1</v>
+        <v>726.45</v>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>0.5% (2.6)</t>
+          <t>2.98% (21.65)</t>
         </is>
       </c>
       <c r="F50" s="4" t="n">
-        <v>518.7</v>
+        <v>748.1</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>521.3</v>
+        <v>769.75</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
           <t>2026-10-01 09:15</t>
         </is>
       </c>
-      <c r="I50" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I50" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 09:15</t>
+          <t>2026-10-01 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K50" s="2" t="n">
-        <v>521.3</v>
-      </c>
-      <c r="L50" s="4" t="n">
-        <v>1.01</v>
+        <v>718</v>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>-1.16</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
@@ -5069,23 +3533,23 @@
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>Week Range: (05-10-2026 to 11-10-2026)</t>
         </is>
       </c>
-      <c r="B51" s="8" t="n"/>
-      <c r="C51" s="8" t="n"/>
-      <c r="D51" s="8" t="n"/>
-      <c r="E51" s="8" t="n"/>
-      <c r="F51" s="8" t="n"/>
-      <c r="G51" s="8" t="n"/>
-      <c r="H51" s="8" t="n"/>
-      <c r="I51" s="8" t="n"/>
-      <c r="J51" s="8" t="n"/>
-      <c r="K51" s="8" t="n"/>
-      <c r="L51" s="8" t="n"/>
-      <c r="M51" s="8" t="n"/>
+      <c r="B51" s="5" t="n"/>
+      <c r="C51" s="5" t="n"/>
+      <c r="D51" s="5" t="n"/>
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" s="5" t="n"/>
+      <c r="G51" s="5" t="n"/>
+      <c r="H51" s="5" t="n"/>
+      <c r="I51" s="5" t="n"/>
+      <c r="J51" s="5" t="n"/>
+      <c r="K51" s="5" t="n"/>
+      <c r="L51" s="5" t="n"/>
+      <c r="M51" s="5" t="n"/>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
@@ -5120,12 +3584,12 @@
       </c>
       <c r="I52" s="7" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 15:00 (Active)</t>
+          <t>2026-10-06 15:00 (Week End)</t>
         </is>
       </c>
       <c r="K52" s="2" t="n">
@@ -5173,12 +3637,12 @@
       </c>
       <c r="I53" s="7" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 15:15 (Active)</t>
+          <t>2026-10-06 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K53" s="2" t="n">
@@ -5226,12 +3690,12 @@
       </c>
       <c r="I54" s="7" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 15:15 (Active)</t>
+          <t>2026-10-06 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K54" s="2" t="n">
@@ -5277,7 +3741,7 @@
           <t>2026-10-06 09:15</t>
         </is>
       </c>
-      <c r="I55" s="5" t="inlineStr">
+      <c r="I55" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -5332,12 +3796,12 @@
       </c>
       <c r="I56" s="7" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 15:15 (Active)</t>
+          <t>2026-10-07 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K56" s="2" t="n">
@@ -5383,7 +3847,7 @@
           <t>2026-10-07 09:15</t>
         </is>
       </c>
-      <c r="I57" s="5" t="inlineStr">
+      <c r="I57" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -5436,7 +3900,7 @@
           <t>2026-10-07 09:15</t>
         </is>
       </c>
-      <c r="I58" s="5" t="inlineStr">
+      <c r="I58" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -5489,7 +3953,7 @@
           <t>2026-10-08 09:15</t>
         </is>
       </c>
-      <c r="I59" s="6" t="inlineStr">
+      <c r="I59" s="8" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -5542,7 +4006,7 @@
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I60" s="6" t="inlineStr">
+      <c r="I60" s="8" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -5595,7 +4059,7 @@
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I61" s="5" t="inlineStr">
+      <c r="I61" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -5648,7 +4112,7 @@
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I62" s="5" t="inlineStr">
+      <c r="I62" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -5703,12 +4167,12 @@
       </c>
       <c r="I63" s="7" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 15:15 (Active)</t>
+          <t>2026-10-09 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K63" s="2" t="n">
@@ -5754,7 +4218,7 @@
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I64" s="5" t="inlineStr">
+      <c r="I64" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -5807,7 +4271,7 @@
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I65" s="5" t="inlineStr">
+      <c r="I65" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>

--- a/data/trade_tracker_results.xlsx
+++ b/data/trade_tracker_results.xlsx
@@ -74,14 +74,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-        <bgColor rgb="00D9E1F2"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -129,10 +129,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -506,19 +506,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="33" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
   </cols>
@@ -613,22 +613,24 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr"/>
+          <t>2026-10-13 09:45</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>1139.1</v>
+      </c>
       <c r="L2" s="4" t="n">
-        <v>0</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
@@ -751,49 +753,51 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr"/>
+          <t>2026-10-13 09:45</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>716.6</v>
+      </c>
       <c r="L5" s="4" t="n">
-        <v>0</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>308.45</v>
+        <v>4782.2</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>305.85</v>
+        <v>4749.6</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>314.3</v>
+        <v>4815.5</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>2.69% (8.45)</t>
+          <t>1.37% (65.9)</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>322.75</v>
+        <v>4881.4</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>331.2</v>
+        <v>4947.3</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -818,28 +822,28 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>441.05</v>
+        <v>308.45</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>441</v>
+        <v>305.85</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>445.8</v>
+        <v>314.3</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>1.08% (4.8)</t>
+          <t>2.69% (8.45)</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>450.6</v>
+        <v>322.75</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>455.4</v>
+        <v>331.2</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -864,28 +868,28 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1658.1</v>
+        <v>441.05</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1658</v>
+        <v>440.55</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1673.9</v>
+        <v>445.8</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>0.95% (15.9)</t>
+          <t>1.18% (5.25)</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1689.8</v>
+        <v>451.05</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1705.7</v>
+        <v>456.3</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -904,6 +908,560 @@
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>1658.1</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>1658</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>1673.9</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>0.95% (15.9)</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>1689.8</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>1705.7</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:30</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>1689.8</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>184.05</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>182.87</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>187.05</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>2.23% (4.18)</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>191.23</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>195.41</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>840.15</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>835</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>867.5</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>3.75% (32.5)</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>900</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>932.5</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>166.3</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>165.87</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>166.83</v>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>0.58% (0.96)</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>167.79</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>168.75</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>886.5</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>882.5</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>895.4</v>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>1.44% (12.9)</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>908.3</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>921.2</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>1828</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>1818.5</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>1829.2</v>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>0.58% (10.7)</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>1839.9</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>1850.6</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>INDUSINDBK</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>857</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>846.1</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>861.85</v>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>1.83% (15.75)</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>877.6</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>893.35</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>125.27</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>125</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>127.28</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>1.79% (2.28)</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>129.56</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>131.84</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>3607</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>3593.2</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>3627.5</v>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>0.95% (34.3)</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>3661.8</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>3696.1</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>11225</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>11130</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>11325</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>1.72% (195.0)</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>11520</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>11715</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>RELIANCE</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>1160.2</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>1152.6</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>1166.7</v>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>1.21% (14.1)</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>1180.8</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>1194.9</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>1486.2</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>1443.3</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>1508</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>4.29% (64.7)</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>1572.7</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>1637.4</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -918,7 +1476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M65"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -929,7 +1487,7 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="33" customWidth="1" min="9" max="9"/>
     <col width="29" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
@@ -1004,23 +1562,23 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Week Range: (21-09-2026 to 27-09-2026)</t>
         </is>
       </c>
-      <c r="B2" s="5" t="n"/>
-      <c r="C2" s="5" t="n"/>
-      <c r="D2" s="5" t="n"/>
-      <c r="E2" s="5" t="n"/>
-      <c r="F2" s="5" t="n"/>
-      <c r="G2" s="5" t="n"/>
-      <c r="H2" s="5" t="n"/>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="n"/>
-      <c r="L2" s="5" t="n"/>
-      <c r="M2" s="5" t="n"/>
+      <c r="B2" s="6" t="n"/>
+      <c r="C2" s="6" t="n"/>
+      <c r="D2" s="6" t="n"/>
+      <c r="E2" s="6" t="n"/>
+      <c r="F2" s="6" t="n"/>
+      <c r="G2" s="6" t="n"/>
+      <c r="H2" s="6" t="n"/>
+      <c r="I2" s="6" t="n"/>
+      <c r="J2" s="6" t="n"/>
+      <c r="K2" s="6" t="n"/>
+      <c r="L2" s="6" t="n"/>
+      <c r="M2" s="6" t="n"/>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -1053,7 +1611,7 @@
           <t>2026-09-23 09:15</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -1424,7 +1982,7 @@
           <t>2026-09-25 10:00</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -1659,23 +2217,23 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Week Range: (28-09-2026 to 04-10-2026)</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="n"/>
-      <c r="L15" s="5" t="n"/>
-      <c r="M15" s="5" t="n"/>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="6" t="n"/>
+      <c r="J15" s="6" t="n"/>
+      <c r="K15" s="6" t="n"/>
+      <c r="L15" s="6" t="n"/>
+      <c r="M15" s="6" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -1761,7 +2319,7 @@
           <t>2026-09-28 11:30</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -1814,7 +2372,7 @@
           <t>2026-09-28 12:00</t>
         </is>
       </c>
-      <c r="I18" s="6" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
@@ -2132,7 +2690,7 @@
           <t>2026-09-29 09:15</t>
         </is>
       </c>
-      <c r="I24" s="6" t="inlineStr">
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
@@ -2687,49 +3245,49 @@
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>4848.5</v>
+        <v>411.8</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>4837</v>
+        <v>402.75</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>4872</v>
+        <v>411.9</v>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>0.72% (35.0)</t>
+          <t>2.22% (9.15)</t>
         </is>
       </c>
       <c r="F35" s="4" t="n">
-        <v>4907</v>
+        <v>421.05</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>4942</v>
+        <v>430.2</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 14:00</t>
         </is>
       </c>
-      <c r="I35" s="6" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 14:45</t>
+          <t>2026-09-29 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K35" s="2" t="n">
-        <v>4942</v>
+        <v>413.35</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>1.44</v>
+        <v>0.35</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
@@ -2740,49 +3298,49 @@
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>411.8</v>
+        <v>4848.5</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>402.75</v>
+        <v>4837</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>411.9</v>
+        <v>4872</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>2.22% (9.15)</t>
+          <t>0.72% (35.0)</t>
         </is>
       </c>
       <c r="F36" s="4" t="n">
-        <v>421.05</v>
+        <v>4907</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>430.2</v>
+        <v>4942</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 14:00</t>
         </is>
       </c>
-      <c r="I36" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:15 (Week End)</t>
+          <t>2026-09-29 14:45</t>
         </is>
       </c>
       <c r="K36" s="2" t="n">
-        <v>413.35</v>
+        <v>4942</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>0.35</v>
+        <v>1.44</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
@@ -3086,7 +3644,7 @@
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I42" s="6" t="inlineStr">
+      <c r="I42" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
@@ -3139,7 +3697,7 @@
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I43" s="6" t="inlineStr">
+      <c r="I43" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
@@ -3245,7 +3803,7 @@
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I45" s="6" t="inlineStr">
+      <c r="I45" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -3404,7 +3962,7 @@
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I48" s="6" t="inlineStr">
+      <c r="I48" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -3457,7 +4015,7 @@
           <t>2026-10-01 09:15</t>
         </is>
       </c>
-      <c r="I49" s="6" t="inlineStr">
+      <c r="I49" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -3533,70 +4091,70 @@
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>Week Range: (05-10-2026 to 11-10-2026)</t>
         </is>
       </c>
-      <c r="B51" s="5" t="n"/>
-      <c r="C51" s="5" t="n"/>
-      <c r="D51" s="5" t="n"/>
-      <c r="E51" s="5" t="n"/>
-      <c r="F51" s="5" t="n"/>
-      <c r="G51" s="5" t="n"/>
-      <c r="H51" s="5" t="n"/>
-      <c r="I51" s="5" t="n"/>
-      <c r="J51" s="5" t="n"/>
-      <c r="K51" s="5" t="n"/>
-      <c r="L51" s="5" t="n"/>
-      <c r="M51" s="5" t="n"/>
+      <c r="B51" s="6" t="n"/>
+      <c r="C51" s="6" t="n"/>
+      <c r="D51" s="6" t="n"/>
+      <c r="E51" s="6" t="n"/>
+      <c r="F51" s="6" t="n"/>
+      <c r="G51" s="6" t="n"/>
+      <c r="H51" s="6" t="n"/>
+      <c r="I51" s="6" t="n"/>
+      <c r="J51" s="6" t="n"/>
+      <c r="K51" s="6" t="n"/>
+      <c r="L51" s="6" t="n"/>
+      <c r="M51" s="6" t="n"/>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>1194.9</v>
+        <v>4737</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>1189.9</v>
+        <v>4734.1</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>1202.9</v>
+        <v>4770.2</v>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>1.08% (13.0)</t>
+          <t>0.76% (36.1)</t>
         </is>
       </c>
       <c r="F52" s="4" t="n">
-        <v>1215.9</v>
+        <v>4806.3</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>1228.9</v>
+        <v>4842.4</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
           <t>2026-10-06 09:15</t>
         </is>
       </c>
-      <c r="I52" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 15:00 (Week End)</t>
+          <t>2026-10-06 11:15</t>
         </is>
       </c>
       <c r="K52" s="2" t="n">
-        <v>1208</v>
+        <v>4842.4</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>0.42</v>
+        <v>1.51</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
@@ -3607,28 +4165,28 @@
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>378.65</v>
+        <v>3930.1</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>377.05</v>
+        <v>3920</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>384.35</v>
+        <v>4031.6</v>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>1.9% (7.3)</t>
+          <t>2.77% (111.6)</t>
         </is>
       </c>
       <c r="F53" s="4" t="n">
-        <v>391.65</v>
+        <v>4143.2</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>398.95</v>
+        <v>4254.8</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -3646,10 +4204,10 @@
         </is>
       </c>
       <c r="K53" s="2" t="n">
-        <v>387.4</v>
-      </c>
-      <c r="L53" s="4" t="n">
-        <v>0.79</v>
+        <v>3981</v>
+      </c>
+      <c r="L53" s="3" t="n">
+        <v>-1.26</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
@@ -3660,28 +4218,28 @@
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>3930.1</v>
+        <v>378.65</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>3920</v>
+        <v>377.05</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>4031.6</v>
+        <v>384.35</v>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>2.77% (111.6)</t>
+          <t>1.9% (7.3)</t>
         </is>
       </c>
       <c r="F54" s="4" t="n">
-        <v>4143.2</v>
+        <v>391.65</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>4254.8</v>
+        <v>398.95</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -3699,10 +4257,10 @@
         </is>
       </c>
       <c r="K54" s="2" t="n">
-        <v>3981</v>
-      </c>
-      <c r="L54" s="3" t="n">
-        <v>-1.26</v>
+        <v>387.4</v>
+      </c>
+      <c r="L54" s="4" t="n">
+        <v>0.79</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
@@ -3713,49 +4271,49 @@
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>4737</v>
+        <v>1194.9</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>4734.1</v>
+        <v>1189.9</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>4770.2</v>
+        <v>1202.9</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>0.76% (36.1)</t>
+          <t>1.08% (13.0)</t>
         </is>
       </c>
       <c r="F55" s="4" t="n">
-        <v>4806.3</v>
+        <v>1215.9</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>4842.4</v>
+        <v>1228.9</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
           <t>2026-10-06 09:15</t>
         </is>
       </c>
-      <c r="I55" s="6" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I55" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 11:15</t>
+          <t>2026-10-06 15:00 (Week End)</t>
         </is>
       </c>
       <c r="K55" s="2" t="n">
-        <v>4842.4</v>
+        <v>1208</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>1.51</v>
+        <v>0.42</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
@@ -3847,7 +4405,7 @@
           <t>2026-10-07 09:15</t>
         </is>
       </c>
-      <c r="I57" s="6" t="inlineStr">
+      <c r="I57" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -3900,7 +4458,7 @@
           <t>2026-10-07 09:15</t>
         </is>
       </c>
-      <c r="I58" s="6" t="inlineStr">
+      <c r="I58" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -4059,7 +4617,7 @@
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I61" s="6" t="inlineStr">
+      <c r="I61" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -4112,7 +4670,7 @@
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I62" s="6" t="inlineStr">
+      <c r="I62" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -4218,7 +4776,7 @@
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I64" s="6" t="inlineStr">
+      <c r="I64" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -4271,7 +4829,7 @@
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I65" s="6" t="inlineStr">
+      <c r="I65" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -4293,11 +4851,190 @@
         </is>
       </c>
     </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>Week Range: (12-10-2026 to 18-10-2026)</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="n"/>
+      <c r="C66" s="6" t="n"/>
+      <c r="D66" s="6" t="n"/>
+      <c r="E66" s="6" t="n"/>
+      <c r="F66" s="6" t="n"/>
+      <c r="G66" s="6" t="n"/>
+      <c r="H66" s="6" t="n"/>
+      <c r="I66" s="6" t="n"/>
+      <c r="J66" s="6" t="n"/>
+      <c r="K66" s="6" t="n"/>
+      <c r="L66" s="6" t="n"/>
+      <c r="M66" s="6" t="n"/>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>1124.6</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>1123.1</v>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>1131.1</v>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>0.71% (8.0)</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>1139.1</v>
+      </c>
+      <c r="G67" s="4" t="n">
+        <v>1147.1</v>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:45</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="n">
+        <v>1139.1</v>
+      </c>
+      <c r="L67" s="4" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>(12-10-2026 to 18-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>709.75</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>708.8</v>
+      </c>
+      <c r="D68" s="4" t="n">
+        <v>711.4</v>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>0.37% (2.6)</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>714</v>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>716.6</v>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:45</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>716.6</v>
+      </c>
+      <c r="L68" s="4" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>(12-10-2026 to 18-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>1658.1</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>1658</v>
+      </c>
+      <c r="D69" s="4" t="n">
+        <v>1673.9</v>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>0.95% (15.9)</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>1689.8</v>
+      </c>
+      <c r="G69" s="4" t="n">
+        <v>1705.7</v>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:30</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="n">
+        <v>1689.8</v>
+      </c>
+      <c r="L69" s="4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>(12-10-2026 to 18-10-2026)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A51:M51"/>
     <mergeCell ref="A15:M15"/>
+    <mergeCell ref="A66:M66"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trade_tracker_results.xlsx
+++ b/data/trade_tracker_results.xlsx
@@ -80,14 +80,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-        <bgColor rgb="00D9E1F2"/>
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -132,10 +132,10 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -518,7 +518,7 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="33" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
   </cols>
@@ -661,22 +661,24 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-14 09:15</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr"/>
+          <t>2026-10-14 11:45</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>418.15</v>
+      </c>
       <c r="L3" s="4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -707,22 +709,24 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-14 09:15</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr"/>
+          <t>2026-10-14 09:15</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>380.2</v>
+      </c>
       <c r="L4" s="4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -847,22 +851,24 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-14 11:30</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="4" t="n">
-        <v>0</v>
+          <t>2026-10-14 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>313.7</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>-0.19</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -893,22 +899,24 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-14 09:15</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr"/>
+          <t>2026-10-14 11:00</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>451.05</v>
+      </c>
       <c r="L8" s="4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -921,42 +929,40 @@
         <v>1658.1</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1658</v>
+        <v>1656</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1673.9</v>
+        <v>1666.2</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>0.95% (15.9)</t>
+          <t>0.61% (10.2)</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1689.8</v>
+        <v>1676.4</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1705.7</v>
+        <v>1686.6</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 09:15</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 09:30</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>1689.8</v>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="4" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -987,22 +993,24 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-14 09:45</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
+          <t>2026-10-14 14:15</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>195.41</v>
+      </c>
       <c r="L10" s="4" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -1033,22 +1041,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-14 13:45</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="4" t="n">
-        <v>0</v>
+          <t>2026-10-14 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>861.7</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>-0.67</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -1171,22 +1181,24 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-14 09:15</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr"/>
+          <t>2026-10-14 09:15</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>1850.6</v>
+      </c>
       <c r="L14" s="4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -1217,22 +1229,24 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-14 09:15</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr"/>
+          <t>2026-10-14 09:30</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>877.6</v>
+      </c>
       <c r="L15" s="4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -1355,22 +1369,24 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-14 09:30</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="4" t="n">
-        <v>0</v>
+          <t>2026-10-14 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>11178</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>-1.3</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -1401,22 +1417,24 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-14 09:15</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr"/>
+          <t>2026-10-14 12:00</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>1180.8</v>
+      </c>
       <c r="L19" s="4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -1447,21 +1465,117 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>2026-10-14 09:15</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:15</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>1572.7</v>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>4.29</v>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>JSWENERGY</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>461</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>457.5</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>461.75</v>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>0.92% (4.25)</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>466</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>470.25</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:15</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:30</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>470.25</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>1745</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>1743.2</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>1770.7</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>1.55% (27.5)</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>1798.2</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>1825.7</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>WAIT (No Entry)</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="4" t="n">
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1476,7 +1590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M69"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1562,23 +1676,23 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Week Range: (21-09-2026 to 27-09-2026)</t>
         </is>
       </c>
-      <c r="B2" s="6" t="n"/>
-      <c r="C2" s="6" t="n"/>
-      <c r="D2" s="6" t="n"/>
-      <c r="E2" s="6" t="n"/>
-      <c r="F2" s="6" t="n"/>
-      <c r="G2" s="6" t="n"/>
-      <c r="H2" s="6" t="n"/>
-      <c r="I2" s="6" t="n"/>
-      <c r="J2" s="6" t="n"/>
-      <c r="K2" s="6" t="n"/>
-      <c r="L2" s="6" t="n"/>
-      <c r="M2" s="6" t="n"/>
+      <c r="B2" s="7" t="n"/>
+      <c r="C2" s="7" t="n"/>
+      <c r="D2" s="7" t="n"/>
+      <c r="E2" s="7" t="n"/>
+      <c r="F2" s="7" t="n"/>
+      <c r="G2" s="7" t="n"/>
+      <c r="H2" s="7" t="n"/>
+      <c r="I2" s="7" t="n"/>
+      <c r="J2" s="7" t="n"/>
+      <c r="K2" s="7" t="n"/>
+      <c r="L2" s="7" t="n"/>
+      <c r="M2" s="7" t="n"/>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -1664,7 +1778,7 @@
           <t>2026-09-23 11:00</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -1717,7 +1831,7 @@
           <t>2026-09-23 14:15</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -1770,7 +1884,7 @@
           <t>2026-09-24 09:30</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -1823,7 +1937,7 @@
           <t>2026-09-24 10:00</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -1876,7 +1990,7 @@
           <t>2026-09-24 10:00</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -1929,7 +2043,7 @@
           <t>2026-09-24 12:30</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2007,35 +2121,35 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>1242.8</v>
+        <v>1927</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1202.6</v>
+        <v>1915.1</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1246</v>
+        <v>1935.1</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>3.48% (43.4)</t>
+          <t>1.03% (20.0)</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1289.4</v>
+        <v>1955.1</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1332.8</v>
+        <v>1975.1</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
           <t>2026-09-25 14:00</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2046,10 +2160,10 @@
         </is>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1254.8</v>
+        <v>1942.9</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.71</v>
+        <v>0.4</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
@@ -2060,35 +2174,35 @@
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>1927</v>
+        <v>1242.8</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1915.1</v>
+        <v>1202.6</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1935.1</v>
+        <v>1246</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>1.03% (20.0)</t>
+          <t>3.48% (43.4)</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1955.1</v>
+        <v>1289.4</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1975.1</v>
+        <v>1332.8</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2026-09-25 14:00</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2099,10 +2213,10 @@
         </is>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1942.9</v>
+        <v>1254.8</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.4</v>
+        <v>0.71</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
@@ -2141,7 +2255,7 @@
           <t>2026-09-25 14:15</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2194,7 +2308,7 @@
           <t>2026-09-25 14:15</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2217,23 +2331,23 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>Week Range: (28-09-2026 to 04-10-2026)</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
-      <c r="I15" s="6" t="n"/>
-      <c r="J15" s="6" t="n"/>
-      <c r="K15" s="6" t="n"/>
-      <c r="L15" s="6" t="n"/>
-      <c r="M15" s="6" t="n"/>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="7" t="n"/>
+      <c r="I15" s="7" t="n"/>
+      <c r="J15" s="7" t="n"/>
+      <c r="K15" s="7" t="n"/>
+      <c r="L15" s="7" t="n"/>
+      <c r="M15" s="7" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -2425,7 +2539,7 @@
           <t>2026-09-28 13:15</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="I19" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2531,7 +2645,7 @@
           <t>2026-09-28 14:00</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="I21" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2556,49 +2670,49 @@
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>171.35</v>
+        <v>906.9</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>171.05</v>
+        <v>889.7</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>172.2</v>
+        <v>907.5</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>0.67% (1.15)</t>
+          <t>1.96% (17.8)</t>
         </is>
       </c>
       <c r="F22" s="4" t="n">
-        <v>173.35</v>
+        <v>925.3</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>174.5</v>
+        <v>943.1</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t>2026-09-28 15:15</t>
         </is>
       </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 15:15 (Week End)</t>
+          <t>2026-09-29 10:15</t>
         </is>
       </c>
       <c r="K22" s="2" t="n">
-        <v>172.45</v>
-      </c>
-      <c r="L22" s="4" t="n">
-        <v>0.15</v>
+        <v>889.7</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>-1.96</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
@@ -2609,49 +2723,49 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>906.9</v>
+        <v>171.35</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>889.7</v>
+        <v>171.05</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>907.5</v>
+        <v>172.2</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>1.96% (17.8)</t>
+          <t>0.67% (1.15)</t>
         </is>
       </c>
       <c r="F23" s="4" t="n">
-        <v>925.3</v>
+        <v>173.35</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>943.1</v>
+        <v>174.5</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
           <t>2026-09-28 15:15</t>
         </is>
       </c>
-      <c r="I23" s="8" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:15</t>
+          <t>2026-09-28 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K23" s="2" t="n">
-        <v>889.7</v>
-      </c>
-      <c r="L23" s="3" t="n">
-        <v>-1.96</v>
+        <v>172.45</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>0.15</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
@@ -2849,7 +2963,7 @@
           <t>2026-09-29 09:30</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="I27" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2902,7 +3016,7 @@
           <t>2026-09-29 11:00</t>
         </is>
       </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="I28" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2955,7 +3069,7 @@
           <t>2026-09-29 11:15</t>
         </is>
       </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="I29" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2980,49 +3094,49 @@
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>1495.7</v>
+        <v>399.3</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1487.1</v>
+        <v>394.7</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1498</v>
+        <v>403.65</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>0.73% (10.9)</t>
+          <t>2.22% (8.95)</t>
         </is>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1508.9</v>
+        <v>412.6</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1519.8</v>
+        <v>421.55</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 11:30</t>
         </is>
       </c>
-      <c r="I30" s="8" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:30</t>
+          <t>2026-09-29 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K30" s="2" t="n">
-        <v>1487.1</v>
-      </c>
-      <c r="L30" s="3" t="n">
-        <v>-0.73</v>
+        <v>406</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>0.58</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
@@ -3033,49 +3147,49 @@
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>399.3</v>
+        <v>1495.7</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>394.7</v>
+        <v>1487.1</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>403.65</v>
+        <v>1498</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>2.22% (8.95)</t>
+          <t>0.73% (10.9)</t>
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>412.6</v>
+        <v>1508.9</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>421.55</v>
+        <v>1519.8</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 11:30</t>
         </is>
       </c>
-      <c r="I31" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I31" s="8" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:15 (Week End)</t>
+          <t>2026-09-29 12:30</t>
         </is>
       </c>
       <c r="K31" s="2" t="n">
-        <v>406</v>
-      </c>
-      <c r="L31" s="4" t="n">
-        <v>0.58</v>
+        <v>1487.1</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>-0.73</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
@@ -3114,7 +3228,7 @@
           <t>2026-09-29 11:45</t>
         </is>
       </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="I32" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3167,7 +3281,7 @@
           <t>2026-09-29 12:00</t>
         </is>
       </c>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="I33" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3220,7 +3334,7 @@
           <t>2026-09-29 13:00</t>
         </is>
       </c>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="I34" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3273,7 +3387,7 @@
           <t>2026-09-29 14:00</t>
         </is>
       </c>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="I35" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3379,7 +3493,7 @@
           <t>2026-09-29 14:45</t>
         </is>
       </c>
-      <c r="I37" s="7" t="inlineStr">
+      <c r="I37" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3485,7 +3599,7 @@
           <t>2026-09-29 15:00</t>
         </is>
       </c>
-      <c r="I39" s="7" t="inlineStr">
+      <c r="I39" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3510,49 +3624,49 @@
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>196.1</v>
+        <v>160.5</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>192.45</v>
+        <v>159.41</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>196.67</v>
+        <v>162.37</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>2.15% (4.22)</t>
+          <t>1.82% (2.96)</t>
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>200.89</v>
+        <v>165.33</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>205.11</v>
+        <v>168.29</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I40" s="7" t="inlineStr">
+      <c r="I40" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:15</t>
+          <t>2026-09-30 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K40" s="2" t="n">
-        <v>200.89</v>
+        <v>163.26</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>2.15</v>
+        <v>0.55</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
@@ -3563,49 +3677,49 @@
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>1766.7</v>
+        <v>2391</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>1736.8</v>
+        <v>2381.6</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>1770.1</v>
+        <v>2420</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>1.88% (33.3)</t>
+          <t>1.59% (38.4)</t>
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>1803.4</v>
+        <v>2458.4</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>1836.7</v>
+        <v>2496.8</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I41" s="7" t="inlineStr">
+      <c r="I41" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 15:15 (Week End)</t>
+          <t>2026-09-30 12:30 (Week End)</t>
         </is>
       </c>
       <c r="K41" s="2" t="n">
-        <v>1798.3</v>
-      </c>
-      <c r="L41" s="4" t="n">
-        <v>1.59</v>
+        <v>2409.1</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>-0.45</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
@@ -3616,28 +3730,28 @@
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>4057</v>
+        <v>399.3</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>4043.3</v>
+        <v>394.7</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>4095</v>
+        <v>403.65</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>1.26% (51.7)</t>
+          <t>2.22% (8.95)</t>
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>4146.7</v>
+        <v>412.6</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>4198.4</v>
+        <v>421.55</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -3646,7 +3760,7 @@
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -3655,10 +3769,10 @@
         </is>
       </c>
       <c r="K42" s="2" t="n">
-        <v>4043.3</v>
-      </c>
-      <c r="L42" s="3" t="n">
-        <v>-1.26</v>
+        <v>421.55</v>
+      </c>
+      <c r="L42" s="4" t="n">
+        <v>4.43</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
@@ -3669,28 +3783,28 @@
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>4848.5</v>
+        <v>991.6</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>4837</v>
+        <v>980.4</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>4872</v>
+        <v>992.7</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>0.72% (35.0)</t>
+          <t>1.24% (12.3)</t>
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>4907</v>
+        <v>1005</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>4942</v>
+        <v>1017.3</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -3699,19 +3813,19 @@
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 10:30</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
       <c r="K43" s="2" t="n">
-        <v>4837</v>
-      </c>
-      <c r="L43" s="3" t="n">
-        <v>-0.72</v>
+        <v>1017.3</v>
+      </c>
+      <c r="L43" s="4" t="n">
+        <v>2.48</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
@@ -3722,49 +3836,49 @@
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>263.55</v>
+        <v>1766.7</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>263.3</v>
+        <v>1736.8</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>266.2</v>
+        <v>1770.1</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>1.09% (2.9)</t>
+          <t>1.88% (33.3)</t>
         </is>
       </c>
       <c r="F44" s="4" t="n">
-        <v>269.1</v>
+        <v>1803.4</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>272</v>
+        <v>1836.7</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I44" s="8" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:15</t>
+          <t>2026-09-30 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K44" s="2" t="n">
-        <v>263.3</v>
-      </c>
-      <c r="L44" s="3" t="n">
-        <v>-1.09</v>
+        <v>1798.3</v>
+      </c>
+      <c r="L44" s="4" t="n">
+        <v>1.59</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
@@ -3775,28 +3889,28 @@
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>991.6</v>
+        <v>4848.5</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>980.4</v>
+        <v>4837</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>992.7</v>
+        <v>4872</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>1.24% (12.3)</t>
+          <t>0.72% (35.0)</t>
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>1005</v>
+        <v>4907</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>1017.3</v>
+        <v>4942</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -3805,19 +3919,19 @@
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-30 10:30</t>
         </is>
       </c>
       <c r="K45" s="2" t="n">
-        <v>1017.3</v>
-      </c>
-      <c r="L45" s="4" t="n">
-        <v>2.48</v>
+        <v>4837</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>-0.72</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
@@ -3828,49 +3942,49 @@
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>2391</v>
+        <v>4057</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>2381.6</v>
+        <v>4043.3</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>2420</v>
+        <v>4095</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>1.59% (38.4)</t>
+          <t>1.26% (51.7)</t>
         </is>
       </c>
       <c r="F46" s="4" t="n">
-        <v>2458.4</v>
+        <v>4146.7</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>2496.8</v>
+        <v>4198.4</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I46" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:30 (Week End)</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="K46" s="2" t="n">
-        <v>2409.1</v>
+        <v>4043.3</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>-0.45</v>
+        <v>-1.26</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
@@ -3881,49 +3995,49 @@
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>160.5</v>
+        <v>196.1</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>159.41</v>
+        <v>192.45</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>162.37</v>
+        <v>196.67</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>1.82% (2.96)</t>
+          <t>2.15% (4.22)</t>
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>165.33</v>
+        <v>200.89</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>168.29</v>
+        <v>205.11</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I47" s="7" t="inlineStr">
+      <c r="I47" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 15:15 (Week End)</t>
+          <t>2026-09-30 09:15</t>
         </is>
       </c>
       <c r="K47" s="2" t="n">
-        <v>163.26</v>
+        <v>200.89</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>0.55</v>
+        <v>2.15</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
@@ -3934,49 +4048,49 @@
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>399.3</v>
+        <v>263.55</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>394.7</v>
+        <v>263.3</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>403.65</v>
+        <v>266.2</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>2.22% (8.95)</t>
+          <t>1.09% (2.9)</t>
         </is>
       </c>
       <c r="F48" s="4" t="n">
-        <v>412.6</v>
+        <v>269.1</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>421.55</v>
+        <v>272</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I48" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I48" s="8" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 09:15</t>
+          <t>2026-09-30 14:15</t>
         </is>
       </c>
       <c r="K48" s="2" t="n">
-        <v>421.55</v>
-      </c>
-      <c r="L48" s="4" t="n">
-        <v>4.43</v>
+        <v>263.3</v>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>-1.09</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
@@ -4068,7 +4182,7 @@
           <t>2026-10-01 09:15</t>
         </is>
       </c>
-      <c r="I50" s="7" t="inlineStr">
+      <c r="I50" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -4091,23 +4205,23 @@
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="6" t="inlineStr">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>Week Range: (05-10-2026 to 11-10-2026)</t>
         </is>
       </c>
-      <c r="B51" s="6" t="n"/>
-      <c r="C51" s="6" t="n"/>
-      <c r="D51" s="6" t="n"/>
-      <c r="E51" s="6" t="n"/>
-      <c r="F51" s="6" t="n"/>
-      <c r="G51" s="6" t="n"/>
-      <c r="H51" s="6" t="n"/>
-      <c r="I51" s="6" t="n"/>
-      <c r="J51" s="6" t="n"/>
-      <c r="K51" s="6" t="n"/>
-      <c r="L51" s="6" t="n"/>
-      <c r="M51" s="6" t="n"/>
+      <c r="B51" s="7" t="n"/>
+      <c r="C51" s="7" t="n"/>
+      <c r="D51" s="7" t="n"/>
+      <c r="E51" s="7" t="n"/>
+      <c r="F51" s="7" t="n"/>
+      <c r="G51" s="7" t="n"/>
+      <c r="H51" s="7" t="n"/>
+      <c r="I51" s="7" t="n"/>
+      <c r="J51" s="7" t="n"/>
+      <c r="K51" s="7" t="n"/>
+      <c r="L51" s="7" t="n"/>
+      <c r="M51" s="7" t="n"/>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
@@ -4193,7 +4307,7 @@
           <t>2026-10-06 09:15</t>
         </is>
       </c>
-      <c r="I53" s="7" t="inlineStr">
+      <c r="I53" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -4246,7 +4360,7 @@
           <t>2026-10-06 09:15</t>
         </is>
       </c>
-      <c r="I54" s="7" t="inlineStr">
+      <c r="I54" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -4299,7 +4413,7 @@
           <t>2026-10-06 09:15</t>
         </is>
       </c>
-      <c r="I55" s="7" t="inlineStr">
+      <c r="I55" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -4352,7 +4466,7 @@
           <t>2026-10-07 09:15</t>
         </is>
       </c>
-      <c r="I56" s="7" t="inlineStr">
+      <c r="I56" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -4536,37 +4650,37 @@
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>LTM</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>902.05</v>
+        <v>3936</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>891.8</v>
+        <v>3908.4</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>903</v>
+        <v>3941.6</v>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>1.24% (11.2)</t>
+          <t>0.84% (33.2)</t>
         </is>
       </c>
       <c r="F60" s="4" t="n">
-        <v>914.2</v>
+        <v>3974.8</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>925.4</v>
+        <v>4008</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I60" s="8" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -4575,10 +4689,10 @@
         </is>
       </c>
       <c r="K60" s="2" t="n">
-        <v>891.8</v>
-      </c>
-      <c r="L60" s="3" t="n">
-        <v>-1.24</v>
+        <v>4008</v>
+      </c>
+      <c r="L60" s="4" t="n">
+        <v>1.68</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
@@ -4589,28 +4703,28 @@
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>1702.1</v>
+        <v>1316.5</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>1701</v>
+        <v>1308.7</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>1710.1</v>
+        <v>1323.7</v>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>0.53% (9.1)</t>
+          <t>1.13% (15.0)</t>
         </is>
       </c>
       <c r="F61" s="4" t="n">
-        <v>1719.2</v>
+        <v>1338.7</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>1728.3</v>
+        <v>1353.7</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -4624,14 +4738,14 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 09:45</t>
+          <t>2026-10-09 10:15</t>
         </is>
       </c>
       <c r="K61" s="2" t="n">
-        <v>1728.3</v>
+        <v>1353.7</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>1.06</v>
+        <v>2.27</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
@@ -4642,49 +4756,49 @@
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>254.65</v>
+        <v>1674.8</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>253.2</v>
+        <v>1658.6</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>255.4</v>
+        <v>1684.2</v>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>0.86% (2.2)</t>
+          <t>1.52% (25.6)</t>
         </is>
       </c>
       <c r="F62" s="4" t="n">
-        <v>257.6</v>
+        <v>1709.8</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>259.8</v>
+        <v>1735.4</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I62" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 10:00</t>
+          <t>2026-10-09 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K62" s="2" t="n">
-        <v>259.8</v>
-      </c>
-      <c r="L62" s="4" t="n">
-        <v>1.72</v>
+        <v>1682</v>
+      </c>
+      <c r="L62" s="3" t="n">
+        <v>-0.13</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
@@ -4695,49 +4809,49 @@
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>1674.8</v>
+        <v>1702.1</v>
       </c>
       <c r="C63" s="3" t="n">
-        <v>1658.6</v>
+        <v>1701</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>1684.2</v>
+        <v>1710.1</v>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>1.52% (25.6)</t>
+          <t>0.53% (9.1)</t>
         </is>
       </c>
       <c r="F63" s="4" t="n">
-        <v>1709.8</v>
+        <v>1719.2</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>1735.4</v>
+        <v>1728.3</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I63" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 15:15 (Week End)</t>
+          <t>2026-10-09 09:45</t>
         </is>
       </c>
       <c r="K63" s="2" t="n">
-        <v>1682</v>
-      </c>
-      <c r="L63" s="3" t="n">
-        <v>-0.13</v>
+        <v>1728.3</v>
+      </c>
+      <c r="L63" s="4" t="n">
+        <v>1.06</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
@@ -4748,49 +4862,49 @@
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>1316.5</v>
+        <v>902.05</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1308.7</v>
+        <v>891.8</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>1323.7</v>
+        <v>903</v>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>1.13% (15.0)</t>
+          <t>1.24% (11.2)</t>
         </is>
       </c>
       <c r="F64" s="4" t="n">
-        <v>1338.7</v>
+        <v>914.2</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>1353.7</v>
+        <v>925.4</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I64" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I64" s="8" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 10:15</t>
+          <t>2026-10-09 09:15</t>
         </is>
       </c>
       <c r="K64" s="2" t="n">
-        <v>1353.7</v>
-      </c>
-      <c r="L64" s="4" t="n">
-        <v>2.27</v>
+        <v>891.8</v>
+      </c>
+      <c r="L64" s="3" t="n">
+        <v>-1.24</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
@@ -4801,28 +4915,28 @@
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>LTM</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>3936</v>
+        <v>254.65</v>
       </c>
       <c r="C65" s="3" t="n">
-        <v>3908.4</v>
+        <v>253.2</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>3941.6</v>
+        <v>255.4</v>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>0.84% (33.2)</t>
+          <t>0.86% (2.2)</t>
         </is>
       </c>
       <c r="F65" s="4" t="n">
-        <v>3974.8</v>
+        <v>257.6</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>4008</v>
+        <v>259.8</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -4836,14 +4950,14 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 09:15</t>
+          <t>2026-10-09 10:00</t>
         </is>
       </c>
       <c r="K65" s="2" t="n">
-        <v>4008</v>
+        <v>259.8</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
@@ -4852,49 +4966,49 @@
       </c>
     </row>
     <row r="66" ht="22" customHeight="1">
-      <c r="A66" s="6" t="inlineStr">
+      <c r="A66" s="7" t="inlineStr">
         <is>
           <t>Week Range: (12-10-2026 to 18-10-2026)</t>
         </is>
       </c>
-      <c r="B66" s="6" t="n"/>
-      <c r="C66" s="6" t="n"/>
-      <c r="D66" s="6" t="n"/>
-      <c r="E66" s="6" t="n"/>
-      <c r="F66" s="6" t="n"/>
-      <c r="G66" s="6" t="n"/>
-      <c r="H66" s="6" t="n"/>
-      <c r="I66" s="6" t="n"/>
-      <c r="J66" s="6" t="n"/>
-      <c r="K66" s="6" t="n"/>
-      <c r="L66" s="6" t="n"/>
-      <c r="M66" s="6" t="n"/>
+      <c r="B66" s="7" t="n"/>
+      <c r="C66" s="7" t="n"/>
+      <c r="D66" s="7" t="n"/>
+      <c r="E66" s="7" t="n"/>
+      <c r="F66" s="7" t="n"/>
+      <c r="G66" s="7" t="n"/>
+      <c r="H66" s="7" t="n"/>
+      <c r="I66" s="7" t="n"/>
+      <c r="J66" s="7" t="n"/>
+      <c r="K66" s="7" t="n"/>
+      <c r="L66" s="7" t="n"/>
+      <c r="M66" s="7" t="n"/>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>1124.6</v>
+        <v>1658.1</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>1123.1</v>
+        <v>1658</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>1131.1</v>
+        <v>1673.9</v>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>0.71% (8.0)</t>
+          <t>0.95% (15.9)</t>
         </is>
       </c>
       <c r="F67" s="4" t="n">
-        <v>1139.1</v>
+        <v>1689.8</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>1147.1</v>
+        <v>1705.7</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -4908,14 +5022,14 @@
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 09:45</t>
+          <t>2026-10-13 09:30</t>
         </is>
       </c>
       <c r="K67" s="2" t="n">
-        <v>1139.1</v>
+        <v>1689.8</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>0.71</v>
+        <v>0.95</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
@@ -4926,28 +5040,28 @@
     <row r="68" ht="18" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>709.75</v>
+        <v>1124.6</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>708.8</v>
+        <v>1123.1</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>711.4</v>
+        <v>1131.1</v>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>0.37% (2.6)</t>
+          <t>0.71% (8.0)</t>
         </is>
       </c>
       <c r="F68" s="4" t="n">
-        <v>714</v>
+        <v>1139.1</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>716.6</v>
+        <v>1147.1</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -4956,7 +5070,7 @@
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -4965,10 +5079,10 @@
         </is>
       </c>
       <c r="K68" s="2" t="n">
-        <v>716.6</v>
+        <v>1139.1</v>
       </c>
       <c r="L68" s="4" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
@@ -4979,28 +5093,28 @@
     <row r="69" ht="18" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>1658.1</v>
+        <v>709.75</v>
       </c>
       <c r="C69" s="3" t="n">
-        <v>1658</v>
+        <v>708.8</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>1673.9</v>
+        <v>711.4</v>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>0.95% (15.9)</t>
+          <t>0.37% (2.6)</t>
         </is>
       </c>
       <c r="F69" s="4" t="n">
-        <v>1689.8</v>
+        <v>714</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>1705.7</v>
+        <v>716.6</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -5009,21 +5123,657 @@
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:45</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="n">
+        <v>716.6</v>
+      </c>
+      <c r="L69" s="4" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>(12-10-2026 to 18-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>RELIANCE</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>1160.2</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>1152.6</v>
+      </c>
+      <c r="D70" s="4" t="n">
+        <v>1166.7</v>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>1.21% (14.1)</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>1180.8</v>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>1194.9</v>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:15</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
           <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-13 09:30</t>
-        </is>
-      </c>
-      <c r="K69" s="2" t="n">
-        <v>1689.8</v>
-      </c>
-      <c r="L69" s="4" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="M69" s="2" t="inlineStr">
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 12:00</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="n">
+        <v>1180.8</v>
+      </c>
+      <c r="L70" s="4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>(12-10-2026 to 18-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>INDUSINDBK</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>857</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>846.1</v>
+      </c>
+      <c r="D71" s="4" t="n">
+        <v>861.85</v>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>1.83% (15.75)</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="n">
+        <v>877.6</v>
+      </c>
+      <c r="G71" s="4" t="n">
+        <v>893.35</v>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:15</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:30</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>877.6</v>
+      </c>
+      <c r="L71" s="4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>(12-10-2026 to 18-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>1828</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>1818.5</v>
+      </c>
+      <c r="D72" s="4" t="n">
+        <v>1829.2</v>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>0.58% (10.7)</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="n">
+        <v>1839.9</v>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>1850.6</v>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:15</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:15</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>1850.6</v>
+      </c>
+      <c r="L72" s="4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>(12-10-2026 to 18-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>JSWENERGY</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>461</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>457.5</v>
+      </c>
+      <c r="D73" s="4" t="n">
+        <v>461.75</v>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>0.92% (4.25)</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="n">
+        <v>466</v>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>470.25</v>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:15</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:30</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="n">
+        <v>470.25</v>
+      </c>
+      <c r="L73" s="4" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>(12-10-2026 to 18-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>DABUR</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>373.3</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>373</v>
+      </c>
+      <c r="D74" s="4" t="n">
+        <v>375.4</v>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>0.64% (2.4)</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>377.8</v>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>380.2</v>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:15</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:15</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="n">
+        <v>380.2</v>
+      </c>
+      <c r="L74" s="4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>(12-10-2026 to 18-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="18" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>403.85</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>402.15</v>
+      </c>
+      <c r="D75" s="4" t="n">
+        <v>410.15</v>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>1.95% (8.0)</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="n">
+        <v>418.15</v>
+      </c>
+      <c r="G75" s="4" t="n">
+        <v>426.15</v>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:15</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 11:45</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="n">
+        <v>418.15</v>
+      </c>
+      <c r="L75" s="4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>(12-10-2026 to 18-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="18" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>1486.2</v>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>1443.3</v>
+      </c>
+      <c r="D76" s="4" t="n">
+        <v>1508</v>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>4.29% (64.7)</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="n">
+        <v>1572.7</v>
+      </c>
+      <c r="G76" s="4" t="n">
+        <v>1637.4</v>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:15</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:15</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="n">
+        <v>1572.7</v>
+      </c>
+      <c r="L76" s="4" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>(12-10-2026 to 18-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="18" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>441.05</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>440.55</v>
+      </c>
+      <c r="D77" s="4" t="n">
+        <v>445.8</v>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>1.18% (5.25)</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>451.05</v>
+      </c>
+      <c r="G77" s="4" t="n">
+        <v>456.3</v>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:15</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 11:00</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="n">
+        <v>451.05</v>
+      </c>
+      <c r="L77" s="4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>(12-10-2026 to 18-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="n">
+        <v>11225</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>11130</v>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>11325</v>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>1.72% (195.0)</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>11520</v>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>11715</v>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:30</t>
+        </is>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v>11178</v>
+      </c>
+      <c r="L78" s="3" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>(12-10-2026 to 18-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="n">
+        <v>184.05</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>182.87</v>
+      </c>
+      <c r="D79" s="4" t="n">
+        <v>187.05</v>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>2.23% (4.18)</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>191.23</v>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>195.41</v>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:45</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:15</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>195.41</v>
+      </c>
+      <c r="L79" s="4" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>(12-10-2026 to 18-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="n">
+        <v>308.45</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>305.85</v>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>314.3</v>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>2.69% (8.45)</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>322.75</v>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>331.2</v>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 11:30</t>
+        </is>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>313.7</v>
+      </c>
+      <c r="L80" s="3" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>(12-10-2026 to 18-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="n">
+        <v>840.15</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>835</v>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>867.5</v>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>3.75% (32.5)</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>900</v>
+      </c>
+      <c r="G81" s="4" t="n">
+        <v>932.5</v>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 13:45</t>
+        </is>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>861.7</v>
+      </c>
+      <c r="L81" s="3" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
         <is>
           <t>(12-10-2026 to 18-10-2026)</t>
         </is>

--- a/data/trade_tracker_results.xlsx
+++ b/data/trade_tracker_results.xlsx
@@ -86,14 +86,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-        <bgColor rgb="00D9E1F2"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -135,10 +135,10 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -618,19 +618,19 @@
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 09:45</t>
+          <t>2026-10-15 10:15</t>
         </is>
       </c>
       <c r="K2" s="2" t="n">
-        <v>1139.1</v>
+        <v>1147.1</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>0.71</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
@@ -787,21 +787,21 @@
         <v>4782.2</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4749.6</v>
+        <v>4679.7</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>4815.5</v>
+        <v>4827.8</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>1.37% (65.9)</t>
+          <t>3.07% (148.1)</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>4881.4</v>
+        <v>4975.9</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>4947.3</v>
+        <v>5124</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -861,14 +861,14 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 15:15 (Active)</t>
+          <t>2026-10-15 15:15 (Active)</t>
         </is>
       </c>
       <c r="K7" s="2" t="n">
-        <v>313.7</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>-0.19</v>
+        <v>314.65</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>0.11</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -929,21 +929,21 @@
         <v>1658.1</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1656</v>
+        <v>1634.8</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>1666.2</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>0.61% (10.2)</t>
+          <t>1.88% (31.4)</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1676.4</v>
+        <v>1697.6</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1686.6</v>
+        <v>1729</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1044,21 +1044,21 @@
           <t>2026-10-14 13:45</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 15:15 (Active)</t>
+          <t>2026-10-15 09:15</t>
         </is>
       </c>
       <c r="K11" s="2" t="n">
-        <v>861.7</v>
+        <v>835</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.67</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -1117,21 +1117,21 @@
         <v>886.5</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>882.5</v>
+        <v>860.1</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>895.4</v>
+        <v>887</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>1.44% (12.9)</t>
+          <t>3.03% (26.9)</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>908.3</v>
+        <v>913.9</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>921.2</v>
+        <v>940.8</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1277,22 +1277,24 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-15 09:15</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr"/>
+          <t>2026-10-15 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>128.83</v>
+      </c>
       <c r="L16" s="4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -1369,24 +1371,22 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 09:30</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="n">
-        <v>11178</v>
-      </c>
-      <c r="L18" s="3" t="n">
-        <v>-1.3</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -1422,19 +1422,19 @@
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 12:00</t>
+          <t>2026-10-15 10:00</t>
         </is>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1180.8</v>
+        <v>1194.9</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.21</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -1470,19 +1470,19 @@
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 14:15</t>
+          <t>2026-10-15 13:15</t>
         </is>
       </c>
       <c r="K20" s="2" t="n">
-        <v>1572.7</v>
+        <v>1637.4</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>4.29</v>
+        <v>8.58</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -1543,21 +1543,21 @@
         <v>1745</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1743.2</v>
+        <v>1725.5</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1770.7</v>
+        <v>1751.3</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>1.55% (27.5)</t>
+          <t>1.47% (25.8)</t>
         </is>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1798.2</v>
+        <v>1777.1</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1825.7</v>
+        <v>1802.9</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1576,6 +1576,144 @@
       </c>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>ICICIPRULI</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>446.05</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>444.1</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>453.95</v>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>2.17% (9.85)</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>463.8</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>473.65</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>LODHA</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>1051.2</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>1038.1</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>1064.7</v>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>2.5% (26.6)</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>1091.3</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>1117.9</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>2559.6</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>2550</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>2593</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>1.66% (43.0)</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>2636</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>2679</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1590,7 +1728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:M82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1676,23 +1814,23 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Week Range: (21-09-2026 to 27-09-2026)</t>
         </is>
       </c>
-      <c r="B2" s="7" t="n"/>
-      <c r="C2" s="7" t="n"/>
-      <c r="D2" s="7" t="n"/>
-      <c r="E2" s="7" t="n"/>
-      <c r="F2" s="7" t="n"/>
-      <c r="G2" s="7" t="n"/>
-      <c r="H2" s="7" t="n"/>
-      <c r="I2" s="7" t="n"/>
-      <c r="J2" s="7" t="n"/>
-      <c r="K2" s="7" t="n"/>
-      <c r="L2" s="7" t="n"/>
-      <c r="M2" s="7" t="n"/>
+      <c r="B2" s="8" t="n"/>
+      <c r="C2" s="8" t="n"/>
+      <c r="D2" s="8" t="n"/>
+      <c r="E2" s="8" t="n"/>
+      <c r="F2" s="8" t="n"/>
+      <c r="G2" s="8" t="n"/>
+      <c r="H2" s="8" t="n"/>
+      <c r="I2" s="8" t="n"/>
+      <c r="J2" s="8" t="n"/>
+      <c r="K2" s="8" t="n"/>
+      <c r="L2" s="8" t="n"/>
+      <c r="M2" s="8" t="n"/>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -2121,28 +2259,28 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>1927</v>
+        <v>1242.8</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1915.1</v>
+        <v>1202.6</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1935.1</v>
+        <v>1246</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>1.03% (20.0)</t>
+          <t>3.48% (43.4)</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1955.1</v>
+        <v>1289.4</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1975.1</v>
+        <v>1332.8</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -2160,10 +2298,10 @@
         </is>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1942.9</v>
+        <v>1254.8</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.4</v>
+        <v>0.71</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
@@ -2174,28 +2312,28 @@
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>1242.8</v>
+        <v>1927</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1202.6</v>
+        <v>1915.1</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1246</v>
+        <v>1935.1</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>3.48% (43.4)</t>
+          <t>1.03% (20.0)</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1289.4</v>
+        <v>1955.1</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1332.8</v>
+        <v>1975.1</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -2213,10 +2351,10 @@
         </is>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1254.8</v>
+        <v>1942.9</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.71</v>
+        <v>0.4</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
@@ -2331,23 +2469,23 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>Week Range: (28-09-2026 to 04-10-2026)</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="n"/>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="7" t="n"/>
-      <c r="I15" s="7" t="n"/>
-      <c r="J15" s="7" t="n"/>
-      <c r="K15" s="7" t="n"/>
-      <c r="L15" s="7" t="n"/>
-      <c r="M15" s="7" t="n"/>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="8" t="n"/>
+      <c r="G15" s="8" t="n"/>
+      <c r="H15" s="8" t="n"/>
+      <c r="I15" s="8" t="n"/>
+      <c r="J15" s="8" t="n"/>
+      <c r="K15" s="8" t="n"/>
+      <c r="L15" s="8" t="n"/>
+      <c r="M15" s="8" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -2380,7 +2518,7 @@
           <t>2026-09-28 10:00</t>
         </is>
       </c>
-      <c r="I16" s="8" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -2592,7 +2730,7 @@
           <t>2026-09-28 13:45</t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -2670,49 +2808,49 @@
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>906.9</v>
+        <v>171.35</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>889.7</v>
+        <v>171.05</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>907.5</v>
+        <v>172.2</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>1.96% (17.8)</t>
+          <t>0.67% (1.15)</t>
         </is>
       </c>
       <c r="F22" s="4" t="n">
-        <v>925.3</v>
+        <v>173.35</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>943.1</v>
+        <v>174.5</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t>2026-09-28 15:15</t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:15</t>
+          <t>2026-09-28 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K22" s="2" t="n">
-        <v>889.7</v>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v>-1.96</v>
+        <v>172.45</v>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>0.15</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
@@ -2723,49 +2861,49 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>171.35</v>
+        <v>906.9</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>171.05</v>
+        <v>889.7</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>172.2</v>
+        <v>907.5</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>0.67% (1.15)</t>
+          <t>1.96% (17.8)</t>
         </is>
       </c>
       <c r="F23" s="4" t="n">
-        <v>173.35</v>
+        <v>925.3</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>174.5</v>
+        <v>943.1</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
           <t>2026-09-28 15:15</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 15:15 (Week End)</t>
+          <t>2026-09-29 10:15</t>
         </is>
       </c>
       <c r="K23" s="2" t="n">
-        <v>172.45</v>
-      </c>
-      <c r="L23" s="4" t="n">
-        <v>0.15</v>
+        <v>889.7</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>-1.96</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
@@ -2857,7 +2995,7 @@
           <t>2026-09-29 09:15</t>
         </is>
       </c>
-      <c r="I25" s="8" t="inlineStr">
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -2910,7 +3048,7 @@
           <t>2026-09-29 09:15</t>
         </is>
       </c>
-      <c r="I26" s="8" t="inlineStr">
+      <c r="I26" s="7" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -3094,49 +3232,49 @@
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>399.3</v>
+        <v>1495.7</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>394.7</v>
+        <v>1487.1</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>403.65</v>
+        <v>1498</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>2.22% (8.95)</t>
+          <t>0.73% (10.9)</t>
         </is>
       </c>
       <c r="F30" s="4" t="n">
-        <v>412.6</v>
+        <v>1508.9</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>421.55</v>
+        <v>1519.8</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 11:30</t>
         </is>
       </c>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:15 (Week End)</t>
+          <t>2026-09-29 12:30</t>
         </is>
       </c>
       <c r="K30" s="2" t="n">
-        <v>406</v>
-      </c>
-      <c r="L30" s="4" t="n">
-        <v>0.58</v>
+        <v>1487.1</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>-0.73</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
@@ -3147,49 +3285,49 @@
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>1495.7</v>
+        <v>399.3</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1487.1</v>
+        <v>394.7</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1498</v>
+        <v>403.65</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>0.73% (10.9)</t>
+          <t>2.22% (8.95)</t>
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1508.9</v>
+        <v>412.6</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1519.8</v>
+        <v>421.55</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 11:30</t>
         </is>
       </c>
-      <c r="I31" s="8" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:30</t>
+          <t>2026-09-29 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K31" s="2" t="n">
-        <v>1487.1</v>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>-0.73</v>
+        <v>406</v>
+      </c>
+      <c r="L31" s="4" t="n">
+        <v>0.58</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
@@ -3546,7 +3684,7 @@
           <t>2026-09-29 14:45</t>
         </is>
       </c>
-      <c r="I38" s="8" t="inlineStr">
+      <c r="I38" s="7" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -3624,28 +3762,28 @@
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>160.5</v>
+        <v>196.1</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>159.41</v>
+        <v>192.45</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>162.37</v>
+        <v>196.67</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>1.82% (2.96)</t>
+          <t>2.15% (4.22)</t>
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>165.33</v>
+        <v>200.89</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>168.29</v>
+        <v>205.11</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -3659,14 +3797,14 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 15:15 (Week End)</t>
+          <t>2026-09-30 09:15</t>
         </is>
       </c>
       <c r="K40" s="2" t="n">
-        <v>163.26</v>
+        <v>200.89</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>0.55</v>
+        <v>2.15</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
@@ -3677,49 +3815,49 @@
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>2391</v>
+        <v>4057</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>2381.6</v>
+        <v>4043.3</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>2420</v>
+        <v>4095</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>1.59% (38.4)</t>
+          <t>1.26% (51.7)</t>
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>2458.4</v>
+        <v>4146.7</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>2496.8</v>
+        <v>4198.4</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:30 (Week End)</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="K41" s="2" t="n">
-        <v>2409.1</v>
+        <v>4043.3</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-0.45</v>
+        <v>-1.26</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
@@ -3730,49 +3868,49 @@
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>399.3</v>
+        <v>263.55</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>394.7</v>
+        <v>263.3</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>403.65</v>
+        <v>266.2</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>2.22% (8.95)</t>
+          <t>1.09% (2.9)</t>
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>412.6</v>
+        <v>269.1</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>421.55</v>
+        <v>272</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I42" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 09:15</t>
+          <t>2026-09-30 14:15</t>
         </is>
       </c>
       <c r="K42" s="2" t="n">
-        <v>421.55</v>
-      </c>
-      <c r="L42" s="4" t="n">
-        <v>4.43</v>
+        <v>263.3</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>-1.09</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
@@ -3783,28 +3921,28 @@
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>991.6</v>
+        <v>4848.5</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>980.4</v>
+        <v>4837</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>992.7</v>
+        <v>4872</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>1.24% (12.3)</t>
+          <t>0.72% (35.0)</t>
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>1005</v>
+        <v>4907</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>1017.3</v>
+        <v>4942</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -3813,19 +3951,19 @@
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-30 10:30</t>
         </is>
       </c>
       <c r="K43" s="2" t="n">
-        <v>1017.3</v>
-      </c>
-      <c r="L43" s="4" t="n">
-        <v>2.48</v>
+        <v>4837</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>-0.72</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
@@ -3836,49 +3974,49 @@
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>1766.7</v>
+        <v>399.3</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>1736.8</v>
+        <v>394.7</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>1770.1</v>
+        <v>403.65</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>1.88% (33.3)</t>
+          <t>2.22% (8.95)</t>
         </is>
       </c>
       <c r="F44" s="4" t="n">
-        <v>1803.4</v>
+        <v>412.6</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>1836.7</v>
+        <v>421.55</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I44" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 15:15 (Week End)</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="K44" s="2" t="n">
-        <v>1798.3</v>
+        <v>421.55</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>1.59</v>
+        <v>4.43</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
@@ -3889,28 +4027,28 @@
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>4848.5</v>
+        <v>991.6</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>4837</v>
+        <v>980.4</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>4872</v>
+        <v>992.7</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>0.72% (35.0)</t>
+          <t>1.24% (12.3)</t>
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>4907</v>
+        <v>1005</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>4942</v>
+        <v>1017.3</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -3919,19 +4057,19 @@
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 10:30</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
       <c r="K45" s="2" t="n">
-        <v>4837</v>
-      </c>
-      <c r="L45" s="3" t="n">
-        <v>-0.72</v>
+        <v>1017.3</v>
+      </c>
+      <c r="L45" s="4" t="n">
+        <v>2.48</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
@@ -3942,49 +4080,49 @@
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>4057</v>
+        <v>2391</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>4043.3</v>
+        <v>2381.6</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>4095</v>
+        <v>2420</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>1.26% (51.7)</t>
+          <t>1.59% (38.4)</t>
         </is>
       </c>
       <c r="F46" s="4" t="n">
-        <v>4146.7</v>
+        <v>2458.4</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>4198.4</v>
+        <v>2496.8</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I46" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 09:15</t>
+          <t>2026-09-30 12:30 (Week End)</t>
         </is>
       </c>
       <c r="K46" s="2" t="n">
-        <v>4043.3</v>
+        <v>2409.1</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>-1.26</v>
+        <v>-0.45</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
@@ -3995,28 +4133,28 @@
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>196.1</v>
+        <v>160.5</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>192.45</v>
+        <v>159.41</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>196.67</v>
+        <v>162.37</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>2.15% (4.22)</t>
+          <t>1.82% (2.96)</t>
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>200.89</v>
+        <v>165.33</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>205.11</v>
+        <v>168.29</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -4030,14 +4168,14 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:15</t>
+          <t>2026-09-30 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K47" s="2" t="n">
-        <v>200.89</v>
+        <v>163.26</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>2.15</v>
+        <v>0.55</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
@@ -4048,49 +4186,49 @@
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>263.55</v>
+        <v>1766.7</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>263.3</v>
+        <v>1736.8</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>266.2</v>
+        <v>1770.1</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>1.09% (2.9)</t>
+          <t>1.88% (33.3)</t>
         </is>
       </c>
       <c r="F48" s="4" t="n">
-        <v>269.1</v>
+        <v>1803.4</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>272</v>
+        <v>1836.7</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I48" s="8" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:15</t>
+          <t>2026-09-30 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K48" s="2" t="n">
-        <v>263.3</v>
-      </c>
-      <c r="L48" s="3" t="n">
-        <v>-1.09</v>
+        <v>1798.3</v>
+      </c>
+      <c r="L48" s="4" t="n">
+        <v>1.59</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
@@ -4205,23 +4343,23 @@
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="7" t="inlineStr">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>Week Range: (05-10-2026 to 11-10-2026)</t>
         </is>
       </c>
-      <c r="B51" s="7" t="n"/>
-      <c r="C51" s="7" t="n"/>
-      <c r="D51" s="7" t="n"/>
-      <c r="E51" s="7" t="n"/>
-      <c r="F51" s="7" t="n"/>
-      <c r="G51" s="7" t="n"/>
-      <c r="H51" s="7" t="n"/>
-      <c r="I51" s="7" t="n"/>
-      <c r="J51" s="7" t="n"/>
-      <c r="K51" s="7" t="n"/>
-      <c r="L51" s="7" t="n"/>
-      <c r="M51" s="7" t="n"/>
+      <c r="B51" s="8" t="n"/>
+      <c r="C51" s="8" t="n"/>
+      <c r="D51" s="8" t="n"/>
+      <c r="E51" s="8" t="n"/>
+      <c r="F51" s="8" t="n"/>
+      <c r="G51" s="8" t="n"/>
+      <c r="H51" s="8" t="n"/>
+      <c r="I51" s="8" t="n"/>
+      <c r="J51" s="8" t="n"/>
+      <c r="K51" s="8" t="n"/>
+      <c r="L51" s="8" t="n"/>
+      <c r="M51" s="8" t="n"/>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
@@ -4625,7 +4763,7 @@
           <t>2026-10-08 09:15</t>
         </is>
       </c>
-      <c r="I59" s="8" t="inlineStr">
+      <c r="I59" s="7" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -4650,28 +4788,28 @@
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>LTM</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>3936</v>
+        <v>254.65</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>3908.4</v>
+        <v>253.2</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>3941.6</v>
+        <v>255.4</v>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>0.84% (33.2)</t>
+          <t>0.86% (2.2)</t>
         </is>
       </c>
       <c r="F60" s="4" t="n">
-        <v>3974.8</v>
+        <v>257.6</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>4008</v>
+        <v>259.8</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -4685,14 +4823,14 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 09:15</t>
+          <t>2026-10-09 10:00</t>
         </is>
       </c>
       <c r="K60" s="2" t="n">
-        <v>4008</v>
+        <v>259.8</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
@@ -4703,49 +4841,49 @@
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>1316.5</v>
+        <v>902.05</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>1308.7</v>
+        <v>891.8</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>1323.7</v>
+        <v>903</v>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>1.13% (15.0)</t>
+          <t>1.24% (11.2)</t>
         </is>
       </c>
       <c r="F61" s="4" t="n">
-        <v>1338.7</v>
+        <v>914.2</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>1353.7</v>
+        <v>925.4</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I61" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I61" s="7" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 10:15</t>
+          <t>2026-10-09 09:15</t>
         </is>
       </c>
       <c r="K61" s="2" t="n">
-        <v>1353.7</v>
-      </c>
-      <c r="L61" s="4" t="n">
-        <v>2.27</v>
+        <v>891.8</v>
+      </c>
+      <c r="L61" s="3" t="n">
+        <v>-1.24</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
@@ -4756,49 +4894,49 @@
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>1674.8</v>
+        <v>1702.1</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>1658.6</v>
+        <v>1701</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>1684.2</v>
+        <v>1710.1</v>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>1.52% (25.6)</t>
+          <t>0.53% (9.1)</t>
         </is>
       </c>
       <c r="F62" s="4" t="n">
-        <v>1709.8</v>
+        <v>1719.2</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>1735.4</v>
+        <v>1728.3</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I62" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 15:15 (Week End)</t>
+          <t>2026-10-09 09:45</t>
         </is>
       </c>
       <c r="K62" s="2" t="n">
-        <v>1682</v>
-      </c>
-      <c r="L62" s="3" t="n">
-        <v>-0.13</v>
+        <v>1728.3</v>
+      </c>
+      <c r="L62" s="4" t="n">
+        <v>1.06</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
@@ -4809,28 +4947,28 @@
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>1702.1</v>
+        <v>1316.5</v>
       </c>
       <c r="C63" s="3" t="n">
-        <v>1701</v>
+        <v>1308.7</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>1710.1</v>
+        <v>1323.7</v>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>0.53% (9.1)</t>
+          <t>1.13% (15.0)</t>
         </is>
       </c>
       <c r="F63" s="4" t="n">
-        <v>1719.2</v>
+        <v>1338.7</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>1728.3</v>
+        <v>1353.7</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -4844,14 +4982,14 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 09:45</t>
+          <t>2026-10-09 10:15</t>
         </is>
       </c>
       <c r="K63" s="2" t="n">
-        <v>1728.3</v>
+        <v>1353.7</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>1.06</v>
+        <v>2.27</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
@@ -4862,37 +5000,37 @@
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>LTM</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>902.05</v>
+        <v>3936</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>891.8</v>
+        <v>3908.4</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>903</v>
+        <v>3941.6</v>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>1.24% (11.2)</t>
+          <t>0.84% (33.2)</t>
         </is>
       </c>
       <c r="F64" s="4" t="n">
-        <v>914.2</v>
+        <v>3974.8</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>925.4</v>
+        <v>4008</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I64" s="8" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -4901,10 +5039,10 @@
         </is>
       </c>
       <c r="K64" s="2" t="n">
-        <v>891.8</v>
-      </c>
-      <c r="L64" s="3" t="n">
-        <v>-1.24</v>
+        <v>4008</v>
+      </c>
+      <c r="L64" s="4" t="n">
+        <v>1.68</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
@@ -4915,49 +5053,49 @@
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>254.65</v>
+        <v>1674.8</v>
       </c>
       <c r="C65" s="3" t="n">
-        <v>253.2</v>
+        <v>1658.6</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>255.4</v>
+        <v>1684.2</v>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>0.86% (2.2)</t>
+          <t>1.52% (25.6)</t>
         </is>
       </c>
       <c r="F65" s="4" t="n">
-        <v>257.6</v>
+        <v>1709.8</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>259.8</v>
+        <v>1735.4</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I65" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 10:00</t>
+          <t>2026-10-09 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K65" s="2" t="n">
-        <v>259.8</v>
-      </c>
-      <c r="L65" s="4" t="n">
-        <v>1.72</v>
+        <v>1682</v>
+      </c>
+      <c r="L65" s="3" t="n">
+        <v>-0.13</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
@@ -4966,23 +5104,23 @@
       </c>
     </row>
     <row r="66" ht="22" customHeight="1">
-      <c r="A66" s="7" t="inlineStr">
+      <c r="A66" s="8" t="inlineStr">
         <is>
           <t>Week Range: (12-10-2026 to 18-10-2026)</t>
         </is>
       </c>
-      <c r="B66" s="7" t="n"/>
-      <c r="C66" s="7" t="n"/>
-      <c r="D66" s="7" t="n"/>
-      <c r="E66" s="7" t="n"/>
-      <c r="F66" s="7" t="n"/>
-      <c r="G66" s="7" t="n"/>
-      <c r="H66" s="7" t="n"/>
-      <c r="I66" s="7" t="n"/>
-      <c r="J66" s="7" t="n"/>
-      <c r="K66" s="7" t="n"/>
-      <c r="L66" s="7" t="n"/>
-      <c r="M66" s="7" t="n"/>
+      <c r="B66" s="8" t="n"/>
+      <c r="C66" s="8" t="n"/>
+      <c r="D66" s="8" t="n"/>
+      <c r="E66" s="8" t="n"/>
+      <c r="F66" s="8" t="n"/>
+      <c r="G66" s="8" t="n"/>
+      <c r="H66" s="8" t="n"/>
+      <c r="I66" s="8" t="n"/>
+      <c r="J66" s="8" t="n"/>
+      <c r="K66" s="8" t="n"/>
+      <c r="L66" s="8" t="n"/>
+      <c r="M66" s="8" t="n"/>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
@@ -5070,19 +5208,19 @@
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 09:45</t>
+          <t>2026-10-15 10:15</t>
         </is>
       </c>
       <c r="K68" s="2" t="n">
-        <v>1139.1</v>
+        <v>1147.1</v>
       </c>
       <c r="L68" s="4" t="n">
-        <v>0.71</v>
+        <v>1.41</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
@@ -5176,19 +5314,19 @@
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 12:00</t>
+          <t>2026-10-15 10:00</t>
         </is>
       </c>
       <c r="K70" s="2" t="n">
-        <v>1180.8</v>
+        <v>1194.9</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>1.21</v>
+        <v>2.42</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
@@ -5305,28 +5443,28 @@
     <row r="73" ht="18" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>461</v>
+        <v>441.05</v>
       </c>
       <c r="C73" s="3" t="n">
-        <v>457.5</v>
+        <v>440.55</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>461.75</v>
+        <v>445.8</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>0.92% (4.25)</t>
+          <t>1.18% (5.25)</t>
         </is>
       </c>
       <c r="F73" s="4" t="n">
-        <v>466</v>
+        <v>451.05</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>470.25</v>
+        <v>456.3</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -5335,19 +5473,19 @@
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 09:30</t>
+          <t>2026-10-14 11:00</t>
         </is>
       </c>
       <c r="K73" s="2" t="n">
-        <v>470.25</v>
+        <v>451.05</v>
       </c>
       <c r="L73" s="4" t="n">
-        <v>1.84</v>
+        <v>1.18</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
@@ -5358,28 +5496,28 @@
     <row r="74" ht="18" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>373.3</v>
+        <v>461</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>373</v>
+        <v>457.5</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>375.4</v>
+        <v>461.75</v>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>0.64% (2.4)</t>
+          <t>0.92% (4.25)</t>
         </is>
       </c>
       <c r="F74" s="4" t="n">
-        <v>377.8</v>
+        <v>466</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>380.2</v>
+        <v>470.25</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -5393,14 +5531,14 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 09:15</t>
+          <t>2026-10-14 09:30</t>
         </is>
       </c>
       <c r="K74" s="2" t="n">
-        <v>380.2</v>
+        <v>470.25</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>1.28</v>
+        <v>1.84</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
@@ -5494,19 +5632,19 @@
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 14:15</t>
+          <t>2026-10-15 13:15</t>
         </is>
       </c>
       <c r="K76" s="2" t="n">
-        <v>1572.7</v>
+        <v>1637.4</v>
       </c>
       <c r="L76" s="4" t="n">
-        <v>4.29</v>
+        <v>8.58</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
@@ -5517,28 +5655,28 @@
     <row r="77" ht="18" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>441.05</v>
+        <v>373.3</v>
       </c>
       <c r="C77" s="3" t="n">
-        <v>440.55</v>
+        <v>373</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>445.8</v>
+        <v>375.4</v>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>1.18% (5.25)</t>
+          <t>0.64% (2.4)</t>
         </is>
       </c>
       <c r="F77" s="4" t="n">
-        <v>451.05</v>
+        <v>377.8</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>456.3</v>
+        <v>380.2</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -5547,19 +5685,19 @@
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 11:00</t>
+          <t>2026-10-14 09:15</t>
         </is>
       </c>
       <c r="K77" s="2" t="n">
-        <v>451.05</v>
+        <v>380.2</v>
       </c>
       <c r="L77" s="4" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
@@ -5711,14 +5849,14 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 15:15 (Active)</t>
+          <t>2026-10-15 15:15 (Active)</t>
         </is>
       </c>
       <c r="K80" s="2" t="n">
-        <v>313.7</v>
-      </c>
-      <c r="L80" s="3" t="n">
-        <v>-0.19</v>
+        <v>314.65</v>
+      </c>
+      <c r="L80" s="4" t="n">
+        <v>0.11</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
@@ -5757,23 +5895,76 @@
           <t>2026-10-14 13:45</t>
         </is>
       </c>
-      <c r="I81" s="6" t="inlineStr">
+      <c r="I81" s="7" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:15</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>835</v>
+      </c>
+      <c r="L81" s="3" t="n">
+        <v>-3.75</v>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>(12-10-2026 to 18-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="n">
+        <v>125.27</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>125</v>
+      </c>
+      <c r="D82" s="4" t="n">
+        <v>127.28</v>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>1.79% (2.28)</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>129.56</v>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>131.84</v>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:15</t>
+        </is>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K81" s="2" t="n">
-        <v>861.7</v>
-      </c>
-      <c r="L81" s="3" t="n">
-        <v>-0.67</v>
-      </c>
-      <c r="M81" s="2" t="inlineStr">
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>128.83</v>
+      </c>
+      <c r="L82" s="4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
         <is>
           <t>(12-10-2026 to 18-10-2026)</t>
         </is>

--- a/data/trade_tracker_results.xlsx
+++ b/data/trade_tracker_results.xlsx
@@ -86,14 +86,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-        <bgColor rgb="00D9E1F2"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -135,10 +135,10 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -861,14 +861,14 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 15:15 (Active)</t>
+          <t>2026-10-16 15:15 (Active)</t>
         </is>
       </c>
       <c r="K7" s="2" t="n">
-        <v>314.65</v>
+        <v>315.15</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.11</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -1023,42 +1023,40 @@
         <v>840.15</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>835</v>
+        <v>808.75</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>867.5</v>
+        <v>861.95</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>3.75% (32.5)</t>
+          <t>6.17% (53.2)</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>900</v>
+        <v>915.15</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>932.5</v>
+        <v>968.35</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 13:45</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 09:15</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="n">
-        <v>835</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>-3.75</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -1089,22 +1087,24 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-16 09:15</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr"/>
+          <t>2026-10-16 09:15</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>168.75</v>
+      </c>
       <c r="L12" s="4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -1135,22 +1135,24 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-16 09:15</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr"/>
+          <t>2026-10-16 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>908</v>
+      </c>
       <c r="L13" s="4" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -1280,21 +1282,21 @@
           <t>2026-10-15 09:15</t>
         </is>
       </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 15:15 (Active)</t>
+          <t>2026-10-16 13:30</t>
         </is>
       </c>
       <c r="K16" s="2" t="n">
-        <v>128.83</v>
+        <v>129.56</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.22</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -1325,22 +1327,24 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-16 09:15</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr"/>
+          <t>2026-10-16 11:30</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>3661.8</v>
+      </c>
       <c r="L17" s="4" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -1371,22 +1375,24 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-16 09:15</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr"/>
+          <t>2026-10-16 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>11489</v>
+      </c>
       <c r="L18" s="4" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -1589,21 +1595,21 @@
         <v>446.05</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>444.1</v>
+        <v>435.65</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>453.95</v>
+        <v>449.1</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>2.17% (9.85)</t>
+          <t>2.99% (13.45)</t>
         </is>
       </c>
       <c r="F23" s="4" t="n">
-        <v>463.8</v>
+        <v>462.55</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>473.65</v>
+        <v>476</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1699,21 +1705,207 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>2026-10-16 09:15</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>2598.3</v>
+      </c>
+      <c r="L25" s="4" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>BANKBARODA</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>230.18</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>225.22</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>233.78</v>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>3.66% (8.56)</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>242.34</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>250.9</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>WAIT (No Entry)</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="4" t="n">
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>9113.5</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>8937.5</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>9170.5</v>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>2.54% (233.0)</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>9403.5</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>9636.5</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>2853.5</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>2843.4</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>2894.1</v>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>1.75% (50.7)</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>2944.8</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>2995.5</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>VBL</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>426.3</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>424.05</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>431.1</v>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>1.64% (7.05)</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>438.15</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>445.2</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1728,7 +1920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M82"/>
+  <dimension ref="A1:M87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1814,23 +2006,23 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Week Range: (21-09-2026 to 27-09-2026)</t>
         </is>
       </c>
-      <c r="B2" s="8" t="n"/>
-      <c r="C2" s="8" t="n"/>
-      <c r="D2" s="8" t="n"/>
-      <c r="E2" s="8" t="n"/>
-      <c r="F2" s="8" t="n"/>
-      <c r="G2" s="8" t="n"/>
-      <c r="H2" s="8" t="n"/>
-      <c r="I2" s="8" t="n"/>
-      <c r="J2" s="8" t="n"/>
-      <c r="K2" s="8" t="n"/>
-      <c r="L2" s="8" t="n"/>
-      <c r="M2" s="8" t="n"/>
+      <c r="B2" s="7" t="n"/>
+      <c r="C2" s="7" t="n"/>
+      <c r="D2" s="7" t="n"/>
+      <c r="E2" s="7" t="n"/>
+      <c r="F2" s="7" t="n"/>
+      <c r="G2" s="7" t="n"/>
+      <c r="H2" s="7" t="n"/>
+      <c r="I2" s="7" t="n"/>
+      <c r="J2" s="7" t="n"/>
+      <c r="K2" s="7" t="n"/>
+      <c r="L2" s="7" t="n"/>
+      <c r="M2" s="7" t="n"/>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -2259,28 +2451,28 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>1242.8</v>
+        <v>1927</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1202.6</v>
+        <v>1915.1</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1246</v>
+        <v>1935.1</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>3.48% (43.4)</t>
+          <t>1.03% (20.0)</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1289.4</v>
+        <v>1955.1</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1332.8</v>
+        <v>1975.1</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -2298,10 +2490,10 @@
         </is>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1254.8</v>
+        <v>1942.9</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.71</v>
+        <v>0.4</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
@@ -2312,28 +2504,28 @@
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>1927</v>
+        <v>1242.8</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1915.1</v>
+        <v>1202.6</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1935.1</v>
+        <v>1246</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>1.03% (20.0)</t>
+          <t>3.48% (43.4)</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1955.1</v>
+        <v>1289.4</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1975.1</v>
+        <v>1332.8</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -2351,10 +2543,10 @@
         </is>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1942.9</v>
+        <v>1254.8</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.4</v>
+        <v>0.71</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
@@ -2469,23 +2661,23 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>Week Range: (28-09-2026 to 04-10-2026)</t>
         </is>
       </c>
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="n"/>
-      <c r="E15" s="8" t="n"/>
-      <c r="F15" s="8" t="n"/>
-      <c r="G15" s="8" t="n"/>
-      <c r="H15" s="8" t="n"/>
-      <c r="I15" s="8" t="n"/>
-      <c r="J15" s="8" t="n"/>
-      <c r="K15" s="8" t="n"/>
-      <c r="L15" s="8" t="n"/>
-      <c r="M15" s="8" t="n"/>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="7" t="n"/>
+      <c r="I15" s="7" t="n"/>
+      <c r="J15" s="7" t="n"/>
+      <c r="K15" s="7" t="n"/>
+      <c r="L15" s="7" t="n"/>
+      <c r="M15" s="7" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -2518,7 +2710,7 @@
           <t>2026-09-28 10:00</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -2730,7 +2922,7 @@
           <t>2026-09-28 13:45</t>
         </is>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="I20" s="8" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -2808,49 +3000,49 @@
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>171.35</v>
+        <v>906.9</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>171.05</v>
+        <v>889.7</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>172.2</v>
+        <v>907.5</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>0.67% (1.15)</t>
+          <t>1.96% (17.8)</t>
         </is>
       </c>
       <c r="F22" s="4" t="n">
-        <v>173.35</v>
+        <v>925.3</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>174.5</v>
+        <v>943.1</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t>2026-09-28 15:15</t>
         </is>
       </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 15:15 (Week End)</t>
+          <t>2026-09-29 10:15</t>
         </is>
       </c>
       <c r="K22" s="2" t="n">
-        <v>172.45</v>
-      </c>
-      <c r="L22" s="4" t="n">
-        <v>0.15</v>
+        <v>889.7</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>-1.96</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
@@ -2861,49 +3053,49 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>906.9</v>
+        <v>171.35</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>889.7</v>
+        <v>171.05</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>907.5</v>
+        <v>172.2</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>1.96% (17.8)</t>
+          <t>0.67% (1.15)</t>
         </is>
       </c>
       <c r="F23" s="4" t="n">
-        <v>925.3</v>
+        <v>173.35</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>943.1</v>
+        <v>174.5</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
           <t>2026-09-28 15:15</t>
         </is>
       </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:15</t>
+          <t>2026-09-28 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K23" s="2" t="n">
-        <v>889.7</v>
-      </c>
-      <c r="L23" s="3" t="n">
-        <v>-1.96</v>
+        <v>172.45</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>0.15</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
@@ -2995,7 +3187,7 @@
           <t>2026-09-29 09:15</t>
         </is>
       </c>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="I25" s="8" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -3048,7 +3240,7 @@
           <t>2026-09-29 09:15</t>
         </is>
       </c>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="I26" s="8" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -3232,49 +3424,49 @@
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>1495.7</v>
+        <v>399.3</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1487.1</v>
+        <v>394.7</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1498</v>
+        <v>403.65</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>0.73% (10.9)</t>
+          <t>2.22% (8.95)</t>
         </is>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1508.9</v>
+        <v>412.6</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1519.8</v>
+        <v>421.55</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 11:30</t>
         </is>
       </c>
-      <c r="I30" s="7" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:30</t>
+          <t>2026-09-29 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K30" s="2" t="n">
-        <v>1487.1</v>
-      </c>
-      <c r="L30" s="3" t="n">
-        <v>-0.73</v>
+        <v>406</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>0.58</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
@@ -3285,49 +3477,49 @@
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>399.3</v>
+        <v>1495.7</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>394.7</v>
+        <v>1487.1</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>403.65</v>
+        <v>1498</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>2.22% (8.95)</t>
+          <t>0.73% (10.9)</t>
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>412.6</v>
+        <v>1508.9</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>421.55</v>
+        <v>1519.8</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 11:30</t>
         </is>
       </c>
-      <c r="I31" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I31" s="8" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:15 (Week End)</t>
+          <t>2026-09-29 12:30</t>
         </is>
       </c>
       <c r="K31" s="2" t="n">
-        <v>406</v>
-      </c>
-      <c r="L31" s="4" t="n">
-        <v>0.58</v>
+        <v>1487.1</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>-0.73</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
@@ -3684,7 +3876,7 @@
           <t>2026-09-29 14:45</t>
         </is>
       </c>
-      <c r="I38" s="7" t="inlineStr">
+      <c r="I38" s="8" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -3762,28 +3954,28 @@
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>196.1</v>
+        <v>160.5</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>192.45</v>
+        <v>159.41</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>196.67</v>
+        <v>162.37</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>2.15% (4.22)</t>
+          <t>1.82% (2.96)</t>
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>200.89</v>
+        <v>165.33</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>205.11</v>
+        <v>168.29</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -3797,14 +3989,14 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:15</t>
+          <t>2026-09-30 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K40" s="2" t="n">
-        <v>200.89</v>
+        <v>163.26</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>2.15</v>
+        <v>0.55</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
@@ -3815,49 +4007,49 @@
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>4057</v>
+        <v>2391</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>4043.3</v>
+        <v>2381.6</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>4095</v>
+        <v>2420</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>1.26% (51.7)</t>
+          <t>1.59% (38.4)</t>
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>4146.7</v>
+        <v>2458.4</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>4198.4</v>
+        <v>2496.8</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 09:15</t>
+          <t>2026-09-30 12:30 (Week End)</t>
         </is>
       </c>
       <c r="K41" s="2" t="n">
-        <v>4043.3</v>
+        <v>2409.1</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-1.26</v>
+        <v>-0.45</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
@@ -3868,49 +4060,49 @@
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>263.55</v>
+        <v>1766.7</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>263.3</v>
+        <v>1736.8</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>266.2</v>
+        <v>1770.1</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>1.09% (2.9)</t>
+          <t>1.88% (33.3)</t>
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>269.1</v>
+        <v>1803.4</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>272</v>
+        <v>1836.7</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I42" s="7" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:15</t>
+          <t>2026-09-30 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K42" s="2" t="n">
-        <v>263.3</v>
-      </c>
-      <c r="L42" s="3" t="n">
-        <v>-1.09</v>
+        <v>1798.3</v>
+      </c>
+      <c r="L42" s="4" t="n">
+        <v>1.59</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
@@ -3921,28 +4113,28 @@
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>4848.5</v>
+        <v>991.6</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>4837</v>
+        <v>980.4</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>4872</v>
+        <v>992.7</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>0.72% (35.0)</t>
+          <t>1.24% (12.3)</t>
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>4907</v>
+        <v>1005</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>4942</v>
+        <v>1017.3</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -3951,19 +4143,19 @@
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 10:30</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
       <c r="K43" s="2" t="n">
-        <v>4837</v>
-      </c>
-      <c r="L43" s="3" t="n">
-        <v>-0.72</v>
+        <v>1017.3</v>
+      </c>
+      <c r="L43" s="4" t="n">
+        <v>2.48</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
@@ -4027,28 +4219,28 @@
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>991.6</v>
+        <v>4848.5</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>980.4</v>
+        <v>4837</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>992.7</v>
+        <v>4872</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>1.24% (12.3)</t>
+          <t>0.72% (35.0)</t>
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>1005</v>
+        <v>4907</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>1017.3</v>
+        <v>4942</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -4057,19 +4249,19 @@
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-30 10:30</t>
         </is>
       </c>
       <c r="K45" s="2" t="n">
-        <v>1017.3</v>
-      </c>
-      <c r="L45" s="4" t="n">
-        <v>2.48</v>
+        <v>4837</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>-0.72</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
@@ -4080,49 +4272,49 @@
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>2391</v>
+        <v>263.55</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>2381.6</v>
+        <v>263.3</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>2420</v>
+        <v>266.2</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>1.59% (38.4)</t>
+          <t>1.09% (2.9)</t>
         </is>
       </c>
       <c r="F46" s="4" t="n">
-        <v>2458.4</v>
+        <v>269.1</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>2496.8</v>
+        <v>272</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I46" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I46" s="8" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:30 (Week End)</t>
+          <t>2026-09-30 14:15</t>
         </is>
       </c>
       <c r="K46" s="2" t="n">
-        <v>2409.1</v>
+        <v>263.3</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>-0.45</v>
+        <v>-1.09</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
@@ -4133,49 +4325,49 @@
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>160.5</v>
+        <v>4057</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>159.41</v>
+        <v>4043.3</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>162.37</v>
+        <v>4095</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>1.82% (2.96)</t>
+          <t>1.26% (51.7)</t>
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>165.33</v>
+        <v>4146.7</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>168.29</v>
+        <v>4198.4</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I47" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 15:15 (Week End)</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="K47" s="2" t="n">
-        <v>163.26</v>
-      </c>
-      <c r="L47" s="4" t="n">
-        <v>0.55</v>
+        <v>4043.3</v>
+      </c>
+      <c r="L47" s="3" t="n">
+        <v>-1.26</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
@@ -4186,28 +4378,28 @@
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>1766.7</v>
+        <v>196.1</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1736.8</v>
+        <v>192.45</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>1770.1</v>
+        <v>196.67</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>1.88% (33.3)</t>
+          <t>2.15% (4.22)</t>
         </is>
       </c>
       <c r="F48" s="4" t="n">
-        <v>1803.4</v>
+        <v>200.89</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>1836.7</v>
+        <v>205.11</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -4221,14 +4413,14 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 15:15 (Week End)</t>
+          <t>2026-09-30 09:15</t>
         </is>
       </c>
       <c r="K48" s="2" t="n">
-        <v>1798.3</v>
+        <v>200.89</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>1.59</v>
+        <v>2.15</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
@@ -4343,23 +4535,23 @@
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>Week Range: (05-10-2026 to 11-10-2026)</t>
         </is>
       </c>
-      <c r="B51" s="8" t="n"/>
-      <c r="C51" s="8" t="n"/>
-      <c r="D51" s="8" t="n"/>
-      <c r="E51" s="8" t="n"/>
-      <c r="F51" s="8" t="n"/>
-      <c r="G51" s="8" t="n"/>
-      <c r="H51" s="8" t="n"/>
-      <c r="I51" s="8" t="n"/>
-      <c r="J51" s="8" t="n"/>
-      <c r="K51" s="8" t="n"/>
-      <c r="L51" s="8" t="n"/>
-      <c r="M51" s="8" t="n"/>
+      <c r="B51" s="7" t="n"/>
+      <c r="C51" s="7" t="n"/>
+      <c r="D51" s="7" t="n"/>
+      <c r="E51" s="7" t="n"/>
+      <c r="F51" s="7" t="n"/>
+      <c r="G51" s="7" t="n"/>
+      <c r="H51" s="7" t="n"/>
+      <c r="I51" s="7" t="n"/>
+      <c r="J51" s="7" t="n"/>
+      <c r="K51" s="7" t="n"/>
+      <c r="L51" s="7" t="n"/>
+      <c r="M51" s="7" t="n"/>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
@@ -4576,49 +4768,49 @@
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>168.43</v>
+        <v>3709.5</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>166.48</v>
+        <v>3695</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>168.99</v>
+        <v>3723.8</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>1.49% (2.51)</t>
+          <t>0.77% (28.8)</t>
         </is>
       </c>
       <c r="F56" s="4" t="n">
-        <v>171.5</v>
+        <v>3752.6</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>174.01</v>
+        <v>3781.4</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
           <t>2026-10-07 09:15</t>
         </is>
       </c>
-      <c r="I56" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 15:15 (Week End)</t>
+          <t>2026-10-07 09:15</t>
         </is>
       </c>
       <c r="K56" s="2" t="n">
-        <v>170.71</v>
+        <v>3781.4</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
@@ -4629,49 +4821,49 @@
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>1295</v>
+        <v>168.43</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>1293</v>
+        <v>166.48</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>1299.4</v>
+        <v>168.99</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>0.49% (6.4)</t>
+          <t>1.49% (2.51)</t>
         </is>
       </c>
       <c r="F57" s="4" t="n">
-        <v>1305.8</v>
+        <v>171.5</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>1312.2</v>
+        <v>174.01</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
           <t>2026-10-07 09:15</t>
         </is>
       </c>
-      <c r="I57" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 09:15</t>
+          <t>2026-10-07 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K57" s="2" t="n">
-        <v>1312.2</v>
+        <v>170.71</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>0.99</v>
+        <v>1.02</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
@@ -4682,28 +4874,28 @@
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>3709.5</v>
+        <v>1295</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>3695</v>
+        <v>1293</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>3723.8</v>
+        <v>1299.4</v>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>0.77% (28.8)</t>
+          <t>0.49% (6.4)</t>
         </is>
       </c>
       <c r="F58" s="4" t="n">
-        <v>3752.6</v>
+        <v>1305.8</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>3781.4</v>
+        <v>1312.2</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -4721,10 +4913,10 @@
         </is>
       </c>
       <c r="K58" s="2" t="n">
-        <v>3781.4</v>
+        <v>1312.2</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>1.55</v>
+        <v>0.99</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
@@ -4763,7 +4955,7 @@
           <t>2026-10-08 09:15</t>
         </is>
       </c>
-      <c r="I59" s="7" t="inlineStr">
+      <c r="I59" s="8" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -4869,7 +5061,7 @@
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I61" s="7" t="inlineStr">
+      <c r="I61" s="8" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -5104,49 +5296,49 @@
       </c>
     </row>
     <row r="66" ht="22" customHeight="1">
-      <c r="A66" s="8" t="inlineStr">
+      <c r="A66" s="7" t="inlineStr">
         <is>
           <t>Week Range: (12-10-2026 to 18-10-2026)</t>
         </is>
       </c>
-      <c r="B66" s="8" t="n"/>
-      <c r="C66" s="8" t="n"/>
-      <c r="D66" s="8" t="n"/>
-      <c r="E66" s="8" t="n"/>
-      <c r="F66" s="8" t="n"/>
-      <c r="G66" s="8" t="n"/>
-      <c r="H66" s="8" t="n"/>
-      <c r="I66" s="8" t="n"/>
-      <c r="J66" s="8" t="n"/>
-      <c r="K66" s="8" t="n"/>
-      <c r="L66" s="8" t="n"/>
-      <c r="M66" s="8" t="n"/>
+      <c r="B66" s="7" t="n"/>
+      <c r="C66" s="7" t="n"/>
+      <c r="D66" s="7" t="n"/>
+      <c r="E66" s="7" t="n"/>
+      <c r="F66" s="7" t="n"/>
+      <c r="G66" s="7" t="n"/>
+      <c r="H66" s="7" t="n"/>
+      <c r="I66" s="7" t="n"/>
+      <c r="J66" s="7" t="n"/>
+      <c r="K66" s="7" t="n"/>
+      <c r="L66" s="7" t="n"/>
+      <c r="M66" s="7" t="n"/>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>1658.1</v>
+        <v>709.75</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>1658</v>
+        <v>708.8</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>1673.9</v>
+        <v>711.4</v>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>0.95% (15.9)</t>
+          <t>0.37% (2.6)</t>
         </is>
       </c>
       <c r="F67" s="4" t="n">
-        <v>1689.8</v>
+        <v>714</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>1705.7</v>
+        <v>716.6</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -5155,19 +5347,19 @@
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 09:30</t>
+          <t>2026-10-13 09:45</t>
         </is>
       </c>
       <c r="K67" s="2" t="n">
-        <v>1689.8</v>
+        <v>716.6</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>0.95</v>
+        <v>0.73</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
@@ -5231,28 +5423,28 @@
     <row r="69" ht="18" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>709.75</v>
+        <v>1658.1</v>
       </c>
       <c r="C69" s="3" t="n">
-        <v>708.8</v>
+        <v>1658</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>711.4</v>
+        <v>1673.9</v>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>0.37% (2.6)</t>
+          <t>0.95% (15.9)</t>
         </is>
       </c>
       <c r="F69" s="4" t="n">
-        <v>714</v>
+        <v>1689.8</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>716.6</v>
+        <v>1705.7</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -5261,19 +5453,19 @@
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 09:45</t>
+          <t>2026-10-13 09:30</t>
         </is>
       </c>
       <c r="K69" s="2" t="n">
-        <v>716.6</v>
+        <v>1689.8</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>0.73</v>
+        <v>0.95</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
@@ -5284,28 +5476,28 @@
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>1160.2</v>
+        <v>403.85</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>1152.6</v>
+        <v>402.15</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>1166.7</v>
+        <v>410.15</v>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>1.21% (14.1)</t>
+          <t>1.95% (8.0)</t>
         </is>
       </c>
       <c r="F70" s="4" t="n">
-        <v>1180.8</v>
+        <v>418.15</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>1194.9</v>
+        <v>426.15</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -5314,19 +5506,19 @@
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 10:00</t>
+          <t>2026-10-14 11:45</t>
         </is>
       </c>
       <c r="K70" s="2" t="n">
-        <v>1194.9</v>
+        <v>418.15</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>2.42</v>
+        <v>1.95</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
@@ -5337,28 +5529,28 @@
     <row r="71" ht="18" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>857</v>
+        <v>373.3</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>846.1</v>
+        <v>373</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>861.85</v>
+        <v>375.4</v>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>1.83% (15.75)</t>
+          <t>0.64% (2.4)</t>
         </is>
       </c>
       <c r="F71" s="4" t="n">
-        <v>877.6</v>
+        <v>377.8</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>893.35</v>
+        <v>380.2</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -5367,19 +5559,19 @@
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 09:30</t>
+          <t>2026-10-14 09:15</t>
         </is>
       </c>
       <c r="K71" s="2" t="n">
-        <v>877.6</v>
+        <v>380.2</v>
       </c>
       <c r="L71" s="4" t="n">
-        <v>1.83</v>
+        <v>1.28</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
@@ -5390,28 +5582,28 @@
     <row r="72" ht="18" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>1828</v>
+        <v>461</v>
       </c>
       <c r="C72" s="3" t="n">
-        <v>1818.5</v>
+        <v>457.5</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>1829.2</v>
+        <v>461.75</v>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>0.58% (10.7)</t>
+          <t>0.92% (4.25)</t>
         </is>
       </c>
       <c r="F72" s="4" t="n">
-        <v>1839.9</v>
+        <v>466</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>1850.6</v>
+        <v>470.25</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -5425,14 +5617,14 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 09:15</t>
+          <t>2026-10-14 09:30</t>
         </is>
       </c>
       <c r="K72" s="2" t="n">
-        <v>1850.6</v>
+        <v>470.25</v>
       </c>
       <c r="L72" s="4" t="n">
-        <v>1.17</v>
+        <v>1.84</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
@@ -5496,28 +5688,28 @@
     <row r="74" ht="18" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>461</v>
+        <v>1486.2</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>457.5</v>
+        <v>1443.3</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>461.75</v>
+        <v>1508</v>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>0.92% (4.25)</t>
+          <t>4.29% (64.7)</t>
         </is>
       </c>
       <c r="F74" s="4" t="n">
-        <v>466</v>
+        <v>1572.7</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>470.25</v>
+        <v>1637.4</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -5531,14 +5723,14 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 09:30</t>
+          <t>2026-10-15 13:15</t>
         </is>
       </c>
       <c r="K74" s="2" t="n">
-        <v>470.25</v>
+        <v>1637.4</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>1.84</v>
+        <v>8.58</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
@@ -5549,28 +5741,28 @@
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>403.85</v>
+        <v>1828</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>402.15</v>
+        <v>1818.5</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>410.15</v>
+        <v>1829.2</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>1.95% (8.0)</t>
+          <t>0.58% (10.7)</t>
         </is>
       </c>
       <c r="F75" s="4" t="n">
-        <v>418.15</v>
+        <v>1839.9</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>426.15</v>
+        <v>1850.6</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -5579,19 +5771,19 @@
       </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 11:45</t>
+          <t>2026-10-14 09:15</t>
         </is>
       </c>
       <c r="K75" s="2" t="n">
-        <v>418.15</v>
+        <v>1850.6</v>
       </c>
       <c r="L75" s="4" t="n">
-        <v>1.95</v>
+        <v>1.17</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
@@ -5602,28 +5794,28 @@
     <row r="76" ht="18" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>1486.2</v>
+        <v>857</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>1443.3</v>
+        <v>846.1</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>1508</v>
+        <v>861.85</v>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>4.29% (64.7)</t>
+          <t>1.83% (15.75)</t>
         </is>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1572.7</v>
+        <v>877.6</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>1637.4</v>
+        <v>893.35</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -5632,19 +5824,19 @@
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 13:15</t>
+          <t>2026-10-14 09:30</t>
         </is>
       </c>
       <c r="K76" s="2" t="n">
-        <v>1637.4</v>
+        <v>877.6</v>
       </c>
       <c r="L76" s="4" t="n">
-        <v>8.58</v>
+        <v>1.83</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
@@ -5655,28 +5847,28 @@
     <row r="77" ht="18" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>373.3</v>
+        <v>1160.2</v>
       </c>
       <c r="C77" s="3" t="n">
-        <v>373</v>
+        <v>1152.6</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>375.4</v>
+        <v>1166.7</v>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>0.64% (2.4)</t>
+          <t>1.21% (14.1)</t>
         </is>
       </c>
       <c r="F77" s="4" t="n">
-        <v>377.8</v>
+        <v>1180.8</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>380.2</v>
+        <v>1194.9</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -5690,14 +5882,14 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 09:15</t>
+          <t>2026-10-15 10:00</t>
         </is>
       </c>
       <c r="K77" s="2" t="n">
-        <v>380.2</v>
+        <v>1194.9</v>
       </c>
       <c r="L77" s="4" t="n">
-        <v>1.28</v>
+        <v>2.42</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
@@ -5849,14 +6041,14 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 15:15 (Active)</t>
+          <t>2026-10-16 15:15 (Active)</t>
         </is>
       </c>
       <c r="K80" s="2" t="n">
-        <v>314.65</v>
+        <v>315.15</v>
       </c>
       <c r="L80" s="4" t="n">
-        <v>0.11</v>
+        <v>0.27</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
@@ -5895,7 +6087,7 @@
           <t>2026-10-14 13:45</t>
         </is>
       </c>
-      <c r="I81" s="7" t="inlineStr">
+      <c r="I81" s="8" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -5948,23 +6140,288 @@
           <t>2026-10-15 09:15</t>
         </is>
       </c>
-      <c r="I82" s="6" t="inlineStr">
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16 13:30</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>129.56</v>
+      </c>
+      <c r="L82" s="4" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>(12-10-2026 to 18-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="18" customHeight="1">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="n">
+        <v>886.5</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>860.1</v>
+      </c>
+      <c r="D83" s="4" t="n">
+        <v>887</v>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>3.03% (26.9)</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="n">
+        <v>913.9</v>
+      </c>
+      <c r="G83" s="4" t="n">
+        <v>940.8</v>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:15</t>
+        </is>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="n">
-        <v>128.83</v>
-      </c>
-      <c r="L82" s="4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="M82" s="2" t="inlineStr">
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>908</v>
+      </c>
+      <c r="L83" s="4" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>(12-10-2026 to 18-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="n">
+        <v>3607</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>3593.2</v>
+      </c>
+      <c r="D84" s="4" t="n">
+        <v>3627.5</v>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>0.95% (34.3)</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="n">
+        <v>3661.8</v>
+      </c>
+      <c r="G84" s="4" t="n">
+        <v>3696.1</v>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:15</t>
+        </is>
+      </c>
+      <c r="I84" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16 11:30</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>3661.8</v>
+      </c>
+      <c r="L84" s="4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>(12-10-2026 to 18-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="18" customHeight="1">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="n">
+        <v>166.3</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>165.87</v>
+      </c>
+      <c r="D85" s="4" t="n">
+        <v>166.83</v>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>0.58% (0.96)</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="n">
+        <v>167.79</v>
+      </c>
+      <c r="G85" s="4" t="n">
+        <v>168.75</v>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:15</t>
+        </is>
+      </c>
+      <c r="I85" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:15</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>168.75</v>
+      </c>
+      <c r="L85" s="4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>(12-10-2026 to 18-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="n">
+        <v>11225</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>11130</v>
+      </c>
+      <c r="D86" s="4" t="n">
+        <v>11325</v>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>1.72% (195.0)</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="n">
+        <v>11520</v>
+      </c>
+      <c r="G86" s="4" t="n">
+        <v>11715</v>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:15</t>
+        </is>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="n">
+        <v>11489</v>
+      </c>
+      <c r="L86" s="4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>(12-10-2026 to 18-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="18" customHeight="1">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="n">
+        <v>2559.6</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>2550</v>
+      </c>
+      <c r="D87" s="4" t="n">
+        <v>2593</v>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>1.66% (43.0)</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="n">
+        <v>2636</v>
+      </c>
+      <c r="G87" s="4" t="n">
+        <v>2679</v>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:15</t>
+        </is>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="n">
+        <v>2598.3</v>
+      </c>
+      <c r="L87" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
         <is>
           <t>(12-10-2026 to 18-10-2026)</t>
         </is>

--- a/data/trade_tracker_results.xlsx
+++ b/data/trade_tracker_results.xlsx
@@ -74,6 +74,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
@@ -82,12 +88,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFEB9C"/>
         <bgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-        <bgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -129,13 +129,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -506,19 +506,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="33" customWidth="1" min="9" max="9"/>
-    <col width="27" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
   </cols>
@@ -588,220 +588,212 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1124.6</v>
+        <v>7688</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1123.1</v>
+        <v>7677</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>1131.1</v>
+        <v>7729</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>0.71% (8.0)</t>
+          <t>0.67% (52.0)</t>
         </is>
       </c>
       <c r="F2" s="4" t="n">
-        <v>1139.1</v>
+        <v>7781</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>1147.1</v>
+        <v>7833</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 09:15</t>
-        </is>
-      </c>
-      <c r="I2" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 10:15</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>1147.1</v>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="4" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>403.85</v>
+        <v>2317.8</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>402.15</v>
+        <v>2310</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>410.15</v>
+        <v>2324.2</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>1.95% (8.0)</t>
+          <t>0.61% (14.2)</t>
         </is>
       </c>
       <c r="F3" s="4" t="n">
-        <v>418.15</v>
+        <v>2338.4</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>426.15</v>
+        <v>2352.6</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 09:15</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 11:45</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>418.15</v>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>373.3</v>
+        <v>426.15</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>373</v>
+        <v>425.6</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>375.4</v>
+        <v>432.8</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>0.64% (2.4)</t>
+          <t>1.66% (7.2)</t>
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>377.8</v>
+        <v>440</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>380.2</v>
+        <v>447.2</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 09:15</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 09:15</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>380.2</v>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="4" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>709.75</v>
+        <v>4591.2</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>708.8</v>
+        <v>4587</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>711.4</v>
+        <v>4610</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>0.37% (2.6)</t>
+          <t>0.5% (23.0)</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>714</v>
+        <v>4633</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>716.6</v>
+        <v>4656</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 09:15</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 09:45</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>716.6</v>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="4" t="n">
-        <v>0.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>ICICIPRULI</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>4782.2</v>
+        <v>435.2</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4679.7</v>
+        <v>435.05</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>4827.8</v>
+        <v>438.35</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>3.07% (148.1)</t>
+          <t>0.75% (3.3)</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>4975.9</v>
+        <v>441.65</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>5124</v>
+        <v>444.95</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -826,1086 +818,46 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>308.45</v>
+        <v>4550.4</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>305.85</v>
+        <v>4533.8</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>314.3</v>
+        <v>4551.2</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>2.69% (8.45)</t>
+          <t>0.38% (17.4)</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>322.75</v>
+        <v>4568.6</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>331.2</v>
+        <v>4586</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 11:30</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>315.15</v>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="4" t="n">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>OIL</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>441.05</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>440.55</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>445.8</v>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>1.18% (5.25)</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>451.05</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>456.3</v>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14 09:15</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14 11:00</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>451.05</v>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v>1.18</v>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>SBILIFE</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>1658.1</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>1634.8</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>1666.2</v>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>1.88% (31.4)</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>1697.6</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>1729</v>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>ADANIPOWER</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>184.05</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>182.87</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>187.05</v>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>2.23% (4.18)</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>191.23</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>195.41</v>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14 09:45</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14 14:15</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>195.41</v>
-      </c>
-      <c r="L10" s="4" t="n">
-        <v>4.47</v>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CGPOWER</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>840.15</v>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>808.75</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>861.95</v>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>6.17% (53.2)</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>915.15</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>968.35</v>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>GAIL</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>166.3</v>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>165.87</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>166.83</v>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>0.58% (0.96)</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>167.79</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>168.75</v>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16 09:15</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16 09:15</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>168.75</v>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v>1.15</v>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>HINDALCO</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>886.5</v>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>860.1</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>887</v>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>3.03% (26.9)</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>913.9</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>940.8</v>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16 09:15</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>908</v>
-      </c>
-      <c r="L13" s="4" t="n">
-        <v>2.37</v>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>HINDUNILVR</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>1828</v>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>1818.5</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>1829.2</v>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>0.58% (10.7)</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>1839.9</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>1850.6</v>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14 09:15</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14 09:15</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>1850.6</v>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v>1.17</v>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>INDUSINDBK</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>857</v>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>846.1</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>861.85</v>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>1.83% (15.75)</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>877.6</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>893.35</v>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14 09:15</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14 09:30</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>877.6</v>
-      </c>
-      <c r="L15" s="4" t="n">
-        <v>1.83</v>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>IOC</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>125.27</v>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>125</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>127.28</v>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>1.79% (2.28)</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>129.56</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>131.84</v>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15 09:15</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16 13:30</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="n">
-        <v>129.56</v>
-      </c>
-      <c r="L16" s="4" t="n">
-        <v>1.79</v>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>LT</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>3607</v>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>3593.2</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>3627.5</v>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>0.95% (34.3)</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>3661.8</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>3696.1</v>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16 09:15</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16 11:30</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="n">
-        <v>3661.8</v>
-      </c>
-      <c r="L17" s="4" t="n">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>MARUTI</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>11225</v>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>11130</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>11325</v>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>1.72% (195.0)</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>11520</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>11715</v>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16 09:15</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="n">
-        <v>11489</v>
-      </c>
-      <c r="L18" s="4" t="n">
-        <v>1.45</v>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>RELIANCE</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>1160.2</v>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>1152.6</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>1166.7</v>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>1.21% (14.1)</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>1180.8</v>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>1194.9</v>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14 09:15</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15 10:00</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="n">
-        <v>1194.9</v>
-      </c>
-      <c r="L19" s="4" t="n">
-        <v>2.42</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>TECHM</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>1486.2</v>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>1443.3</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>1508</v>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>4.29% (64.7)</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>1572.7</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>1637.4</v>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14 09:15</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-15 13:15</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="n">
-        <v>1637.4</v>
-      </c>
-      <c r="L20" s="4" t="n">
-        <v>8.58</v>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>JSWENERGY</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>461</v>
-      </c>
-      <c r="C21" s="3" t="n">
-        <v>457.5</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>461.75</v>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>0.92% (4.25)</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>466</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>470.25</v>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14 09:15</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-14 09:30</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="n">
-        <v>470.25</v>
-      </c>
-      <c r="L21" s="4" t="n">
-        <v>1.84</v>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>SUNPHARMA</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>1745</v>
-      </c>
-      <c r="C22" s="3" t="n">
-        <v>1725.5</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>1751.3</v>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>1.47% (25.8)</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="n">
-        <v>1777.1</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>1802.9</v>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>ICICIPRULI</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>446.05</v>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>435.65</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>449.1</v>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>2.99% (13.45)</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="n">
-        <v>462.55</v>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>476</v>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>LODHA</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>1051.2</v>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>1038.1</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>1064.7</v>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>2.5% (26.6)</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="n">
-        <v>1091.3</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>1117.9</v>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>MUTHOOTFIN</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>2559.6</v>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>2550</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>2593</v>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>1.66% (43.0)</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="n">
-        <v>2636</v>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>2679</v>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16 09:15</t>
-        </is>
-      </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="n">
-        <v>2598.3</v>
-      </c>
-      <c r="L25" s="4" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>BANKBARODA</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>230.18</v>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>225.22</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>233.78</v>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>3.66% (8.56)</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="n">
-        <v>242.34</v>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>250.9</v>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>DIVISLAB</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>9113.5</v>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>8937.5</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>9170.5</v>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>2.54% (233.0)</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="n">
-        <v>9403.5</v>
-      </c>
-      <c r="G27" s="4" t="n">
-        <v>9636.5</v>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>GRASIM</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>2853.5</v>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>2843.4</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>2894.1</v>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>1.75% (50.7)</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="n">
-        <v>2944.8</v>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v>2995.5</v>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>VBL</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>426.3</v>
-      </c>
-      <c r="C29" s="3" t="n">
-        <v>424.05</v>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>431.1</v>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>1.64% (7.05)</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="n">
-        <v>438.15</v>
-      </c>
-      <c r="G29" s="4" t="n">
-        <v>445.2</v>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1931,7 +883,7 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="33" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
     <col width="29" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
@@ -2006,23 +958,23 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Week Range: (21-09-2026 to 27-09-2026)</t>
         </is>
       </c>
-      <c r="B2" s="7" t="n"/>
-      <c r="C2" s="7" t="n"/>
-      <c r="D2" s="7" t="n"/>
-      <c r="E2" s="7" t="n"/>
-      <c r="F2" s="7" t="n"/>
-      <c r="G2" s="7" t="n"/>
-      <c r="H2" s="7" t="n"/>
-      <c r="I2" s="7" t="n"/>
-      <c r="J2" s="7" t="n"/>
-      <c r="K2" s="7" t="n"/>
-      <c r="L2" s="7" t="n"/>
-      <c r="M2" s="7" t="n"/>
+      <c r="B2" s="5" t="n"/>
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="5" t="n"/>
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="n"/>
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="5" t="n"/>
+      <c r="L2" s="5" t="n"/>
+      <c r="M2" s="5" t="n"/>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -2055,7 +1007,7 @@
           <t>2026-09-23 09:15</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -2108,7 +1060,7 @@
           <t>2026-09-23 11:00</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2161,7 +1113,7 @@
           <t>2026-09-23 14:15</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2214,7 +1166,7 @@
           <t>2026-09-24 09:30</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2267,7 +1219,7 @@
           <t>2026-09-24 10:00</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2320,7 +1272,7 @@
           <t>2026-09-24 10:00</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2373,7 +1325,7 @@
           <t>2026-09-24 12:30</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2426,7 +1378,7 @@
           <t>2026-09-25 10:00</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -2451,35 +1403,35 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>1927</v>
+        <v>1242.8</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1915.1</v>
+        <v>1202.6</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1935.1</v>
+        <v>1246</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>1.03% (20.0)</t>
+          <t>3.48% (43.4)</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1955.1</v>
+        <v>1289.4</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1975.1</v>
+        <v>1332.8</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
           <t>2026-09-25 14:00</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2490,10 +1442,10 @@
         </is>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1942.9</v>
+        <v>1254.8</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.4</v>
+        <v>0.71</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
@@ -2504,35 +1456,35 @@
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>1242.8</v>
+        <v>1927</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1202.6</v>
+        <v>1915.1</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1246</v>
+        <v>1935.1</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>3.48% (43.4)</t>
+          <t>1.03% (20.0)</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1289.4</v>
+        <v>1955.1</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1332.8</v>
+        <v>1975.1</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2026-09-25 14:00</t>
         </is>
       </c>
-      <c r="I12" s="6" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2543,10 +1495,10 @@
         </is>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1254.8</v>
+        <v>1942.9</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.71</v>
+        <v>0.4</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
@@ -2585,7 +1537,7 @@
           <t>2026-09-25 14:15</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2638,7 +1590,7 @@
           <t>2026-09-25 14:15</t>
         </is>
       </c>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2661,23 +1613,23 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Week Range: (28-09-2026 to 04-10-2026)</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="n"/>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="7" t="n"/>
-      <c r="I15" s="7" t="n"/>
-      <c r="J15" s="7" t="n"/>
-      <c r="K15" s="7" t="n"/>
-      <c r="L15" s="7" t="n"/>
-      <c r="M15" s="7" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -2763,7 +1715,7 @@
           <t>2026-09-28 11:30</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -2816,7 +1768,7 @@
           <t>2026-09-28 12:00</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
@@ -2869,7 +1821,7 @@
           <t>2026-09-28 13:15</t>
         </is>
       </c>
-      <c r="I19" s="6" t="inlineStr">
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2975,7 +1927,7 @@
           <t>2026-09-28 14:00</t>
         </is>
       </c>
-      <c r="I21" s="6" t="inlineStr">
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3000,49 +1952,49 @@
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>906.9</v>
+        <v>171.35</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>889.7</v>
+        <v>171.05</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>907.5</v>
+        <v>172.2</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>1.96% (17.8)</t>
+          <t>0.67% (1.15)</t>
         </is>
       </c>
       <c r="F22" s="4" t="n">
-        <v>925.3</v>
+        <v>173.35</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>943.1</v>
+        <v>174.5</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t>2026-09-28 15:15</t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:15</t>
+          <t>2026-09-28 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K22" s="2" t="n">
-        <v>889.7</v>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v>-1.96</v>
+        <v>172.45</v>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>0.15</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
@@ -3053,49 +2005,49 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>171.35</v>
+        <v>906.9</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>171.05</v>
+        <v>889.7</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>172.2</v>
+        <v>907.5</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>0.67% (1.15)</t>
+          <t>1.96% (17.8)</t>
         </is>
       </c>
       <c r="F23" s="4" t="n">
-        <v>173.35</v>
+        <v>925.3</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>174.5</v>
+        <v>943.1</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
           <t>2026-09-28 15:15</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 15:15 (Week End)</t>
+          <t>2026-09-29 10:15</t>
         </is>
       </c>
       <c r="K23" s="2" t="n">
-        <v>172.45</v>
-      </c>
-      <c r="L23" s="4" t="n">
-        <v>0.15</v>
+        <v>889.7</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>-1.96</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
@@ -3134,7 +2086,7 @@
           <t>2026-09-29 09:15</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="I24" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
@@ -3293,7 +2245,7 @@
           <t>2026-09-29 09:30</t>
         </is>
       </c>
-      <c r="I27" s="6" t="inlineStr">
+      <c r="I27" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3346,7 +2298,7 @@
           <t>2026-09-29 11:00</t>
         </is>
       </c>
-      <c r="I28" s="6" t="inlineStr">
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3399,7 +2351,7 @@
           <t>2026-09-29 11:15</t>
         </is>
       </c>
-      <c r="I29" s="6" t="inlineStr">
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3424,49 +2376,49 @@
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>399.3</v>
+        <v>1495.7</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>394.7</v>
+        <v>1487.1</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>403.65</v>
+        <v>1498</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>2.22% (8.95)</t>
+          <t>0.73% (10.9)</t>
         </is>
       </c>
       <c r="F30" s="4" t="n">
-        <v>412.6</v>
+        <v>1508.9</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>421.55</v>
+        <v>1519.8</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 11:30</t>
         </is>
       </c>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I30" s="8" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:15 (Week End)</t>
+          <t>2026-09-29 12:30</t>
         </is>
       </c>
       <c r="K30" s="2" t="n">
-        <v>406</v>
-      </c>
-      <c r="L30" s="4" t="n">
-        <v>0.58</v>
+        <v>1487.1</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>-0.73</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
@@ -3477,49 +2429,49 @@
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>1495.7</v>
+        <v>399.3</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1487.1</v>
+        <v>394.7</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1498</v>
+        <v>403.65</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>0.73% (10.9)</t>
+          <t>2.22% (8.95)</t>
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1508.9</v>
+        <v>412.6</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1519.8</v>
+        <v>421.55</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 11:30</t>
         </is>
       </c>
-      <c r="I31" s="8" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:30</t>
+          <t>2026-09-29 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K31" s="2" t="n">
-        <v>1487.1</v>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>-0.73</v>
+        <v>406</v>
+      </c>
+      <c r="L31" s="4" t="n">
+        <v>0.58</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
@@ -3558,7 +2510,7 @@
           <t>2026-09-29 11:45</t>
         </is>
       </c>
-      <c r="I32" s="6" t="inlineStr">
+      <c r="I32" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3611,7 +2563,7 @@
           <t>2026-09-29 12:00</t>
         </is>
       </c>
-      <c r="I33" s="6" t="inlineStr">
+      <c r="I33" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3664,7 +2616,7 @@
           <t>2026-09-29 13:00</t>
         </is>
       </c>
-      <c r="I34" s="6" t="inlineStr">
+      <c r="I34" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3717,7 +2669,7 @@
           <t>2026-09-29 14:00</t>
         </is>
       </c>
-      <c r="I35" s="6" t="inlineStr">
+      <c r="I35" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3770,7 +2722,7 @@
           <t>2026-09-29 14:00</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="I36" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -3823,7 +2775,7 @@
           <t>2026-09-29 14:45</t>
         </is>
       </c>
-      <c r="I37" s="6" t="inlineStr">
+      <c r="I37" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3929,7 +2881,7 @@
           <t>2026-09-29 15:00</t>
         </is>
       </c>
-      <c r="I39" s="6" t="inlineStr">
+      <c r="I39" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3954,28 +2906,28 @@
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>160.5</v>
+        <v>4057</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>159.41</v>
+        <v>4043.3</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>162.37</v>
+        <v>4095</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>1.82% (2.96)</t>
+          <t>1.26% (51.7)</t>
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>165.33</v>
+        <v>4146.7</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>168.29</v>
+        <v>4198.4</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -3984,19 +2936,19 @@
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>ACTIVE (Week End)</t>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 15:15 (Week End)</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="K40" s="2" t="n">
-        <v>163.26</v>
-      </c>
-      <c r="L40" s="4" t="n">
-        <v>0.55</v>
+        <v>4043.3</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>-1.26</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
@@ -4007,49 +2959,49 @@
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>2391</v>
+        <v>263.55</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>2381.6</v>
+        <v>263.3</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>2420</v>
+        <v>266.2</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>1.59% (38.4)</t>
+          <t>1.09% (2.9)</t>
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>2458.4</v>
+        <v>269.1</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>2496.8</v>
+        <v>272</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I41" s="8" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:30 (Week End)</t>
+          <t>2026-09-30 14:15</t>
         </is>
       </c>
       <c r="K41" s="2" t="n">
-        <v>2409.1</v>
+        <v>263.3</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-0.45</v>
+        <v>-1.09</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
@@ -4060,49 +3012,49 @@
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>1766.7</v>
+        <v>196.1</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>1736.8</v>
+        <v>192.45</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>1770.1</v>
+        <v>196.67</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>1.88% (33.3)</t>
+          <t>2.15% (4.22)</t>
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>1803.4</v>
+        <v>200.89</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>1836.7</v>
+        <v>205.11</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I42" s="6" t="inlineStr">
+      <c r="I42" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 15:15 (Week End)</t>
+          <t>2026-09-30 09:15</t>
         </is>
       </c>
       <c r="K42" s="2" t="n">
-        <v>1798.3</v>
+        <v>200.89</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>1.59</v>
+        <v>2.15</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
@@ -4113,49 +3065,49 @@
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>991.6</v>
+        <v>4848.5</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>980.4</v>
+        <v>4837</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>992.7</v>
+        <v>4872</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>1.24% (12.3)</t>
+          <t>0.72% (35.0)</t>
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>1005</v>
+        <v>4907</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>1017.3</v>
+        <v>4942</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-30 10:30</t>
         </is>
       </c>
       <c r="K43" s="2" t="n">
-        <v>1017.3</v>
-      </c>
-      <c r="L43" s="4" t="n">
-        <v>2.48</v>
+        <v>4837</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>-0.72</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
@@ -4194,7 +3146,7 @@
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I44" s="5" t="inlineStr">
+      <c r="I44" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -4219,49 +3171,49 @@
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>4848.5</v>
+        <v>991.6</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>4837</v>
+        <v>980.4</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>4872</v>
+        <v>992.7</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>0.72% (35.0)</t>
+          <t>1.24% (12.3)</t>
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>4907</v>
+        <v>1005</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>4942</v>
+        <v>1017.3</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 10:30</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
       <c r="K45" s="2" t="n">
-        <v>4837</v>
-      </c>
-      <c r="L45" s="3" t="n">
-        <v>-0.72</v>
+        <v>1017.3</v>
+      </c>
+      <c r="L45" s="4" t="n">
+        <v>2.48</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
@@ -4272,49 +3224,49 @@
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>263.55</v>
+        <v>1766.7</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>263.3</v>
+        <v>1736.8</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>266.2</v>
+        <v>1770.1</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>1.09% (2.9)</t>
+          <t>1.88% (33.3)</t>
         </is>
       </c>
       <c r="F46" s="4" t="n">
-        <v>269.1</v>
+        <v>1803.4</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>272</v>
+        <v>1836.7</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I46" s="8" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:15</t>
+          <t>2026-09-30 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K46" s="2" t="n">
-        <v>263.3</v>
-      </c>
-      <c r="L46" s="3" t="n">
-        <v>-1.09</v>
+        <v>1798.3</v>
+      </c>
+      <c r="L46" s="4" t="n">
+        <v>1.59</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
@@ -4325,49 +3277,49 @@
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>4057</v>
+        <v>2391</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>4043.3</v>
+        <v>2381.6</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>4095</v>
+        <v>2420</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>1.26% (51.7)</t>
+          <t>1.59% (38.4)</t>
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>4146.7</v>
+        <v>2458.4</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>4198.4</v>
+        <v>2496.8</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I47" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 09:15</t>
+          <t>2026-09-30 12:30 (Week End)</t>
         </is>
       </c>
       <c r="K47" s="2" t="n">
-        <v>4043.3</v>
+        <v>2409.1</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>-1.26</v>
+        <v>-0.45</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
@@ -4378,49 +3330,49 @@
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>196.1</v>
+        <v>160.5</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>192.45</v>
+        <v>159.41</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>196.67</v>
+        <v>162.37</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>2.15% (4.22)</t>
+          <t>1.82% (2.96)</t>
         </is>
       </c>
       <c r="F48" s="4" t="n">
-        <v>200.89</v>
+        <v>165.33</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>205.11</v>
+        <v>168.29</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I48" s="6" t="inlineStr">
+      <c r="I48" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:15</t>
+          <t>2026-09-30 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K48" s="2" t="n">
-        <v>200.89</v>
+        <v>163.26</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>2.15</v>
+        <v>0.55</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
@@ -4459,7 +3411,7 @@
           <t>2026-10-01 09:15</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="I49" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -4512,7 +3464,7 @@
           <t>2026-10-01 09:15</t>
         </is>
       </c>
-      <c r="I50" s="6" t="inlineStr">
+      <c r="I50" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -4535,23 +3487,23 @@
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="7" t="inlineStr">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>Week Range: (05-10-2026 to 11-10-2026)</t>
         </is>
       </c>
-      <c r="B51" s="7" t="n"/>
-      <c r="C51" s="7" t="n"/>
-      <c r="D51" s="7" t="n"/>
-      <c r="E51" s="7" t="n"/>
-      <c r="F51" s="7" t="n"/>
-      <c r="G51" s="7" t="n"/>
-      <c r="H51" s="7" t="n"/>
-      <c r="I51" s="7" t="n"/>
-      <c r="J51" s="7" t="n"/>
-      <c r="K51" s="7" t="n"/>
-      <c r="L51" s="7" t="n"/>
-      <c r="M51" s="7" t="n"/>
+      <c r="B51" s="5" t="n"/>
+      <c r="C51" s="5" t="n"/>
+      <c r="D51" s="5" t="n"/>
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" s="5" t="n"/>
+      <c r="G51" s="5" t="n"/>
+      <c r="H51" s="5" t="n"/>
+      <c r="I51" s="5" t="n"/>
+      <c r="J51" s="5" t="n"/>
+      <c r="K51" s="5" t="n"/>
+      <c r="L51" s="5" t="n"/>
+      <c r="M51" s="5" t="n"/>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
@@ -4584,7 +3536,7 @@
           <t>2026-10-06 09:15</t>
         </is>
       </c>
-      <c r="I52" s="5" t="inlineStr">
+      <c r="I52" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -4637,7 +3589,7 @@
           <t>2026-10-06 09:15</t>
         </is>
       </c>
-      <c r="I53" s="6" t="inlineStr">
+      <c r="I53" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -4690,7 +3642,7 @@
           <t>2026-10-06 09:15</t>
         </is>
       </c>
-      <c r="I54" s="6" t="inlineStr">
+      <c r="I54" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -4743,7 +3695,7 @@
           <t>2026-10-06 09:15</t>
         </is>
       </c>
-      <c r="I55" s="6" t="inlineStr">
+      <c r="I55" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -4768,35 +3720,35 @@
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>3709.5</v>
+        <v>1295</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>3695</v>
+        <v>1293</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>3723.8</v>
+        <v>1299.4</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>0.77% (28.8)</t>
+          <t>0.49% (6.4)</t>
         </is>
       </c>
       <c r="F56" s="4" t="n">
-        <v>3752.6</v>
+        <v>1305.8</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>3781.4</v>
+        <v>1312.2</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
           <t>2026-10-07 09:15</t>
         </is>
       </c>
-      <c r="I56" s="5" t="inlineStr">
+      <c r="I56" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -4807,10 +3759,10 @@
         </is>
       </c>
       <c r="K56" s="2" t="n">
-        <v>3781.4</v>
+        <v>1312.2</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>1.55</v>
+        <v>0.99</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
@@ -4821,28 +3773,28 @@
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>168.43</v>
+        <v>3709.5</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>166.48</v>
+        <v>3695</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>168.99</v>
+        <v>3723.8</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>1.49% (2.51)</t>
+          <t>0.77% (28.8)</t>
         </is>
       </c>
       <c r="F57" s="4" t="n">
-        <v>171.5</v>
+        <v>3752.6</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>174.01</v>
+        <v>3781.4</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -4851,19 +3803,19 @@
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
-          <t>ACTIVE (Week End)</t>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 15:15 (Week End)</t>
+          <t>2026-10-07 09:15</t>
         </is>
       </c>
       <c r="K57" s="2" t="n">
-        <v>170.71</v>
+        <v>3781.4</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
@@ -4874,49 +3826,49 @@
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>1295</v>
+        <v>168.43</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>1293</v>
+        <v>166.48</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>1299.4</v>
+        <v>168.99</v>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>0.49% (6.4)</t>
+          <t>1.49% (2.51)</t>
         </is>
       </c>
       <c r="F58" s="4" t="n">
-        <v>1305.8</v>
+        <v>171.5</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>1312.2</v>
+        <v>174.01</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
           <t>2026-10-07 09:15</t>
         </is>
       </c>
-      <c r="I58" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I58" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 09:15</t>
+          <t>2026-10-07 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K58" s="2" t="n">
-        <v>1312.2</v>
+        <v>170.71</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>0.99</v>
+        <v>1.02</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
@@ -4980,49 +3932,49 @@
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>254.65</v>
+        <v>1674.8</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>253.2</v>
+        <v>1658.6</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>255.4</v>
+        <v>1684.2</v>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>0.86% (2.2)</t>
+          <t>1.52% (25.6)</t>
         </is>
       </c>
       <c r="F60" s="4" t="n">
-        <v>257.6</v>
+        <v>1709.8</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>259.8</v>
+        <v>1735.4</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I60" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I60" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 10:00</t>
+          <t>2026-10-09 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K60" s="2" t="n">
-        <v>259.8</v>
-      </c>
-      <c r="L60" s="4" t="n">
-        <v>1.72</v>
+        <v>1682</v>
+      </c>
+      <c r="L60" s="3" t="n">
+        <v>-0.13</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
@@ -5033,49 +3985,49 @@
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>902.05</v>
+        <v>254.65</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>891.8</v>
+        <v>253.2</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>903</v>
+        <v>255.4</v>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>1.24% (11.2)</t>
+          <t>0.86% (2.2)</t>
         </is>
       </c>
       <c r="F61" s="4" t="n">
-        <v>914.2</v>
+        <v>257.6</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>925.4</v>
+        <v>259.8</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I61" s="8" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 09:15</t>
+          <t>2026-10-09 10:00</t>
         </is>
       </c>
       <c r="K61" s="2" t="n">
-        <v>891.8</v>
-      </c>
-      <c r="L61" s="3" t="n">
-        <v>-1.24</v>
+        <v>259.8</v>
+      </c>
+      <c r="L61" s="4" t="n">
+        <v>1.72</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
@@ -5086,49 +4038,49 @@
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>1702.1</v>
+        <v>902.05</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>1701</v>
+        <v>891.8</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>1710.1</v>
+        <v>903</v>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>0.53% (9.1)</t>
+          <t>1.24% (11.2)</t>
         </is>
       </c>
       <c r="F62" s="4" t="n">
-        <v>1719.2</v>
+        <v>914.2</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>1728.3</v>
+        <v>925.4</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I62" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I62" s="8" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 09:45</t>
+          <t>2026-10-09 09:15</t>
         </is>
       </c>
       <c r="K62" s="2" t="n">
-        <v>1728.3</v>
-      </c>
-      <c r="L62" s="4" t="n">
-        <v>1.06</v>
+        <v>891.8</v>
+      </c>
+      <c r="L62" s="3" t="n">
+        <v>-1.24</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
@@ -5139,49 +4091,49 @@
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>1316.5</v>
+        <v>1702.1</v>
       </c>
       <c r="C63" s="3" t="n">
-        <v>1308.7</v>
+        <v>1701</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>1323.7</v>
+        <v>1710.1</v>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>1.13% (15.0)</t>
+          <t>0.53% (9.1)</t>
         </is>
       </c>
       <c r="F63" s="4" t="n">
-        <v>1338.7</v>
+        <v>1719.2</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>1353.7</v>
+        <v>1728.3</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I63" s="5" t="inlineStr">
+      <c r="I63" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 10:15</t>
+          <t>2026-10-09 09:45</t>
         </is>
       </c>
       <c r="K63" s="2" t="n">
-        <v>1353.7</v>
+        <v>1728.3</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>2.27</v>
+        <v>1.06</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
@@ -5192,49 +4144,49 @@
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>LTM</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>3936</v>
+        <v>1316.5</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>3908.4</v>
+        <v>1308.7</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>3941.6</v>
+        <v>1323.7</v>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>0.84% (33.2)</t>
+          <t>1.13% (15.0)</t>
         </is>
       </c>
       <c r="F64" s="4" t="n">
-        <v>3974.8</v>
+        <v>1338.7</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>4008</v>
+        <v>1353.7</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I64" s="5" t="inlineStr">
+      <c r="I64" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 09:15</t>
+          <t>2026-10-09 10:15</t>
         </is>
       </c>
       <c r="K64" s="2" t="n">
-        <v>4008</v>
+        <v>1353.7</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>1.68</v>
+        <v>2.27</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
@@ -5245,28 +4197,28 @@
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>LTM</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>1674.8</v>
+        <v>3936</v>
       </c>
       <c r="C65" s="3" t="n">
-        <v>1658.6</v>
+        <v>3908.4</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>1684.2</v>
+        <v>3941.6</v>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>1.52% (25.6)</t>
+          <t>0.84% (33.2)</t>
         </is>
       </c>
       <c r="F65" s="4" t="n">
-        <v>1709.8</v>
+        <v>3974.8</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>1735.4</v>
+        <v>4008</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -5275,19 +4227,19 @@
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
-          <t>ACTIVE (Week End)</t>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 15:15 (Week End)</t>
+          <t>2026-10-09 09:15</t>
         </is>
       </c>
       <c r="K65" s="2" t="n">
-        <v>1682</v>
-      </c>
-      <c r="L65" s="3" t="n">
-        <v>-0.13</v>
+        <v>4008</v>
+      </c>
+      <c r="L65" s="4" t="n">
+        <v>1.68</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
@@ -5296,70 +4248,70 @@
       </c>
     </row>
     <row r="66" ht="22" customHeight="1">
-      <c r="A66" s="7" t="inlineStr">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>Week Range: (12-10-2026 to 18-10-2026)</t>
         </is>
       </c>
-      <c r="B66" s="7" t="n"/>
-      <c r="C66" s="7" t="n"/>
-      <c r="D66" s="7" t="n"/>
-      <c r="E66" s="7" t="n"/>
-      <c r="F66" s="7" t="n"/>
-      <c r="G66" s="7" t="n"/>
-      <c r="H66" s="7" t="n"/>
-      <c r="I66" s="7" t="n"/>
-      <c r="J66" s="7" t="n"/>
-      <c r="K66" s="7" t="n"/>
-      <c r="L66" s="7" t="n"/>
-      <c r="M66" s="7" t="n"/>
+      <c r="B66" s="5" t="n"/>
+      <c r="C66" s="5" t="n"/>
+      <c r="D66" s="5" t="n"/>
+      <c r="E66" s="5" t="n"/>
+      <c r="F66" s="5" t="n"/>
+      <c r="G66" s="5" t="n"/>
+      <c r="H66" s="5" t="n"/>
+      <c r="I66" s="5" t="n"/>
+      <c r="J66" s="5" t="n"/>
+      <c r="K66" s="5" t="n"/>
+      <c r="L66" s="5" t="n"/>
+      <c r="M66" s="5" t="n"/>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>709.75</v>
+        <v>1658.1</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>708.8</v>
+        <v>1658</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>711.4</v>
+        <v>1673.9</v>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>0.37% (2.6)</t>
+          <t>0.95% (15.9)</t>
         </is>
       </c>
       <c r="F67" s="4" t="n">
-        <v>714</v>
+        <v>1689.8</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>716.6</v>
+        <v>1705.7</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
           <t>2026-10-13 09:15</t>
         </is>
       </c>
-      <c r="I67" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I67" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 09:45</t>
+          <t>2026-10-13 09:30</t>
         </is>
       </c>
       <c r="K67" s="2" t="n">
-        <v>716.6</v>
+        <v>1689.8</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>0.73</v>
+        <v>0.95</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
@@ -5370,49 +4322,49 @@
     <row r="68" ht="18" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>1124.6</v>
+        <v>709.75</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>1123.1</v>
+        <v>708.8</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>1131.1</v>
+        <v>711.4</v>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>0.71% (8.0)</t>
+          <t>0.37% (2.6)</t>
         </is>
       </c>
       <c r="F68" s="4" t="n">
-        <v>1139.1</v>
+        <v>714</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>1147.1</v>
+        <v>716.6</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
           <t>2026-10-13 09:15</t>
         </is>
       </c>
-      <c r="I68" s="5" t="inlineStr">
+      <c r="I68" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 10:15</t>
+          <t>2026-10-13 09:45</t>
         </is>
       </c>
       <c r="K68" s="2" t="n">
-        <v>1147.1</v>
+        <v>716.6</v>
       </c>
       <c r="L68" s="4" t="n">
-        <v>1.41</v>
+        <v>0.73</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
@@ -5423,49 +4375,49 @@
     <row r="69" ht="18" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>1658.1</v>
+        <v>1124.6</v>
       </c>
       <c r="C69" s="3" t="n">
-        <v>1658</v>
+        <v>1123.1</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>1673.9</v>
+        <v>1131.1</v>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>0.95% (15.9)</t>
+          <t>0.71% (8.0)</t>
         </is>
       </c>
       <c r="F69" s="4" t="n">
-        <v>1689.8</v>
+        <v>1139.1</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>1705.7</v>
+        <v>1147.1</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
           <t>2026-10-13 09:15</t>
         </is>
       </c>
-      <c r="I69" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 09:30</t>
+          <t>2026-10-15 10:15</t>
         </is>
       </c>
       <c r="K69" s="2" t="n">
-        <v>1689.8</v>
+        <v>1147.1</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>0.95</v>
+        <v>1.41</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
@@ -5504,9 +4456,9 @@
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I70" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+      <c r="I70" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -5557,7 +4509,7 @@
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I71" s="5" t="inlineStr">
+      <c r="I71" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -5610,7 +4562,7 @@
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I72" s="5" t="inlineStr">
+      <c r="I72" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -5663,9 +4615,9 @@
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I73" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+      <c r="I73" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -5716,7 +4668,7 @@
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I74" s="5" t="inlineStr">
+      <c r="I74" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -5769,7 +4721,7 @@
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I75" s="5" t="inlineStr">
+      <c r="I75" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -5822,9 +4774,9 @@
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I76" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+      <c r="I76" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -5875,7 +4827,7 @@
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I77" s="5" t="inlineStr">
+      <c r="I77" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -5928,14 +4880,14 @@
           <t>2026-10-14 09:30</t>
         </is>
       </c>
-      <c r="I78" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I78" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 15:15 (Active)</t>
+          <t>2026-10-14 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K78" s="2" t="n">
@@ -5981,7 +4933,7 @@
           <t>2026-10-14 09:45</t>
         </is>
       </c>
-      <c r="I79" s="5" t="inlineStr">
+      <c r="I79" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -6034,14 +4986,14 @@
           <t>2026-10-14 11:30</t>
         </is>
       </c>
-      <c r="I80" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I80" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 15:15 (Active)</t>
+          <t>2026-10-16 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K80" s="2" t="n">
@@ -6140,9 +5092,9 @@
           <t>2026-10-15 09:15</t>
         </is>
       </c>
-      <c r="I82" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+      <c r="I82" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -6165,28 +5117,28 @@
     <row r="83" ht="18" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>886.5</v>
+        <v>166.3</v>
       </c>
       <c r="C83" s="3" t="n">
-        <v>860.1</v>
+        <v>165.87</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>887</v>
+        <v>166.83</v>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>3.03% (26.9)</t>
+          <t>0.58% (0.96)</t>
         </is>
       </c>
       <c r="F83" s="4" t="n">
-        <v>913.9</v>
+        <v>167.79</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>940.8</v>
+        <v>168.75</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -6195,19 +5147,19 @@
       </c>
       <c r="I83" s="6" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 15:15 (Active)</t>
+          <t>2026-10-16 09:15</t>
         </is>
       </c>
       <c r="K83" s="2" t="n">
-        <v>908</v>
+        <v>168.75</v>
       </c>
       <c r="L83" s="4" t="n">
-        <v>2.37</v>
+        <v>1.15</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
@@ -6218,49 +5170,49 @@
     <row r="84" ht="18" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>3607</v>
+        <v>11225</v>
       </c>
       <c r="C84" s="3" t="n">
-        <v>3593.2</v>
+        <v>11130</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>3627.5</v>
+        <v>11325</v>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>0.95% (34.3)</t>
+          <t>1.72% (195.0)</t>
         </is>
       </c>
       <c r="F84" s="4" t="n">
-        <v>3661.8</v>
+        <v>11520</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>3696.1</v>
+        <v>11715</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
           <t>2026-10-16 09:15</t>
         </is>
       </c>
-      <c r="I84" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+      <c r="I84" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 11:30</t>
+          <t>2026-10-16 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K84" s="2" t="n">
-        <v>3661.8</v>
+        <v>11489</v>
       </c>
       <c r="L84" s="4" t="n">
-        <v>0.95</v>
+        <v>1.45</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
@@ -6271,49 +5223,49 @@
     <row r="85" ht="18" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>166.3</v>
+        <v>886.5</v>
       </c>
       <c r="C85" s="3" t="n">
-        <v>165.87</v>
+        <v>860.1</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>166.83</v>
+        <v>887</v>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>0.58% (0.96)</t>
+          <t>3.03% (26.9)</t>
         </is>
       </c>
       <c r="F85" s="4" t="n">
-        <v>167.79</v>
+        <v>913.9</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>168.75</v>
+        <v>940.8</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
           <t>2026-10-16 09:15</t>
         </is>
       </c>
-      <c r="I85" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I85" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 09:15</t>
+          <t>2026-10-16 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K85" s="2" t="n">
-        <v>168.75</v>
+        <v>908</v>
       </c>
       <c r="L85" s="4" t="n">
-        <v>1.15</v>
+        <v>2.37</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
@@ -6324,49 +5276,49 @@
     <row r="86" ht="18" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>11225</v>
+        <v>3607</v>
       </c>
       <c r="C86" s="3" t="n">
-        <v>11130</v>
+        <v>3593.2</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>11325</v>
+        <v>3627.5</v>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>1.72% (195.0)</t>
+          <t>0.95% (34.3)</t>
         </is>
       </c>
       <c r="F86" s="4" t="n">
-        <v>11520</v>
+        <v>3661.8</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>11715</v>
+        <v>3696.1</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
           <t>2026-10-16 09:15</t>
         </is>
       </c>
-      <c r="I86" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I86" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 15:15 (Active)</t>
+          <t>2026-10-16 11:30</t>
         </is>
       </c>
       <c r="K86" s="2" t="n">
-        <v>11489</v>
+        <v>3661.8</v>
       </c>
       <c r="L86" s="4" t="n">
-        <v>1.45</v>
+        <v>0.95</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
@@ -6405,14 +5357,14 @@
           <t>2026-10-16 09:15</t>
         </is>
       </c>
-      <c r="I87" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I87" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 15:15 (Active)</t>
+          <t>2026-10-16 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K87" s="2" t="n">

--- a/data/trade_tracker_results.xlsx
+++ b/data/trade_tracker_results.xlsx
@@ -1403,28 +1403,28 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>1242.8</v>
+        <v>1927</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1202.6</v>
+        <v>1915.1</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1246</v>
+        <v>1935.1</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>3.48% (43.4)</t>
+          <t>1.03% (20.0)</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1289.4</v>
+        <v>1955.1</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1332.8</v>
+        <v>1975.1</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1254.8</v>
+        <v>1942.9</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.71</v>
+        <v>0.4</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
@@ -1456,28 +1456,28 @@
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>1927</v>
+        <v>1242.8</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1915.1</v>
+        <v>1202.6</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1935.1</v>
+        <v>1246</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>1.03% (20.0)</t>
+          <t>3.48% (43.4)</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1955.1</v>
+        <v>1289.4</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1975.1</v>
+        <v>1332.8</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1942.9</v>
+        <v>1254.8</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.4</v>
+        <v>0.71</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
@@ -1952,49 +1952,49 @@
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>171.35</v>
+        <v>906.9</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>171.05</v>
+        <v>889.7</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>172.2</v>
+        <v>907.5</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>0.67% (1.15)</t>
+          <t>1.96% (17.8)</t>
         </is>
       </c>
       <c r="F22" s="4" t="n">
-        <v>173.35</v>
+        <v>925.3</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>174.5</v>
+        <v>943.1</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t>2026-09-28 15:15</t>
         </is>
       </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 15:15 (Week End)</t>
+          <t>2026-09-29 10:15</t>
         </is>
       </c>
       <c r="K22" s="2" t="n">
-        <v>172.45</v>
-      </c>
-      <c r="L22" s="4" t="n">
-        <v>0.15</v>
+        <v>889.7</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>-1.96</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
@@ -2005,49 +2005,49 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>906.9</v>
+        <v>171.35</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>889.7</v>
+        <v>171.05</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>907.5</v>
+        <v>172.2</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>1.96% (17.8)</t>
+          <t>0.67% (1.15)</t>
         </is>
       </c>
       <c r="F23" s="4" t="n">
-        <v>925.3</v>
+        <v>173.35</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>943.1</v>
+        <v>174.5</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
           <t>2026-09-28 15:15</t>
         </is>
       </c>
-      <c r="I23" s="8" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:15</t>
+          <t>2026-09-28 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K23" s="2" t="n">
-        <v>889.7</v>
-      </c>
-      <c r="L23" s="3" t="n">
-        <v>-1.96</v>
+        <v>172.45</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>0.15</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
@@ -2376,49 +2376,49 @@
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>1495.7</v>
+        <v>399.3</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1487.1</v>
+        <v>394.7</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1498</v>
+        <v>403.65</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>0.73% (10.9)</t>
+          <t>2.22% (8.95)</t>
         </is>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1508.9</v>
+        <v>412.6</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1519.8</v>
+        <v>421.55</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 11:30</t>
         </is>
       </c>
-      <c r="I30" s="8" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:30</t>
+          <t>2026-09-29 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K30" s="2" t="n">
-        <v>1487.1</v>
-      </c>
-      <c r="L30" s="3" t="n">
-        <v>-0.73</v>
+        <v>406</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>0.58</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
@@ -2429,49 +2429,49 @@
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>399.3</v>
+        <v>1495.7</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>394.7</v>
+        <v>1487.1</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>403.65</v>
+        <v>1498</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>2.22% (8.95)</t>
+          <t>0.73% (10.9)</t>
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>412.6</v>
+        <v>1508.9</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>421.55</v>
+        <v>1519.8</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 11:30</t>
         </is>
       </c>
-      <c r="I31" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I31" s="8" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:15 (Week End)</t>
+          <t>2026-09-29 12:30</t>
         </is>
       </c>
       <c r="K31" s="2" t="n">
-        <v>406</v>
-      </c>
-      <c r="L31" s="4" t="n">
-        <v>0.58</v>
+        <v>1487.1</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>-0.73</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
@@ -2906,49 +2906,49 @@
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>4057</v>
+        <v>2391</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>4043.3</v>
+        <v>2381.6</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>4095</v>
+        <v>2420</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>1.26% (51.7)</t>
+          <t>1.59% (38.4)</t>
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>4146.7</v>
+        <v>2458.4</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>4198.4</v>
+        <v>2496.8</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I40" s="6" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 09:15</t>
+          <t>2026-09-30 12:30 (Week End)</t>
         </is>
       </c>
       <c r="K40" s="2" t="n">
-        <v>4043.3</v>
+        <v>2409.1</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>-1.26</v>
+        <v>-0.45</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
@@ -2959,49 +2959,49 @@
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>263.55</v>
+        <v>1766.7</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>263.3</v>
+        <v>1736.8</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>266.2</v>
+        <v>1770.1</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>1.09% (2.9)</t>
+          <t>1.88% (33.3)</t>
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>269.1</v>
+        <v>1803.4</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>272</v>
+        <v>1836.7</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I41" s="8" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:15</t>
+          <t>2026-09-30 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K41" s="2" t="n">
-        <v>263.3</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>-1.09</v>
+        <v>1798.3</v>
+      </c>
+      <c r="L41" s="4" t="n">
+        <v>1.59</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
@@ -3012,28 +3012,28 @@
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>196.1</v>
+        <v>160.5</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>192.45</v>
+        <v>159.41</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>196.67</v>
+        <v>162.37</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>2.15% (4.22)</t>
+          <t>1.82% (2.96)</t>
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>200.89</v>
+        <v>165.33</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>205.11</v>
+        <v>168.29</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -3047,14 +3047,14 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:15</t>
+          <t>2026-09-30 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K42" s="2" t="n">
-        <v>200.89</v>
+        <v>163.26</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>2.15</v>
+        <v>0.55</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
@@ -3065,28 +3065,28 @@
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>4848.5</v>
+        <v>991.6</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>4837</v>
+        <v>980.4</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>4872</v>
+        <v>992.7</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>0.72% (35.0)</t>
+          <t>1.24% (12.3)</t>
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>4907</v>
+        <v>1005</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>4942</v>
+        <v>1017.3</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -3095,19 +3095,19 @@
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 10:30</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
       <c r="K43" s="2" t="n">
-        <v>4837</v>
-      </c>
-      <c r="L43" s="3" t="n">
-        <v>-0.72</v>
+        <v>1017.3</v>
+      </c>
+      <c r="L43" s="4" t="n">
+        <v>2.48</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
@@ -3171,28 +3171,28 @@
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>991.6</v>
+        <v>4848.5</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>980.4</v>
+        <v>4837</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>992.7</v>
+        <v>4872</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>1.24% (12.3)</t>
+          <t>0.72% (35.0)</t>
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>1005</v>
+        <v>4907</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>1017.3</v>
+        <v>4942</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -3201,19 +3201,19 @@
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-30 10:30</t>
         </is>
       </c>
       <c r="K45" s="2" t="n">
-        <v>1017.3</v>
-      </c>
-      <c r="L45" s="4" t="n">
-        <v>2.48</v>
+        <v>4837</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>-0.72</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
@@ -3224,28 +3224,28 @@
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>1766.7</v>
+        <v>196.1</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>1736.8</v>
+        <v>192.45</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>1770.1</v>
+        <v>196.67</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>1.88% (33.3)</t>
+          <t>2.15% (4.22)</t>
         </is>
       </c>
       <c r="F46" s="4" t="n">
-        <v>1803.4</v>
+        <v>200.89</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>1836.7</v>
+        <v>205.11</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -3259,14 +3259,14 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 15:15 (Week End)</t>
+          <t>2026-09-30 09:15</t>
         </is>
       </c>
       <c r="K46" s="2" t="n">
-        <v>1798.3</v>
+        <v>200.89</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>1.59</v>
+        <v>2.15</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
@@ -3277,49 +3277,49 @@
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>2391</v>
+        <v>263.55</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>2381.6</v>
+        <v>263.3</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>2420</v>
+        <v>266.2</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>1.59% (38.4)</t>
+          <t>1.09% (2.9)</t>
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>2458.4</v>
+        <v>269.1</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>2496.8</v>
+        <v>272</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I47" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I47" s="8" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:30 (Week End)</t>
+          <t>2026-09-30 14:15</t>
         </is>
       </c>
       <c r="K47" s="2" t="n">
-        <v>2409.1</v>
+        <v>263.3</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>-0.45</v>
+        <v>-1.09</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
@@ -3330,49 +3330,49 @@
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>160.5</v>
+        <v>4057</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>159.41</v>
+        <v>4043.3</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>162.37</v>
+        <v>4095</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>1.82% (2.96)</t>
+          <t>1.26% (51.7)</t>
         </is>
       </c>
       <c r="F48" s="4" t="n">
-        <v>165.33</v>
+        <v>4146.7</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>168.29</v>
+        <v>4198.4</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I48" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 15:15 (Week End)</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="K48" s="2" t="n">
-        <v>163.26</v>
-      </c>
-      <c r="L48" s="4" t="n">
-        <v>0.55</v>
+        <v>4043.3</v>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>-1.26</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
@@ -3720,49 +3720,49 @@
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>1295</v>
+        <v>168.43</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>1293</v>
+        <v>166.48</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>1299.4</v>
+        <v>168.99</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>0.49% (6.4)</t>
+          <t>1.49% (2.51)</t>
         </is>
       </c>
       <c r="F56" s="4" t="n">
-        <v>1305.8</v>
+        <v>171.5</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>1312.2</v>
+        <v>174.01</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
           <t>2026-10-07 09:15</t>
         </is>
       </c>
-      <c r="I56" s="6" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I56" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 09:15</t>
+          <t>2026-10-07 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K56" s="2" t="n">
-        <v>1312.2</v>
+        <v>170.71</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>0.99</v>
+        <v>1.02</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
@@ -3773,28 +3773,28 @@
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>3709.5</v>
+        <v>1295</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>3695</v>
+        <v>1293</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>3723.8</v>
+        <v>1299.4</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>0.77% (28.8)</t>
+          <t>0.49% (6.4)</t>
         </is>
       </c>
       <c r="F57" s="4" t="n">
-        <v>3752.6</v>
+        <v>1305.8</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>3781.4</v>
+        <v>1312.2</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3812,10 +3812,10 @@
         </is>
       </c>
       <c r="K57" s="2" t="n">
-        <v>3781.4</v>
+        <v>1312.2</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>1.55</v>
+        <v>0.99</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
@@ -3826,49 +3826,49 @@
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>168.43</v>
+        <v>3709.5</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>166.48</v>
+        <v>3695</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>168.99</v>
+        <v>3723.8</v>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>1.49% (2.51)</t>
+          <t>0.77% (28.8)</t>
         </is>
       </c>
       <c r="F58" s="4" t="n">
-        <v>171.5</v>
+        <v>3752.6</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>174.01</v>
+        <v>3781.4</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
           <t>2026-10-07 09:15</t>
         </is>
       </c>
-      <c r="I58" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 15:15 (Week End)</t>
+          <t>2026-10-07 09:15</t>
         </is>
       </c>
       <c r="K58" s="2" t="n">
-        <v>170.71</v>
+        <v>3781.4</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
@@ -3932,49 +3932,49 @@
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>LTM</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>1674.8</v>
+        <v>3936</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>1658.6</v>
+        <v>3908.4</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>1684.2</v>
+        <v>3941.6</v>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>1.52% (25.6)</t>
+          <t>0.84% (33.2)</t>
         </is>
       </c>
       <c r="F60" s="4" t="n">
-        <v>1709.8</v>
+        <v>3974.8</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>1735.4</v>
+        <v>4008</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I60" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 15:15 (Week End)</t>
+          <t>2026-10-09 09:15</t>
         </is>
       </c>
       <c r="K60" s="2" t="n">
-        <v>1682</v>
-      </c>
-      <c r="L60" s="3" t="n">
-        <v>-0.13</v>
+        <v>4008</v>
+      </c>
+      <c r="L60" s="4" t="n">
+        <v>1.68</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
@@ -3985,49 +3985,49 @@
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>254.65</v>
+        <v>1674.8</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>253.2</v>
+        <v>1658.6</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>255.4</v>
+        <v>1684.2</v>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>0.86% (2.2)</t>
+          <t>1.52% (25.6)</t>
         </is>
       </c>
       <c r="F61" s="4" t="n">
-        <v>257.6</v>
+        <v>1709.8</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>259.8</v>
+        <v>1735.4</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I61" s="6" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I61" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 10:00</t>
+          <t>2026-10-09 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K61" s="2" t="n">
-        <v>259.8</v>
-      </c>
-      <c r="L61" s="4" t="n">
-        <v>1.72</v>
+        <v>1682</v>
+      </c>
+      <c r="L61" s="3" t="n">
+        <v>-0.13</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
@@ -4038,49 +4038,49 @@
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>902.05</v>
+        <v>254.65</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>891.8</v>
+        <v>253.2</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>903</v>
+        <v>255.4</v>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>1.24% (11.2)</t>
+          <t>0.86% (2.2)</t>
         </is>
       </c>
       <c r="F62" s="4" t="n">
-        <v>914.2</v>
+        <v>257.6</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>925.4</v>
+        <v>259.8</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I62" s="8" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 09:15</t>
+          <t>2026-10-09 10:00</t>
         </is>
       </c>
       <c r="K62" s="2" t="n">
-        <v>891.8</v>
-      </c>
-      <c r="L62" s="3" t="n">
-        <v>-1.24</v>
+        <v>259.8</v>
+      </c>
+      <c r="L62" s="4" t="n">
+        <v>1.72</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
@@ -4091,49 +4091,49 @@
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>1702.1</v>
+        <v>902.05</v>
       </c>
       <c r="C63" s="3" t="n">
-        <v>1701</v>
+        <v>891.8</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>1710.1</v>
+        <v>903</v>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>0.53% (9.1)</t>
+          <t>1.24% (11.2)</t>
         </is>
       </c>
       <c r="F63" s="4" t="n">
-        <v>1719.2</v>
+        <v>914.2</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>1728.3</v>
+        <v>925.4</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I63" s="6" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I63" s="8" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 09:45</t>
+          <t>2026-10-09 09:15</t>
         </is>
       </c>
       <c r="K63" s="2" t="n">
-        <v>1728.3</v>
-      </c>
-      <c r="L63" s="4" t="n">
-        <v>1.06</v>
+        <v>891.8</v>
+      </c>
+      <c r="L63" s="3" t="n">
+        <v>-1.24</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
@@ -4144,28 +4144,28 @@
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>1316.5</v>
+        <v>1702.1</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1308.7</v>
+        <v>1701</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>1323.7</v>
+        <v>1710.1</v>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>1.13% (15.0)</t>
+          <t>0.53% (9.1)</t>
         </is>
       </c>
       <c r="F64" s="4" t="n">
-        <v>1338.7</v>
+        <v>1719.2</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>1353.7</v>
+        <v>1728.3</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -4179,14 +4179,14 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 10:15</t>
+          <t>2026-10-09 09:45</t>
         </is>
       </c>
       <c r="K64" s="2" t="n">
-        <v>1353.7</v>
+        <v>1728.3</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>2.27</v>
+        <v>1.06</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
@@ -4197,28 +4197,28 @@
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>LTM</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>3936</v>
+        <v>1316.5</v>
       </c>
       <c r="C65" s="3" t="n">
-        <v>3908.4</v>
+        <v>1308.7</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>3941.6</v>
+        <v>1323.7</v>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>0.84% (33.2)</t>
+          <t>1.13% (15.0)</t>
         </is>
       </c>
       <c r="F65" s="4" t="n">
-        <v>3974.8</v>
+        <v>1338.7</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>4008</v>
+        <v>1353.7</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -4232,14 +4232,14 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 09:15</t>
+          <t>2026-10-09 10:15</t>
         </is>
       </c>
       <c r="K65" s="2" t="n">
-        <v>4008</v>
+        <v>1353.7</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>1.68</v>
+        <v>2.27</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
@@ -4269,49 +4269,49 @@
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>1658.1</v>
+        <v>1124.6</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>1658</v>
+        <v>1123.1</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>1673.9</v>
+        <v>1131.1</v>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>0.95% (15.9)</t>
+          <t>0.71% (8.0)</t>
         </is>
       </c>
       <c r="F67" s="4" t="n">
-        <v>1689.8</v>
+        <v>1139.1</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>1705.7</v>
+        <v>1147.1</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
           <t>2026-10-13 09:15</t>
         </is>
       </c>
-      <c r="I67" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 09:30</t>
+          <t>2026-10-15 10:15</t>
         </is>
       </c>
       <c r="K67" s="2" t="n">
-        <v>1689.8</v>
+        <v>1147.1</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>0.95</v>
+        <v>1.41</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
@@ -4322,49 +4322,49 @@
     <row r="68" ht="18" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>709.75</v>
+        <v>1658.1</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>708.8</v>
+        <v>1658</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>711.4</v>
+        <v>1673.9</v>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>0.37% (2.6)</t>
+          <t>0.95% (15.9)</t>
         </is>
       </c>
       <c r="F68" s="4" t="n">
-        <v>714</v>
+        <v>1689.8</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>716.6</v>
+        <v>1705.7</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
           <t>2026-10-13 09:15</t>
         </is>
       </c>
-      <c r="I68" s="6" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I68" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 09:45</t>
+          <t>2026-10-13 09:30</t>
         </is>
       </c>
       <c r="K68" s="2" t="n">
-        <v>716.6</v>
+        <v>1689.8</v>
       </c>
       <c r="L68" s="4" t="n">
-        <v>0.73</v>
+        <v>0.95</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
@@ -4375,28 +4375,28 @@
     <row r="69" ht="18" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>1124.6</v>
+        <v>709.75</v>
       </c>
       <c r="C69" s="3" t="n">
-        <v>1123.1</v>
+        <v>708.8</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>1131.1</v>
+        <v>711.4</v>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>0.71% (8.0)</t>
+          <t>0.37% (2.6)</t>
         </is>
       </c>
       <c r="F69" s="4" t="n">
-        <v>1139.1</v>
+        <v>714</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>1147.1</v>
+        <v>716.6</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -4410,14 +4410,14 @@
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 10:15</t>
+          <t>2026-10-13 09:45</t>
         </is>
       </c>
       <c r="K69" s="2" t="n">
-        <v>1147.1</v>
+        <v>716.6</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>1.41</v>
+        <v>0.73</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
@@ -5117,49 +5117,49 @@
     <row r="83" ht="18" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>166.3</v>
+        <v>886.5</v>
       </c>
       <c r="C83" s="3" t="n">
-        <v>165.87</v>
+        <v>860.1</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>166.83</v>
+        <v>887</v>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>0.58% (0.96)</t>
+          <t>3.03% (26.9)</t>
         </is>
       </c>
       <c r="F83" s="4" t="n">
-        <v>167.79</v>
+        <v>913.9</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>168.75</v>
+        <v>940.8</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
           <t>2026-10-16 09:15</t>
         </is>
       </c>
-      <c r="I83" s="6" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I83" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 09:15</t>
+          <t>2026-10-16 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K83" s="2" t="n">
-        <v>168.75</v>
+        <v>908</v>
       </c>
       <c r="L83" s="4" t="n">
-        <v>1.15</v>
+        <v>2.37</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
@@ -5170,28 +5170,28 @@
     <row r="84" ht="18" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>11225</v>
+        <v>3607</v>
       </c>
       <c r="C84" s="3" t="n">
-        <v>11130</v>
+        <v>3593.2</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>11325</v>
+        <v>3627.5</v>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>1.72% (195.0)</t>
+          <t>0.95% (34.3)</t>
         </is>
       </c>
       <c r="F84" s="4" t="n">
-        <v>11520</v>
+        <v>3661.8</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>11715</v>
+        <v>3696.1</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -5205,14 +5205,14 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 15:15 (Week End)</t>
+          <t>2026-10-16 11:30</t>
         </is>
       </c>
       <c r="K84" s="2" t="n">
-        <v>11489</v>
+        <v>3661.8</v>
       </c>
       <c r="L84" s="4" t="n">
-        <v>1.45</v>
+        <v>0.95</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
@@ -5223,49 +5223,49 @@
     <row r="85" ht="18" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>886.5</v>
+        <v>166.3</v>
       </c>
       <c r="C85" s="3" t="n">
-        <v>860.1</v>
+        <v>165.87</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>887</v>
+        <v>166.83</v>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>3.03% (26.9)</t>
+          <t>0.58% (0.96)</t>
         </is>
       </c>
       <c r="F85" s="4" t="n">
-        <v>913.9</v>
+        <v>167.79</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>940.8</v>
+        <v>168.75</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
           <t>2026-10-16 09:15</t>
         </is>
       </c>
-      <c r="I85" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 15:15 (Week End)</t>
+          <t>2026-10-16 09:15</t>
         </is>
       </c>
       <c r="K85" s="2" t="n">
-        <v>908</v>
+        <v>168.75</v>
       </c>
       <c r="L85" s="4" t="n">
-        <v>2.37</v>
+        <v>1.15</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
@@ -5276,28 +5276,28 @@
     <row r="86" ht="18" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>3607</v>
+        <v>11225</v>
       </c>
       <c r="C86" s="3" t="n">
-        <v>3593.2</v>
+        <v>11130</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>3627.5</v>
+        <v>11325</v>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>0.95% (34.3)</t>
+          <t>1.72% (195.0)</t>
         </is>
       </c>
       <c r="F86" s="4" t="n">
-        <v>3661.8</v>
+        <v>11520</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>3696.1</v>
+        <v>11715</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -5311,14 +5311,14 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 11:30</t>
+          <t>2026-10-16 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K86" s="2" t="n">
-        <v>3661.8</v>
+        <v>11489</v>
       </c>
       <c r="L86" s="4" t="n">
-        <v>0.95</v>
+        <v>1.45</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>

--- a/data/trade_tracker_results.xlsx
+++ b/data/trade_tracker_results.xlsx
@@ -74,6 +74,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
         <bgColor rgb="00D9E1F2"/>
       </patternFill>
@@ -88,12 +94,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFEB9C"/>
         <bgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -129,16 +129,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -506,19 +506,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
   </cols>
@@ -613,22 +613,24 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-21 09:15</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="4" t="n">
-        <v>0</v>
+          <t>2026-10-21 10:15</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>7677</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>-0.67</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
@@ -641,21 +643,21 @@
         <v>2317.8</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2310</v>
+        <v>2299</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>2324.2</v>
+        <v>2341.5</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>0.61% (14.2)</t>
+          <t>1.82% (42.5)</t>
         </is>
       </c>
       <c r="F3" s="4" t="n">
-        <v>2338.4</v>
+        <v>2384</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>2352.6</v>
+        <v>2426.5</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -751,22 +753,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-21 09:15</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="4" t="n">
-        <v>0</v>
+          <t>2026-10-21 09:15</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>4587</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>-0.5</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -779,21 +783,21 @@
         <v>435.2</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>435.05</v>
+        <v>434.75</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>438.35</v>
+        <v>438.45</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>0.75% (3.3)</t>
+          <t>0.84% (3.7)</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>441.65</v>
+        <v>442.15</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>444.95</v>
+        <v>445.85</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -825,21 +829,21 @@
         <v>4550.4</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>4533.8</v>
+        <v>4474.6</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>4551.2</v>
+        <v>4572.1</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>0.38% (17.4)</t>
+          <t>2.13% (97.5)</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>4568.6</v>
+        <v>4669.6</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>4586</v>
+        <v>4767.1</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -858,6 +862,834 @@
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>1255.4</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1245.6</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>1272.2</v>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>2.09% (26.6)</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>1298.8</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>1325.4</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>1725.1</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>1724.5</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>1735.6</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>0.64% (11.1)</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>1746.7</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>1757.8</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>369.4</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>366.95</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>369.6</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>0.72% (2.65)</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>372.25</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>374.9</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>DABUR</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>372.8</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>371.75</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>373.9</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>0.58% (2.15)</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>376.05</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>378.2</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>165.87</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>164.88</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>165.92</v>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>0.63% (1.04)</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>166.96</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>168</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>700.35</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>698.5</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>704.5</v>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>0.85% (6.0)</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>710.5</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>716.5</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>532.6</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>531.7</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>542.7</v>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>2.03% (11.0)</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>553.7</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>564.7</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>1631</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>1626.4</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>1640.6</v>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>0.87% (14.2)</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>1654.8</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>1669</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>4615</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>4585</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>4634.2</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>1.06% (49.2)</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>4683.4</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>4732.6</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>INDUSINDBK</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>845.7</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>831.25</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>853.7</v>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>2.63% (22.45)</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>876.15</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>898.6</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>437.2</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>436</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>446.85</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>2.43% (10.85)</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>457.7</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>468.55</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>NHPC</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>71.44</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>70.61</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>71.87</v>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>1.75% (1.26)</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>73.13</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>74.39</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>1462</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>1460.3</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>1465.7</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>0.37% (5.4)</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>1471.1</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>1476.5</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>RECLTD</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>299.1</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>300.5</v>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>0.47% (1.4)</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>301.9</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>303.3</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>1725.5</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>1721.7</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>1725.9</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>0.24% (4.2)</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>1730.1</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>1734.3</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>TATASTEEL</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>171.66</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>170.66</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>173.97</v>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>1.9% (3.31)</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>177.28</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>180.59</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>4361</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>4351.1</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>0.32% (14.0)</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>4379.1</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>4393.1</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>1107.3</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>1106</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>1116.6</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>0.95% (10.6)</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>1127.2</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>1137.8</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -872,7 +1704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M87"/>
+  <dimension ref="A1:M90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -958,23 +1790,23 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Week Range: (21-09-2026 to 27-09-2026)</t>
         </is>
       </c>
-      <c r="B2" s="5" t="n"/>
-      <c r="C2" s="5" t="n"/>
-      <c r="D2" s="5" t="n"/>
-      <c r="E2" s="5" t="n"/>
-      <c r="F2" s="5" t="n"/>
-      <c r="G2" s="5" t="n"/>
-      <c r="H2" s="5" t="n"/>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="n"/>
-      <c r="L2" s="5" t="n"/>
-      <c r="M2" s="5" t="n"/>
+      <c r="B2" s="6" t="n"/>
+      <c r="C2" s="6" t="n"/>
+      <c r="D2" s="6" t="n"/>
+      <c r="E2" s="6" t="n"/>
+      <c r="F2" s="6" t="n"/>
+      <c r="G2" s="6" t="n"/>
+      <c r="H2" s="6" t="n"/>
+      <c r="I2" s="6" t="n"/>
+      <c r="J2" s="6" t="n"/>
+      <c r="K2" s="6" t="n"/>
+      <c r="L2" s="6" t="n"/>
+      <c r="M2" s="6" t="n"/>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -1007,7 +1839,7 @@
           <t>2026-09-23 09:15</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -1060,7 +1892,7 @@
           <t>2026-09-23 11:00</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -1113,7 +1945,7 @@
           <t>2026-09-23 14:15</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I5" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -1166,7 +1998,7 @@
           <t>2026-09-24 09:30</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -1219,7 +2051,7 @@
           <t>2026-09-24 10:00</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -1272,7 +2104,7 @@
           <t>2026-09-24 10:00</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -1325,7 +2157,7 @@
           <t>2026-09-24 12:30</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I9" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -1378,7 +2210,7 @@
           <t>2026-09-25 10:00</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -1403,35 +2235,35 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>1927</v>
+        <v>1242.8</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1915.1</v>
+        <v>1202.6</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1935.1</v>
+        <v>1246</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>1.03% (20.0)</t>
+          <t>3.48% (43.4)</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1955.1</v>
+        <v>1289.4</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1975.1</v>
+        <v>1332.8</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
           <t>2026-09-25 14:00</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I11" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -1442,10 +2274,10 @@
         </is>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1942.9</v>
+        <v>1254.8</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.4</v>
+        <v>0.71</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
@@ -1456,35 +2288,35 @@
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>1242.8</v>
+        <v>1927</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1202.6</v>
+        <v>1915.1</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1246</v>
+        <v>1935.1</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>3.48% (43.4)</t>
+          <t>1.03% (20.0)</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1289.4</v>
+        <v>1955.1</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1332.8</v>
+        <v>1975.1</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2026-09-25 14:00</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -1495,10 +2327,10 @@
         </is>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1254.8</v>
+        <v>1942.9</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.71</v>
+        <v>0.4</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
@@ -1537,7 +2369,7 @@
           <t>2026-09-25 14:15</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I13" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -1590,7 +2422,7 @@
           <t>2026-09-25 14:15</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -1613,23 +2445,23 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Week Range: (28-09-2026 to 04-10-2026)</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="n"/>
-      <c r="L15" s="5" t="n"/>
-      <c r="M15" s="5" t="n"/>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="6" t="n"/>
+      <c r="J15" s="6" t="n"/>
+      <c r="K15" s="6" t="n"/>
+      <c r="L15" s="6" t="n"/>
+      <c r="M15" s="6" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -1662,7 +2494,7 @@
           <t>2026-09-28 10:00</t>
         </is>
       </c>
-      <c r="I16" s="8" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -1715,7 +2547,7 @@
           <t>2026-09-28 11:30</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -1768,7 +2600,7 @@
           <t>2026-09-28 12:00</t>
         </is>
       </c>
-      <c r="I18" s="6" t="inlineStr">
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
@@ -1821,7 +2653,7 @@
           <t>2026-09-28 13:15</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="I19" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -1874,7 +2706,7 @@
           <t>2026-09-28 13:45</t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -1927,7 +2759,7 @@
           <t>2026-09-28 14:00</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="I21" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -1952,28 +2784,28 @@
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>906.9</v>
+        <v>171.35</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>889.7</v>
+        <v>171.05</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>907.5</v>
+        <v>172.2</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>1.96% (17.8)</t>
+          <t>0.67% (1.15)</t>
         </is>
       </c>
       <c r="F22" s="4" t="n">
-        <v>925.3</v>
+        <v>173.35</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>943.1</v>
+        <v>174.5</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1982,19 +2814,19 @@
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>SL HIT</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:15</t>
+          <t>2026-09-28 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K22" s="2" t="n">
-        <v>889.7</v>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v>-1.96</v>
+        <v>172.45</v>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>0.15</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
@@ -2005,49 +2837,49 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>171.35</v>
+        <v>906.9</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>171.05</v>
+        <v>889.7</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>172.2</v>
+        <v>907.5</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>0.67% (1.15)</t>
+          <t>1.96% (17.8)</t>
         </is>
       </c>
       <c r="F23" s="4" t="n">
-        <v>173.35</v>
+        <v>925.3</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>174.5</v>
+        <v>943.1</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
           <t>2026-09-28 15:15</t>
         </is>
       </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 15:15 (Week End)</t>
+          <t>2026-09-29 10:15</t>
         </is>
       </c>
       <c r="K23" s="2" t="n">
-        <v>172.45</v>
-      </c>
-      <c r="L23" s="4" t="n">
-        <v>0.15</v>
+        <v>889.7</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>-1.96</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
@@ -2086,7 +2918,7 @@
           <t>2026-09-29 09:15</t>
         </is>
       </c>
-      <c r="I24" s="6" t="inlineStr">
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
@@ -2139,7 +2971,7 @@
           <t>2026-09-29 09:15</t>
         </is>
       </c>
-      <c r="I25" s="8" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -2192,7 +3024,7 @@
           <t>2026-09-29 09:15</t>
         </is>
       </c>
-      <c r="I26" s="8" t="inlineStr">
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -2245,7 +3077,7 @@
           <t>2026-09-29 09:30</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="I27" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2298,7 +3130,7 @@
           <t>2026-09-29 11:00</t>
         </is>
       </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="I28" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2351,7 +3183,7 @@
           <t>2026-09-29 11:15</t>
         </is>
       </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="I29" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2376,49 +3208,49 @@
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>399.3</v>
+        <v>1495.7</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>394.7</v>
+        <v>1487.1</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>403.65</v>
+        <v>1498</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>2.22% (8.95)</t>
+          <t>0.73% (10.9)</t>
         </is>
       </c>
       <c r="F30" s="4" t="n">
-        <v>412.6</v>
+        <v>1508.9</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>421.55</v>
+        <v>1519.8</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 11:30</t>
         </is>
       </c>
-      <c r="I30" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:15 (Week End)</t>
+          <t>2026-09-29 12:30</t>
         </is>
       </c>
       <c r="K30" s="2" t="n">
-        <v>406</v>
-      </c>
-      <c r="L30" s="4" t="n">
-        <v>0.58</v>
+        <v>1487.1</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>-0.73</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
@@ -2429,28 +3261,28 @@
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>1495.7</v>
+        <v>399.3</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1487.1</v>
+        <v>394.7</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1498</v>
+        <v>403.65</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>0.73% (10.9)</t>
+          <t>2.22% (8.95)</t>
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1508.9</v>
+        <v>412.6</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1519.8</v>
+        <v>421.55</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -2459,19 +3291,19 @@
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>SL HIT</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:30</t>
+          <t>2026-09-29 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K31" s="2" t="n">
-        <v>1487.1</v>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>-0.73</v>
+        <v>406</v>
+      </c>
+      <c r="L31" s="4" t="n">
+        <v>0.58</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
@@ -2510,7 +3342,7 @@
           <t>2026-09-29 11:45</t>
         </is>
       </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="I32" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2563,7 +3395,7 @@
           <t>2026-09-29 12:00</t>
         </is>
       </c>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="I33" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2616,7 +3448,7 @@
           <t>2026-09-29 13:00</t>
         </is>
       </c>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="I34" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2669,7 +3501,7 @@
           <t>2026-09-29 14:00</t>
         </is>
       </c>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="I35" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2722,7 +3554,7 @@
           <t>2026-09-29 14:00</t>
         </is>
       </c>
-      <c r="I36" s="6" t="inlineStr">
+      <c r="I36" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -2775,7 +3607,7 @@
           <t>2026-09-29 14:45</t>
         </is>
       </c>
-      <c r="I37" s="7" t="inlineStr">
+      <c r="I37" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2828,7 +3660,7 @@
           <t>2026-09-29 14:45</t>
         </is>
       </c>
-      <c r="I38" s="8" t="inlineStr">
+      <c r="I38" s="5" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -2881,7 +3713,7 @@
           <t>2026-09-29 15:00</t>
         </is>
       </c>
-      <c r="I39" s="7" t="inlineStr">
+      <c r="I39" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2906,49 +3738,49 @@
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>2391</v>
+        <v>263.55</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>2381.6</v>
+        <v>263.3</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>2420</v>
+        <v>266.2</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>1.59% (38.4)</t>
+          <t>1.09% (2.9)</t>
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>2458.4</v>
+        <v>269.1</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>2496.8</v>
+        <v>272</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I40" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:30 (Week End)</t>
+          <t>2026-09-30 14:15</t>
         </is>
       </c>
       <c r="K40" s="2" t="n">
-        <v>2409.1</v>
+        <v>263.3</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>-0.45</v>
+        <v>-1.09</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
@@ -2959,49 +3791,49 @@
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>1766.7</v>
+        <v>196.1</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>1736.8</v>
+        <v>192.45</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>1770.1</v>
+        <v>196.67</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>1.88% (33.3)</t>
+          <t>2.15% (4.22)</t>
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>1803.4</v>
+        <v>200.89</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>1836.7</v>
+        <v>205.11</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I41" s="7" t="inlineStr">
+      <c r="I41" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 15:15 (Week End)</t>
+          <t>2026-09-30 09:15</t>
         </is>
       </c>
       <c r="K41" s="2" t="n">
-        <v>1798.3</v>
+        <v>200.89</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>1.59</v>
+        <v>2.15</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
@@ -3012,28 +3844,28 @@
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>160.5</v>
+        <v>4057</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>159.41</v>
+        <v>4043.3</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>162.37</v>
+        <v>4095</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>1.82% (2.96)</t>
+          <t>1.26% (51.7)</t>
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>165.33</v>
+        <v>4146.7</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>168.29</v>
+        <v>4198.4</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -3042,19 +3874,19 @@
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>ACTIVE (Week End)</t>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 15:15 (Week End)</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="K42" s="2" t="n">
-        <v>163.26</v>
-      </c>
-      <c r="L42" s="4" t="n">
-        <v>0.55</v>
+        <v>4043.3</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>-1.26</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
@@ -3065,49 +3897,49 @@
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>991.6</v>
+        <v>399.3</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>980.4</v>
+        <v>394.7</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>992.7</v>
+        <v>403.65</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>1.24% (12.3)</t>
+          <t>2.22% (8.95)</t>
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>1005</v>
+        <v>412.6</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>1017.3</v>
+        <v>421.55</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I43" s="6" t="inlineStr">
+      <c r="I43" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="K43" s="2" t="n">
-        <v>1017.3</v>
+        <v>421.55</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>2.48</v>
+        <v>4.43</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
@@ -3118,49 +3950,49 @@
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>399.3</v>
+        <v>4848.5</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>394.7</v>
+        <v>4837</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>403.65</v>
+        <v>4872</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>2.22% (8.95)</t>
+          <t>0.72% (35.0)</t>
         </is>
       </c>
       <c r="F44" s="4" t="n">
-        <v>412.6</v>
+        <v>4907</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>421.55</v>
+        <v>4942</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I44" s="6" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 09:15</t>
+          <t>2026-09-30 10:30</t>
         </is>
       </c>
       <c r="K44" s="2" t="n">
-        <v>421.55</v>
-      </c>
-      <c r="L44" s="4" t="n">
-        <v>4.43</v>
+        <v>4837</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>-0.72</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
@@ -3171,49 +4003,49 @@
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>4848.5</v>
+        <v>991.6</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>4837</v>
+        <v>980.4</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>4872</v>
+        <v>992.7</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>0.72% (35.0)</t>
+          <t>1.24% (12.3)</t>
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>4907</v>
+        <v>1005</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>4942</v>
+        <v>1017.3</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 10:30</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
       <c r="K45" s="2" t="n">
-        <v>4837</v>
-      </c>
-      <c r="L45" s="3" t="n">
-        <v>-0.72</v>
+        <v>1017.3</v>
+      </c>
+      <c r="L45" s="4" t="n">
+        <v>2.48</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
@@ -3224,49 +4056,49 @@
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>196.1</v>
+        <v>160.5</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>192.45</v>
+        <v>159.41</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>196.67</v>
+        <v>162.37</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>2.15% (4.22)</t>
+          <t>1.82% (2.96)</t>
         </is>
       </c>
       <c r="F46" s="4" t="n">
-        <v>200.89</v>
+        <v>165.33</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>205.11</v>
+        <v>168.29</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I46" s="7" t="inlineStr">
+      <c r="I46" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:15</t>
+          <t>2026-09-30 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K46" s="2" t="n">
-        <v>200.89</v>
+        <v>163.26</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>2.15</v>
+        <v>0.55</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
@@ -3277,28 +4109,28 @@
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>263.55</v>
+        <v>1766.7</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>263.3</v>
+        <v>1736.8</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>266.2</v>
+        <v>1770.1</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>1.09% (2.9)</t>
+          <t>1.88% (33.3)</t>
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>269.1</v>
+        <v>1803.4</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>272</v>
+        <v>1836.7</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -3307,19 +4139,19 @@
       </c>
       <c r="I47" s="8" t="inlineStr">
         <is>
-          <t>SL HIT</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:15</t>
+          <t>2026-09-30 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K47" s="2" t="n">
-        <v>263.3</v>
-      </c>
-      <c r="L47" s="3" t="n">
-        <v>-1.09</v>
+        <v>1798.3</v>
+      </c>
+      <c r="L47" s="4" t="n">
+        <v>1.59</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
@@ -3330,49 +4162,49 @@
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>4057</v>
+        <v>2391</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>4043.3</v>
+        <v>2381.6</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>4095</v>
+        <v>2420</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>1.26% (51.7)</t>
+          <t>1.59% (38.4)</t>
         </is>
       </c>
       <c r="F48" s="4" t="n">
-        <v>4146.7</v>
+        <v>2458.4</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>4198.4</v>
+        <v>2496.8</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I48" s="6" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
+      <c r="I48" s="8" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 09:15</t>
+          <t>2026-09-30 12:30 (Week End)</t>
         </is>
       </c>
       <c r="K48" s="2" t="n">
-        <v>4043.3</v>
+        <v>2409.1</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>-1.26</v>
+        <v>-0.45</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
@@ -3411,7 +4243,7 @@
           <t>2026-10-01 09:15</t>
         </is>
       </c>
-      <c r="I49" s="6" t="inlineStr">
+      <c r="I49" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -3464,7 +4296,7 @@
           <t>2026-10-01 09:15</t>
         </is>
       </c>
-      <c r="I50" s="7" t="inlineStr">
+      <c r="I50" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3487,23 +4319,23 @@
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>Week Range: (05-10-2026 to 11-10-2026)</t>
         </is>
       </c>
-      <c r="B51" s="5" t="n"/>
-      <c r="C51" s="5" t="n"/>
-      <c r="D51" s="5" t="n"/>
-      <c r="E51" s="5" t="n"/>
-      <c r="F51" s="5" t="n"/>
-      <c r="G51" s="5" t="n"/>
-      <c r="H51" s="5" t="n"/>
-      <c r="I51" s="5" t="n"/>
-      <c r="J51" s="5" t="n"/>
-      <c r="K51" s="5" t="n"/>
-      <c r="L51" s="5" t="n"/>
-      <c r="M51" s="5" t="n"/>
+      <c r="B51" s="6" t="n"/>
+      <c r="C51" s="6" t="n"/>
+      <c r="D51" s="6" t="n"/>
+      <c r="E51" s="6" t="n"/>
+      <c r="F51" s="6" t="n"/>
+      <c r="G51" s="6" t="n"/>
+      <c r="H51" s="6" t="n"/>
+      <c r="I51" s="6" t="n"/>
+      <c r="J51" s="6" t="n"/>
+      <c r="K51" s="6" t="n"/>
+      <c r="L51" s="6" t="n"/>
+      <c r="M51" s="6" t="n"/>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
@@ -3536,7 +4368,7 @@
           <t>2026-10-06 09:15</t>
         </is>
       </c>
-      <c r="I52" s="6" t="inlineStr">
+      <c r="I52" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -3589,7 +4421,7 @@
           <t>2026-10-06 09:15</t>
         </is>
       </c>
-      <c r="I53" s="7" t="inlineStr">
+      <c r="I53" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3642,7 +4474,7 @@
           <t>2026-10-06 09:15</t>
         </is>
       </c>
-      <c r="I54" s="7" t="inlineStr">
+      <c r="I54" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3695,7 +4527,7 @@
           <t>2026-10-06 09:15</t>
         </is>
       </c>
-      <c r="I55" s="7" t="inlineStr">
+      <c r="I55" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3720,28 +4552,28 @@
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>168.43</v>
+        <v>3709.5</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>166.48</v>
+        <v>3695</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>168.99</v>
+        <v>3723.8</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>1.49% (2.51)</t>
+          <t>0.77% (28.8)</t>
         </is>
       </c>
       <c r="F56" s="4" t="n">
-        <v>171.5</v>
+        <v>3752.6</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>174.01</v>
+        <v>3781.4</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3750,19 +4582,19 @@
       </c>
       <c r="I56" s="7" t="inlineStr">
         <is>
-          <t>ACTIVE (Week End)</t>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 15:15 (Week End)</t>
+          <t>2026-10-07 09:15</t>
         </is>
       </c>
       <c r="K56" s="2" t="n">
-        <v>170.71</v>
+        <v>3781.4</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
@@ -3773,49 +4605,49 @@
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>1295</v>
+        <v>168.43</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>1293</v>
+        <v>166.48</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>1299.4</v>
+        <v>168.99</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>0.49% (6.4)</t>
+          <t>1.49% (2.51)</t>
         </is>
       </c>
       <c r="F57" s="4" t="n">
-        <v>1305.8</v>
+        <v>171.5</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>1312.2</v>
+        <v>174.01</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
           <t>2026-10-07 09:15</t>
         </is>
       </c>
-      <c r="I57" s="6" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I57" s="8" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 09:15</t>
+          <t>2026-10-07 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K57" s="2" t="n">
-        <v>1312.2</v>
+        <v>170.71</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>0.99</v>
+        <v>1.02</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
@@ -3826,35 +4658,35 @@
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>3709.5</v>
+        <v>1295</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>3695</v>
+        <v>1293</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>3723.8</v>
+        <v>1299.4</v>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>0.77% (28.8)</t>
+          <t>0.49% (6.4)</t>
         </is>
       </c>
       <c r="F58" s="4" t="n">
-        <v>3752.6</v>
+        <v>1305.8</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>3781.4</v>
+        <v>1312.2</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
           <t>2026-10-07 09:15</t>
         </is>
       </c>
-      <c r="I58" s="6" t="inlineStr">
+      <c r="I58" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -3865,10 +4697,10 @@
         </is>
       </c>
       <c r="K58" s="2" t="n">
-        <v>3781.4</v>
+        <v>1312.2</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>1.55</v>
+        <v>0.99</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
@@ -3907,7 +4739,7 @@
           <t>2026-10-08 09:15</t>
         </is>
       </c>
-      <c r="I59" s="8" t="inlineStr">
+      <c r="I59" s="5" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -3960,7 +4792,7 @@
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I60" s="6" t="inlineStr">
+      <c r="I60" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -4013,7 +4845,7 @@
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I61" s="7" t="inlineStr">
+      <c r="I61" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -4066,7 +4898,7 @@
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I62" s="6" t="inlineStr">
+      <c r="I62" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -4119,7 +4951,7 @@
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I63" s="8" t="inlineStr">
+      <c r="I63" s="5" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -4172,7 +5004,7 @@
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I64" s="6" t="inlineStr">
+      <c r="I64" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -4225,7 +5057,7 @@
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I65" s="6" t="inlineStr">
+      <c r="I65" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -4248,70 +5080,70 @@
       </c>
     </row>
     <row r="66" ht="22" customHeight="1">
-      <c r="A66" s="5" t="inlineStr">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>Week Range: (12-10-2026 to 18-10-2026)</t>
         </is>
       </c>
-      <c r="B66" s="5" t="n"/>
-      <c r="C66" s="5" t="n"/>
-      <c r="D66" s="5" t="n"/>
-      <c r="E66" s="5" t="n"/>
-      <c r="F66" s="5" t="n"/>
-      <c r="G66" s="5" t="n"/>
-      <c r="H66" s="5" t="n"/>
-      <c r="I66" s="5" t="n"/>
-      <c r="J66" s="5" t="n"/>
-      <c r="K66" s="5" t="n"/>
-      <c r="L66" s="5" t="n"/>
-      <c r="M66" s="5" t="n"/>
+      <c r="B66" s="6" t="n"/>
+      <c r="C66" s="6" t="n"/>
+      <c r="D66" s="6" t="n"/>
+      <c r="E66" s="6" t="n"/>
+      <c r="F66" s="6" t="n"/>
+      <c r="G66" s="6" t="n"/>
+      <c r="H66" s="6" t="n"/>
+      <c r="I66" s="6" t="n"/>
+      <c r="J66" s="6" t="n"/>
+      <c r="K66" s="6" t="n"/>
+      <c r="L66" s="6" t="n"/>
+      <c r="M66" s="6" t="n"/>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>1124.6</v>
+        <v>709.75</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>1123.1</v>
+        <v>708.8</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>1131.1</v>
+        <v>711.4</v>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>0.71% (8.0)</t>
+          <t>0.37% (2.6)</t>
         </is>
       </c>
       <c r="F67" s="4" t="n">
-        <v>1139.1</v>
+        <v>714</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>1147.1</v>
+        <v>716.6</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
           <t>2026-10-13 09:15</t>
         </is>
       </c>
-      <c r="I67" s="6" t="inlineStr">
+      <c r="I67" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 10:15</t>
+          <t>2026-10-13 09:45</t>
         </is>
       </c>
       <c r="K67" s="2" t="n">
-        <v>1147.1</v>
+        <v>716.6</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>1.41</v>
+        <v>0.73</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
@@ -4350,7 +5182,7 @@
           <t>2026-10-13 09:15</t>
         </is>
       </c>
-      <c r="I68" s="7" t="inlineStr">
+      <c r="I68" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -4375,49 +5207,49 @@
     <row r="69" ht="18" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>709.75</v>
+        <v>1124.6</v>
       </c>
       <c r="C69" s="3" t="n">
-        <v>708.8</v>
+        <v>1123.1</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>711.4</v>
+        <v>1131.1</v>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>0.37% (2.6)</t>
+          <t>0.71% (8.0)</t>
         </is>
       </c>
       <c r="F69" s="4" t="n">
-        <v>714</v>
+        <v>1139.1</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>716.6</v>
+        <v>1147.1</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
           <t>2026-10-13 09:15</t>
         </is>
       </c>
-      <c r="I69" s="6" t="inlineStr">
+      <c r="I69" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 09:45</t>
+          <t>2026-10-15 10:15</t>
         </is>
       </c>
       <c r="K69" s="2" t="n">
-        <v>716.6</v>
+        <v>1147.1</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>0.73</v>
+        <v>1.41</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
@@ -4456,7 +5288,7 @@
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I70" s="7" t="inlineStr">
+      <c r="I70" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -4509,7 +5341,7 @@
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I71" s="6" t="inlineStr">
+      <c r="I71" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -4562,7 +5394,7 @@
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I72" s="6" t="inlineStr">
+      <c r="I72" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -4615,7 +5447,7 @@
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I73" s="7" t="inlineStr">
+      <c r="I73" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -4668,7 +5500,7 @@
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I74" s="6" t="inlineStr">
+      <c r="I74" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -4721,7 +5553,7 @@
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I75" s="6" t="inlineStr">
+      <c r="I75" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -4774,7 +5606,7 @@
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I76" s="7" t="inlineStr">
+      <c r="I76" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -4827,7 +5659,7 @@
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I77" s="6" t="inlineStr">
+      <c r="I77" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -4880,7 +5712,7 @@
           <t>2026-10-14 09:30</t>
         </is>
       </c>
-      <c r="I78" s="7" t="inlineStr">
+      <c r="I78" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -4933,7 +5765,7 @@
           <t>2026-10-14 09:45</t>
         </is>
       </c>
-      <c r="I79" s="6" t="inlineStr">
+      <c r="I79" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -4986,7 +5818,7 @@
           <t>2026-10-14 11:30</t>
         </is>
       </c>
-      <c r="I80" s="7" t="inlineStr">
+      <c r="I80" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -5039,7 +5871,7 @@
           <t>2026-10-14 13:45</t>
         </is>
       </c>
-      <c r="I81" s="8" t="inlineStr">
+      <c r="I81" s="5" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -5092,7 +5924,7 @@
           <t>2026-10-15 09:15</t>
         </is>
       </c>
-      <c r="I82" s="7" t="inlineStr">
+      <c r="I82" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -5145,7 +5977,7 @@
           <t>2026-10-16 09:15</t>
         </is>
       </c>
-      <c r="I83" s="7" t="inlineStr">
+      <c r="I83" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -5198,7 +6030,7 @@
           <t>2026-10-16 09:15</t>
         </is>
       </c>
-      <c r="I84" s="7" t="inlineStr">
+      <c r="I84" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -5251,7 +6083,7 @@
           <t>2026-10-16 09:15</t>
         </is>
       </c>
-      <c r="I85" s="6" t="inlineStr">
+      <c r="I85" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -5304,7 +6136,7 @@
           <t>2026-10-16 09:15</t>
         </is>
       </c>
-      <c r="I86" s="7" t="inlineStr">
+      <c r="I86" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -5357,7 +6189,7 @@
           <t>2026-10-16 09:15</t>
         </is>
       </c>
-      <c r="I87" s="7" t="inlineStr">
+      <c r="I87" s="8" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -5379,12 +6211,138 @@
         </is>
       </c>
     </row>
+    <row r="88" ht="22" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>Week Range: (19-10-2026 to 25-10-2026)</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="n"/>
+      <c r="C88" s="6" t="n"/>
+      <c r="D88" s="6" t="n"/>
+      <c r="E88" s="6" t="n"/>
+      <c r="F88" s="6" t="n"/>
+      <c r="G88" s="6" t="n"/>
+      <c r="H88" s="6" t="n"/>
+      <c r="I88" s="6" t="n"/>
+      <c r="J88" s="6" t="n"/>
+      <c r="K88" s="6" t="n"/>
+      <c r="L88" s="6" t="n"/>
+      <c r="M88" s="6" t="n"/>
+    </row>
+    <row r="89" ht="18" customHeight="1">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="n">
+        <v>7688</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>7677</v>
+      </c>
+      <c r="D89" s="4" t="n">
+        <v>7729</v>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>0.67% (52.0)</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="n">
+        <v>7781</v>
+      </c>
+      <c r="G89" s="4" t="n">
+        <v>7833</v>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 09:15</t>
+        </is>
+      </c>
+      <c r="I89" s="5" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 10:15</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>7677</v>
+      </c>
+      <c r="L89" s="3" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>(19-10-2026 to 25-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="18" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>CUMMINSIND</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="n">
+        <v>4591.2</v>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>4587</v>
+      </c>
+      <c r="D90" s="4" t="n">
+        <v>4610</v>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>0.5% (23.0)</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="n">
+        <v>4633</v>
+      </c>
+      <c r="G90" s="4" t="n">
+        <v>4656</v>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 09:15</t>
+        </is>
+      </c>
+      <c r="I90" s="5" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21 09:15</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>4587</v>
+      </c>
+      <c r="L90" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>(19-10-2026 to 25-10-2026)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
+    <mergeCell ref="A66:M66"/>
+    <mergeCell ref="A88:M88"/>
+    <mergeCell ref="A15:M15"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A51:M51"/>
-    <mergeCell ref="A15:M15"/>
-    <mergeCell ref="A66:M66"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trade_tracker_results.xlsx
+++ b/data/trade_tracker_results.xlsx
@@ -80,6 +80,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
         <bgColor rgb="00D9E1F2"/>
       </patternFill>
@@ -88,12 +94,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
         <bgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -132,13 +132,13 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -506,19 +506,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
   </cols>
@@ -875,21 +875,21 @@
         <v>1255.4</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1245.6</v>
+        <v>1214.1</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1272.2</v>
+        <v>1259</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>2.09% (26.6)</t>
+          <t>3.57% (44.9)</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1298.8</v>
+        <v>1303.9</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1325.4</v>
+        <v>1348.8</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -921,21 +921,21 @@
         <v>1725.1</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1724.5</v>
+        <v>1715.3</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1735.6</v>
+        <v>1748.8</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>0.64% (11.1)</t>
+          <t>1.92% (33.5)</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1746.7</v>
+        <v>1782.3</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1757.8</v>
+        <v>1815.8</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1013,21 +1013,21 @@
         <v>372.8</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>371.75</v>
+        <v>368.5</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>373.9</v>
+        <v>379.05</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>0.58% (2.15)</t>
+          <t>2.78% (10.55)</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>376.05</v>
+        <v>389.6</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>378.2</v>
+        <v>400.15</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1105,21 +1105,21 @@
         <v>700.35</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>698.5</v>
+        <v>691.65</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>704.5</v>
+        <v>706.95</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>0.85% (6.0)</t>
+          <t>2.16% (15.3)</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>710.5</v>
+        <v>722.25</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>716.5</v>
+        <v>737.55</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1151,21 +1151,21 @@
         <v>532.6</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>531.7</v>
+        <v>528.9</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>542.7</v>
+        <v>539.65</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>2.03% (11.0)</t>
+          <t>1.99% (10.75)</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>553.7</v>
+        <v>550.4</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>564.7</v>
+        <v>561.15</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1197,21 +1197,21 @@
         <v>1631</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1626.4</v>
+        <v>1616.6</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1640.6</v>
+        <v>1644.9</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>0.87% (14.2)</t>
+          <t>1.72% (28.3)</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1654.8</v>
+        <v>1673.2</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1669</v>
+        <v>1701.5</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1243,21 +1243,21 @@
         <v>4615</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>4585</v>
+        <v>4548.9</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>4634.2</v>
+        <v>4641.5</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>1.06% (49.2)</t>
+          <t>2.0% (92.6)</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>4683.4</v>
+        <v>4734.1</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>4732.6</v>
+        <v>4826.7</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1335,21 +1335,21 @@
         <v>437.2</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>436</v>
+        <v>433.75</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>446.85</v>
+        <v>438.2</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>2.43% (10.85)</t>
+          <t>1.02% (4.45)</t>
         </is>
       </c>
       <c r="F18" s="4" t="n">
-        <v>457.7</v>
+        <v>442.65</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>468.55</v>
+        <v>447.1</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1399,22 +1399,24 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr"/>
+          <t>2026-10-22 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>72.38</v>
+      </c>
       <c r="L19" s="4" t="n">
-        <v>0</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -1427,21 +1429,21 @@
         <v>1462</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1460.3</v>
+        <v>1451</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1465.7</v>
+        <v>1484.9</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>0.37% (5.4)</t>
+          <t>2.28% (33.9)</t>
         </is>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1471.1</v>
+        <v>1518.8</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1476.5</v>
+        <v>1552.7</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1473,21 +1475,21 @@
         <v>300</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>299.1</v>
+        <v>295.55</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>300.5</v>
+        <v>302.5</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>0.47% (1.4)</t>
+          <t>2.3% (6.95)</t>
         </is>
       </c>
       <c r="F21" s="4" t="n">
-        <v>301.9</v>
+        <v>309.45</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>303.3</v>
+        <v>316.4</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1512,28 +1514,28 @@
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>1725.5</v>
+        <v>1634.5</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1721.7</v>
+        <v>1620</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1725.9</v>
+        <v>1667.3</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>0.24% (4.2)</t>
+          <t>2.84% (47.3)</t>
         </is>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1730.1</v>
+        <v>1714.6</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1734.3</v>
+        <v>1761.9</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1558,28 +1560,28 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>171.66</v>
+        <v>1725.5</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>170.66</v>
+        <v>1719.6</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>173.97</v>
+        <v>1745.1</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>1.9% (3.31)</t>
+          <t>1.46% (25.5)</t>
         </is>
       </c>
       <c r="F23" s="4" t="n">
-        <v>177.28</v>
+        <v>1770.6</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>180.59</v>
+        <v>1796.1</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1604,28 +1606,28 @@
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>4361</v>
+        <v>171.66</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>4351.1</v>
+        <v>168.11</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>4365.1</v>
+        <v>172.45</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>0.32% (14.0)</t>
+          <t>2.52% (4.34)</t>
         </is>
       </c>
       <c r="F24" s="4" t="n">
-        <v>4379.1</v>
+        <v>176.79</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>4393.1</v>
+        <v>181.13</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1650,28 +1652,28 @@
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>1107.3</v>
+        <v>4361</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1106</v>
+        <v>4329.2</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1116.6</v>
+        <v>4380.9</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>0.95% (10.6)</t>
+          <t>1.18% (51.7)</t>
         </is>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1127.2</v>
+        <v>4432.6</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1137.8</v>
+        <v>4484.3</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1690,6 +1692,604 @@
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>1107.3</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>1100.3</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>1117.3</v>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>1.52% (17.0)</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>1134.3</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>1151.3</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>BPCL</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>283.25</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>277</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>288</v>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>3.82% (11.0)</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>299</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>310</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>808.55</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>808.4</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>821.75</v>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>1.62% (13.35)</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>835.1</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>848.45</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>1300.2</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>1296.7</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>1314</v>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>1.32% (17.3)</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>1331.3</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>1348.6</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>402.1</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>395.75</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>407.5</v>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>2.88% (11.75)</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>419.25</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>431</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>2843.4</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>2828.2</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>2889.1</v>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>2.11% (60.9)</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>2950</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>3010.9</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>1814.4</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>1810.6</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>1822.3</v>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>0.64% (11.7)</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>1834</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>1845.7</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>256.95</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>256.45</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>260.35</v>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>1.5% (3.9)</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>264.25</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>268.15</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>1003.5</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>1001.4</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>1028</v>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>2.59% (26.6)</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>1054.6</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>1081.2</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>11125</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>10990</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>11200</v>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>1.88% (210.0)</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>11410</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>11620</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>152.77</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>152.4</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>155.43</v>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>1.95% (3.03)</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>158.46</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>161.49</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>244.8</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>252.15</v>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>2.91% (7.35)</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>259.5</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>266.85</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>TATACONSUM</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>953.2</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>949.5</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>970.65</v>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>2.18% (21.15)</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>991.8</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>1012.95</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1704,7 +2304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M90"/>
+  <dimension ref="A1:M91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1790,23 +2390,23 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Week Range: (21-09-2026 to 27-09-2026)</t>
         </is>
       </c>
-      <c r="B2" s="6" t="n"/>
-      <c r="C2" s="6" t="n"/>
-      <c r="D2" s="6" t="n"/>
-      <c r="E2" s="6" t="n"/>
-      <c r="F2" s="6" t="n"/>
-      <c r="G2" s="6" t="n"/>
-      <c r="H2" s="6" t="n"/>
-      <c r="I2" s="6" t="n"/>
-      <c r="J2" s="6" t="n"/>
-      <c r="K2" s="6" t="n"/>
-      <c r="L2" s="6" t="n"/>
-      <c r="M2" s="6" t="n"/>
+      <c r="B2" s="7" t="n"/>
+      <c r="C2" s="7" t="n"/>
+      <c r="D2" s="7" t="n"/>
+      <c r="E2" s="7" t="n"/>
+      <c r="F2" s="7" t="n"/>
+      <c r="G2" s="7" t="n"/>
+      <c r="H2" s="7" t="n"/>
+      <c r="I2" s="7" t="n"/>
+      <c r="J2" s="7" t="n"/>
+      <c r="K2" s="7" t="n"/>
+      <c r="L2" s="7" t="n"/>
+      <c r="M2" s="7" t="n"/>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -1839,7 +2439,7 @@
           <t>2026-09-23 09:15</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="I3" s="8" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -1892,7 +2492,7 @@
           <t>2026-09-23 11:00</t>
         </is>
       </c>
-      <c r="I4" s="8" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -1945,7 +2545,7 @@
           <t>2026-09-23 14:15</t>
         </is>
       </c>
-      <c r="I5" s="8" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -1998,7 +2598,7 @@
           <t>2026-09-24 09:30</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2051,7 +2651,7 @@
           <t>2026-09-24 10:00</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2104,7 +2704,7 @@
           <t>2026-09-24 10:00</t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr">
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2157,7 +2757,7 @@
           <t>2026-09-24 12:30</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2210,7 +2810,7 @@
           <t>2026-09-25 10:00</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -2235,35 +2835,35 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>1242.8</v>
+        <v>1927</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1202.6</v>
+        <v>1915.1</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1246</v>
+        <v>1935.1</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>3.48% (43.4)</t>
+          <t>1.03% (20.0)</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1289.4</v>
+        <v>1955.1</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1332.8</v>
+        <v>1975.1</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
           <t>2026-09-25 14:00</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2274,10 +2874,10 @@
         </is>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1254.8</v>
+        <v>1942.9</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.71</v>
+        <v>0.4</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
@@ -2288,35 +2888,35 @@
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>1927</v>
+        <v>1242.8</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1915.1</v>
+        <v>1202.6</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1935.1</v>
+        <v>1246</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>1.03% (20.0)</t>
+          <t>3.48% (43.4)</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1955.1</v>
+        <v>1289.4</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1975.1</v>
+        <v>1332.8</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2026-09-25 14:00</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2327,10 +2927,10 @@
         </is>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1942.9</v>
+        <v>1254.8</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.4</v>
+        <v>0.71</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
@@ -2369,7 +2969,7 @@
           <t>2026-09-25 14:15</t>
         </is>
       </c>
-      <c r="I13" s="8" t="inlineStr">
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2422,7 +3022,7 @@
           <t>2026-09-25 14:15</t>
         </is>
       </c>
-      <c r="I14" s="8" t="inlineStr">
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2445,23 +3045,23 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>Week Range: (28-09-2026 to 04-10-2026)</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
-      <c r="I15" s="6" t="n"/>
-      <c r="J15" s="6" t="n"/>
-      <c r="K15" s="6" t="n"/>
-      <c r="L15" s="6" t="n"/>
-      <c r="M15" s="6" t="n"/>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="7" t="n"/>
+      <c r="I15" s="7" t="n"/>
+      <c r="J15" s="7" t="n"/>
+      <c r="K15" s="7" t="n"/>
+      <c r="L15" s="7" t="n"/>
+      <c r="M15" s="7" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -2547,7 +3147,7 @@
           <t>2026-09-28 11:30</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="I17" s="8" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -2600,7 +3200,7 @@
           <t>2026-09-28 12:00</t>
         </is>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="I18" s="8" t="inlineStr">
         <is>
           <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
@@ -2653,7 +3253,7 @@
           <t>2026-09-28 13:15</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
+      <c r="I19" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2759,7 +3359,7 @@
           <t>2026-09-28 14:00</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr">
+      <c r="I21" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2784,49 +3384,49 @@
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>171.35</v>
+        <v>906.9</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>171.05</v>
+        <v>889.7</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>172.2</v>
+        <v>907.5</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>0.67% (1.15)</t>
+          <t>1.96% (17.8)</t>
         </is>
       </c>
       <c r="F22" s="4" t="n">
-        <v>173.35</v>
+        <v>925.3</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>174.5</v>
+        <v>943.1</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t>2026-09-28 15:15</t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 15:15 (Week End)</t>
+          <t>2026-09-29 10:15</t>
         </is>
       </c>
       <c r="K22" s="2" t="n">
-        <v>172.45</v>
-      </c>
-      <c r="L22" s="4" t="n">
-        <v>0.15</v>
+        <v>889.7</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>-1.96</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
@@ -2837,49 +3437,49 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>906.9</v>
+        <v>171.35</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>889.7</v>
+        <v>171.05</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>907.5</v>
+        <v>172.2</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>1.96% (17.8)</t>
+          <t>0.67% (1.15)</t>
         </is>
       </c>
       <c r="F23" s="4" t="n">
-        <v>925.3</v>
+        <v>173.35</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>943.1</v>
+        <v>174.5</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
           <t>2026-09-28 15:15</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:15</t>
+          <t>2026-09-28 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K23" s="2" t="n">
-        <v>889.7</v>
-      </c>
-      <c r="L23" s="3" t="n">
-        <v>-1.96</v>
+        <v>172.45</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>0.15</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
@@ -2918,7 +3518,7 @@
           <t>2026-09-29 09:15</t>
         </is>
       </c>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="I24" s="8" t="inlineStr">
         <is>
           <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
@@ -3077,7 +3677,7 @@
           <t>2026-09-29 09:30</t>
         </is>
       </c>
-      <c r="I27" s="8" t="inlineStr">
+      <c r="I27" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3130,7 +3730,7 @@
           <t>2026-09-29 11:00</t>
         </is>
       </c>
-      <c r="I28" s="8" t="inlineStr">
+      <c r="I28" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3183,7 +3783,7 @@
           <t>2026-09-29 11:15</t>
         </is>
       </c>
-      <c r="I29" s="8" t="inlineStr">
+      <c r="I29" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3208,49 +3808,49 @@
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>1495.7</v>
+        <v>399.3</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1487.1</v>
+        <v>394.7</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1498</v>
+        <v>403.65</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>0.73% (10.9)</t>
+          <t>2.22% (8.95)</t>
         </is>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1508.9</v>
+        <v>412.6</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1519.8</v>
+        <v>421.55</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 11:30</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 12:30</t>
+          <t>2026-09-29 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K30" s="2" t="n">
-        <v>1487.1</v>
-      </c>
-      <c r="L30" s="3" t="n">
-        <v>-0.73</v>
+        <v>406</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>0.58</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
@@ -3261,49 +3861,49 @@
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>399.3</v>
+        <v>1495.7</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>394.7</v>
+        <v>1487.1</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>403.65</v>
+        <v>1498</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>2.22% (8.95)</t>
+          <t>0.73% (10.9)</t>
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>412.6</v>
+        <v>1508.9</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>421.55</v>
+        <v>1519.8</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 11:30</t>
         </is>
       </c>
-      <c r="I31" s="8" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:15 (Week End)</t>
+          <t>2026-09-29 12:30</t>
         </is>
       </c>
       <c r="K31" s="2" t="n">
-        <v>406</v>
-      </c>
-      <c r="L31" s="4" t="n">
-        <v>0.58</v>
+        <v>1487.1</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>-0.73</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
@@ -3342,7 +3942,7 @@
           <t>2026-09-29 11:45</t>
         </is>
       </c>
-      <c r="I32" s="8" t="inlineStr">
+      <c r="I32" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3395,7 +3995,7 @@
           <t>2026-09-29 12:00</t>
         </is>
       </c>
-      <c r="I33" s="8" t="inlineStr">
+      <c r="I33" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3448,7 +4048,7 @@
           <t>2026-09-29 13:00</t>
         </is>
       </c>
-      <c r="I34" s="8" t="inlineStr">
+      <c r="I34" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3501,7 +4101,7 @@
           <t>2026-09-29 14:00</t>
         </is>
       </c>
-      <c r="I35" s="8" t="inlineStr">
+      <c r="I35" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3554,7 +4154,7 @@
           <t>2026-09-29 14:00</t>
         </is>
       </c>
-      <c r="I36" s="7" t="inlineStr">
+      <c r="I36" s="8" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -3607,7 +4207,7 @@
           <t>2026-09-29 14:45</t>
         </is>
       </c>
-      <c r="I37" s="8" t="inlineStr">
+      <c r="I37" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3713,7 +4313,7 @@
           <t>2026-09-29 15:00</t>
         </is>
       </c>
-      <c r="I39" s="8" t="inlineStr">
+      <c r="I39" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3738,49 +4338,49 @@
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>263.55</v>
+        <v>1766.7</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>263.3</v>
+        <v>1736.8</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>266.2</v>
+        <v>1770.1</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>1.09% (2.9)</t>
+          <t>1.88% (33.3)</t>
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>269.1</v>
+        <v>1803.4</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>272</v>
+        <v>1836.7</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I40" s="5" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:15</t>
+          <t>2026-09-30 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K40" s="2" t="n">
-        <v>263.3</v>
-      </c>
-      <c r="L40" s="3" t="n">
-        <v>-1.09</v>
+        <v>1798.3</v>
+      </c>
+      <c r="L40" s="4" t="n">
+        <v>1.59</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
@@ -3791,28 +4391,28 @@
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>196.1</v>
+        <v>991.6</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>192.45</v>
+        <v>980.4</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>196.67</v>
+        <v>992.7</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>2.15% (4.22)</t>
+          <t>1.24% (12.3)</t>
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>200.89</v>
+        <v>1005</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>205.11</v>
+        <v>1017.3</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -3821,19 +4421,19 @@
       </c>
       <c r="I41" s="8" t="inlineStr">
         <is>
-          <t>ACTIVE (Week End)</t>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:15</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
       <c r="K41" s="2" t="n">
-        <v>200.89</v>
+        <v>1017.3</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>2.15</v>
+        <v>2.48</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
@@ -3844,49 +4444,49 @@
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>4057</v>
+        <v>2391</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>4043.3</v>
+        <v>2381.6</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>4095</v>
+        <v>2420</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>1.26% (51.7)</t>
+          <t>1.59% (38.4)</t>
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>4146.7</v>
+        <v>2458.4</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>4198.4</v>
+        <v>2496.8</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I42" s="7" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 09:15</t>
+          <t>2026-09-30 12:30 (Week End)</t>
         </is>
       </c>
       <c r="K42" s="2" t="n">
-        <v>4043.3</v>
+        <v>2409.1</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>-1.26</v>
+        <v>-0.45</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
@@ -3897,49 +4497,49 @@
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>399.3</v>
+        <v>4848.5</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>394.7</v>
+        <v>4837</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>403.65</v>
+        <v>4872</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>2.22% (8.95)</t>
+          <t>0.72% (35.0)</t>
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>412.6</v>
+        <v>4907</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>421.55</v>
+        <v>4942</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I43" s="7" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I43" s="8" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 09:15</t>
+          <t>2026-09-30 10:30</t>
         </is>
       </c>
       <c r="K43" s="2" t="n">
-        <v>421.55</v>
-      </c>
-      <c r="L43" s="4" t="n">
-        <v>4.43</v>
+        <v>4837</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>-0.72</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
@@ -3950,49 +4550,49 @@
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>4848.5</v>
+        <v>160.5</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>4837</v>
+        <v>159.41</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>4872</v>
+        <v>162.37</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>0.72% (35.0)</t>
+          <t>1.82% (2.96)</t>
         </is>
       </c>
       <c r="F44" s="4" t="n">
-        <v>4907</v>
+        <v>165.33</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>4942</v>
+        <v>168.29</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I44" s="7" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 10:30</t>
+          <t>2026-09-30 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K44" s="2" t="n">
-        <v>4837</v>
-      </c>
-      <c r="L44" s="3" t="n">
-        <v>-0.72</v>
+        <v>163.26</v>
+      </c>
+      <c r="L44" s="4" t="n">
+        <v>0.55</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
@@ -4003,49 +4603,49 @@
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>991.6</v>
+        <v>4057</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>980.4</v>
+        <v>4043.3</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>992.7</v>
+        <v>4095</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>1.24% (12.3)</t>
+          <t>1.26% (51.7)</t>
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>1005</v>
+        <v>4146.7</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>1017.3</v>
+        <v>4198.4</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I45" s="7" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I45" s="8" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="K45" s="2" t="n">
-        <v>1017.3</v>
-      </c>
-      <c r="L45" s="4" t="n">
-        <v>2.48</v>
+        <v>4043.3</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>-1.26</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
@@ -4056,49 +4656,49 @@
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>160.5</v>
+        <v>263.55</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>159.41</v>
+        <v>263.3</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>162.37</v>
+        <v>266.2</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>1.82% (2.96)</t>
+          <t>1.09% (2.9)</t>
         </is>
       </c>
       <c r="F46" s="4" t="n">
-        <v>165.33</v>
+        <v>269.1</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>168.29</v>
+        <v>272</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I46" s="8" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 15:15 (Week End)</t>
+          <t>2026-09-30 14:15</t>
         </is>
       </c>
       <c r="K46" s="2" t="n">
-        <v>163.26</v>
-      </c>
-      <c r="L46" s="4" t="n">
-        <v>0.55</v>
+        <v>263.3</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>-1.09</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
@@ -4109,28 +4709,28 @@
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>1766.7</v>
+        <v>399.3</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>1736.8</v>
+        <v>394.7</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>1770.1</v>
+        <v>403.65</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>1.88% (33.3)</t>
+          <t>2.22% (8.95)</t>
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>1803.4</v>
+        <v>412.6</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>1836.7</v>
+        <v>421.55</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -4139,19 +4739,19 @@
       </c>
       <c r="I47" s="8" t="inlineStr">
         <is>
-          <t>ACTIVE (Week End)</t>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 15:15 (Week End)</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="K47" s="2" t="n">
-        <v>1798.3</v>
+        <v>421.55</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>1.59</v>
+        <v>4.43</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
@@ -4162,49 +4762,49 @@
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>2391</v>
+        <v>196.1</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2381.6</v>
+        <v>192.45</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>2420</v>
+        <v>196.67</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>1.59% (38.4)</t>
+          <t>2.15% (4.22)</t>
         </is>
       </c>
       <c r="F48" s="4" t="n">
-        <v>2458.4</v>
+        <v>200.89</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>2496.8</v>
+        <v>205.11</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I48" s="8" t="inlineStr">
+      <c r="I48" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:30 (Week End)</t>
+          <t>2026-09-30 09:15</t>
         </is>
       </c>
       <c r="K48" s="2" t="n">
-        <v>2409.1</v>
-      </c>
-      <c r="L48" s="3" t="n">
-        <v>-0.45</v>
+        <v>200.89</v>
+      </c>
+      <c r="L48" s="4" t="n">
+        <v>2.15</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
@@ -4243,7 +4843,7 @@
           <t>2026-10-01 09:15</t>
         </is>
       </c>
-      <c r="I49" s="7" t="inlineStr">
+      <c r="I49" s="8" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -4296,7 +4896,7 @@
           <t>2026-10-01 09:15</t>
         </is>
       </c>
-      <c r="I50" s="8" t="inlineStr">
+      <c r="I50" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -4319,23 +4919,23 @@
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="6" t="inlineStr">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>Week Range: (05-10-2026 to 11-10-2026)</t>
         </is>
       </c>
-      <c r="B51" s="6" t="n"/>
-      <c r="C51" s="6" t="n"/>
-      <c r="D51" s="6" t="n"/>
-      <c r="E51" s="6" t="n"/>
-      <c r="F51" s="6" t="n"/>
-      <c r="G51" s="6" t="n"/>
-      <c r="H51" s="6" t="n"/>
-      <c r="I51" s="6" t="n"/>
-      <c r="J51" s="6" t="n"/>
-      <c r="K51" s="6" t="n"/>
-      <c r="L51" s="6" t="n"/>
-      <c r="M51" s="6" t="n"/>
+      <c r="B51" s="7" t="n"/>
+      <c r="C51" s="7" t="n"/>
+      <c r="D51" s="7" t="n"/>
+      <c r="E51" s="7" t="n"/>
+      <c r="F51" s="7" t="n"/>
+      <c r="G51" s="7" t="n"/>
+      <c r="H51" s="7" t="n"/>
+      <c r="I51" s="7" t="n"/>
+      <c r="J51" s="7" t="n"/>
+      <c r="K51" s="7" t="n"/>
+      <c r="L51" s="7" t="n"/>
+      <c r="M51" s="7" t="n"/>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
@@ -4368,7 +4968,7 @@
           <t>2026-10-06 09:15</t>
         </is>
       </c>
-      <c r="I52" s="7" t="inlineStr">
+      <c r="I52" s="8" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -4421,7 +5021,7 @@
           <t>2026-10-06 09:15</t>
         </is>
       </c>
-      <c r="I53" s="8" t="inlineStr">
+      <c r="I53" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -4474,7 +5074,7 @@
           <t>2026-10-06 09:15</t>
         </is>
       </c>
-      <c r="I54" s="8" t="inlineStr">
+      <c r="I54" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -4527,7 +5127,7 @@
           <t>2026-10-06 09:15</t>
         </is>
       </c>
-      <c r="I55" s="8" t="inlineStr">
+      <c r="I55" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -4552,49 +5152,49 @@
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>3709.5</v>
+        <v>168.43</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>3695</v>
+        <v>166.48</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>3723.8</v>
+        <v>168.99</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>0.77% (28.8)</t>
+          <t>1.49% (2.51)</t>
         </is>
       </c>
       <c r="F56" s="4" t="n">
-        <v>3752.6</v>
+        <v>171.5</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>3781.4</v>
+        <v>174.01</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
           <t>2026-10-07 09:15</t>
         </is>
       </c>
-      <c r="I56" s="7" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 09:15</t>
+          <t>2026-10-07 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K56" s="2" t="n">
-        <v>3781.4</v>
+        <v>170.71</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>1.55</v>
+        <v>1.02</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
@@ -4605,28 +5205,28 @@
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>168.43</v>
+        <v>1295</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>166.48</v>
+        <v>1293</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>168.99</v>
+        <v>1299.4</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>1.49% (2.51)</t>
+          <t>0.49% (6.4)</t>
         </is>
       </c>
       <c r="F57" s="4" t="n">
-        <v>171.5</v>
+        <v>1305.8</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>174.01</v>
+        <v>1312.2</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -4635,19 +5235,19 @@
       </c>
       <c r="I57" s="8" t="inlineStr">
         <is>
-          <t>ACTIVE (Week End)</t>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 15:15 (Week End)</t>
+          <t>2026-10-07 09:15</t>
         </is>
       </c>
       <c r="K57" s="2" t="n">
-        <v>170.71</v>
+        <v>1312.2</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>1.02</v>
+        <v>0.99</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
@@ -4658,35 +5258,35 @@
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>1295</v>
+        <v>3709.5</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>1293</v>
+        <v>3695</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>1299.4</v>
+        <v>3723.8</v>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>0.49% (6.4)</t>
+          <t>0.77% (28.8)</t>
         </is>
       </c>
       <c r="F58" s="4" t="n">
-        <v>1305.8</v>
+        <v>3752.6</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>1312.2</v>
+        <v>3781.4</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
           <t>2026-10-07 09:15</t>
         </is>
       </c>
-      <c r="I58" s="7" t="inlineStr">
+      <c r="I58" s="8" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -4697,10 +5297,10 @@
         </is>
       </c>
       <c r="K58" s="2" t="n">
-        <v>1312.2</v>
+        <v>3781.4</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>0.99</v>
+        <v>1.55</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
@@ -4792,7 +5392,7 @@
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I60" s="7" t="inlineStr">
+      <c r="I60" s="8" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -4845,7 +5445,7 @@
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I61" s="8" t="inlineStr">
+      <c r="I61" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -4898,7 +5498,7 @@
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I62" s="7" t="inlineStr">
+      <c r="I62" s="8" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -5004,7 +5604,7 @@
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I64" s="7" t="inlineStr">
+      <c r="I64" s="8" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -5057,7 +5657,7 @@
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I65" s="7" t="inlineStr">
+      <c r="I65" s="8" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -5080,70 +5680,70 @@
       </c>
     </row>
     <row r="66" ht="22" customHeight="1">
-      <c r="A66" s="6" t="inlineStr">
+      <c r="A66" s="7" t="inlineStr">
         <is>
           <t>Week Range: (12-10-2026 to 18-10-2026)</t>
         </is>
       </c>
-      <c r="B66" s="6" t="n"/>
-      <c r="C66" s="6" t="n"/>
-      <c r="D66" s="6" t="n"/>
-      <c r="E66" s="6" t="n"/>
-      <c r="F66" s="6" t="n"/>
-      <c r="G66" s="6" t="n"/>
-      <c r="H66" s="6" t="n"/>
-      <c r="I66" s="6" t="n"/>
-      <c r="J66" s="6" t="n"/>
-      <c r="K66" s="6" t="n"/>
-      <c r="L66" s="6" t="n"/>
-      <c r="M66" s="6" t="n"/>
+      <c r="B66" s="7" t="n"/>
+      <c r="C66" s="7" t="n"/>
+      <c r="D66" s="7" t="n"/>
+      <c r="E66" s="7" t="n"/>
+      <c r="F66" s="7" t="n"/>
+      <c r="G66" s="7" t="n"/>
+      <c r="H66" s="7" t="n"/>
+      <c r="I66" s="7" t="n"/>
+      <c r="J66" s="7" t="n"/>
+      <c r="K66" s="7" t="n"/>
+      <c r="L66" s="7" t="n"/>
+      <c r="M66" s="7" t="n"/>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>709.75</v>
+        <v>1124.6</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>708.8</v>
+        <v>1123.1</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>711.4</v>
+        <v>1131.1</v>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>0.37% (2.6)</t>
+          <t>0.71% (8.0)</t>
         </is>
       </c>
       <c r="F67" s="4" t="n">
-        <v>714</v>
+        <v>1139.1</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>716.6</v>
+        <v>1147.1</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
           <t>2026-10-13 09:15</t>
         </is>
       </c>
-      <c r="I67" s="7" t="inlineStr">
+      <c r="I67" s="8" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 09:45</t>
+          <t>2026-10-15 10:15</t>
         </is>
       </c>
       <c r="K67" s="2" t="n">
-        <v>716.6</v>
+        <v>1147.1</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>0.73</v>
+        <v>1.41</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
@@ -5182,7 +5782,7 @@
           <t>2026-10-13 09:15</t>
         </is>
       </c>
-      <c r="I68" s="8" t="inlineStr">
+      <c r="I68" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -5207,49 +5807,49 @@
     <row r="69" ht="18" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>1124.6</v>
+        <v>709.75</v>
       </c>
       <c r="C69" s="3" t="n">
-        <v>1123.1</v>
+        <v>708.8</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>1131.1</v>
+        <v>711.4</v>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>0.71% (8.0)</t>
+          <t>0.37% (2.6)</t>
         </is>
       </c>
       <c r="F69" s="4" t="n">
-        <v>1139.1</v>
+        <v>714</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>1147.1</v>
+        <v>716.6</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
           <t>2026-10-13 09:15</t>
         </is>
       </c>
-      <c r="I69" s="7" t="inlineStr">
+      <c r="I69" s="8" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 10:15</t>
+          <t>2026-10-13 09:45</t>
         </is>
       </c>
       <c r="K69" s="2" t="n">
-        <v>1147.1</v>
+        <v>716.6</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>1.41</v>
+        <v>0.73</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
@@ -5288,7 +5888,7 @@
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I70" s="8" t="inlineStr">
+      <c r="I70" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -5341,7 +5941,7 @@
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I71" s="7" t="inlineStr">
+      <c r="I71" s="8" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -5394,7 +5994,7 @@
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I72" s="7" t="inlineStr">
+      <c r="I72" s="8" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -5447,7 +6047,7 @@
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I73" s="8" t="inlineStr">
+      <c r="I73" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -5500,7 +6100,7 @@
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I74" s="7" t="inlineStr">
+      <c r="I74" s="8" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -5553,7 +6153,7 @@
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I75" s="7" t="inlineStr">
+      <c r="I75" s="8" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -5606,7 +6206,7 @@
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I76" s="8" t="inlineStr">
+      <c r="I76" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -5659,7 +6259,7 @@
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I77" s="7" t="inlineStr">
+      <c r="I77" s="8" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -5712,7 +6312,7 @@
           <t>2026-10-14 09:30</t>
         </is>
       </c>
-      <c r="I78" s="8" t="inlineStr">
+      <c r="I78" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -5765,7 +6365,7 @@
           <t>2026-10-14 09:45</t>
         </is>
       </c>
-      <c r="I79" s="7" t="inlineStr">
+      <c r="I79" s="8" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -5818,7 +6418,7 @@
           <t>2026-10-14 11:30</t>
         </is>
       </c>
-      <c r="I80" s="8" t="inlineStr">
+      <c r="I80" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -5924,7 +6524,7 @@
           <t>2026-10-15 09:15</t>
         </is>
       </c>
-      <c r="I82" s="8" t="inlineStr">
+      <c r="I82" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -5977,7 +6577,7 @@
           <t>2026-10-16 09:15</t>
         </is>
       </c>
-      <c r="I83" s="8" t="inlineStr">
+      <c r="I83" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -6030,7 +6630,7 @@
           <t>2026-10-16 09:15</t>
         </is>
       </c>
-      <c r="I84" s="8" t="inlineStr">
+      <c r="I84" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -6083,7 +6683,7 @@
           <t>2026-10-16 09:15</t>
         </is>
       </c>
-      <c r="I85" s="7" t="inlineStr">
+      <c r="I85" s="8" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -6136,7 +6736,7 @@
           <t>2026-10-16 09:15</t>
         </is>
       </c>
-      <c r="I86" s="8" t="inlineStr">
+      <c r="I86" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -6189,7 +6789,7 @@
           <t>2026-10-16 09:15</t>
         </is>
       </c>
-      <c r="I87" s="8" t="inlineStr">
+      <c r="I87" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -6212,49 +6812,49 @@
       </c>
     </row>
     <row r="88" ht="22" customHeight="1">
-      <c r="A88" s="6" t="inlineStr">
+      <c r="A88" s="7" t="inlineStr">
         <is>
           <t>Week Range: (19-10-2026 to 25-10-2026)</t>
         </is>
       </c>
-      <c r="B88" s="6" t="n"/>
-      <c r="C88" s="6" t="n"/>
-      <c r="D88" s="6" t="n"/>
-      <c r="E88" s="6" t="n"/>
-      <c r="F88" s="6" t="n"/>
-      <c r="G88" s="6" t="n"/>
-      <c r="H88" s="6" t="n"/>
-      <c r="I88" s="6" t="n"/>
-      <c r="J88" s="6" t="n"/>
-      <c r="K88" s="6" t="n"/>
-      <c r="L88" s="6" t="n"/>
-      <c r="M88" s="6" t="n"/>
+      <c r="B88" s="7" t="n"/>
+      <c r="C88" s="7" t="n"/>
+      <c r="D88" s="7" t="n"/>
+      <c r="E88" s="7" t="n"/>
+      <c r="F88" s="7" t="n"/>
+      <c r="G88" s="7" t="n"/>
+      <c r="H88" s="7" t="n"/>
+      <c r="I88" s="7" t="n"/>
+      <c r="J88" s="7" t="n"/>
+      <c r="K88" s="7" t="n"/>
+      <c r="L88" s="7" t="n"/>
+      <c r="M88" s="7" t="n"/>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>7688</v>
+        <v>4591.2</v>
       </c>
       <c r="C89" s="3" t="n">
-        <v>7677</v>
+        <v>4587</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>7729</v>
+        <v>4610</v>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>0.67% (52.0)</t>
+          <t>0.5% (23.0)</t>
         </is>
       </c>
       <c r="F89" s="4" t="n">
-        <v>7781</v>
+        <v>4633</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>7833</v>
+        <v>4656</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -6268,14 +6868,14 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 10:15</t>
+          <t>2026-10-21 09:15</t>
         </is>
       </c>
       <c r="K89" s="2" t="n">
-        <v>7677</v>
+        <v>4587</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>-0.67</v>
+        <v>-0.5</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
@@ -6286,28 +6886,28 @@
     <row r="90" ht="18" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>4591.2</v>
+        <v>7688</v>
       </c>
       <c r="C90" s="3" t="n">
-        <v>4587</v>
+        <v>7677</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>4610</v>
+        <v>7729</v>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>0.5% (23.0)</t>
+          <t>0.67% (52.0)</t>
         </is>
       </c>
       <c r="F90" s="4" t="n">
-        <v>4633</v>
+        <v>7781</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>4656</v>
+        <v>7833</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -6321,16 +6921,69 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 09:15</t>
+          <t>2026-10-21 10:15</t>
         </is>
       </c>
       <c r="K90" s="2" t="n">
-        <v>4587</v>
+        <v>7677</v>
       </c>
       <c r="L90" s="3" t="n">
-        <v>-0.5</v>
+        <v>-0.67</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>(19-10-2026 to 25-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="18" customHeight="1">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>NHPC</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="n">
+        <v>71.44</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>70.61</v>
+      </c>
+      <c r="D91" s="4" t="n">
+        <v>71.87</v>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>1.75% (1.26)</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="n">
+        <v>73.13</v>
+      </c>
+      <c r="G91" s="4" t="n">
+        <v>74.39</v>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>72.38</v>
+      </c>
+      <c r="L91" s="4" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
         <is>
           <t>(19-10-2026 to 25-10-2026)</t>
         </is>

--- a/data/trade_tracker_results.xlsx
+++ b/data/trade_tracker_results.xlsx
@@ -86,14 +86,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-        <bgColor rgb="00D9E1F2"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -135,10 +135,10 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -517,7 +517,7 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="33" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
@@ -595,42 +595,40 @@
         <v>7688</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>7677</v>
+        <v>7468</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>7729</v>
+        <v>7705</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>0.67% (52.0)</t>
+          <t>3.08% (237.0)</t>
         </is>
       </c>
       <c r="F2" s="4" t="n">
-        <v>7781</v>
+        <v>7942</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>7833</v>
+        <v>8179</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 09:15</t>
-        </is>
-      </c>
-      <c r="I2" s="5" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 10:15</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>7677</v>
-      </c>
-      <c r="L2" s="3" t="n">
-        <v>-0.67</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
@@ -847,22 +845,24 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-23 09:15</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="4" t="n">
-        <v>0</v>
+          <t>2026-10-23 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>4524.4</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>-1.04</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -1077,22 +1077,24 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-23 09:15</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="4" t="n">
-        <v>0</v>
+          <t>2026-10-23 09:30</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>164.88</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>-0.63</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -1353,22 +1355,24 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-23 09:15</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="4" t="n">
-        <v>0</v>
+          <t>2026-10-23 10:00</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>433.75</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>-1.02</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -1399,24 +1403,22 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
-        </is>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="n">
-        <v>72.38</v>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="4" t="n">
-        <v>0.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -1521,21 +1523,21 @@
         <v>1634.5</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1620</v>
+        <v>1609</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1667.3</v>
+        <v>1647.5</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>2.84% (47.3)</t>
+          <t>2.34% (38.5)</t>
         </is>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1714.6</v>
+        <v>1686</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1761.9</v>
+        <v>1724.5</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1585,22 +1587,24 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-23 09:15</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr"/>
+          <t>2026-10-23 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>1748</v>
+      </c>
       <c r="L23" s="4" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -1723,22 +1727,24 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-23 09:15</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr"/>
+          <t>2026-10-23 09:15</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>1134.3</v>
+      </c>
       <c r="L26" s="4" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -1797,21 +1803,21 @@
         <v>808.55</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>808.4</v>
+        <v>772.5</v>
       </c>
       <c r="D28" s="4" t="n">
         <v>821.75</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>1.62% (13.35)</t>
+          <t>5.99% (49.25)</t>
         </is>
       </c>
       <c r="F28" s="4" t="n">
-        <v>835.1</v>
+        <v>871</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>848.45</v>
+        <v>920.25</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1861,22 +1867,24 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-23 09:15</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr"/>
+          <t>2026-10-23 09:15</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>1331.3</v>
+      </c>
       <c r="L29" s="4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -1953,22 +1961,24 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-23 09:15</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr"/>
+          <t>2026-10-23 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>2894</v>
+      </c>
       <c r="L31" s="4" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -1981,21 +1991,21 @@
         <v>1814.4</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>1810.6</v>
+        <v>1781.1</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>1822.3</v>
+        <v>1834.9</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>0.64% (11.7)</t>
+          <t>2.93% (53.8)</t>
         </is>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1834</v>
+        <v>1888.7</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1845.7</v>
+        <v>1942.5</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2027,21 +2037,21 @@
         <v>256.95</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>256.45</v>
+        <v>254.85</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>260.35</v>
+        <v>257.05</v>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>1.5% (3.9)</t>
+          <t>0.86% (2.2)</t>
         </is>
       </c>
       <c r="F33" s="4" t="n">
-        <v>264.25</v>
+        <v>259.25</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>268.15</v>
+        <v>261.45</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2091,22 +2101,24 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-23 09:15</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="4" t="n">
-        <v>0</v>
+          <t>2026-10-23 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>1015.9</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>-1.18</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -2211,21 +2223,21 @@
         <v>245</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>244.8</v>
+        <v>242.3</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>252.15</v>
+        <v>248.4</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>2.91% (7.35)</t>
+          <t>2.46% (6.1)</t>
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>259.5</v>
+        <v>254.5</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>266.85</v>
+        <v>260.6</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -2257,21 +2269,21 @@
         <v>953.2</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>949.5</v>
+        <v>948.9</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>970.65</v>
+        <v>961.4</v>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>2.18% (21.15)</t>
+          <t>1.3% (12.5)</t>
         </is>
       </c>
       <c r="F38" s="4" t="n">
-        <v>991.8</v>
+        <v>973.9</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>1012.95</v>
+        <v>986.4</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2290,6 +2302,282 @@
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>8937.5</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>8797.5</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>8946.5</v>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>1.67% (149.0)</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>9095.5</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>9244.5</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>7008.5</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>6918</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>7084.5</v>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>2.35% (166.5)</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>7251</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>7417.5</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>GODREJCP</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>840.5</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>837.3</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>846</v>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>1.03% (8.7)</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>854.7</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>863.4</v>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>857.15</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>852</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>889.8</v>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>4.25% (37.8)</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>927.6</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>965.4</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>TATACOMM</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>1636.2</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>1605.1</v>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>1694</v>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>5.25% (88.9)</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>1782.9</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>1871.8</v>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>340.7</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>340.4</v>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>345.25</v>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>1.4% (4.85)</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>350.1</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>354.95</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2304,7 +2592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M91"/>
+  <dimension ref="A1:M99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2315,7 +2603,7 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="33" customWidth="1" min="9" max="9"/>
     <col width="29" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
@@ -2390,23 +2678,23 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Week Range: (21-09-2026 to 27-09-2026)</t>
         </is>
       </c>
-      <c r="B2" s="7" t="n"/>
-      <c r="C2" s="7" t="n"/>
-      <c r="D2" s="7" t="n"/>
-      <c r="E2" s="7" t="n"/>
-      <c r="F2" s="7" t="n"/>
-      <c r="G2" s="7" t="n"/>
-      <c r="H2" s="7" t="n"/>
-      <c r="I2" s="7" t="n"/>
-      <c r="J2" s="7" t="n"/>
-      <c r="K2" s="7" t="n"/>
-      <c r="L2" s="7" t="n"/>
-      <c r="M2" s="7" t="n"/>
+      <c r="B2" s="8" t="n"/>
+      <c r="C2" s="8" t="n"/>
+      <c r="D2" s="8" t="n"/>
+      <c r="E2" s="8" t="n"/>
+      <c r="F2" s="8" t="n"/>
+      <c r="G2" s="8" t="n"/>
+      <c r="H2" s="8" t="n"/>
+      <c r="I2" s="8" t="n"/>
+      <c r="J2" s="8" t="n"/>
+      <c r="K2" s="8" t="n"/>
+      <c r="L2" s="8" t="n"/>
+      <c r="M2" s="8" t="n"/>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -2439,7 +2727,7 @@
           <t>2026-09-23 09:15</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -2810,7 +3098,7 @@
           <t>2026-09-25 10:00</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -2941,28 +3229,28 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>3029.5</v>
+        <v>200.4</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>2967.1</v>
+        <v>196.1</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>3039</v>
+        <v>203.34</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>2.37% (71.9)</t>
+          <t>3.56% (7.24)</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>3110.9</v>
+        <v>210.58</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>3182.8</v>
+        <v>217.82</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -2976,14 +3264,14 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:00 (Week End)</t>
+          <t>2026-09-25 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K13" s="2" t="n">
-        <v>3035</v>
+        <v>202.75</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>-0.13</v>
+        <v>-0.29</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
@@ -2994,28 +3282,28 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>200.4</v>
+        <v>3029.5</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>196.1</v>
+        <v>2967.1</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>203.34</v>
+        <v>3039</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>3.56% (7.24)</t>
+          <t>2.37% (71.9)</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>210.58</v>
+        <v>3110.9</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>217.82</v>
+        <v>3182.8</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -3029,14 +3317,14 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:15 (Week End)</t>
+          <t>2026-09-25 15:00 (Week End)</t>
         </is>
       </c>
       <c r="K14" s="2" t="n">
-        <v>202.75</v>
+        <v>3035</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>-0.29</v>
+        <v>-0.13</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
@@ -3045,23 +3333,23 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>Week Range: (28-09-2026 to 04-10-2026)</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="n"/>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="7" t="n"/>
-      <c r="I15" s="7" t="n"/>
-      <c r="J15" s="7" t="n"/>
-      <c r="K15" s="7" t="n"/>
-      <c r="L15" s="7" t="n"/>
-      <c r="M15" s="7" t="n"/>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="8" t="n"/>
+      <c r="G15" s="8" t="n"/>
+      <c r="H15" s="8" t="n"/>
+      <c r="I15" s="8" t="n"/>
+      <c r="J15" s="8" t="n"/>
+      <c r="K15" s="8" t="n"/>
+      <c r="L15" s="8" t="n"/>
+      <c r="M15" s="8" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -3147,7 +3435,7 @@
           <t>2026-09-28 11:30</t>
         </is>
       </c>
-      <c r="I17" s="8" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -3200,7 +3488,7 @@
           <t>2026-09-28 12:00</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
@@ -3490,49 +3778,49 @@
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>864.2</v>
+        <v>906.9</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>859.7</v>
+        <v>889.7</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>864.8</v>
+        <v>907.5</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>0.59% (5.1)</t>
+          <t>1.96% (17.8)</t>
         </is>
       </c>
       <c r="F24" s="4" t="n">
-        <v>869.9</v>
+        <v>925.3</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>875</v>
+        <v>943.1</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 09:15</t>
         </is>
       </c>
-      <c r="I24" s="8" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 09:30</t>
+          <t>2026-09-29 10:15</t>
         </is>
       </c>
       <c r="K24" s="2" t="n">
-        <v>859.7</v>
+        <v>889.7</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>-0.59</v>
+        <v>-1.96</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
@@ -3543,28 +3831,28 @@
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>906.9</v>
+        <v>8821.5</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>889.7</v>
+        <v>8804.5</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>907.5</v>
+        <v>8893</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>1.96% (17.8)</t>
+          <t>1.0% (88.5)</t>
         </is>
       </c>
       <c r="F25" s="4" t="n">
-        <v>925.3</v>
+        <v>8981.5</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>943.1</v>
+        <v>9070</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -3578,14 +3866,14 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:15</t>
+          <t>2026-09-29 10:00</t>
         </is>
       </c>
       <c r="K25" s="2" t="n">
-        <v>889.7</v>
+        <v>8804.5</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>-1.96</v>
+        <v>-1</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
@@ -3596,49 +3884,49 @@
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>8821.5</v>
+        <v>864.2</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>8804.5</v>
+        <v>859.7</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>8893</v>
+        <v>864.8</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>1.0% (88.5)</t>
+          <t>0.59% (5.1)</t>
         </is>
       </c>
       <c r="F26" s="4" t="n">
-        <v>8981.5</v>
+        <v>869.9</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>9070</v>
+        <v>875</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 09:15</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:00</t>
+          <t>2026-09-29 09:30</t>
         </is>
       </c>
       <c r="K26" s="2" t="n">
-        <v>8804.5</v>
+        <v>859.7</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-1</v>
+        <v>-0.59</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
@@ -4154,7 +4442,7 @@
           <t>2026-09-29 14:00</t>
         </is>
       </c>
-      <c r="I36" s="8" t="inlineStr">
+      <c r="I36" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -4179,49 +4467,49 @@
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>1629.9</v>
+        <v>22165</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1600.2</v>
+        <v>22025</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>1642.9</v>
+        <v>22195</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>2.6% (42.7)</t>
+          <t>0.77% (170.0)</t>
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>1685.6</v>
+        <v>22365</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>1728.3</v>
+        <v>22535</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 14:45</t>
         </is>
       </c>
-      <c r="I37" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:15 (Week End)</t>
+          <t>2026-09-29 15:00</t>
         </is>
       </c>
       <c r="K37" s="2" t="n">
-        <v>1627.3</v>
+        <v>22025</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>-0.95</v>
+        <v>-0.77</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
@@ -4232,49 +4520,49 @@
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>22165</v>
+        <v>1629.9</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>22025</v>
+        <v>1600.2</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>22195</v>
+        <v>1642.9</v>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>0.77% (170.0)</t>
+          <t>2.6% (42.7)</t>
         </is>
       </c>
       <c r="F38" s="4" t="n">
-        <v>22365</v>
+        <v>1685.6</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>22535</v>
+        <v>1728.3</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 14:45</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:00</t>
+          <t>2026-09-29 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K38" s="2" t="n">
-        <v>22025</v>
+        <v>1627.3</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>-0.77</v>
+        <v>-0.95</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
@@ -4338,49 +4626,49 @@
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>1766.7</v>
+        <v>263.55</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1736.8</v>
+        <v>263.3</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>1770.1</v>
+        <v>266.2</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>1.88% (33.3)</t>
+          <t>1.09% (2.9)</t>
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>1803.4</v>
+        <v>269.1</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>1836.7</v>
+        <v>272</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I40" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 15:15 (Week End)</t>
+          <t>2026-09-30 14:15</t>
         </is>
       </c>
       <c r="K40" s="2" t="n">
-        <v>1798.3</v>
-      </c>
-      <c r="L40" s="4" t="n">
-        <v>1.59</v>
+        <v>263.3</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>-1.09</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
@@ -4391,49 +4679,49 @@
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>991.6</v>
+        <v>4057</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>980.4</v>
+        <v>4043.3</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>992.7</v>
+        <v>4095</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>1.24% (12.3)</t>
+          <t>1.26% (51.7)</t>
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>1005</v>
+        <v>4146.7</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>1017.3</v>
+        <v>4198.4</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I41" s="8" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="K41" s="2" t="n">
-        <v>1017.3</v>
-      </c>
-      <c r="L41" s="4" t="n">
-        <v>2.48</v>
+        <v>4043.3</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>-1.26</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
@@ -4444,28 +4732,28 @@
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>2391</v>
+        <v>160.5</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>2381.6</v>
+        <v>159.41</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>2420</v>
+        <v>162.37</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>1.59% (38.4)</t>
+          <t>1.82% (2.96)</t>
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>2458.4</v>
+        <v>165.33</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>2496.8</v>
+        <v>168.29</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -4479,14 +4767,14 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:30 (Week End)</t>
+          <t>2026-09-30 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K42" s="2" t="n">
-        <v>2409.1</v>
-      </c>
-      <c r="L42" s="3" t="n">
-        <v>-0.45</v>
+        <v>163.26</v>
+      </c>
+      <c r="L42" s="4" t="n">
+        <v>0.55</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
@@ -4497,49 +4785,49 @@
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>4848.5</v>
+        <v>399.3</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>4837</v>
+        <v>394.7</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>4872</v>
+        <v>403.65</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>0.72% (35.0)</t>
+          <t>2.22% (8.95)</t>
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>4907</v>
+        <v>412.6</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>4942</v>
+        <v>421.55</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I43" s="8" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 10:30</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="K43" s="2" t="n">
-        <v>4837</v>
-      </c>
-      <c r="L43" s="3" t="n">
-        <v>-0.72</v>
+        <v>421.55</v>
+      </c>
+      <c r="L43" s="4" t="n">
+        <v>4.43</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
@@ -4550,28 +4838,28 @@
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>160.5</v>
+        <v>2391</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>159.41</v>
+        <v>2381.6</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>162.37</v>
+        <v>2420</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>1.82% (2.96)</t>
+          <t>1.59% (38.4)</t>
         </is>
       </c>
       <c r="F44" s="4" t="n">
-        <v>165.33</v>
+        <v>2458.4</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>168.29</v>
+        <v>2496.8</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -4585,14 +4873,14 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 15:15 (Week End)</t>
+          <t>2026-09-30 12:30 (Week End)</t>
         </is>
       </c>
       <c r="K44" s="2" t="n">
-        <v>163.26</v>
-      </c>
-      <c r="L44" s="4" t="n">
-        <v>0.55</v>
+        <v>2409.1</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>-0.45</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
@@ -4603,49 +4891,49 @@
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>4057</v>
+        <v>991.6</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>4043.3</v>
+        <v>980.4</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>4095</v>
+        <v>992.7</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>1.26% (51.7)</t>
+          <t>1.24% (12.3)</t>
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>4146.7</v>
+        <v>1005</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>4198.4</v>
+        <v>1017.3</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I45" s="8" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 09:15</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
       <c r="K45" s="2" t="n">
-        <v>4043.3</v>
-      </c>
-      <c r="L45" s="3" t="n">
-        <v>-1.26</v>
+        <v>1017.3</v>
+      </c>
+      <c r="L45" s="4" t="n">
+        <v>2.48</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
@@ -4656,49 +4944,49 @@
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>263.55</v>
+        <v>1766.7</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>263.3</v>
+        <v>1736.8</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>266.2</v>
+        <v>1770.1</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>1.09% (2.9)</t>
+          <t>1.88% (33.3)</t>
         </is>
       </c>
       <c r="F46" s="4" t="n">
-        <v>269.1</v>
+        <v>1803.4</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>272</v>
+        <v>1836.7</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I46" s="5" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:15</t>
+          <t>2026-09-30 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K46" s="2" t="n">
-        <v>263.3</v>
-      </c>
-      <c r="L46" s="3" t="n">
-        <v>-1.09</v>
+        <v>1798.3</v>
+      </c>
+      <c r="L46" s="4" t="n">
+        <v>1.59</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
@@ -4709,49 +4997,49 @@
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>399.3</v>
+        <v>4848.5</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>394.7</v>
+        <v>4837</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>403.65</v>
+        <v>4872</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>2.22% (8.95)</t>
+          <t>0.72% (35.0)</t>
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>412.6</v>
+        <v>4907</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>421.55</v>
+        <v>4942</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I47" s="8" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 09:15</t>
+          <t>2026-09-30 10:30</t>
         </is>
       </c>
       <c r="K47" s="2" t="n">
-        <v>421.55</v>
-      </c>
-      <c r="L47" s="4" t="n">
-        <v>4.43</v>
+        <v>4837</v>
+      </c>
+      <c r="L47" s="3" t="n">
+        <v>-0.72</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
@@ -4815,49 +5103,49 @@
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>514</v>
+        <v>721.95</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>513.5</v>
+        <v>704.8</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>516.1</v>
+        <v>726.45</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>0.5% (2.6)</t>
+          <t>2.98% (21.65)</t>
         </is>
       </c>
       <c r="F49" s="4" t="n">
-        <v>518.7</v>
+        <v>748.1</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>521.3</v>
+        <v>769.75</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
           <t>2026-10-01 09:15</t>
         </is>
       </c>
-      <c r="I49" s="8" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 09:15</t>
+          <t>2026-10-01 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K49" s="2" t="n">
-        <v>521.3</v>
-      </c>
-      <c r="L49" s="4" t="n">
-        <v>1.01</v>
+        <v>718</v>
+      </c>
+      <c r="L49" s="3" t="n">
+        <v>-1.16</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
@@ -4868,49 +5156,49 @@
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>721.95</v>
+        <v>514</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>704.8</v>
+        <v>513.5</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>726.45</v>
+        <v>516.1</v>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>2.98% (21.65)</t>
+          <t>0.5% (2.6)</t>
         </is>
       </c>
       <c r="F50" s="4" t="n">
-        <v>748.1</v>
+        <v>518.7</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>769.75</v>
+        <v>521.3</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
           <t>2026-10-01 09:15</t>
         </is>
       </c>
-      <c r="I50" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I50" s="7" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 15:15 (Week End)</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="K50" s="2" t="n">
-        <v>718</v>
-      </c>
-      <c r="L50" s="3" t="n">
-        <v>-1.16</v>
+        <v>521.3</v>
+      </c>
+      <c r="L50" s="4" t="n">
+        <v>1.01</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
@@ -4919,23 +5207,23 @@
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="7" t="inlineStr">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>Week Range: (05-10-2026 to 11-10-2026)</t>
         </is>
       </c>
-      <c r="B51" s="7" t="n"/>
-      <c r="C51" s="7" t="n"/>
-      <c r="D51" s="7" t="n"/>
-      <c r="E51" s="7" t="n"/>
-      <c r="F51" s="7" t="n"/>
-      <c r="G51" s="7" t="n"/>
-      <c r="H51" s="7" t="n"/>
-      <c r="I51" s="7" t="n"/>
-      <c r="J51" s="7" t="n"/>
-      <c r="K51" s="7" t="n"/>
-      <c r="L51" s="7" t="n"/>
-      <c r="M51" s="7" t="n"/>
+      <c r="B51" s="8" t="n"/>
+      <c r="C51" s="8" t="n"/>
+      <c r="D51" s="8" t="n"/>
+      <c r="E51" s="8" t="n"/>
+      <c r="F51" s="8" t="n"/>
+      <c r="G51" s="8" t="n"/>
+      <c r="H51" s="8" t="n"/>
+      <c r="I51" s="8" t="n"/>
+      <c r="J51" s="8" t="n"/>
+      <c r="K51" s="8" t="n"/>
+      <c r="L51" s="8" t="n"/>
+      <c r="M51" s="8" t="n"/>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
@@ -4968,7 +5256,7 @@
           <t>2026-10-06 09:15</t>
         </is>
       </c>
-      <c r="I52" s="8" t="inlineStr">
+      <c r="I52" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -5233,7 +5521,7 @@
           <t>2026-10-07 09:15</t>
         </is>
       </c>
-      <c r="I57" s="8" t="inlineStr">
+      <c r="I57" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -5286,7 +5574,7 @@
           <t>2026-10-07 09:15</t>
         </is>
       </c>
-      <c r="I58" s="8" t="inlineStr">
+      <c r="I58" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -5364,49 +5652,49 @@
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>LTM</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>3936</v>
+        <v>1674.8</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>3908.4</v>
+        <v>1658.6</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>3941.6</v>
+        <v>1684.2</v>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>0.84% (33.2)</t>
+          <t>1.52% (25.6)</t>
         </is>
       </c>
       <c r="F60" s="4" t="n">
-        <v>3974.8</v>
+        <v>1709.8</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>4008</v>
+        <v>1735.4</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I60" s="8" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 09:15</t>
+          <t>2026-10-09 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K60" s="2" t="n">
-        <v>4008</v>
-      </c>
-      <c r="L60" s="4" t="n">
-        <v>1.68</v>
+        <v>1682</v>
+      </c>
+      <c r="L60" s="3" t="n">
+        <v>-0.13</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
@@ -5417,49 +5705,49 @@
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>1674.8</v>
+        <v>1316.5</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>1658.6</v>
+        <v>1308.7</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>1684.2</v>
+        <v>1323.7</v>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>1.52% (25.6)</t>
+          <t>1.13% (15.0)</t>
         </is>
       </c>
       <c r="F61" s="4" t="n">
-        <v>1709.8</v>
+        <v>1338.7</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>1735.4</v>
+        <v>1353.7</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I61" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I61" s="7" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 15:15 (Week End)</t>
+          <t>2026-10-09 10:15</t>
         </is>
       </c>
       <c r="K61" s="2" t="n">
-        <v>1682</v>
-      </c>
-      <c r="L61" s="3" t="n">
-        <v>-0.13</v>
+        <v>1353.7</v>
+      </c>
+      <c r="L61" s="4" t="n">
+        <v>2.27</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
@@ -5470,49 +5758,49 @@
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>254.65</v>
+        <v>1702.1</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>253.2</v>
+        <v>1701</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>255.4</v>
+        <v>1710.1</v>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>0.86% (2.2)</t>
+          <t>0.53% (9.1)</t>
         </is>
       </c>
       <c r="F62" s="4" t="n">
-        <v>257.6</v>
+        <v>1719.2</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>259.8</v>
+        <v>1728.3</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I62" s="8" t="inlineStr">
+      <c r="I62" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 10:00</t>
+          <t>2026-10-09 09:45</t>
         </is>
       </c>
       <c r="K62" s="2" t="n">
-        <v>259.8</v>
+        <v>1728.3</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>1.72</v>
+        <v>1.06</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
@@ -5523,37 +5811,37 @@
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>LTM</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>902.05</v>
+        <v>3936</v>
       </c>
       <c r="C63" s="3" t="n">
-        <v>891.8</v>
+        <v>3908.4</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>903</v>
+        <v>3941.6</v>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>1.24% (11.2)</t>
+          <t>0.84% (33.2)</t>
         </is>
       </c>
       <c r="F63" s="4" t="n">
-        <v>914.2</v>
+        <v>3974.8</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>925.4</v>
+        <v>4008</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I63" s="5" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I63" s="7" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -5562,10 +5850,10 @@
         </is>
       </c>
       <c r="K63" s="2" t="n">
-        <v>891.8</v>
-      </c>
-      <c r="L63" s="3" t="n">
-        <v>-1.24</v>
+        <v>4008</v>
+      </c>
+      <c r="L63" s="4" t="n">
+        <v>1.68</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
@@ -5576,49 +5864,49 @@
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>1702.1</v>
+        <v>254.65</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1701</v>
+        <v>253.2</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>1710.1</v>
+        <v>255.4</v>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>0.53% (9.1)</t>
+          <t>0.86% (2.2)</t>
         </is>
       </c>
       <c r="F64" s="4" t="n">
-        <v>1719.2</v>
+        <v>257.6</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>1728.3</v>
+        <v>259.8</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I64" s="8" t="inlineStr">
+      <c r="I64" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 09:45</t>
+          <t>2026-10-09 10:00</t>
         </is>
       </c>
       <c r="K64" s="2" t="n">
-        <v>1728.3</v>
+        <v>259.8</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>1.06</v>
+        <v>1.72</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
@@ -5629,49 +5917,49 @@
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>1316.5</v>
+        <v>902.05</v>
       </c>
       <c r="C65" s="3" t="n">
-        <v>1308.7</v>
+        <v>891.8</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>1323.7</v>
+        <v>903</v>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>1.13% (15.0)</t>
+          <t>1.24% (11.2)</t>
         </is>
       </c>
       <c r="F65" s="4" t="n">
-        <v>1338.7</v>
+        <v>914.2</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>1353.7</v>
+        <v>925.4</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I65" s="8" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 10:15</t>
+          <t>2026-10-09 09:15</t>
         </is>
       </c>
       <c r="K65" s="2" t="n">
-        <v>1353.7</v>
-      </c>
-      <c r="L65" s="4" t="n">
-        <v>2.27</v>
+        <v>891.8</v>
+      </c>
+      <c r="L65" s="3" t="n">
+        <v>-1.24</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
@@ -5680,70 +5968,70 @@
       </c>
     </row>
     <row r="66" ht="22" customHeight="1">
-      <c r="A66" s="7" t="inlineStr">
+      <c r="A66" s="8" t="inlineStr">
         <is>
           <t>Week Range: (12-10-2026 to 18-10-2026)</t>
         </is>
       </c>
-      <c r="B66" s="7" t="n"/>
-      <c r="C66" s="7" t="n"/>
-      <c r="D66" s="7" t="n"/>
-      <c r="E66" s="7" t="n"/>
-      <c r="F66" s="7" t="n"/>
-      <c r="G66" s="7" t="n"/>
-      <c r="H66" s="7" t="n"/>
-      <c r="I66" s="7" t="n"/>
-      <c r="J66" s="7" t="n"/>
-      <c r="K66" s="7" t="n"/>
-      <c r="L66" s="7" t="n"/>
-      <c r="M66" s="7" t="n"/>
+      <c r="B66" s="8" t="n"/>
+      <c r="C66" s="8" t="n"/>
+      <c r="D66" s="8" t="n"/>
+      <c r="E66" s="8" t="n"/>
+      <c r="F66" s="8" t="n"/>
+      <c r="G66" s="8" t="n"/>
+      <c r="H66" s="8" t="n"/>
+      <c r="I66" s="8" t="n"/>
+      <c r="J66" s="8" t="n"/>
+      <c r="K66" s="8" t="n"/>
+      <c r="L66" s="8" t="n"/>
+      <c r="M66" s="8" t="n"/>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>1124.6</v>
+        <v>709.75</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>1123.1</v>
+        <v>708.8</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>1131.1</v>
+        <v>711.4</v>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>0.71% (8.0)</t>
+          <t>0.37% (2.6)</t>
         </is>
       </c>
       <c r="F67" s="4" t="n">
-        <v>1139.1</v>
+        <v>714</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>1147.1</v>
+        <v>716.6</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
           <t>2026-10-13 09:15</t>
         </is>
       </c>
-      <c r="I67" s="8" t="inlineStr">
+      <c r="I67" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 10:15</t>
+          <t>2026-10-13 09:45</t>
         </is>
       </c>
       <c r="K67" s="2" t="n">
-        <v>1147.1</v>
+        <v>716.6</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>1.41</v>
+        <v>0.73</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
@@ -5754,49 +6042,49 @@
     <row r="68" ht="18" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>1658.1</v>
+        <v>1124.6</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>1658</v>
+        <v>1123.1</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>1673.9</v>
+        <v>1131.1</v>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>0.95% (15.9)</t>
+          <t>0.71% (8.0)</t>
         </is>
       </c>
       <c r="F68" s="4" t="n">
-        <v>1689.8</v>
+        <v>1139.1</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>1705.7</v>
+        <v>1147.1</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
           <t>2026-10-13 09:15</t>
         </is>
       </c>
-      <c r="I68" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I68" s="7" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 09:30</t>
+          <t>2026-10-15 10:15</t>
         </is>
       </c>
       <c r="K68" s="2" t="n">
-        <v>1689.8</v>
+        <v>1147.1</v>
       </c>
       <c r="L68" s="4" t="n">
-        <v>0.95</v>
+        <v>1.41</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
@@ -5807,49 +6095,49 @@
     <row r="69" ht="18" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>709.75</v>
+        <v>1658.1</v>
       </c>
       <c r="C69" s="3" t="n">
-        <v>708.8</v>
+        <v>1658</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>711.4</v>
+        <v>1673.9</v>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>0.37% (2.6)</t>
+          <t>0.95% (15.9)</t>
         </is>
       </c>
       <c r="F69" s="4" t="n">
-        <v>714</v>
+        <v>1689.8</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>716.6</v>
+        <v>1705.7</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
           <t>2026-10-13 09:15</t>
         </is>
       </c>
-      <c r="I69" s="8" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 09:45</t>
+          <t>2026-10-13 09:30</t>
         </is>
       </c>
       <c r="K69" s="2" t="n">
-        <v>716.6</v>
+        <v>1689.8</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>0.73</v>
+        <v>0.95</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
@@ -5860,28 +6148,28 @@
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>403.85</v>
+        <v>857</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>402.15</v>
+        <v>846.1</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>410.15</v>
+        <v>861.85</v>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>1.95% (8.0)</t>
+          <t>1.83% (15.75)</t>
         </is>
       </c>
       <c r="F70" s="4" t="n">
-        <v>418.15</v>
+        <v>877.6</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>426.15</v>
+        <v>893.35</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -5895,14 +6183,14 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 11:45</t>
+          <t>2026-10-14 09:30</t>
         </is>
       </c>
       <c r="K70" s="2" t="n">
-        <v>418.15</v>
+        <v>877.6</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
@@ -5913,35 +6201,35 @@
     <row r="71" ht="18" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>373.3</v>
+        <v>1828</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>373</v>
+        <v>1818.5</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>375.4</v>
+        <v>1829.2</v>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>0.64% (2.4)</t>
+          <t>0.58% (10.7)</t>
         </is>
       </c>
       <c r="F71" s="4" t="n">
-        <v>377.8</v>
+        <v>1839.9</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>380.2</v>
+        <v>1850.6</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I71" s="8" t="inlineStr">
+      <c r="I71" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -5952,10 +6240,10 @@
         </is>
       </c>
       <c r="K71" s="2" t="n">
-        <v>380.2</v>
+        <v>1850.6</v>
       </c>
       <c r="L71" s="4" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
@@ -5966,49 +6254,49 @@
     <row r="72" ht="18" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>461</v>
+        <v>1160.2</v>
       </c>
       <c r="C72" s="3" t="n">
-        <v>457.5</v>
+        <v>1152.6</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>461.75</v>
+        <v>1166.7</v>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>0.92% (4.25)</t>
+          <t>1.21% (14.1)</t>
         </is>
       </c>
       <c r="F72" s="4" t="n">
-        <v>466</v>
+        <v>1180.8</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>470.25</v>
+        <v>1194.9</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I72" s="8" t="inlineStr">
+      <c r="I72" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 09:30</t>
+          <t>2026-10-15 10:00</t>
         </is>
       </c>
       <c r="K72" s="2" t="n">
-        <v>470.25</v>
+        <v>1194.9</v>
       </c>
       <c r="L72" s="4" t="n">
-        <v>1.84</v>
+        <v>2.42</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
@@ -6019,49 +6307,49 @@
     <row r="73" ht="18" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>441.05</v>
+        <v>1486.2</v>
       </c>
       <c r="C73" s="3" t="n">
-        <v>440.55</v>
+        <v>1443.3</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>445.8</v>
+        <v>1508</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>1.18% (5.25)</t>
+          <t>4.29% (64.7)</t>
         </is>
       </c>
       <c r="F73" s="4" t="n">
-        <v>451.05</v>
+        <v>1572.7</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>456.3</v>
+        <v>1637.4</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I73" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I73" s="7" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 11:00</t>
+          <t>2026-10-15 13:15</t>
         </is>
       </c>
       <c r="K73" s="2" t="n">
-        <v>451.05</v>
+        <v>1637.4</v>
       </c>
       <c r="L73" s="4" t="n">
-        <v>1.18</v>
+        <v>8.58</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
@@ -6072,49 +6360,49 @@
     <row r="74" ht="18" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>1486.2</v>
+        <v>461</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>1443.3</v>
+        <v>457.5</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>1508</v>
+        <v>461.75</v>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>4.29% (64.7)</t>
+          <t>0.92% (4.25)</t>
         </is>
       </c>
       <c r="F74" s="4" t="n">
-        <v>1572.7</v>
+        <v>466</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>1637.4</v>
+        <v>470.25</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I74" s="8" t="inlineStr">
+      <c r="I74" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 13:15</t>
+          <t>2026-10-14 09:30</t>
         </is>
       </c>
       <c r="K74" s="2" t="n">
-        <v>1637.4</v>
+        <v>470.25</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>8.58</v>
+        <v>1.84</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
@@ -6125,35 +6413,35 @@
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>1828</v>
+        <v>373.3</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>1818.5</v>
+        <v>373</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>1829.2</v>
+        <v>375.4</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>0.58% (10.7)</t>
+          <t>0.64% (2.4)</t>
         </is>
       </c>
       <c r="F75" s="4" t="n">
-        <v>1839.9</v>
+        <v>377.8</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>1850.6</v>
+        <v>380.2</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I75" s="8" t="inlineStr">
+      <c r="I75" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -6164,10 +6452,10 @@
         </is>
       </c>
       <c r="K75" s="2" t="n">
-        <v>1850.6</v>
+        <v>380.2</v>
       </c>
       <c r="L75" s="4" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
@@ -6178,28 +6466,28 @@
     <row r="76" ht="18" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>857</v>
+        <v>403.85</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>846.1</v>
+        <v>402.15</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>861.85</v>
+        <v>410.15</v>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>1.83% (15.75)</t>
+          <t>1.95% (8.0)</t>
         </is>
       </c>
       <c r="F76" s="4" t="n">
-        <v>877.6</v>
+        <v>418.15</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>893.35</v>
+        <v>426.15</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -6213,14 +6501,14 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 09:30</t>
+          <t>2026-10-14 11:45</t>
         </is>
       </c>
       <c r="K76" s="2" t="n">
-        <v>877.6</v>
+        <v>418.15</v>
       </c>
       <c r="L76" s="4" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
@@ -6231,49 +6519,49 @@
     <row r="77" ht="18" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>1160.2</v>
+        <v>441.05</v>
       </c>
       <c r="C77" s="3" t="n">
-        <v>1152.6</v>
+        <v>440.55</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>1166.7</v>
+        <v>445.8</v>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>1.21% (14.1)</t>
+          <t>1.18% (5.25)</t>
         </is>
       </c>
       <c r="F77" s="4" t="n">
-        <v>1180.8</v>
+        <v>451.05</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>1194.9</v>
+        <v>456.3</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I77" s="8" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 10:00</t>
+          <t>2026-10-14 11:00</t>
         </is>
       </c>
       <c r="K77" s="2" t="n">
-        <v>1194.9</v>
+        <v>451.05</v>
       </c>
       <c r="L77" s="4" t="n">
-        <v>2.42</v>
+        <v>1.18</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
@@ -6365,7 +6653,7 @@
           <t>2026-10-14 09:45</t>
         </is>
       </c>
-      <c r="I79" s="8" t="inlineStr">
+      <c r="I79" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -6549,28 +6837,28 @@
     <row r="83" ht="18" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>886.5</v>
+        <v>3607</v>
       </c>
       <c r="C83" s="3" t="n">
-        <v>860.1</v>
+        <v>3593.2</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>887</v>
+        <v>3627.5</v>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>3.03% (26.9)</t>
+          <t>0.95% (34.3)</t>
         </is>
       </c>
       <c r="F83" s="4" t="n">
-        <v>913.9</v>
+        <v>3661.8</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>940.8</v>
+        <v>3696.1</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -6584,14 +6872,14 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 15:15 (Week End)</t>
+          <t>2026-10-16 11:30</t>
         </is>
       </c>
       <c r="K83" s="2" t="n">
-        <v>908</v>
+        <v>3661.8</v>
       </c>
       <c r="L83" s="4" t="n">
-        <v>2.37</v>
+        <v>0.95</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
@@ -6602,28 +6890,28 @@
     <row r="84" ht="18" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>3607</v>
+        <v>886.5</v>
       </c>
       <c r="C84" s="3" t="n">
-        <v>3593.2</v>
+        <v>860.1</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>3627.5</v>
+        <v>887</v>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>0.95% (34.3)</t>
+          <t>3.03% (26.9)</t>
         </is>
       </c>
       <c r="F84" s="4" t="n">
-        <v>3661.8</v>
+        <v>913.9</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>3696.1</v>
+        <v>940.8</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -6637,14 +6925,14 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 11:30</t>
+          <t>2026-10-16 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K84" s="2" t="n">
-        <v>3661.8</v>
+        <v>908</v>
       </c>
       <c r="L84" s="4" t="n">
-        <v>0.95</v>
+        <v>2.37</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
@@ -6683,7 +6971,7 @@
           <t>2026-10-16 09:15</t>
         </is>
       </c>
-      <c r="I85" s="8" t="inlineStr">
+      <c r="I85" s="7" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -6812,49 +7100,49 @@
       </c>
     </row>
     <row r="88" ht="22" customHeight="1">
-      <c r="A88" s="7" t="inlineStr">
+      <c r="A88" s="8" t="inlineStr">
         <is>
           <t>Week Range: (19-10-2026 to 25-10-2026)</t>
         </is>
       </c>
-      <c r="B88" s="7" t="n"/>
-      <c r="C88" s="7" t="n"/>
-      <c r="D88" s="7" t="n"/>
-      <c r="E88" s="7" t="n"/>
-      <c r="F88" s="7" t="n"/>
-      <c r="G88" s="7" t="n"/>
-      <c r="H88" s="7" t="n"/>
-      <c r="I88" s="7" t="n"/>
-      <c r="J88" s="7" t="n"/>
-      <c r="K88" s="7" t="n"/>
-      <c r="L88" s="7" t="n"/>
-      <c r="M88" s="7" t="n"/>
+      <c r="B88" s="8" t="n"/>
+      <c r="C88" s="8" t="n"/>
+      <c r="D88" s="8" t="n"/>
+      <c r="E88" s="8" t="n"/>
+      <c r="F88" s="8" t="n"/>
+      <c r="G88" s="8" t="n"/>
+      <c r="H88" s="8" t="n"/>
+      <c r="I88" s="8" t="n"/>
+      <c r="J88" s="8" t="n"/>
+      <c r="K88" s="8" t="n"/>
+      <c r="L88" s="8" t="n"/>
+      <c r="M88" s="8" t="n"/>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>4591.2</v>
+        <v>7688</v>
       </c>
       <c r="C89" s="3" t="n">
-        <v>4587</v>
+        <v>7677</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>4610</v>
+        <v>7729</v>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>0.5% (23.0)</t>
+          <t>0.67% (52.0)</t>
         </is>
       </c>
       <c r="F89" s="4" t="n">
-        <v>4633</v>
+        <v>7781</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>4656</v>
+        <v>7833</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -6868,14 +7156,14 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 09:15</t>
+          <t>2026-10-21 10:15</t>
         </is>
       </c>
       <c r="K89" s="2" t="n">
-        <v>4587</v>
+        <v>7677</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>-0.5</v>
+        <v>-0.67</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
@@ -6886,28 +7174,28 @@
     <row r="90" ht="18" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>7688</v>
+        <v>4591.2</v>
       </c>
       <c r="C90" s="3" t="n">
-        <v>7677</v>
+        <v>4587</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>7729</v>
+        <v>4610</v>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>0.67% (52.0)</t>
+          <t>0.5% (23.0)</t>
         </is>
       </c>
       <c r="F90" s="4" t="n">
-        <v>7781</v>
+        <v>4633</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>7833</v>
+        <v>4656</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -6921,14 +7209,14 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 10:15</t>
+          <t>2026-10-21 09:15</t>
         </is>
       </c>
       <c r="K90" s="2" t="n">
-        <v>7677</v>
+        <v>4587</v>
       </c>
       <c r="L90" s="3" t="n">
-        <v>-0.67</v>
+        <v>-0.5</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
@@ -6984,6 +7272,430 @@
         <v>0.71</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>(19-10-2026 to 25-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="n">
+        <v>1107.3</v>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>1100.3</v>
+      </c>
+      <c r="D92" s="4" t="n">
+        <v>1117.3</v>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>1.52% (17.0)</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="n">
+        <v>1134.3</v>
+      </c>
+      <c r="G92" s="4" t="n">
+        <v>1151.3</v>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 09:15</t>
+        </is>
+      </c>
+      <c r="I92" s="7" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 09:15</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>1134.3</v>
+      </c>
+      <c r="L92" s="4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>(19-10-2026 to 25-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="n">
+        <v>1300.2</v>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>1296.7</v>
+      </c>
+      <c r="D93" s="4" t="n">
+        <v>1314</v>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>1.32% (17.3)</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="n">
+        <v>1331.3</v>
+      </c>
+      <c r="G93" s="4" t="n">
+        <v>1348.6</v>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 09:15</t>
+        </is>
+      </c>
+      <c r="I93" s="7" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 09:15</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>1331.3</v>
+      </c>
+      <c r="L93" s="4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>(19-10-2026 to 25-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="n">
+        <v>1725.5</v>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>1719.6</v>
+      </c>
+      <c r="D94" s="4" t="n">
+        <v>1745.1</v>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>1.46% (25.5)</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="n">
+        <v>1770.6</v>
+      </c>
+      <c r="G94" s="4" t="n">
+        <v>1796.1</v>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 09:15</t>
+        </is>
+      </c>
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>1748</v>
+      </c>
+      <c r="L94" s="4" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>(19-10-2026 to 25-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="n">
+        <v>2843.4</v>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>2828.2</v>
+      </c>
+      <c r="D95" s="4" t="n">
+        <v>2889.1</v>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>2.11% (60.9)</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="n">
+        <v>2950</v>
+      </c>
+      <c r="G95" s="4" t="n">
+        <v>3010.9</v>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 09:15</t>
+        </is>
+      </c>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>2894</v>
+      </c>
+      <c r="L95" s="4" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>(19-10-2026 to 25-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="18" customHeight="1">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="n">
+        <v>165.87</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>164.88</v>
+      </c>
+      <c r="D96" s="4" t="n">
+        <v>165.92</v>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>0.63% (1.04)</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="n">
+        <v>166.96</v>
+      </c>
+      <c r="G96" s="4" t="n">
+        <v>168</v>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 09:15</t>
+        </is>
+      </c>
+      <c r="I96" s="7" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Then SL)</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 09:30</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>164.88</v>
+      </c>
+      <c r="L96" s="3" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>(19-10-2026 to 25-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="n">
+        <v>4550.4</v>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>4474.6</v>
+      </c>
+      <c r="D97" s="4" t="n">
+        <v>4572.1</v>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>2.13% (97.5)</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="n">
+        <v>4669.6</v>
+      </c>
+      <c r="G97" s="4" t="n">
+        <v>4767.1</v>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 09:15</t>
+        </is>
+      </c>
+      <c r="I97" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>4524.4</v>
+      </c>
+      <c r="L97" s="3" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>(19-10-2026 to 25-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="18" customHeight="1">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="n">
+        <v>437.2</v>
+      </c>
+      <c r="C98" s="3" t="n">
+        <v>433.75</v>
+      </c>
+      <c r="D98" s="4" t="n">
+        <v>438.2</v>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>1.02% (4.45)</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="n">
+        <v>442.65</v>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>447.1</v>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 09:15</t>
+        </is>
+      </c>
+      <c r="I98" s="5" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:00</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>433.75</v>
+      </c>
+      <c r="L98" s="3" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>(19-10-2026 to 25-10-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="18" customHeight="1">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="n">
+        <v>1003.5</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>1001.4</v>
+      </c>
+      <c r="D99" s="4" t="n">
+        <v>1028</v>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>2.59% (26.6)</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="n">
+        <v>1054.6</v>
+      </c>
+      <c r="G99" s="4" t="n">
+        <v>1081.2</v>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 09:15</t>
+        </is>
+      </c>
+      <c r="I99" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>1015.9</v>
+      </c>
+      <c r="L99" s="3" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
         <is>
           <t>(19-10-2026 to 25-10-2026)</t>
         </is>

--- a/data/trade_tracker_results.xlsx
+++ b/data/trade_tracker_results.xlsx
@@ -74,8 +74,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -86,14 +92,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-        <bgColor rgb="00D9E1F2"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -129,16 +129,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -506,19 +506,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="33" customWidth="1" min="9" max="9"/>
-    <col width="27" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
   </cols>
@@ -588,28 +588,28 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>7688</v>
+        <v>6070</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>7468</v>
+        <v>6065</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>7705</v>
+        <v>6152</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>3.08% (237.0)</t>
+          <t>1.41% (87.0)</t>
         </is>
       </c>
       <c r="F2" s="4" t="n">
-        <v>7942</v>
+        <v>6239</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>8179</v>
+        <v>6326</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -634,28 +634,28 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>2317.8</v>
+        <v>2462.1</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2299</v>
+        <v>2447.8</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>2341.5</v>
+        <v>2481</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>1.82% (42.5)</t>
+          <t>1.34% (33.2)</t>
         </is>
       </c>
       <c r="F3" s="4" t="n">
-        <v>2384</v>
+        <v>2514.2</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>2426.5</v>
+        <v>2547.4</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -680,28 +680,28 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>426.15</v>
+        <v>2260</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>425.6</v>
+        <v>2234.3</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>432.8</v>
+        <v>2283.3</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>1.66% (7.2)</t>
+          <t>2.15% (49.0)</t>
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>440</v>
+        <v>2332.3</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>447.2</v>
+        <v>2381.3</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -726,76 +726,74 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4591.2</v>
+        <v>907.4</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>4587</v>
+        <v>906.55</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>4610</v>
+        <v>920.6</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>0.5% (23.0)</t>
+          <t>1.53% (14.05)</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>4633</v>
+        <v>934.65</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>4656</v>
+        <v>948.7</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 09:15</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 09:15</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>4587</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>-0.5</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ICICIPRULI</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>435.2</v>
+        <v>229.2</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>434.75</v>
+        <v>227.3</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>438.45</v>
+        <v>229.7</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>0.84% (3.7)</t>
+          <t>1.04% (2.4)</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>442.15</v>
+        <v>232.1</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>445.85</v>
+        <v>234.5</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -820,76 +818,74 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>4550.4</v>
+        <v>4515</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>4474.6</v>
+        <v>4507.9</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>4572.1</v>
+        <v>4540.1</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>2.13% (97.5)</t>
+          <t>0.71% (32.2)</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>4669.6</v>
+        <v>4572.3</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>4767.1</v>
+        <v>4604.5</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:15</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>4524.4</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>-1.04</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1255.4</v>
+        <v>115.37</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1214.1</v>
+        <v>114.72</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1259</v>
+        <v>115.75</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>3.57% (44.9)</t>
+          <t>0.89% (1.03)</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1303.9</v>
+        <v>116.78</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1348.8</v>
+        <v>117.81</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -914,28 +910,28 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>1725.1</v>
+        <v>4716.3</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1715.3</v>
+        <v>4642.1</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1748.8</v>
+        <v>4733</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>1.92% (33.5)</t>
+          <t>1.92% (90.9)</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1782.3</v>
+        <v>4823.9</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1815.8</v>
+        <v>4914.8</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -960,28 +956,28 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>369.4</v>
+        <v>686.85</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>366.95</v>
+        <v>684</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>369.6</v>
+        <v>690</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>0.72% (2.65)</t>
+          <t>0.87% (6.0)</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>372.25</v>
+        <v>696</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>374.9</v>
+        <v>702</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1006,28 +1002,28 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>372.8</v>
+        <v>4994.5</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>368.5</v>
+        <v>4977.5</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>379.05</v>
+        <v>5054.5</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>2.78% (10.55)</t>
+          <t>1.52% (77.0)</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>389.6</v>
+        <v>5131.5</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>400.15</v>
+        <v>5208.5</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1052,76 +1048,74 @@
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>165.87</v>
+        <v>852</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>164.88</v>
+        <v>851.35</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>165.92</v>
+        <v>864</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>0.63% (1.04)</t>
+          <t>1.46% (12.65)</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>166.96</v>
+        <v>876.65</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>168</v>
+        <v>889.3</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:15</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:30</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>164.88</v>
-      </c>
-      <c r="L12" s="3" t="n">
-        <v>-0.63</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>IRFC</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>700.35</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>691.65</v>
+        <v>73.22</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>706.95</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>2.16% (15.3)</t>
+          <t>2.18% (1.63)</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>722.25</v>
+        <v>76.48</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>737.55</v>
+        <v>78.11</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1146,28 +1140,28 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>532.6</v>
+        <v>254.8</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>528.9</v>
+        <v>254.5</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>539.65</v>
+        <v>256.25</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>1.99% (10.75)</t>
+          <t>0.68% (1.75)</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>550.4</v>
+        <v>258</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>561.15</v>
+        <v>259.75</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1192,28 +1186,28 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>1631</v>
+        <v>440.15</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1616.6</v>
+        <v>440.15</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1644.9</v>
+        <v>446.35</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>1.72% (28.3)</t>
+          <t>1.39% (6.2)</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1673.2</v>
+        <v>452.55</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1701.5</v>
+        <v>458.75</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1238,28 +1232,28 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>LODHA</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>4615</v>
+        <v>941</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>4548.9</v>
+        <v>939.8</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>4641.5</v>
+        <v>948.2</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>2.0% (92.6)</t>
+          <t>0.89% (8.4)</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>4734.1</v>
+        <v>956.6</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>4826.7</v>
+        <v>965</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1284,28 +1278,28 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>845.7</v>
+        <v>1845</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>831.25</v>
+        <v>1838.7</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>853.7</v>
+        <v>1860.9</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>2.63% (22.45)</t>
+          <t>1.19% (22.2)</t>
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>876.15</v>
+        <v>1883.1</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>898.6</v>
+        <v>1905.3</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1330,76 +1324,74 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>437.2</v>
+        <v>148.07</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>433.75</v>
+        <v>147.32</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>438.2</v>
+        <v>148.9</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>1.02% (4.45)</t>
+          <t>1.06% (1.58)</t>
         </is>
       </c>
       <c r="F18" s="4" t="n">
-        <v>442.65</v>
+        <v>150.48</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>447.1</v>
+        <v>152.06</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:15</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 10:00</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="n">
-        <v>433.75</v>
-      </c>
-      <c r="L18" s="3" t="n">
-        <v>-1.02</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>71.44</v>
+        <v>1177.6</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>70.61</v>
+        <v>1169.8</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>71.87</v>
+        <v>1188.2</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>1.75% (1.26)</t>
+          <t>1.55% (18.4)</t>
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>73.13</v>
+        <v>1206.6</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>74.39</v>
+        <v>1225</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1424,28 +1416,28 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>1462</v>
+        <v>69.03</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1451</v>
+        <v>68.84</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1484.9</v>
+        <v>69.33</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>2.28% (33.9)</t>
+          <t>0.71% (0.49)</t>
         </is>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1518.8</v>
+        <v>69.81999999999999</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1552.7</v>
+        <v>70.31</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1470,28 +1462,28 @@
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>300</v>
+        <v>444.9</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>295.55</v>
+        <v>441.7</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>302.5</v>
+        <v>447.5</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>2.3% (6.95)</t>
+          <t>1.3% (5.8)</t>
         </is>
       </c>
       <c r="F21" s="4" t="n">
-        <v>309.45</v>
+        <v>453.3</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>316.4</v>
+        <v>459.1</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1516,28 +1508,28 @@
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>PFC</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>1634.5</v>
+        <v>312.75</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1609</v>
+        <v>310.5</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1647.5</v>
+        <v>313.9</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>2.34% (38.5)</t>
+          <t>1.08% (3.4)</t>
         </is>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1686</v>
+        <v>317.3</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1724.5</v>
+        <v>320.7</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1562,76 +1554,74 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>1725.5</v>
+        <v>119.06</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1719.6</v>
+        <v>118.25</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1745.1</v>
+        <v>119.24</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>1.46% (25.5)</t>
+          <t>0.83% (0.99)</t>
         </is>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1770.6</v>
+        <v>120.23</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1796.1</v>
+        <v>121.22</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:15</t>
-        </is>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="n">
-        <v>1748</v>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="4" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>171.66</v>
+        <v>290.65</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>168.11</v>
+        <v>289.5</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>172.45</v>
+        <v>291.8</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>2.52% (4.34)</t>
+          <t>0.79% (2.3)</t>
         </is>
       </c>
       <c r="F24" s="4" t="n">
-        <v>176.79</v>
+        <v>294.1</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>181.13</v>
+        <v>296.4</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1656,28 +1646,28 @@
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>4361</v>
+        <v>949.95</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>4329.2</v>
+        <v>943.5</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>4380.9</v>
+        <v>958</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>1.18% (51.7)</t>
+          <t>1.51% (14.5)</t>
         </is>
       </c>
       <c r="F25" s="4" t="n">
-        <v>4432.6</v>
+        <v>972.5</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>4484.3</v>
+        <v>987</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1702,76 +1692,74 @@
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>1107.3</v>
+        <v>4470.4</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>1100.3</v>
+        <v>4467.3</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1117.3</v>
+        <v>4565</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>1.52% (17.0)</t>
+          <t>2.14% (97.7)</t>
         </is>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1134.3</v>
+        <v>4662.7</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1151.3</v>
+        <v>4760.4</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:15</t>
-        </is>
-      </c>
-      <c r="I26" s="7" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:15</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="n">
-        <v>1134.3</v>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="4" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>283.25</v>
+        <v>3898.1</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>277</v>
+        <v>3875.1</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>288</v>
+        <v>3961.9</v>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>3.82% (11.0)</t>
+          <t>2.19% (86.8)</t>
         </is>
       </c>
       <c r="F27" s="4" t="n">
-        <v>299</v>
+        <v>4048.7</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>310</v>
+        <v>4135.5</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -1796,28 +1784,28 @@
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>808.55</v>
+        <v>223.35</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>772.5</v>
+        <v>221.8</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>821.75</v>
+        <v>225</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>5.99% (49.25)</t>
+          <t>1.42% (3.2)</t>
         </is>
       </c>
       <c r="F28" s="4" t="n">
-        <v>871</v>
+        <v>228.2</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>920.25</v>
+        <v>231.4</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -1842,742 +1830,46 @@
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>1300.2</v>
+        <v>1100.3</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1296.7</v>
+        <v>1094</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1314</v>
+        <v>1158.5</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>1.32% (17.3)</t>
+          <t>5.57% (64.5)</t>
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1331.3</v>
+        <v>1223</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1348.6</v>
+        <v>1287.5</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:15</t>
-        </is>
-      </c>
-      <c r="I29" s="7" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:15</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="n">
-        <v>1331.3</v>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="4" t="n">
-        <v>1.32</v>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>COALINDIA</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>402.1</v>
-      </c>
-      <c r="C30" s="3" t="n">
-        <v>395.75</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>407.5</v>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>2.88% (11.75)</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="n">
-        <v>419.25</v>
-      </c>
-      <c r="G30" s="4" t="n">
-        <v>431</v>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>GRASIM</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>2843.4</v>
-      </c>
-      <c r="C31" s="3" t="n">
-        <v>2828.2</v>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>2889.1</v>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>2.11% (60.9)</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="n">
-        <v>2950</v>
-      </c>
-      <c r="G31" s="4" t="n">
-        <v>3010.9</v>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23 09:15</t>
-        </is>
-      </c>
-      <c r="I31" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="n">
-        <v>2894</v>
-      </c>
-      <c r="L31" s="4" t="n">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>HINDUNILVR</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>1814.4</v>
-      </c>
-      <c r="C32" s="3" t="n">
-        <v>1781.1</v>
-      </c>
-      <c r="D32" s="4" t="n">
-        <v>1834.9</v>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>2.93% (53.8)</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="n">
-        <v>1888.7</v>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>1942.5</v>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>ITC</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>256.95</v>
-      </c>
-      <c r="C33" s="3" t="n">
-        <v>254.85</v>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>257.05</v>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>0.86% (2.2)</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="n">
-        <v>259.25</v>
-      </c>
-      <c r="G33" s="4" t="n">
-        <v>261.45</v>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>JINDALSTEL</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>1003.5</v>
-      </c>
-      <c r="C34" s="3" t="n">
-        <v>1001.4</v>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>1028</v>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>2.59% (26.6)</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="n">
-        <v>1054.6</v>
-      </c>
-      <c r="G34" s="4" t="n">
-        <v>1081.2</v>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23 09:15</t>
-        </is>
-      </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="n">
-        <v>1015.9</v>
-      </c>
-      <c r="L34" s="3" t="n">
-        <v>-1.18</v>
-      </c>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>MARUTI</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="n">
-        <v>11125</v>
-      </c>
-      <c r="C35" s="3" t="n">
-        <v>10990</v>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>11200</v>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>1.88% (210.0)</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="n">
-        <v>11410</v>
-      </c>
-      <c r="G35" s="4" t="n">
-        <v>11620</v>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr"/>
-      <c r="L35" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>MOTHERSON</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>152.77</v>
-      </c>
-      <c r="C36" s="3" t="n">
-        <v>152.4</v>
-      </c>
-      <c r="D36" s="4" t="n">
-        <v>155.43</v>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>1.95% (3.03)</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="n">
-        <v>158.46</v>
-      </c>
-      <c r="G36" s="4" t="n">
-        <v>161.49</v>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>POWERGRID</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n">
-        <v>245</v>
-      </c>
-      <c r="C37" s="3" t="n">
-        <v>242.3</v>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>248.4</v>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>2.46% (6.1)</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="n">
-        <v>254.5</v>
-      </c>
-      <c r="G37" s="4" t="n">
-        <v>260.6</v>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>TATACONSUM</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>953.2</v>
-      </c>
-      <c r="C38" s="3" t="n">
-        <v>948.9</v>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>961.4</v>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>1.3% (12.5)</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="n">
-        <v>973.9</v>
-      </c>
-      <c r="G38" s="4" t="n">
-        <v>986.4</v>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>DIVISLAB</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="n">
-        <v>8937.5</v>
-      </c>
-      <c r="C39" s="3" t="n">
-        <v>8797.5</v>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>8946.5</v>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>1.67% (149.0)</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="n">
-        <v>9095.5</v>
-      </c>
-      <c r="G39" s="4" t="n">
-        <v>9244.5</v>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>EICHERMOT</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>7008.5</v>
-      </c>
-      <c r="C40" s="3" t="n">
-        <v>6918</v>
-      </c>
-      <c r="D40" s="4" t="n">
-        <v>7084.5</v>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>2.35% (166.5)</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="n">
-        <v>7251</v>
-      </c>
-      <c r="G40" s="4" t="n">
-        <v>7417.5</v>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>GODREJCP</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="n">
-        <v>840.5</v>
-      </c>
-      <c r="C41" s="3" t="n">
-        <v>837.3</v>
-      </c>
-      <c r="D41" s="4" t="n">
-        <v>846</v>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>1.03% (8.7)</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="n">
-        <v>854.7</v>
-      </c>
-      <c r="G41" s="4" t="n">
-        <v>863.4</v>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>HINDALCO</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="n">
-        <v>857.15</v>
-      </c>
-      <c r="C42" s="3" t="n">
-        <v>852</v>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>889.8</v>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>4.25% (37.8)</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="n">
-        <v>927.6</v>
-      </c>
-      <c r="G42" s="4" t="n">
-        <v>965.4</v>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>TATACOMM</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="n">
-        <v>1636.2</v>
-      </c>
-      <c r="C43" s="3" t="n">
-        <v>1605.1</v>
-      </c>
-      <c r="D43" s="4" t="n">
-        <v>1694</v>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>5.25% (88.9)</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="n">
-        <v>1782.9</v>
-      </c>
-      <c r="G43" s="4" t="n">
-        <v>1871.8</v>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>TATAPOWER</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="n">
-        <v>340.7</v>
-      </c>
-      <c r="C44" s="3" t="n">
-        <v>340.4</v>
-      </c>
-      <c r="D44" s="4" t="n">
-        <v>345.25</v>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>1.4% (4.85)</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="n">
-        <v>350.1</v>
-      </c>
-      <c r="G44" s="4" t="n">
-        <v>354.95</v>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2603,7 +1895,7 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="33" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
     <col width="29" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
@@ -2678,23 +1970,23 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Week Range: (21-09-2026 to 27-09-2026)</t>
         </is>
       </c>
-      <c r="B2" s="8" t="n"/>
-      <c r="C2" s="8" t="n"/>
-      <c r="D2" s="8" t="n"/>
-      <c r="E2" s="8" t="n"/>
-      <c r="F2" s="8" t="n"/>
-      <c r="G2" s="8" t="n"/>
-      <c r="H2" s="8" t="n"/>
-      <c r="I2" s="8" t="n"/>
-      <c r="J2" s="8" t="n"/>
-      <c r="K2" s="8" t="n"/>
-      <c r="L2" s="8" t="n"/>
-      <c r="M2" s="8" t="n"/>
+      <c r="B2" s="5" t="n"/>
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="5" t="n"/>
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="n"/>
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="5" t="n"/>
+      <c r="L2" s="5" t="n"/>
+      <c r="M2" s="5" t="n"/>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -2727,7 +2019,7 @@
           <t>2026-09-23 09:15</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -2780,7 +2072,7 @@
           <t>2026-09-23 11:00</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2833,7 +2125,7 @@
           <t>2026-09-23 14:15</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2886,7 +2178,7 @@
           <t>2026-09-24 09:30</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2939,7 +2231,7 @@
           <t>2026-09-24 10:00</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2992,7 +2284,7 @@
           <t>2026-09-24 10:00</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3045,7 +2337,7 @@
           <t>2026-09-24 12:30</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3098,7 +2390,7 @@
           <t>2026-09-25 10:00</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -3151,7 +2443,7 @@
           <t>2026-09-25 14:00</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3204,7 +2496,7 @@
           <t>2026-09-25 14:00</t>
         </is>
       </c>
-      <c r="I12" s="6" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3229,49 +2521,49 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>200.4</v>
+        <v>3029.5</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>196.1</v>
+        <v>2967.1</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>203.34</v>
+        <v>3039</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>3.56% (7.24)</t>
+          <t>2.37% (71.9)</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>210.58</v>
+        <v>3110.9</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>217.82</v>
+        <v>3182.8</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
           <t>2026-09-25 14:15</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:15 (Week End)</t>
+          <t>2026-09-25 15:00 (Week End)</t>
         </is>
       </c>
       <c r="K13" s="2" t="n">
-        <v>202.75</v>
+        <v>3035</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>-0.29</v>
+        <v>-0.13</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
@@ -3282,49 +2574,49 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>3029.5</v>
+        <v>200.4</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>2967.1</v>
+        <v>196.1</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3039</v>
+        <v>203.34</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>2.37% (71.9)</t>
+          <t>3.56% (7.24)</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3110.9</v>
+        <v>210.58</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3182.8</v>
+        <v>217.82</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2026-09-25 14:15</t>
         </is>
       </c>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:00 (Week End)</t>
+          <t>2026-09-25 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K14" s="2" t="n">
-        <v>3035</v>
+        <v>202.75</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>-0.13</v>
+        <v>-0.29</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
@@ -3333,23 +2625,23 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Week Range: (28-09-2026 to 04-10-2026)</t>
         </is>
       </c>
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="n"/>
-      <c r="E15" s="8" t="n"/>
-      <c r="F15" s="8" t="n"/>
-      <c r="G15" s="8" t="n"/>
-      <c r="H15" s="8" t="n"/>
-      <c r="I15" s="8" t="n"/>
-      <c r="J15" s="8" t="n"/>
-      <c r="K15" s="8" t="n"/>
-      <c r="L15" s="8" t="n"/>
-      <c r="M15" s="8" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -3382,7 +2674,7 @@
           <t>2026-09-28 10:00</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -3435,7 +2727,7 @@
           <t>2026-09-28 11:30</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -3488,7 +2780,7 @@
           <t>2026-09-28 12:00</t>
         </is>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
@@ -3541,7 +2833,7 @@
           <t>2026-09-28 13:15</t>
         </is>
       </c>
-      <c r="I19" s="6" t="inlineStr">
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3594,7 +2886,7 @@
           <t>2026-09-28 13:45</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I20" s="8" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -3647,7 +2939,7 @@
           <t>2026-09-28 14:00</t>
         </is>
       </c>
-      <c r="I21" s="6" t="inlineStr">
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3700,7 +2992,7 @@
           <t>2026-09-28 15:15</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="I22" s="8" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -3753,7 +3045,7 @@
           <t>2026-09-28 15:15</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
+      <c r="I23" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3778,49 +3070,49 @@
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>906.9</v>
+        <v>8821.5</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>889.7</v>
+        <v>8804.5</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>907.5</v>
+        <v>8893</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>1.96% (17.8)</t>
+          <t>1.0% (88.5)</t>
         </is>
       </c>
       <c r="F24" s="4" t="n">
-        <v>925.3</v>
+        <v>8981.5</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>943.1</v>
+        <v>9070</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 09:15</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="I24" s="8" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:15</t>
+          <t>2026-09-29 10:00</t>
         </is>
       </c>
       <c r="K24" s="2" t="n">
-        <v>889.7</v>
+        <v>8804.5</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>-1.96</v>
+        <v>-1</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
@@ -3831,49 +3123,49 @@
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>8821.5</v>
+        <v>864.2</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>8804.5</v>
+        <v>859.7</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>8893</v>
+        <v>864.8</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>1.0% (88.5)</t>
+          <t>0.59% (5.1)</t>
         </is>
       </c>
       <c r="F25" s="4" t="n">
-        <v>8981.5</v>
+        <v>869.9</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>9070</v>
+        <v>875</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 09:15</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 10:00</t>
+          <t>2026-09-29 09:30</t>
         </is>
       </c>
       <c r="K25" s="2" t="n">
-        <v>8804.5</v>
+        <v>859.7</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>-1</v>
+        <v>-0.59</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
@@ -3884,49 +3176,49 @@
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>864.2</v>
+        <v>906.9</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>859.7</v>
+        <v>889.7</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>864.8</v>
+        <v>907.5</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>0.59% (5.1)</t>
+          <t>1.96% (17.8)</t>
         </is>
       </c>
       <c r="F26" s="4" t="n">
-        <v>869.9</v>
+        <v>925.3</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>875</v>
+        <v>943.1</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 09:15</t>
         </is>
       </c>
-      <c r="I26" s="7" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 09:30</t>
+          <t>2026-09-29 10:15</t>
         </is>
       </c>
       <c r="K26" s="2" t="n">
-        <v>859.7</v>
+        <v>889.7</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-0.59</v>
+        <v>-1.96</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
@@ -3965,7 +3257,7 @@
           <t>2026-09-29 09:30</t>
         </is>
       </c>
-      <c r="I27" s="6" t="inlineStr">
+      <c r="I27" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -4018,7 +3310,7 @@
           <t>2026-09-29 11:00</t>
         </is>
       </c>
-      <c r="I28" s="6" t="inlineStr">
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -4071,7 +3363,7 @@
           <t>2026-09-29 11:15</t>
         </is>
       </c>
-      <c r="I29" s="6" t="inlineStr">
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -4124,7 +3416,7 @@
           <t>2026-09-29 11:30</t>
         </is>
       </c>
-      <c r="I30" s="6" t="inlineStr">
+      <c r="I30" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -4177,7 +3469,7 @@
           <t>2026-09-29 11:30</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="I31" s="8" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -4230,7 +3522,7 @@
           <t>2026-09-29 11:45</t>
         </is>
       </c>
-      <c r="I32" s="6" t="inlineStr">
+      <c r="I32" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -4283,7 +3575,7 @@
           <t>2026-09-29 12:00</t>
         </is>
       </c>
-      <c r="I33" s="6" t="inlineStr">
+      <c r="I33" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -4336,7 +3628,7 @@
           <t>2026-09-29 13:00</t>
         </is>
       </c>
-      <c r="I34" s="6" t="inlineStr">
+      <c r="I34" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -4389,7 +3681,7 @@
           <t>2026-09-29 14:00</t>
         </is>
       </c>
-      <c r="I35" s="6" t="inlineStr">
+      <c r="I35" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -4442,7 +3734,7 @@
           <t>2026-09-29 14:00</t>
         </is>
       </c>
-      <c r="I36" s="7" t="inlineStr">
+      <c r="I36" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -4467,49 +3759,49 @@
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>22165</v>
+        <v>1629.9</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>22025</v>
+        <v>1600.2</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>22195</v>
+        <v>1642.9</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>0.77% (170.0)</t>
+          <t>2.6% (42.7)</t>
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>22365</v>
+        <v>1685.6</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>22535</v>
+        <v>1728.3</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 14:45</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:00</t>
+          <t>2026-09-29 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K37" s="2" t="n">
-        <v>22025</v>
+        <v>1627.3</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>-0.77</v>
+        <v>-0.95</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
@@ -4520,49 +3812,49 @@
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>1629.9</v>
+        <v>22165</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>1600.2</v>
+        <v>22025</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>1642.9</v>
+        <v>22195</v>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>2.6% (42.7)</t>
+          <t>0.77% (170.0)</t>
         </is>
       </c>
       <c r="F38" s="4" t="n">
-        <v>1685.6</v>
+        <v>22365</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>1728.3</v>
+        <v>22535</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 14:45</t>
         </is>
       </c>
-      <c r="I38" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:15 (Week End)</t>
+          <t>2026-09-29 15:00</t>
         </is>
       </c>
       <c r="K38" s="2" t="n">
-        <v>1627.3</v>
+        <v>22025</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>-0.95</v>
+        <v>-0.77</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
@@ -4601,7 +3893,7 @@
           <t>2026-09-29 15:00</t>
         </is>
       </c>
-      <c r="I39" s="6" t="inlineStr">
+      <c r="I39" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -4626,49 +3918,49 @@
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>263.55</v>
+        <v>1766.7</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>263.3</v>
+        <v>1736.8</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>266.2</v>
+        <v>1770.1</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>1.09% (2.9)</t>
+          <t>1.88% (33.3)</t>
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>269.1</v>
+        <v>1803.4</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>272</v>
+        <v>1836.7</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I40" s="5" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:15</t>
+          <t>2026-09-30 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K40" s="2" t="n">
-        <v>263.3</v>
-      </c>
-      <c r="L40" s="3" t="n">
-        <v>-1.09</v>
+        <v>1798.3</v>
+      </c>
+      <c r="L40" s="4" t="n">
+        <v>1.59</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
@@ -4679,49 +3971,49 @@
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>4057</v>
+        <v>991.6</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>4043.3</v>
+        <v>980.4</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>4095</v>
+        <v>992.7</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>1.26% (51.7)</t>
+          <t>1.24% (12.3)</t>
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>4146.7</v>
+        <v>1005</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>4198.4</v>
+        <v>1017.3</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I41" s="7" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 09:15</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
       <c r="K41" s="2" t="n">
-        <v>4043.3</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>-1.26</v>
+        <v>1017.3</v>
+      </c>
+      <c r="L41" s="4" t="n">
+        <v>2.48</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
@@ -4732,49 +4024,49 @@
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>160.5</v>
+        <v>2391</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>159.41</v>
+        <v>2381.6</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>162.37</v>
+        <v>2420</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>1.82% (2.96)</t>
+          <t>1.59% (38.4)</t>
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>165.33</v>
+        <v>2458.4</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>168.29</v>
+        <v>2496.8</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I42" s="6" t="inlineStr">
+      <c r="I42" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 15:15 (Week End)</t>
+          <t>2026-09-30 12:30 (Week End)</t>
         </is>
       </c>
       <c r="K42" s="2" t="n">
-        <v>163.26</v>
-      </c>
-      <c r="L42" s="4" t="n">
-        <v>0.55</v>
+        <v>2409.1</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>-0.45</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
@@ -4785,49 +4077,49 @@
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>399.3</v>
+        <v>4848.5</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>394.7</v>
+        <v>4837</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>403.65</v>
+        <v>4872</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>2.22% (8.95)</t>
+          <t>0.72% (35.0)</t>
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>412.6</v>
+        <v>4907</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>421.55</v>
+        <v>4942</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I43" s="7" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 09:15</t>
+          <t>2026-09-30 10:30</t>
         </is>
       </c>
       <c r="K43" s="2" t="n">
-        <v>421.55</v>
-      </c>
-      <c r="L43" s="4" t="n">
-        <v>4.43</v>
+        <v>4837</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>-0.72</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
@@ -4838,49 +4130,49 @@
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>2391</v>
+        <v>160.5</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>2381.6</v>
+        <v>159.41</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>2420</v>
+        <v>162.37</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>1.59% (38.4)</t>
+          <t>1.82% (2.96)</t>
         </is>
       </c>
       <c r="F44" s="4" t="n">
-        <v>2458.4</v>
+        <v>165.33</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>2496.8</v>
+        <v>168.29</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I44" s="6" t="inlineStr">
+      <c r="I44" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:30 (Week End)</t>
+          <t>2026-09-30 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K44" s="2" t="n">
-        <v>2409.1</v>
-      </c>
-      <c r="L44" s="3" t="n">
-        <v>-0.45</v>
+        <v>163.26</v>
+      </c>
+      <c r="L44" s="4" t="n">
+        <v>0.55</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
@@ -4891,49 +4183,49 @@
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>991.6</v>
+        <v>4057</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>980.4</v>
+        <v>4043.3</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>992.7</v>
+        <v>4095</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>1.24% (12.3)</t>
+          <t>1.26% (51.7)</t>
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>1005</v>
+        <v>4146.7</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>1017.3</v>
+        <v>4198.4</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I45" s="7" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="K45" s="2" t="n">
-        <v>1017.3</v>
-      </c>
-      <c r="L45" s="4" t="n">
-        <v>2.48</v>
+        <v>4043.3</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>-1.26</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
@@ -4944,49 +4236,49 @@
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>1766.7</v>
+        <v>263.55</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>1736.8</v>
+        <v>263.3</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>1770.1</v>
+        <v>266.2</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>1.88% (33.3)</t>
+          <t>1.09% (2.9)</t>
         </is>
       </c>
       <c r="F46" s="4" t="n">
-        <v>1803.4</v>
+        <v>269.1</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>1836.7</v>
+        <v>272</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I46" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I46" s="8" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 15:15 (Week End)</t>
+          <t>2026-09-30 14:15</t>
         </is>
       </c>
       <c r="K46" s="2" t="n">
-        <v>1798.3</v>
-      </c>
-      <c r="L46" s="4" t="n">
-        <v>1.59</v>
+        <v>263.3</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>-1.09</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
@@ -4997,49 +4289,49 @@
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>4848.5</v>
+        <v>399.3</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>4837</v>
+        <v>394.7</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>4872</v>
+        <v>403.65</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>0.72% (35.0)</t>
+          <t>2.22% (8.95)</t>
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>4907</v>
+        <v>412.6</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>4942</v>
+        <v>421.55</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I47" s="7" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 10:30</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="K47" s="2" t="n">
-        <v>4837</v>
-      </c>
-      <c r="L47" s="3" t="n">
-        <v>-0.72</v>
+        <v>421.55</v>
+      </c>
+      <c r="L47" s="4" t="n">
+        <v>4.43</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
@@ -5078,7 +4370,7 @@
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I48" s="6" t="inlineStr">
+      <c r="I48" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -5103,28 +4395,28 @@
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>721.95</v>
+        <v>514</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>704.8</v>
+        <v>513.5</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>726.45</v>
+        <v>516.1</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>2.98% (21.65)</t>
+          <t>0.5% (2.6)</t>
         </is>
       </c>
       <c r="F49" s="4" t="n">
-        <v>748.1</v>
+        <v>518.7</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>769.75</v>
+        <v>521.3</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -5133,19 +4425,19 @@
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>ACTIVE (Week End)</t>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 15:15 (Week End)</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="K49" s="2" t="n">
-        <v>718</v>
-      </c>
-      <c r="L49" s="3" t="n">
-        <v>-1.16</v>
+        <v>521.3</v>
+      </c>
+      <c r="L49" s="4" t="n">
+        <v>1.01</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
@@ -5156,28 +4448,28 @@
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>514</v>
+        <v>721.95</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>513.5</v>
+        <v>704.8</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>516.1</v>
+        <v>726.45</v>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>0.5% (2.6)</t>
+          <t>2.98% (21.65)</t>
         </is>
       </c>
       <c r="F50" s="4" t="n">
-        <v>518.7</v>
+        <v>748.1</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>521.3</v>
+        <v>769.75</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -5186,19 +4478,19 @@
       </c>
       <c r="I50" s="7" t="inlineStr">
         <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 09:15</t>
+          <t>2026-10-01 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K50" s="2" t="n">
-        <v>521.3</v>
-      </c>
-      <c r="L50" s="4" t="n">
-        <v>1.01</v>
+        <v>718</v>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>-1.16</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
@@ -5207,23 +4499,23 @@
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>Week Range: (05-10-2026 to 11-10-2026)</t>
         </is>
       </c>
-      <c r="B51" s="8" t="n"/>
-      <c r="C51" s="8" t="n"/>
-      <c r="D51" s="8" t="n"/>
-      <c r="E51" s="8" t="n"/>
-      <c r="F51" s="8" t="n"/>
-      <c r="G51" s="8" t="n"/>
-      <c r="H51" s="8" t="n"/>
-      <c r="I51" s="8" t="n"/>
-      <c r="J51" s="8" t="n"/>
-      <c r="K51" s="8" t="n"/>
-      <c r="L51" s="8" t="n"/>
-      <c r="M51" s="8" t="n"/>
+      <c r="B51" s="5" t="n"/>
+      <c r="C51" s="5" t="n"/>
+      <c r="D51" s="5" t="n"/>
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" s="5" t="n"/>
+      <c r="G51" s="5" t="n"/>
+      <c r="H51" s="5" t="n"/>
+      <c r="I51" s="5" t="n"/>
+      <c r="J51" s="5" t="n"/>
+      <c r="K51" s="5" t="n"/>
+      <c r="L51" s="5" t="n"/>
+      <c r="M51" s="5" t="n"/>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
@@ -5256,7 +4548,7 @@
           <t>2026-10-06 09:15</t>
         </is>
       </c>
-      <c r="I52" s="7" t="inlineStr">
+      <c r="I52" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -5309,7 +4601,7 @@
           <t>2026-10-06 09:15</t>
         </is>
       </c>
-      <c r="I53" s="6" t="inlineStr">
+      <c r="I53" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -5362,7 +4654,7 @@
           <t>2026-10-06 09:15</t>
         </is>
       </c>
-      <c r="I54" s="6" t="inlineStr">
+      <c r="I54" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -5415,7 +4707,7 @@
           <t>2026-10-06 09:15</t>
         </is>
       </c>
-      <c r="I55" s="6" t="inlineStr">
+      <c r="I55" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -5468,7 +4760,7 @@
           <t>2026-10-07 09:15</t>
         </is>
       </c>
-      <c r="I56" s="6" t="inlineStr">
+      <c r="I56" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -5521,7 +4813,7 @@
           <t>2026-10-07 09:15</t>
         </is>
       </c>
-      <c r="I57" s="7" t="inlineStr">
+      <c r="I57" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -5574,7 +4866,7 @@
           <t>2026-10-07 09:15</t>
         </is>
       </c>
-      <c r="I58" s="7" t="inlineStr">
+      <c r="I58" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -5627,7 +4919,7 @@
           <t>2026-10-08 09:15</t>
         </is>
       </c>
-      <c r="I59" s="5" t="inlineStr">
+      <c r="I59" s="8" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -5652,28 +4944,28 @@
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>1674.8</v>
+        <v>1316.5</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>1658.6</v>
+        <v>1308.7</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>1684.2</v>
+        <v>1323.7</v>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>1.52% (25.6)</t>
+          <t>1.13% (15.0)</t>
         </is>
       </c>
       <c r="F60" s="4" t="n">
-        <v>1709.8</v>
+        <v>1338.7</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>1735.4</v>
+        <v>1353.7</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -5682,19 +4974,19 @@
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
-          <t>ACTIVE (Week End)</t>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 15:15 (Week End)</t>
+          <t>2026-10-09 10:15</t>
         </is>
       </c>
       <c r="K60" s="2" t="n">
-        <v>1682</v>
-      </c>
-      <c r="L60" s="3" t="n">
-        <v>-0.13</v>
+        <v>1353.7</v>
+      </c>
+      <c r="L60" s="4" t="n">
+        <v>2.27</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
@@ -5705,49 +4997,49 @@
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>1316.5</v>
+        <v>902.05</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>1308.7</v>
+        <v>891.8</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>1323.7</v>
+        <v>903</v>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>1.13% (15.0)</t>
+          <t>1.24% (11.2)</t>
         </is>
       </c>
       <c r="F61" s="4" t="n">
-        <v>1338.7</v>
+        <v>914.2</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>1353.7</v>
+        <v>925.4</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I61" s="7" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I61" s="8" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 10:15</t>
+          <t>2026-10-09 09:15</t>
         </is>
       </c>
       <c r="K61" s="2" t="n">
-        <v>1353.7</v>
-      </c>
-      <c r="L61" s="4" t="n">
-        <v>2.27</v>
+        <v>891.8</v>
+      </c>
+      <c r="L61" s="3" t="n">
+        <v>-1.24</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
@@ -5758,49 +5050,49 @@
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>1702.1</v>
+        <v>254.65</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>1701</v>
+        <v>253.2</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>1710.1</v>
+        <v>255.4</v>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>0.53% (9.1)</t>
+          <t>0.86% (2.2)</t>
         </is>
       </c>
       <c r="F62" s="4" t="n">
-        <v>1719.2</v>
+        <v>257.6</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>1728.3</v>
+        <v>259.8</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I62" s="7" t="inlineStr">
+      <c r="I62" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 09:45</t>
+          <t>2026-10-09 10:00</t>
         </is>
       </c>
       <c r="K62" s="2" t="n">
-        <v>1728.3</v>
+        <v>259.8</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>1.06</v>
+        <v>1.72</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
@@ -5811,28 +5103,28 @@
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>LTM</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>3936</v>
+        <v>1674.8</v>
       </c>
       <c r="C63" s="3" t="n">
-        <v>3908.4</v>
+        <v>1658.6</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>3941.6</v>
+        <v>1684.2</v>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>0.84% (33.2)</t>
+          <t>1.52% (25.6)</t>
         </is>
       </c>
       <c r="F63" s="4" t="n">
-        <v>3974.8</v>
+        <v>1709.8</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>4008</v>
+        <v>1735.4</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -5841,19 +5133,19 @@
       </c>
       <c r="I63" s="7" t="inlineStr">
         <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 09:15</t>
+          <t>2026-10-09 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K63" s="2" t="n">
-        <v>4008</v>
-      </c>
-      <c r="L63" s="4" t="n">
-        <v>1.68</v>
+        <v>1682</v>
+      </c>
+      <c r="L63" s="3" t="n">
+        <v>-0.13</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
@@ -5864,49 +5156,49 @@
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>254.65</v>
+        <v>1702.1</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>253.2</v>
+        <v>1701</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>255.4</v>
+        <v>1710.1</v>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>0.86% (2.2)</t>
+          <t>0.53% (9.1)</t>
         </is>
       </c>
       <c r="F64" s="4" t="n">
-        <v>257.6</v>
+        <v>1719.2</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>259.8</v>
+        <v>1728.3</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I64" s="7" t="inlineStr">
+      <c r="I64" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 10:00</t>
+          <t>2026-10-09 09:45</t>
         </is>
       </c>
       <c r="K64" s="2" t="n">
-        <v>259.8</v>
+        <v>1728.3</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>1.72</v>
+        <v>1.06</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
@@ -5917,37 +5209,37 @@
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>LTM</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>902.05</v>
+        <v>3936</v>
       </c>
       <c r="C65" s="3" t="n">
-        <v>891.8</v>
+        <v>3908.4</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>903</v>
+        <v>3941.6</v>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>1.24% (11.2)</t>
+          <t>0.84% (33.2)</t>
         </is>
       </c>
       <c r="F65" s="4" t="n">
-        <v>914.2</v>
+        <v>3974.8</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>925.4</v>
+        <v>4008</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I65" s="5" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -5956,10 +5248,10 @@
         </is>
       </c>
       <c r="K65" s="2" t="n">
-        <v>891.8</v>
-      </c>
-      <c r="L65" s="3" t="n">
-        <v>-1.24</v>
+        <v>4008</v>
+      </c>
+      <c r="L65" s="4" t="n">
+        <v>1.68</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
@@ -5968,49 +5260,49 @@
       </c>
     </row>
     <row r="66" ht="22" customHeight="1">
-      <c r="A66" s="8" t="inlineStr">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>Week Range: (12-10-2026 to 18-10-2026)</t>
         </is>
       </c>
-      <c r="B66" s="8" t="n"/>
-      <c r="C66" s="8" t="n"/>
-      <c r="D66" s="8" t="n"/>
-      <c r="E66" s="8" t="n"/>
-      <c r="F66" s="8" t="n"/>
-      <c r="G66" s="8" t="n"/>
-      <c r="H66" s="8" t="n"/>
-      <c r="I66" s="8" t="n"/>
-      <c r="J66" s="8" t="n"/>
-      <c r="K66" s="8" t="n"/>
-      <c r="L66" s="8" t="n"/>
-      <c r="M66" s="8" t="n"/>
+      <c r="B66" s="5" t="n"/>
+      <c r="C66" s="5" t="n"/>
+      <c r="D66" s="5" t="n"/>
+      <c r="E66" s="5" t="n"/>
+      <c r="F66" s="5" t="n"/>
+      <c r="G66" s="5" t="n"/>
+      <c r="H66" s="5" t="n"/>
+      <c r="I66" s="5" t="n"/>
+      <c r="J66" s="5" t="n"/>
+      <c r="K66" s="5" t="n"/>
+      <c r="L66" s="5" t="n"/>
+      <c r="M66" s="5" t="n"/>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>709.75</v>
+        <v>1658.1</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>708.8</v>
+        <v>1658</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>711.4</v>
+        <v>1673.9</v>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>0.37% (2.6)</t>
+          <t>0.95% (15.9)</t>
         </is>
       </c>
       <c r="F67" s="4" t="n">
-        <v>714</v>
+        <v>1689.8</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>716.6</v>
+        <v>1705.7</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -6019,19 +5311,19 @@
       </c>
       <c r="I67" s="7" t="inlineStr">
         <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 09:45</t>
+          <t>2026-10-13 09:30</t>
         </is>
       </c>
       <c r="K67" s="2" t="n">
-        <v>716.6</v>
+        <v>1689.8</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>0.73</v>
+        <v>0.95</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
@@ -6042,49 +5334,49 @@
     <row r="68" ht="18" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>1124.6</v>
+        <v>709.75</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>1123.1</v>
+        <v>708.8</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>1131.1</v>
+        <v>711.4</v>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>0.71% (8.0)</t>
+          <t>0.37% (2.6)</t>
         </is>
       </c>
       <c r="F68" s="4" t="n">
-        <v>1139.1</v>
+        <v>714</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>1147.1</v>
+        <v>716.6</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
           <t>2026-10-13 09:15</t>
         </is>
       </c>
-      <c r="I68" s="7" t="inlineStr">
+      <c r="I68" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 10:15</t>
+          <t>2026-10-13 09:45</t>
         </is>
       </c>
       <c r="K68" s="2" t="n">
-        <v>1147.1</v>
+        <v>716.6</v>
       </c>
       <c r="L68" s="4" t="n">
-        <v>1.41</v>
+        <v>0.73</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
@@ -6095,28 +5387,28 @@
     <row r="69" ht="18" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>1658.1</v>
+        <v>1124.6</v>
       </c>
       <c r="C69" s="3" t="n">
-        <v>1658</v>
+        <v>1123.1</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>1673.9</v>
+        <v>1131.1</v>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>0.95% (15.9)</t>
+          <t>0.71% (8.0)</t>
         </is>
       </c>
       <c r="F69" s="4" t="n">
-        <v>1689.8</v>
+        <v>1139.1</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>1705.7</v>
+        <v>1147.1</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -6125,19 +5417,19 @@
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
-          <t>ACTIVE (Week End)</t>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 09:30</t>
+          <t>2026-10-15 10:15</t>
         </is>
       </c>
       <c r="K69" s="2" t="n">
-        <v>1689.8</v>
+        <v>1147.1</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>0.95</v>
+        <v>1.41</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
@@ -6148,49 +5440,49 @@
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>857</v>
+        <v>403.85</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>846.1</v>
+        <v>402.15</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>861.85</v>
+        <v>410.15</v>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>1.83% (15.75)</t>
+          <t>1.95% (8.0)</t>
         </is>
       </c>
       <c r="F70" s="4" t="n">
-        <v>877.6</v>
+        <v>418.15</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>893.35</v>
+        <v>426.15</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I70" s="6" t="inlineStr">
+      <c r="I70" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 09:30</t>
+          <t>2026-10-14 11:45</t>
         </is>
       </c>
       <c r="K70" s="2" t="n">
-        <v>877.6</v>
+        <v>418.15</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
@@ -6201,35 +5493,35 @@
     <row r="71" ht="18" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>1828</v>
+        <v>373.3</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>1818.5</v>
+        <v>373</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>1829.2</v>
+        <v>375.4</v>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>0.58% (10.7)</t>
+          <t>0.64% (2.4)</t>
         </is>
       </c>
       <c r="F71" s="4" t="n">
-        <v>1839.9</v>
+        <v>377.8</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>1850.6</v>
+        <v>380.2</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I71" s="7" t="inlineStr">
+      <c r="I71" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -6240,10 +5532,10 @@
         </is>
       </c>
       <c r="K71" s="2" t="n">
-        <v>1850.6</v>
+        <v>380.2</v>
       </c>
       <c r="L71" s="4" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
@@ -6254,28 +5546,28 @@
     <row r="72" ht="18" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>1160.2</v>
+        <v>441.05</v>
       </c>
       <c r="C72" s="3" t="n">
-        <v>1152.6</v>
+        <v>440.55</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>1166.7</v>
+        <v>445.8</v>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>1.21% (14.1)</t>
+          <t>1.18% (5.25)</t>
         </is>
       </c>
       <c r="F72" s="4" t="n">
-        <v>1180.8</v>
+        <v>451.05</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>1194.9</v>
+        <v>456.3</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -6284,19 +5576,19 @@
       </c>
       <c r="I72" s="7" t="inlineStr">
         <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 10:00</t>
+          <t>2026-10-14 11:00</t>
         </is>
       </c>
       <c r="K72" s="2" t="n">
-        <v>1194.9</v>
+        <v>451.05</v>
       </c>
       <c r="L72" s="4" t="n">
-        <v>2.42</v>
+        <v>1.18</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
@@ -6307,49 +5599,49 @@
     <row r="73" ht="18" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>1486.2</v>
+        <v>461</v>
       </c>
       <c r="C73" s="3" t="n">
-        <v>1443.3</v>
+        <v>457.5</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>1508</v>
+        <v>461.75</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>4.29% (64.7)</t>
+          <t>0.92% (4.25)</t>
         </is>
       </c>
       <c r="F73" s="4" t="n">
-        <v>1572.7</v>
+        <v>466</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>1637.4</v>
+        <v>470.25</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I73" s="7" t="inlineStr">
+      <c r="I73" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 13:15</t>
+          <t>2026-10-14 09:30</t>
         </is>
       </c>
       <c r="K73" s="2" t="n">
-        <v>1637.4</v>
+        <v>470.25</v>
       </c>
       <c r="L73" s="4" t="n">
-        <v>8.58</v>
+        <v>1.84</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
@@ -6360,49 +5652,49 @@
     <row r="74" ht="18" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>461</v>
+        <v>1160.2</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>457.5</v>
+        <v>1152.6</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>461.75</v>
+        <v>1166.7</v>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>0.92% (4.25)</t>
+          <t>1.21% (14.1)</t>
         </is>
       </c>
       <c r="F74" s="4" t="n">
-        <v>466</v>
+        <v>1180.8</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>470.25</v>
+        <v>1194.9</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I74" s="7" t="inlineStr">
+      <c r="I74" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 09:30</t>
+          <t>2026-10-15 10:00</t>
         </is>
       </c>
       <c r="K74" s="2" t="n">
-        <v>470.25</v>
+        <v>1194.9</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>1.84</v>
+        <v>2.42</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
@@ -6413,35 +5705,35 @@
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>373.3</v>
+        <v>1828</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>373</v>
+        <v>1818.5</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>375.4</v>
+        <v>1829.2</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>0.64% (2.4)</t>
+          <t>0.58% (10.7)</t>
         </is>
       </c>
       <c r="F75" s="4" t="n">
-        <v>377.8</v>
+        <v>1839.9</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>380.2</v>
+        <v>1850.6</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I75" s="7" t="inlineStr">
+      <c r="I75" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -6452,10 +5744,10 @@
         </is>
       </c>
       <c r="K75" s="2" t="n">
-        <v>380.2</v>
+        <v>1850.6</v>
       </c>
       <c r="L75" s="4" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
@@ -6466,49 +5758,49 @@
     <row r="76" ht="18" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>403.85</v>
+        <v>857</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>402.15</v>
+        <v>846.1</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>410.15</v>
+        <v>861.85</v>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>1.95% (8.0)</t>
+          <t>1.83% (15.75)</t>
         </is>
       </c>
       <c r="F76" s="4" t="n">
-        <v>418.15</v>
+        <v>877.6</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>426.15</v>
+        <v>893.35</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I76" s="6" t="inlineStr">
+      <c r="I76" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 11:45</t>
+          <t>2026-10-14 09:30</t>
         </is>
       </c>
       <c r="K76" s="2" t="n">
-        <v>418.15</v>
+        <v>877.6</v>
       </c>
       <c r="L76" s="4" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
@@ -6519,28 +5811,28 @@
     <row r="77" ht="18" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>441.05</v>
+        <v>1486.2</v>
       </c>
       <c r="C77" s="3" t="n">
-        <v>440.55</v>
+        <v>1443.3</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>445.8</v>
+        <v>1508</v>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>1.18% (5.25)</t>
+          <t>4.29% (64.7)</t>
         </is>
       </c>
       <c r="F77" s="4" t="n">
-        <v>451.05</v>
+        <v>1572.7</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>456.3</v>
+        <v>1637.4</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -6549,19 +5841,19 @@
       </c>
       <c r="I77" s="6" t="inlineStr">
         <is>
-          <t>ACTIVE (Week End)</t>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 11:00</t>
+          <t>2026-10-15 13:15</t>
         </is>
       </c>
       <c r="K77" s="2" t="n">
-        <v>451.05</v>
+        <v>1637.4</v>
       </c>
       <c r="L77" s="4" t="n">
-        <v>1.18</v>
+        <v>8.58</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
@@ -6600,7 +5892,7 @@
           <t>2026-10-14 09:30</t>
         </is>
       </c>
-      <c r="I78" s="6" t="inlineStr">
+      <c r="I78" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -6653,7 +5945,7 @@
           <t>2026-10-14 09:45</t>
         </is>
       </c>
-      <c r="I79" s="7" t="inlineStr">
+      <c r="I79" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -6706,7 +5998,7 @@
           <t>2026-10-14 11:30</t>
         </is>
       </c>
-      <c r="I80" s="6" t="inlineStr">
+      <c r="I80" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -6759,7 +6051,7 @@
           <t>2026-10-14 13:45</t>
         </is>
       </c>
-      <c r="I81" s="5" t="inlineStr">
+      <c r="I81" s="8" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -6812,7 +6104,7 @@
           <t>2026-10-15 09:15</t>
         </is>
       </c>
-      <c r="I82" s="6" t="inlineStr">
+      <c r="I82" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -6837,49 +6129,49 @@
     <row r="83" ht="18" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>3607</v>
+        <v>886.5</v>
       </c>
       <c r="C83" s="3" t="n">
-        <v>3593.2</v>
+        <v>860.1</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>3627.5</v>
+        <v>887</v>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>0.95% (34.3)</t>
+          <t>3.03% (26.9)</t>
         </is>
       </c>
       <c r="F83" s="4" t="n">
-        <v>3661.8</v>
+        <v>913.9</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>3696.1</v>
+        <v>940.8</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
           <t>2026-10-16 09:15</t>
         </is>
       </c>
-      <c r="I83" s="6" t="inlineStr">
+      <c r="I83" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 11:30</t>
+          <t>2026-10-16 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K83" s="2" t="n">
-        <v>3661.8</v>
+        <v>908</v>
       </c>
       <c r="L83" s="4" t="n">
-        <v>0.95</v>
+        <v>2.37</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
@@ -6890,49 +6182,49 @@
     <row r="84" ht="18" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>886.5</v>
+        <v>3607</v>
       </c>
       <c r="C84" s="3" t="n">
-        <v>860.1</v>
+        <v>3593.2</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>887</v>
+        <v>3627.5</v>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>3.03% (26.9)</t>
+          <t>0.95% (34.3)</t>
         </is>
       </c>
       <c r="F84" s="4" t="n">
-        <v>913.9</v>
+        <v>3661.8</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>940.8</v>
+        <v>3696.1</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
           <t>2026-10-16 09:15</t>
         </is>
       </c>
-      <c r="I84" s="6" t="inlineStr">
+      <c r="I84" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 15:15 (Week End)</t>
+          <t>2026-10-16 11:30</t>
         </is>
       </c>
       <c r="K84" s="2" t="n">
-        <v>908</v>
+        <v>3661.8</v>
       </c>
       <c r="L84" s="4" t="n">
-        <v>2.37</v>
+        <v>0.95</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
@@ -6971,7 +6263,7 @@
           <t>2026-10-16 09:15</t>
         </is>
       </c>
-      <c r="I85" s="7" t="inlineStr">
+      <c r="I85" s="6" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -7024,7 +6316,7 @@
           <t>2026-10-16 09:15</t>
         </is>
       </c>
-      <c r="I86" s="6" t="inlineStr">
+      <c r="I86" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -7077,7 +6369,7 @@
           <t>2026-10-16 09:15</t>
         </is>
       </c>
-      <c r="I87" s="6" t="inlineStr">
+      <c r="I87" s="7" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -7100,23 +6392,23 @@
       </c>
     </row>
     <row r="88" ht="22" customHeight="1">
-      <c r="A88" s="8" t="inlineStr">
+      <c r="A88" s="5" t="inlineStr">
         <is>
           <t>Week Range: (19-10-2026 to 25-10-2026)</t>
         </is>
       </c>
-      <c r="B88" s="8" t="n"/>
-      <c r="C88" s="8" t="n"/>
-      <c r="D88" s="8" t="n"/>
-      <c r="E88" s="8" t="n"/>
-      <c r="F88" s="8" t="n"/>
-      <c r="G88" s="8" t="n"/>
-      <c r="H88" s="8" t="n"/>
-      <c r="I88" s="8" t="n"/>
-      <c r="J88" s="8" t="n"/>
-      <c r="K88" s="8" t="n"/>
-      <c r="L88" s="8" t="n"/>
-      <c r="M88" s="8" t="n"/>
+      <c r="B88" s="5" t="n"/>
+      <c r="C88" s="5" t="n"/>
+      <c r="D88" s="5" t="n"/>
+      <c r="E88" s="5" t="n"/>
+      <c r="F88" s="5" t="n"/>
+      <c r="G88" s="5" t="n"/>
+      <c r="H88" s="5" t="n"/>
+      <c r="I88" s="5" t="n"/>
+      <c r="J88" s="5" t="n"/>
+      <c r="K88" s="5" t="n"/>
+      <c r="L88" s="5" t="n"/>
+      <c r="M88" s="5" t="n"/>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
@@ -7149,7 +6441,7 @@
           <t>2026-10-21 09:15</t>
         </is>
       </c>
-      <c r="I89" s="5" t="inlineStr">
+      <c r="I89" s="8" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -7202,7 +6494,7 @@
           <t>2026-10-21 09:15</t>
         </is>
       </c>
-      <c r="I90" s="5" t="inlineStr">
+      <c r="I90" s="8" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -7255,14 +6547,14 @@
           <t>2026-10-22 09:15</t>
         </is>
       </c>
-      <c r="I91" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I91" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22 15:15 (Active)</t>
+          <t>2026-10-22 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K91" s="2" t="n">
@@ -7280,49 +6572,49 @@
     <row r="92" ht="18" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>1107.3</v>
+        <v>165.87</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>1100.3</v>
+        <v>164.88</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>1117.3</v>
+        <v>165.92</v>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>1.52% (17.0)</t>
+          <t>0.63% (1.04)</t>
         </is>
       </c>
       <c r="F92" s="4" t="n">
-        <v>1134.3</v>
+        <v>166.96</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>1151.3</v>
+        <v>168</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
           <t>2026-10-23 09:15</t>
         </is>
       </c>
-      <c r="I92" s="7" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+      <c r="I92" s="6" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:15</t>
+          <t>2026-10-23 09:30</t>
         </is>
       </c>
       <c r="K92" s="2" t="n">
-        <v>1134.3</v>
-      </c>
-      <c r="L92" s="4" t="n">
-        <v>1.52</v>
+        <v>164.88</v>
+      </c>
+      <c r="L92" s="3" t="n">
+        <v>-0.63</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
@@ -7333,28 +6625,28 @@
     <row r="93" ht="18" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>1300.2</v>
+        <v>4550.4</v>
       </c>
       <c r="C93" s="3" t="n">
-        <v>1296.7</v>
+        <v>4474.6</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>1314</v>
+        <v>4572.1</v>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>1.32% (17.3)</t>
+          <t>2.13% (97.5)</t>
         </is>
       </c>
       <c r="F93" s="4" t="n">
-        <v>1331.3</v>
+        <v>4669.6</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>1348.6</v>
+        <v>4767.1</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -7363,19 +6655,19 @@
       </c>
       <c r="I93" s="7" t="inlineStr">
         <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:15</t>
+          <t>2026-10-23 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K93" s="2" t="n">
-        <v>1331.3</v>
-      </c>
-      <c r="L93" s="4" t="n">
-        <v>1.32</v>
+        <v>4524.4</v>
+      </c>
+      <c r="L93" s="3" t="n">
+        <v>-1.04</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
@@ -7386,46 +6678,46 @@
     <row r="94" ht="18" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>1725.5</v>
+        <v>2843.4</v>
       </c>
       <c r="C94" s="3" t="n">
-        <v>1719.6</v>
+        <v>2828.2</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>1745.1</v>
+        <v>2889.1</v>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>1.46% (25.5)</t>
+          <t>2.11% (60.9)</t>
         </is>
       </c>
       <c r="F94" s="4" t="n">
-        <v>1770.6</v>
+        <v>2950</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>1796.1</v>
+        <v>3010.9</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
           <t>2026-10-23 09:15</t>
         </is>
       </c>
-      <c r="I94" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I94" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 15:15 (Active)</t>
+          <t>2026-10-23 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K94" s="2" t="n">
-        <v>1748</v>
+        <v>2894</v>
       </c>
       <c r="L94" s="4" t="n">
         <v>0.17</v>
@@ -7439,49 +6731,49 @@
     <row r="95" ht="18" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>2843.4</v>
+        <v>437.2</v>
       </c>
       <c r="C95" s="3" t="n">
-        <v>2828.2</v>
+        <v>433.75</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>2889.1</v>
+        <v>438.2</v>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>2.11% (60.9)</t>
+          <t>1.02% (4.45)</t>
         </is>
       </c>
       <c r="F95" s="4" t="n">
-        <v>2950</v>
+        <v>442.65</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>3010.9</v>
+        <v>447.1</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
           <t>2026-10-23 09:15</t>
         </is>
       </c>
-      <c r="I95" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I95" s="8" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 15:15 (Active)</t>
+          <t>2026-10-23 10:00</t>
         </is>
       </c>
       <c r="K95" s="2" t="n">
-        <v>2894</v>
-      </c>
-      <c r="L95" s="4" t="n">
-        <v>0.17</v>
+        <v>433.75</v>
+      </c>
+      <c r="L95" s="3" t="n">
+        <v>-1.02</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
@@ -7492,28 +6784,28 @@
     <row r="96" ht="18" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>165.87</v>
+        <v>1300.2</v>
       </c>
       <c r="C96" s="3" t="n">
-        <v>164.88</v>
+        <v>1296.7</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>165.92</v>
+        <v>1314</v>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>0.63% (1.04)</t>
+          <t>1.32% (17.3)</t>
         </is>
       </c>
       <c r="F96" s="4" t="n">
-        <v>166.96</v>
+        <v>1331.3</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>168</v>
+        <v>1348.6</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -7522,19 +6814,19 @@
       </c>
       <c r="I96" s="7" t="inlineStr">
         <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:30</t>
+          <t>2026-10-23 09:15</t>
         </is>
       </c>
       <c r="K96" s="2" t="n">
-        <v>164.88</v>
-      </c>
-      <c r="L96" s="3" t="n">
-        <v>-0.63</v>
+        <v>1331.3</v>
+      </c>
+      <c r="L96" s="4" t="n">
+        <v>1.32</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
@@ -7545,49 +6837,49 @@
     <row r="97" ht="18" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>4550.4</v>
+        <v>1107.3</v>
       </c>
       <c r="C97" s="3" t="n">
-        <v>4474.6</v>
+        <v>1100.3</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>4572.1</v>
+        <v>1117.3</v>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>2.13% (97.5)</t>
+          <t>1.52% (17.0)</t>
         </is>
       </c>
       <c r="F97" s="4" t="n">
-        <v>4669.6</v>
+        <v>1134.3</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>4767.1</v>
+        <v>1151.3</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
           <t>2026-10-23 09:15</t>
         </is>
       </c>
-      <c r="I97" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I97" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 15:15 (Active)</t>
+          <t>2026-10-23 09:15</t>
         </is>
       </c>
       <c r="K97" s="2" t="n">
-        <v>4524.4</v>
-      </c>
-      <c r="L97" s="3" t="n">
-        <v>-1.04</v>
+        <v>1134.3</v>
+      </c>
+      <c r="L97" s="4" t="n">
+        <v>1.52</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
@@ -7598,49 +6890,49 @@
     <row r="98" ht="18" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>437.2</v>
+        <v>1725.5</v>
       </c>
       <c r="C98" s="3" t="n">
-        <v>433.75</v>
+        <v>1719.6</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>438.2</v>
+        <v>1745.1</v>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>1.02% (4.45)</t>
+          <t>1.46% (25.5)</t>
         </is>
       </c>
       <c r="F98" s="4" t="n">
-        <v>442.65</v>
+        <v>1770.6</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>447.1</v>
+        <v>1796.1</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
           <t>2026-10-23 09:15</t>
         </is>
       </c>
-      <c r="I98" s="5" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I98" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 10:00</t>
+          <t>2026-10-23 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K98" s="2" t="n">
-        <v>433.75</v>
-      </c>
-      <c r="L98" s="3" t="n">
-        <v>-1.02</v>
+        <v>1748</v>
+      </c>
+      <c r="L98" s="4" t="n">
+        <v>0.17</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
@@ -7679,14 +6971,14 @@
           <t>2026-10-23 09:15</t>
         </is>
       </c>
-      <c r="I99" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I99" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 15:15 (Active)</t>
+          <t>2026-10-23 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K99" s="2" t="n">

--- a/data/trade_tracker_results.xlsx
+++ b/data/trade_tracker_results.xlsx
@@ -74,12 +74,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-        <bgColor rgb="00D9E1F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
@@ -94,6 +88,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
         <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -129,16 +129,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -506,19 +506,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="33" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
   </cols>
@@ -613,22 +613,24 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr"/>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>6326</v>
+      </c>
       <c r="L2" s="4" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
@@ -641,21 +643,21 @@
         <v>2462.1</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2447.8</v>
+        <v>2433.4</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>2481</v>
+        <v>2492.8</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>1.34% (33.2)</t>
+          <t>2.38% (59.4)</t>
         </is>
       </c>
       <c r="F3" s="4" t="n">
-        <v>2514.2</v>
+        <v>2552.2</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>2547.4</v>
+        <v>2611.6</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -705,22 +707,24 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="4" t="n">
-        <v>0</v>
+          <t>2026-10-27 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>2277</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>-0.28</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -751,22 +755,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-27 09:30</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="4" t="n">
-        <v>0</v>
+          <t>2026-10-27 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>912</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>-0.93</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -797,22 +803,24 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr"/>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>232.1</v>
+      </c>
       <c r="L6" s="4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -843,22 +851,24 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr"/>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>4572.3</v>
+      </c>
       <c r="L7" s="4" t="n">
-        <v>0</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -889,22 +899,24 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr"/>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>117.81</v>
+      </c>
       <c r="L8" s="4" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -935,22 +947,24 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr"/>
+          <t>2026-10-27 09:30</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>4914.8</v>
+      </c>
       <c r="L9" s="4" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -963,21 +977,21 @@
         <v>686.85</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>684</v>
+        <v>683.85</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>690</v>
+        <v>688.3</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>0.87% (6.0)</t>
+          <t>0.65% (4.45)</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>696</v>
+        <v>692.75</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>702</v>
+        <v>697.2</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1027,22 +1041,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr"/>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>5208.5</v>
+      </c>
       <c r="L11" s="4" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -1073,22 +1089,24 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr"/>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>889.3</v>
+      </c>
       <c r="L12" s="4" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -1101,21 +1119,21 @@
         <v>73.76000000000001</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>73.22</v>
+        <v>73.19</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>74.84999999999999</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>2.18% (1.63)</t>
+          <t>1.67% (1.24)</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>76.48</v>
+        <v>75.67</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>78.11</v>
+        <v>76.91</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1165,22 +1183,24 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr"/>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>259.75</v>
+      </c>
       <c r="L14" s="4" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -1211,22 +1231,24 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr"/>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>458.75</v>
+      </c>
       <c r="L15" s="4" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -1257,22 +1279,24 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr"/>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>965</v>
+      </c>
       <c r="L16" s="4" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -1303,22 +1327,24 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr"/>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>1905.3</v>
+      </c>
       <c r="L17" s="4" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -1349,22 +1375,24 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr"/>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>152.06</v>
+      </c>
       <c r="L18" s="4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -1395,22 +1423,24 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr"/>
+          <t>2026-10-27 10:00</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>1206.6</v>
+      </c>
       <c r="L19" s="4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -1441,22 +1471,24 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr"/>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>70.31</v>
+      </c>
       <c r="L20" s="4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -1487,22 +1519,24 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr"/>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>453.3</v>
+      </c>
       <c r="L21" s="4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -1518,18 +1552,18 @@
         <v>310.5</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>313.9</v>
+        <v>314.45</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>1.08% (3.4)</t>
+          <t>1.26% (3.95)</t>
         </is>
       </c>
       <c r="F22" s="4" t="n">
-        <v>317.3</v>
+        <v>318.4</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>320.7</v>
+        <v>322.35</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1579,22 +1613,24 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr"/>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>121.22</v>
+      </c>
       <c r="L23" s="4" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -1625,22 +1661,24 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="4" t="n">
-        <v>0</v>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>289.5</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>-0.79</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -1717,22 +1755,24 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr"/>
+          <t>2026-10-27 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>4625</v>
+      </c>
       <c r="L26" s="4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -1763,22 +1803,24 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr"/>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>4048.7</v>
+      </c>
       <c r="L27" s="4" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -1809,22 +1851,24 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr"/>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>228.2</v>
+      </c>
       <c r="L28" s="4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -1855,21 +1899,393 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>1172.9</v>
+      </c>
+      <c r="L29" s="4" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>1134.6</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>1118.1</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>1166.5</v>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>4.15% (48.4)</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>1214.9</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>1263.3</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>WAIT (No Entry)</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="4" t="n">
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>10834</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>10735</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>10856</v>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>1.11% (121.0)</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>10977</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>11098</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>1450</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>1415</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>1452.6</v>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>2.59% (37.6)</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>1490.2</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>1527.8</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>1469</v>
+      </c>
+      <c r="L32" s="4" t="n">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>DABUR</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>356.05</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>354.3</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>359.3</v>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>1.39% (5.0)</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>364.3</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>369.3</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>HAVELLS</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>1002.8</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>999.7</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>1014.8</v>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>1.49% (15.1)</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>1029.9</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>1045</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>1781.1</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>1758.2</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>1818.6</v>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>3.32% (60.4)</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>1879</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>1939.4</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>437.45</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>437</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>440.25</v>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>0.74% (3.25)</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>443.5</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>446.75</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>UNITDSPR</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>1240</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>1227</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>1241.5</v>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>1.17% (14.5)</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>1256</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>1270.5</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1884,7 +2300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M99"/>
+  <dimension ref="A1:M124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1895,7 +2311,7 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="33" customWidth="1" min="9" max="9"/>
     <col width="29" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
@@ -1970,23 +2386,23 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Week Range: (21-09-2026 to 27-09-2026)</t>
         </is>
       </c>
-      <c r="B2" s="5" t="n"/>
-      <c r="C2" s="5" t="n"/>
-      <c r="D2" s="5" t="n"/>
-      <c r="E2" s="5" t="n"/>
-      <c r="F2" s="5" t="n"/>
-      <c r="G2" s="5" t="n"/>
-      <c r="H2" s="5" t="n"/>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="n"/>
-      <c r="L2" s="5" t="n"/>
-      <c r="M2" s="5" t="n"/>
+      <c r="B2" s="8" t="n"/>
+      <c r="C2" s="8" t="n"/>
+      <c r="D2" s="8" t="n"/>
+      <c r="E2" s="8" t="n"/>
+      <c r="F2" s="8" t="n"/>
+      <c r="G2" s="8" t="n"/>
+      <c r="H2" s="8" t="n"/>
+      <c r="I2" s="8" t="n"/>
+      <c r="J2" s="8" t="n"/>
+      <c r="K2" s="8" t="n"/>
+      <c r="L2" s="8" t="n"/>
+      <c r="M2" s="8" t="n"/>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -2019,7 +2435,7 @@
           <t>2026-09-23 09:15</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -2072,7 +2488,7 @@
           <t>2026-09-23 11:00</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2125,7 +2541,7 @@
           <t>2026-09-23 14:15</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2178,7 +2594,7 @@
           <t>2026-09-24 09:30</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2231,7 +2647,7 @@
           <t>2026-09-24 10:00</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2284,7 +2700,7 @@
           <t>2026-09-24 10:00</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2337,7 +2753,7 @@
           <t>2026-09-24 12:30</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2390,7 +2806,7 @@
           <t>2026-09-25 10:00</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -2443,7 +2859,7 @@
           <t>2026-09-25 14:00</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2496,7 +2912,7 @@
           <t>2026-09-25 14:00</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2549,7 +2965,7 @@
           <t>2026-09-25 14:15</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2602,7 +3018,7 @@
           <t>2026-09-25 14:15</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2625,23 +3041,23 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>Week Range: (28-09-2026 to 04-10-2026)</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="n"/>
-      <c r="L15" s="5" t="n"/>
-      <c r="M15" s="5" t="n"/>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="8" t="n"/>
+      <c r="G15" s="8" t="n"/>
+      <c r="H15" s="8" t="n"/>
+      <c r="I15" s="8" t="n"/>
+      <c r="J15" s="8" t="n"/>
+      <c r="K15" s="8" t="n"/>
+      <c r="L15" s="8" t="n"/>
+      <c r="M15" s="8" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -2674,7 +3090,7 @@
           <t>2026-09-28 10:00</t>
         </is>
       </c>
-      <c r="I16" s="8" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -2727,7 +3143,7 @@
           <t>2026-09-28 11:30</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -2780,7 +3196,7 @@
           <t>2026-09-28 12:00</t>
         </is>
       </c>
-      <c r="I18" s="6" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
@@ -2833,7 +3249,7 @@
           <t>2026-09-28 13:15</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="I19" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2886,7 +3302,7 @@
           <t>2026-09-28 13:45</t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -2939,7 +3355,7 @@
           <t>2026-09-28 14:00</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="I21" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -2992,7 +3408,7 @@
           <t>2026-09-28 15:15</t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr">
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -3045,7 +3461,7 @@
           <t>2026-09-28 15:15</t>
         </is>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="I23" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3098,7 +3514,7 @@
           <t>2026-09-29 09:15</t>
         </is>
       </c>
-      <c r="I24" s="8" t="inlineStr">
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -3151,7 +3567,7 @@
           <t>2026-09-29 09:15</t>
         </is>
       </c>
-      <c r="I25" s="6" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
@@ -3204,7 +3620,7 @@
           <t>2026-09-29 09:15</t>
         </is>
       </c>
-      <c r="I26" s="8" t="inlineStr">
+      <c r="I26" s="7" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -3257,7 +3673,7 @@
           <t>2026-09-29 09:30</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="I27" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3310,7 +3726,7 @@
           <t>2026-09-29 11:00</t>
         </is>
       </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="I28" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3363,7 +3779,7 @@
           <t>2026-09-29 11:15</t>
         </is>
       </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="I29" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3416,7 +3832,7 @@
           <t>2026-09-29 11:30</t>
         </is>
       </c>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="I30" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3469,7 +3885,7 @@
           <t>2026-09-29 11:30</t>
         </is>
       </c>
-      <c r="I31" s="8" t="inlineStr">
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -3522,7 +3938,7 @@
           <t>2026-09-29 11:45</t>
         </is>
       </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="I32" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3575,7 +3991,7 @@
           <t>2026-09-29 12:00</t>
         </is>
       </c>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="I33" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3628,7 +4044,7 @@
           <t>2026-09-29 13:00</t>
         </is>
       </c>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="I34" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3681,7 +4097,7 @@
           <t>2026-09-29 14:00</t>
         </is>
       </c>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="I35" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3734,7 +4150,7 @@
           <t>2026-09-29 14:00</t>
         </is>
       </c>
-      <c r="I36" s="6" t="inlineStr">
+      <c r="I36" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -3787,7 +4203,7 @@
           <t>2026-09-29 14:45</t>
         </is>
       </c>
-      <c r="I37" s="7" t="inlineStr">
+      <c r="I37" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3840,7 +4256,7 @@
           <t>2026-09-29 14:45</t>
         </is>
       </c>
-      <c r="I38" s="8" t="inlineStr">
+      <c r="I38" s="7" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -3893,7 +4309,7 @@
           <t>2026-09-29 15:00</t>
         </is>
       </c>
-      <c r="I39" s="7" t="inlineStr">
+      <c r="I39" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -3918,49 +4334,49 @@
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>1766.7</v>
+        <v>196.1</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1736.8</v>
+        <v>192.45</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>1770.1</v>
+        <v>196.67</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>1.88% (33.3)</t>
+          <t>2.15% (4.22)</t>
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>1803.4</v>
+        <v>200.89</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>1836.7</v>
+        <v>205.11</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I40" s="7" t="inlineStr">
+      <c r="I40" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 15:15 (Week End)</t>
+          <t>2026-09-30 09:15</t>
         </is>
       </c>
       <c r="K40" s="2" t="n">
-        <v>1798.3</v>
+        <v>200.89</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>1.59</v>
+        <v>2.15</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
@@ -3971,49 +4387,49 @@
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>991.6</v>
+        <v>399.3</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>980.4</v>
+        <v>394.7</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>992.7</v>
+        <v>403.65</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>1.24% (12.3)</t>
+          <t>2.22% (8.95)</t>
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>1005</v>
+        <v>412.6</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>1017.3</v>
+        <v>421.55</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I41" s="6" t="inlineStr">
+      <c r="I41" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="K41" s="2" t="n">
-        <v>1017.3</v>
+        <v>421.55</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>2.48</v>
+        <v>4.43</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
@@ -4024,49 +4440,49 @@
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>2391</v>
+        <v>4057</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>2381.6</v>
+        <v>4043.3</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>2420</v>
+        <v>4095</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>1.59% (38.4)</t>
+          <t>1.26% (51.7)</t>
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>2458.4</v>
+        <v>4146.7</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>2496.8</v>
+        <v>4198.4</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I42" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:30 (Week End)</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="K42" s="2" t="n">
-        <v>2409.1</v>
+        <v>4043.3</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>-0.45</v>
+        <v>-1.26</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
@@ -4077,28 +4493,28 @@
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>4848.5</v>
+        <v>160.5</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>4837</v>
+        <v>159.41</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>4872</v>
+        <v>162.37</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>0.72% (35.0)</t>
+          <t>1.82% (2.96)</t>
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>4907</v>
+        <v>165.33</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>4942</v>
+        <v>168.29</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -4107,19 +4523,19 @@
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 10:30</t>
+          <t>2026-09-30 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K43" s="2" t="n">
-        <v>4837</v>
-      </c>
-      <c r="L43" s="3" t="n">
-        <v>-0.72</v>
+        <v>163.26</v>
+      </c>
+      <c r="L43" s="4" t="n">
+        <v>0.55</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
@@ -4130,28 +4546,28 @@
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>160.5</v>
+        <v>263.55</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>159.41</v>
+        <v>263.3</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>162.37</v>
+        <v>266.2</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>1.82% (2.96)</t>
+          <t>1.09% (2.9)</t>
         </is>
       </c>
       <c r="F44" s="4" t="n">
-        <v>165.33</v>
+        <v>269.1</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>168.29</v>
+        <v>272</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -4160,19 +4576,19 @@
       </c>
       <c r="I44" s="7" t="inlineStr">
         <is>
-          <t>ACTIVE (Week End)</t>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 15:15 (Week End)</t>
+          <t>2026-09-30 14:15</t>
         </is>
       </c>
       <c r="K44" s="2" t="n">
-        <v>163.26</v>
-      </c>
-      <c r="L44" s="4" t="n">
-        <v>0.55</v>
+        <v>263.3</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>-1.09</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
@@ -4183,28 +4599,28 @@
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>4057</v>
+        <v>2391</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>4043.3</v>
+        <v>2381.6</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>4095</v>
+        <v>2420</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>1.26% (51.7)</t>
+          <t>1.59% (38.4)</t>
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>4146.7</v>
+        <v>2458.4</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>4198.4</v>
+        <v>2496.8</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -4213,19 +4629,19 @@
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 09:15</t>
+          <t>2026-09-30 12:30 (Week End)</t>
         </is>
       </c>
       <c r="K45" s="2" t="n">
-        <v>4043.3</v>
+        <v>2409.1</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>-1.26</v>
+        <v>-0.45</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
@@ -4236,49 +4652,49 @@
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>263.55</v>
+        <v>991.6</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>263.3</v>
+        <v>980.4</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>266.2</v>
+        <v>992.7</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>1.09% (2.9)</t>
+          <t>1.24% (12.3)</t>
         </is>
       </c>
       <c r="F46" s="4" t="n">
-        <v>269.1</v>
+        <v>1005</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>272</v>
+        <v>1017.3</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I46" s="8" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:15</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
       <c r="K46" s="2" t="n">
-        <v>263.3</v>
-      </c>
-      <c r="L46" s="3" t="n">
-        <v>-1.09</v>
+        <v>1017.3</v>
+      </c>
+      <c r="L46" s="4" t="n">
+        <v>2.48</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
@@ -4289,28 +4705,28 @@
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>399.3</v>
+        <v>1766.7</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>394.7</v>
+        <v>1736.8</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>403.65</v>
+        <v>1770.1</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>2.22% (8.95)</t>
+          <t>1.88% (33.3)</t>
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>412.6</v>
+        <v>1803.4</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>421.55</v>
+        <v>1836.7</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -4319,19 +4735,19 @@
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 09:15</t>
+          <t>2026-09-30 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K47" s="2" t="n">
-        <v>421.55</v>
+        <v>1798.3</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>4.43</v>
+        <v>1.59</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
@@ -4342,49 +4758,49 @@
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>196.1</v>
+        <v>4848.5</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>192.45</v>
+        <v>4837</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>196.67</v>
+        <v>4872</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>2.15% (4.22)</t>
+          <t>0.72% (35.0)</t>
         </is>
       </c>
       <c r="F48" s="4" t="n">
-        <v>200.89</v>
+        <v>4907</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>205.11</v>
+        <v>4942</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I48" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:15</t>
+          <t>2026-09-30 10:30</t>
         </is>
       </c>
       <c r="K48" s="2" t="n">
-        <v>200.89</v>
-      </c>
-      <c r="L48" s="4" t="n">
-        <v>2.15</v>
+        <v>4837</v>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>-0.72</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
@@ -4423,7 +4839,7 @@
           <t>2026-10-01 09:15</t>
         </is>
       </c>
-      <c r="I49" s="6" t="inlineStr">
+      <c r="I49" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -4476,7 +4892,7 @@
           <t>2026-10-01 09:15</t>
         </is>
       </c>
-      <c r="I50" s="7" t="inlineStr">
+      <c r="I50" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -4499,23 +4915,23 @@
       </c>
     </row>
     <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>Week Range: (05-10-2026 to 11-10-2026)</t>
         </is>
       </c>
-      <c r="B51" s="5" t="n"/>
-      <c r="C51" s="5" t="n"/>
-      <c r="D51" s="5" t="n"/>
-      <c r="E51" s="5" t="n"/>
-      <c r="F51" s="5" t="n"/>
-      <c r="G51" s="5" t="n"/>
-      <c r="H51" s="5" t="n"/>
-      <c r="I51" s="5" t="n"/>
-      <c r="J51" s="5" t="n"/>
-      <c r="K51" s="5" t="n"/>
-      <c r="L51" s="5" t="n"/>
-      <c r="M51" s="5" t="n"/>
+      <c r="B51" s="8" t="n"/>
+      <c r="C51" s="8" t="n"/>
+      <c r="D51" s="8" t="n"/>
+      <c r="E51" s="8" t="n"/>
+      <c r="F51" s="8" t="n"/>
+      <c r="G51" s="8" t="n"/>
+      <c r="H51" s="8" t="n"/>
+      <c r="I51" s="8" t="n"/>
+      <c r="J51" s="8" t="n"/>
+      <c r="K51" s="8" t="n"/>
+      <c r="L51" s="8" t="n"/>
+      <c r="M51" s="8" t="n"/>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
@@ -4548,7 +4964,7 @@
           <t>2026-10-06 09:15</t>
         </is>
       </c>
-      <c r="I52" s="6" t="inlineStr">
+      <c r="I52" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -4601,7 +5017,7 @@
           <t>2026-10-06 09:15</t>
         </is>
       </c>
-      <c r="I53" s="7" t="inlineStr">
+      <c r="I53" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -4654,7 +5070,7 @@
           <t>2026-10-06 09:15</t>
         </is>
       </c>
-      <c r="I54" s="7" t="inlineStr">
+      <c r="I54" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -4707,7 +5123,7 @@
           <t>2026-10-06 09:15</t>
         </is>
       </c>
-      <c r="I55" s="7" t="inlineStr">
+      <c r="I55" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -4760,7 +5176,7 @@
           <t>2026-10-07 09:15</t>
         </is>
       </c>
-      <c r="I56" s="7" t="inlineStr">
+      <c r="I56" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -4813,7 +5229,7 @@
           <t>2026-10-07 09:15</t>
         </is>
       </c>
-      <c r="I57" s="6" t="inlineStr">
+      <c r="I57" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -4866,7 +5282,7 @@
           <t>2026-10-07 09:15</t>
         </is>
       </c>
-      <c r="I58" s="6" t="inlineStr">
+      <c r="I58" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -4919,7 +5335,7 @@
           <t>2026-10-08 09:15</t>
         </is>
       </c>
-      <c r="I59" s="8" t="inlineStr">
+      <c r="I59" s="7" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -4944,49 +5360,49 @@
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>LTM</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>1316.5</v>
+        <v>3936</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>1308.7</v>
+        <v>3908.4</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>1323.7</v>
+        <v>3941.6</v>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>1.13% (15.0)</t>
+          <t>0.84% (33.2)</t>
         </is>
       </c>
       <c r="F60" s="4" t="n">
-        <v>1338.7</v>
+        <v>3974.8</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>1353.7</v>
+        <v>4008</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I60" s="6" t="inlineStr">
+      <c r="I60" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 10:15</t>
+          <t>2026-10-09 09:15</t>
         </is>
       </c>
       <c r="K60" s="2" t="n">
-        <v>1353.7</v>
+        <v>4008</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>2.27</v>
+        <v>1.68</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
@@ -4997,49 +5413,49 @@
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>902.05</v>
+        <v>1702.1</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>891.8</v>
+        <v>1701</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>903</v>
+        <v>1710.1</v>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>1.24% (11.2)</t>
+          <t>0.53% (9.1)</t>
         </is>
       </c>
       <c r="F61" s="4" t="n">
-        <v>914.2</v>
+        <v>1719.2</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>925.4</v>
+        <v>1728.3</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I61" s="8" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 09:15</t>
+          <t>2026-10-09 09:45</t>
         </is>
       </c>
       <c r="K61" s="2" t="n">
-        <v>891.8</v>
-      </c>
-      <c r="L61" s="3" t="n">
-        <v>-1.24</v>
+        <v>1728.3</v>
+      </c>
+      <c r="L61" s="4" t="n">
+        <v>1.06</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
@@ -5050,28 +5466,28 @@
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>254.65</v>
+        <v>1674.8</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>253.2</v>
+        <v>1658.6</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>255.4</v>
+        <v>1684.2</v>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>0.86% (2.2)</t>
+          <t>1.52% (25.6)</t>
         </is>
       </c>
       <c r="F62" s="4" t="n">
-        <v>257.6</v>
+        <v>1709.8</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>259.8</v>
+        <v>1735.4</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -5080,19 +5496,19 @@
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 10:00</t>
+          <t>2026-10-09 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K62" s="2" t="n">
-        <v>259.8</v>
-      </c>
-      <c r="L62" s="4" t="n">
-        <v>1.72</v>
+        <v>1682</v>
+      </c>
+      <c r="L62" s="3" t="n">
+        <v>-0.13</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
@@ -5103,28 +5519,28 @@
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>1674.8</v>
+        <v>902.05</v>
       </c>
       <c r="C63" s="3" t="n">
-        <v>1658.6</v>
+        <v>891.8</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>1684.2</v>
+        <v>903</v>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>1.52% (25.6)</t>
+          <t>1.24% (11.2)</t>
         </is>
       </c>
       <c r="F63" s="4" t="n">
-        <v>1709.8</v>
+        <v>914.2</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>1735.4</v>
+        <v>925.4</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -5133,19 +5549,19 @@
       </c>
       <c r="I63" s="7" t="inlineStr">
         <is>
-          <t>ACTIVE (Week End)</t>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 15:15 (Week End)</t>
+          <t>2026-10-09 09:15</t>
         </is>
       </c>
       <c r="K63" s="2" t="n">
-        <v>1682</v>
+        <v>891.8</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>-0.13</v>
+        <v>-1.24</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
@@ -5156,49 +5572,49 @@
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>1702.1</v>
+        <v>1316.5</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1701</v>
+        <v>1308.7</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>1710.1</v>
+        <v>1323.7</v>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>0.53% (9.1)</t>
+          <t>1.13% (15.0)</t>
         </is>
       </c>
       <c r="F64" s="4" t="n">
-        <v>1719.2</v>
+        <v>1338.7</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>1728.3</v>
+        <v>1353.7</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I64" s="6" t="inlineStr">
+      <c r="I64" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 09:45</t>
+          <t>2026-10-09 10:15</t>
         </is>
       </c>
       <c r="K64" s="2" t="n">
-        <v>1728.3</v>
+        <v>1353.7</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>1.06</v>
+        <v>2.27</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
@@ -5209,49 +5625,49 @@
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>LTM</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>3936</v>
+        <v>254.65</v>
       </c>
       <c r="C65" s="3" t="n">
-        <v>3908.4</v>
+        <v>253.2</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>3941.6</v>
+        <v>255.4</v>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>0.84% (33.2)</t>
+          <t>0.86% (2.2)</t>
         </is>
       </c>
       <c r="F65" s="4" t="n">
-        <v>3974.8</v>
+        <v>257.6</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>4008</v>
+        <v>259.8</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I65" s="6" t="inlineStr">
+      <c r="I65" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 09:15</t>
+          <t>2026-10-09 10:00</t>
         </is>
       </c>
       <c r="K65" s="2" t="n">
-        <v>4008</v>
+        <v>259.8</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
@@ -5260,23 +5676,23 @@
       </c>
     </row>
     <row r="66" ht="22" customHeight="1">
-      <c r="A66" s="5" t="inlineStr">
+      <c r="A66" s="8" t="inlineStr">
         <is>
           <t>Week Range: (12-10-2026 to 18-10-2026)</t>
         </is>
       </c>
-      <c r="B66" s="5" t="n"/>
-      <c r="C66" s="5" t="n"/>
-      <c r="D66" s="5" t="n"/>
-      <c r="E66" s="5" t="n"/>
-      <c r="F66" s="5" t="n"/>
-      <c r="G66" s="5" t="n"/>
-      <c r="H66" s="5" t="n"/>
-      <c r="I66" s="5" t="n"/>
-      <c r="J66" s="5" t="n"/>
-      <c r="K66" s="5" t="n"/>
-      <c r="L66" s="5" t="n"/>
-      <c r="M66" s="5" t="n"/>
+      <c r="B66" s="8" t="n"/>
+      <c r="C66" s="8" t="n"/>
+      <c r="D66" s="8" t="n"/>
+      <c r="E66" s="8" t="n"/>
+      <c r="F66" s="8" t="n"/>
+      <c r="G66" s="8" t="n"/>
+      <c r="H66" s="8" t="n"/>
+      <c r="I66" s="8" t="n"/>
+      <c r="J66" s="8" t="n"/>
+      <c r="K66" s="8" t="n"/>
+      <c r="L66" s="8" t="n"/>
+      <c r="M66" s="8" t="n"/>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
@@ -5309,7 +5725,7 @@
           <t>2026-10-13 09:15</t>
         </is>
       </c>
-      <c r="I67" s="7" t="inlineStr">
+      <c r="I67" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -5362,7 +5778,7 @@
           <t>2026-10-13 09:15</t>
         </is>
       </c>
-      <c r="I68" s="6" t="inlineStr">
+      <c r="I68" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -5415,7 +5831,7 @@
           <t>2026-10-13 09:15</t>
         </is>
       </c>
-      <c r="I69" s="6" t="inlineStr">
+      <c r="I69" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -5440,49 +5856,49 @@
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>403.85</v>
+        <v>1160.2</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>402.15</v>
+        <v>1152.6</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>410.15</v>
+        <v>1166.7</v>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>1.95% (8.0)</t>
+          <t>1.21% (14.1)</t>
         </is>
       </c>
       <c r="F70" s="4" t="n">
-        <v>418.15</v>
+        <v>1180.8</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>426.15</v>
+        <v>1194.9</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I70" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 11:45</t>
+          <t>2026-10-15 10:00</t>
         </is>
       </c>
       <c r="K70" s="2" t="n">
-        <v>418.15</v>
+        <v>1194.9</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>1.95</v>
+        <v>2.42</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
@@ -5493,28 +5909,28 @@
     <row r="71" ht="18" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>373.3</v>
+        <v>403.85</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>373</v>
+        <v>402.15</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>375.4</v>
+        <v>410.15</v>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>0.64% (2.4)</t>
+          <t>1.95% (8.0)</t>
         </is>
       </c>
       <c r="F71" s="4" t="n">
-        <v>377.8</v>
+        <v>418.15</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>380.2</v>
+        <v>426.15</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -5523,19 +5939,19 @@
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 09:15</t>
+          <t>2026-10-14 11:45</t>
         </is>
       </c>
       <c r="K71" s="2" t="n">
-        <v>380.2</v>
+        <v>418.15</v>
       </c>
       <c r="L71" s="4" t="n">
-        <v>1.28</v>
+        <v>1.95</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
@@ -5546,49 +5962,49 @@
     <row r="72" ht="18" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>441.05</v>
+        <v>373.3</v>
       </c>
       <c r="C72" s="3" t="n">
-        <v>440.55</v>
+        <v>373</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>445.8</v>
+        <v>375.4</v>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>1.18% (5.25)</t>
+          <t>0.64% (2.4)</t>
         </is>
       </c>
       <c r="F72" s="4" t="n">
-        <v>451.05</v>
+        <v>377.8</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>456.3</v>
+        <v>380.2</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I72" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 11:00</t>
+          <t>2026-10-14 09:15</t>
         </is>
       </c>
       <c r="K72" s="2" t="n">
-        <v>451.05</v>
+        <v>380.2</v>
       </c>
       <c r="L72" s="4" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
@@ -5599,28 +6015,28 @@
     <row r="73" ht="18" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>461</v>
+        <v>441.05</v>
       </c>
       <c r="C73" s="3" t="n">
-        <v>457.5</v>
+        <v>440.55</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>461.75</v>
+        <v>445.8</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>0.92% (4.25)</t>
+          <t>1.18% (5.25)</t>
         </is>
       </c>
       <c r="F73" s="4" t="n">
-        <v>466</v>
+        <v>451.05</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>470.25</v>
+        <v>456.3</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -5629,19 +6045,19 @@
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 09:30</t>
+          <t>2026-10-14 11:00</t>
         </is>
       </c>
       <c r="K73" s="2" t="n">
-        <v>470.25</v>
+        <v>451.05</v>
       </c>
       <c r="L73" s="4" t="n">
-        <v>1.84</v>
+        <v>1.18</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
@@ -5652,49 +6068,49 @@
     <row r="74" ht="18" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>1160.2</v>
+        <v>461</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>1152.6</v>
+        <v>457.5</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>1166.7</v>
+        <v>461.75</v>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>1.21% (14.1)</t>
+          <t>0.92% (4.25)</t>
         </is>
       </c>
       <c r="F74" s="4" t="n">
-        <v>1180.8</v>
+        <v>466</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>1194.9</v>
+        <v>470.25</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I74" s="6" t="inlineStr">
+      <c r="I74" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 10:00</t>
+          <t>2026-10-14 09:30</t>
         </is>
       </c>
       <c r="K74" s="2" t="n">
-        <v>1194.9</v>
+        <v>470.25</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>2.42</v>
+        <v>1.84</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
@@ -5733,7 +6149,7 @@
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I75" s="6" t="inlineStr">
+      <c r="I75" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -5786,7 +6202,7 @@
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I76" s="7" t="inlineStr">
+      <c r="I76" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -5839,7 +6255,7 @@
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I77" s="6" t="inlineStr">
+      <c r="I77" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -5892,7 +6308,7 @@
           <t>2026-10-14 09:30</t>
         </is>
       </c>
-      <c r="I78" s="7" t="inlineStr">
+      <c r="I78" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -5945,7 +6361,7 @@
           <t>2026-10-14 09:45</t>
         </is>
       </c>
-      <c r="I79" s="6" t="inlineStr">
+      <c r="I79" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
@@ -5998,7 +6414,7 @@
           <t>2026-10-14 11:30</t>
         </is>
       </c>
-      <c r="I80" s="7" t="inlineStr">
+      <c r="I80" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -6051,7 +6467,7 @@
           <t>2026-10-14 13:45</t>
         </is>
       </c>
-      <c r="I81" s="8" t="inlineStr">
+      <c r="I81" s="7" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -6104,7 +6520,7 @@
           <t>2026-10-15 09:15</t>
         </is>
       </c>
-      <c r="I82" s="7" t="inlineStr">
+      <c r="I82" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -6129,35 +6545,35 @@
     <row r="83" ht="18" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>886.5</v>
+        <v>2559.6</v>
       </c>
       <c r="C83" s="3" t="n">
-        <v>860.1</v>
+        <v>2550</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>887</v>
+        <v>2593</v>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>3.03% (26.9)</t>
+          <t>1.66% (43.0)</t>
         </is>
       </c>
       <c r="F83" s="4" t="n">
-        <v>913.9</v>
+        <v>2636</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>940.8</v>
+        <v>2679</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
           <t>2026-10-16 09:15</t>
         </is>
       </c>
-      <c r="I83" s="7" t="inlineStr">
+      <c r="I83" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -6168,10 +6584,10 @@
         </is>
       </c>
       <c r="K83" s="2" t="n">
-        <v>908</v>
+        <v>2598.3</v>
       </c>
       <c r="L83" s="4" t="n">
-        <v>2.37</v>
+        <v>0.2</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
@@ -6182,49 +6598,49 @@
     <row r="84" ht="18" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>3607</v>
+        <v>166.3</v>
       </c>
       <c r="C84" s="3" t="n">
-        <v>3593.2</v>
+        <v>165.87</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>3627.5</v>
+        <v>166.83</v>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>0.95% (34.3)</t>
+          <t>0.58% (0.96)</t>
         </is>
       </c>
       <c r="F84" s="4" t="n">
-        <v>3661.8</v>
+        <v>167.79</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>3696.1</v>
+        <v>168.75</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
           <t>2026-10-16 09:15</t>
         </is>
       </c>
-      <c r="I84" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I84" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 11:30</t>
+          <t>2026-10-16 09:15</t>
         </is>
       </c>
       <c r="K84" s="2" t="n">
-        <v>3661.8</v>
+        <v>168.75</v>
       </c>
       <c r="L84" s="4" t="n">
-        <v>0.95</v>
+        <v>1.15</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
@@ -6235,28 +6651,28 @@
     <row r="85" ht="18" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>166.3</v>
+        <v>11225</v>
       </c>
       <c r="C85" s="3" t="n">
-        <v>165.87</v>
+        <v>11130</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>166.83</v>
+        <v>11325</v>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>0.58% (0.96)</t>
+          <t>1.72% (195.0)</t>
         </is>
       </c>
       <c r="F85" s="4" t="n">
-        <v>167.79</v>
+        <v>11520</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>168.75</v>
+        <v>11715</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -6265,19 +6681,19 @@
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 09:15</t>
+          <t>2026-10-16 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K85" s="2" t="n">
-        <v>168.75</v>
+        <v>11489</v>
       </c>
       <c r="L85" s="4" t="n">
-        <v>1.15</v>
+        <v>1.45</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
@@ -6288,35 +6704,35 @@
     <row r="86" ht="18" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>11225</v>
+        <v>886.5</v>
       </c>
       <c r="C86" s="3" t="n">
-        <v>11130</v>
+        <v>860.1</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>11325</v>
+        <v>887</v>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>1.72% (195.0)</t>
+          <t>3.03% (26.9)</t>
         </is>
       </c>
       <c r="F86" s="4" t="n">
-        <v>11520</v>
+        <v>913.9</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>11715</v>
+        <v>940.8</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
           <t>2026-10-16 09:15</t>
         </is>
       </c>
-      <c r="I86" s="7" t="inlineStr">
+      <c r="I86" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -6327,10 +6743,10 @@
         </is>
       </c>
       <c r="K86" s="2" t="n">
-        <v>11489</v>
+        <v>908</v>
       </c>
       <c r="L86" s="4" t="n">
-        <v>1.45</v>
+        <v>2.37</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
@@ -6341,49 +6757,49 @@
     <row r="87" ht="18" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>2559.6</v>
+        <v>3607</v>
       </c>
       <c r="C87" s="3" t="n">
-        <v>2550</v>
+        <v>3593.2</v>
       </c>
       <c r="D87" s="4" t="n">
-        <v>2593</v>
+        <v>3627.5</v>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>1.66% (43.0)</t>
+          <t>0.95% (34.3)</t>
         </is>
       </c>
       <c r="F87" s="4" t="n">
-        <v>2636</v>
+        <v>3661.8</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>2679</v>
+        <v>3696.1</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
           <t>2026-10-16 09:15</t>
         </is>
       </c>
-      <c r="I87" s="7" t="inlineStr">
+      <c r="I87" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 15:15 (Week End)</t>
+          <t>2026-10-16 11:30</t>
         </is>
       </c>
       <c r="K87" s="2" t="n">
-        <v>2598.3</v>
+        <v>3661.8</v>
       </c>
       <c r="L87" s="4" t="n">
-        <v>0.2</v>
+        <v>0.95</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
@@ -6392,23 +6808,23 @@
       </c>
     </row>
     <row r="88" ht="22" customHeight="1">
-      <c r="A88" s="5" t="inlineStr">
+      <c r="A88" s="8" t="inlineStr">
         <is>
           <t>Week Range: (19-10-2026 to 25-10-2026)</t>
         </is>
       </c>
-      <c r="B88" s="5" t="n"/>
-      <c r="C88" s="5" t="n"/>
-      <c r="D88" s="5" t="n"/>
-      <c r="E88" s="5" t="n"/>
-      <c r="F88" s="5" t="n"/>
-      <c r="G88" s="5" t="n"/>
-      <c r="H88" s="5" t="n"/>
-      <c r="I88" s="5" t="n"/>
-      <c r="J88" s="5" t="n"/>
-      <c r="K88" s="5" t="n"/>
-      <c r="L88" s="5" t="n"/>
-      <c r="M88" s="5" t="n"/>
+      <c r="B88" s="8" t="n"/>
+      <c r="C88" s="8" t="n"/>
+      <c r="D88" s="8" t="n"/>
+      <c r="E88" s="8" t="n"/>
+      <c r="F88" s="8" t="n"/>
+      <c r="G88" s="8" t="n"/>
+      <c r="H88" s="8" t="n"/>
+      <c r="I88" s="8" t="n"/>
+      <c r="J88" s="8" t="n"/>
+      <c r="K88" s="8" t="n"/>
+      <c r="L88" s="8" t="n"/>
+      <c r="M88" s="8" t="n"/>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
@@ -6441,7 +6857,7 @@
           <t>2026-10-21 09:15</t>
         </is>
       </c>
-      <c r="I89" s="8" t="inlineStr">
+      <c r="I89" s="7" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -6494,7 +6910,7 @@
           <t>2026-10-21 09:15</t>
         </is>
       </c>
-      <c r="I90" s="8" t="inlineStr">
+      <c r="I90" s="7" t="inlineStr">
         <is>
           <t>SL HIT</t>
         </is>
@@ -6547,7 +6963,7 @@
           <t>2026-10-22 09:15</t>
         </is>
       </c>
-      <c r="I91" s="7" t="inlineStr">
+      <c r="I91" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -6572,28 +6988,28 @@
     <row r="92" ht="18" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>165.87</v>
+        <v>1003.5</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>164.88</v>
+        <v>1001.4</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>165.92</v>
+        <v>1028</v>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>0.63% (1.04)</t>
+          <t>2.59% (26.6)</t>
         </is>
       </c>
       <c r="F92" s="4" t="n">
-        <v>166.96</v>
+        <v>1054.6</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>168</v>
+        <v>1081.2</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -6602,19 +7018,19 @@
       </c>
       <c r="I92" s="6" t="inlineStr">
         <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:30</t>
+          <t>2026-10-23 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K92" s="2" t="n">
-        <v>164.88</v>
+        <v>1015.9</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>-0.63</v>
+        <v>-1.18</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
@@ -6625,35 +7041,35 @@
     <row r="93" ht="18" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>4550.4</v>
+        <v>1725.5</v>
       </c>
       <c r="C93" s="3" t="n">
-        <v>4474.6</v>
+        <v>1719.6</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>4572.1</v>
+        <v>1745.1</v>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>2.13% (97.5)</t>
+          <t>1.46% (25.5)</t>
         </is>
       </c>
       <c r="F93" s="4" t="n">
-        <v>4669.6</v>
+        <v>1770.6</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>4767.1</v>
+        <v>1796.1</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
           <t>2026-10-23 09:15</t>
         </is>
       </c>
-      <c r="I93" s="7" t="inlineStr">
+      <c r="I93" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
@@ -6664,10 +7080,10 @@
         </is>
       </c>
       <c r="K93" s="2" t="n">
-        <v>4524.4</v>
-      </c>
-      <c r="L93" s="3" t="n">
-        <v>-1.04</v>
+        <v>1748</v>
+      </c>
+      <c r="L93" s="4" t="n">
+        <v>0.17</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
@@ -6678,49 +7094,49 @@
     <row r="94" ht="18" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>2843.4</v>
+        <v>1107.3</v>
       </c>
       <c r="C94" s="3" t="n">
-        <v>2828.2</v>
+        <v>1100.3</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>2889.1</v>
+        <v>1117.3</v>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>2.11% (60.9)</t>
+          <t>1.52% (17.0)</t>
         </is>
       </c>
       <c r="F94" s="4" t="n">
-        <v>2950</v>
+        <v>1134.3</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>3010.9</v>
+        <v>1151.3</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
           <t>2026-10-23 09:15</t>
         </is>
       </c>
-      <c r="I94" s="7" t="inlineStr">
+      <c r="I94" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 15:15 (Week End)</t>
+          <t>2026-10-23 09:15</t>
         </is>
       </c>
       <c r="K94" s="2" t="n">
-        <v>2894</v>
+        <v>1134.3</v>
       </c>
       <c r="L94" s="4" t="n">
-        <v>0.17</v>
+        <v>1.52</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
@@ -6731,49 +7147,49 @@
     <row r="95" ht="18" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>437.2</v>
+        <v>1300.2</v>
       </c>
       <c r="C95" s="3" t="n">
-        <v>433.75</v>
+        <v>1296.7</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>438.2</v>
+        <v>1314</v>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>1.02% (4.45)</t>
+          <t>1.32% (17.3)</t>
         </is>
       </c>
       <c r="F95" s="4" t="n">
-        <v>442.65</v>
+        <v>1331.3</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>447.1</v>
+        <v>1348.6</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
           <t>2026-10-23 09:15</t>
         </is>
       </c>
-      <c r="I95" s="8" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 10:00</t>
+          <t>2026-10-23 09:15</t>
         </is>
       </c>
       <c r="K95" s="2" t="n">
-        <v>433.75</v>
-      </c>
-      <c r="L95" s="3" t="n">
-        <v>-1.02</v>
+        <v>1331.3</v>
+      </c>
+      <c r="L95" s="4" t="n">
+        <v>1.32</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
@@ -6784,49 +7200,49 @@
     <row r="96" ht="18" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>1300.2</v>
+        <v>2843.4</v>
       </c>
       <c r="C96" s="3" t="n">
-        <v>1296.7</v>
+        <v>2828.2</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>1314</v>
+        <v>2889.1</v>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>1.32% (17.3)</t>
+          <t>2.11% (60.9)</t>
         </is>
       </c>
       <c r="F96" s="4" t="n">
-        <v>1331.3</v>
+        <v>2950</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>1348.6</v>
+        <v>3010.9</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
           <t>2026-10-23 09:15</t>
         </is>
       </c>
-      <c r="I96" s="7" t="inlineStr">
+      <c r="I96" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:15</t>
+          <t>2026-10-23 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K96" s="2" t="n">
-        <v>1331.3</v>
+        <v>2894</v>
       </c>
       <c r="L96" s="4" t="n">
-        <v>1.32</v>
+        <v>0.17</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
@@ -6837,49 +7253,49 @@
     <row r="97" ht="18" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>1107.3</v>
+        <v>4550.4</v>
       </c>
       <c r="C97" s="3" t="n">
-        <v>1100.3</v>
+        <v>4474.6</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>1117.3</v>
+        <v>4572.1</v>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>1.52% (17.0)</t>
+          <t>2.13% (97.5)</t>
         </is>
       </c>
       <c r="F97" s="4" t="n">
-        <v>1134.3</v>
+        <v>4669.6</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>1151.3</v>
+        <v>4767.1</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
           <t>2026-10-23 09:15</t>
         </is>
       </c>
-      <c r="I97" s="7" t="inlineStr">
+      <c r="I97" s="6" t="inlineStr">
         <is>
           <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:15</t>
+          <t>2026-10-23 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K97" s="2" t="n">
-        <v>1134.3</v>
-      </c>
-      <c r="L97" s="4" t="n">
-        <v>1.52</v>
+        <v>4524.4</v>
+      </c>
+      <c r="L97" s="3" t="n">
+        <v>-1.04</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
@@ -6890,49 +7306,49 @@
     <row r="98" ht="18" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>1725.5</v>
+        <v>165.87</v>
       </c>
       <c r="C98" s="3" t="n">
-        <v>1719.6</v>
+        <v>164.88</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>1745.1</v>
+        <v>165.92</v>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>1.46% (25.5)</t>
+          <t>0.63% (1.04)</t>
         </is>
       </c>
       <c r="F98" s="4" t="n">
-        <v>1770.6</v>
+        <v>166.96</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>1796.1</v>
+        <v>168</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
           <t>2026-10-23 09:15</t>
         </is>
       </c>
-      <c r="I98" s="7" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I98" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 15:15 (Week End)</t>
+          <t>2026-10-23 09:30</t>
         </is>
       </c>
       <c r="K98" s="2" t="n">
-        <v>1748</v>
-      </c>
-      <c r="L98" s="4" t="n">
-        <v>0.17</v>
+        <v>164.88</v>
+      </c>
+      <c r="L98" s="3" t="n">
+        <v>-0.63</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
@@ -6943,28 +7359,28 @@
     <row r="99" ht="18" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>1003.5</v>
+        <v>437.2</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>1001.4</v>
+        <v>433.75</v>
       </c>
       <c r="D99" s="4" t="n">
-        <v>1028</v>
+        <v>438.2</v>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>2.59% (26.6)</t>
+          <t>1.02% (4.45)</t>
         </is>
       </c>
       <c r="F99" s="4" t="n">
-        <v>1054.6</v>
+        <v>442.65</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>1081.2</v>
+        <v>447.1</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -6973,19 +7389,19 @@
       </c>
       <c r="I99" s="7" t="inlineStr">
         <is>
-          <t>ACTIVE (Week End)</t>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 15:15 (Week End)</t>
+          <t>2026-10-23 10:00</t>
         </is>
       </c>
       <c r="K99" s="2" t="n">
-        <v>1015.9</v>
+        <v>433.75</v>
       </c>
       <c r="L99" s="3" t="n">
-        <v>-1.18</v>
+        <v>-1.02</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
@@ -6993,10 +7409,1302 @@
         </is>
       </c>
     </row>
+    <row r="100" ht="22" customHeight="1">
+      <c r="A100" s="8" t="inlineStr">
+        <is>
+          <t>Week Range: (26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+      <c r="B100" s="8" t="n"/>
+      <c r="C100" s="8" t="n"/>
+      <c r="D100" s="8" t="n"/>
+      <c r="E100" s="8" t="n"/>
+      <c r="F100" s="8" t="n"/>
+      <c r="G100" s="8" t="n"/>
+      <c r="H100" s="8" t="n"/>
+      <c r="I100" s="8" t="n"/>
+      <c r="J100" s="8" t="n"/>
+      <c r="K100" s="8" t="n"/>
+      <c r="L100" s="8" t="n"/>
+      <c r="M100" s="8" t="n"/>
+    </row>
+    <row r="101" ht="18" customHeight="1">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>MAZDOCK</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="n">
+        <v>1845</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>1838.7</v>
+      </c>
+      <c r="D101" s="4" t="n">
+        <v>1860.9</v>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>1.19% (22.2)</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="n">
+        <v>1883.1</v>
+      </c>
+      <c r="G101" s="4" t="n">
+        <v>1905.3</v>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I101" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>1905.3</v>
+      </c>
+      <c r="L101" s="4" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="18" customHeight="1">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>VEDL</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="n">
+        <v>223.35</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>221.8</v>
+      </c>
+      <c r="D102" s="4" t="n">
+        <v>225</v>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>1.42% (3.2)</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="n">
+        <v>228.2</v>
+      </c>
+      <c r="G102" s="4" t="n">
+        <v>231.4</v>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I102" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>228.2</v>
+      </c>
+      <c r="L102" s="4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="n">
+        <v>3898.1</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>3875.1</v>
+      </c>
+      <c r="D103" s="4" t="n">
+        <v>3961.9</v>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>2.19% (86.8)</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="n">
+        <v>4048.7</v>
+      </c>
+      <c r="G103" s="4" t="n">
+        <v>4135.5</v>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I103" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>4048.7</v>
+      </c>
+      <c r="L103" s="4" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="18" customHeight="1">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="n">
+        <v>4470.4</v>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>4467.3</v>
+      </c>
+      <c r="D104" s="4" t="n">
+        <v>4565</v>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>2.14% (97.7)</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="n">
+        <v>4662.7</v>
+      </c>
+      <c r="G104" s="4" t="n">
+        <v>4760.4</v>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I104" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>4625</v>
+      </c>
+      <c r="L104" s="4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>RECLTD</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="n">
+        <v>290.65</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>289.5</v>
+      </c>
+      <c r="D105" s="4" t="n">
+        <v>291.8</v>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>0.79% (2.3)</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="n">
+        <v>294.1</v>
+      </c>
+      <c r="G105" s="4" t="n">
+        <v>296.4</v>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I105" s="7" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>289.5</v>
+      </c>
+      <c r="L105" s="3" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="18" customHeight="1">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="n">
+        <v>119.06</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>118.25</v>
+      </c>
+      <c r="D106" s="4" t="n">
+        <v>119.24</v>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>0.83% (0.99)</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="n">
+        <v>120.23</v>
+      </c>
+      <c r="G106" s="4" t="n">
+        <v>121.22</v>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I106" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>121.22</v>
+      </c>
+      <c r="L106" s="4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="18" customHeight="1">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="n">
+        <v>444.9</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>441.7</v>
+      </c>
+      <c r="D107" s="4" t="n">
+        <v>447.5</v>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>1.3% (5.8)</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="n">
+        <v>453.3</v>
+      </c>
+      <c r="G107" s="4" t="n">
+        <v>459.1</v>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I107" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>453.3</v>
+      </c>
+      <c r="L107" s="4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="18" customHeight="1">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>NHPC</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="n">
+        <v>69.03</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>68.84</v>
+      </c>
+      <c r="D108" s="4" t="n">
+        <v>69.33</v>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>0.71% (0.49)</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="n">
+        <v>69.81999999999999</v>
+      </c>
+      <c r="G108" s="4" t="n">
+        <v>70.31</v>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I108" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>70.31</v>
+      </c>
+      <c r="L108" s="4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="18" customHeight="1">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="n">
+        <v>1177.6</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>1169.8</v>
+      </c>
+      <c r="D109" s="4" t="n">
+        <v>1188.2</v>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>1.55% (18.4)</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="n">
+        <v>1206.6</v>
+      </c>
+      <c r="G109" s="4" t="n">
+        <v>1225</v>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I109" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 10:00</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>1206.6</v>
+      </c>
+      <c r="L109" s="4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="18" customHeight="1">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="n">
+        <v>148.07</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>147.32</v>
+      </c>
+      <c r="D110" s="4" t="n">
+        <v>148.9</v>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>1.06% (1.58)</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="n">
+        <v>150.48</v>
+      </c>
+      <c r="G110" s="4" t="n">
+        <v>152.06</v>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I110" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="n">
+        <v>152.06</v>
+      </c>
+      <c r="L110" s="4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>LODHA</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="n">
+        <v>941</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>939.8</v>
+      </c>
+      <c r="D111" s="4" t="n">
+        <v>948.2</v>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>0.89% (8.4)</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="n">
+        <v>956.6</v>
+      </c>
+      <c r="G111" s="4" t="n">
+        <v>965</v>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I111" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>965</v>
+      </c>
+      <c r="L111" s="4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="18" customHeight="1">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="n">
+        <v>1100.3</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>1094</v>
+      </c>
+      <c r="D112" s="4" t="n">
+        <v>1158.5</v>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>5.57% (64.5)</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="n">
+        <v>1223</v>
+      </c>
+      <c r="G112" s="4" t="n">
+        <v>1287.5</v>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I112" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>1172.9</v>
+      </c>
+      <c r="L112" s="4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="18" customHeight="1">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="n">
+        <v>254.8</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>254.5</v>
+      </c>
+      <c r="D113" s="4" t="n">
+        <v>256.25</v>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>0.68% (1.75)</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="n">
+        <v>258</v>
+      </c>
+      <c r="G113" s="4" t="n">
+        <v>259.75</v>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I113" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>259.75</v>
+      </c>
+      <c r="L113" s="4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="18" customHeight="1">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="n">
+        <v>852</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>851.35</v>
+      </c>
+      <c r="D114" s="4" t="n">
+        <v>864</v>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>1.46% (12.65)</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="n">
+        <v>876.65</v>
+      </c>
+      <c r="G114" s="4" t="n">
+        <v>889.3</v>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I114" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>889.3</v>
+      </c>
+      <c r="L114" s="4" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="18" customHeight="1">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="n">
+        <v>4994.5</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>4977.5</v>
+      </c>
+      <c r="D115" s="4" t="n">
+        <v>5054.5</v>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>1.52% (77.0)</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="n">
+        <v>5131.5</v>
+      </c>
+      <c r="G115" s="4" t="n">
+        <v>5208.5</v>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I115" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>5208.5</v>
+      </c>
+      <c r="L115" s="4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="18" customHeight="1">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="n">
+        <v>4716.3</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>4642.1</v>
+      </c>
+      <c r="D116" s="4" t="n">
+        <v>4733</v>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>1.92% (90.9)</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="n">
+        <v>4823.9</v>
+      </c>
+      <c r="G116" s="4" t="n">
+        <v>4914.8</v>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I116" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:30</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>4914.8</v>
+      </c>
+      <c r="L116" s="4" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="18" customHeight="1">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>CANBK</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="n">
+        <v>115.37</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>114.72</v>
+      </c>
+      <c r="D117" s="4" t="n">
+        <v>115.75</v>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>0.89% (1.03)</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="n">
+        <v>116.78</v>
+      </c>
+      <c r="G117" s="4" t="n">
+        <v>117.81</v>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I117" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>117.81</v>
+      </c>
+      <c r="L117" s="4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="18" customHeight="1">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="n">
+        <v>4515</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>4507.9</v>
+      </c>
+      <c r="D118" s="4" t="n">
+        <v>4540.1</v>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>0.71% (32.2)</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="n">
+        <v>4572.3</v>
+      </c>
+      <c r="G118" s="4" t="n">
+        <v>4604.5</v>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I118" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="n">
+        <v>4572.3</v>
+      </c>
+      <c r="L118" s="4" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="18" customHeight="1">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>BANKBARODA</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="n">
+        <v>229.2</v>
+      </c>
+      <c r="C119" s="3" t="n">
+        <v>227.3</v>
+      </c>
+      <c r="D119" s="4" t="n">
+        <v>229.7</v>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>1.04% (2.4)</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="n">
+        <v>232.1</v>
+      </c>
+      <c r="G119" s="4" t="n">
+        <v>234.5</v>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I119" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="n">
+        <v>232.1</v>
+      </c>
+      <c r="L119" s="4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="18" customHeight="1">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="n">
+        <v>2260</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>2234.3</v>
+      </c>
+      <c r="D120" s="4" t="n">
+        <v>2283.3</v>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>2.15% (49.0)</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="n">
+        <v>2332.3</v>
+      </c>
+      <c r="G120" s="4" t="n">
+        <v>2381.3</v>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I120" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="n">
+        <v>2277</v>
+      </c>
+      <c r="L120" s="3" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="18" customHeight="1">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="n">
+        <v>6070</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>6065</v>
+      </c>
+      <c r="D121" s="4" t="n">
+        <v>6152</v>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>1.41% (87.0)</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="n">
+        <v>6239</v>
+      </c>
+      <c r="G121" s="4" t="n">
+        <v>6326</v>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I121" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="n">
+        <v>6326</v>
+      </c>
+      <c r="L121" s="4" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="18" customHeight="1">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>JSWENERGY</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="n">
+        <v>440.15</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>440.15</v>
+      </c>
+      <c r="D122" s="4" t="n">
+        <v>446.35</v>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>1.39% (6.2)</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="n">
+        <v>452.55</v>
+      </c>
+      <c r="G122" s="4" t="n">
+        <v>458.75</v>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I122" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="n">
+        <v>458.75</v>
+      </c>
+      <c r="L122" s="4" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="18" customHeight="1">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="n">
+        <v>1450</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>1415</v>
+      </c>
+      <c r="D123" s="4" t="n">
+        <v>1452.6</v>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>2.59% (37.6)</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="n">
+        <v>1490.2</v>
+      </c>
+      <c r="G123" s="4" t="n">
+        <v>1527.8</v>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="I123" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="n">
+        <v>1469</v>
+      </c>
+      <c r="L123" s="4" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="18" customHeight="1">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>BAJFINANCE</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="n">
+        <v>907.4</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>906.55</v>
+      </c>
+      <c r="D124" s="4" t="n">
+        <v>920.6</v>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>1.53% (14.05)</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="n">
+        <v>934.65</v>
+      </c>
+      <c r="G124" s="4" t="n">
+        <v>948.7</v>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:30</t>
+        </is>
+      </c>
+      <c r="I124" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="n">
+        <v>912</v>
+      </c>
+      <c r="L124" s="3" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A66:M66"/>
     <mergeCell ref="A88:M88"/>
+    <mergeCell ref="A100:M100"/>
     <mergeCell ref="A15:M15"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A51:M51"/>

--- a/data/trade_tracker_results.xlsx
+++ b/data/trade_tracker_results.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:L46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -707,24 +707,22 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:15</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>2277</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>-0.28</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -737,42 +735,40 @@
         <v>907.4</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>906.55</v>
+        <v>900.05</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>920.6</v>
+        <v>913.05</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>1.53% (14.05)</t>
+          <t>1.42% (13.0)</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>934.65</v>
+        <v>926.05</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>948.7</v>
+        <v>939.05</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:30</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>912</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>-0.93</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -833,42 +829,40 @@
         <v>4515</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>4507.9</v>
+        <v>4500</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>4540.1</v>
+        <v>4564</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>0.71% (32.2)</t>
+          <t>1.4% (64.0)</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>4572.3</v>
+        <v>4628</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>4604.5</v>
+        <v>4692</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:15</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:15</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>4572.3</v>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="4" t="n">
-        <v>0.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -1165,42 +1159,40 @@
         <v>254.8</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>254.5</v>
+        <v>252.85</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>256.25</v>
+        <v>255.9</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>0.68% (1.75)</t>
+          <t>1.19% (3.05)</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>258</v>
+        <v>258.95</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>259.75</v>
+        <v>262</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:15</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:15</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>259.75</v>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="4" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -1405,42 +1397,40 @@
         <v>1177.6</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1169.8</v>
+        <v>1139.2</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1188.2</v>
+        <v>1261.4</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>1.55% (18.4)</t>
+          <t>9.69% (122.2)</t>
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1206.6</v>
+        <v>1383.6</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1225</v>
+        <v>1505.8</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:15</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 10:00</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="n">
-        <v>1206.6</v>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="4" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -1552,18 +1542,18 @@
         <v>310.5</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>314.45</v>
+        <v>315.4</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>1.26% (3.95)</t>
+          <t>1.55% (4.9)</t>
         </is>
       </c>
       <c r="F22" s="4" t="n">
-        <v>318.4</v>
+        <v>320.3</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>322.35</v>
+        <v>325.2</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1643,42 +1633,40 @@
         <v>290.65</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>289.5</v>
+        <v>283.7</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>291.8</v>
+        <v>298.2</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>0.79% (2.3)</t>
+          <t>4.86% (14.5)</t>
         </is>
       </c>
       <c r="F24" s="4" t="n">
-        <v>294.1</v>
+        <v>312.7</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>296.4</v>
+        <v>327.2</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:15</t>
-        </is>
-      </c>
-      <c r="I24" s="7" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:15</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="n">
-        <v>289.5</v>
-      </c>
-      <c r="L24" s="3" t="n">
-        <v>-0.79</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -1765,14 +1753,14 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 15:15 (Active)</t>
+          <t>2026-10-28 15:15 (Active)</t>
         </is>
       </c>
       <c r="K26" s="2" t="n">
-        <v>4625</v>
-      </c>
-      <c r="L26" s="4" t="n">
-        <v>1.31</v>
+        <v>4557</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>-0.18</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -1808,19 +1796,19 @@
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:15</t>
+          <t>2026-10-28 11:30</t>
         </is>
       </c>
       <c r="K27" s="2" t="n">
-        <v>4048.7</v>
+        <v>4135.5</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>2.19</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -1856,19 +1844,19 @@
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:15</t>
+          <t>2026-10-28 12:30</t>
         </is>
       </c>
       <c r="K28" s="2" t="n">
-        <v>228.2</v>
+        <v>231.4</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>1.42</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -1909,14 +1897,14 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 15:15 (Active)</t>
+          <t>2026-10-28 15:15 (Active)</t>
         </is>
       </c>
       <c r="K29" s="2" t="n">
-        <v>1172.9</v>
+        <v>1175.5</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>1.24</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -1993,22 +1981,24 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-28 09:15</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr"/>
-      <c r="L31" s="4" t="n">
-        <v>0</v>
+          <t>2026-10-28 10:15</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>10735</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>-1.11</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2042,21 +2032,21 @@
           <t>2026-10-27 09:15</t>
         </is>
       </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 15:15 (Active)</t>
+          <t>2026-10-28 13:30</t>
         </is>
       </c>
       <c r="K32" s="2" t="n">
-        <v>1469</v>
+        <v>1527.8</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>1.13</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -2087,22 +2077,24 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-28 09:15</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr"/>
+          <t>2026-10-28 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>360</v>
+      </c>
       <c r="L33" s="4" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -2225,22 +2217,24 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-28 09:15</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr"/>
+          <t>2026-10-28 09:45</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>446.75</v>
+      </c>
       <c r="L36" s="4" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -2271,21 +2265,437 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
+          <t>2026-10-28 09:15</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:45</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>1270.5</v>
+      </c>
+      <c r="L37" s="4" t="n">
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>1635</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>1628.2</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>1680</v>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>3.08% (51.8)</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>1731.8</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>1783.6</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>WAIT (No Entry)</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="4" t="n">
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>511.5</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>508.4</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>516.75</v>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>1.62% (8.35)</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>525.1</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>533.45</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>1375.1</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>1361.4</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>1387.9</v>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>1.91% (26.5)</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>1414.4</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>1440.9</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>1580</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>1556.1</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>1583.9</v>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>1.76% (27.8)</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>1611.7</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>1639.5</v>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>LTM</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>4100</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>3930.5</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>4125</v>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>4.72% (194.5)</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>4319.5</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>4514</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>1156.2</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>1148</v>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>1180.5</v>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>2.75% (32.5)</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>1213</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>1245.5</v>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>TMPV</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>259.35</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>259.3</v>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>262.35</v>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>1.16% (3.05)</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>265.4</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>268.45</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>2432.1</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>2408.2</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>2432.4</v>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>0.99% (24.2)</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>2456.6</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>2480.8</v>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>1738.33</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>1734.9</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>1811.4</v>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>4.22% (76.5)</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>1887.9</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>1964.4</v>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2300,7 +2710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M124"/>
+  <dimension ref="A1:M128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4334,49 +4744,49 @@
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>196.1</v>
+        <v>4848.5</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>192.45</v>
+        <v>4837</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>196.67</v>
+        <v>4872</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>2.15% (4.22)</t>
+          <t>0.72% (35.0)</t>
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>200.89</v>
+        <v>4907</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>205.11</v>
+        <v>4942</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I40" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:15</t>
+          <t>2026-09-30 10:30</t>
         </is>
       </c>
       <c r="K40" s="2" t="n">
-        <v>200.89</v>
-      </c>
-      <c r="L40" s="4" t="n">
-        <v>2.15</v>
+        <v>4837</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>-0.72</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
@@ -4387,49 +4797,49 @@
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>399.3</v>
+        <v>1766.7</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>394.7</v>
+        <v>1736.8</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>403.65</v>
+        <v>1770.1</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>2.22% (8.95)</t>
+          <t>1.88% (33.3)</t>
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>412.6</v>
+        <v>1803.4</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>421.55</v>
+        <v>1836.7</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 09:15</t>
+          <t>2026-09-30 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K41" s="2" t="n">
-        <v>421.55</v>
+        <v>1798.3</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>4.43</v>
+        <v>1.59</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
@@ -4440,49 +4850,49 @@
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>4057</v>
+        <v>2391</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>4043.3</v>
+        <v>2381.6</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>4095</v>
+        <v>2420</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>1.26% (51.7)</t>
+          <t>1.59% (38.4)</t>
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>4146.7</v>
+        <v>2458.4</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>4198.4</v>
+        <v>2496.8</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I42" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 09:15</t>
+          <t>2026-09-30 12:30 (Week End)</t>
         </is>
       </c>
       <c r="K42" s="2" t="n">
-        <v>4043.3</v>
+        <v>2409.1</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>-1.26</v>
+        <v>-0.45</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
@@ -4493,49 +4903,49 @@
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>160.5</v>
+        <v>263.55</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>159.41</v>
+        <v>263.3</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>162.37</v>
+        <v>266.2</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>1.82% (2.96)</t>
+          <t>1.09% (2.9)</t>
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>165.33</v>
+        <v>269.1</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>168.29</v>
+        <v>272</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I43" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 15:15 (Week End)</t>
+          <t>2026-09-30 14:15</t>
         </is>
       </c>
       <c r="K43" s="2" t="n">
-        <v>163.26</v>
-      </c>
-      <c r="L43" s="4" t="n">
-        <v>0.55</v>
+        <v>263.3</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>-1.09</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
@@ -4546,49 +4956,49 @@
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>263.55</v>
+        <v>991.6</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>263.3</v>
+        <v>980.4</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>266.2</v>
+        <v>992.7</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>1.09% (2.9)</t>
+          <t>1.24% (12.3)</t>
         </is>
       </c>
       <c r="F44" s="4" t="n">
-        <v>269.1</v>
+        <v>1005</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>272</v>
+        <v>1017.3</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I44" s="7" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:15</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
       <c r="K44" s="2" t="n">
-        <v>263.3</v>
-      </c>
-      <c r="L44" s="3" t="n">
-        <v>-1.09</v>
+        <v>1017.3</v>
+      </c>
+      <c r="L44" s="4" t="n">
+        <v>2.48</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
@@ -4599,49 +5009,49 @@
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>2391</v>
+        <v>4057</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>2381.6</v>
+        <v>4043.3</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>2420</v>
+        <v>4095</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>1.59% (38.4)</t>
+          <t>1.26% (51.7)</t>
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>2458.4</v>
+        <v>4146.7</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>2496.8</v>
+        <v>4198.4</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:30 (Week End)</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="K45" s="2" t="n">
-        <v>2409.1</v>
+        <v>4043.3</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>-0.45</v>
+        <v>-1.26</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
@@ -4652,28 +5062,28 @@
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>991.6</v>
+        <v>399.3</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>980.4</v>
+        <v>394.7</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>992.7</v>
+        <v>403.65</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>1.24% (12.3)</t>
+          <t>2.22% (8.95)</t>
         </is>
       </c>
       <c r="F46" s="4" t="n">
-        <v>1005</v>
+        <v>412.6</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>1017.3</v>
+        <v>421.55</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -4687,14 +5097,14 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="K46" s="2" t="n">
-        <v>1017.3</v>
+        <v>421.55</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>2.48</v>
+        <v>4.43</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
@@ -4705,28 +5115,28 @@
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>1766.7</v>
+        <v>196.1</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>1736.8</v>
+        <v>192.45</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>1770.1</v>
+        <v>196.67</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>1.88% (33.3)</t>
+          <t>2.15% (4.22)</t>
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>1803.4</v>
+        <v>200.89</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>1836.7</v>
+        <v>205.11</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -4740,14 +5150,14 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 15:15 (Week End)</t>
+          <t>2026-09-30 09:15</t>
         </is>
       </c>
       <c r="K47" s="2" t="n">
-        <v>1798.3</v>
+        <v>200.89</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>1.59</v>
+        <v>2.15</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
@@ -4758,49 +5168,49 @@
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>4848.5</v>
+        <v>160.5</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>4837</v>
+        <v>159.41</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>4872</v>
+        <v>162.37</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>0.72% (35.0)</t>
+          <t>1.82% (2.96)</t>
         </is>
       </c>
       <c r="F48" s="4" t="n">
-        <v>4907</v>
+        <v>165.33</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>4942</v>
+        <v>168.29</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I48" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 10:30</t>
+          <t>2026-09-30 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K48" s="2" t="n">
-        <v>4837</v>
-      </c>
-      <c r="L48" s="3" t="n">
-        <v>-0.72</v>
+        <v>163.26</v>
+      </c>
+      <c r="L48" s="4" t="n">
+        <v>0.55</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
@@ -5360,28 +5770,28 @@
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>LTM</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>3936</v>
+        <v>1316.5</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>3908.4</v>
+        <v>1308.7</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>3941.6</v>
+        <v>1323.7</v>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>0.84% (33.2)</t>
+          <t>1.13% (15.0)</t>
         </is>
       </c>
       <c r="F60" s="4" t="n">
-        <v>3974.8</v>
+        <v>1338.7</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>4008</v>
+        <v>1353.7</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -5395,14 +5805,14 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 09:15</t>
+          <t>2026-10-09 10:15</t>
         </is>
       </c>
       <c r="K60" s="2" t="n">
-        <v>4008</v>
+        <v>1353.7</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>1.68</v>
+        <v>2.27</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
@@ -5413,49 +5823,49 @@
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>1702.1</v>
+        <v>902.05</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>1701</v>
+        <v>891.8</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>1710.1</v>
+        <v>903</v>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>0.53% (9.1)</t>
+          <t>1.24% (11.2)</t>
         </is>
       </c>
       <c r="F61" s="4" t="n">
-        <v>1719.2</v>
+        <v>914.2</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>1728.3</v>
+        <v>925.4</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I61" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I61" s="7" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 09:45</t>
+          <t>2026-10-09 09:15</t>
         </is>
       </c>
       <c r="K61" s="2" t="n">
-        <v>1728.3</v>
-      </c>
-      <c r="L61" s="4" t="n">
-        <v>1.06</v>
+        <v>891.8</v>
+      </c>
+      <c r="L61" s="3" t="n">
+        <v>-1.24</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
@@ -5466,49 +5876,49 @@
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>1674.8</v>
+        <v>254.65</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>1658.6</v>
+        <v>253.2</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>1684.2</v>
+        <v>255.4</v>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>1.52% (25.6)</t>
+          <t>0.86% (2.2)</t>
         </is>
       </c>
       <c r="F62" s="4" t="n">
-        <v>1709.8</v>
+        <v>257.6</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>1735.4</v>
+        <v>259.8</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I62" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 15:15 (Week End)</t>
+          <t>2026-10-09 10:00</t>
         </is>
       </c>
       <c r="K62" s="2" t="n">
-        <v>1682</v>
-      </c>
-      <c r="L62" s="3" t="n">
-        <v>-0.13</v>
+        <v>259.8</v>
+      </c>
+      <c r="L62" s="4" t="n">
+        <v>1.72</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
@@ -5519,49 +5929,49 @@
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>902.05</v>
+        <v>1702.1</v>
       </c>
       <c r="C63" s="3" t="n">
-        <v>891.8</v>
+        <v>1701</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>903</v>
+        <v>1710.1</v>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>1.24% (11.2)</t>
+          <t>0.53% (9.1)</t>
         </is>
       </c>
       <c r="F63" s="4" t="n">
-        <v>914.2</v>
+        <v>1719.2</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>925.4</v>
+        <v>1728.3</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I63" s="7" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 09:15</t>
+          <t>2026-10-09 09:45</t>
         </is>
       </c>
       <c r="K63" s="2" t="n">
-        <v>891.8</v>
-      </c>
-      <c r="L63" s="3" t="n">
-        <v>-1.24</v>
+        <v>1728.3</v>
+      </c>
+      <c r="L63" s="4" t="n">
+        <v>1.06</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
@@ -5572,49 +5982,49 @@
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>1316.5</v>
+        <v>1674.8</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1308.7</v>
+        <v>1658.6</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>1323.7</v>
+        <v>1684.2</v>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>1.13% (15.0)</t>
+          <t>1.52% (25.6)</t>
         </is>
       </c>
       <c r="F64" s="4" t="n">
-        <v>1338.7</v>
+        <v>1709.8</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>1353.7</v>
+        <v>1735.4</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I64" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 10:15</t>
+          <t>2026-10-09 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K64" s="2" t="n">
-        <v>1353.7</v>
-      </c>
-      <c r="L64" s="4" t="n">
-        <v>2.27</v>
+        <v>1682</v>
+      </c>
+      <c r="L64" s="3" t="n">
+        <v>-0.13</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
@@ -5625,28 +6035,28 @@
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>LTM</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>254.65</v>
+        <v>3936</v>
       </c>
       <c r="C65" s="3" t="n">
-        <v>253.2</v>
+        <v>3908.4</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>255.4</v>
+        <v>3941.6</v>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>0.86% (2.2)</t>
+          <t>0.84% (33.2)</t>
         </is>
       </c>
       <c r="F65" s="4" t="n">
-        <v>257.6</v>
+        <v>3974.8</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>259.8</v>
+        <v>4008</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -5660,14 +6070,14 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 10:00</t>
+          <t>2026-10-09 09:15</t>
         </is>
       </c>
       <c r="K65" s="2" t="n">
-        <v>259.8</v>
+        <v>4008</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
@@ -6988,49 +7398,49 @@
     <row r="92" ht="18" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>1003.5</v>
+        <v>165.87</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>1001.4</v>
+        <v>164.88</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>1028</v>
+        <v>165.92</v>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>2.59% (26.6)</t>
+          <t>0.63% (1.04)</t>
         </is>
       </c>
       <c r="F92" s="4" t="n">
-        <v>1054.6</v>
+        <v>166.96</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>1081.2</v>
+        <v>168</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
           <t>2026-10-23 09:15</t>
         </is>
       </c>
-      <c r="I92" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I92" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 15:15 (Week End)</t>
+          <t>2026-10-23 09:30</t>
         </is>
       </c>
       <c r="K92" s="2" t="n">
-        <v>1015.9</v>
+        <v>164.88</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>-1.18</v>
+        <v>-0.63</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
@@ -7041,28 +7451,28 @@
     <row r="93" ht="18" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>1725.5</v>
+        <v>4550.4</v>
       </c>
       <c r="C93" s="3" t="n">
-        <v>1719.6</v>
+        <v>4474.6</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>1745.1</v>
+        <v>4572.1</v>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>1.46% (25.5)</t>
+          <t>2.13% (97.5)</t>
         </is>
       </c>
       <c r="F93" s="4" t="n">
-        <v>1770.6</v>
+        <v>4669.6</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>1796.1</v>
+        <v>4767.1</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -7080,10 +7490,10 @@
         </is>
       </c>
       <c r="K93" s="2" t="n">
-        <v>1748</v>
-      </c>
-      <c r="L93" s="4" t="n">
-        <v>0.17</v>
+        <v>4524.4</v>
+      </c>
+      <c r="L93" s="3" t="n">
+        <v>-1.04</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
@@ -7094,49 +7504,49 @@
     <row r="94" ht="18" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>1107.3</v>
+        <v>437.2</v>
       </c>
       <c r="C94" s="3" t="n">
-        <v>1100.3</v>
+        <v>433.75</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>1117.3</v>
+        <v>438.2</v>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>1.52% (17.0)</t>
+          <t>1.02% (4.45)</t>
         </is>
       </c>
       <c r="F94" s="4" t="n">
-        <v>1134.3</v>
+        <v>442.65</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>1151.3</v>
+        <v>447.1</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
           <t>2026-10-23 09:15</t>
         </is>
       </c>
-      <c r="I94" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I94" s="7" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:15</t>
+          <t>2026-10-23 10:00</t>
         </is>
       </c>
       <c r="K94" s="2" t="n">
-        <v>1134.3</v>
-      </c>
-      <c r="L94" s="4" t="n">
-        <v>1.52</v>
+        <v>433.75</v>
+      </c>
+      <c r="L94" s="3" t="n">
+        <v>-1.02</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
@@ -7147,28 +7557,28 @@
     <row r="95" ht="18" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>1300.2</v>
+        <v>2843.4</v>
       </c>
       <c r="C95" s="3" t="n">
-        <v>1296.7</v>
+        <v>2828.2</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>1314</v>
+        <v>2889.1</v>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>1.32% (17.3)</t>
+          <t>2.11% (60.9)</t>
         </is>
       </c>
       <c r="F95" s="4" t="n">
-        <v>1331.3</v>
+        <v>2950</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>1348.6</v>
+        <v>3010.9</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -7182,14 +7592,14 @@
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:15</t>
+          <t>2026-10-23 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K95" s="2" t="n">
-        <v>1331.3</v>
+        <v>2894</v>
       </c>
       <c r="L95" s="4" t="n">
-        <v>1.32</v>
+        <v>0.17</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
@@ -7200,28 +7610,28 @@
     <row r="96" ht="18" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>2843.4</v>
+        <v>1107.3</v>
       </c>
       <c r="C96" s="3" t="n">
-        <v>2828.2</v>
+        <v>1100.3</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>2889.1</v>
+        <v>1117.3</v>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>2.11% (60.9)</t>
+          <t>1.52% (17.0)</t>
         </is>
       </c>
       <c r="F96" s="4" t="n">
-        <v>2950</v>
+        <v>1134.3</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>3010.9</v>
+        <v>1151.3</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -7235,14 +7645,14 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 15:15 (Week End)</t>
+          <t>2026-10-23 09:15</t>
         </is>
       </c>
       <c r="K96" s="2" t="n">
-        <v>2894</v>
+        <v>1134.3</v>
       </c>
       <c r="L96" s="4" t="n">
-        <v>0.17</v>
+        <v>1.52</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
@@ -7253,28 +7663,28 @@
     <row r="97" ht="18" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>4550.4</v>
+        <v>1725.5</v>
       </c>
       <c r="C97" s="3" t="n">
-        <v>4474.6</v>
+        <v>1719.6</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>4572.1</v>
+        <v>1745.1</v>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>2.13% (97.5)</t>
+          <t>1.46% (25.5)</t>
         </is>
       </c>
       <c r="F97" s="4" t="n">
-        <v>4669.6</v>
+        <v>1770.6</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>4767.1</v>
+        <v>1796.1</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -7292,10 +7702,10 @@
         </is>
       </c>
       <c r="K97" s="2" t="n">
-        <v>4524.4</v>
-      </c>
-      <c r="L97" s="3" t="n">
-        <v>-1.04</v>
+        <v>1748</v>
+      </c>
+      <c r="L97" s="4" t="n">
+        <v>0.17</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
@@ -7306,49 +7716,49 @@
     <row r="98" ht="18" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>165.87</v>
+        <v>1003.5</v>
       </c>
       <c r="C98" s="3" t="n">
-        <v>164.88</v>
+        <v>1001.4</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>165.92</v>
+        <v>1028</v>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>0.63% (1.04)</t>
+          <t>2.59% (26.6)</t>
         </is>
       </c>
       <c r="F98" s="4" t="n">
-        <v>166.96</v>
+        <v>1054.6</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>168</v>
+        <v>1081.2</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
           <t>2026-10-23 09:15</t>
         </is>
       </c>
-      <c r="I98" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:30</t>
+          <t>2026-10-23 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K98" s="2" t="n">
-        <v>164.88</v>
+        <v>1015.9</v>
       </c>
       <c r="L98" s="3" t="n">
-        <v>-0.63</v>
+        <v>-1.18</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
@@ -7359,49 +7769,49 @@
     <row r="99" ht="18" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>437.2</v>
+        <v>1300.2</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>433.75</v>
+        <v>1296.7</v>
       </c>
       <c r="D99" s="4" t="n">
-        <v>438.2</v>
+        <v>1314</v>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>1.02% (4.45)</t>
+          <t>1.32% (17.3)</t>
         </is>
       </c>
       <c r="F99" s="4" t="n">
-        <v>442.65</v>
+        <v>1331.3</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>447.1</v>
+        <v>1348.6</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
           <t>2026-10-23 09:15</t>
         </is>
       </c>
-      <c r="I99" s="7" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I99" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 10:00</t>
+          <t>2026-10-23 09:15</t>
         </is>
       </c>
       <c r="K99" s="2" t="n">
-        <v>433.75</v>
-      </c>
-      <c r="L99" s="3" t="n">
-        <v>-1.02</v>
+        <v>1331.3</v>
+      </c>
+      <c r="L99" s="4" t="n">
+        <v>1.32</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
@@ -7431,28 +7841,28 @@
     <row r="101" ht="18" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>1845</v>
+        <v>1450</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>1838.7</v>
+        <v>1415</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>1860.9</v>
+        <v>1452.6</v>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>1.19% (22.2)</t>
+          <t>2.59% (37.6)</t>
         </is>
       </c>
       <c r="F101" s="4" t="n">
-        <v>1883.1</v>
+        <v>1490.2</v>
       </c>
       <c r="G101" s="4" t="n">
-        <v>1905.3</v>
+        <v>1527.8</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -7466,14 +7876,14 @@
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:15</t>
+          <t>2026-10-28 13:30</t>
         </is>
       </c>
       <c r="K101" s="2" t="n">
-        <v>1905.3</v>
+        <v>1527.8</v>
       </c>
       <c r="L101" s="4" t="n">
-        <v>2.39</v>
+        <v>5.18</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
@@ -7484,49 +7894,49 @@
     <row r="102" ht="18" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>223.35</v>
+        <v>1100.3</v>
       </c>
       <c r="C102" s="3" t="n">
-        <v>221.8</v>
+        <v>1094</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>225</v>
+        <v>1158.5</v>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>1.42% (3.2)</t>
+          <t>5.57% (64.5)</t>
         </is>
       </c>
       <c r="F102" s="4" t="n">
-        <v>228.2</v>
+        <v>1223</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>231.4</v>
+        <v>1287.5</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
           <t>2026-10-27 09:15</t>
         </is>
       </c>
-      <c r="I102" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+      <c r="I102" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:15</t>
+          <t>2026-10-28 15:15 (Active)</t>
         </is>
       </c>
       <c r="K102" s="2" t="n">
-        <v>228.2</v>
+        <v>1175.5</v>
       </c>
       <c r="L102" s="4" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
@@ -7537,28 +7947,28 @@
     <row r="103" ht="18" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>3898.1</v>
+        <v>223.35</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>3875.1</v>
+        <v>221.8</v>
       </c>
       <c r="D103" s="4" t="n">
-        <v>3961.9</v>
+        <v>225</v>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>2.19% (86.8)</t>
+          <t>1.42% (3.2)</t>
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>4048.7</v>
+        <v>228.2</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>4135.5</v>
+        <v>231.4</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -7567,19 +7977,19 @@
       </c>
       <c r="I103" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:15</t>
+          <t>2026-10-28 12:30</t>
         </is>
       </c>
       <c r="K103" s="2" t="n">
-        <v>4048.7</v>
+        <v>231.4</v>
       </c>
       <c r="L103" s="4" t="n">
-        <v>2.19</v>
+        <v>2.84</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
@@ -7590,49 +8000,49 @@
     <row r="104" ht="18" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>4470.4</v>
+        <v>3898.1</v>
       </c>
       <c r="C104" s="3" t="n">
-        <v>4467.3</v>
+        <v>3875.1</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>4565</v>
+        <v>3961.9</v>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>2.14% (97.7)</t>
+          <t>2.19% (86.8)</t>
         </is>
       </c>
       <c r="F104" s="4" t="n">
-        <v>4662.7</v>
+        <v>4048.7</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>4760.4</v>
+        <v>4135.5</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
           <t>2026-10-27 09:15</t>
         </is>
       </c>
-      <c r="I104" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I104" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 15:15 (Active)</t>
+          <t>2026-10-28 11:30</t>
         </is>
       </c>
       <c r="K104" s="2" t="n">
-        <v>4625</v>
+        <v>4135.5</v>
       </c>
       <c r="L104" s="4" t="n">
-        <v>1.31</v>
+        <v>4.38</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
@@ -7643,49 +8053,49 @@
     <row r="105" ht="18" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B105" s="2" t="n">
-        <v>290.65</v>
+        <v>4470.4</v>
       </c>
       <c r="C105" s="3" t="n">
-        <v>289.5</v>
+        <v>4467.3</v>
       </c>
       <c r="D105" s="4" t="n">
-        <v>291.8</v>
+        <v>4565</v>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>0.79% (2.3)</t>
+          <t>2.14% (97.7)</t>
         </is>
       </c>
       <c r="F105" s="4" t="n">
-        <v>294.1</v>
+        <v>4662.7</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>296.4</v>
+        <v>4760.4</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
           <t>2026-10-27 09:15</t>
         </is>
       </c>
-      <c r="I105" s="7" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I105" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:15</t>
+          <t>2026-10-28 15:15 (Active)</t>
         </is>
       </c>
       <c r="K105" s="2" t="n">
-        <v>289.5</v>
+        <v>4557</v>
       </c>
       <c r="L105" s="3" t="n">
-        <v>-0.79</v>
+        <v>-0.18</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
@@ -7855,28 +8265,28 @@
     <row r="109" ht="18" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B109" s="2" t="n">
-        <v>1177.6</v>
+        <v>148.07</v>
       </c>
       <c r="C109" s="3" t="n">
-        <v>1169.8</v>
+        <v>147.32</v>
       </c>
       <c r="D109" s="4" t="n">
-        <v>1188.2</v>
+        <v>148.9</v>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>1.55% (18.4)</t>
+          <t>1.06% (1.58)</t>
         </is>
       </c>
       <c r="F109" s="4" t="n">
-        <v>1206.6</v>
+        <v>150.48</v>
       </c>
       <c r="G109" s="4" t="n">
-        <v>1225</v>
+        <v>152.06</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -7885,19 +8295,19 @@
       </c>
       <c r="I109" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 10:00</t>
+          <t>2026-10-27 09:15</t>
         </is>
       </c>
       <c r="K109" s="2" t="n">
-        <v>1206.6</v>
+        <v>152.06</v>
       </c>
       <c r="L109" s="4" t="n">
-        <v>1.55</v>
+        <v>2.12</v>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
@@ -7908,28 +8318,28 @@
     <row r="110" ht="18" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="B110" s="2" t="n">
-        <v>148.07</v>
+        <v>1845</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>147.32</v>
+        <v>1838.7</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>148.9</v>
+        <v>1860.9</v>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>1.06% (1.58)</t>
+          <t>1.19% (22.2)</t>
         </is>
       </c>
       <c r="F110" s="4" t="n">
-        <v>150.48</v>
+        <v>1883.1</v>
       </c>
       <c r="G110" s="4" t="n">
-        <v>152.06</v>
+        <v>1905.3</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -7947,10 +8357,10 @@
         </is>
       </c>
       <c r="K110" s="2" t="n">
-        <v>152.06</v>
+        <v>1905.3</v>
       </c>
       <c r="L110" s="4" t="n">
-        <v>2.12</v>
+        <v>2.39</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
@@ -8014,49 +8424,49 @@
     <row r="112" ht="18" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="B112" s="2" t="n">
-        <v>1100.3</v>
+        <v>440.15</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>1094</v>
+        <v>440.15</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>1158.5</v>
+        <v>446.35</v>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>5.57% (64.5)</t>
+          <t>1.39% (6.2)</t>
         </is>
       </c>
       <c r="F112" s="4" t="n">
-        <v>1223</v>
+        <v>452.55</v>
       </c>
       <c r="G112" s="4" t="n">
-        <v>1287.5</v>
+        <v>458.75</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
           <t>2026-10-27 09:15</t>
         </is>
       </c>
-      <c r="I112" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I112" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 15:15 (Active)</t>
+          <t>2026-10-27 09:15</t>
         </is>
       </c>
       <c r="K112" s="2" t="n">
-        <v>1172.9</v>
+        <v>458.75</v>
       </c>
       <c r="L112" s="4" t="n">
-        <v>1.24</v>
+        <v>2.78</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
@@ -8067,28 +8477,28 @@
     <row r="113" ht="18" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="B113" s="2" t="n">
-        <v>254.8</v>
+        <v>852</v>
       </c>
       <c r="C113" s="3" t="n">
-        <v>254.5</v>
+        <v>851.35</v>
       </c>
       <c r="D113" s="4" t="n">
-        <v>256.25</v>
+        <v>864</v>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>0.68% (1.75)</t>
+          <t>1.46% (12.65)</t>
         </is>
       </c>
       <c r="F113" s="4" t="n">
-        <v>258</v>
+        <v>876.65</v>
       </c>
       <c r="G113" s="4" t="n">
-        <v>259.75</v>
+        <v>889.3</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -8106,10 +8516,10 @@
         </is>
       </c>
       <c r="K113" s="2" t="n">
-        <v>259.75</v>
+        <v>889.3</v>
       </c>
       <c r="L113" s="4" t="n">
-        <v>1.37</v>
+        <v>2.93</v>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
@@ -8120,28 +8530,28 @@
     <row r="114" ht="18" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="B114" s="2" t="n">
-        <v>852</v>
+        <v>4716.3</v>
       </c>
       <c r="C114" s="3" t="n">
-        <v>851.35</v>
+        <v>4642.1</v>
       </c>
       <c r="D114" s="4" t="n">
-        <v>864</v>
+        <v>4733</v>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>1.46% (12.65)</t>
+          <t>1.92% (90.9)</t>
         </is>
       </c>
       <c r="F114" s="4" t="n">
-        <v>876.65</v>
+        <v>4823.9</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>889.3</v>
+        <v>4914.8</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -8155,14 +8565,14 @@
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:15</t>
+          <t>2026-10-27 09:30</t>
         </is>
       </c>
       <c r="K114" s="2" t="n">
-        <v>889.3</v>
+        <v>4914.8</v>
       </c>
       <c r="L114" s="4" t="n">
-        <v>2.93</v>
+        <v>3.84</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
@@ -8173,28 +8583,28 @@
     <row r="115" ht="18" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="B115" s="2" t="n">
-        <v>4994.5</v>
+        <v>115.37</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>4977.5</v>
+        <v>114.72</v>
       </c>
       <c r="D115" s="4" t="n">
-        <v>5054.5</v>
+        <v>115.75</v>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>1.52% (77.0)</t>
+          <t>0.89% (1.03)</t>
         </is>
       </c>
       <c r="F115" s="4" t="n">
-        <v>5131.5</v>
+        <v>116.78</v>
       </c>
       <c r="G115" s="4" t="n">
-        <v>5208.5</v>
+        <v>117.81</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -8212,10 +8622,10 @@
         </is>
       </c>
       <c r="K115" s="2" t="n">
-        <v>5208.5</v>
+        <v>117.81</v>
       </c>
       <c r="L115" s="4" t="n">
-        <v>3.05</v>
+        <v>1.78</v>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
@@ -8226,28 +8636,28 @@
     <row r="116" ht="18" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
       <c r="B116" s="2" t="n">
-        <v>4716.3</v>
+        <v>229.2</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>4642.1</v>
+        <v>227.3</v>
       </c>
       <c r="D116" s="4" t="n">
-        <v>4733</v>
+        <v>229.7</v>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>1.92% (90.9)</t>
+          <t>1.04% (2.4)</t>
         </is>
       </c>
       <c r="F116" s="4" t="n">
-        <v>4823.9</v>
+        <v>232.1</v>
       </c>
       <c r="G116" s="4" t="n">
-        <v>4914.8</v>
+        <v>234.5</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -8256,19 +8666,19 @@
       </c>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:30</t>
+          <t>2026-10-27 09:15</t>
         </is>
       </c>
       <c r="K116" s="2" t="n">
-        <v>4914.8</v>
+        <v>232.1</v>
       </c>
       <c r="L116" s="4" t="n">
-        <v>3.84</v>
+        <v>1.04</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
@@ -8279,28 +8689,28 @@
     <row r="117" ht="18" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="B117" s="2" t="n">
-        <v>115.37</v>
+        <v>6070</v>
       </c>
       <c r="C117" s="3" t="n">
-        <v>114.72</v>
+        <v>6065</v>
       </c>
       <c r="D117" s="4" t="n">
-        <v>115.75</v>
+        <v>6152</v>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>0.89% (1.03)</t>
+          <t>1.41% (87.0)</t>
         </is>
       </c>
       <c r="F117" s="4" t="n">
-        <v>116.78</v>
+        <v>6239</v>
       </c>
       <c r="G117" s="4" t="n">
-        <v>117.81</v>
+        <v>6326</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
@@ -8318,10 +8728,10 @@
         </is>
       </c>
       <c r="K117" s="2" t="n">
-        <v>117.81</v>
+        <v>6326</v>
       </c>
       <c r="L117" s="4" t="n">
-        <v>1.78</v>
+        <v>2.83</v>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
@@ -8332,49 +8742,49 @@
     <row r="118" ht="18" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B118" s="2" t="n">
-        <v>4515</v>
+        <v>2260</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>4507.9</v>
+        <v>2234.3</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>4540.1</v>
+        <v>2283.3</v>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>0.71% (32.2)</t>
+          <t>2.15% (49.0)</t>
         </is>
       </c>
       <c r="F118" s="4" t="n">
-        <v>4572.3</v>
+        <v>2332.3</v>
       </c>
       <c r="G118" s="4" t="n">
-        <v>4604.5</v>
+        <v>2381.3</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
           <t>2026-10-27 09:15</t>
         </is>
       </c>
-      <c r="I118" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+      <c r="I118" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:15</t>
+          <t>2026-10-27 15:15 (Active)</t>
         </is>
       </c>
       <c r="K118" s="2" t="n">
-        <v>4572.3</v>
-      </c>
-      <c r="L118" s="4" t="n">
-        <v>0.71</v>
+        <v>2277</v>
+      </c>
+      <c r="L118" s="3" t="n">
+        <v>-0.28</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
@@ -8385,28 +8795,28 @@
     <row r="119" ht="18" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B119" s="2" t="n">
-        <v>229.2</v>
+        <v>4515</v>
       </c>
       <c r="C119" s="3" t="n">
-        <v>227.3</v>
+        <v>4507.9</v>
       </c>
       <c r="D119" s="4" t="n">
-        <v>229.7</v>
+        <v>4540.1</v>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>1.04% (2.4)</t>
+          <t>0.71% (32.2)</t>
         </is>
       </c>
       <c r="F119" s="4" t="n">
-        <v>232.1</v>
+        <v>4572.3</v>
       </c>
       <c r="G119" s="4" t="n">
-        <v>234.5</v>
+        <v>4604.5</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -8424,10 +8834,10 @@
         </is>
       </c>
       <c r="K119" s="2" t="n">
-        <v>232.1</v>
+        <v>4572.3</v>
       </c>
       <c r="L119" s="4" t="n">
-        <v>1.04</v>
+        <v>0.71</v>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
@@ -8438,49 +8848,49 @@
     <row r="120" ht="18" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B120" s="2" t="n">
-        <v>2260</v>
+        <v>254.8</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>2234.3</v>
+        <v>254.5</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>2283.3</v>
+        <v>256.25</v>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>2.15% (49.0)</t>
+          <t>0.68% (1.75)</t>
         </is>
       </c>
       <c r="F120" s="4" t="n">
-        <v>2332.3</v>
+        <v>258</v>
       </c>
       <c r="G120" s="4" t="n">
-        <v>2381.3</v>
+        <v>259.75</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
           <t>2026-10-27 09:15</t>
         </is>
       </c>
-      <c r="I120" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I120" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 15:15 (Active)</t>
+          <t>2026-10-27 09:15</t>
         </is>
       </c>
       <c r="K120" s="2" t="n">
-        <v>2277</v>
-      </c>
-      <c r="L120" s="3" t="n">
-        <v>-0.28</v>
+        <v>259.75</v>
+      </c>
+      <c r="L120" s="4" t="n">
+        <v>1.37</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
@@ -8491,28 +8901,28 @@
     <row r="121" ht="18" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="B121" s="2" t="n">
-        <v>6070</v>
+        <v>1177.6</v>
       </c>
       <c r="C121" s="3" t="n">
-        <v>6065</v>
+        <v>1169.8</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>6152</v>
+        <v>1188.2</v>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>1.41% (87.0)</t>
+          <t>1.55% (18.4)</t>
         </is>
       </c>
       <c r="F121" s="4" t="n">
-        <v>6239</v>
+        <v>1206.6</v>
       </c>
       <c r="G121" s="4" t="n">
-        <v>6326</v>
+        <v>1225</v>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
@@ -8521,19 +8931,19 @@
       </c>
       <c r="I121" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:15</t>
+          <t>2026-10-27 10:00</t>
         </is>
       </c>
       <c r="K121" s="2" t="n">
-        <v>6326</v>
+        <v>1206.6</v>
       </c>
       <c r="L121" s="4" t="n">
-        <v>2.83</v>
+        <v>1.55</v>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
@@ -8544,37 +8954,37 @@
     <row r="122" ht="18" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="B122" s="2" t="n">
-        <v>440.15</v>
+        <v>290.65</v>
       </c>
       <c r="C122" s="3" t="n">
-        <v>440.15</v>
+        <v>289.5</v>
       </c>
       <c r="D122" s="4" t="n">
-        <v>446.35</v>
+        <v>291.8</v>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>1.39% (6.2)</t>
+          <t>0.79% (2.3)</t>
         </is>
       </c>
       <c r="F122" s="4" t="n">
-        <v>452.55</v>
+        <v>294.1</v>
       </c>
       <c r="G122" s="4" t="n">
-        <v>458.75</v>
+        <v>296.4</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
           <t>2026-10-27 09:15</t>
         </is>
       </c>
-      <c r="I122" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I122" s="7" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
@@ -8583,10 +8993,10 @@
         </is>
       </c>
       <c r="K122" s="2" t="n">
-        <v>458.75</v>
-      </c>
-      <c r="L122" s="4" t="n">
-        <v>2.78</v>
+        <v>289.5</v>
+      </c>
+      <c r="L122" s="3" t="n">
+        <v>-0.79</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
@@ -8597,49 +9007,49 @@
     <row r="123" ht="18" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="B123" s="2" t="n">
-        <v>1450</v>
+        <v>4994.5</v>
       </c>
       <c r="C123" s="3" t="n">
-        <v>1415</v>
+        <v>4977.5</v>
       </c>
       <c r="D123" s="4" t="n">
-        <v>1452.6</v>
+        <v>5054.5</v>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>2.59% (37.6)</t>
+          <t>1.52% (77.0)</t>
         </is>
       </c>
       <c r="F123" s="4" t="n">
-        <v>1490.2</v>
+        <v>5131.5</v>
       </c>
       <c r="G123" s="4" t="n">
-        <v>1527.8</v>
+        <v>5208.5</v>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
           <t>2026-10-27 09:15</t>
         </is>
       </c>
-      <c r="I123" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I123" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 15:15 (Active)</t>
+          <t>2026-10-27 09:15</t>
         </is>
       </c>
       <c r="K123" s="2" t="n">
-        <v>1469</v>
+        <v>5208.5</v>
       </c>
       <c r="L123" s="4" t="n">
-        <v>1.13</v>
+        <v>3.05</v>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
@@ -8695,6 +9105,218 @@
         <v>-0.93</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="18" customHeight="1">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="n">
+        <v>10834</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>10735</v>
+      </c>
+      <c r="D125" s="4" t="n">
+        <v>10856</v>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>1.11% (121.0)</t>
+        </is>
+      </c>
+      <c r="F125" s="4" t="n">
+        <v>10977</v>
+      </c>
+      <c r="G125" s="4" t="n">
+        <v>11098</v>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:15</t>
+        </is>
+      </c>
+      <c r="I125" s="7" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 10:15</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>10735</v>
+      </c>
+      <c r="L125" s="3" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="18" customHeight="1">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="n">
+        <v>437.45</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>437</v>
+      </c>
+      <c r="D126" s="4" t="n">
+        <v>440.25</v>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>0.74% (3.25)</t>
+        </is>
+      </c>
+      <c r="F126" s="4" t="n">
+        <v>443.5</v>
+      </c>
+      <c r="G126" s="4" t="n">
+        <v>446.75</v>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:15</t>
+        </is>
+      </c>
+      <c r="I126" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:45</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>446.75</v>
+      </c>
+      <c r="L126" s="4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="18" customHeight="1">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>DABUR</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="n">
+        <v>356.05</v>
+      </c>
+      <c r="C127" s="3" t="n">
+        <v>354.3</v>
+      </c>
+      <c r="D127" s="4" t="n">
+        <v>359.3</v>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>1.39% (5.0)</t>
+        </is>
+      </c>
+      <c r="F127" s="4" t="n">
+        <v>364.3</v>
+      </c>
+      <c r="G127" s="4" t="n">
+        <v>369.3</v>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:15</t>
+        </is>
+      </c>
+      <c r="I127" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="L127" s="4" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="18" customHeight="1">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>UNITDSPR</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="n">
+        <v>1240</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>1227</v>
+      </c>
+      <c r="D128" s="4" t="n">
+        <v>1241.5</v>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>1.17% (14.5)</t>
+        </is>
+      </c>
+      <c r="F128" s="4" t="n">
+        <v>1256</v>
+      </c>
+      <c r="G128" s="4" t="n">
+        <v>1270.5</v>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:15</t>
+        </is>
+      </c>
+      <c r="I128" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:45</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>1270.5</v>
+      </c>
+      <c r="L128" s="4" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
         <is>
           <t>(26-10-2026 to 01-11-2026)</t>
         </is>

--- a/data/trade_tracker_results.xlsx
+++ b/data/trade_tracker_results.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L46"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -661,22 +661,24 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-29 09:15</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr"/>
+          <t>2026-10-29 14:00</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>2611.6</v>
+      </c>
       <c r="L3" s="4" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -689,21 +691,21 @@
         <v>2260</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2234.3</v>
+        <v>2220</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>2283.3</v>
+        <v>2282.3</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>2.15% (49.0)</t>
+          <t>2.73% (62.3)</t>
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>2332.3</v>
+        <v>2344.6</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>2381.3</v>
+        <v>2406.9</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -753,22 +755,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-29 09:15</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr"/>
+          <t>2026-10-29 14:00</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>939.05</v>
+      </c>
       <c r="L5" s="4" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -804,19 +808,19 @@
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:15</t>
+          <t>2026-10-29 09:15</t>
         </is>
       </c>
       <c r="K6" s="2" t="n">
-        <v>232.1</v>
+        <v>234.5</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>1.04</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -847,22 +851,24 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-29 09:15</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr"/>
+          <t>2026-10-29 14:45</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>4692</v>
+      </c>
       <c r="L7" s="4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -1131,22 +1137,24 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-29 09:15</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr"/>
+          <t>2026-10-29 14:15</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>75.67</v>
+      </c>
       <c r="L13" s="4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -1177,22 +1185,24 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-29 09:15</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr"/>
+          <t>2026-10-29 10:00</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>262</v>
+      </c>
       <c r="L14" s="4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -1557,22 +1567,24 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-29 09:15</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr"/>
+          <t>2026-10-29 09:15</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>320.3</v>
+      </c>
       <c r="L22" s="4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -1651,22 +1663,24 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-29 09:15</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="4" t="n">
-        <v>0</v>
+          <t>2026-10-29 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>296.15</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -1697,22 +1711,24 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-29 09:15</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr"/>
+          <t>2026-10-29 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>971.9</v>
+      </c>
       <c r="L25" s="4" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -1753,14 +1769,14 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 15:15 (Active)</t>
+          <t>2026-10-29 15:15 (Active)</t>
         </is>
       </c>
       <c r="K26" s="2" t="n">
-        <v>4557</v>
-      </c>
-      <c r="L26" s="3" t="n">
-        <v>-0.18</v>
+        <v>4580</v>
+      </c>
+      <c r="L26" s="4" t="n">
+        <v>0.33</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -1897,14 +1913,14 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 15:15 (Active)</t>
+          <t>2026-10-29 15:15 (Active)</t>
         </is>
       </c>
       <c r="K29" s="2" t="n">
-        <v>1175.5</v>
+        <v>1184.4</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>1.47</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -1935,22 +1951,24 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-29 14:30</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="4" t="n">
-        <v>0</v>
+          <t>2026-10-29 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>1154.1</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>-1.06</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2080,21 +2098,21 @@
           <t>2026-10-28 09:15</t>
         </is>
       </c>
-      <c r="I33" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 15:15 (Active)</t>
+          <t>2026-10-29 11:30</t>
         </is>
       </c>
       <c r="K33" s="2" t="n">
-        <v>360</v>
+        <v>369.3</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.19</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -2125,22 +2143,24 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-29 09:15</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr"/>
+          <t>2026-10-29 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>1020</v>
+      </c>
       <c r="L34" s="4" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -2171,22 +2191,24 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-29 09:15</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr"/>
+          <t>2026-10-29 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>1858.2</v>
+      </c>
       <c r="L35" s="4" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -2589,22 +2611,24 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-29 09:15</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr"/>
+          <t>2026-10-29 10:30</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>265.4</v>
+      </c>
       <c r="L44" s="4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -2635,22 +2659,24 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-29 09:15</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr"/>
+          <t>2026-10-29 09:15</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>2480.8</v>
+      </c>
       <c r="L45" s="4" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -2696,6 +2722,190 @@
       </c>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>390.65</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>388.7</v>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>396.7</v>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>2.02% (8.0)</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>404.7</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>412.7</v>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>RELIANCE</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>1163.1</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>1156.2</v>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>1168.6</v>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>1.06% (12.4)</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>1181</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>1193.4</v>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>827.09</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>810.2</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>832.5</v>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>2.68% (22.3)</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>854.8</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>877.1</v>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>340.3</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>333.5</v>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>348.4</v>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>4.28% (14.9)</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>363.3</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>378.2</v>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2710,7 +2920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M128"/>
+  <dimension ref="A1:M141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4585,49 +4795,49 @@
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>1629.9</v>
+        <v>22165</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1600.2</v>
+        <v>22025</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>1642.9</v>
+        <v>22195</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>2.6% (42.7)</t>
+          <t>0.77% (170.0)</t>
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>1685.6</v>
+        <v>22365</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>1728.3</v>
+        <v>22535</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 14:45</t>
         </is>
       </c>
-      <c r="I37" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:15 (Week End)</t>
+          <t>2026-09-29 15:00</t>
         </is>
       </c>
       <c r="K37" s="2" t="n">
-        <v>1627.3</v>
+        <v>22025</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>-0.95</v>
+        <v>-0.77</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
@@ -4638,49 +4848,49 @@
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>22165</v>
+        <v>1629.9</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>22025</v>
+        <v>1600.2</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>22195</v>
+        <v>1642.9</v>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>0.77% (170.0)</t>
+          <t>2.6% (42.7)</t>
         </is>
       </c>
       <c r="F38" s="4" t="n">
-        <v>22365</v>
+        <v>1685.6</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>22535</v>
+        <v>1728.3</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 14:45</t>
         </is>
       </c>
-      <c r="I38" s="7" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:00</t>
+          <t>2026-09-29 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K38" s="2" t="n">
-        <v>22025</v>
+        <v>1627.3</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>-0.77</v>
+        <v>-0.95</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
@@ -4744,49 +4954,49 @@
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>4848.5</v>
+        <v>160.5</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>4837</v>
+        <v>159.41</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>4872</v>
+        <v>162.37</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>0.72% (35.0)</t>
+          <t>1.82% (2.96)</t>
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>4907</v>
+        <v>165.33</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>4942</v>
+        <v>168.29</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I40" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 10:30</t>
+          <t>2026-09-30 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K40" s="2" t="n">
-        <v>4837</v>
-      </c>
-      <c r="L40" s="3" t="n">
-        <v>-0.72</v>
+        <v>163.26</v>
+      </c>
+      <c r="L40" s="4" t="n">
+        <v>0.55</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
@@ -4797,49 +5007,49 @@
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>1766.7</v>
+        <v>399.3</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>1736.8</v>
+        <v>394.7</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>1770.1</v>
+        <v>403.65</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>1.88% (33.3)</t>
+          <t>2.22% (8.95)</t>
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>1803.4</v>
+        <v>412.6</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>1836.7</v>
+        <v>421.55</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 15:15 (Week End)</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="K41" s="2" t="n">
-        <v>1798.3</v>
+        <v>421.55</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>1.59</v>
+        <v>4.43</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
@@ -4850,49 +5060,49 @@
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>2391</v>
+        <v>4057</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>2381.6</v>
+        <v>4043.3</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>2420</v>
+        <v>4095</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>1.59% (38.4)</t>
+          <t>1.26% (51.7)</t>
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>2458.4</v>
+        <v>4146.7</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>2496.8</v>
+        <v>4198.4</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I42" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:30 (Week End)</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="K42" s="2" t="n">
-        <v>2409.1</v>
+        <v>4043.3</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>-0.45</v>
+        <v>-1.26</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
@@ -4903,49 +5113,49 @@
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>263.55</v>
+        <v>991.6</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>263.3</v>
+        <v>980.4</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>266.2</v>
+        <v>992.7</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>1.09% (2.9)</t>
+          <t>1.24% (12.3)</t>
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>269.1</v>
+        <v>1005</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>272</v>
+        <v>1017.3</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I43" s="7" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:15</t>
+          <t>2026-09-30 09:45</t>
         </is>
       </c>
       <c r="K43" s="2" t="n">
-        <v>263.3</v>
-      </c>
-      <c r="L43" s="3" t="n">
-        <v>-1.09</v>
+        <v>1017.3</v>
+      </c>
+      <c r="L43" s="4" t="n">
+        <v>2.48</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
@@ -4956,49 +5166,49 @@
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>991.6</v>
+        <v>196.1</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>980.4</v>
+        <v>192.45</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>992.7</v>
+        <v>196.67</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>1.24% (12.3)</t>
+          <t>2.15% (4.22)</t>
         </is>
       </c>
       <c r="F44" s="4" t="n">
-        <v>1005</v>
+        <v>200.89</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>1017.3</v>
+        <v>205.11</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I44" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:45</t>
+          <t>2026-09-30 09:15</t>
         </is>
       </c>
       <c r="K44" s="2" t="n">
-        <v>1017.3</v>
+        <v>200.89</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>2.48</v>
+        <v>2.15</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
@@ -5009,49 +5219,49 @@
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>4057</v>
+        <v>2391</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>4043.3</v>
+        <v>2381.6</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>4095</v>
+        <v>2420</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>1.26% (51.7)</t>
+          <t>1.59% (38.4)</t>
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>4146.7</v>
+        <v>2458.4</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>4198.4</v>
+        <v>2496.8</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 09:15</t>
+          <t>2026-09-30 12:30 (Week End)</t>
         </is>
       </c>
       <c r="K45" s="2" t="n">
-        <v>4043.3</v>
+        <v>2409.1</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>-1.26</v>
+        <v>-0.45</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
@@ -5062,49 +5272,49 @@
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>399.3</v>
+        <v>1766.7</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>394.7</v>
+        <v>1736.8</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>403.65</v>
+        <v>1770.1</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>2.22% (8.95)</t>
+          <t>1.88% (33.3)</t>
         </is>
       </c>
       <c r="F46" s="4" t="n">
-        <v>412.6</v>
+        <v>1803.4</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>421.55</v>
+        <v>1836.7</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I46" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 09:15</t>
+          <t>2026-09-30 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K46" s="2" t="n">
-        <v>421.55</v>
+        <v>1798.3</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>4.43</v>
+        <v>1.59</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
@@ -5115,49 +5325,49 @@
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>196.1</v>
+        <v>4848.5</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>192.45</v>
+        <v>4837</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>196.67</v>
+        <v>4872</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>2.15% (4.22)</t>
+          <t>0.72% (35.0)</t>
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>200.89</v>
+        <v>4907</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>205.11</v>
+        <v>4942</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I47" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 09:15</t>
+          <t>2026-09-30 10:30</t>
         </is>
       </c>
       <c r="K47" s="2" t="n">
-        <v>200.89</v>
-      </c>
-      <c r="L47" s="4" t="n">
-        <v>2.15</v>
+        <v>4837</v>
+      </c>
+      <c r="L47" s="3" t="n">
+        <v>-0.72</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
@@ -5168,49 +5378,49 @@
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>160.5</v>
+        <v>263.55</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>159.41</v>
+        <v>263.3</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>162.37</v>
+        <v>266.2</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>1.82% (2.96)</t>
+          <t>1.09% (2.9)</t>
         </is>
       </c>
       <c r="F48" s="4" t="n">
-        <v>165.33</v>
+        <v>269.1</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>168.29</v>
+        <v>272</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>2026-09-30 09:15</t>
         </is>
       </c>
-      <c r="I48" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 15:15 (Week End)</t>
+          <t>2026-09-30 14:15</t>
         </is>
       </c>
       <c r="K48" s="2" t="n">
-        <v>163.26</v>
-      </c>
-      <c r="L48" s="4" t="n">
-        <v>0.55</v>
+        <v>263.3</v>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>-1.09</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
@@ -5346,49 +5556,49 @@
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>4737</v>
+        <v>1194.9</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>4734.1</v>
+        <v>1189.9</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>4770.2</v>
+        <v>1202.9</v>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>0.76% (36.1)</t>
+          <t>1.08% (13.0)</t>
         </is>
       </c>
       <c r="F52" s="4" t="n">
-        <v>4806.3</v>
+        <v>1215.9</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>4842.4</v>
+        <v>1228.9</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
           <t>2026-10-06 09:15</t>
         </is>
       </c>
-      <c r="I52" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 11:15</t>
+          <t>2026-10-06 15:00 (Week End)</t>
         </is>
       </c>
       <c r="K52" s="2" t="n">
-        <v>4842.4</v>
+        <v>1208</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>1.51</v>
+        <v>0.42</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
@@ -5399,49 +5609,49 @@
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>3930.1</v>
+        <v>4737</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>3920</v>
+        <v>4734.1</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>4031.6</v>
+        <v>4770.2</v>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>2.77% (111.6)</t>
+          <t>0.76% (36.1)</t>
         </is>
       </c>
       <c r="F53" s="4" t="n">
-        <v>4143.2</v>
+        <v>4806.3</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>4254.8</v>
+        <v>4842.4</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
           <t>2026-10-06 09:15</t>
         </is>
       </c>
-      <c r="I53" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 15:15 (Week End)</t>
+          <t>2026-10-06 11:15</t>
         </is>
       </c>
       <c r="K53" s="2" t="n">
-        <v>3981</v>
-      </c>
-      <c r="L53" s="3" t="n">
-        <v>-1.26</v>
+        <v>4842.4</v>
+      </c>
+      <c r="L53" s="4" t="n">
+        <v>1.51</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
@@ -5452,28 +5662,28 @@
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>378.65</v>
+        <v>3930.1</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>377.05</v>
+        <v>3920</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>384.35</v>
+        <v>4031.6</v>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>1.9% (7.3)</t>
+          <t>2.77% (111.6)</t>
         </is>
       </c>
       <c r="F54" s="4" t="n">
-        <v>391.65</v>
+        <v>4143.2</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>398.95</v>
+        <v>4254.8</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -5491,10 +5701,10 @@
         </is>
       </c>
       <c r="K54" s="2" t="n">
-        <v>387.4</v>
-      </c>
-      <c r="L54" s="4" t="n">
-        <v>0.79</v>
+        <v>3981</v>
+      </c>
+      <c r="L54" s="3" t="n">
+        <v>-1.26</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
@@ -5505,28 +5715,28 @@
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>1194.9</v>
+        <v>378.65</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>1189.9</v>
+        <v>377.05</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>1202.9</v>
+        <v>384.35</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>1.08% (13.0)</t>
+          <t>1.9% (7.3)</t>
         </is>
       </c>
       <c r="F55" s="4" t="n">
-        <v>1215.9</v>
+        <v>391.65</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>1228.9</v>
+        <v>398.95</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -5540,14 +5750,14 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 15:00 (Week End)</t>
+          <t>2026-10-06 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K55" s="2" t="n">
-        <v>1208</v>
+        <v>387.4</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>0.42</v>
+        <v>0.79</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
@@ -5558,49 +5768,49 @@
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>168.43</v>
+        <v>3709.5</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>166.48</v>
+        <v>3695</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>168.99</v>
+        <v>3723.8</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>1.49% (2.51)</t>
+          <t>0.77% (28.8)</t>
         </is>
       </c>
       <c r="F56" s="4" t="n">
-        <v>171.5</v>
+        <v>3752.6</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>174.01</v>
+        <v>3781.4</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
           <t>2026-10-07 09:15</t>
         </is>
       </c>
-      <c r="I56" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 15:15 (Week End)</t>
+          <t>2026-10-07 09:15</t>
         </is>
       </c>
       <c r="K56" s="2" t="n">
-        <v>170.71</v>
+        <v>3781.4</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
@@ -5611,49 +5821,49 @@
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>1295</v>
+        <v>168.43</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>1293</v>
+        <v>166.48</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>1299.4</v>
+        <v>168.99</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>0.49% (6.4)</t>
+          <t>1.49% (2.51)</t>
         </is>
       </c>
       <c r="F57" s="4" t="n">
-        <v>1305.8</v>
+        <v>171.5</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>1312.2</v>
+        <v>174.01</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
           <t>2026-10-07 09:15</t>
         </is>
       </c>
-      <c r="I57" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 09:15</t>
+          <t>2026-10-07 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K57" s="2" t="n">
-        <v>1312.2</v>
+        <v>170.71</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>0.99</v>
+        <v>1.02</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
@@ -5664,28 +5874,28 @@
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>3709.5</v>
+        <v>1295</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>3695</v>
+        <v>1293</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>3723.8</v>
+        <v>1299.4</v>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>0.77% (28.8)</t>
+          <t>0.49% (6.4)</t>
         </is>
       </c>
       <c r="F58" s="4" t="n">
-        <v>3752.6</v>
+        <v>1305.8</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>3781.4</v>
+        <v>1312.2</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -5703,10 +5913,10 @@
         </is>
       </c>
       <c r="K58" s="2" t="n">
-        <v>3781.4</v>
+        <v>1312.2</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>1.55</v>
+        <v>0.99</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
@@ -6266,28 +6476,28 @@
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>1160.2</v>
+        <v>1828</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>1152.6</v>
+        <v>1818.5</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>1166.7</v>
+        <v>1829.2</v>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>1.21% (14.1)</t>
+          <t>0.58% (10.7)</t>
         </is>
       </c>
       <c r="F70" s="4" t="n">
-        <v>1180.8</v>
+        <v>1839.9</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>1194.9</v>
+        <v>1850.6</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -6301,14 +6511,14 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 10:00</t>
+          <t>2026-10-14 09:15</t>
         </is>
       </c>
       <c r="K70" s="2" t="n">
-        <v>1194.9</v>
+        <v>1850.6</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>2.42</v>
+        <v>1.17</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
@@ -6319,49 +6529,49 @@
     <row r="71" ht="18" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>403.85</v>
+        <v>1486.2</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>402.15</v>
+        <v>1443.3</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>410.15</v>
+        <v>1508</v>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>1.95% (8.0)</t>
+          <t>4.29% (64.7)</t>
         </is>
       </c>
       <c r="F71" s="4" t="n">
-        <v>418.15</v>
+        <v>1572.7</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>426.15</v>
+        <v>1637.4</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I71" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 11:45</t>
+          <t>2026-10-15 13:15</t>
         </is>
       </c>
       <c r="K71" s="2" t="n">
-        <v>418.15</v>
+        <v>1637.4</v>
       </c>
       <c r="L71" s="4" t="n">
-        <v>1.95</v>
+        <v>8.58</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
@@ -6372,49 +6582,49 @@
     <row r="72" ht="18" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>373.3</v>
+        <v>857</v>
       </c>
       <c r="C72" s="3" t="n">
-        <v>373</v>
+        <v>846.1</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>375.4</v>
+        <v>861.85</v>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>0.64% (2.4)</t>
+          <t>1.83% (15.75)</t>
         </is>
       </c>
       <c r="F72" s="4" t="n">
-        <v>377.8</v>
+        <v>877.6</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>380.2</v>
+        <v>893.35</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I72" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 09:15</t>
+          <t>2026-10-14 09:30</t>
         </is>
       </c>
       <c r="K72" s="2" t="n">
-        <v>380.2</v>
+        <v>877.6</v>
       </c>
       <c r="L72" s="4" t="n">
-        <v>1.28</v>
+        <v>1.83</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
@@ -6425,49 +6635,49 @@
     <row r="73" ht="18" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>441.05</v>
+        <v>461</v>
       </c>
       <c r="C73" s="3" t="n">
-        <v>440.55</v>
+        <v>457.5</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>445.8</v>
+        <v>461.75</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>1.18% (5.25)</t>
+          <t>0.92% (4.25)</t>
         </is>
       </c>
       <c r="F73" s="4" t="n">
-        <v>451.05</v>
+        <v>466</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>456.3</v>
+        <v>470.25</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I73" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 11:00</t>
+          <t>2026-10-14 09:30</t>
         </is>
       </c>
       <c r="K73" s="2" t="n">
-        <v>451.05</v>
+        <v>470.25</v>
       </c>
       <c r="L73" s="4" t="n">
-        <v>1.18</v>
+        <v>1.84</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
@@ -6478,28 +6688,28 @@
     <row r="74" ht="18" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>461</v>
+        <v>373.3</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>457.5</v>
+        <v>373</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>461.75</v>
+        <v>375.4</v>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>0.92% (4.25)</t>
+          <t>0.64% (2.4)</t>
         </is>
       </c>
       <c r="F74" s="4" t="n">
-        <v>466</v>
+        <v>377.8</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>470.25</v>
+        <v>380.2</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -6513,14 +6723,14 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 09:30</t>
+          <t>2026-10-14 09:15</t>
         </is>
       </c>
       <c r="K74" s="2" t="n">
-        <v>470.25</v>
+        <v>380.2</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>1.84</v>
+        <v>1.28</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
@@ -6531,49 +6741,49 @@
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>1828</v>
+        <v>403.85</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>1818.5</v>
+        <v>402.15</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>1829.2</v>
+        <v>410.15</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>0.58% (10.7)</t>
+          <t>1.95% (8.0)</t>
         </is>
       </c>
       <c r="F75" s="4" t="n">
-        <v>1839.9</v>
+        <v>418.15</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>1850.6</v>
+        <v>426.15</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I75" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 09:15</t>
+          <t>2026-10-14 11:45</t>
         </is>
       </c>
       <c r="K75" s="2" t="n">
-        <v>1850.6</v>
+        <v>418.15</v>
       </c>
       <c r="L75" s="4" t="n">
-        <v>1.17</v>
+        <v>1.95</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
@@ -6584,49 +6794,49 @@
     <row r="76" ht="18" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>857</v>
+        <v>1160.2</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>846.1</v>
+        <v>1152.6</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>861.85</v>
+        <v>1166.7</v>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>1.83% (15.75)</t>
+          <t>1.21% (14.1)</t>
         </is>
       </c>
       <c r="F76" s="4" t="n">
-        <v>877.6</v>
+        <v>1180.8</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>893.35</v>
+        <v>1194.9</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I76" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 09:30</t>
+          <t>2026-10-15 10:00</t>
         </is>
       </c>
       <c r="K76" s="2" t="n">
-        <v>877.6</v>
+        <v>1194.9</v>
       </c>
       <c r="L76" s="4" t="n">
-        <v>1.83</v>
+        <v>2.42</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
@@ -6637,49 +6847,49 @@
     <row r="77" ht="18" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>1486.2</v>
+        <v>441.05</v>
       </c>
       <c r="C77" s="3" t="n">
-        <v>1443.3</v>
+        <v>440.55</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>1508</v>
+        <v>445.8</v>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>4.29% (64.7)</t>
+          <t>1.18% (5.25)</t>
         </is>
       </c>
       <c r="F77" s="4" t="n">
-        <v>1572.7</v>
+        <v>451.05</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>1637.4</v>
+        <v>456.3</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I77" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 13:15</t>
+          <t>2026-10-14 11:00</t>
         </is>
       </c>
       <c r="K77" s="2" t="n">
-        <v>1637.4</v>
+        <v>451.05</v>
       </c>
       <c r="L77" s="4" t="n">
-        <v>8.58</v>
+        <v>1.18</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
@@ -6955,49 +7165,49 @@
     <row r="83" ht="18" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>2559.6</v>
+        <v>166.3</v>
       </c>
       <c r="C83" s="3" t="n">
-        <v>2550</v>
+        <v>165.87</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>2593</v>
+        <v>166.83</v>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>1.66% (43.0)</t>
+          <t>0.58% (0.96)</t>
         </is>
       </c>
       <c r="F83" s="4" t="n">
-        <v>2636</v>
+        <v>167.79</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>2679</v>
+        <v>168.75</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
           <t>2026-10-16 09:15</t>
         </is>
       </c>
-      <c r="I83" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I83" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 15:15 (Week End)</t>
+          <t>2026-10-16 09:15</t>
         </is>
       </c>
       <c r="K83" s="2" t="n">
-        <v>2598.3</v>
+        <v>168.75</v>
       </c>
       <c r="L83" s="4" t="n">
-        <v>0.2</v>
+        <v>1.15</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
@@ -7008,49 +7218,49 @@
     <row r="84" ht="18" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>166.3</v>
+        <v>2559.6</v>
       </c>
       <c r="C84" s="3" t="n">
-        <v>165.87</v>
+        <v>2550</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>166.83</v>
+        <v>2593</v>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>0.58% (0.96)</t>
+          <t>1.66% (43.0)</t>
         </is>
       </c>
       <c r="F84" s="4" t="n">
-        <v>167.79</v>
+        <v>2636</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>168.75</v>
+        <v>2679</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
           <t>2026-10-16 09:15</t>
         </is>
       </c>
-      <c r="I84" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 09:15</t>
+          <t>2026-10-16 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K84" s="2" t="n">
-        <v>168.75</v>
+        <v>2598.3</v>
       </c>
       <c r="L84" s="4" t="n">
-        <v>1.15</v>
+        <v>0.2</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
@@ -7239,28 +7449,28 @@
     <row r="89" ht="18" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>7688</v>
+        <v>4591.2</v>
       </c>
       <c r="C89" s="3" t="n">
-        <v>7677</v>
+        <v>4587</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>7729</v>
+        <v>4610</v>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>0.67% (52.0)</t>
+          <t>0.5% (23.0)</t>
         </is>
       </c>
       <c r="F89" s="4" t="n">
-        <v>7781</v>
+        <v>4633</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>7833</v>
+        <v>4656</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -7274,14 +7484,14 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 10:15</t>
+          <t>2026-10-21 09:15</t>
         </is>
       </c>
       <c r="K89" s="2" t="n">
-        <v>7677</v>
+        <v>4587</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>-0.67</v>
+        <v>-0.5</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
@@ -7292,28 +7502,28 @@
     <row r="90" ht="18" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>4591.2</v>
+        <v>7688</v>
       </c>
       <c r="C90" s="3" t="n">
-        <v>4587</v>
+        <v>7677</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>4610</v>
+        <v>7729</v>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>0.5% (23.0)</t>
+          <t>0.67% (52.0)</t>
         </is>
       </c>
       <c r="F90" s="4" t="n">
-        <v>4633</v>
+        <v>7781</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>4656</v>
+        <v>7833</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -7327,14 +7537,14 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 09:15</t>
+          <t>2026-10-21 10:15</t>
         </is>
       </c>
       <c r="K90" s="2" t="n">
-        <v>4587</v>
+        <v>7677</v>
       </c>
       <c r="L90" s="3" t="n">
-        <v>-0.5</v>
+        <v>-0.67</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
@@ -7398,49 +7608,49 @@
     <row r="92" ht="18" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>165.87</v>
+        <v>1725.5</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>164.88</v>
+        <v>1719.6</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>165.92</v>
+        <v>1745.1</v>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>0.63% (1.04)</t>
+          <t>1.46% (25.5)</t>
         </is>
       </c>
       <c r="F92" s="4" t="n">
-        <v>166.96</v>
+        <v>1770.6</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>168</v>
+        <v>1796.1</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
           <t>2026-10-23 09:15</t>
         </is>
       </c>
-      <c r="I92" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
+      <c r="I92" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:30</t>
+          <t>2026-10-23 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K92" s="2" t="n">
-        <v>164.88</v>
-      </c>
-      <c r="L92" s="3" t="n">
-        <v>-0.63</v>
+        <v>1748</v>
+      </c>
+      <c r="L92" s="4" t="n">
+        <v>0.17</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
@@ -7451,28 +7661,28 @@
     <row r="93" ht="18" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>4550.4</v>
+        <v>1300.2</v>
       </c>
       <c r="C93" s="3" t="n">
-        <v>4474.6</v>
+        <v>1296.7</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>4572.1</v>
+        <v>1314</v>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>2.13% (97.5)</t>
+          <t>1.32% (17.3)</t>
         </is>
       </c>
       <c r="F93" s="4" t="n">
-        <v>4669.6</v>
+        <v>1331.3</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>4767.1</v>
+        <v>1348.6</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -7486,14 +7696,14 @@
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 15:15 (Week End)</t>
+          <t>2026-10-23 09:15</t>
         </is>
       </c>
       <c r="K93" s="2" t="n">
-        <v>4524.4</v>
-      </c>
-      <c r="L93" s="3" t="n">
-        <v>-1.04</v>
+        <v>1331.3</v>
+      </c>
+      <c r="L93" s="4" t="n">
+        <v>1.32</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
@@ -7504,49 +7714,49 @@
     <row r="94" ht="18" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>437.2</v>
+        <v>1003.5</v>
       </c>
       <c r="C94" s="3" t="n">
-        <v>433.75</v>
+        <v>1001.4</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>438.2</v>
+        <v>1028</v>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>1.02% (4.45)</t>
+          <t>2.59% (26.6)</t>
         </is>
       </c>
       <c r="F94" s="4" t="n">
-        <v>442.65</v>
+        <v>1054.6</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>447.1</v>
+        <v>1081.2</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
           <t>2026-10-23 09:15</t>
         </is>
       </c>
-      <c r="I94" s="7" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 10:00</t>
+          <t>2026-10-23 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K94" s="2" t="n">
-        <v>433.75</v>
+        <v>1015.9</v>
       </c>
       <c r="L94" s="3" t="n">
-        <v>-1.02</v>
+        <v>-1.18</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
@@ -7557,28 +7767,28 @@
     <row r="95" ht="18" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>2843.4</v>
+        <v>1107.3</v>
       </c>
       <c r="C95" s="3" t="n">
-        <v>2828.2</v>
+        <v>1100.3</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>2889.1</v>
+        <v>1117.3</v>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>2.11% (60.9)</t>
+          <t>1.52% (17.0)</t>
         </is>
       </c>
       <c r="F95" s="4" t="n">
-        <v>2950</v>
+        <v>1134.3</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>3010.9</v>
+        <v>1151.3</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
@@ -7592,14 +7802,14 @@
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 15:15 (Week End)</t>
+          <t>2026-10-23 09:15</t>
         </is>
       </c>
       <c r="K95" s="2" t="n">
-        <v>2894</v>
+        <v>1134.3</v>
       </c>
       <c r="L95" s="4" t="n">
-        <v>0.17</v>
+        <v>1.52</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
@@ -7610,49 +7820,49 @@
     <row r="96" ht="18" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>1107.3</v>
+        <v>437.2</v>
       </c>
       <c r="C96" s="3" t="n">
-        <v>1100.3</v>
+        <v>433.75</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>1117.3</v>
+        <v>438.2</v>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>1.52% (17.0)</t>
+          <t>1.02% (4.45)</t>
         </is>
       </c>
       <c r="F96" s="4" t="n">
-        <v>1134.3</v>
+        <v>442.65</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>1151.3</v>
+        <v>447.1</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
           <t>2026-10-23 09:15</t>
         </is>
       </c>
-      <c r="I96" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I96" s="7" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:15</t>
+          <t>2026-10-23 10:00</t>
         </is>
       </c>
       <c r="K96" s="2" t="n">
-        <v>1134.3</v>
-      </c>
-      <c r="L96" s="4" t="n">
-        <v>1.52</v>
+        <v>433.75</v>
+      </c>
+      <c r="L96" s="3" t="n">
+        <v>-1.02</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
@@ -7663,28 +7873,28 @@
     <row r="97" ht="18" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>1725.5</v>
+        <v>4550.4</v>
       </c>
       <c r="C97" s="3" t="n">
-        <v>1719.6</v>
+        <v>4474.6</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>1745.1</v>
+        <v>4572.1</v>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>1.46% (25.5)</t>
+          <t>2.13% (97.5)</t>
         </is>
       </c>
       <c r="F97" s="4" t="n">
-        <v>1770.6</v>
+        <v>4669.6</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>1796.1</v>
+        <v>4767.1</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -7702,10 +7912,10 @@
         </is>
       </c>
       <c r="K97" s="2" t="n">
-        <v>1748</v>
-      </c>
-      <c r="L97" s="4" t="n">
-        <v>0.17</v>
+        <v>4524.4</v>
+      </c>
+      <c r="L97" s="3" t="n">
+        <v>-1.04</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
@@ -7716,49 +7926,49 @@
     <row r="98" ht="18" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>1003.5</v>
+        <v>165.87</v>
       </c>
       <c r="C98" s="3" t="n">
-        <v>1001.4</v>
+        <v>164.88</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>1028</v>
+        <v>165.92</v>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>2.59% (26.6)</t>
+          <t>0.63% (1.04)</t>
         </is>
       </c>
       <c r="F98" s="4" t="n">
-        <v>1054.6</v>
+        <v>166.96</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>1081.2</v>
+        <v>168</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
           <t>2026-10-23 09:15</t>
         </is>
       </c>
-      <c r="I98" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I98" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 15:15 (Week End)</t>
+          <t>2026-10-23 09:30</t>
         </is>
       </c>
       <c r="K98" s="2" t="n">
-        <v>1015.9</v>
+        <v>164.88</v>
       </c>
       <c r="L98" s="3" t="n">
-        <v>-1.18</v>
+        <v>-0.63</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
@@ -7769,28 +7979,28 @@
     <row r="99" ht="18" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>1300.2</v>
+        <v>2843.4</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>1296.7</v>
+        <v>2828.2</v>
       </c>
       <c r="D99" s="4" t="n">
-        <v>1314</v>
+        <v>2889.1</v>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>1.32% (17.3)</t>
+          <t>2.11% (60.9)</t>
         </is>
       </c>
       <c r="F99" s="4" t="n">
-        <v>1331.3</v>
+        <v>2950</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>1348.6</v>
+        <v>3010.9</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -7804,14 +8014,14 @@
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:15</t>
+          <t>2026-10-23 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K99" s="2" t="n">
-        <v>1331.3</v>
+        <v>2894</v>
       </c>
       <c r="L99" s="4" t="n">
-        <v>1.32</v>
+        <v>0.17</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
@@ -7841,28 +8051,28 @@
     <row r="101" ht="18" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>1450</v>
+        <v>440.15</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>1415</v>
+        <v>440.15</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>1452.6</v>
+        <v>446.35</v>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>2.59% (37.6)</t>
+          <t>1.39% (6.2)</t>
         </is>
       </c>
       <c r="F101" s="4" t="n">
-        <v>1490.2</v>
+        <v>452.55</v>
       </c>
       <c r="G101" s="4" t="n">
-        <v>1527.8</v>
+        <v>458.75</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -7876,14 +8086,14 @@
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 13:30</t>
+          <t>2026-10-27 09:15</t>
         </is>
       </c>
       <c r="K101" s="2" t="n">
-        <v>1527.8</v>
+        <v>458.75</v>
       </c>
       <c r="L101" s="4" t="n">
-        <v>5.18</v>
+        <v>2.78</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
@@ -7894,49 +8104,49 @@
     <row r="102" ht="18" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>LODHA</t>
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>1100.3</v>
+        <v>941</v>
       </c>
       <c r="C102" s="3" t="n">
-        <v>1094</v>
+        <v>939.8</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>1158.5</v>
+        <v>948.2</v>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>5.57% (64.5)</t>
+          <t>0.89% (8.4)</t>
         </is>
       </c>
       <c r="F102" s="4" t="n">
-        <v>1223</v>
+        <v>956.6</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>1287.5</v>
+        <v>965</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
           <t>2026-10-27 09:15</t>
         </is>
       </c>
-      <c r="I102" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I102" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 15:15 (Active)</t>
+          <t>2026-10-27 09:15</t>
         </is>
       </c>
       <c r="K102" s="2" t="n">
-        <v>1175.5</v>
+        <v>965</v>
       </c>
       <c r="L102" s="4" t="n">
-        <v>1.47</v>
+        <v>1.77</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
@@ -7947,28 +8157,28 @@
     <row r="103" ht="18" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>223.35</v>
+        <v>148.07</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>221.8</v>
+        <v>147.32</v>
       </c>
       <c r="D103" s="4" t="n">
-        <v>225</v>
+        <v>148.9</v>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>1.42% (3.2)</t>
+          <t>1.06% (1.58)</t>
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>228.2</v>
+        <v>150.48</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>231.4</v>
+        <v>152.06</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -7982,14 +8192,14 @@
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 12:30</t>
+          <t>2026-10-27 09:15</t>
         </is>
       </c>
       <c r="K103" s="2" t="n">
-        <v>231.4</v>
+        <v>152.06</v>
       </c>
       <c r="L103" s="4" t="n">
-        <v>2.84</v>
+        <v>2.12</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
@@ -8000,28 +8210,28 @@
     <row r="104" ht="18" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>3898.1</v>
+        <v>1845</v>
       </c>
       <c r="C104" s="3" t="n">
-        <v>3875.1</v>
+        <v>1838.7</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>3961.9</v>
+        <v>1860.9</v>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>2.19% (86.8)</t>
+          <t>1.19% (22.2)</t>
         </is>
       </c>
       <c r="F104" s="4" t="n">
-        <v>4048.7</v>
+        <v>1883.1</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>4135.5</v>
+        <v>1905.3</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -8035,14 +8245,14 @@
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 11:30</t>
+          <t>2026-10-27 09:15</t>
         </is>
       </c>
       <c r="K104" s="2" t="n">
-        <v>4135.5</v>
+        <v>1905.3</v>
       </c>
       <c r="L104" s="4" t="n">
-        <v>4.38</v>
+        <v>2.39</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
@@ -8053,49 +8263,49 @@
     <row r="105" ht="18" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="B105" s="2" t="n">
-        <v>4470.4</v>
+        <v>69.03</v>
       </c>
       <c r="C105" s="3" t="n">
-        <v>4467.3</v>
+        <v>68.84</v>
       </c>
       <c r="D105" s="4" t="n">
-        <v>4565</v>
+        <v>69.33</v>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>2.14% (97.7)</t>
+          <t>0.71% (0.49)</t>
         </is>
       </c>
       <c r="F105" s="4" t="n">
-        <v>4662.7</v>
+        <v>69.81999999999999</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>4760.4</v>
+        <v>70.31</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
           <t>2026-10-27 09:15</t>
         </is>
       </c>
-      <c r="I105" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I105" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 15:15 (Active)</t>
+          <t>2026-10-27 09:15</t>
         </is>
       </c>
       <c r="K105" s="2" t="n">
-        <v>4557</v>
-      </c>
-      <c r="L105" s="3" t="n">
-        <v>-0.18</v>
+        <v>70.31</v>
+      </c>
+      <c r="L105" s="4" t="n">
+        <v>1.41</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
@@ -8106,28 +8316,28 @@
     <row r="106" ht="18" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="B106" s="2" t="n">
-        <v>119.06</v>
+        <v>1177.6</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>118.25</v>
+        <v>1169.8</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>119.24</v>
+        <v>1188.2</v>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>0.83% (0.99)</t>
+          <t>1.55% (18.4)</t>
         </is>
       </c>
       <c r="F106" s="4" t="n">
-        <v>120.23</v>
+        <v>1206.6</v>
       </c>
       <c r="G106" s="4" t="n">
-        <v>121.22</v>
+        <v>1225</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -8136,19 +8346,19 @@
       </c>
       <c r="I106" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:15</t>
+          <t>2026-10-27 10:00</t>
         </is>
       </c>
       <c r="K106" s="2" t="n">
-        <v>121.22</v>
+        <v>1206.6</v>
       </c>
       <c r="L106" s="4" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
@@ -8159,28 +8369,28 @@
     <row r="107" ht="18" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="B107" s="2" t="n">
-        <v>444.9</v>
+        <v>119.06</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>441.7</v>
+        <v>118.25</v>
       </c>
       <c r="D107" s="4" t="n">
-        <v>447.5</v>
+        <v>119.24</v>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>1.3% (5.8)</t>
+          <t>0.83% (0.99)</t>
         </is>
       </c>
       <c r="F107" s="4" t="n">
-        <v>453.3</v>
+        <v>120.23</v>
       </c>
       <c r="G107" s="4" t="n">
-        <v>459.1</v>
+        <v>121.22</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -8189,7 +8399,7 @@
       </c>
       <c r="I107" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
@@ -8198,10 +8408,10 @@
         </is>
       </c>
       <c r="K107" s="2" t="n">
-        <v>453.3</v>
+        <v>121.22</v>
       </c>
       <c r="L107" s="4" t="n">
-        <v>1.3</v>
+        <v>1.66</v>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
@@ -8212,28 +8422,28 @@
     <row r="108" ht="18" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B108" s="2" t="n">
-        <v>69.03</v>
+        <v>1450</v>
       </c>
       <c r="C108" s="3" t="n">
-        <v>68.84</v>
+        <v>1415</v>
       </c>
       <c r="D108" s="4" t="n">
-        <v>69.33</v>
+        <v>1452.6</v>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>0.71% (0.49)</t>
+          <t>2.59% (37.6)</t>
         </is>
       </c>
       <c r="F108" s="4" t="n">
-        <v>69.81999999999999</v>
+        <v>1490.2</v>
       </c>
       <c r="G108" s="4" t="n">
-        <v>70.31</v>
+        <v>1527.8</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -8247,14 +8457,14 @@
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:15</t>
+          <t>2026-10-28 13:30</t>
         </is>
       </c>
       <c r="K108" s="2" t="n">
-        <v>70.31</v>
+        <v>1527.8</v>
       </c>
       <c r="L108" s="4" t="n">
-        <v>1.41</v>
+        <v>5.18</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
@@ -8265,49 +8475,49 @@
     <row r="109" ht="18" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B109" s="2" t="n">
-        <v>148.07</v>
+        <v>4470.4</v>
       </c>
       <c r="C109" s="3" t="n">
-        <v>147.32</v>
+        <v>4467.3</v>
       </c>
       <c r="D109" s="4" t="n">
-        <v>148.9</v>
+        <v>4565</v>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>1.06% (1.58)</t>
+          <t>2.14% (97.7)</t>
         </is>
       </c>
       <c r="F109" s="4" t="n">
-        <v>150.48</v>
+        <v>4662.7</v>
       </c>
       <c r="G109" s="4" t="n">
-        <v>152.06</v>
+        <v>4760.4</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
           <t>2026-10-27 09:15</t>
         </is>
       </c>
-      <c r="I109" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I109" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:15</t>
+          <t>2026-10-29 15:15 (Active)</t>
         </is>
       </c>
       <c r="K109" s="2" t="n">
-        <v>152.06</v>
+        <v>4580</v>
       </c>
       <c r="L109" s="4" t="n">
-        <v>2.12</v>
+        <v>0.33</v>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
@@ -8318,28 +8528,28 @@
     <row r="110" ht="18" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B110" s="2" t="n">
-        <v>1845</v>
+        <v>3898.1</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>1838.7</v>
+        <v>3875.1</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>1860.9</v>
+        <v>3961.9</v>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>1.19% (22.2)</t>
+          <t>2.19% (86.8)</t>
         </is>
       </c>
       <c r="F110" s="4" t="n">
-        <v>1883.1</v>
+        <v>4048.7</v>
       </c>
       <c r="G110" s="4" t="n">
-        <v>1905.3</v>
+        <v>4135.5</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -8353,14 +8563,14 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:15</t>
+          <t>2026-10-28 11:30</t>
         </is>
       </c>
       <c r="K110" s="2" t="n">
-        <v>1905.3</v>
+        <v>4135.5</v>
       </c>
       <c r="L110" s="4" t="n">
-        <v>2.39</v>
+        <v>4.38</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
@@ -8371,28 +8581,28 @@
     <row r="111" ht="18" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>LODHA</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="B111" s="2" t="n">
-        <v>941</v>
+        <v>852</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>939.8</v>
+        <v>851.35</v>
       </c>
       <c r="D111" s="4" t="n">
-        <v>948.2</v>
+        <v>864</v>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>0.89% (8.4)</t>
+          <t>1.46% (12.65)</t>
         </is>
       </c>
       <c r="F111" s="4" t="n">
-        <v>956.6</v>
+        <v>876.65</v>
       </c>
       <c r="G111" s="4" t="n">
-        <v>965</v>
+        <v>889.3</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -8410,10 +8620,10 @@
         </is>
       </c>
       <c r="K111" s="2" t="n">
-        <v>965</v>
+        <v>889.3</v>
       </c>
       <c r="L111" s="4" t="n">
-        <v>1.77</v>
+        <v>2.93</v>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
@@ -8424,28 +8634,28 @@
     <row r="112" ht="18" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="B112" s="2" t="n">
-        <v>440.15</v>
+        <v>444.9</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>440.15</v>
+        <v>441.7</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>446.35</v>
+        <v>447.5</v>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>1.39% (6.2)</t>
+          <t>1.3% (5.8)</t>
         </is>
       </c>
       <c r="F112" s="4" t="n">
-        <v>452.55</v>
+        <v>453.3</v>
       </c>
       <c r="G112" s="4" t="n">
-        <v>458.75</v>
+        <v>459.1</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -8454,7 +8664,7 @@
       </c>
       <c r="I112" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
@@ -8463,10 +8673,10 @@
         </is>
       </c>
       <c r="K112" s="2" t="n">
-        <v>458.75</v>
+        <v>453.3</v>
       </c>
       <c r="L112" s="4" t="n">
-        <v>2.78</v>
+        <v>1.3</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
@@ -8477,28 +8687,28 @@
     <row r="113" ht="18" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="B113" s="2" t="n">
-        <v>852</v>
+        <v>4994.5</v>
       </c>
       <c r="C113" s="3" t="n">
-        <v>851.35</v>
+        <v>4977.5</v>
       </c>
       <c r="D113" s="4" t="n">
-        <v>864</v>
+        <v>5054.5</v>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>1.46% (12.65)</t>
+          <t>1.52% (77.0)</t>
         </is>
       </c>
       <c r="F113" s="4" t="n">
-        <v>876.65</v>
+        <v>5131.5</v>
       </c>
       <c r="G113" s="4" t="n">
-        <v>889.3</v>
+        <v>5208.5</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -8516,10 +8726,10 @@
         </is>
       </c>
       <c r="K113" s="2" t="n">
-        <v>889.3</v>
+        <v>5208.5</v>
       </c>
       <c r="L113" s="4" t="n">
-        <v>2.93</v>
+        <v>3.05</v>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
@@ -8530,49 +8740,49 @@
     <row r="114" ht="18" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="B114" s="2" t="n">
-        <v>4716.3</v>
+        <v>1100.3</v>
       </c>
       <c r="C114" s="3" t="n">
-        <v>4642.1</v>
+        <v>1094</v>
       </c>
       <c r="D114" s="4" t="n">
-        <v>4733</v>
+        <v>1158.5</v>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>1.92% (90.9)</t>
+          <t>5.57% (64.5)</t>
         </is>
       </c>
       <c r="F114" s="4" t="n">
-        <v>4823.9</v>
+        <v>1223</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>4914.8</v>
+        <v>1287.5</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
           <t>2026-10-27 09:15</t>
         </is>
       </c>
-      <c r="I114" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I114" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:30</t>
+          <t>2026-10-29 15:15 (Active)</t>
         </is>
       </c>
       <c r="K114" s="2" t="n">
-        <v>4914.8</v>
+        <v>1184.4</v>
       </c>
       <c r="L114" s="4" t="n">
-        <v>3.84</v>
+        <v>2.24</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
@@ -8636,49 +8846,49 @@
     <row r="116" ht="18" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B116" s="2" t="n">
-        <v>229.2</v>
+        <v>2260</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>227.3</v>
+        <v>2234.3</v>
       </c>
       <c r="D116" s="4" t="n">
-        <v>229.7</v>
+        <v>2283.3</v>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>1.04% (2.4)</t>
+          <t>2.15% (49.0)</t>
         </is>
       </c>
       <c r="F116" s="4" t="n">
-        <v>232.1</v>
+        <v>2332.3</v>
       </c>
       <c r="G116" s="4" t="n">
-        <v>234.5</v>
+        <v>2381.3</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
           <t>2026-10-27 09:15</t>
         </is>
       </c>
-      <c r="I116" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+      <c r="I116" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:15</t>
+          <t>2026-10-27 15:15 (Active)</t>
         </is>
       </c>
       <c r="K116" s="2" t="n">
-        <v>232.1</v>
-      </c>
-      <c r="L116" s="4" t="n">
-        <v>1.04</v>
+        <v>2277</v>
+      </c>
+      <c r="L116" s="3" t="n">
+        <v>-0.28</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
@@ -8689,28 +8899,28 @@
     <row r="117" ht="18" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B117" s="2" t="n">
-        <v>6070</v>
+        <v>4515</v>
       </c>
       <c r="C117" s="3" t="n">
-        <v>6065</v>
+        <v>4507.9</v>
       </c>
       <c r="D117" s="4" t="n">
-        <v>6152</v>
+        <v>4540.1</v>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>1.41% (87.0)</t>
+          <t>0.71% (32.2)</t>
         </is>
       </c>
       <c r="F117" s="4" t="n">
-        <v>6239</v>
+        <v>4572.3</v>
       </c>
       <c r="G117" s="4" t="n">
-        <v>6326</v>
+        <v>4604.5</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
@@ -8719,7 +8929,7 @@
       </c>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
@@ -8728,10 +8938,10 @@
         </is>
       </c>
       <c r="K117" s="2" t="n">
-        <v>6326</v>
+        <v>4572.3</v>
       </c>
       <c r="L117" s="4" t="n">
-        <v>2.83</v>
+        <v>0.71</v>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
@@ -8742,49 +8952,49 @@
     <row r="118" ht="18" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B118" s="2" t="n">
-        <v>2260</v>
+        <v>254.8</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>2234.3</v>
+        <v>254.5</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>2283.3</v>
+        <v>256.25</v>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>2.15% (49.0)</t>
+          <t>0.68% (1.75)</t>
         </is>
       </c>
       <c r="F118" s="4" t="n">
-        <v>2332.3</v>
+        <v>258</v>
       </c>
       <c r="G118" s="4" t="n">
-        <v>2381.3</v>
+        <v>259.75</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
           <t>2026-10-27 09:15</t>
         </is>
       </c>
-      <c r="I118" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I118" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 15:15 (Active)</t>
+          <t>2026-10-27 09:15</t>
         </is>
       </c>
       <c r="K118" s="2" t="n">
-        <v>2277</v>
-      </c>
-      <c r="L118" s="3" t="n">
-        <v>-0.28</v>
+        <v>259.75</v>
+      </c>
+      <c r="L118" s="4" t="n">
+        <v>1.37</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
@@ -8795,28 +9005,28 @@
     <row r="119" ht="18" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="B119" s="2" t="n">
-        <v>4515</v>
+        <v>223.35</v>
       </c>
       <c r="C119" s="3" t="n">
-        <v>4507.9</v>
+        <v>221.8</v>
       </c>
       <c r="D119" s="4" t="n">
-        <v>4540.1</v>
+        <v>225</v>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>0.71% (32.2)</t>
+          <t>1.42% (3.2)</t>
         </is>
       </c>
       <c r="F119" s="4" t="n">
-        <v>4572.3</v>
+        <v>228.2</v>
       </c>
       <c r="G119" s="4" t="n">
-        <v>4604.5</v>
+        <v>231.4</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -8825,19 +9035,19 @@
       </c>
       <c r="I119" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:15</t>
+          <t>2026-10-28 12:30</t>
         </is>
       </c>
       <c r="K119" s="2" t="n">
-        <v>4572.3</v>
+        <v>231.4</v>
       </c>
       <c r="L119" s="4" t="n">
-        <v>0.71</v>
+        <v>2.84</v>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
@@ -8848,28 +9058,28 @@
     <row r="120" ht="18" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="B120" s="2" t="n">
-        <v>254.8</v>
+        <v>4716.3</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>254.5</v>
+        <v>4642.1</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>256.25</v>
+        <v>4733</v>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>0.68% (1.75)</t>
+          <t>1.92% (90.9)</t>
         </is>
       </c>
       <c r="F120" s="4" t="n">
-        <v>258</v>
+        <v>4823.9</v>
       </c>
       <c r="G120" s="4" t="n">
-        <v>259.75</v>
+        <v>4914.8</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -8883,14 +9093,14 @@
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:15</t>
+          <t>2026-10-27 09:30</t>
         </is>
       </c>
       <c r="K120" s="2" t="n">
-        <v>259.75</v>
+        <v>4914.8</v>
       </c>
       <c r="L120" s="4" t="n">
-        <v>1.37</v>
+        <v>3.84</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
@@ -8901,49 +9111,49 @@
     <row r="121" ht="18" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="B121" s="2" t="n">
-        <v>1177.6</v>
+        <v>290.65</v>
       </c>
       <c r="C121" s="3" t="n">
-        <v>1169.8</v>
+        <v>289.5</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>1188.2</v>
+        <v>291.8</v>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>1.55% (18.4)</t>
+          <t>0.79% (2.3)</t>
         </is>
       </c>
       <c r="F121" s="4" t="n">
-        <v>1206.6</v>
+        <v>294.1</v>
       </c>
       <c r="G121" s="4" t="n">
-        <v>1225</v>
+        <v>296.4</v>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
           <t>2026-10-27 09:15</t>
         </is>
       </c>
-      <c r="I121" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+      <c r="I121" s="7" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 10:00</t>
+          <t>2026-10-27 09:15</t>
         </is>
       </c>
       <c r="K121" s="2" t="n">
-        <v>1206.6</v>
-      </c>
-      <c r="L121" s="4" t="n">
-        <v>1.55</v>
+        <v>289.5</v>
+      </c>
+      <c r="L121" s="3" t="n">
+        <v>-0.79</v>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
@@ -8954,49 +9164,49 @@
     <row r="122" ht="18" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
       <c r="B122" s="2" t="n">
-        <v>290.65</v>
+        <v>229.2</v>
       </c>
       <c r="C122" s="3" t="n">
-        <v>289.5</v>
+        <v>227.3</v>
       </c>
       <c r="D122" s="4" t="n">
-        <v>291.8</v>
+        <v>229.7</v>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>0.79% (2.3)</t>
+          <t>1.04% (2.4)</t>
         </is>
       </c>
       <c r="F122" s="4" t="n">
-        <v>294.1</v>
+        <v>232.1</v>
       </c>
       <c r="G122" s="4" t="n">
-        <v>296.4</v>
+        <v>234.5</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
           <t>2026-10-27 09:15</t>
         </is>
       </c>
-      <c r="I122" s="7" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I122" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:15</t>
+          <t>2026-10-29 09:15</t>
         </is>
       </c>
       <c r="K122" s="2" t="n">
-        <v>289.5</v>
-      </c>
-      <c r="L122" s="3" t="n">
-        <v>-0.79</v>
+        <v>234.5</v>
+      </c>
+      <c r="L122" s="4" t="n">
+        <v>2.09</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
@@ -9007,28 +9217,28 @@
     <row r="123" ht="18" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="B123" s="2" t="n">
-        <v>4994.5</v>
+        <v>6070</v>
       </c>
       <c r="C123" s="3" t="n">
-        <v>4977.5</v>
+        <v>6065</v>
       </c>
       <c r="D123" s="4" t="n">
-        <v>5054.5</v>
+        <v>6152</v>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>1.52% (77.0)</t>
+          <t>1.41% (87.0)</t>
         </is>
       </c>
       <c r="F123" s="4" t="n">
-        <v>5131.5</v>
+        <v>6239</v>
       </c>
       <c r="G123" s="4" t="n">
-        <v>5208.5</v>
+        <v>6326</v>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
@@ -9046,10 +9256,10 @@
         </is>
       </c>
       <c r="K123" s="2" t="n">
-        <v>5208.5</v>
+        <v>6326</v>
       </c>
       <c r="L123" s="4" t="n">
-        <v>3.05</v>
+        <v>2.83</v>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
@@ -9113,49 +9323,49 @@
     <row r="125" ht="18" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
       <c r="B125" s="2" t="n">
-        <v>10834</v>
+        <v>1240</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>10735</v>
+        <v>1227</v>
       </c>
       <c r="D125" s="4" t="n">
-        <v>10856</v>
+        <v>1241.5</v>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>1.11% (121.0)</t>
+          <t>1.17% (14.5)</t>
         </is>
       </c>
       <c r="F125" s="4" t="n">
-        <v>10977</v>
+        <v>1256</v>
       </c>
       <c r="G125" s="4" t="n">
-        <v>11098</v>
+        <v>1270.5</v>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
           <t>2026-10-28 09:15</t>
         </is>
       </c>
-      <c r="I125" s="7" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I125" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 10:15</t>
+          <t>2026-10-28 09:45</t>
         </is>
       </c>
       <c r="K125" s="2" t="n">
-        <v>10735</v>
-      </c>
-      <c r="L125" s="3" t="n">
-        <v>-1.11</v>
+        <v>1270.5</v>
+      </c>
+      <c r="L125" s="4" t="n">
+        <v>2.34</v>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
@@ -9166,28 +9376,28 @@
     <row r="126" ht="18" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="B126" s="2" t="n">
-        <v>437.45</v>
+        <v>356.05</v>
       </c>
       <c r="C126" s="3" t="n">
-        <v>437</v>
+        <v>354.3</v>
       </c>
       <c r="D126" s="4" t="n">
-        <v>440.25</v>
+        <v>359.3</v>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>0.74% (3.25)</t>
+          <t>1.39% (5.0)</t>
         </is>
       </c>
       <c r="F126" s="4" t="n">
-        <v>443.5</v>
+        <v>364.3</v>
       </c>
       <c r="G126" s="4" t="n">
-        <v>446.75</v>
+        <v>369.3</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -9201,14 +9411,14 @@
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 09:45</t>
+          <t>2026-10-29 11:30</t>
         </is>
       </c>
       <c r="K126" s="2" t="n">
-        <v>446.75</v>
+        <v>369.3</v>
       </c>
       <c r="L126" s="4" t="n">
-        <v>1.48</v>
+        <v>2.78</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
@@ -9219,49 +9429,49 @@
     <row r="127" ht="18" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="B127" s="2" t="n">
-        <v>356.05</v>
+        <v>437.45</v>
       </c>
       <c r="C127" s="3" t="n">
-        <v>354.3</v>
+        <v>437</v>
       </c>
       <c r="D127" s="4" t="n">
-        <v>359.3</v>
+        <v>440.25</v>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>1.39% (5.0)</t>
+          <t>0.74% (3.25)</t>
         </is>
       </c>
       <c r="F127" s="4" t="n">
-        <v>364.3</v>
+        <v>443.5</v>
       </c>
       <c r="G127" s="4" t="n">
-        <v>369.3</v>
+        <v>446.75</v>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
           <t>2026-10-28 09:15</t>
         </is>
       </c>
-      <c r="I127" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I127" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 15:15 (Active)</t>
+          <t>2026-10-28 09:45</t>
         </is>
       </c>
       <c r="K127" s="2" t="n">
-        <v>360</v>
+        <v>446.75</v>
       </c>
       <c r="L127" s="4" t="n">
-        <v>0.19</v>
+        <v>1.48</v>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
@@ -9272,51 +9482,740 @@
     <row r="128" ht="18" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="B128" s="2" t="n">
-        <v>1240</v>
+        <v>10834</v>
       </c>
       <c r="C128" s="3" t="n">
-        <v>1227</v>
+        <v>10735</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>1241.5</v>
+        <v>10856</v>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>1.17% (14.5)</t>
+          <t>1.11% (121.0)</t>
         </is>
       </c>
       <c r="F128" s="4" t="n">
-        <v>1256</v>
+        <v>10977</v>
       </c>
       <c r="G128" s="4" t="n">
-        <v>1270.5</v>
+        <v>11098</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
           <t>2026-10-28 09:15</t>
         </is>
       </c>
-      <c r="I128" s="5" t="inlineStr">
+      <c r="I128" s="7" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 10:15</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>10735</v>
+      </c>
+      <c r="L128" s="3" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="18" customHeight="1">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>HAVELLS</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="n">
+        <v>1002.8</v>
+      </c>
+      <c r="C129" s="3" t="n">
+        <v>999.7</v>
+      </c>
+      <c r="D129" s="4" t="n">
+        <v>1014.8</v>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>1.49% (15.1)</t>
+        </is>
+      </c>
+      <c r="F129" s="4" t="n">
+        <v>1029.9</v>
+      </c>
+      <c r="G129" s="4" t="n">
+        <v>1045</v>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 09:15</t>
+        </is>
+      </c>
+      <c r="I129" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="n">
+        <v>1020</v>
+      </c>
+      <c r="L129" s="4" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="18" customHeight="1">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="n">
+        <v>1781.1</v>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>1758.2</v>
+      </c>
+      <c r="D130" s="4" t="n">
+        <v>1818.6</v>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>3.32% (60.4)</t>
+        </is>
+      </c>
+      <c r="F130" s="4" t="n">
+        <v>1879</v>
+      </c>
+      <c r="G130" s="4" t="n">
+        <v>1939.4</v>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 09:15</t>
+        </is>
+      </c>
+      <c r="I130" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="n">
+        <v>1858.2</v>
+      </c>
+      <c r="L130" s="4" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="18" customHeight="1">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>TMPV</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="n">
+        <v>259.35</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>259.3</v>
+      </c>
+      <c r="D131" s="4" t="n">
+        <v>262.35</v>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>1.16% (3.05)</t>
+        </is>
+      </c>
+      <c r="F131" s="4" t="n">
+        <v>265.4</v>
+      </c>
+      <c r="G131" s="4" t="n">
+        <v>268.45</v>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 09:15</t>
+        </is>
+      </c>
+      <c r="I131" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 10:30</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="n">
+        <v>265.4</v>
+      </c>
+      <c r="L131" s="4" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="18" customHeight="1">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>BAJFINANCE</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="n">
+        <v>907.4</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>900.05</v>
+      </c>
+      <c r="D132" s="4" t="n">
+        <v>913.05</v>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>1.42% (13.0)</t>
+        </is>
+      </c>
+      <c r="F132" s="4" t="n">
+        <v>926.05</v>
+      </c>
+      <c r="G132" s="4" t="n">
+        <v>939.05</v>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 09:15</t>
+        </is>
+      </c>
+      <c r="I132" s="5" t="inlineStr">
         <is>
           <t>TARGET 1:2 HIT</t>
         </is>
       </c>
-      <c r="J128" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-28 09:45</t>
-        </is>
-      </c>
-      <c r="K128" s="2" t="n">
-        <v>1270.5</v>
-      </c>
-      <c r="L128" s="4" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="M128" s="2" t="inlineStr">
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 14:00</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="n">
+        <v>939.05</v>
+      </c>
+      <c r="L132" s="4" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="18" customHeight="1">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="n">
+        <v>949.95</v>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>943.5</v>
+      </c>
+      <c r="D133" s="4" t="n">
+        <v>958</v>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>1.51% (14.5)</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="n">
+        <v>972.5</v>
+      </c>
+      <c r="G133" s="4" t="n">
+        <v>987</v>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 09:15</t>
+        </is>
+      </c>
+      <c r="I133" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="n">
+        <v>971.9</v>
+      </c>
+      <c r="L133" s="4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="18" customHeight="1">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>RECLTD</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="n">
+        <v>290.65</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>283.7</v>
+      </c>
+      <c r="D134" s="4" t="n">
+        <v>298.2</v>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>4.86% (14.5)</t>
+        </is>
+      </c>
+      <c r="F134" s="4" t="n">
+        <v>312.7</v>
+      </c>
+      <c r="G134" s="4" t="n">
+        <v>327.2</v>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 09:15</t>
+        </is>
+      </c>
+      <c r="I134" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="n">
+        <v>296.15</v>
+      </c>
+      <c r="L134" s="3" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="18" customHeight="1">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="n">
+        <v>312.75</v>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>310.5</v>
+      </c>
+      <c r="D135" s="4" t="n">
+        <v>315.4</v>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>1.55% (4.9)</t>
+        </is>
+      </c>
+      <c r="F135" s="4" t="n">
+        <v>320.3</v>
+      </c>
+      <c r="G135" s="4" t="n">
+        <v>325.2</v>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 09:15</t>
+        </is>
+      </c>
+      <c r="I135" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 09:15</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="n">
+        <v>320.3</v>
+      </c>
+      <c r="L135" s="4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="18" customHeight="1">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="n">
+        <v>254.8</v>
+      </c>
+      <c r="C136" s="3" t="n">
+        <v>252.85</v>
+      </c>
+      <c r="D136" s="4" t="n">
+        <v>255.9</v>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>1.19% (3.05)</t>
+        </is>
+      </c>
+      <c r="F136" s="4" t="n">
+        <v>258.95</v>
+      </c>
+      <c r="G136" s="4" t="n">
+        <v>262</v>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 09:15</t>
+        </is>
+      </c>
+      <c r="I136" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 10:00</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="n">
+        <v>262</v>
+      </c>
+      <c r="L136" s="4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="18" customHeight="1">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>IRFC</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="n">
+        <v>73.76000000000001</v>
+      </c>
+      <c r="C137" s="3" t="n">
+        <v>73.19</v>
+      </c>
+      <c r="D137" s="4" t="n">
+        <v>74.43000000000001</v>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>1.67% (1.24)</t>
+        </is>
+      </c>
+      <c r="F137" s="4" t="n">
+        <v>75.67</v>
+      </c>
+      <c r="G137" s="4" t="n">
+        <v>76.91</v>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 09:15</t>
+        </is>
+      </c>
+      <c r="I137" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 14:15</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="n">
+        <v>75.67</v>
+      </c>
+      <c r="L137" s="4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="18" customHeight="1">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="n">
+        <v>4515</v>
+      </c>
+      <c r="C138" s="3" t="n">
+        <v>4500</v>
+      </c>
+      <c r="D138" s="4" t="n">
+        <v>4564</v>
+      </c>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>1.4% (64.0)</t>
+        </is>
+      </c>
+      <c r="F138" s="4" t="n">
+        <v>4628</v>
+      </c>
+      <c r="G138" s="4" t="n">
+        <v>4692</v>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 09:15</t>
+        </is>
+      </c>
+      <c r="I138" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 14:45</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="n">
+        <v>4692</v>
+      </c>
+      <c r="L138" s="4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="18" customHeight="1">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="n">
+        <v>2462.1</v>
+      </c>
+      <c r="C139" s="3" t="n">
+        <v>2433.4</v>
+      </c>
+      <c r="D139" s="4" t="n">
+        <v>2492.8</v>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>2.38% (59.4)</t>
+        </is>
+      </c>
+      <c r="F139" s="4" t="n">
+        <v>2552.2</v>
+      </c>
+      <c r="G139" s="4" t="n">
+        <v>2611.6</v>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 09:15</t>
+        </is>
+      </c>
+      <c r="I139" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 14:00</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="n">
+        <v>2611.6</v>
+      </c>
+      <c r="L139" s="4" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="18" customHeight="1">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="n">
+        <v>2432.1</v>
+      </c>
+      <c r="C140" s="3" t="n">
+        <v>2408.2</v>
+      </c>
+      <c r="D140" s="4" t="n">
+        <v>2432.4</v>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>0.99% (24.2)</t>
+        </is>
+      </c>
+      <c r="F140" s="4" t="n">
+        <v>2456.6</v>
+      </c>
+      <c r="G140" s="4" t="n">
+        <v>2480.8</v>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 09:15</t>
+        </is>
+      </c>
+      <c r="I140" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 09:15</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="n">
+        <v>2480.8</v>
+      </c>
+      <c r="L140" s="4" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="18" customHeight="1">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="n">
+        <v>1134.6</v>
+      </c>
+      <c r="C141" s="3" t="n">
+        <v>1118.1</v>
+      </c>
+      <c r="D141" s="4" t="n">
+        <v>1166.5</v>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>4.15% (48.4)</t>
+        </is>
+      </c>
+      <c r="F141" s="4" t="n">
+        <v>1214.9</v>
+      </c>
+      <c r="G141" s="4" t="n">
+        <v>1263.3</v>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 14:30</t>
+        </is>
+      </c>
+      <c r="I141" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="n">
+        <v>1154.1</v>
+      </c>
+      <c r="L141" s="3" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="M141" s="2" t="inlineStr">
         <is>
           <t>(26-10-2026 to 01-11-2026)</t>
         </is>

--- a/data/trade_tracker_results.xlsx
+++ b/data/trade_tracker_results.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L50"/>
+  <dimension ref="A1:L51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -709,22 +709,24 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-30 09:15</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr"/>
+          <t>2026-10-30 13:45</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>2344.6</v>
+      </c>
       <c r="L4" s="4" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -977,21 +979,21 @@
         <v>686.85</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>683.85</v>
+        <v>669.5</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>688.3</v>
+        <v>687.25</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>0.65% (4.45)</t>
+          <t>2.58% (17.75)</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>692.75</v>
+        <v>705</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>697.2</v>
+        <v>722.75</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1137,24 +1139,22 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 09:15</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 14:15</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>75.67</v>
-      </c>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="4" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -1663,24 +1663,22 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 09:15</t>
-        </is>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="n">
-        <v>296.15</v>
-      </c>
-      <c r="L24" s="3" t="n">
-        <v>-0.6899999999999999</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -1721,14 +1719,14 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 15:15 (Active)</t>
+          <t>2026-10-30 15:15 (Active)</t>
         </is>
       </c>
       <c r="K25" s="2" t="n">
-        <v>971.9</v>
+        <v>961.85</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>1.45</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -1762,21 +1760,21 @@
           <t>2026-10-27 09:15</t>
         </is>
       </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 15:15 (Active)</t>
+          <t>2026-10-30 11:30</t>
         </is>
       </c>
       <c r="K26" s="2" t="n">
-        <v>4580</v>
+        <v>4662.7</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.33</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -1906,21 +1904,21 @@
           <t>2026-10-27 09:15</t>
         </is>
       </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 15:15 (Active)</t>
+          <t>2026-10-30 10:30</t>
         </is>
       </c>
       <c r="K29" s="2" t="n">
-        <v>1184.4</v>
+        <v>1223</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>2.24</v>
+        <v>5.57</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -1951,24 +1949,22 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 14:30</t>
-        </is>
-      </c>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 15:15 (Active)</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="n">
-        <v>1154.1</v>
-      </c>
-      <c r="L30" s="3" t="n">
-        <v>-1.06</v>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2153,14 +2149,14 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 15:15 (Active)</t>
+          <t>2026-10-30 15:15 (Active)</t>
         </is>
       </c>
       <c r="K34" s="2" t="n">
-        <v>1020</v>
-      </c>
-      <c r="L34" s="4" t="n">
-        <v>0.51</v>
+        <v>1013.8</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -2201,14 +2197,14 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 15:15 (Active)</t>
+          <t>2026-10-30 15:15 (Active)</t>
         </is>
       </c>
       <c r="K35" s="2" t="n">
-        <v>1858.2</v>
+        <v>1864.6</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>2.18</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -2427,22 +2423,24 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-30 09:15</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr"/>
+          <t>2026-10-30 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>1398</v>
+      </c>
       <c r="L40" s="4" t="n">
-        <v>0</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -2455,21 +2453,21 @@
         <v>1580</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>1556.1</v>
+        <v>1553.3</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>1583.9</v>
+        <v>1585.7</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>1.76% (27.8)</t>
+          <t>2.04% (32.4)</t>
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>1611.7</v>
+        <v>1618.1</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>1639.5</v>
+        <v>1650.5</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2519,22 +2517,24 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-30 09:15</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr"/>
+          <t>2026-10-30 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>4233.5</v>
+      </c>
       <c r="L42" s="4" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -2565,22 +2565,24 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-30 09:15</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="4" t="n">
-        <v>0</v>
+          <t>2026-10-30 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>1167</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>-1.14</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -2707,22 +2709,24 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-30 12:00</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="4" t="n">
-        <v>0</v>
+          <t>2026-10-30 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>1790.8</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>-1.14</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -2753,22 +2757,24 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>WAIT (No Entry)</t>
+          <t>2026-10-30 09:15</t>
+        </is>
+      </c>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr"/>
-      <c r="L47" s="4" t="n">
-        <v>0</v>
+          <t>2026-10-30 09:15</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>388.7</v>
+      </c>
+      <c r="L47" s="3" t="n">
+        <v>-2.02</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -2781,21 +2787,21 @@
         <v>1163.1</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1156.2</v>
+        <v>1152.6</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>1168.6</v>
+        <v>1164.5</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>1.06% (12.4)</t>
+          <t>1.02% (11.9)</t>
         </is>
       </c>
       <c r="F48" s="4" t="n">
-        <v>1181</v>
+        <v>1176.4</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>1193.4</v>
+        <v>1188.3</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -2830,18 +2836,18 @@
         <v>810.2</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>832.5</v>
+        <v>828.25</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>2.68% (22.3)</t>
+          <t>2.18% (18.05)</t>
         </is>
       </c>
       <c r="F49" s="4" t="n">
-        <v>854.8</v>
+        <v>846.3</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>877.1</v>
+        <v>864.35</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -2906,6 +2912,52 @@
       </c>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>1450.5</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>1342.5</v>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>1457</v>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>7.86% (114.5)</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>1571.5</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>1686</v>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>WAIT (No Entry)</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2920,7 +2972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M141"/>
+  <dimension ref="A1:M147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4795,49 +4847,49 @@
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>22165</v>
+        <v>1629.9</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>22025</v>
+        <v>1600.2</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>22195</v>
+        <v>1642.9</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>0.77% (170.0)</t>
+          <t>2.6% (42.7)</t>
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>22365</v>
+        <v>1685.6</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>22535</v>
+        <v>1728.3</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 14:45</t>
         </is>
       </c>
-      <c r="I37" s="7" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:00</t>
+          <t>2026-09-29 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K37" s="2" t="n">
-        <v>22025</v>
+        <v>1627.3</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>-0.77</v>
+        <v>-0.95</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
@@ -4848,49 +4900,49 @@
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>1629.9</v>
+        <v>22165</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>1600.2</v>
+        <v>22025</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>1642.9</v>
+        <v>22195</v>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>2.6% (42.7)</t>
+          <t>0.77% (170.0)</t>
         </is>
       </c>
       <c r="F38" s="4" t="n">
-        <v>1685.6</v>
+        <v>22365</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>1728.3</v>
+        <v>22535</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>2026-09-29 14:45</t>
         </is>
       </c>
-      <c r="I38" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:15 (Week End)</t>
+          <t>2026-09-29 15:00</t>
         </is>
       </c>
       <c r="K38" s="2" t="n">
-        <v>1627.3</v>
+        <v>22025</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>-0.95</v>
+        <v>-0.77</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
@@ -5556,28 +5608,28 @@
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>1194.9</v>
+        <v>3930.1</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>1189.9</v>
+        <v>3920</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>1202.9</v>
+        <v>4031.6</v>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>1.08% (13.0)</t>
+          <t>2.77% (111.6)</t>
         </is>
       </c>
       <c r="F52" s="4" t="n">
-        <v>1215.9</v>
+        <v>4143.2</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>1228.9</v>
+        <v>4254.8</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -5591,14 +5643,14 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 15:00 (Week End)</t>
+          <t>2026-10-06 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K52" s="2" t="n">
-        <v>1208</v>
-      </c>
-      <c r="L52" s="4" t="n">
-        <v>0.42</v>
+        <v>3981</v>
+      </c>
+      <c r="L52" s="3" t="n">
+        <v>-1.26</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
@@ -5609,49 +5661,49 @@
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>4737</v>
+        <v>378.65</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>4734.1</v>
+        <v>377.05</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>4770.2</v>
+        <v>384.35</v>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>0.76% (36.1)</t>
+          <t>1.9% (7.3)</t>
         </is>
       </c>
       <c r="F53" s="4" t="n">
-        <v>4806.3</v>
+        <v>391.65</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>4842.4</v>
+        <v>398.95</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
           <t>2026-10-06 09:15</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 11:15</t>
+          <t>2026-10-06 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K53" s="2" t="n">
-        <v>4842.4</v>
+        <v>387.4</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>1.51</v>
+        <v>0.79</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
@@ -5662,28 +5714,28 @@
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>3930.1</v>
+        <v>1194.9</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>3920</v>
+        <v>1189.9</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>4031.6</v>
+        <v>1202.9</v>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>2.77% (111.6)</t>
+          <t>1.08% (13.0)</t>
         </is>
       </c>
       <c r="F54" s="4" t="n">
-        <v>4143.2</v>
+        <v>1215.9</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>4254.8</v>
+        <v>1228.9</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -5697,14 +5749,14 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 15:15 (Week End)</t>
+          <t>2026-10-06 15:00 (Week End)</t>
         </is>
       </c>
       <c r="K54" s="2" t="n">
-        <v>3981</v>
-      </c>
-      <c r="L54" s="3" t="n">
-        <v>-1.26</v>
+        <v>1208</v>
+      </c>
+      <c r="L54" s="4" t="n">
+        <v>0.42</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
@@ -5715,49 +5767,49 @@
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>378.65</v>
+        <v>4737</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>377.05</v>
+        <v>4734.1</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>384.35</v>
+        <v>4770.2</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>1.9% (7.3)</t>
+          <t>0.76% (36.1)</t>
         </is>
       </c>
       <c r="F55" s="4" t="n">
-        <v>391.65</v>
+        <v>4806.3</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>398.95</v>
+        <v>4842.4</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
           <t>2026-10-06 09:15</t>
         </is>
       </c>
-      <c r="I55" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06 15:15 (Week End)</t>
+          <t>2026-10-06 11:15</t>
         </is>
       </c>
       <c r="K55" s="2" t="n">
-        <v>387.4</v>
+        <v>4842.4</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>0.79</v>
+        <v>1.51</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
@@ -5980,28 +6032,28 @@
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>LTM</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>1316.5</v>
+        <v>3936</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>1308.7</v>
+        <v>3908.4</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>1323.7</v>
+        <v>3941.6</v>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>1.13% (15.0)</t>
+          <t>0.84% (33.2)</t>
         </is>
       </c>
       <c r="F60" s="4" t="n">
-        <v>1338.7</v>
+        <v>3974.8</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>1353.7</v>
+        <v>4008</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -6015,14 +6067,14 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 10:15</t>
+          <t>2026-10-09 09:15</t>
         </is>
       </c>
       <c r="K60" s="2" t="n">
-        <v>1353.7</v>
+        <v>4008</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>2.27</v>
+        <v>1.68</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
@@ -6033,49 +6085,49 @@
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>902.05</v>
+        <v>1674.8</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>891.8</v>
+        <v>1658.6</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>903</v>
+        <v>1684.2</v>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>1.24% (11.2)</t>
+          <t>1.52% (25.6)</t>
         </is>
       </c>
       <c r="F61" s="4" t="n">
-        <v>914.2</v>
+        <v>1709.8</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>925.4</v>
+        <v>1735.4</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I61" s="7" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 09:15</t>
+          <t>2026-10-09 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K61" s="2" t="n">
-        <v>891.8</v>
+        <v>1682</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>-1.24</v>
+        <v>-0.13</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
@@ -6086,28 +6138,28 @@
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>254.65</v>
+        <v>1702.1</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>253.2</v>
+        <v>1701</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>255.4</v>
+        <v>1710.1</v>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>0.86% (2.2)</t>
+          <t>0.53% (9.1)</t>
         </is>
       </c>
       <c r="F62" s="4" t="n">
-        <v>257.6</v>
+        <v>1719.2</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>259.8</v>
+        <v>1728.3</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -6121,14 +6173,14 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 10:00</t>
+          <t>2026-10-09 09:45</t>
         </is>
       </c>
       <c r="K62" s="2" t="n">
-        <v>259.8</v>
+        <v>1728.3</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>1.72</v>
+        <v>1.06</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
@@ -6139,28 +6191,28 @@
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>1702.1</v>
+        <v>254.65</v>
       </c>
       <c r="C63" s="3" t="n">
-        <v>1701</v>
+        <v>253.2</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>1710.1</v>
+        <v>255.4</v>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>0.53% (9.1)</t>
+          <t>0.86% (2.2)</t>
         </is>
       </c>
       <c r="F63" s="4" t="n">
-        <v>1719.2</v>
+        <v>257.6</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>1728.3</v>
+        <v>259.8</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -6174,14 +6226,14 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 09:45</t>
+          <t>2026-10-09 10:00</t>
         </is>
       </c>
       <c r="K63" s="2" t="n">
-        <v>1728.3</v>
+        <v>259.8</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>1.06</v>
+        <v>1.72</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
@@ -6192,49 +6244,49 @@
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>1674.8</v>
+        <v>1316.5</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1658.6</v>
+        <v>1308.7</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>1684.2</v>
+        <v>1323.7</v>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>1.52% (25.6)</t>
+          <t>1.13% (15.0)</t>
         </is>
       </c>
       <c r="F64" s="4" t="n">
-        <v>1709.8</v>
+        <v>1338.7</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>1735.4</v>
+        <v>1353.7</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I64" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09 15:15 (Week End)</t>
+          <t>2026-10-09 10:15</t>
         </is>
       </c>
       <c r="K64" s="2" t="n">
-        <v>1682</v>
-      </c>
-      <c r="L64" s="3" t="n">
-        <v>-0.13</v>
+        <v>1353.7</v>
+      </c>
+      <c r="L64" s="4" t="n">
+        <v>2.27</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
@@ -6245,37 +6297,37 @@
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>LTM</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>3936</v>
+        <v>902.05</v>
       </c>
       <c r="C65" s="3" t="n">
-        <v>3908.4</v>
+        <v>891.8</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>3941.6</v>
+        <v>903</v>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>0.84% (33.2)</t>
+          <t>1.24% (11.2)</t>
         </is>
       </c>
       <c r="F65" s="4" t="n">
-        <v>3974.8</v>
+        <v>914.2</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>4008</v>
+        <v>925.4</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
           <t>2026-10-09 09:15</t>
         </is>
       </c>
-      <c r="I65" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I65" s="7" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -6284,10 +6336,10 @@
         </is>
       </c>
       <c r="K65" s="2" t="n">
-        <v>4008</v>
-      </c>
-      <c r="L65" s="4" t="n">
-        <v>1.68</v>
+        <v>891.8</v>
+      </c>
+      <c r="L65" s="3" t="n">
+        <v>-1.24</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
@@ -6476,28 +6528,28 @@
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>1828</v>
+        <v>1160.2</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>1818.5</v>
+        <v>1152.6</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>1829.2</v>
+        <v>1166.7</v>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>0.58% (10.7)</t>
+          <t>1.21% (14.1)</t>
         </is>
       </c>
       <c r="F70" s="4" t="n">
-        <v>1839.9</v>
+        <v>1180.8</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>1850.6</v>
+        <v>1194.9</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -6511,14 +6563,14 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 09:15</t>
+          <t>2026-10-15 10:00</t>
         </is>
       </c>
       <c r="K70" s="2" t="n">
-        <v>1850.6</v>
+        <v>1194.9</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>1.17</v>
+        <v>2.42</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
@@ -6529,49 +6581,49 @@
     <row r="71" ht="18" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>1486.2</v>
+        <v>441.05</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>1443.3</v>
+        <v>440.55</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>1508</v>
+        <v>445.8</v>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>4.29% (64.7)</t>
+          <t>1.18% (5.25)</t>
         </is>
       </c>
       <c r="F71" s="4" t="n">
-        <v>1572.7</v>
+        <v>451.05</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>1637.4</v>
+        <v>456.3</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I71" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 13:15</t>
+          <t>2026-10-14 11:00</t>
         </is>
       </c>
       <c r="K71" s="2" t="n">
-        <v>1637.4</v>
+        <v>451.05</v>
       </c>
       <c r="L71" s="4" t="n">
-        <v>8.58</v>
+        <v>1.18</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
@@ -6582,49 +6634,49 @@
     <row r="72" ht="18" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>857</v>
+        <v>373.3</v>
       </c>
       <c r="C72" s="3" t="n">
-        <v>846.1</v>
+        <v>373</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>861.85</v>
+        <v>375.4</v>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>1.83% (15.75)</t>
+          <t>0.64% (2.4)</t>
         </is>
       </c>
       <c r="F72" s="4" t="n">
-        <v>877.6</v>
+        <v>377.8</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>893.35</v>
+        <v>380.2</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I72" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 09:30</t>
+          <t>2026-10-14 09:15</t>
         </is>
       </c>
       <c r="K72" s="2" t="n">
-        <v>877.6</v>
+        <v>380.2</v>
       </c>
       <c r="L72" s="4" t="n">
-        <v>1.83</v>
+        <v>1.28</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
@@ -6635,49 +6687,49 @@
     <row r="73" ht="18" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>461</v>
+        <v>403.85</v>
       </c>
       <c r="C73" s="3" t="n">
-        <v>457.5</v>
+        <v>402.15</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>461.75</v>
+        <v>410.15</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>0.92% (4.25)</t>
+          <t>1.95% (8.0)</t>
         </is>
       </c>
       <c r="F73" s="4" t="n">
-        <v>466</v>
+        <v>418.15</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>470.25</v>
+        <v>426.15</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I73" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 09:30</t>
+          <t>2026-10-14 11:45</t>
         </is>
       </c>
       <c r="K73" s="2" t="n">
-        <v>470.25</v>
+        <v>418.15</v>
       </c>
       <c r="L73" s="4" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
@@ -6688,49 +6740,49 @@
     <row r="74" ht="18" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>373.3</v>
+        <v>857</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>373</v>
+        <v>846.1</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>375.4</v>
+        <v>861.85</v>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>0.64% (2.4)</t>
+          <t>1.83% (15.75)</t>
         </is>
       </c>
       <c r="F74" s="4" t="n">
-        <v>377.8</v>
+        <v>877.6</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>380.2</v>
+        <v>893.35</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I74" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 09:15</t>
+          <t>2026-10-14 09:30</t>
         </is>
       </c>
       <c r="K74" s="2" t="n">
-        <v>380.2</v>
+        <v>877.6</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>1.28</v>
+        <v>1.83</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
@@ -6741,49 +6793,49 @@
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>403.85</v>
+        <v>461</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>402.15</v>
+        <v>457.5</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>410.15</v>
+        <v>461.75</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>1.95% (8.0)</t>
+          <t>0.92% (4.25)</t>
         </is>
       </c>
       <c r="F75" s="4" t="n">
-        <v>418.15</v>
+        <v>466</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>426.15</v>
+        <v>470.25</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I75" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 11:45</t>
+          <t>2026-10-14 09:30</t>
         </is>
       </c>
       <c r="K75" s="2" t="n">
-        <v>418.15</v>
+        <v>470.25</v>
       </c>
       <c r="L75" s="4" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
@@ -6794,28 +6846,28 @@
     <row r="76" ht="18" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>1160.2</v>
+        <v>1486.2</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>1152.6</v>
+        <v>1443.3</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>1166.7</v>
+        <v>1508</v>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>1.21% (14.1)</t>
+          <t>4.29% (64.7)</t>
         </is>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1180.8</v>
+        <v>1572.7</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>1194.9</v>
+        <v>1637.4</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -6829,14 +6881,14 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 10:00</t>
+          <t>2026-10-15 13:15</t>
         </is>
       </c>
       <c r="K76" s="2" t="n">
-        <v>1194.9</v>
+        <v>1637.4</v>
       </c>
       <c r="L76" s="4" t="n">
-        <v>2.42</v>
+        <v>8.58</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
@@ -6847,49 +6899,49 @@
     <row r="77" ht="18" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>441.05</v>
+        <v>1828</v>
       </c>
       <c r="C77" s="3" t="n">
-        <v>440.55</v>
+        <v>1818.5</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>445.8</v>
+        <v>1829.2</v>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>1.18% (5.25)</t>
+          <t>0.58% (10.7)</t>
         </is>
       </c>
       <c r="F77" s="4" t="n">
-        <v>451.05</v>
+        <v>1839.9</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>456.3</v>
+        <v>1850.6</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
           <t>2026-10-14 09:15</t>
         </is>
       </c>
-      <c r="I77" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 11:00</t>
+          <t>2026-10-14 09:15</t>
         </is>
       </c>
       <c r="K77" s="2" t="n">
-        <v>451.05</v>
+        <v>1850.6</v>
       </c>
       <c r="L77" s="4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
@@ -7165,49 +7217,49 @@
     <row r="83" ht="18" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>166.3</v>
+        <v>3607</v>
       </c>
       <c r="C83" s="3" t="n">
-        <v>165.87</v>
+        <v>3593.2</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>166.83</v>
+        <v>3627.5</v>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>0.58% (0.96)</t>
+          <t>0.95% (34.3)</t>
         </is>
       </c>
       <c r="F83" s="4" t="n">
-        <v>167.79</v>
+        <v>3661.8</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>168.75</v>
+        <v>3696.1</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
           <t>2026-10-16 09:15</t>
         </is>
       </c>
-      <c r="I83" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 09:15</t>
+          <t>2026-10-16 11:30</t>
         </is>
       </c>
       <c r="K83" s="2" t="n">
-        <v>168.75</v>
+        <v>3661.8</v>
       </c>
       <c r="L83" s="4" t="n">
-        <v>1.15</v>
+        <v>0.95</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
@@ -7218,28 +7270,28 @@
     <row r="84" ht="18" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>2559.6</v>
+        <v>886.5</v>
       </c>
       <c r="C84" s="3" t="n">
-        <v>2550</v>
+        <v>860.1</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>2593</v>
+        <v>887</v>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>1.66% (43.0)</t>
+          <t>3.03% (26.9)</t>
         </is>
       </c>
       <c r="F84" s="4" t="n">
-        <v>2636</v>
+        <v>913.9</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>2679</v>
+        <v>940.8</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -7257,10 +7309,10 @@
         </is>
       </c>
       <c r="K84" s="2" t="n">
-        <v>2598.3</v>
+        <v>908</v>
       </c>
       <c r="L84" s="4" t="n">
-        <v>0.2</v>
+        <v>2.37</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
@@ -7271,28 +7323,28 @@
     <row r="85" ht="18" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>11225</v>
+        <v>2559.6</v>
       </c>
       <c r="C85" s="3" t="n">
-        <v>11130</v>
+        <v>2550</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>11325</v>
+        <v>2593</v>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>1.72% (195.0)</t>
+          <t>1.66% (43.0)</t>
         </is>
       </c>
       <c r="F85" s="4" t="n">
-        <v>11520</v>
+        <v>2636</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>11715</v>
+        <v>2679</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -7310,10 +7362,10 @@
         </is>
       </c>
       <c r="K85" s="2" t="n">
-        <v>11489</v>
+        <v>2598.3</v>
       </c>
       <c r="L85" s="4" t="n">
-        <v>1.45</v>
+        <v>0.2</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
@@ -7324,49 +7376,49 @@
     <row r="86" ht="18" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>886.5</v>
+        <v>166.3</v>
       </c>
       <c r="C86" s="3" t="n">
-        <v>860.1</v>
+        <v>165.87</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>887</v>
+        <v>166.83</v>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>3.03% (26.9)</t>
+          <t>0.58% (0.96)</t>
         </is>
       </c>
       <c r="F86" s="4" t="n">
-        <v>913.9</v>
+        <v>167.79</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>940.8</v>
+        <v>168.75</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
           <t>2026-10-16 09:15</t>
         </is>
       </c>
-      <c r="I86" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I86" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 15:15 (Week End)</t>
+          <t>2026-10-16 09:15</t>
         </is>
       </c>
       <c r="K86" s="2" t="n">
-        <v>908</v>
+        <v>168.75</v>
       </c>
       <c r="L86" s="4" t="n">
-        <v>2.37</v>
+        <v>1.15</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
@@ -7377,28 +7429,28 @@
     <row r="87" ht="18" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>3607</v>
+        <v>11225</v>
       </c>
       <c r="C87" s="3" t="n">
-        <v>3593.2</v>
+        <v>11130</v>
       </c>
       <c r="D87" s="4" t="n">
-        <v>3627.5</v>
+        <v>11325</v>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>0.95% (34.3)</t>
+          <t>1.72% (195.0)</t>
         </is>
       </c>
       <c r="F87" s="4" t="n">
-        <v>3661.8</v>
+        <v>11520</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>3696.1</v>
+        <v>11715</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -7412,14 +7464,14 @@
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 11:30</t>
+          <t>2026-10-16 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K87" s="2" t="n">
-        <v>3661.8</v>
+        <v>11489</v>
       </c>
       <c r="L87" s="4" t="n">
-        <v>0.95</v>
+        <v>1.45</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
@@ -7608,28 +7660,28 @@
     <row r="92" ht="18" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>1725.5</v>
+        <v>4550.4</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>1719.6</v>
+        <v>4474.6</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>1745.1</v>
+        <v>4572.1</v>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>1.46% (25.5)</t>
+          <t>2.13% (97.5)</t>
         </is>
       </c>
       <c r="F92" s="4" t="n">
-        <v>1770.6</v>
+        <v>4669.6</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>1796.1</v>
+        <v>4767.1</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -7647,10 +7699,10 @@
         </is>
       </c>
       <c r="K92" s="2" t="n">
-        <v>1748</v>
-      </c>
-      <c r="L92" s="4" t="n">
-        <v>0.17</v>
+        <v>4524.4</v>
+      </c>
+      <c r="L92" s="3" t="n">
+        <v>-1.04</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
@@ -7661,28 +7713,28 @@
     <row r="93" ht="18" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>1300.2</v>
+        <v>2843.4</v>
       </c>
       <c r="C93" s="3" t="n">
-        <v>1296.7</v>
+        <v>2828.2</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>1314</v>
+        <v>2889.1</v>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>1.32% (17.3)</t>
+          <t>2.11% (60.9)</t>
         </is>
       </c>
       <c r="F93" s="4" t="n">
-        <v>1331.3</v>
+        <v>2950</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>1348.6</v>
+        <v>3010.9</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
@@ -7696,14 +7748,14 @@
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:15</t>
+          <t>2026-10-23 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K93" s="2" t="n">
-        <v>1331.3</v>
+        <v>2894</v>
       </c>
       <c r="L93" s="4" t="n">
-        <v>1.32</v>
+        <v>0.17</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
@@ -7714,49 +7766,49 @@
     <row r="94" ht="18" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>1003.5</v>
+        <v>165.87</v>
       </c>
       <c r="C94" s="3" t="n">
-        <v>1001.4</v>
+        <v>164.88</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>1028</v>
+        <v>165.92</v>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>2.59% (26.6)</t>
+          <t>0.63% (1.04)</t>
         </is>
       </c>
       <c r="F94" s="4" t="n">
-        <v>1054.6</v>
+        <v>166.96</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>1081.2</v>
+        <v>168</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
           <t>2026-10-23 09:15</t>
         </is>
       </c>
-      <c r="I94" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I94" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Then SL)</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 15:15 (Week End)</t>
+          <t>2026-10-23 09:30</t>
         </is>
       </c>
       <c r="K94" s="2" t="n">
-        <v>1015.9</v>
+        <v>164.88</v>
       </c>
       <c r="L94" s="3" t="n">
-        <v>-1.18</v>
+        <v>-0.63</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
@@ -7767,49 +7819,49 @@
     <row r="95" ht="18" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>1107.3</v>
+        <v>437.2</v>
       </c>
       <c r="C95" s="3" t="n">
-        <v>1100.3</v>
+        <v>433.75</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>1117.3</v>
+        <v>438.2</v>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>1.52% (17.0)</t>
+          <t>1.02% (4.45)</t>
         </is>
       </c>
       <c r="F95" s="4" t="n">
-        <v>1134.3</v>
+        <v>442.65</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>1151.3</v>
+        <v>447.1</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
           <t>2026-10-23 09:15</t>
         </is>
       </c>
-      <c r="I95" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE (Week End)</t>
+      <c r="I95" s="7" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:15</t>
+          <t>2026-10-23 10:00</t>
         </is>
       </c>
       <c r="K95" s="2" t="n">
-        <v>1134.3</v>
-      </c>
-      <c r="L95" s="4" t="n">
-        <v>1.52</v>
+        <v>433.75</v>
+      </c>
+      <c r="L95" s="3" t="n">
+        <v>-1.02</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
@@ -7820,49 +7872,49 @@
     <row r="96" ht="18" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>437.2</v>
+        <v>1003.5</v>
       </c>
       <c r="C96" s="3" t="n">
-        <v>433.75</v>
+        <v>1001.4</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>438.2</v>
+        <v>1028</v>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>1.02% (4.45)</t>
+          <t>2.59% (26.6)</t>
         </is>
       </c>
       <c r="F96" s="4" t="n">
-        <v>442.65</v>
+        <v>1054.6</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>447.1</v>
+        <v>1081.2</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
           <t>2026-10-23 09:15</t>
         </is>
       </c>
-      <c r="I96" s="7" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I96" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 10:00</t>
+          <t>2026-10-23 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K96" s="2" t="n">
-        <v>433.75</v>
+        <v>1015.9</v>
       </c>
       <c r="L96" s="3" t="n">
-        <v>-1.02</v>
+        <v>-1.18</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
@@ -7873,28 +7925,28 @@
     <row r="97" ht="18" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>4550.4</v>
+        <v>1300.2</v>
       </c>
       <c r="C97" s="3" t="n">
-        <v>4474.6</v>
+        <v>1296.7</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>4572.1</v>
+        <v>1314</v>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>2.13% (97.5)</t>
+          <t>1.32% (17.3)</t>
         </is>
       </c>
       <c r="F97" s="4" t="n">
-        <v>4669.6</v>
+        <v>1331.3</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>4767.1</v>
+        <v>1348.6</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -7908,14 +7960,14 @@
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 15:15 (Week End)</t>
+          <t>2026-10-23 09:15</t>
         </is>
       </c>
       <c r="K97" s="2" t="n">
-        <v>4524.4</v>
-      </c>
-      <c r="L97" s="3" t="n">
-        <v>-1.04</v>
+        <v>1331.3</v>
+      </c>
+      <c r="L97" s="4" t="n">
+        <v>1.32</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
@@ -7926,49 +7978,49 @@
     <row r="98" ht="18" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>165.87</v>
+        <v>1725.5</v>
       </c>
       <c r="C98" s="3" t="n">
-        <v>164.88</v>
+        <v>1719.6</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>165.92</v>
+        <v>1745.1</v>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>0.63% (1.04)</t>
+          <t>1.46% (25.5)</t>
         </is>
       </c>
       <c r="F98" s="4" t="n">
-        <v>166.96</v>
+        <v>1770.6</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>168</v>
+        <v>1796.1</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
           <t>2026-10-23 09:15</t>
         </is>
       </c>
-      <c r="I98" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Then SL)</t>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE (Week End)</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 09:30</t>
+          <t>2026-10-23 15:15 (Week End)</t>
         </is>
       </c>
       <c r="K98" s="2" t="n">
-        <v>164.88</v>
-      </c>
-      <c r="L98" s="3" t="n">
-        <v>-0.63</v>
+        <v>1748</v>
+      </c>
+      <c r="L98" s="4" t="n">
+        <v>0.17</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
@@ -7979,28 +8031,28 @@
     <row r="99" ht="18" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>2843.4</v>
+        <v>1107.3</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>2828.2</v>
+        <v>1100.3</v>
       </c>
       <c r="D99" s="4" t="n">
-        <v>2889.1</v>
+        <v>1117.3</v>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>2.11% (60.9)</t>
+          <t>1.52% (17.0)</t>
         </is>
       </c>
       <c r="F99" s="4" t="n">
-        <v>2950</v>
+        <v>1134.3</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>3010.9</v>
+        <v>1151.3</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
@@ -8014,14 +8066,14 @@
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23 15:15 (Week End)</t>
+          <t>2026-10-23 09:15</t>
         </is>
       </c>
       <c r="K99" s="2" t="n">
-        <v>2894</v>
+        <v>1134.3</v>
       </c>
       <c r="L99" s="4" t="n">
-        <v>0.17</v>
+        <v>1.52</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
@@ -8051,28 +8103,28 @@
     <row r="101" ht="18" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>440.15</v>
+        <v>4716.3</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>440.15</v>
+        <v>4642.1</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>446.35</v>
+        <v>4733</v>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>1.39% (6.2)</t>
+          <t>1.92% (90.9)</t>
         </is>
       </c>
       <c r="F101" s="4" t="n">
-        <v>452.55</v>
+        <v>4823.9</v>
       </c>
       <c r="G101" s="4" t="n">
-        <v>458.75</v>
+        <v>4914.8</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
@@ -8086,14 +8138,14 @@
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:15</t>
+          <t>2026-10-27 09:30</t>
         </is>
       </c>
       <c r="K101" s="2" t="n">
-        <v>458.75</v>
+        <v>4914.8</v>
       </c>
       <c r="L101" s="4" t="n">
-        <v>2.78</v>
+        <v>3.84</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
@@ -8104,28 +8156,28 @@
     <row r="102" ht="18" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>LODHA</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>941</v>
+        <v>4994.5</v>
       </c>
       <c r="C102" s="3" t="n">
-        <v>939.8</v>
+        <v>4977.5</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>948.2</v>
+        <v>5054.5</v>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>0.89% (8.4)</t>
+          <t>1.52% (77.0)</t>
         </is>
       </c>
       <c r="F102" s="4" t="n">
-        <v>956.6</v>
+        <v>5131.5</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>965</v>
+        <v>5208.5</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -8143,10 +8195,10 @@
         </is>
       </c>
       <c r="K102" s="2" t="n">
-        <v>965</v>
+        <v>5208.5</v>
       </c>
       <c r="L102" s="4" t="n">
-        <v>1.77</v>
+        <v>3.05</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
@@ -8157,28 +8209,28 @@
     <row r="103" ht="18" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>148.07</v>
+        <v>4470.4</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>147.32</v>
+        <v>4467.3</v>
       </c>
       <c r="D103" s="4" t="n">
-        <v>148.9</v>
+        <v>4565</v>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>1.06% (1.58)</t>
+          <t>2.14% (97.7)</t>
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>150.48</v>
+        <v>4662.7</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>152.06</v>
+        <v>4760.4</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
@@ -8187,19 +8239,19 @@
       </c>
       <c r="I103" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:15</t>
+          <t>2026-10-30 11:30</t>
         </is>
       </c>
       <c r="K103" s="2" t="n">
-        <v>152.06</v>
+        <v>4662.7</v>
       </c>
       <c r="L103" s="4" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
@@ -8210,28 +8262,28 @@
     <row r="104" ht="18" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>1845</v>
+        <v>852</v>
       </c>
       <c r="C104" s="3" t="n">
-        <v>1838.7</v>
+        <v>851.35</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>1860.9</v>
+        <v>864</v>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>1.19% (22.2)</t>
+          <t>1.46% (12.65)</t>
         </is>
       </c>
       <c r="F104" s="4" t="n">
-        <v>1883.1</v>
+        <v>876.65</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>1905.3</v>
+        <v>889.3</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -8249,10 +8301,10 @@
         </is>
       </c>
       <c r="K104" s="2" t="n">
-        <v>1905.3</v>
+        <v>889.3</v>
       </c>
       <c r="L104" s="4" t="n">
-        <v>2.39</v>
+        <v>2.93</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
@@ -8263,28 +8315,28 @@
     <row r="105" ht="18" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B105" s="2" t="n">
-        <v>69.03</v>
+        <v>1450</v>
       </c>
       <c r="C105" s="3" t="n">
-        <v>68.84</v>
+        <v>1415</v>
       </c>
       <c r="D105" s="4" t="n">
-        <v>69.33</v>
+        <v>1452.6</v>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>0.71% (0.49)</t>
+          <t>2.59% (37.6)</t>
         </is>
       </c>
       <c r="F105" s="4" t="n">
-        <v>69.81999999999999</v>
+        <v>1490.2</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>70.31</v>
+        <v>1527.8</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
@@ -8298,14 +8350,14 @@
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:15</t>
+          <t>2026-10-28 13:30</t>
         </is>
       </c>
       <c r="K105" s="2" t="n">
-        <v>70.31</v>
+        <v>1527.8</v>
       </c>
       <c r="L105" s="4" t="n">
-        <v>1.41</v>
+        <v>5.18</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
@@ -8316,28 +8368,28 @@
     <row r="106" ht="18" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="B106" s="2" t="n">
-        <v>1177.6</v>
+        <v>440.15</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>1169.8</v>
+        <v>440.15</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>1188.2</v>
+        <v>446.35</v>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>1.55% (18.4)</t>
+          <t>1.39% (6.2)</t>
         </is>
       </c>
       <c r="F106" s="4" t="n">
-        <v>1206.6</v>
+        <v>452.55</v>
       </c>
       <c r="G106" s="4" t="n">
-        <v>1225</v>
+        <v>458.75</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -8346,19 +8398,19 @@
       </c>
       <c r="I106" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 10:00</t>
+          <t>2026-10-27 09:15</t>
         </is>
       </c>
       <c r="K106" s="2" t="n">
-        <v>1206.6</v>
+        <v>458.75</v>
       </c>
       <c r="L106" s="4" t="n">
-        <v>1.55</v>
+        <v>2.78</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
@@ -8369,28 +8421,28 @@
     <row r="107" ht="18" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="B107" s="2" t="n">
-        <v>119.06</v>
+        <v>1845</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>118.25</v>
+        <v>1838.7</v>
       </c>
       <c r="D107" s="4" t="n">
-        <v>119.24</v>
+        <v>1860.9</v>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>0.83% (0.99)</t>
+          <t>1.19% (22.2)</t>
         </is>
       </c>
       <c r="F107" s="4" t="n">
-        <v>120.23</v>
+        <v>1883.1</v>
       </c>
       <c r="G107" s="4" t="n">
-        <v>121.22</v>
+        <v>1905.3</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -8408,10 +8460,10 @@
         </is>
       </c>
       <c r="K107" s="2" t="n">
-        <v>121.22</v>
+        <v>1905.3</v>
       </c>
       <c r="L107" s="4" t="n">
-        <v>1.66</v>
+        <v>2.39</v>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
@@ -8422,28 +8474,28 @@
     <row r="108" ht="18" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B108" s="2" t="n">
-        <v>1450</v>
+        <v>148.07</v>
       </c>
       <c r="C108" s="3" t="n">
-        <v>1415</v>
+        <v>147.32</v>
       </c>
       <c r="D108" s="4" t="n">
-        <v>1452.6</v>
+        <v>148.9</v>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>2.59% (37.6)</t>
+          <t>1.06% (1.58)</t>
         </is>
       </c>
       <c r="F108" s="4" t="n">
-        <v>1490.2</v>
+        <v>150.48</v>
       </c>
       <c r="G108" s="4" t="n">
-        <v>1527.8</v>
+        <v>152.06</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -8457,14 +8509,14 @@
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 13:30</t>
+          <t>2026-10-27 09:15</t>
         </is>
       </c>
       <c r="K108" s="2" t="n">
-        <v>1527.8</v>
+        <v>152.06</v>
       </c>
       <c r="L108" s="4" t="n">
-        <v>5.18</v>
+        <v>2.12</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
@@ -8475,49 +8527,49 @@
     <row r="109" ht="18" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="B109" s="2" t="n">
-        <v>4470.4</v>
+        <v>69.03</v>
       </c>
       <c r="C109" s="3" t="n">
-        <v>4467.3</v>
+        <v>68.84</v>
       </c>
       <c r="D109" s="4" t="n">
-        <v>4565</v>
+        <v>69.33</v>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>2.14% (97.7)</t>
+          <t>0.71% (0.49)</t>
         </is>
       </c>
       <c r="F109" s="4" t="n">
-        <v>4662.7</v>
+        <v>69.81999999999999</v>
       </c>
       <c r="G109" s="4" t="n">
-        <v>4760.4</v>
+        <v>70.31</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
           <t>2026-10-27 09:15</t>
         </is>
       </c>
-      <c r="I109" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I109" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 15:15 (Active)</t>
+          <t>2026-10-27 09:15</t>
         </is>
       </c>
       <c r="K109" s="2" t="n">
-        <v>4580</v>
+        <v>70.31</v>
       </c>
       <c r="L109" s="4" t="n">
-        <v>0.33</v>
+        <v>1.41</v>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
@@ -8528,28 +8580,28 @@
     <row r="110" ht="18" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="B110" s="2" t="n">
-        <v>3898.1</v>
+        <v>444.9</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>3875.1</v>
+        <v>441.7</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>3961.9</v>
+        <v>447.5</v>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>2.19% (86.8)</t>
+          <t>1.3% (5.8)</t>
         </is>
       </c>
       <c r="F110" s="4" t="n">
-        <v>4048.7</v>
+        <v>453.3</v>
       </c>
       <c r="G110" s="4" t="n">
-        <v>4135.5</v>
+        <v>459.1</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -8558,19 +8610,19 @@
       </c>
       <c r="I110" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 11:30</t>
+          <t>2026-10-27 09:15</t>
         </is>
       </c>
       <c r="K110" s="2" t="n">
-        <v>4135.5</v>
+        <v>453.3</v>
       </c>
       <c r="L110" s="4" t="n">
-        <v>4.38</v>
+        <v>1.3</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
@@ -8581,28 +8633,28 @@
     <row r="111" ht="18" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="B111" s="2" t="n">
-        <v>852</v>
+        <v>119.06</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>851.35</v>
+        <v>118.25</v>
       </c>
       <c r="D111" s="4" t="n">
-        <v>864</v>
+        <v>119.24</v>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>1.46% (12.65)</t>
+          <t>0.83% (0.99)</t>
         </is>
       </c>
       <c r="F111" s="4" t="n">
-        <v>876.65</v>
+        <v>120.23</v>
       </c>
       <c r="G111" s="4" t="n">
-        <v>889.3</v>
+        <v>121.22</v>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
@@ -8620,10 +8672,10 @@
         </is>
       </c>
       <c r="K111" s="2" t="n">
-        <v>889.3</v>
+        <v>121.22</v>
       </c>
       <c r="L111" s="4" t="n">
-        <v>2.93</v>
+        <v>1.66</v>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
@@ -8634,28 +8686,28 @@
     <row r="112" ht="18" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="B112" s="2" t="n">
-        <v>444.9</v>
+        <v>1100.3</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>441.7</v>
+        <v>1094</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>447.5</v>
+        <v>1158.5</v>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>1.3% (5.8)</t>
+          <t>5.57% (64.5)</t>
         </is>
       </c>
       <c r="F112" s="4" t="n">
-        <v>453.3</v>
+        <v>1223</v>
       </c>
       <c r="G112" s="4" t="n">
-        <v>459.1</v>
+        <v>1287.5</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -8669,14 +8721,14 @@
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:15</t>
+          <t>2026-10-30 10:30</t>
         </is>
       </c>
       <c r="K112" s="2" t="n">
-        <v>453.3</v>
+        <v>1223</v>
       </c>
       <c r="L112" s="4" t="n">
-        <v>1.3</v>
+        <v>5.57</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
@@ -8687,28 +8739,28 @@
     <row r="113" ht="18" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>LODHA</t>
         </is>
       </c>
       <c r="B113" s="2" t="n">
-        <v>4994.5</v>
+        <v>941</v>
       </c>
       <c r="C113" s="3" t="n">
-        <v>4977.5</v>
+        <v>939.8</v>
       </c>
       <c r="D113" s="4" t="n">
-        <v>5054.5</v>
+        <v>948.2</v>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>1.52% (77.0)</t>
+          <t>0.89% (8.4)</t>
         </is>
       </c>
       <c r="F113" s="4" t="n">
-        <v>5131.5</v>
+        <v>956.6</v>
       </c>
       <c r="G113" s="4" t="n">
-        <v>5208.5</v>
+        <v>965</v>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
@@ -8726,10 +8778,10 @@
         </is>
       </c>
       <c r="K113" s="2" t="n">
-        <v>5208.5</v>
+        <v>965</v>
       </c>
       <c r="L113" s="4" t="n">
-        <v>3.05</v>
+        <v>1.77</v>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
@@ -8740,49 +8792,49 @@
     <row r="114" ht="18" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="B114" s="2" t="n">
-        <v>1100.3</v>
+        <v>115.37</v>
       </c>
       <c r="C114" s="3" t="n">
-        <v>1094</v>
+        <v>114.72</v>
       </c>
       <c r="D114" s="4" t="n">
-        <v>1158.5</v>
+        <v>115.75</v>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>5.57% (64.5)</t>
+          <t>0.89% (1.03)</t>
         </is>
       </c>
       <c r="F114" s="4" t="n">
-        <v>1223</v>
+        <v>116.78</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>1287.5</v>
+        <v>117.81</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
           <t>2026-10-27 09:15</t>
         </is>
       </c>
-      <c r="I114" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I114" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 15:15 (Active)</t>
+          <t>2026-10-27 09:15</t>
         </is>
       </c>
       <c r="K114" s="2" t="n">
-        <v>1184.4</v>
+        <v>117.81</v>
       </c>
       <c r="L114" s="4" t="n">
-        <v>2.24</v>
+        <v>1.78</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
@@ -8793,28 +8845,28 @@
     <row r="115" ht="18" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B115" s="2" t="n">
-        <v>115.37</v>
+        <v>254.8</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>114.72</v>
+        <v>254.5</v>
       </c>
       <c r="D115" s="4" t="n">
-        <v>115.75</v>
+        <v>256.25</v>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>0.89% (1.03)</t>
+          <t>0.68% (1.75)</t>
         </is>
       </c>
       <c r="F115" s="4" t="n">
-        <v>116.78</v>
+        <v>258</v>
       </c>
       <c r="G115" s="4" t="n">
-        <v>117.81</v>
+        <v>259.75</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -8832,10 +8884,10 @@
         </is>
       </c>
       <c r="K115" s="2" t="n">
-        <v>117.81</v>
+        <v>259.75</v>
       </c>
       <c r="L115" s="4" t="n">
-        <v>1.78</v>
+        <v>1.37</v>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
@@ -8846,49 +8898,49 @@
     <row r="116" ht="18" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
       <c r="B116" s="2" t="n">
-        <v>2260</v>
+        <v>229.2</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>2234.3</v>
+        <v>227.3</v>
       </c>
       <c r="D116" s="4" t="n">
-        <v>2283.3</v>
+        <v>229.7</v>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>2.15% (49.0)</t>
+          <t>1.04% (2.4)</t>
         </is>
       </c>
       <c r="F116" s="4" t="n">
-        <v>2332.3</v>
+        <v>232.1</v>
       </c>
       <c r="G116" s="4" t="n">
-        <v>2381.3</v>
+        <v>234.5</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
           <t>2026-10-27 09:15</t>
         </is>
       </c>
-      <c r="I116" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I116" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 15:15 (Active)</t>
+          <t>2026-10-29 09:15</t>
         </is>
       </c>
       <c r="K116" s="2" t="n">
-        <v>2277</v>
-      </c>
-      <c r="L116" s="3" t="n">
-        <v>-0.28</v>
+        <v>234.5</v>
+      </c>
+      <c r="L116" s="4" t="n">
+        <v>2.09</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
@@ -8899,28 +8951,28 @@
     <row r="117" ht="18" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="B117" s="2" t="n">
-        <v>4515</v>
+        <v>1177.6</v>
       </c>
       <c r="C117" s="3" t="n">
-        <v>4507.9</v>
+        <v>1169.8</v>
       </c>
       <c r="D117" s="4" t="n">
-        <v>4540.1</v>
+        <v>1188.2</v>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>0.71% (32.2)</t>
+          <t>1.55% (18.4)</t>
         </is>
       </c>
       <c r="F117" s="4" t="n">
-        <v>4572.3</v>
+        <v>1206.6</v>
       </c>
       <c r="G117" s="4" t="n">
-        <v>4604.5</v>
+        <v>1225</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
@@ -8934,14 +8986,14 @@
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:15</t>
+          <t>2026-10-27 10:00</t>
         </is>
       </c>
       <c r="K117" s="2" t="n">
-        <v>4572.3</v>
+        <v>1206.6</v>
       </c>
       <c r="L117" s="4" t="n">
-        <v>0.71</v>
+        <v>1.55</v>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
@@ -8952,49 +9004,49 @@
     <row r="118" ht="18" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B118" s="2" t="n">
-        <v>254.8</v>
+        <v>2260</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>254.5</v>
+        <v>2234.3</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>256.25</v>
+        <v>2283.3</v>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>0.68% (1.75)</t>
+          <t>2.15% (49.0)</t>
         </is>
       </c>
       <c r="F118" s="4" t="n">
-        <v>258</v>
+        <v>2332.3</v>
       </c>
       <c r="G118" s="4" t="n">
-        <v>259.75</v>
+        <v>2381.3</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
           <t>2026-10-27 09:15</t>
         </is>
       </c>
-      <c r="I118" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I118" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:15</t>
+          <t>2026-10-27 15:15 (Active)</t>
         </is>
       </c>
       <c r="K118" s="2" t="n">
-        <v>259.75</v>
-      </c>
-      <c r="L118" s="4" t="n">
-        <v>1.37</v>
+        <v>2277</v>
+      </c>
+      <c r="L118" s="3" t="n">
+        <v>-0.28</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
@@ -9005,28 +9057,28 @@
     <row r="119" ht="18" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B119" s="2" t="n">
-        <v>223.35</v>
+        <v>4515</v>
       </c>
       <c r="C119" s="3" t="n">
-        <v>221.8</v>
+        <v>4507.9</v>
       </c>
       <c r="D119" s="4" t="n">
-        <v>225</v>
+        <v>4540.1</v>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>1.42% (3.2)</t>
+          <t>0.71% (32.2)</t>
         </is>
       </c>
       <c r="F119" s="4" t="n">
-        <v>228.2</v>
+        <v>4572.3</v>
       </c>
       <c r="G119" s="4" t="n">
-        <v>231.4</v>
+        <v>4604.5</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -9035,19 +9087,19 @@
       </c>
       <c r="I119" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 12:30</t>
+          <t>2026-10-27 09:15</t>
         </is>
       </c>
       <c r="K119" s="2" t="n">
-        <v>231.4</v>
+        <v>4572.3</v>
       </c>
       <c r="L119" s="4" t="n">
-        <v>2.84</v>
+        <v>0.71</v>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
@@ -9058,28 +9110,28 @@
     <row r="120" ht="18" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B120" s="2" t="n">
-        <v>4716.3</v>
+        <v>3898.1</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>4642.1</v>
+        <v>3875.1</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>4733</v>
+        <v>3961.9</v>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>1.92% (90.9)</t>
+          <t>2.19% (86.8)</t>
         </is>
       </c>
       <c r="F120" s="4" t="n">
-        <v>4823.9</v>
+        <v>4048.7</v>
       </c>
       <c r="G120" s="4" t="n">
-        <v>4914.8</v>
+        <v>4135.5</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -9093,14 +9145,14 @@
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:30</t>
+          <t>2026-10-28 11:30</t>
         </is>
       </c>
       <c r="K120" s="2" t="n">
-        <v>4914.8</v>
+        <v>4135.5</v>
       </c>
       <c r="L120" s="4" t="n">
-        <v>3.84</v>
+        <v>4.38</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
@@ -9164,28 +9216,28 @@
     <row r="122" ht="18" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="B122" s="2" t="n">
-        <v>229.2</v>
+        <v>6070</v>
       </c>
       <c r="C122" s="3" t="n">
-        <v>227.3</v>
+        <v>6065</v>
       </c>
       <c r="D122" s="4" t="n">
-        <v>229.7</v>
+        <v>6152</v>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>1.04% (2.4)</t>
+          <t>1.41% (87.0)</t>
         </is>
       </c>
       <c r="F122" s="4" t="n">
-        <v>232.1</v>
+        <v>6239</v>
       </c>
       <c r="G122" s="4" t="n">
-        <v>234.5</v>
+        <v>6326</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -9199,14 +9251,14 @@
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 09:15</t>
+          <t>2026-10-27 09:15</t>
         </is>
       </c>
       <c r="K122" s="2" t="n">
-        <v>234.5</v>
+        <v>6326</v>
       </c>
       <c r="L122" s="4" t="n">
-        <v>2.09</v>
+        <v>2.83</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
@@ -9217,28 +9269,28 @@
     <row r="123" ht="18" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="B123" s="2" t="n">
-        <v>6070</v>
+        <v>223.35</v>
       </c>
       <c r="C123" s="3" t="n">
-        <v>6065</v>
+        <v>221.8</v>
       </c>
       <c r="D123" s="4" t="n">
-        <v>6152</v>
+        <v>225</v>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>1.41% (87.0)</t>
+          <t>1.42% (3.2)</t>
         </is>
       </c>
       <c r="F123" s="4" t="n">
-        <v>6239</v>
+        <v>228.2</v>
       </c>
       <c r="G123" s="4" t="n">
-        <v>6326</v>
+        <v>231.4</v>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
@@ -9252,14 +9304,14 @@
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27 09:15</t>
+          <t>2026-10-28 12:30</t>
         </is>
       </c>
       <c r="K123" s="2" t="n">
-        <v>6326</v>
+        <v>231.4</v>
       </c>
       <c r="L123" s="4" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
@@ -9323,28 +9375,28 @@
     <row r="125" ht="18" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="B125" s="2" t="n">
-        <v>1240</v>
+        <v>356.05</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>1227</v>
+        <v>354.3</v>
       </c>
       <c r="D125" s="4" t="n">
-        <v>1241.5</v>
+        <v>359.3</v>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>1.17% (14.5)</t>
+          <t>1.39% (5.0)</t>
         </is>
       </c>
       <c r="F125" s="4" t="n">
-        <v>1256</v>
+        <v>364.3</v>
       </c>
       <c r="G125" s="4" t="n">
-        <v>1270.5</v>
+        <v>369.3</v>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
@@ -9358,14 +9410,14 @@
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 09:45</t>
+          <t>2026-10-29 11:30</t>
         </is>
       </c>
       <c r="K125" s="2" t="n">
-        <v>1270.5</v>
+        <v>369.3</v>
       </c>
       <c r="L125" s="4" t="n">
-        <v>2.34</v>
+        <v>2.78</v>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
@@ -9376,28 +9428,28 @@
     <row r="126" ht="18" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="B126" s="2" t="n">
-        <v>356.05</v>
+        <v>437.45</v>
       </c>
       <c r="C126" s="3" t="n">
-        <v>354.3</v>
+        <v>437</v>
       </c>
       <c r="D126" s="4" t="n">
-        <v>359.3</v>
+        <v>440.25</v>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>1.39% (5.0)</t>
+          <t>0.74% (3.25)</t>
         </is>
       </c>
       <c r="F126" s="4" t="n">
-        <v>364.3</v>
+        <v>443.5</v>
       </c>
       <c r="G126" s="4" t="n">
-        <v>369.3</v>
+        <v>446.75</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -9411,14 +9463,14 @@
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 11:30</t>
+          <t>2026-10-28 09:45</t>
         </is>
       </c>
       <c r="K126" s="2" t="n">
-        <v>369.3</v>
+        <v>446.75</v>
       </c>
       <c r="L126" s="4" t="n">
-        <v>2.78</v>
+        <v>1.48</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
@@ -9429,49 +9481,49 @@
     <row r="127" ht="18" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="B127" s="2" t="n">
-        <v>437.45</v>
+        <v>10834</v>
       </c>
       <c r="C127" s="3" t="n">
-        <v>437</v>
+        <v>10735</v>
       </c>
       <c r="D127" s="4" t="n">
-        <v>440.25</v>
+        <v>10856</v>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>0.74% (3.25)</t>
+          <t>1.11% (121.0)</t>
         </is>
       </c>
       <c r="F127" s="4" t="n">
-        <v>443.5</v>
+        <v>10977</v>
       </c>
       <c r="G127" s="4" t="n">
-        <v>446.75</v>
+        <v>11098</v>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
           <t>2026-10-28 09:15</t>
         </is>
       </c>
-      <c r="I127" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I127" s="7" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 09:45</t>
+          <t>2026-10-28 10:15</t>
         </is>
       </c>
       <c r="K127" s="2" t="n">
-        <v>446.75</v>
-      </c>
-      <c r="L127" s="4" t="n">
-        <v>1.48</v>
+        <v>10735</v>
+      </c>
+      <c r="L127" s="3" t="n">
+        <v>-1.11</v>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
@@ -9482,49 +9534,49 @@
     <row r="128" ht="18" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
       <c r="B128" s="2" t="n">
-        <v>10834</v>
+        <v>1240</v>
       </c>
       <c r="C128" s="3" t="n">
-        <v>10735</v>
+        <v>1227</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>10856</v>
+        <v>1241.5</v>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>1.11% (121.0)</t>
+          <t>1.17% (14.5)</t>
         </is>
       </c>
       <c r="F128" s="4" t="n">
-        <v>10977</v>
+        <v>1256</v>
       </c>
       <c r="G128" s="4" t="n">
-        <v>11098</v>
+        <v>1270.5</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
           <t>2026-10-28 09:15</t>
         </is>
       </c>
-      <c r="I128" s="7" t="inlineStr">
-        <is>
-          <t>SL HIT</t>
+      <c r="I128" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 10:15</t>
+          <t>2026-10-28 09:45</t>
         </is>
       </c>
       <c r="K128" s="2" t="n">
-        <v>10735</v>
-      </c>
-      <c r="L128" s="3" t="n">
-        <v>-1.11</v>
+        <v>1270.5</v>
+      </c>
+      <c r="L128" s="4" t="n">
+        <v>2.34</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
@@ -9535,49 +9587,49 @@
     <row r="129" ht="18" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>TMPV</t>
         </is>
       </c>
       <c r="B129" s="2" t="n">
-        <v>1002.8</v>
+        <v>259.35</v>
       </c>
       <c r="C129" s="3" t="n">
-        <v>999.7</v>
+        <v>259.3</v>
       </c>
       <c r="D129" s="4" t="n">
-        <v>1014.8</v>
+        <v>262.35</v>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>1.49% (15.1)</t>
+          <t>1.16% (3.05)</t>
         </is>
       </c>
       <c r="F129" s="4" t="n">
-        <v>1029.9</v>
+        <v>265.4</v>
       </c>
       <c r="G129" s="4" t="n">
-        <v>1045</v>
+        <v>268.45</v>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
           <t>2026-10-29 09:15</t>
         </is>
       </c>
-      <c r="I129" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I129" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 15:15 (Active)</t>
+          <t>2026-10-29 10:30</t>
         </is>
       </c>
       <c r="K129" s="2" t="n">
-        <v>1020</v>
+        <v>265.4</v>
       </c>
       <c r="L129" s="4" t="n">
-        <v>0.51</v>
+        <v>1.16</v>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
@@ -9623,14 +9675,14 @@
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 15:15 (Active)</t>
+          <t>2026-10-30 15:15 (Active)</t>
         </is>
       </c>
       <c r="K130" s="2" t="n">
-        <v>1858.2</v>
+        <v>1864.6</v>
       </c>
       <c r="L130" s="4" t="n">
-        <v>2.18</v>
+        <v>2.53</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
@@ -9641,49 +9693,49 @@
     <row r="131" ht="18" customHeight="1">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>TMPV</t>
+          <t>HAVELLS</t>
         </is>
       </c>
       <c r="B131" s="2" t="n">
-        <v>259.35</v>
+        <v>1002.8</v>
       </c>
       <c r="C131" s="3" t="n">
-        <v>259.3</v>
+        <v>999.7</v>
       </c>
       <c r="D131" s="4" t="n">
-        <v>262.35</v>
+        <v>1014.8</v>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>1.16% (3.05)</t>
+          <t>1.49% (15.1)</t>
         </is>
       </c>
       <c r="F131" s="4" t="n">
-        <v>265.4</v>
+        <v>1029.9</v>
       </c>
       <c r="G131" s="4" t="n">
-        <v>268.45</v>
+        <v>1045</v>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
           <t>2026-10-29 09:15</t>
         </is>
       </c>
-      <c r="I131" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+      <c r="I131" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 10:30</t>
+          <t>2026-10-30 15:15 (Active)</t>
         </is>
       </c>
       <c r="K131" s="2" t="n">
-        <v>265.4</v>
-      </c>
-      <c r="L131" s="4" t="n">
-        <v>1.16</v>
+        <v>1013.8</v>
+      </c>
+      <c r="L131" s="3" t="n">
+        <v>-0.1</v>
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
@@ -9694,28 +9746,28 @@
     <row r="132" ht="18" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="B132" s="2" t="n">
-        <v>907.4</v>
+        <v>2432.1</v>
       </c>
       <c r="C132" s="3" t="n">
-        <v>900.05</v>
+        <v>2408.2</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>913.05</v>
+        <v>2432.4</v>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>1.42% (13.0)</t>
+          <t>0.99% (24.2)</t>
         </is>
       </c>
       <c r="F132" s="4" t="n">
-        <v>926.05</v>
+        <v>2456.6</v>
       </c>
       <c r="G132" s="4" t="n">
-        <v>939.05</v>
+        <v>2480.8</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -9729,14 +9781,14 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 14:00</t>
+          <t>2026-10-29 09:15</t>
         </is>
       </c>
       <c r="K132" s="2" t="n">
-        <v>939.05</v>
+        <v>2480.8</v>
       </c>
       <c r="L132" s="4" t="n">
-        <v>2.85</v>
+        <v>1.99</v>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
@@ -9747,49 +9799,49 @@
     <row r="133" ht="18" customHeight="1">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B133" s="2" t="n">
-        <v>949.95</v>
+        <v>2462.1</v>
       </c>
       <c r="C133" s="3" t="n">
-        <v>943.5</v>
+        <v>2433.4</v>
       </c>
       <c r="D133" s="4" t="n">
-        <v>958</v>
+        <v>2492.8</v>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>1.51% (14.5)</t>
+          <t>2.38% (59.4)</t>
         </is>
       </c>
       <c r="F133" s="4" t="n">
-        <v>972.5</v>
+        <v>2552.2</v>
       </c>
       <c r="G133" s="4" t="n">
-        <v>987</v>
+        <v>2611.6</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
           <t>2026-10-29 09:15</t>
         </is>
       </c>
-      <c r="I133" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I133" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 15:15 (Active)</t>
+          <t>2026-10-29 14:00</t>
         </is>
       </c>
       <c r="K133" s="2" t="n">
-        <v>971.9</v>
+        <v>2611.6</v>
       </c>
       <c r="L133" s="4" t="n">
-        <v>1.45</v>
+        <v>4.77</v>
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
@@ -9800,49 +9852,49 @@
     <row r="134" ht="18" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>PFC</t>
         </is>
       </c>
       <c r="B134" s="2" t="n">
-        <v>290.65</v>
+        <v>312.75</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>283.7</v>
+        <v>310.5</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>298.2</v>
+        <v>315.4</v>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>4.86% (14.5)</t>
+          <t>1.55% (4.9)</t>
         </is>
       </c>
       <c r="F134" s="4" t="n">
-        <v>312.7</v>
+        <v>320.3</v>
       </c>
       <c r="G134" s="4" t="n">
-        <v>327.2</v>
+        <v>325.2</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
           <t>2026-10-29 09:15</t>
         </is>
       </c>
-      <c r="I134" s="6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="I134" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 15:15 (Active)</t>
+          <t>2026-10-29 09:15</t>
         </is>
       </c>
       <c r="K134" s="2" t="n">
-        <v>296.15</v>
-      </c>
-      <c r="L134" s="3" t="n">
-        <v>-0.6899999999999999</v>
+        <v>320.3</v>
+      </c>
+      <c r="L134" s="4" t="n">
+        <v>1.55</v>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
@@ -9853,28 +9905,28 @@
     <row r="135" ht="18" customHeight="1">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B135" s="2" t="n">
-        <v>312.75</v>
+        <v>254.8</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>310.5</v>
+        <v>252.85</v>
       </c>
       <c r="D135" s="4" t="n">
-        <v>315.4</v>
+        <v>255.9</v>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>1.55% (4.9)</t>
+          <t>1.19% (3.05)</t>
         </is>
       </c>
       <c r="F135" s="4" t="n">
-        <v>320.3</v>
+        <v>258.95</v>
       </c>
       <c r="G135" s="4" t="n">
-        <v>325.2</v>
+        <v>262</v>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
@@ -9883,19 +9935,19 @@
       </c>
       <c r="I135" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 09:15</t>
+          <t>2026-10-29 10:00</t>
         </is>
       </c>
       <c r="K135" s="2" t="n">
-        <v>320.3</v>
+        <v>262</v>
       </c>
       <c r="L135" s="4" t="n">
-        <v>1.55</v>
+        <v>2.38</v>
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
@@ -9906,28 +9958,28 @@
     <row r="136" ht="18" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B136" s="2" t="n">
-        <v>254.8</v>
+        <v>4515</v>
       </c>
       <c r="C136" s="3" t="n">
-        <v>252.85</v>
+        <v>4500</v>
       </c>
       <c r="D136" s="4" t="n">
-        <v>255.9</v>
+        <v>4564</v>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>1.19% (3.05)</t>
+          <t>1.4% (64.0)</t>
         </is>
       </c>
       <c r="F136" s="4" t="n">
-        <v>258.95</v>
+        <v>4628</v>
       </c>
       <c r="G136" s="4" t="n">
-        <v>262</v>
+        <v>4692</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -9941,14 +9993,14 @@
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 10:00</t>
+          <t>2026-10-29 14:45</t>
         </is>
       </c>
       <c r="K136" s="2" t="n">
-        <v>262</v>
+        <v>4692</v>
       </c>
       <c r="L136" s="4" t="n">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
@@ -9959,28 +10011,28 @@
     <row r="137" ht="18" customHeight="1">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>IRFC</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="B137" s="2" t="n">
-        <v>73.76000000000001</v>
+        <v>907.4</v>
       </c>
       <c r="C137" s="3" t="n">
-        <v>73.19</v>
+        <v>900.05</v>
       </c>
       <c r="D137" s="4" t="n">
-        <v>74.43000000000001</v>
+        <v>913.05</v>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>1.67% (1.24)</t>
+          <t>1.42% (13.0)</t>
         </is>
       </c>
       <c r="F137" s="4" t="n">
-        <v>75.67</v>
+        <v>926.05</v>
       </c>
       <c r="G137" s="4" t="n">
-        <v>76.91</v>
+        <v>939.05</v>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
@@ -9989,19 +10041,19 @@
       </c>
       <c r="I137" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+          <t>TARGET 1:2 HIT</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 14:15</t>
+          <t>2026-10-29 14:00</t>
         </is>
       </c>
       <c r="K137" s="2" t="n">
-        <v>75.67</v>
+        <v>939.05</v>
       </c>
       <c r="L137" s="4" t="n">
-        <v>1.67</v>
+        <v>2.85</v>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
@@ -10012,28 +10064,28 @@
     <row r="138" ht="18" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>IRFC</t>
         </is>
       </c>
       <c r="B138" s="2" t="n">
-        <v>4515</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="C138" s="3" t="n">
-        <v>4500</v>
+        <v>73.19</v>
       </c>
       <c r="D138" s="4" t="n">
-        <v>4564</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>1.4% (64.0)</t>
+          <t>1.67% (1.24)</t>
         </is>
       </c>
       <c r="F138" s="4" t="n">
-        <v>4628</v>
+        <v>75.67</v>
       </c>
       <c r="G138" s="4" t="n">
-        <v>4692</v>
+        <v>76.91</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -10042,19 +10094,19 @@
       </c>
       <c r="I138" s="5" t="inlineStr">
         <is>
-          <t>TARGET 1:2 HIT</t>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 14:45</t>
+          <t>2026-10-29 14:15</t>
         </is>
       </c>
       <c r="K138" s="2" t="n">
-        <v>4692</v>
+        <v>75.67</v>
       </c>
       <c r="L138" s="4" t="n">
-        <v>2.8</v>
+        <v>1.67</v>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
@@ -10065,49 +10117,49 @@
     <row r="139" ht="18" customHeight="1">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="B139" s="2" t="n">
-        <v>2462.1</v>
+        <v>290.65</v>
       </c>
       <c r="C139" s="3" t="n">
-        <v>2433.4</v>
+        <v>283.7</v>
       </c>
       <c r="D139" s="4" t="n">
-        <v>2492.8</v>
+        <v>298.2</v>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>2.38% (59.4)</t>
+          <t>4.86% (14.5)</t>
         </is>
       </c>
       <c r="F139" s="4" t="n">
-        <v>2552.2</v>
+        <v>312.7</v>
       </c>
       <c r="G139" s="4" t="n">
-        <v>2611.6</v>
+        <v>327.2</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
           <t>2026-10-29 09:15</t>
         </is>
       </c>
-      <c r="I139" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I139" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 14:00</t>
+          <t>2026-10-29 15:15 (Active)</t>
         </is>
       </c>
       <c r="K139" s="2" t="n">
-        <v>2611.6</v>
-      </c>
-      <c r="L139" s="4" t="n">
-        <v>4.77</v>
+        <v>296.15</v>
+      </c>
+      <c r="L139" s="3" t="n">
+        <v>-0.6899999999999999</v>
       </c>
       <c r="M139" s="2" t="inlineStr">
         <is>
@@ -10118,49 +10170,49 @@
     <row r="140" ht="18" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="B140" s="2" t="n">
-        <v>2432.1</v>
+        <v>949.95</v>
       </c>
       <c r="C140" s="3" t="n">
-        <v>2408.2</v>
+        <v>943.5</v>
       </c>
       <c r="D140" s="4" t="n">
-        <v>2432.4</v>
+        <v>958</v>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>0.99% (24.2)</t>
+          <t>1.51% (14.5)</t>
         </is>
       </c>
       <c r="F140" s="4" t="n">
-        <v>2456.6</v>
+        <v>972.5</v>
       </c>
       <c r="G140" s="4" t="n">
-        <v>2480.8</v>
+        <v>987</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
           <t>2026-10-29 09:15</t>
         </is>
       </c>
-      <c r="I140" s="5" t="inlineStr">
-        <is>
-          <t>TARGET 1:2 HIT</t>
+      <c r="I140" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 09:15</t>
+          <t>2026-10-30 15:15 (Active)</t>
         </is>
       </c>
       <c r="K140" s="2" t="n">
-        <v>2480.8</v>
+        <v>961.85</v>
       </c>
       <c r="L140" s="4" t="n">
-        <v>1.99</v>
+        <v>0.4</v>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
@@ -10216,6 +10268,324 @@
         <v>-1.06</v>
       </c>
       <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="18" customHeight="1">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="n">
+        <v>2260</v>
+      </c>
+      <c r="C142" s="3" t="n">
+        <v>2220</v>
+      </c>
+      <c r="D142" s="4" t="n">
+        <v>2282.3</v>
+      </c>
+      <c r="E142" s="3" t="inlineStr">
+        <is>
+          <t>2.73% (62.3)</t>
+        </is>
+      </c>
+      <c r="F142" s="4" t="n">
+        <v>2344.6</v>
+      </c>
+      <c r="G142" s="4" t="n">
+        <v>2406.9</v>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 09:15</t>
+        </is>
+      </c>
+      <c r="I142" s="5" t="inlineStr">
+        <is>
+          <t>TARGET 1:1 HIT (Active for 1:2)</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 13:45</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="n">
+        <v>2344.6</v>
+      </c>
+      <c r="L142" s="4" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="18" customHeight="1">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="n">
+        <v>1375.1</v>
+      </c>
+      <c r="C143" s="3" t="n">
+        <v>1361.4</v>
+      </c>
+      <c r="D143" s="4" t="n">
+        <v>1387.9</v>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>1.91% (26.5)</t>
+        </is>
+      </c>
+      <c r="F143" s="4" t="n">
+        <v>1414.4</v>
+      </c>
+      <c r="G143" s="4" t="n">
+        <v>1440.9</v>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 09:15</t>
+        </is>
+      </c>
+      <c r="I143" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="n">
+        <v>1398</v>
+      </c>
+      <c r="L143" s="4" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="18" customHeight="1">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>LTM</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="n">
+        <v>4100</v>
+      </c>
+      <c r="C144" s="3" t="n">
+        <v>3930.5</v>
+      </c>
+      <c r="D144" s="4" t="n">
+        <v>4125</v>
+      </c>
+      <c r="E144" s="3" t="inlineStr">
+        <is>
+          <t>4.72% (194.5)</t>
+        </is>
+      </c>
+      <c r="F144" s="4" t="n">
+        <v>4319.5</v>
+      </c>
+      <c r="G144" s="4" t="n">
+        <v>4514</v>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 09:15</t>
+        </is>
+      </c>
+      <c r="I144" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="n">
+        <v>4233.5</v>
+      </c>
+      <c r="L144" s="4" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="18" customHeight="1">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="n">
+        <v>1156.2</v>
+      </c>
+      <c r="C145" s="3" t="n">
+        <v>1148</v>
+      </c>
+      <c r="D145" s="4" t="n">
+        <v>1180.5</v>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>2.75% (32.5)</t>
+        </is>
+      </c>
+      <c r="F145" s="4" t="n">
+        <v>1213</v>
+      </c>
+      <c r="G145" s="4" t="n">
+        <v>1245.5</v>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 09:15</t>
+        </is>
+      </c>
+      <c r="I145" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="n">
+        <v>1167</v>
+      </c>
+      <c r="L145" s="3" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="18" customHeight="1">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="n">
+        <v>390.65</v>
+      </c>
+      <c r="C146" s="3" t="n">
+        <v>388.7</v>
+      </c>
+      <c r="D146" s="4" t="n">
+        <v>396.7</v>
+      </c>
+      <c r="E146" s="3" t="inlineStr">
+        <is>
+          <t>2.02% (8.0)</t>
+        </is>
+      </c>
+      <c r="F146" s="4" t="n">
+        <v>404.7</v>
+      </c>
+      <c r="G146" s="4" t="n">
+        <v>412.7</v>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 09:15</t>
+        </is>
+      </c>
+      <c r="I146" s="7" t="inlineStr">
+        <is>
+          <t>SL HIT</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 09:15</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="n">
+        <v>388.7</v>
+      </c>
+      <c r="L146" s="3" t="n">
+        <v>-2.02</v>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>(26-10-2026 to 01-11-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="18" customHeight="1">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="n">
+        <v>1738.33</v>
+      </c>
+      <c r="C147" s="3" t="n">
+        <v>1734.9</v>
+      </c>
+      <c r="D147" s="4" t="n">
+        <v>1811.4</v>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>4.22% (76.5)</t>
+        </is>
+      </c>
+      <c r="F147" s="4" t="n">
+        <v>1887.9</v>
+      </c>
+      <c r="G147" s="4" t="n">
+        <v>1964.4</v>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 12:00</t>
+        </is>
+      </c>
+      <c r="I147" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 15:15 (Active)</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="n">
+        <v>1790.8</v>
+      </c>
+      <c r="L147" s="3" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="M147" s="2" t="inlineStr">
         <is>
           <t>(26-10-2026 to 01-11-2026)</t>
         </is>
